--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,77 +478,77 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PorJulieth Cicua Caballero</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -575,29 +575,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -666,25 +666,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PorDaniella Mazo González</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -694,19 +698,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PorJhon Bernal</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -726,47 +726,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorJhon Bernal</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PorJimmy Nomesqui Rivera</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -776,29 +780,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>PorJuan Sánchez Romero</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -823,29 +823,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -855,74 +855,106 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorDahana Ospina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Infobae</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,24 +483,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -510,77 +510,77 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PorJulieth Cicua Caballero</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -607,29 +607,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -698,25 +698,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PorDaniella Mazo González</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -726,19 +730,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PorJhon Bernal</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,30 +775,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PorJhon Bernal</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -808,29 +812,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PorJuan Sánchez Romero</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -855,29 +855,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -887,74 +887,106 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorDahana Ospina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,24 +483,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -510,29 +510,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -542,126 +542,126 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PorSantiago Cifuentes Quintero</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
+          <t>PorJulieth Cicua Caballero</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -671,44 +671,44 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,25 +730,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PorGabriela Cicero</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -758,29 +762,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -790,57 +794,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>PorJhon Bernal</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PorJhon Bernal</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -850,17 +854,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PorJuan Sánchez Romero</t>
+          <t>PorJimmy Nomesqui Rivera</t>
         </is>
       </c>
     </row>
@@ -872,39 +876,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -919,74 +919,138 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PorDahana Ospina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -720,7 +720,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,19 +730,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PorGabriela Cicero</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -784,7 +780,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,15 +790,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PorGabriela Cicero</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,17 +478,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -547,24 +547,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -579,24 +579,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,77 +606,77 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PorJulieth Cicua Caballero</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -703,42 +703,46 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -758,17 +762,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -790,29 +794,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -822,19 +826,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PorJhon Bernal</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,30 +871,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PorJhon Bernal</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -904,29 +908,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PorJuan Sánchez Romero</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -951,29 +951,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -983,74 +983,106 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorDahana Ospina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,81 +463,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PorPaula Naranjo</t>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,24 +543,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PorFrederic Dumoulin</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -574,29 +566,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -611,24 +603,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -638,62 +630,66 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PorDaniella Mazo González</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -703,148 +699,148 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>PorJulieth Cicua Caballero</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -859,24 +855,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PorJimmy Nomesqui Rivera</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -886,57 +878,61 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PorGabriela Cicero</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -946,34 +942,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PorJuan Sánchez Romero</t>
+          <t>PorJimmy Nomesqui Rivera</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -983,106 +979,198 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJhon Bernal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>PorDahana Ospina</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Diario ADN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PorDahana Ospina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,49 +463,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,7 +511,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -523,17 +519,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,57 +539,57 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PorPaula Naranjo</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,56 +599,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -662,29 +654,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -694,29 +686,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -726,62 +718,66 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PorFrederic Dumoulin</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -791,61 +787,57 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>PorJulieth Cicua Caballero</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -855,57 +847,61 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -915,24 +911,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -942,29 +938,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,39 +975,39 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1019,12 +1015,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1039,138 +1035,230 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PorJuan Sánchez Romero</t>
+          <t>PorJhon Bernal</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJimmy Nomesqui Rivera</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PorDahana Ospina</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Diario ADN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PorDahana Ospina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -524,44 +524,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -571,10 +567,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -599,14 +599,10 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -616,12 +612,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -631,52 +627,52 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PorPaula Naranjo</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -691,12 +687,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
@@ -708,7 +704,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -718,29 +714,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -755,24 +751,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -787,24 +783,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -814,77 +810,77 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PorJulieth Cicua Caballero</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
@@ -896,7 +892,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -911,44 +907,44 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1011,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1030,17 +1026,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1048,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1062,47 +1058,51 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorJhon Bernal</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PorJimmy Nomesqui Rivera</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1112,29 +1112,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>PorJuan Sánchez Romero</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1144,12 +1140,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1159,29 +1155,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1191,74 +1187,106 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorDahana Ospina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,40 +463,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -506,12 +510,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -579,17 +583,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -599,7 +603,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -612,12 +616,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -627,14 +631,10 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -659,52 +659,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PorPaula Naranjo</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -746,29 +746,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -783,24 +783,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -815,24 +815,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -842,77 +842,77 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PorJulieth Cicua Caballero</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -998,15 +998,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PorGabriela Cicero</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1016,7 +1020,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1026,29 +1030,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1090,47 +1090,51 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorJhon Bernal</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PorJimmy Nomesqui Rivera</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1140,29 +1144,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PorJuan Sánchez Romero</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1187,29 +1187,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1219,74 +1219,106 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorDahana Ospina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,122 +463,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+          <t>PorJhoan Pardo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>1Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/masacre-riohacha-ataque-sicarios-deja-tres-muertos-hay-dura-hipotesis-PP5023694A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,12 +592,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,35 +607,39 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -639,17 +647,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -659,14 +667,10 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -699,76 +703,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PorPaula Naranjo</t>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -778,29 +778,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -810,29 +810,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -847,24 +847,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -874,126 +874,126 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PorSantiago Cifuentes Quintero</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
+          <t>PorJulieth Cicua Caballero</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1003,42 +1003,46 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1048,7 +1052,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1058,29 +1062,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1090,29 +1090,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1122,57 +1122,61 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PorJhon Bernal</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1182,17 +1186,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PorJuan Sánchez Romero</t>
+          <t>PorJimmy Nomesqui Rivera</t>
         </is>
       </c>
     </row>
@@ -1204,39 +1208,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1251,74 +1251,138 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PorDahana Ospina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,32 +463,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://www.pulzo.com/nacion/bogota/muertos-bogota-hoy-menor-edad-fue-asesinado-por-no-dejarse-robar-celular-PP5030714</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PorJhoan Pardo</t>
+          <t>Menor de edad fue asesinado en Bogotá, tras no dejarse robar el celular; recién salía de su casa</t>
         </is>
       </c>
     </row>
@@ -527,94 +527,94 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+          <t>PorJhoan Pardo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -624,25 +624,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -652,7 +656,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -662,12 +666,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -675,17 +679,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -708,12 +712,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -723,14 +727,10 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -755,52 +755,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>PorPaula Naranjo</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -842,29 +842,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -879,24 +879,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -911,24 +911,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -938,77 +938,77 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PorJulieth Cicua Caballero</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
@@ -1047,30 +1047,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/vida</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1080,7 +1084,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1090,19 +1094,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1186,47 +1186,51 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorJhon Bernal</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PorJimmy Nomesqui Rivera</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1236,29 +1240,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PorJuan Sánchez Romero</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1283,29 +1283,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1315,74 +1315,106 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorDahana Ospina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,24 +483,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/muertos-bogota-hoy-menor-edad-fue-asesinado-por-no-dejarse-robar-celular-PP5030714</t>
+          <t>https://www.pulzo.com/nacion/bogota/cuantos-colegios-han-cerrado-bogota-varios-eran-pupys-con-buenos-icfes-PP5032950</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Menor de edad fue asesinado en Bogotá, tras no dejarse robar el celular; recién salía de su casa</t>
+          <t>Colegios más 'puppys' de Bogotá que han cerrado: fueron 'top' en Icfes y con estudiantes famosos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+          <t>1Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -515,88 +515,88 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/masacre-riohacha-ataque-sicarios-deja-tres-muertos-hay-dura-hipotesis-PP5023694A</t>
+          <t>https://www.pulzo.com/nacion/cuantos-colegios-han-cerrado-colombia-1-cada-5-no-logra-50-ocupacion-PP5031212</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+          <t>Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://www.pulzo.com/nacion/bogota/muertos-bogota-hoy-menor-edad-fue-asesinado-por-no-dejarse-robar-celular-PP5030714</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PorJhoan Pardo</t>
+          <t>Menor de edad fue asesinado en Bogotá, tras no dejarse robar el celular; recién salía de su casa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>1Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
+          <t>https://www.pulzo.com/nacion/masacre-riohacha-ataque-sicarios-deja-tres-muertos-hay-dura-hipotesis-PP5023694A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+          <t>Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,30 +606,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PorJhoan Pardo</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -639,24 +643,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -671,7 +675,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -684,12 +688,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -699,35 +703,39 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -735,17 +743,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -755,14 +763,10 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -787,7 +791,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -795,76 +799,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PorPaula Naranjo</t>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -874,29 +874,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -906,29 +906,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -943,24 +943,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -970,169 +970,173 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PorSantiago Cifuentes Quintero</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
+          <t>PorJulieth Cicua Caballero</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/vida</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1148,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1154,29 +1158,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PorGabriela Cicero</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1186,29 +1186,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1218,57 +1218,61 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PorJhon Bernal</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1278,17 +1282,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PorJuan Sánchez Romero</t>
+          <t>PorJimmy Nomesqui Rivera</t>
         </is>
       </c>
     </row>
@@ -1300,39 +1304,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1347,74 +1347,138 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PorDahana Ospina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,29 +478,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/cuantos-colegios-han-cerrado-bogota-varios-eran-pupys-con-buenos-icfes-PP5032950</t>
+          <t>https://www.pulzo.com/nacion/bogota/veterinario-zulma-guzman-pago-domiciliario-que-envio-frambuesas-PP5033639A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Colegios más 'puppys' de Bogotá que han cerrado: fueron 'top' en Icfes y con estudiantes famosos</t>
+          <t>Nuevo implicado en muerte de niñas con talio: veterinario de Zulma Guzmán le pagó a domiciliario</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
+          <t>1Pelea de jóvenes frente a colegio de Bogotá acabó en tragedia: menor murió por herida con arma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -510,29 +510,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/cuantos-colegios-han-cerrado-colombia-1-cada-5-no-logra-50-ocupacion-PP5031212</t>
+          <t>https://www.pulzo.com/nacion/bogota/rina-afuera-colegio-la-candelaria-bogota-dejo-menor-fallecido-PP5033637A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
+          <t>Pelea de jóvenes frente a colegio de Bogotá acabó en tragedia: menor murió por herida con arma</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -542,29 +542,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/muertos-bogota-hoy-menor-edad-fue-asesinado-por-no-dejarse-robar-celular-PP5030714</t>
+          <t>https://www.pulzo.com/nacion/cuantos-colegios-han-cerrado-colombia-1-cada-5-no-logra-50-ocupacion-PP5031212</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Menor de edad fue asesinado en Bogotá, tras no dejarse robar el celular; recién salía de su casa</t>
+          <t>Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -574,126 +574,130 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/masacre-riohacha-ataque-sicarios-deja-tres-muertos-hay-dura-hipotesis-PP5023694A</t>
+          <t>https://www.pulzo.com/nacion/bogota/cuantos-colegios-han-cerrado-bogota-varios-eran-pupys-con-buenos-icfes-PP5032950</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+          <t>Colegios más 'puppys' de Bogotá que han cerrado: fueron 'top' en Icfes y con estudiantes famosos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://www.pulzo.com/nacion/bogota/muertos-bogota-hoy-menor-edad-fue-asesinado-por-no-dejarse-robar-celular-PP5030714</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PorJhoan Pardo</t>
+          <t>Menor de edad fue asesinado en Bogotá, tras no dejarse robar el celular; recién salía de su casa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+          <t>PorJhoan Pardo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>1Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/masacre-riohacha-ataque-sicarios-deja-tres-muertos-hay-dura-hipotesis-PP5023694A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -703,24 +707,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -735,7 +739,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -748,12 +752,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -763,35 +767,39 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -799,17 +807,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -819,14 +827,10 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -851,7 +855,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -859,76 +863,72 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PorPaula Naranjo</t>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PorDaniella Mazo González</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -938,29 +938,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -970,29 +970,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1007,24 +1007,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1034,169 +1034,173 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PorSantiago Cifuentes Quintero</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
+          <t>PorJulieth Cicua Caballero</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/vida</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1212,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1218,29 +1222,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>PorGabriela Cicero</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PorJhon Bernal</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1282,57 +1282,61 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PorJhon Bernal</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1342,17 +1346,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PorJuan Sánchez Romero</t>
+          <t>PorJimmy Nomesqui Rivera</t>
         </is>
       </c>
     </row>
@@ -1364,39 +1368,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1411,74 +1411,138 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PorDahana Ospina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1222,15 +1222,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PorDaniella Mazo González</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1240,7 +1244,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1250,17 +1254,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1276,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1282,19 +1286,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>PorGabriela Cicero</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1254,19 +1254,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PorGabriela Cicero</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1276,7 +1272,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1286,15 +1282,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PorDaniella Mazo González</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1222,19 +1222,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>PorGabriela Cicero</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1244,7 +1240,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1254,15 +1250,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PorDaniella Mazo González</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1282,17 +1282,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1222,15 +1222,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PorDaniella Mazo González</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1240,7 +1244,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1250,17 +1254,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorGabriela Cicero</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1276,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1282,19 +1286,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>PorGabriela Cicero</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,17 +463,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,12 +483,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/veterinario-zulma-guzman-pago-domiciliario-que-envio-frambuesas-PP5033639A</t>
+          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nuevo implicado en muerte de niñas con talio: veterinario de Zulma Guzmán le pagó a domiciliario</t>
+          <t>PorLina Muñoz Medina</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/cuantos-colegios-han-cerrado-colombia-1-cada-5-no-logra-50-ocupacion-PP5031212</t>
+          <t>https://www.pulzo.com/nacion/bogota/veterinario-zulma-guzman-pago-domiciliario-que-envio-frambuesas-PP5033639A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
+          <t>Nuevo implicado en muerte de niñas con talio: veterinario de Zulma Guzmán le pagó a domiciliario</t>
         </is>
       </c>
     </row>
@@ -591,12 +591,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,49 +606,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/muertos-bogota-hoy-menor-edad-fue-asesinado-por-no-dejarse-robar-celular-PP5030714</t>
+          <t>https://www.pulzo.com/nacion/cuantos-colegios-han-cerrado-colombia-1-cada-5-no-logra-50-ocupacion-PP5031212</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Menor de edad fue asesinado en Bogotá, tras no dejarse robar el celular; recién salía de su casa</t>
+          <t>Colegios en Colombia no alcanzan ni el 50 % de estudiantes: les tocará hasta regalar los pupitres</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://www.pulzo.com/nacion/bogota/muertos-bogota-hoy-menor-edad-fue-asesinado-por-no-dejarse-robar-celular-PP5030714</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PorJhoan Pardo</t>
+          <t>Menor de edad fue asesinado en Bogotá, tras no dejarse robar el celular; recién salía de su casa</t>
         </is>
       </c>
     </row>
@@ -660,121 +660,121 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/masacre-riohacha-ataque-sicarios-deja-tres-muertos-hay-dura-hipotesis-PP5023694A</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
+          <t>PorJhoan Pardo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>1Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
+          <t>https://www.pulzo.com/nacion/masacre-riohacha-ataque-sicarios-deja-tres-muertos-hay-dura-hipotesis-PP5023694A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+          <t>Masacre en Colombia: ataque de sicarios dejó a tres jóvenes muertos en pleno parque</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -784,25 +784,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/hablo-papa-ninas-envenenadas-con-talio-bogota-PP5011766A</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>“Para mí fue un error”: habló papá de una de las niñas envenenadas con talio</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,7 +816,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -822,12 +826,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -835,17 +839,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -855,7 +859,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -868,12 +872,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -883,14 +887,10 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -915,52 +915,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>https://www.pulzo.com/nacion/intencione-zulma-guzman-daria-giro-caso-ninas-envenenadas-bogota-PP5009034A</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dan versión sobre las verdaderas intenciones de Zulma Guzmán: daría giro a caso de niñas envenenadas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>PorPaula Naranjo</t>
-        </is>
-      </c>
+          <t>https://www.bluradio.com/nacion</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>PorPaula Naranjo</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1002,29 +1002,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PorFrederic Dumoulin</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>La viuda del último sha de Irán dijo que quiere regresar: “La juventud y todo el pueblo iraní serán finalmente libres”</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1039,24 +1039,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://www.infobae.com/america/mundo/2026/01/21/la-viuda-del-ultimo-sha-de-iran-dijo-que-quiere-regresar-la-juventud-y-todo-el-pueblo-irani-seran-finalmente-libres/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PorSantiago Cifuentes Quintero</t>
+          <t>PorFrederic Dumoulin</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1071,24 +1071,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PorJulieth Cicua Caballero</t>
+          <t>PorSantiago Cifuentes Quintero</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1098,77 +1098,77 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PorJulieth Cicua Caballero</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
+          <t>https://www.pulzo.com/nacion/que-trata-cambio-estructural-educacion-colombia-por-giro-pae-PP4995431</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+          <t>Anuncian cambio estructural para educación en Colombia: nueva resolución toca a 550.000 niños</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1195,44 +1195,44 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
+          <t>https://www.diarioadn.co/seccion/vida</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PorDaniella Mazo González</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1254,17 +1254,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PorGabriela Cicero</t>
+          <t>PorDaniella Mazo González</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1286,25 +1286,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PorGabriela Cicero</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1314,19 +1318,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>PorJhon Bernal</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1346,47 +1346,51 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PorJimmy Nomesqui Rivera</t>
+          <t>PorJhon Bernal</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PorJimmy Nomesqui Rivera</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1396,29 +1400,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>PorJuan Sánchez Romero</t>
-        </is>
-      </c>
+          <t>https://www.alertabogota.com/noticias/local</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1443,29 +1443,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+          <t>PorJuan Sánchez Romero</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1475,74 +1475,106 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PorDahana Ospina</t>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+          <t>PorDahana Ospina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Alerta Bogotá</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.alertabogota.com/noticias/local/estudiantes-respiran-con-el-aumento-del-pasaje-de-transmilenio-no-tendran-que-gastarse-lo-del-almuerzo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>El incremento en el pasaje no será una barrera para que los estudiantes continúen asistiendo a clases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Infobae</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Barranquilla</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>PorPaula Naranjo</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="618">
   <si>
     <t>fecha</t>
   </si>
@@ -43,6 +43,24 @@
     <t>resumen</t>
   </si>
   <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
     <t>2026-02-12</t>
   </si>
   <si>
@@ -214,46 +232,121 @@
     <t>2025-12-15</t>
   </si>
   <si>
+    <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
+  </si>
+  <si>
+    <t>Subsidios y endeudamiento juvenil: puntos críticos de la reforma pensional en Colombia - Caracol Radio</t>
+  </si>
+  <si>
+    <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+  </si>
+  <si>
+    <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+  </si>
+  <si>
+    <t>Plan en Bogotá busca convertir a jóvenes habitantes de calle en promotores ambientales - Periodismo Público</t>
+  </si>
+  <si>
+    <t>Jóvenes habitantes de calle serán guardianes de Bogotá: se capacitarán en temas de reciclaje - Bogota.gov.co</t>
+  </si>
+  <si>
+    <t>Alcaldía conecta a estudiantes con universidades y oportunidades de financiación - Alcaldía de Armenia</t>
+  </si>
+  <si>
+    <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
+  </si>
+  <si>
+    <t>En el oriente de Cali tenían a dos adolescentes que serían reclutados por la estructura criminal 'Jacobo Arenas': los iban a llevar al Cauca - ELTIEMPO.COM</t>
+  </si>
+  <si>
+    <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños - Yahoo</t>
+  </si>
+  <si>
+    <t>Elecciones 2026: 70% de los jóvenes en Colombia todavía no saben por quién votar a la Presidencia, según encuesta | El Colombiano - El Colombiano</t>
+  </si>
+  <si>
+    <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños | El Colombiano - El Colombiano</t>
+  </si>
+  <si>
+    <t>Jóvenes en Colombia están eligiendo las carreras universitarias teniendo en cuenta la demanda: conozca cuáles son - Portafolio.co</t>
+  </si>
+  <si>
+    <t>Carreras académicas más elegidas por los jóvenes en Colombia este 2026: tecnología y salud son algunas - ELTIEMPO.COM</t>
+  </si>
+  <si>
+    <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
+  </si>
+  <si>
+    <t>Colegios en Colombia implementarán cátedra obligatoria de protección animal y biodiversidad - Senado.gov.co</t>
+  </si>
+  <si>
+    <t>Estudiantes de Cali pajarearon en el Orquideorama durante la Colombia Birdfair - cali.gov.co</t>
+  </si>
+  <si>
+    <t>¡Batacazo de Juventud en Quito! Eliminó a Universidad Católica y clasificó en la CONMEBOL Libertadores - ESPN Colombia</t>
+  </si>
+  <si>
+    <t>Estadounidense inadmitido en Cartagena por delitos sexuales contra menores de edad - Caracol Radio</t>
+  </si>
+  <si>
+    <t>En el Día de las Manos Rojas, la Defensoría del Pueblo alza la voz contra el reclutamiento de niñas, niños y adolescentes - Defensoría del Pueblo de Colombia</t>
+  </si>
+  <si>
+    <t>Infancias en la guerra: el reclutamiento vuelve a aumentar en Colombia y así es el negocio que hay detrás - CAMBIO Colombia</t>
+  </si>
+  <si>
+    <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
+  </si>
+  <si>
+    <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
+  </si>
+  <si>
+    <t>Colombia: El reclutamiento de niños por grupos armados se cuadruplicó en cinco años | Noticias ONU - UN News</t>
+  </si>
+  <si>
+    <t>Cada dos días es reclutado un menor de edad en Colombia: en 2025, 40 % fueron niñas, dice la Defensoría - ELTIEMPO.COM</t>
+  </si>
+  <si>
     <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
   </si>
   <si>
-    <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
+    <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
+  </si>
+  <si>
+    <t>Enfoque Internacional - Niños soldado en Colombia: 'Tiktok es una red muy usual para el reclutamiento' - RFI</t>
+  </si>
+  <si>
+    <t>Colombia está perdiendo a sus niños en la guerra - EL PAÍS</t>
+  </si>
+  <si>
+    <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
+  </si>
+  <si>
+    <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+  </si>
+  <si>
+    <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
   </si>
   <si>
     <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
   </si>
   <si>
-    <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
-  </si>
-  <si>
-    <t>Enfoque Internacional - Niños soldado en Colombia: 'Tiktok es una red muy usual para el reclutamiento' - RFI</t>
-  </si>
-  <si>
-    <t>Colombia está perdiendo a sus niños en la guerra - EL PAÍS</t>
-  </si>
-  <si>
-    <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
-  </si>
-  <si>
-    <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
-  </si>
-  <si>
-    <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
-  </si>
-  <si>
     <t>¿Le apasiona el aviturismo? Programe su visita a Cali para el Colombia Birdfair, una iniciativa de conservación con foco en la infancia y la juventud - ELTIEMPO.COM</t>
   </si>
   <si>
+    <t>Tres jóvenes indígenas ingresan a la Universidad Nacional - Radio Nacional de Colombia</t>
+  </si>
+  <si>
     <t>Adolescentes colombianos pasan en promedio 2,2 horas al día socializando en internet: Universidad de los Andes - UNIMINUTO Radio</t>
   </si>
   <si>
-    <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
+    <t>¿Quién es Jacques Leveugle? El francés acusado de abusar de 89 niños en 9 países, incluido Colombia - Semana.com</t>
   </si>
   <si>
     <t>Exclusivo: 13,8 millones de niños, niñas y adolescentes en Colombia crecen entre conflicto, migración y crisis climática, según nuevo informe - ELTIEMPO.COM</t>
   </si>
   <si>
-    <t>¿Quién es Jacques Leveugle? El francés acusado de abusar de 89 niños en 9 países, incluido Colombia - Semana.com</t>
+    <t>El uso de redes sociales por grupos armados para reclutar jóvenes crece en Colombia, México y Ucrania - WIRED</t>
   </si>
   <si>
     <t>Contraloría alerta que más de 1 millón 200 mil niños no tienen acceso al PAE en Colombia - ELTIEMPO.COM</t>
@@ -283,16 +376,22 @@
     <t>Solo 13 de cada 100 estudiantes en Colombia alcanza los aprendizajes básicos y la mitad no llega a grado once: Advierten consecuencias 'catastróficas' - ELTIEMPO.COM</t>
   </si>
   <si>
+    <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+  </si>
+  <si>
+    <t>Estas son las universidades bogotanas que más han perdido estudiantes en los últimos 4 años - Portafolio.co</t>
+  </si>
+  <si>
     <t>Tratado START, niños en Colombia y España, Gaza... Las noticias del jueves - UN News</t>
   </si>
   <si>
     <t>Juventud que honra la patria - policia.gov.co</t>
   </si>
   <si>
-    <t>Estas son las universidades bogotanas que más han perdido estudiantes en los últimos 4 años - Portafolio.co</t>
-  </si>
-  <si>
-    <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+    <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
+  </si>
+  <si>
+    <t>“Ahora que estamos un poco más viejos, queremos ser un ejemplo para la juventud”: Camilo Villegas, golfista colombiano - UNIMINUTO Radio</t>
   </si>
   <si>
     <t>Menores de edad en Colombia pueden viajar sin permiso de ambos padres en 2026: en estos casos aplica - Eluniversal.com.co</t>
@@ -301,9 +400,6 @@
     <t>El discurso oficial planteó retos para la juventud y riesgos en la frontera mientras la reorganización de redes criminales se traslada al sur del continente - facebook.com</t>
   </si>
   <si>
-    <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
-  </si>
-  <si>
     <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
   </si>
   <si>
@@ -313,13 +409,16 @@
     <t>Google y Colombia ofrecerán 20 mil becas para jóvenes en inteligencia artificial y ciberseguridad - Radio Nacional de Colombia</t>
   </si>
   <si>
+    <t>¿Cuáles universidades en Colombia ganaron y perdieron más estudiantes en 2025?: aquí el listado - La FM</t>
+  </si>
+  <si>
+    <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+  </si>
+  <si>
     <t>La ley colombiana que permite que un menor de edad salga del país sin la autorización de ambos padres: ¿en qué casos aplica? - ELTIEMPO.COM</t>
   </si>
   <si>
-    <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
-  </si>
-  <si>
-    <t>¿Cuáles universidades en Colombia ganaron y perdieron más estudiantes en 2025?: aquí el listado - La FM</t>
+    <t>'Los jóvenes son apáticos a la política porque no les han cumplido; los invito a quedarse en Colombia'. - Portafolio.co</t>
   </si>
   <si>
     <t>16 colegios y guarderías han cerrado en Medellín desde 2023: caída de nacimientos sería una de las causas | El Colombiano - El Colombiano</t>
@@ -328,27 +427,27 @@
     <t>Los motivos detrás del cierre de 16 colegios en Medellín en los últimos tres años | El Colombiano - El Colombiano</t>
   </si>
   <si>
-    <t>'Los jóvenes son apáticos a la política porque no les han cumplido; los invito a quedarse en Colombia'. - Portafolio.co</t>
-  </si>
-  <si>
     <t>En San Cristóbal se fortalece la participación juvenil con la instalación del Consejo Local de Juventud - Bogota.gov.co</t>
   </si>
   <si>
     <t>¡Anote! Prosperidad Social revela fechas de pagos de Renta Ciudadana, Colombia Mayor, IVA y programas para jóvenes | El Colombiano - El Colombiano</t>
   </si>
   <si>
+    <t>La Fundación Inter Miami CF y Royal Caribbean inspiran a jóvenes talentos en Medellín, Colombia, durante la cuarta Clínica Internacional de Fútbol Juvenil - Inter Miami CF</t>
+  </si>
+  <si>
     <t>UNAD se consolida como la universidad con más estudiantes matriculados en Colombia - Noticias UNAD</t>
   </si>
   <si>
+    <t>Indepaz advierte que cada 48 horas reclutan a un menor de edad en Colombia - Asuntos Legales</t>
+  </si>
+  <si>
+    <t>Alerta nacional: Niñas y adolescentes fueron las principales víctimas de delitos sexuales en 2025 - Publimetro Colombia</t>
+  </si>
+  <si>
     <t>Llega el fin de polémica norma en los colegios: no podrán impedir el ingreso de estudiantes aunque incumpla... - redmas.com.co</t>
   </si>
   <si>
-    <t>Alerta nacional: Niñas y adolescentes fueron las principales víctimas de delitos sexuales en 2025 - Publimetro Colombia</t>
-  </si>
-  <si>
-    <t>Indepaz advierte que cada 48 horas reclutan a un menor de edad en Colombia - Asuntos Legales</t>
-  </si>
-  <si>
     <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
   </si>
   <si>
@@ -364,36 +463,48 @@
     <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
   </si>
   <si>
+    <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+  </si>
+  <si>
+    <t>Fundación Marina Orth celebra 20 años transformando la educación de miles de jóvenes en Colombia - Caracol Radio</t>
+  </si>
+  <si>
     <t>Plataformas digitales de movilidad refuerzan medidas de seguridad para adolescentes - Hora 13 Noticias</t>
   </si>
   <si>
-    <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+    <t>Maestra de español une estudiantes de NC y Colombia - quepasamedia.com</t>
   </si>
   <si>
     <t>🔎 Uribe alerta sobre 1.157 jóvenes asesinados en gobierno Petro. ¿Preocupación real o politización? #Seguridad #Juventud #Colombia - facebook.com</t>
   </si>
   <si>
-    <t>Maestra de español une estudiantes de NC y Colombia - quepasamedia.com</t>
-  </si>
-  <si>
-    <t>Fundación Marina Orth celebra 20 años transformando la educación de miles de jóvenes en Colombia - Caracol Radio</t>
+    <t>En Japón estudiantes colombianos podrán estudiar lengua y cultura de ese país con becas de intercambio del ICETEX y el gobierno del Japón. - icetex.gov.co</t>
   </si>
   <si>
     <t>Inició el calendario escolar 2026 para los estudiantes de Cali establecido en la Resolución No. 4143.0.21.0. 06508 del 31 de octubre de 2025 - cali.gov.co</t>
   </si>
   <si>
+    <t>Estos son los programas de educación superior que la candidata Paloma Valencia propone revivir para los jóvenes en Colombia - ELTIEMPO.COM</t>
+  </si>
+  <si>
     <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
   </si>
   <si>
+    <t>Reconocidos colegios de Colombia no abrieron sus puertas en 2026 tras años de historia: se despiden de estu... - redmas.com.co</t>
+  </si>
+  <si>
     <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
   </si>
   <si>
+    <t>IEEE. Del campo de batalla a la construcción de la paz: el papel de las autoridades en la desmovilización y reinserción de las niñas soldados en la Colombia del futuro - Ministerio de Defensa</t>
+  </si>
+  <si>
+    <t>Ley aprieta a los estudiantes por el uso de celulares en los colegios: profesores podrán revisar el disposi... - redmas.com.co</t>
+  </si>
+  <si>
     <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
   </si>
   <si>
-    <t>Ley aprieta a los estudiantes por el uso de celulares en los colegios: profesores podrán revisar el disposi... - redmas.com.co</t>
-  </si>
-  <si>
     <t>Posesionados 51 consejeros de juventudes en Santa Marta - Caracol Radio</t>
   </si>
   <si>
@@ -406,10 +517,19 @@
     <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
   </si>
   <si>
+    <t>Estados Unidos reclama a Colombia ante ONU el incremento de reclutamiento de menores de edad - El Espectador</t>
+  </si>
+  <si>
+    <t>Estados Unidos hizo llamado de atención a Colombia ante la ONU por aumento de reclutamiento de menores de edad:“Dudas sobre impunidad al terrorismo” - Infobae</t>
+  </si>
+  <si>
     <t>Causas de la crisis colegios privados en Colombia - Radio Nacional de Colombia</t>
   </si>
   <si>
-    <t>Estados Unidos hizo llamado de atención a Colombia ante la ONU por aumento de reclutamiento de menores de edad:“Dudas sobre impunidad al terrorismo” - Infobae</t>
+    <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad - Infobae</t>
+  </si>
+  <si>
+    <t>⚽ Santa Fe propone torneo sub-23 para dar oportunidades a jóvenes y futbolistas sin club. #Fútbol #Juventud #Colombia - Facebook</t>
   </si>
   <si>
     <t>Colombia presentó avances en la protección de la niñez y la adolescencia ante el Comité de los Derechos del Niño - Instituto Colombiano de Bienestar Familiar ICBF</t>
@@ -433,30 +553,33 @@
     <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
   </si>
   <si>
+    <t>Imposición de boinas: jóvenes construyen un futuro sólido al servicio de Colombia - Fuerza Aeroespacial Colombiana</t>
+  </si>
+  <si>
+    <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
+  </si>
+  <si>
+    <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+  </si>
+  <si>
+    <t>Medicina Legal confirma la muerte de cuatro menores de edad por los enfrentamientos entre disidencias en Guaviare - EL PAÍS</t>
+  </si>
+  <si>
     <t>¿Dónde estudian los genios de Colombia? Estos son los únicos colegios del país con calificación AAA+ - Portafolio.co</t>
   </si>
   <si>
+    <t>Se posesionaron los consejeros de juventud electos en el Distrito de Barranquilla - ELHERALDO.CO</t>
+  </si>
+  <si>
     <t>La deserción escolar le cuesta a Colombia $2,8 billones al año: casi el 40% de los estudiantes abandona las aulas - Publimetro Colombia</t>
   </si>
   <si>
-    <t>Se posesionaron los consejeros de juventud electos en el Distrito de Barranquilla - ELHERALDO.CO</t>
+    <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
   </si>
   <si>
     <t>Consejos Locales de Juventud en Bogotá: 21 jóvenes se posesionaron en Tunjuelito - Bogota.gov.co</t>
   </si>
   <si>
-    <t>Imposición de boinas: jóvenes construyen un futuro sólido al servicio de Colombia - Fuerza Aeroespacial Colombiana</t>
-  </si>
-  <si>
-    <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
-  </si>
-  <si>
-    <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
-  </si>
-  <si>
-    <t>Medicina Legal confirma la muerte de cuatro menores de edad por los enfrentamientos entre disidencias en Guaviare - EL PAÍS</t>
-  </si>
-  <si>
     <t>La industria del éxito temprano está dañando a los jóvenes en Colombia - La Silla Vacía</t>
   </si>
   <si>
@@ -469,10 +592,16 @@
     <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
   </si>
   <si>
+    <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
+  </si>
+  <si>
     <t>Menos estudiantes, cierre de colegios y menor fuerza laboral: el efecto dominó que causaría la caída de los nacimientos en Colombia - ELTIEMPO.COM</t>
   </si>
   <si>
-    <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
+    <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+  </si>
+  <si>
+    <t>En los últimos cinco años nivel nacional han cerrado las puertas más de 800 colegios - LaRepublica.co</t>
   </si>
   <si>
     <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
@@ -490,15 +619,18 @@
     <t>Día Internacional de la Educación 2026 celebra el poder de la juventud - UNESCO</t>
   </si>
   <si>
-    <t>En los últimos cinco años nivel nacional han cerrado las puertas más de 800 colegios - LaRepublica.co</t>
-  </si>
-  <si>
-    <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
-  </si>
-  <si>
     <t>Cambió el calendario en colegios en Colombia: esas son las nuevas fechas de vacaciones - La FM</t>
   </si>
   <si>
+    <t>Abierta convocatoria para estudiantes quienes recibirán $2 millones mensuales por ir a la universidad</t>
+  </si>
+  <si>
+    <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+  </si>
+  <si>
+    <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+  </si>
+  <si>
     <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
   </si>
   <si>
@@ -517,16 +649,19 @@
     <t>80 adolescentes vinculadas a Bienestar Familiar reciben formación en salud menstrual - Instituto Colombiano de Bienestar Familiar ICBF</t>
   </si>
   <si>
+    <t>Jóvenes creen en democracia, pero ven barreras para incidir y participar: las claves de nueva encuesta de percepción de Cifras y Conceptos - ELTIEMPO.COM</t>
+  </si>
+  <si>
     <t>Armenia posesionó a los nuevos Consejeros Municipales de Juventud para el periodo 2026–2029 - Alcaldía de Armenia</t>
   </si>
   <si>
-    <t>Jóvenes creen en democracia, pero ven barreras para incidir y participar: las claves de nueva encuesta de percepción de Cifras y Conceptos - ELTIEMPO.COM</t>
-  </si>
-  <si>
-    <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
-  </si>
-  <si>
-    <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+    <t>Así inicia el calendario escolar 2026 - Ministerio de Educación Nacional</t>
+  </si>
+  <si>
+    <t>La crisis de los colegios privados no se detiene: 35 instituciones cerraron en Bogotá para la vigencia 2026, ya van más de 400 en seis años - ELTIEMPO.COM</t>
+  </si>
+  <si>
+    <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
   </si>
   <si>
     <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
@@ -547,51 +682,48 @@
     <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
   </si>
   <si>
-    <t>La crisis de los colegios privados no se detiene: 35 instituciones cerraron en Bogotá para la vigencia 2026, ya van más de 400 en seis años - ELTIEMPO.COM</t>
-  </si>
-  <si>
     <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
   </si>
   <si>
-    <t>Así inicia el calendario escolar 2026 - Ministerio de Educación Nacional</t>
-  </si>
-  <si>
-    <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
-  </si>
-  <si>
     <t>IDIPRON abre inscripciones a talleres gratuitos para niños y jóvenes en Bogotá - City Tv</t>
   </si>
   <si>
+    <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+  </si>
+  <si>
     <t>La lista de útiles escolares que está prohibido pedir en los colegios de Colombia - ELTIEMPO.COM</t>
   </si>
   <si>
-    <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
-  </si>
-  <si>
     <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
   </si>
   <si>
+    <t>PTIES: La apuesta del Gobierno Nacional para llevar educación superior digna a más de 27.000 jóvenes en las regiones más remotas de Colombia - Ministerio de Educación Nacional</t>
+  </si>
+  <si>
     <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
   </si>
   <si>
     <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
   </si>
   <si>
+    <t>Una generación que ora: el encuentro juvenil que revela otra cara de la juventud colombiana - elpais.com.co</t>
+  </si>
+  <si>
     <t>Tumban común norma para entrar a los colegios de Colombia: ley prohíbe que les exijan a sus estudiantes una... - redmas.com.co</t>
   </si>
   <si>
+    <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+  </si>
+  <si>
     <t>Confirmado el calendario escolar 2026 para alumnos y docentes en Colombia: cuándo habrá vacaciones, puentes y - AS Colombia</t>
   </si>
   <si>
-    <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+    <t>Menos ninis, mismas preguntas: ¿Qué hay detrás de la reducción de jóvenes que ni estudian ni trabajan en Colombia? - ELTIEMPO.COM</t>
   </si>
   <si>
     <t>Colombia promueve estrategia de prevención de castigo físico en niños - Prensa Latina</t>
   </si>
   <si>
-    <t>Menos ninis, mismas preguntas: ¿Qué hay detrás de la reducción de jóvenes que ni estudian ni trabajan en Colombia? - ELTIEMPO.COM</t>
-  </si>
-  <si>
     <t>17 son menores de edad y los casos se concentran en Montería y otros 16 municipios, según autoridades de salud - facebook.com</t>
   </si>
   <si>
@@ -604,6 +736,9 @@
     <t>Petro refuerza su apoyo a los estudiantes de las universidades públicas con miras a las elecciones - EL PAÍS</t>
   </si>
   <si>
+    <t>¿Cuándo inician las clases en los colegios distritales de Bogotá este 2026? Fechas y más - Bogota.gov.co</t>
+  </si>
+  <si>
     <t>¿Cuándo entran a clases los colegios públicos y distritales en enero de 2026? - El Espectador</t>
   </si>
   <si>
@@ -631,9 +766,6 @@
     <t>Reputados colegios de Colombia estarán cerrados en 2026: no pudieron sobrevivir a realidad con sus estudian... - redmas.com.co</t>
   </si>
   <si>
-    <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
-  </si>
-  <si>
     <t>Estudiantes de Medicina anunciaron protesta y Gustavo Petro les respondió: habría plantón en 17 ciudades - Infobae</t>
   </si>
   <si>
@@ -649,12 +781,12 @@
     <t>Balance de gestión 2025 evidenció avances en la participación juvenil en Bogotá - Bogota.gov.co</t>
   </si>
   <si>
+    <t>Consejeros de juventud deben ser posesionados antes del 19 de enero - lanacion.com.co</t>
+  </si>
+  <si>
     <t>Accidente de estudiantes del Liceo Antioqueño: bus iba con el 97% de su capacidad, sin cinturones y con fallas graves de seguridad - Infobae</t>
   </si>
   <si>
-    <t>Consejeros de juventud deben ser posesionados antes del 19 de enero - lanacion.com.co</t>
-  </si>
-  <si>
     <t>Criar en la era digital: ¿cómo acompañar a niñas, niños y adolescentes en un mundo lleno de pantallas? - Crónica del Quindio</t>
   </si>
   <si>
@@ -670,6 +802,9 @@
     <t>Ni matemáticas, ni inglés: esta es la nueva asignatura obligatoria en los colegios a partir de 2026 - AS Colombia</t>
   </si>
   <si>
+    <t>Colombia fortalece la respuesta institucional frente a la niñez y adolescencia migrante - Instituto Colombiano de Bienestar Familiar ICBF</t>
+  </si>
+  <si>
     <t>Más de 64.000 estudiantes se matricularon en programas en línea - Noticias UNAD</t>
   </si>
   <si>
@@ -679,34 +814,34 @@
     <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
   </si>
   <si>
-    <t>Colombia fortalece la respuesta institucional frente a la niñez y adolescencia migrante - Instituto Colombiano de Bienestar Familiar ICBF</t>
-  </si>
-  <si>
     <t>Bogotá también abraza en Navidad a jóvenes vulnerables y en riesgo de calle - La FM</t>
   </si>
   <si>
     <t>Bogotá presenta el primer estudio sobre dinámicas de niños y jóvenes en condición de calle - Caracol Radio</t>
   </si>
   <si>
+    <t>Bogotá presenta por primera vez un estudio Georreferenciado de los Contextos de Calle de la Niñez y la Adolescencia - Bogota.gov.co</t>
+  </si>
+  <si>
+    <t>Barranquilla será escenario de la Asamblea Nacional de Juventudes: 2.000 participantes de todo el país - notasdeactualidad.com</t>
+  </si>
+  <si>
+    <t>Colombia conmemora una década de la Resolución 2250 con un diálogo nacional sobre juventudes, paz y seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
+  </si>
+  <si>
+    <t>El mapa de riesgo de la niñez: estudio del Idipron revela la grave situación de los menores en contexto de calle en Bogotá - Semana.com</t>
+  </si>
+  <si>
     <t>Colombia y Alemania se unen para que más estudiantes aprendan alemán en los colegios públicos - Ministerio de Educación Nacional</t>
   </si>
   <si>
-    <t>Bogotá presenta por primera vez un estudio Georreferenciado de los Contextos de Calle de la Niñez y la Adolescencia - Bogota.gov.co</t>
-  </si>
-  <si>
-    <t>Barranquilla será escenario de la Asamblea Nacional de Juventudes: 2.000 participantes de todo el país - notasdeactualidad.com</t>
-  </si>
-  <si>
     <t>Barranquilla será sede de la Asamblea Nacional de Juventudes 2025 desde este viernes - ELHERALDO.CO</t>
   </si>
   <si>
     <t>IDIPRON alerta sobre niños y jóvenes en riesgo de habitar calle en Bogotá - City Tv</t>
   </si>
   <si>
-    <t>El mapa de riesgo de la niñez: estudio del Idipron revela la grave situación de los menores en contexto de calle en Bogotá - Semana.com</t>
-  </si>
-  <si>
-    <t>Colombia conmemora una década de la Resolución 2250 con un diálogo nacional sobre juventudes, paz y seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
+    <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
   </si>
   <si>
     <t>Colegios endurecen las reglas en 2026: Llega el fin de la ley que respaldaba a los estudiantes en este caso - redmas.com.co</t>
@@ -715,9 +850,6 @@
     <t>Ley 30 beneficia a estudiantes, pero ¿soluciona el problema estructural de la educación en Colombia? - WRadio</t>
   </si>
   <si>
-    <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
-  </si>
-  <si>
     <t>Los estudiantes a los que los colegios en Colombia no podrán negar el cupo a pesar de esta situación - AS Colombia</t>
   </si>
   <si>
@@ -727,6 +859,9 @@
     <t>Colombia reporta 185 casos de niños quemados por pólvora, un crecimiento del 9% frente al 2024 - Caracol Radio</t>
   </si>
   <si>
+    <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
+  </si>
+  <si>
     <t>Tragedia en Antioquia: 17 adolescentes mueren al caer micro a un precipicio en Colombia - El Litoral</t>
   </si>
   <si>
@@ -745,45 +880,87 @@
     <t>Jóvenes del Atlántico gritan “¡No más bullyng!” a través del arte - Gobernación del Atlántico</t>
   </si>
   <si>
-    <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
-  </si>
-  <si>
     <t>La chispa que está moviendo a Colombia: jóvenes que ya no sueñan con el futuro, lo construyen - ELTIEMPO.COM</t>
   </si>
   <si>
-    <t>Abierta convocatoria para estudiantes quienes recibirán $2 millones mensuales por ir a la universidad</t>
-  </si>
-  <si>
-    <t>Menores de edad habrían participado en ataques de las disidencias en Buenos Aires, Cauca</t>
+    <t>Diario ADN</t>
+  </si>
+  <si>
+    <t>Caracol Radio</t>
+  </si>
+  <si>
+    <t>El Espectador</t>
+  </si>
+  <si>
+    <t>Periodismo Público</t>
+  </si>
+  <si>
+    <t>Bogota.gov.co</t>
+  </si>
+  <si>
+    <t>Alcaldía de Armenia</t>
   </si>
   <si>
     <t>Infobae</t>
   </si>
   <si>
+    <t>ELTIEMPO.COM</t>
+  </si>
+  <si>
+    <t>Yahoo</t>
+  </si>
+  <si>
+    <t>El Colombiano</t>
+  </si>
+  <si>
+    <t>Portafolio.co</t>
+  </si>
+  <si>
+    <t>bogota.alerta.com.co</t>
+  </si>
+  <si>
+    <t>Senado.gov.co</t>
+  </si>
+  <si>
+    <t>cali.gov.co</t>
+  </si>
+  <si>
+    <t>ESPN Colombia</t>
+  </si>
+  <si>
+    <t>Defensoría del Pueblo de Colombia</t>
+  </si>
+  <si>
+    <t>CAMBIO Colombia</t>
+  </si>
+  <si>
+    <t>Unicef</t>
+  </si>
+  <si>
     <t>Pulzo</t>
   </si>
   <si>
+    <t>UN News</t>
+  </si>
+  <si>
     <t>RFI</t>
   </si>
   <si>
     <t>EL PAÍS</t>
   </si>
   <si>
-    <t>El Espectador</t>
-  </si>
-  <si>
-    <t>ELTIEMPO.COM</t>
+    <t>Radio Nacional de Colombia</t>
   </si>
   <si>
     <t>UNIMINUTO Radio</t>
   </si>
   <si>
-    <t>Unicef</t>
-  </si>
-  <si>
     <t>Semana.com</t>
   </si>
   <si>
+    <t>WIRED</t>
+  </si>
+  <si>
     <t>Fuerza Aeroespacial Colombiana</t>
   </si>
   <si>
@@ -796,21 +973,12 @@
     <t>Universidad Católica De Colombia</t>
   </si>
   <si>
-    <t>Bogota.gov.co</t>
-  </si>
-  <si>
     <t>integracionsocial.gov.co</t>
   </si>
   <si>
-    <t>UN News</t>
-  </si>
-  <si>
     <t>policia.gov.co</t>
   </si>
   <si>
-    <t>Portafolio.co</t>
-  </si>
-  <si>
     <t>Eluniversal.com.co</t>
   </si>
   <si>
@@ -820,37 +988,31 @@
     <t>Noticias Caracol</t>
   </si>
   <si>
-    <t>Radio Nacional de Colombia</t>
-  </si>
-  <si>
-    <t>El Colombiano</t>
+    <t>Inter Miami CF</t>
   </si>
   <si>
     <t>Noticias UNAD</t>
   </si>
   <si>
+    <t>Asuntos Legales</t>
+  </si>
+  <si>
+    <t>Publimetro Colombia</t>
+  </si>
+  <si>
     <t>redmas.com.co</t>
   </si>
   <si>
-    <t>Publimetro Colombia</t>
-  </si>
-  <si>
-    <t>Asuntos Legales</t>
-  </si>
-  <si>
-    <t>Diario ADN</t>
-  </si>
-  <si>
     <t>Hora 13 Noticias</t>
   </si>
   <si>
     <t>quepasamedia.com</t>
   </si>
   <si>
-    <t>Caracol Radio</t>
-  </si>
-  <si>
-    <t>cali.gov.co</t>
+    <t>icetex.gov.co</t>
+  </si>
+  <si>
+    <t>Ministerio de Defensa</t>
   </si>
   <si>
     <t>Blu Radio</t>
@@ -859,6 +1021,9 @@
     <t>Ministerio de Educación Nacional</t>
   </si>
   <si>
+    <t>Facebook</t>
+  </si>
+  <si>
     <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
   </si>
   <si>
@@ -871,21 +1036,18 @@
     <t>La Silla Vacía</t>
   </si>
   <si>
+    <t>LaRepublica.co</t>
+  </si>
+  <si>
     <t>UNESCO</t>
   </si>
   <si>
-    <t>LaRepublica.co</t>
-  </si>
-  <si>
     <t>EL INFORMADOR - Santa Marta, Colombia</t>
   </si>
   <si>
     <t>Colombia.com</t>
   </si>
   <si>
-    <t>Alcaldía de Armenia</t>
-  </si>
-  <si>
     <t>elpais.com.co</t>
   </si>
   <si>
@@ -904,9 +1066,6 @@
     <t>Colexret</t>
   </si>
   <si>
-    <t>bogota.alerta.com.co</t>
-  </si>
-  <si>
     <t>El Nacional</t>
   </si>
   <si>
@@ -937,33 +1096,30 @@
     <t>Gobernación del Atlántico</t>
   </si>
   <si>
-    <t>icetex.gov.co</t>
-  </si>
-  <si>
     <t>gratuito</t>
   </si>
   <si>
     <t>diario pago</t>
   </si>
   <si>
+    <t>Violencia</t>
+  </si>
+  <si>
+    <t>Política pública</t>
+  </si>
+  <si>
+    <t>Educación</t>
+  </si>
+  <si>
+    <t>Otra</t>
+  </si>
+  <si>
     <t>Salud</t>
   </si>
   <si>
-    <t>Educación</t>
-  </si>
-  <si>
     <t>Protección</t>
   </si>
   <si>
-    <t>Otra</t>
-  </si>
-  <si>
-    <t>Violencia</t>
-  </si>
-  <si>
-    <t>Política pública</t>
-  </si>
-  <si>
     <t>Seguridad</t>
   </si>
   <si>
@@ -976,13 +1132,16 @@
     <t>Sin identificar</t>
   </si>
   <si>
+    <t>Colombia</t>
+  </si>
+  <si>
     <t>Bogotá</t>
   </si>
   <si>
     <t>Cali</t>
   </si>
   <si>
-    <t>Colombia</t>
+    <t>Armenia</t>
   </si>
   <si>
     <t>Cartagena</t>
@@ -997,9 +1156,6 @@
     <t>Barranquilla</t>
   </si>
   <si>
-    <t>Armenia</t>
-  </si>
-  <si>
     <t>Montería</t>
   </si>
   <si>
@@ -1009,46 +1165,127 @@
     <t>Sí</t>
   </si>
   <si>
+    <t>https://www.diarioadn.co/seccion/cultura</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQYk9nR0dVZ3JPRXBES2dxRmV2WXZqaFRqWkxOcFlxeWE4Snllb3h1YlpOTTdjRElEc3gtSFFkbWtDeUlCYkM5THo3cDFrcWRXMm5MRzBiWVFtZlFJNVprMC03VDRJcGo4Q1FDanJFa1BGWG5ZWnZQSjFJSk9tNllBc2xXVVpxVW82Z1RKMFZPQVRnT0Z4Z25lVllVTzlwb1BRQXpvYmlfeC1oRlNBbFRhYUl6MG9CRTRwOGNwc3VyVkNYTHpFdXpyU0x6VjBaUk1r0gHQAUFVX3lxTFBiT2dHR1Vnck9FcERLZ3FGZXZZdmpoVGpaTE5wWXF5YThKeWVveHViWk5NN2NESURzeC1IUWRta0N5SUJiQzlMejdwMWtxZFcybkxHMGJZUW1mUUk1WmswLTdUNElwajhDUUNqckVrUEZYblladlBKMUlKT202WUFzbFdVWnFVbzZnVEowVk9BVGdPRnhnbmVWWVVPOXBvUFFBem9iaV94LWhGU0FsVGFhSXowb0JFNHA4Y3BzdXJWQ1hMekV1enJTTHpWMFpSTWs?oc=5</t>
+  </si>
+  <si>
+    <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+  </si>
+  <si>
+    <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNYjhpNDNHdXpiRVI4Uk56Tlk0dlZQbVZUa0RvN1VMTW9ubU1vTDI3Q3R1WW1nUDYyUzRkM0NubGN0dXBvY0xWRVdwaW9qQzQyc3NSLU9FRV91OGh1bnVvanhrcmFpdVl6amdvNnpQamNQMFktX0hPdUl2SkNnbFI3WFNSakhyQVpSOGt5elZGcGc4blNici10bXpmTHM0TlIxNUdBT2x3YkMyb3lvT044aXRNWDg1Z0E?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZTlVbXhUR0VMSmF3NDJXWVlwWmwyYzBISlQ0MVRNSUdOSWQwcThFZWt3eTBJUmpRMVl1YkVDR3NSa0FEWEpqdVJfWnlNcHA4SWhpai05OHo0czdBVF8wTnlLVGRfVEpzeEc4NDhXcGlEaThvcDlHdXJIZ01INDlaN1lad2tubHVWM0Z0ZFlEOGV0dmhESjNmZDJPMFlJY01ETHBNUmhlOWtJZkNaUkRkQnowdHd3Wlp2MlE?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSGNJLWNiT0JsQlpPUmVWSjJDZE82M2pOVGtLNkozcXFjdU5pa1pMaENkbFQ3c3dmSGc2X1dtdy1KM0txRUlaMjNvZEY3T19lNmZmWk1wZllDdWhqelEzd3ludXhRRnlVZG9OU09xLTlyLUUzTWE2LTFGcURsWmVFeWNxc3lLY05hWFZsR1FwTTFGZl9ZeURESE1HTkoxbWhhMVp2TWg3bklENzFsakRkdUlIQXAwT1pUZlVDMTBqMlBYS1JxQ3BzeGZ2VmF6ZU12c24xVw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxPUDNwLXRyY3FHY2JlX0luT0d3UzBjSXpGZFBsRFptUnBFUTZRbVJLWUhWQmpVVzhlc1pVMEMtSjhCR2NvRFNocGtCZkZ3MDFxbEFJci10bmZtdGdFS0R5WGtnMU1lOTJxSXBpSVQtMlRKSGtWaWpmWE0tbzdqNHF2RVpYQ0UwUmYtVlMxMFJmZGpReHZhWm1uYUFKQmtIbjRsS2FUdzFDcFVidlQ1cjBuR0RkUTB1YUVhN0hQNTdELVdQYy1lcDZ5a09YUllmLUVFck1DemFsX2hSOVVjZEZhZm5XY2FWYjFXblNmenZxb0JrUVVvT3pHRW5PUlhKZEVuUlZSSklUMGpmZ0hxX2VZaURuamxFeW_SAZcCQVVfeXFMT1AzcC10cmNxR2NiZV9Jbk9Hd1MwY0l6RmRQbERabVJwRVE2UW1SS1lIVkJqVVc4ZXNaVTBDLUo4Qkdjb0RTaHBrQmZGdzAxcWxBSXItdG5mbXRnRUtEeVhrZzFNZTkycUlwaUlULTJUSkhrVmlqZlhNLW83ajRxdkVaWENFMFJmLVZTMTBSZmRqUXh2YVptbmFBSkJrSG40bEthVHcxQ3BVYnZUNXIwbkdEZFEwdWFFYTdIUDU3RC1XUGMtZXA2eWtPWFJZZi1FRXJNQ3phbF9oUjlVY2RGYWZuV2NhVmIxV25TZnp2cW9Ca1FVb096R0VuT1JYSmRFblJWUkpJVDBqZmdIcV9lWWlEbmpsRXlv?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNaV96T3o5U1J0ZnloNEVVajBYWVktU3BzNFV5Y1ZpbmdOQmhCSE5ONTRneUxtdDJESjZ0SDRfMjNYOUpZTUZjZlF0elAzTzdTMXlndExqMzZRQS1FNUhoRjRUU05SZ1dHR0V4SkJ2bHZzNlphN094aERlTnk5a29LYldYcWVMYW1tYTdsQjN5Y0g?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZlNPMmVNZ0lHTEh6bFpBTjJqUzZXdU11czVXbDBYeTNhS2k5ODRJejhtU2NQRDZqd3p4eFMxOEVLSWl3UUU1RmNicy1ZVnItc2FiWHBnTlJVd3c2SUlUSzAyQVBQYTlZc2VaUUlIOXBtSFp4UDY1TWlfcHdNQjVSVmUzTldUUGxqbzVDY0tsb29mOEo2S3FlNXVWWXpHd2FtM3dYNzN1QjhwUUd4YnN3adIBtgFBVV95cUxPb2Z2OW1VRWVkVU90ZUpaanJ4NklTejBBaUNSQ2MzTERhb1JZZEJHY1lYeUhydmVkelB5cGVDRTliNHVHV1JEc0dlQURNbWJmVElfdUhwMzNhREh5WnQwMkgzVFZqTElNNkUxMzdYYVlhbDZEemhpNmFScHUzM3JVc3ZQOXAxQU1HRXJpU3FxQTNhSFZnb21qZHl4ejJ5a2VNbFNPLVJ6Wk1qeEt6amhzc1Q2aTNUdw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQSDhDeEZJVVh5SGI1Zk1iekZWQnhDbVctZnVUYzhqQ2E1aWJRS1VCeHVkNGw0ZWpPQm1Eci1LcDdFWGZXU181dHk1R29RRC1QeXZuWFNSYXhLUjhubTBBRnQ1T01zV2VpZEw2VHBzYkNFbWVrdFlFNWtKX0p4a0N2dlV2aXBBX29hWlpyVk9jR0lOVzJ1WmIwRW9lTkQ4THBxSkhiNTlZa9IBrAFBVV95cUxNWjh0d2x2QVNiM0Y2WXNZeXYyZm1mUEkxOG9LMjBjcWVhbjVwMjlvdUtLOVNJVk5ZNTR3dkd4RW9GVGMwZ19GUEhPckRrdGVFZVVSN2ZDaWFGbDZUX2d2dDJMQm4zNkZmYkYzbjVEbWJRcTJLaVktR19CN2pYNzkzaTRPdW9OeW5IVzFGWU9fbnpTeWM5ODZ2MHdNa0dXVFM2QXFzQS0wRnRrNXVa?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNTmo1b3RtV2pFUnA5UXRpTUJyOE5NM3VWMkotNkppc0tCMXlyMWI5d3A0T08tcllCMGtvWHoyVWtlbjRnM2ZZV1piaTdabXJWV1ZLS2dXWm4zV2NFb2Z6NnplSXRsV0tjSHMtNWVUU0VfNjN0a3lycjBOTHd2bk5qT1pUQ2dCTWphbzlOX1d1Ylg5bXI2Ml9pQXFSa2lYQjZFRUZDaDlOdlpTRENVZHJ5dkRSOGVIV0ZhdUJIUGxUeGRFVnl1R2fSAcsBQVVfeXFMUHBoR2RJZDlxTW9Jc1VTYk1SR3ViZi1EUmpOenBYLXAzUDhaM3gtaV95T2dwaDZ4cjdJRVhNdjZfSmZWLXFaclBfc1ktWnJGVndfTmE1aFM0M2pFZUcxbDdQdEpOQmEtVThvdmVEd3dSOUNiWlpGaF9oOVNxTUN5UURsZVRDb2w4WUZPZTlPNi03S1V1ZGh2RHZ0ZlFpc0k0R3RXQVlNTkNJbUxNVk9NSnlmUHVmRlE0UEFYN1NzT0NRT0tobGZYcDNkWGM?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNbG9GRW1GYVhUNWlIWDJ0eHdlNHdvenBSeW80MFF6aThCWi0xcUZmN2VlTnoyY3dVdjZaRDJocENhQnRrMGdfa3Y4Z2diS0F2RU9lTXdyUkM4a1pESnB4Qzc5bFJXeEZfYTZfWFRHV0lFVTU2M3daMFpWUk53OU5wR1luNXFoejNYc0xBb2kwZHhqck9obW1DaGtUR1Z5bWdKa2ZGQmFWaGRBNTRITXBpNF84NVBDTGtiZkc3WlJ6bkxSc1RRZklrUUhaaXdGNXFHOU82eDR3M2prcUstMHZQZ0xKSdIB6AFBVV95cUxOb3lzVlp1cU5CN3lTU0F4bm1aVk1SeENCd2JIQzI5aXhaZGJfWUlhWXBpSnQ2NjhGZFlOY2NrbzYwdWdZOVZfVF9vUE5zYVhSaGtPbjd1WVVRNUZBYjlVZkVTZW13ZWZrbld6SjNDN1FtU2M1M2F5REtidFFuTzByV2g0TDBUOFp0Wms1Sm5IV2plTHp4UkpDMjJSMWdaRExXVE5uSmx0VzZXR2VlVDkxTWY0SE1TRVU1QVZLMGV3eUp0andRVm8zOW4zTFdvdWlxd2dldVAtOTVDU0xCVy1TQmQ2SUJtd1Fr?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOblktRDZRdDlQREx0SWFrYjhnWkoxMmY3MHJJcEJCQU9lbDcwUi1wTFAtVTVySlhnbG9LNGtpd2NHZ05VQ1p0cFpqNkdiU05ENWlISEZUQV9aNExDb3NUUHU1MkduSHJ5LUlsUlhYR0FOMkRvVXloSW1PS1RZZzV3T3VUU1EyQWdGMWhmQTF4a1ZXV0ZlRFRvdDVQcVgyN1ZyakZoeEZuZXpGbG53ZzVfdG5oQ01lajJo0gG8AUFVX3lxTE45S1pNZFFOTUdlajl3elgyYkNGZ01TVGxaRjVPMENmQ2Qwek1GQUhGcVNSSURsN01uM1FYSTR4R2J5U29LSVRWbElNc3hOaUo4V09MdG82SnhHWUFMd1hqTU5DWTFtWmJOZEZqUFRjUmtaZUs4YXQyWjdMZjVyS0J6Q1FNbHBfNENodDRGQ3VZNGVwY2RTS1YzekN4UkwtakV4TlFPYzU5WFA3aGJmd01YOHpfQUNiZ21xSTJp?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPdkRscDEzLTMzYnhsa2M2N2JfZ3M4ampEZzM5ZVFDRm9aSHBySC1idWljUS1BbW8yVjlUcmF4YW9NNVA2M0dzblQ3aGo3emV5RTFnc1ZkclFHWF9XVDBubmU2Q0lpQmJCTzFiUTNOMnNIdm90NmJua0RwNlNuZXJ1bDIweU95akZQWmFNcmFfT2sxNG1Qb3BDU3hyQmJsT3hqQVlHZnBGb2RNUnJBS201YzV6SFVRR21IX0U3eHNSZEo3MFNuZmVPakgwZGEzVlFYTGJZcEg0dGtSdFpvMnU3TExoMzIxZw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQV0NTeVBLODFJYjFsQkJVWHdNRXdLc3h4S1VGdlpQaFhZNVZGYnU5SXp4R3ZfbEFReGFxRW15X2dienNBV1l3SlFMSEZqUW81bXZBLUgwQkdIX2RHcTNpOTZSaWZoekdubkVUSHV3OEp2V05hV1VzaGh0SFRmXzctb2JWbHprWmFuRVI1TTRVcmJCRlc0X3dIMk96dXNEaG5HQjN3S1JnYnh0eVVteEZXQ25reWwtY04xREZoby1YSXg1clgyY194bHpLOHNCVk0?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPMmtfdmViQkxLOGhpUFB4eWZyM3ZvM3ROYXBfNEgydVpnbHlQc1A5ZVVXVml2dTk5ZGdtVkhkVmhoOFZOWTRhN0VETnVNZnJNOE1mYTRIdmthTUpTQmxsSVlkS3RZOXk1eU93SGdpc09IZ1dDTVJqQmxpTHZsMVJoRllyTkJaOE9pZW13ZXk0eWoyWTFoX0JZemdiWDBPZXloSTZTNUswTVd4Ni1PUXJwTUpzMExYQU1zV0Z2NzBRNGhfYzczOUpBc3E2RVEtcHdqMjJVLUdzSklSQ0NaRGlrRjBtQUlxZw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxObHNKT2otaW5sc28xYzd6a3JNYWlVUVRNaHpuSFJhVjZVSl9oVzlOSnUybk5BRG9rdkJSUlpuQlZFTEpqU01TS3I2OHZ6YmR6UXREYlZzRGdQYVk3VThUZGVUUVpidGVYLVltNzVlVHkzR0toMTNNMzlobWtXSEU5eVMtQWdleUNzZkowSHZITk5xbVVwOEozT0RNZHZobGhUTEpEd05GWUY3N2NfY0xoQllpTHlCZF8t0gHMAUFVX3lxTE1wR2F2Q19MNDlFY1M4cVFwTDhGMGFJdGZubU9CSmJJZllVYjlyWU1fLUJXYl8wRGgzRjhRNlpDcGk2dWJEbEc2V1VqY3J3d0E1R3l3YllSNkN1d2FGelE2TmN3M3k2aWlwR3A0YzFCTC1YNTV1UzFVX2J3amFwaExsWFpTN2RSZHNfMFp5Z0NENS1tTFQyTHN3Sm9zMGlqWDRITHpyLUdUQlV1bm56UENZRTV1alFFTVZGZERlRE42TzUxdWJpQ25tNVgzbw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOeEM0U1NNTGdPenhCTGZmZ0l6ZkxXdWppZHJXM1FfaGFqUHFRc2JvUDJqUDBwUVdFenh5QWhlbi1JSV85UmNRVE1mcjdxNkNQWVNnSFZBem9MLTdnX2paeFFZZ1N3TjZPZlZjSUdrOEZWRTM1bXF6SVJFdHNCaW0xQzM1ZE1pdFFENXB2OENSRFNTZkd5OXdsYzZpcDg2X3FWaFRDa0NLT2w2Z1ptUXVXalBQSzN5UXFOMktuVWJtS050YzRReGx4YmFuZw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPWTRzcnA4QnE0QS1RSF92WnBRbVRLM3c5cVFRcVlOQ2VhXzRSa1NLalZpNHRNME0zc2Nid3BzeU1Kb0xIdTFMYlZqQ2llVUotWS12bHY3bEtoZEY1M29GM0JWM1BHYXBVZmY0UEN4czNtRHBIQ09uZmYzYmlLQ2IzcV85QXJNbXpvajZ3YWtnX0FHU3pyTjV5d3RTNUJiSW9wODJJTy1jUHV6M241cFRtM3JIdnVIZjZaRjdtNlUzWmF6ZUM2MFVLaGIzMWc0WjNKZldCcmthdm1OWi1Rb1ZCR1NyQTV2M3gxeUFoTHAweWJIMElBQjdIbEthRlZaR2VUTmJ4Zjl4OW0?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOaE5BNl9aTGdKUjlkdW1BaGZOUnNCSTFLYXBRcGdGamVqR2xlazBGZmhjYjBxYUxYa1BfZ2t3NDZpOS14eWRmbFFIWkFfLUMzSVdFQV9oRGNXeUlycl9CMkJjc0R3MVBIcnVtVk5BcERONnJnVFBpckFCQWNKaGlhbFVCUjhyQTlSb24tSElRYWJyQ1FELVdTMlhRQ3BmeDJXMlNKMnRhdm91RjVxMTFOOVpuMkF6SFdQSUs1TFU5LVgxN1JMSWQ3X1piT0lXN3FI?oc=5</t>
+  </si>
+  <si>
+    <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9wSzZjZVpFS1l3NGk2RTY1NlEweXZQcGhjaG9VRm11d0Y4U2xkLVBCYzhoY1o5dmJmQ1g2UE5wR2cxckxPZEowdnpnZkdDT2tyTWRfcmlXYw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQcDdFdmtDc2pySXhNZEtwcTVsTk9ZS1JDSEtHSGl0YXk3dEhNQ1V6dlBmYXZBUTBfNnBqaVR5TUFfNVdSemdFdE1hVDhHVV9TSUhaVnR3d0IzanJIbGhjb1B4aS04djYwWnp6YS1NekYtb1YyWWlkekhEZjV5TmhfbWhHNmswWlpqT1JTTl95NWV5eWd3ajhYTEpiaXJIRldnX0pqT3hRVnRMSEJGQW9OTlpFRWkxRGxESV83QkdCVGx3LUJySVR4TEs1TGFNM0pxVEY2OEdUQ2VSbjh1ckVud1BldVhHdXI0c1h1R0ZvX09YVm53d1HSAfsBQVVfeXFMTTRod3NmNUxMSDhrc29tdzR2RFMyVFpfWmh3b01yNVVRR1ZPQnl6Q0ZZQ3VMc2x6UXhpaHAwVzhQWjdPZ294YnRNMXNVQUdrVnp4VFFIZVowRHdEVm4wR0J4NGpzVjlDWkpBMmU4R0p5UUNTREZOWGlGNDBXS3N4RkJvNDlfQTYzd2FDUEVsUE5WdGF6NU4zVzM1MnVlVDQ4SVIxZDRaTmNZd1RpMWxvelpPUm0xZlBkZDhfanp5WVotbjZxTjJydE45NGRCeTk2c1RzcnZGVUhzakxWRjBNZVMwN2tFUlFQMXVTUWF4SHRFdWs1SUE1dmZWMVk?oc=5</t>
+  </si>
+  <si>
     <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
   </si>
   <si>
-    <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
+    <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPSXVVRUV0NTJIWUpLRjctUXJwTkZ5bnR2clhrc0JQSzVseXZnY0VZSWZoVFRTblJGNFQ4TWxWZ2kxaUxIckxxVTdORGE5ZGdXU0ZsOUVvSWYxWEtobWhNbjB2THg5NGxidFNMcnNFWmNtR251WVZSTHc4ajB5NkZkdFQ4YUpTa0MwVDlHUzV5QWhCUjh3b0xTdnNweFpEb21LT2VUMWJOQWJHT1lQWThRV2Z5a0U2RWtTOHN3R2VMWFNjemMwdUhUdE9RU29NZ2xZSnBzbTluY0pRa1E?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPc0p4UDhDd3FDTi1IQUUwUzRzd3dTTHE4cEZuSUp5cTY5dDRUMFRiSHlEUk5naU1ZZUctWEFGODlhLWowNmNuSkE0eUcxZlI1dzJJaU93N1pUaXFid3RjdkNHeHhJbmpQel9CM3hQaUdXUFBVZ2hlQjR0WnZ6emI3TERNZmF3RC1laFpwWjZzSlp4X1QyUmdvTHVZQmYxempldUHSAbYBQVVfeXFMTVBPN1dRZWxmb3pMMFM2TmdwMmlhTVVqTHVmWDdOdDlqWGUtQmRzODdFYmdVSHlYT295Z0tCSmJhOGlFUFJXVG9pd24yMDRUTUJRR25XZkxYeWc3TUpqNF90d28wdDEwTlRGOHNOaTVqbTNtbmxUUkxtSkdTOGtCajljY29LOTJ3TGMtNU5jZXZ1RnBnRTl4UHRLZ1A5MGFiVUFnQ3h2SzFEV2V1S3dKcW5URmQ0anc?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
+  </si>
+  <si>
+    <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
   </si>
   <si>
     <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
   </si>
   <si>
-    <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPSXVVRUV0NTJIWUpLRjctUXJwTkZ5bnR2clhrc0JQSzVseXZnY0VZSWZoVFRTblJGNFQ4TWxWZ2kxaUxIckxxVTdORGE5ZGdXU0ZsOUVvSWYxWEtobWhNbjB2THg5NGxidFNMcnNFWmNtR251WVZSTHc4ajB5NkZkdFQ4YUpTa0MwVDlHUzV5QWhCUjh3b0xTdnNweFpEb21LT2VUMWJOQWJHT1lQWThRV2Z5a0U2RWtTOHN3R2VMWFNjemMwdUhUdE9RU29NZ2xZSnBzbTluY0pRa1E?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPc0p4UDhDd3FDTi1IQUUwUzRzd3dTTHE4cEZuSUp5cTY5dDRUMFRiSHlEUk5naU1ZZUctWEFGODlhLWowNmNuSkE0eUcxZlI1dzJJaU93N1pUaXFid3RjdkNHeHhJbmpQel9CM3hQaUdXUFBVZ2hlQjR0WnZ6emI3TERNZmF3RC1laFpwWjZzSlp4X1QyUmdvTHVZQmYxempldUHSAbYBQVVfeXFMTVBPN1dRZWxmb3pMMFM2TmdwMmlhTVVqTHVmWDdOdDlqWGUtQmRzODdFYmdVSHlYT295Z0tCSmJhOGlFUFJXVG9pd24yMDRUTUJRR25XZkxYeWc3TUpqNF90d28wdDEwTlRGOHNOaTVqbTNtbmxUUkxtSkdTOGtCajljY29LOTJ3TGMtNU5jZXZ1RnBnRTl4UHRLZ1A5MGFiVUFnQ3h2SzFEV2V1S3dKcW5URmQ0anc?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
-  </si>
-  <si>
-    <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPdHFDVmxhT0NQQkxpakdYUjREMjVIcllPbHZuTFh6OHVDN0hGWDE1YVIwbmFoNW5ESEFELVluZHJSLUg2MVJ1cWpOaEtvcXMyY0Jpb2tVcVYteFBCSXZhQWh4c1dtVjFFVS14d0Z1OWtSY1Ewd0JqNGZlVjRxeGwweF9WLWg5a20tZF94eXBuaGxTVHdxc1Rfa0c3TUxKTXFxMjlVdXY5N3hwUzJGUURfczY5Ulc0bTQ2NFJWZWJ4SXhfZmZhYUl5ekJhRDFObDFNdVZMYVBURVM2ZXNPVEVhMER0UUJYTTRwTUFWMlM0cFN4alNEYm9MbUQ4ZVhoRlNYSUpzSjI3bjdobmNGajdiVUNqMkJjbmxfTFo1XzZn?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNbTQxeVdtTWhaUkVLeXYtdDJuMVVZSnpKWS1RWWRXakNLbDY2ZngwZTAtZE5rOWpXd1g5WmFHajN3enpCRnVxcDdoZnBBbzI0RG5fcWVTVWFnUlAwcGhDdHQ0ZEZ3emN5MFlVMXVYcTBaWHZzNldXd0JYOEROZ1lPYWZBeWpyRE50ZFpHTlZ6RHh3d1lEdWQ2NXJMek1HaTlRY3ZIWHZGb03SAawBQVVfeXFMTkZ2NUNGdldMTWJkb2d4MEI2SDNxSjlXbGlWZ2tucVI4OU0yWWhVWTNYMjBWT3hjZWdNNFFvdDBrLThoYU5wMUhOOXoyMTMzRm15R3NMbmRoSi1PMEZDRF9IcmRpTlhuVDZVbDZtS0ZJX0dQcVhRSFlIdk80MkZKd0RyNFNRWFdBT1JYdkxiVGVORnk5c2F4aUs4VWNiR055NW9rdEFyaVIxNHZTRQ?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOeEVEUlI0ZFJoQ1BYTGdrMWRkekxsZldhWUxQc3dlREt1LVo3djhaU0trUnZlMVlfcl9FdGJDbkRVWndzd3ZnbjJnTURaZnplZ3dQSDZFckN2cG9EWjRWa1ZON1JFZ0Z1WlY4MmZ2b2FsdEFEWjZqZmpnSXdSZVg1Wk9xZEZSb1BCOUVuVDI5QWFsM3dTQUh6VjZDUnBfQlRJNG5ZdHVQUF9fZUpUYlJVTG0tYjJucGdvMFRIZDNXSlRJNGZIWHlaTk13dllWWFhFRWZXaHdVbVZQVmM?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQMWdqbWZUSHduQkx2Y3F4VEJZTkxKS0ZBbExLVHZTc21KbmNoQ2Y3cHNJTWJhWlZ0dWNFalJQcUxIQXNWOTQtc1JCY2VVOTdlaXpESnhGRzdwVmlEODJEOHdDXzY4d0Z6RGpqTHJ3eWR1TVl0MDY0S1Y2VU9GNkVfWUlwX0N2MzBYYmFMX0xWQ0RBeGN4Q1p4LU9UTW9GM3hTb0pwOWRxcWJvNEg0UjVpQw?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNZDJsMDBhWUFjNkxEVUhYU0U5WHFQVXdSbEJLaFVuTGtDSk9HZkRrSGQxVUZ3Z0xOLVVTU3hQUlNYUjFYWFlJb01aTmtHVkFMV1dlQWJEeEVkeEtSOElWSmVKMjBiTklHZ3JYQVhKbGNPTThMcWhMS3ZOSHdUWi1aZkdhekFfVVBFSHdlMFB0U1VjbDd6SVptN1RUc2R2LV95VmE4ZVNpaXlsd0tlb1NVQnN2dnRYdHN5eUQ0aHRzcDg3WmxVVGRUNmkxY3V2Y0NnVU14Tm9VajZhUdIB3wFBVV95cUxOSmJsYkNUNDRZdEItbXNLcWY1SVVZQmJRMjYyOFkzNzNieHlBc2xGSmVPX0pGWkUxbmt0aDJhNVJOWVJGbTJCSkJqa2FNTmJGRG1FWExMWjZTNEFPVDhtQVkwQzZTU3lIYnZZendkX2hLdFlWLVVDN3JGOVBDdVlzeERNRC1OazFtUEUyR0MtVTlUOGRTTUhXRTFVNlo0VXBJZUUtY0ZQNW04cVBVcUxLdmQzTEdmc1hmWW9Hc1Z0VnFRME5kQ3JQSlVERjN5bFRCbzhRSTZLNUpHemoxMDlB?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPdHFDVmxhT0NQQkxpakdYUjREMjVIcllPbHZuTFh6OHVDN0hGWDE1YVIwbmFoNW5ESEFELVluZHJSLUg2MVJ1cWpOaEtvcXMyY0Jpb2tVcVYteFBCSXZhQWh4c1dtVjFFVS14d0Z1OWtSY1Ewd0JqNGZlVjRxeGwweF9WLWg5a20tZF94eXBuaGxTVHdxc1Rfa0c3TUxKTXFxMjlVdXY5N3hwUzJGUURfczY5Ulc0bTQ2NFJWZWJ4SXhfZmZhYUl5ekJhRDFObDFNdVZMYVBURVM2ZXNPVEVhMER0UUJYTTRwTUFWMlM0cFN4alNEYm9MbUQ4ZVhoRlNYSUpzSjI3bjdobmNGajdiVUNqMkJjbmxfTFo1XzZn0gGjAkFVX3lxTE9jQ2hLRkFKNnVWckhPbjNnOHdCN1JIMTVVLUo1a2VQNmxpWWxUbDY5TV96eWZQYWxpcEJ4cUEySFZCS2NLaFFVWGFOT0lrd3ZiYzN0Y1JJcVI3VFFCdnRZcksxR2ljell6anVfOHY1ejRrcE1rdUcwLVRCenVrVVJrazRwNzJFc3ZWV0JFVWNfVm9lRjAyV1plVkIxV3BpMmdURG1iemZhX1hnNkp0UHNDZ3VZOHRLVXJ6UEFKOXVfVTVlR1prMGtOZ2RYN0E3czREcDZxYkwwb2hQZExQVDNVT01RTk9QemhnS1NiaU5ld3FsalNFbWVrUWFxOE11aW9iWWx2ajBPblQ5UDAzZG1DVloxWS1RN0lxOWkxbVg1SEN3NA?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNOTlaVExIaU54TkxnMFIzY3lBUjdvN0dTOVVMc3lvVENfU2VhY2tGTlNFYWdOcnJUdjdYdk9rdWRSOFRueVh4TW92NnVZSkg2TmI1WENFZFVXLTVVaEFDcTdpNWdxdmtiU3dpQ1RhTTg0N0NEakhucUd4bFh4aHoyRGlIaXRUS2d0YmdHZlpRNU95RndEUmFBRVZkTGpBMllkTWZQVVRORzVWb3Y1UHhELUZhVV9JWk5MbnI0eExucHVCdVV5dHJhcl9vVXJRdGM5WVRnR19xbXZXajlJbS1Ja2ZhdFlCOVM3cWJ0N0NBNTVtd9IB9wFBVV95cUxOM0RDc3lsTDZIdlNxaVZxcUxvN0gxRF8xQzc0czJfRUJGZmpmVlFyb2pMVC1fZ0ZNazJMZjdJd1laTDFEcDJubnAyQ05OOXdXSmRrU09vRUZpdFNaT21aOWtoajFTSDlnWkpKVWo4VVVZU1NTLVlvNzRTQXdFZXl1ekNqSmtsU0twWmx1YmQwSV83VkhqZFQ3TW9ILUxBb1Z4SlZWSUhYQWtDTlhJRHhZSmJRaTNzWXJyMDBXZGQydUx0anFQMGZWMmxGSE84ZzVkVmNENHQtdDJfLXlDV09kb0VuOVYzSVdJenVBa1p2Nzkydkw5eEtF?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNZDJsMDBhWUFjNkxEVUhYU0U5WHFQVXdSbEJLaFVuTGtDSk9HZkRrSGQxVUZ3Z0xOLVVTU3hQUlNYUjFYWFlJb01aTmtHVkFMV1dlQWJEeEVkeEtSOElWSmVKMjBiTklHZ3JYQVhKbGNPTThMcWhMS3ZOSHdUWi1aZkdhekFfVVBFSHdlMFB0U1VjbDd6SVptN1RUc2R2LV95VmE4ZVNpaXlsd0tlb1NVQnN2dnRYdHN5eUQ0aHRzcDg3WmxVVGRUNmkxY3V2Y0NnVU14Tm9VajZhUdIB3wFBVV95cUxOSmJsYkNUNDRZdEItbXNLcWY1SVVZQmJRMjYyOFkzNzNieHlBc2xGSmVPX0pGWkUxbmt0aDJhNVJOWVJGbTJCSkJqa2FNTmJGRG1FWExMWjZTNEFPVDhtQVkwQzZTU3lIYnZZendkX2hLdFlWLVVDN3JGOVBDdVlzeERNRC1OazFtUEUyR0MtVTlUOGRTTUhXRTFVNlo0VXBJZUUtY0ZQNW04cVBVcUxLdmQzTEdmc1hmWW9Hc1Z0VnFRME5kQ3JQSlVERjN5bFRCbzhRSTZLNUpHemoxMDlB?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNc0lDNjdNaXRmRDJJcFNCazB3OGpPLTdFS0JjV3FyS1F4dFFuV3RXMTA2S25UOTh0NWt0VE1IV2g2V1R4TDVPWGlmMXB3ZHVTWkhzb1loOWpCd0xUZnFlSFZFeWd5ZmxnQ1pKWFVRdTAwOTlCWWZINjBPMVdrYWxsejBIWl9XVi1UVHp1LXNaRVRMdms4QVZpWGxOSWdfLVBTeWQ5YUR1RmwzRlo0enJOT1ZmN3R1Y3RaX3B1cjlmUGZYckdPTndtQ3hUcw?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQTzdCMmlSTHhPT3dIM29QaWkybFplRjN1T1BuM05SU2VEdUZuY0dPdk5seUhSSmpyQ0VHbnlIV05NaFFoTFMzSUx2QlBZLXVlaC1pSi1nd25QNjh0azk2MWpNMUV0bjhsSzktZmF1MnVsZTRFZnB2YmZ6azc5cU9oVGE4WlU3WXZwZnRwcW85aF9iVEl0dWplT3pCTkczS013Y0IwZHkxTFpRd1RMc1JySTdxX0ZoSjh0TS0tNldtVUxTUXhRc3l2Rm55RWN3VHU0ZkxQSE1XODEyVEhs0gHiAUFVX3lxTFB4RmYtelFvZ3FuNlpTaXhpN1BPcm94ODh3c3U0c0kxUmVRcVlMOFU2MWpUVmtzdUt2VGtDQzB4QmR4Y1h2b2hxc2lNNld1SXhOM2ZqY1piQnJsT19uc3ZzZnVuUEVzRGoxdGQwTkNvdFVSdUljR1BSNnJla1FBSHhNNnZTUTVzX1AyekVranZCWHR0WDZpTnBYNVlxRl9LU0ExazZrdGhFa1hQcEpXSGcxTEJIVmU3SHROODgzaURZQWh5QUxwSjRUcEhLbTlwNlBCVFpVNk12bjc4am4xQnp0dnc?oc=5</t>
@@ -1075,19 +1312,31 @@
     <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQRE5KUVBWM2tVV3FSR0E5OWYzZTdfWm0ybU50TzVFNUNlRkFmazZtVzdiZlVTSXFQMTQzajNpYlduWUtfaXZIRWdUVHRBeHVvM1FzQ1o2cEYzRjZIa1ZiZFU0azlXa2dZaXU0X19EdjR1YTIxRmVEVnpXUmotT1JtMGln?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxNMzJhelJqNkVVMlpLUDNKMjlBazI0c3ZIemxfRE1oRFdFWjh4WWRxbTJScTV4QWF1ZG1ZOHFvWmJ2Si1iUzlOQ3NPUVVaTmV0ZVZSOWxSanhWd1hkSHFlUmYyUnZQaHJFdUZNNDFqZm9GQ1IyeVhfUENReEg3RHNMQlZYd0Q2emw3dXh4ODdIUVozU09lVks4VU90ODhNTjNLVmxNbGlMV0k4WXFNdURHaVpCSjlPUTJOdllnNVJ0VVVPOVN4OEo4djBkamJvSjE1Ny0yMFVNdGRxYU1zTlJEaU1PTTMxbDZkVGxxNWlscnBicEwxN20wX2VmdzRqdE43bUUxdkZuSVZRMG5GZmc?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNNE9BSllXSG53VWU5clFlTjBXanVlUEswSmdVVkxCeDJCS0NtNzQ5cTJPckc3ZDNDXzdHWnZLZnFSakwyV29kTXcxZWxvN1pWdzNMOURXTDd1aHRVM195V0pMaGd3N2xSNWs5MXVwWE5Qa2hoVFN6aHNaRlhNT2RuVFhDSi1GWXc3TkE0V2pzd2RkV3o5TFc1MmJfZ3pCOWtocVR1YmlNdThWVEdsSFZDSnpiQ1N3TVFxYXhOX3l0WUtZWWVOOU5fc3hIdm0wZEhHUGtCWVpReGdtZzd5U1VIWTRYU1g5bVZHSUtjRDJnbk5BeGEwRDBRRkVINDAyQkowcUYzM1ZDZ1dPTms3Yng3Z3ZBQWhGa21VT0pOeDVEU2rSAaYCQVVfeXFMUHlhLVdiMUJtOXNBVldTaVRacEo4V3JtYm9QODhHdlhBY3pfQnlQMW5vbWhYa1hHLS1nVGZ1dHRqSkh1b0VjaEhRcVVSTmlpREdEZ0VOMWE5ZjU2Vk8ySG0tQ19acTZwcHYxelg0NDZmMDI0NFpvTTZvNTFqVTBVb3dYSjhQYjNPSUE1aXN1LThzaHVweW1XRWxYTUN0VFlXV3RuZV9JcXZWeDNwUWtQLVhjMWx5UjdiMXdzTlB3TGw1TjJNbElNX2FYOHdhb1ltWXA4bUY3SmwzelBHSkdVNnpyanl1QzQtbDJYc0JkdElCODFLaUlnemhOWjV1UkhnVFVEVzVaVjlvajFWd0FOOTlob3B5NmZHaWVtR3ZPeDRXVEQxMmxR?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTlRkZkdaSEtLcWdXRDJqS0xGa2ZuMFdISTVSUm5pR2NvWFZaeG9ZQXlNdVFLMmpmbWd0Nzh3cUcwaEtNbUpVdnJhSkdNNk9WSXNYU1dfcHZ4R3FXSG1yY2twX3d2N1ktWHgxN2FrdmgwRVRmTkZhZWVUWDk5SzB4R3ZzaWVJNmZRSDRyY0wyd3ctS2VNUWI5SU9raXItRW5PUElJMDVuTHh3LVdYQlB4ZXJQSHNjVmpmdWtaN0RNRm5ZeXZqd0RxOFdsNjZSYzdxNE95NmFvYWJEd9IB3wFBVV95cUxPa0V1SER3OUR4QlMzUVFScDZPQmlsbXdjOHBuSHlHS2pjZkw3N3l2NE9XNU1xU0gzNkJvNGNGV0oxTVczaTdjWm5jUlAzSjVpMkJEVm9zOFpXQ3NKMDA2aXE3S3pXVU1PYml6NTB1eUR0dEdseTJhNFZLeWxTTWhqOTJNaW5tQ09kTjduLThpX3FKbEFvTnRaY3F4UVhpOW1NYmtNbXFRaTVaVVA1S1pMeTRGRU94VVllcDIyYlVjYU5pemxnUDRsSlVuZnM4NmpmRDE5emw2RVdHdTRMMmZr?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA3d21fTnBoQS1hakduX0ExZXJSUlZzcmlneHN5TFJUQW1WMjI4dU1CWV9vN21QaWNLX0JZcjJ1UElINTFfTXFYbWI0bWxRNkpXUGdMaTZYWQ?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1GT0lYblBCXzFacFBoWjdCTzNrUGxhT25ROVVMc3RhOGUzVk5VdTVHdlU3aC1OcnREYmxuUHE0QlFYcnZLblh2THpaVFRtLUJWRXpudFg2QWxmN1VRVi1pSUVEUXRNUDlJQlZ3MA?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTlRkZkdaSEtLcWdXRDJqS0xGa2ZuMFdISTVSUm5pR2NvWFZaeG9ZQXlNdVFLMmpmbWd0Nzh3cUcwaEtNbUpVdnJhSkdNNk9WSXNYU1dfcHZ4R3FXSG1yY2twX3d2N1ktWHgxN2FrdmgwRVRmTkZhZWVUWDk5SzB4R3ZzaWVJNmZRSDRyY0wyd3ctS2VNUWI5SU9raXItRW5PUElJMDVuTHh3LVdYQlB4ZXJQSHNjVmpmdWtaN0RNRm5ZeXZqd0RxOFdsNjZSYzdxNE95NmFvYWJEd9IB3wFBVV95cUxPa0V1SER3OUR4QlMzUVFScDZPQmlsbXdjOHBuSHlHS2pjZkw3N3l2NE9XNU1xU0gzNkJvNGNGV0oxTVczaTdjWm5jUlAzSjVpMkJEVm9zOFpXQ3NKMDA2aXE3S3pXVU1PYml6NTB1eUR0dEdseTJhNFZLeWxTTWhqOTJNaW5tQ09kTjduLThpX3FKbEFvTnRaY3F4UVhpOW1NYmtNbXFRaTVaVVA1S1pMeTRGRU94VVllcDIyYlVjYU5pemxnUDRsSlVuZnM4NmpmRDE5emw2RVdHdTRMMmZr?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPOFJRNk52Mkx1Q2hFTm5oQV9UUFlLYkVlMjZEanRsN0hnQU9xRTJTR08tQTl2MVYzQTFMWkRuYXJFcG4zbk5iYWE0clBva0dWVXFlMmt5NTQxTUhtamwzazlacC1HdXZjRkRFVW03U3ZNVVdGTEZHY0JHalFaVXJwLXpZRVpIYm1FcWhkUWVyY29Ud1Rzb1NDUG1UczFJdXNJNnh5MkpPbU5WTDFnV3hmcjBTbXpTcndtNnotMmNqNzdEYXJLSEM1cTA3U0F1ZzctQy1tMUhjc28wcU9kT04wc053?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNUkViVng5bVFEQmo3RnFIQXA5dWV6b0czWnJnaC0zRkc2QWx4dUJsZGZ1cXp3R2RfazFVeGdQZUU3Y1dvWUhlQ2o3NlVIaWlMamJNLXNUdlBzeFIyaFJSSVBoZEotTjRiNjRyUFV4Q1FEWFgxWGIyVGtRbUdrQl9mc0dzNXZlejhIelR3WkwwSDFGTzBydll5M1RHZm9YcmFId2NrMVF5eUczbW82bVU4X3p4dTliaTNRcWYwTlI0UG90b2hDUHYyTkhlbGRoelMzVGh3OGhLQnlPanNiOEgxTWlrYklBZw?oc=5</t>
@@ -1096,9 +1345,6 @@
     <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdlNPUVI5dDdwZ3B3eHdpemJIa1VFMnh0STBza3hUb3lzVGxYQS1JRHpya21SSHF3RXdBcjROYUptREtXVlJWdjR6dWNhWDd2akZmVVhpdGJjNHlITnZDeVRlRzFHR2xpcV9adWVXS3huM1R5ZUpOVnlYX1FKd3U4WXc4eXFaVlpQT2kwZHlKOTI0U0QtdlQ1STNBM1RhTkhOMVE3SlJRNHJ3VzB5YXdoNVFyT2RIWGhWY0dnaVcwWFNVVHZ2ekVSVTd0S3Rxc1VVRUNkdmgxUm41X3ZsLW9JVG9QRnR0QQ?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
   </si>
   <si>
@@ -1108,13 +1354,16 @@
     <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNLXpWa2dvSjF2b21RNzQyN2EwdS1tR1FidXFzaEtSWVJ5eDRQWlE0cUJzWmExdWRYcmR3dlo2VXJDV2cwejJoa29JUVhIVEtPcFZjRlp6eHgtZkhsV2JwamkzY3RDREdlZi1BeUlPeGF6d1Zsd2lPS29mQVlrdVk2b2RNMlJVVHcxbENaaUdyRWVCWmdacl9QNTF6X3doWjY5bHliMzJsa3RwazRwWW1kbkNObzJWWUI3eTNYRdIBwAFBVV95cUxNbk1SdEsyOEFxQV91a1RYSm81bUhTdVgxSjdEeG1FVEY1V09pX2hPU29kRnNaMEhwZjB6WnZfSTFfb0tnTWMzdWtLZTlHbVh3emZRckpRblhveE5xVnY5dzRCMzlMZ2dPWmk5cHJHMzNVVzRlTkVtMjd4Znpuall4V2dVUy1EbWNMM1lJdTlrLTVkU1ZNQWdhUER5MGdHbjhXQno0cE44WW1ZdS1md2JaOEc0aFF5c29iUVVFbUw2Z3E?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNeWdma2NDUFpvSzNlS2hSLV9tY2hxeGJ1VXNnTUFxRVJ3M3dkYnFsRU1COGtVdW41Vmt2a05laUJtMmE5WHlLNlBFNUNzMjJxSXRfam5YV0J5cndmT3l6SXNfUjZ2WFdtdWFaMHNLb0JtQk94WFdjVG5zVWJJQ2VQSEowclQzOW9YZ3FwcnZUY1MxZkY1b0hWUlk5ZlNVTFnSAZ8BQVVfeXFMT3JGVXFySEYwOWJwT21FMXp2bkFHR3MwZHFTRDVmTndleFlJOTBjRi1oVzZBejJyejNsMlNNa1NoNnF3TTVnX1BZSjRUOF9ObGs0eW9BNzAwYl9qallvRmpwMmZ4SnByVmotNHhoU0pTY2hIZEZiT3gtcmVWb1ZhdUtWUzRGX2JfVl96Mm1KYk9nTXhEaUE2cmdtdy1fc25n?oc=5</t>
+  </si>
+  <si>
+    <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPdUc1dGVMTXJvN3c2c29yMVA3aHRBVV9sRlZRdmJqM25wUzhpNC1kSzQ4U2VEU0ZfRVY1ZUJjM0JRT282b3dkUVlpVFZNN2lEc21yNUl0Yk1qZXRvNmppdGQzazdGcHI4YTZ0Z2NlX25leFhUSjlCOXNUSnV0azRwS19lUlJtODEwcDJRd0Vic2s2R05idWp4d2ZkWWZqMTlFcmtwUzlwU0tvMHRWcDEzR2REMTdEbXVabm9lVUtQWWRjUy1vazc1SXpWZ1dqOERIbHN3TGhZYm9GajJOSy1ES3NqX2RqYTJCVl9ZZHFFSkJ1WTRmVVhEYnpB0gH_AUFVX3lxTFBUOEp4NTVxaTM4dW9UX215aDV4ak5UY0N4MzVzYjZCTWtmUU5XRWxOMDBlRXZnVTl0NXpFQW5yNlFIRTM3NmU3dXlQNTRoUk1IWnBnMjRuRGxsTExnRTVrR2xkNG93R2s1RXMwdFN0TmtTWG12ZEFWQ3NobWxjMDdtYXZBUE5rZFZvd1NWQlExMWVPVTV6VVlzQmJqclZmX0tzbzg2NGQ0ZFVWelgya3MwcExUTHEtUWl2S09Dd2JHYTNYZ3VnZjVhSm9UbXFtOVdzbTNUdExLekFHekI4XzhzTndGcjYwNWZxeVV1aWkxdEZaa0w4YlIwenV3WVBaYw?oc=5</t>
   </si>
   <si>
-    <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNeWdma2NDUFpvSzNlS2hSLV9tY2hxeGJ1VXNnTUFxRVJ3M3dkYnFsRU1COGtVdW41Vmt2a05laUJtMmE5WHlLNlBFNUNzMjJxSXRfam5YV0J5cndmT3l6SXNfUjZ2WFdtdWFaMHNLb0JtQk94WFdjVG5zVWJJQ2VQSEowclQzOW9YZ3FwcnZUY1MxZkY1b0hWUlk5ZlNVTFnSAZ8BQVVfeXFMT3JGVXFySEYwOWJwT21FMXp2bkFHR3MwZHFTRDVmTndleFlJOTBjRi1oVzZBejJyejNsMlNNa1NoNnF3TTVnX1BZSjRUOF9ObGs0eW9BNzAwYl9qallvRmpwMmZ4SnByVmotNHhoU0pTY2hIZEZiT3gtcmVWb1ZhdUtWUzRGX2JfVl96Mm1KYk9nTXhEaUE2cmdtdy1fc25n?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPTFB4Z1ZGMHU2Q2hKcjVObjFEYV90WnpaU0dIc1hQODNtN05SaC16Nnl3Ny1hNV9VRWxma0tyTzhlNFJ1ZURzMV9JdkhUMnNKQU16ZUEtV3VYQVp4RlduMkpIdXFSY09Pak4wZWEzM0pmS19lZ1dpSVZseFp5X0JuWnZCWFk0VXlaeUtyS19GNGlNOHE0LUEwblJkZnF2dkxnTV9hN3lEcDZhaTZZeXdKS3lOYkxLSFhhRUhsOVFMamRjYzhJSXMwZF9rSHBMSXhmUGUzekhTbGVySWJSNzBjLUQ0djHSAeoBQVVfeXFMTUFTM3Zpb3M1Z2lPdUlVd1llQU5FWmVrSWE5a01jZklSRDJpQkFIZ3VEVXJndkZmQXBVSUVDNGFnSHJrX0lvQS1DcTc5MEYzWEZMZkFrRFFSUTZfeXkySkdOUEdLZnJGdTl2NENNSGxtS3FfZHNhR210UVJxRG5wUkxtTzlnVURPZXdhVmh6UnktNFZtYWxicXp0S0NaSlh5akxuNnp1WlJhYjM5RkJEX1ZDelFJQkpZbjhiNFpibDNaem5HNll0elNrTGdqTU5mbld6VVJ4MkpqS2F1TmpZZHRCTnJTSlVGUDVR?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNUhQeTlqb0hCbnZUSVk0dzJBZ1V0OFJWSEM2MkNBMlBPYzFKRmRWWk5NRjBHX0tBS1dsWll4d1cyNGRQTmNScjVuYkprcGYxcXlhV0lDanpZbXNNeXZmS1NUb0RXTnVXTXlVOWdjWXpQYlhhSk53WFZiSU8xREtkYUlNWTluby0tYzBuMTR2NW5VSEJFRWlDazQ2clZvZ9IBowFBVV95cUxNQW5kQnBqdDYyWldMcXhiWXNZcU1rc0NBMzh2UURMZkZhZ0JtSXhFNklCMnpDdkQ5ak5sY3I5aVlXWV9sWTVpbDFLNjAwaGtsMHl3bFVXSS03ZEs5RS16WmF0aUZudnpCZzNIdko0WFg5UC0zRnB2TnZrQ1JYOWJqak90OVNzS3RiUVV0QWNRUWdudzR4b2hPbWlKZTJQU2M3RnRv?oc=5</t>
@@ -1123,27 +1372,27 @@
     <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUU5vYUFOTGVaS2lNNl9wTTZXMnc5Sm9tWVRkTVpxV3RER3NCbklwQVdHV1NFdGNJNVNOTzFhS2YwbEV4akZtVG5VSzFaakppZVl4dDN1RE10WE1oVlZjRlc3Sl85M3VTR0d0RFZNUFNSdXM2anltc0d2V2VGU0IyZThIOU1DdGRSZGJtakExUkbSAZYBQVVfeXFMTzVHWUpWb0Y3a2h3Z1d1T0Njbk9vaWdCdHZCTmZkelEyM2Rmb3JQQXJGZE5LLXBpM1hjbWVuM2RoUS1KSktYMnVKSHAxaVRzcU4yQlNxMFpKVWRIM1loWk5CZ1Q0TEJScTU3Z1RTUmVmbW53OEk4STJrVmlIWi1NcERkNng3VFFQM1Z5OGU5SlpfX0ZFTUVR?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPTFB4Z1ZGMHU2Q2hKcjVObjFEYV90WnpaU0dIc1hQODNtN05SaC16Nnl3Ny1hNV9VRWxma0tyTzhlNFJ1ZURzMV9JdkhUMnNKQU16ZUEtV3VYQVp4RlduMkpIdXFSY09Pak4wZWEzM0pmS19lZ1dpSVZseFp5X0JuWnZCWFk0VXlaeUtyS19GNGlNOHE0LUEwblJkZnF2dkxnTV9hN3lEcDZhaTZZeXdKS3lOYkxLSFhhRUhsOVFMamRjYzhJSXMwZF9rSHBMSXhmUGUzekhTbGVySWJSNzBjLUQ0djHSAeoBQVVfeXFMTUFTM3Zpb3M1Z2lPdUlVd1llQU5FWmVrSWE5a01jZklSRDJpQkFIZ3VEVXJndkZmQXBVSUVDNGFnSHJrX0lvQS1DcTc5MEYzWEZMZkFrRFFSUTZfeXkySkdOUEdLZnJGdTl2NENNSGxtS3FfZHNhR210UVJxRG5wUkxtTzlnVURPZXdhVmh6UnktNFZtYWxicXp0S0NaSlh5akxuNnp1WlJhYjM5RkJEX1ZDelFJQkpZbjhiNFpibDNaem5HNll0elNrTGdqTU5mbld6VVJ4MkpqS2F1TmpZZHRCTnJTSlVGUDVR?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT0NxRk9zUGZMNzd0TG80N0lKaGwtZlpGSmpKMzVsZW5VU3haNHJ5Z0lZZFlPVFI4U05kQ0VRQjBERGIwMkVUUEgyVVlGR192R0w2TTMxa0h4MHNHMHBDRVBFa0paVmdwdWg1b003X3ljMU9qb3RuQTNXT3hMQnY5MWJrS0p6amV2bW10cGpwOUxsV2hzekRnd0ZNQ1g5YWdLeWZPd1pWem14aTRW?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOVY3YjlmWmt4SnctbF9Hd3IzZzZSMWNpaC1YWTZkNVdEcnhyb256VFFZRTFiLWtULUdSREVQRGJmREhORmJQbFpubkY5NkViZEVfMEp5ck5GQWppTmhfTHVmWEU0eGlMTUN5NVhNTjlJNnpRR0wwVUQ1ZUlIODBCeDVvN3RuYkpKSzVCOGhfRFNCVUNJaERDYmZUaUlZMmxPWVJSOUdwTWhETmM4MGpVVUsxS0dHTU1tLXlzQ3dKS29FNTBJakFCT3F1WlJueWprU19KVGNDaFA4SjjSAeABQVVfeXFMT0lSMjYwM3VVcFQ0c3ZSdXczQldoczBwajdIWENEYU8zeVRIU1JtNnpJQUw3MklYbUNjWTVHS3Vfd3I4UzNzcmRGbDVXU0tDbG5jaGZ5MklUcENJc2htRFdZcGI1c0JIeGxfSFhQOEI3WHNrR21faHRZa21ZME5rVjVvVDd0MXlLVHlxNG43X0RYWDA2ZV9hUHlqeHVSQnRRbXdBQnFDRVc0YjRWQ2J3eWUzQmtaUjl6RmFVMEoza1dEUnZRWEZuakRhY0N6ZVNQSzRXQk5ZVVo2TlpnWmlwZ00?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxQVVZ0LWJZWktJWHZaR0lvT1p2VDdsRTdMSGVQLUttZGVuNF9oVm1pRUZvWlE5U0JKVUVqTmxUMl96SUVkX054bHpmUEozQ3VjSk1YUlFuUlhIcDZfWWxwRVBKX2dFbUxxODRCRFVNek14OVY1RnFNTFcyLXoyM1R0dTB1azhSMTRhcmRKdm85aGdvQzBMNi1BYVlZQklOUzBZb3huM3E1QnE1ODJQbTR1LTB2clJraDNVUjlNdVBPRUtJdGhYOGoxdm83SVBtWVlCcGU4WWtBby1XNFVOMGVtWk5nOGYwSWhzSzVkRE5ZdmRlcjB3YWh5aU1zQi1IdjlvUTlfallRb216Si1TamFmTGRwOERNX2VH?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPRXI2ZFJ2VWhVRVI2MVBYUG1mbEZ5YjQzR1JuTVZwQ0QyMS1UbXl0aFdxX3hvNGVzTm1rMjNPTDAwUXFCVmtZZk43WkdyZUd3cXZkMjdxdE1acTczWmRmZVNyT05vcjFUUW5oZmRGVFFpeFozZjc4T2Jnb0JzNDVOVHVyS0liak56NzVZUEQ3anF1TlFOVVdkYWhJNTU1RmhtckJGWGlTN2xzem5NZTA2WFZ2bmE3c25ScndCeTZ1OWpxYVlLd0NaQUg2a3lvdjlR?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzZRdHpsR0ppR0ZOcHpRQkM3X0xRYUpQQXZTYmNSMkVPVTY0eHEzeUNXVXYyNFE2SVpaNDNOSG1aajZrUWdFZW9KQU5xS1ZsWjAzaGt0Q2tuUHRzanNCMmQ5OW5CaVhuSmo1bFZsTGR4OEtrTHJGNFR1RlVJZm8yQzNvYThsdDFhQnNKcHZnTi1GN2pYbEFibzdkcV9VT0lsUUdldi10ZUVTRWd4bVdoOE1OcUxyMnFpRlB6OU9kNUxLVHFvcGc?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNDJzNU02WjZVRFlSSDlrcGRZQVh5eXowNnR3S0tJVUtwbE9Qb3h6dnN4UkhyTG92WWtrMVlIaXB4RXpFcHVFU2RybTRVM1JyaVJPU05WbDJEeHpiZ3JCTGw2WkRoY0JmM2kzTndoWkUwcVVmeDBKckhUSDlfMkhRMk1qeHJDd3JadWdTdndkZ1diRFJVdGdLcG9QbENyVmpZY3FxeG5qdEF0dWdqenZRQ25qNUdlMnpuem9MRTRsYXpZMzJFMVg3MWN3ZTl2OHk0eUdURzBqN25tS28?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQa0Q4WmNWV1NnY0hxOGhTRDB4Q0tyNW9VLTNFaTBIU2ZIN1ZRQ1R3LURaR0YwSHplWW5ZcGxDUnNvbXJyNFdWQmNtc0FPUnMzdnhxMkExbTVTdzlOTmQ0RGp0UG11RWRrZldGcnNlM0xPclh2MkozOW4yallGNm5JU0xBVHBhYUlPU0cxamI4NHVNcEMzbnhHZGp0aFpvQ0QyOGJUbzRqd3k4a3ppNXpJSDUxNl9JODgwOXVTNFdFWWhfendmeVQwS192X0ktMnFKVHNJMlR3X3dXUXRDZExHcUFqQndNd2R5RWFtWVZSRGRlTGM1Y2NiUEhkaTjSAYICQVVfeXFMTnFIaUUyVDJYOU9aOHJ1MnZ4ZlFMN3JDdkxTR1NoaTI1Uko0MzVJbFI5aWdpaUhfdDlYeVFrRE1tV2JkX21SaFJCVEtMc3IxMG1EUWZwakZZSlRPZ2JiLUtJLXpwSHAxb2EtUy1nejFRcWRxdFBNX29KV0ExMzNHTUZZQXpGQXFwRHVfSG5sX0FpclBoSHhwa1RidndpMFoxT2JiV0hLb3plSmFUZ05UdmxVb1Q5QkFDUmV3VUR3eWlQTFI3OFdNSjh5NFEzNnJzQzBpdnZ4TVhUSU91T3BROEFLTThBZkVKbU1KUU0xUURDaG5ObWR1UC1GSlZ4N0JLdzhB?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNDJzNU02WjZVRFlSSDlrcGRZQVh5eXowNnR3S0tJVUtwbE9Qb3h6dnN4UkhyTG92WWtrMVlIaXB4RXpFcHVFU2RybTRVM1JyaVJPU05WbDJEeHpiZ3JCTGw2WkRoY0JmM2kzTndoWkUwcVVmeDBKckhUSDlfMkhRMk1qeHJDd3JadWdTdndkZ1diRFJVdGdLcG9QbENyVmpZY3FxeG5qdEF0dWdqenZRQ25qNUdlMnpuem9MRTRsYXpZMzJFMVg3MWN3ZTl2OHk0eUdURzBqN25tS28?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzZRdHpsR0ppR0ZOcHpRQkM3X0xRYUpQQXZTYmNSMkVPVTY0eHEzeUNXVXYyNFE2SVpaNDNOSG1aajZrUWdFZW9KQU5xS1ZsWjAzaGt0Q2tuUHRzanNCMmQ5OW5CaVhuSmo1bFZsTGR4OEtrTHJGNFR1RlVJZm8yQzNvYThsdDFhQnNKcHZnTi1GN2pYbEFibzdkcV9VT0lsUUdldi10ZUVTRWd4bVdoOE1OcUxyMnFpRlB6OU9kNUxLVHFvcGc?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
   </si>
   <si>
@@ -1159,36 +1408,51 @@
     <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
   </si>
   <si>
+    <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZ1dFSEpLY2JtUkxkZzhsMlpxdE9HQ01QUHBGZ1RsM0U4NXFSQzlXV3FZWW51blk0QzdpVllrQVpmcHRxQzYxaXlpa3JpbHE5SHJhWjJRZGdHbnVleGhuV0VfQkdQbWZzVnAybmEzUXpFT0p3S3doMlJNR1g4b3Bib3ZaVWN0OE1LMU9fUi15czVHb0h1YnAwamtFRW5EamdMemdQTHBfcWVHUWU2ME9wMTFxTEpjS3BfeWRjY01hbzJZNmlCUGo2UzF4bw?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBZSnJnMGRCcWhkUTNheVhzeEFtUEhBcGpibjVvQ1Z2bzZkN1FwQjR3MHRqN2N3dmx4M25YdmpROGhYVmtpOFhsZEJ2Y3B1cHRrWXBRZVNLdHlabl91dHRwQlVBYnZLUm1qMmtGU1B2TmUxcFE?oc=5</t>
   </si>
   <si>
-    <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZ1dFSEpLY2JtUkxkZzhsMlpxdE9HQ01QUHBGZ1RsM0U4NXFSQzlXV3FZWW51blk0QzdpVllrQVpmcHRxQzYxaXlpa3JpbHE5SHJhWjJRZGdHbnVleGhuV0VfQkdQbWZzVnAybmEzUXpFT0p3S3doMlJNR1g4b3Bib3ZaVWN0OE1LMU9fUi15czVHb0h1YnAwamtFRW5EamdMemdQTHBfcWVHUWU2ME9wMTFxTEpjS3BfeWRjY01hbzJZNmlCUGo2UzF4b9IB3wFBVV95cUxPM3ladUtkX3NFSHk5Y3RfbWhCZl9ENWRVWGNlWFlLUFpxOTlhRlNYTTAwM0FRRXU1TWVZTk1KRC1RNTlHcmpKd3lDaUttelRza2RGVmhxQWxuZ2VmZThMSDRsWVFONzFNdk15NnIxZ1FjMzVNbl83d2RzUFV2eUJvblppSmR6TWRoVVp5Q3BLWHdBbkVweU5WSWg1QVQ3M1htZnJOQ2VfTjZ4OXZhd2RoN3RheXFfWXBrSWlVWWx3allFZVlUVlRxY0hJd21PMkRMcll3RkctR2diS181UWg4?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOcktHWlBuS2xxaGNjWURCYmVSZ3pyNUxTSEVscTlFblUyTWROTkQtczU2UjdtOUlCb1dDMWdMbTIwRi12SFM5Y3RVTFVBbDZULU5lTk0zcGV0bG9IQUVlX0Nja05TeHpMaTJZLXRjbkhJTkx0Mk42X1I1OVg1bndidExIdTdpQUxodU01RmNjcWhvVllTS3JEd1M5aTE?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOLWFUcUtpZ0pFLUNNVXI1YzgzZENRM2tBVlV5Z01XTEsyZTZJQnBPTFFNeVlaeXpzaTRGZmZlN1YxOGVqMnIxaF81NDc3c0tlTkZldTRaREZwNmo2MmZla3lZbXhzYjhyZnk0bHgtM1ZuT3F2THU0ejVOd3o4eGtpWlpjLWhNVlNzX1lPdkJlWGVsNWFuZlVVRWNyZlJsclJYWHh5MExVOEtzSGRzNjl5VmhDeFRIWlhMYTd1RS1QUFhFbllKY2FmNXB6V2lmZ2lRLUdXU3NsU1BpWFpCWUo3LUZMcHE1bGNFZlIw?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOcktHWlBuS2xxaGNjWURCYmVSZ3pyNUxTSEVscTlFblUyTWROTkQtczU2UjdtOUlCb1dDMWdMbTIwRi12SFM5Y3RVTFVBbDZULU5lTk0zcGV0bG9IQUVlX0Nja05TeHpMaTJZLXRjbkhJTkx0Mk42X1I1OVg1bndidExIdTdpQUxodU01RmNjcWhvVllTS3JEd1M5aTE?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZ1dFSEpLY2JtUkxkZzhsMlpxdE9HQ01QUHBGZ1RsM0U4NXFSQzlXV3FZWW51blk0QzdpVllrQVpmcHRxQzYxaXlpa3JpbHE5SHJhWjJRZGdHbnVleGhuV0VfQkdQbWZzVnAybmEzUXpFT0p3S3doMlJNR1g4b3Bib3ZaVWN0OE1LMU9fUi15czVHb0h1YnAwamtFRW5EamdMemdQTHBfcWVHUWU2ME9wMTFxTEpjS3BfeWRjY01hbzJZNmlCUGo2UzF4bw?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOR3VLZkYwT0EzdC1YZkZFSktLdlFzRGZfVDQwWlE2Vlc2SkY3WmJaZkxvLXU3dVhZd0l5VHl5ZVRwMkw5NGdpTDdYODYyc096ZnhTNkd1V3NGNkdaZjZxM3hicHg2V3kyU0dvLVV0bkpRTWtQZTQ5eGtOY3BXNWxpSnhCZWJtWmtZelFKSlJfUmJfYmxHdlRKY2F0aUxrNXhRQ3MwREtFeHdzcFd3eWgwV1RMclVNckxTSm5qSjVwMVZzS0tEYzlleTFlalhlRzlOLUFmSjRpbTZWLXJsMlNzQg?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNWlRsbG45VUtFQ04wZTVnTUpVVENFbU9kZkxiNTd4c3RPTUR3bmRJSF9ZR3k1U3NjN1BKN3RBbF9Nc0dqUzBmZDZweE1mOUZxb2s2REgyR19VZ1NiZi1VLUFUTTFyUUE1RDN6bDdKN1ZtNkQ4bjV6R3lJZTJtT2JRdzJWUGo2TTFDLVpEWkpGZWVYaWZBbTdQaFljSHVYOHhCY1JCdEVQOC1xSGlZWDN0QUJCY1BRVjFienNpNzEyOWpzc1ZfNG5fanItY3B1SkktMFZaRUxZcDQ0T0J3d3hUVFZ6c2hhbTR6YUdJZVhxanlBb2twY1JfSHhLNWxvSlNLN2dBLWlRd3Rvbm1FYmFQeEZlTEYwdG4zQzVJ?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQbFBTcllrWjJwdEJlbnJRN3Fpa2I5U2V6NTJiRWpfRlNqY0J0ODNPS2cyZEllM1c3V2pvUWtKWXM2endVdFR5WHhzQU5fdHZ5OTBfN3lXaFBqRzdHb0lhb3RON3ZJNTUyTXFDN3IzVE54d0hkMHNuUUNkbGhLanMxWUNkZG1YYzJ5dUNRMXhRbVZELUZLOG1ZMTl2eVUtcUxDMWdkYndPUWpVb25RUFFpb1NzWHk3cVh3d0JPSWhpYzBhVWFfaWp5YkxOUS1sWUNvXzBNWXhRS2VlcGt4YVRIX2VjYzk4RzBmeHBXVzBLOHFuQTJrOGRjc2Z4QXB6TS1oMEM4N0t3SXk5YzlOaEtPdS1iVVY4RGNILXpHVXlyNjV2TWfSAagCQVVfeXFMTmRvRUNOVGpWeUQxZUtaN1UtTjlOMjBLTmZpbHN5cmZVRzRpeFE1QlcyTFdjN0xtQVNuLVJzREdTc2ZYRWpVMFl5dXg2SG1HenR0NE9WNklvZkEwYk1VaTRPNTJHbC0xRG1lcDZfRG1XLW1sZHJLcVIzd1pSektGUUNTbFZFWlN6VWMxTF9rbGV0bC0tdUNmaWJpUjRSX1VUM0podFloLWt0dlI5WllVeDRyWV9PUGswZE5oV2dzbXRkY1FjeERRRkJzTkpVcVV1LVBhazVoQWtCbGJVSy1nUFZyQ0dacER5RG1aOWJmWFFHalpBUkxiV3RBZ045X05tWHd4Y2hoWGJDLS1EcDhYOHBnNGVlWEpiUGNwQmhoeUJ5M0NoTU9zSGg?oc=5</t>
+  </si>
+  <si>
     <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPUzRTZldvRkIxRnROTWFON1RxYjhpb0V3a0psY0lFYUVMYlVCb1dPSVUyRzlMOENOTENqeWF4MUtiT181bDJ1TnZuQ0dSYU1yZEljZVR1Qm5pYldRNjhVV0lndy1qSWpNZkFTWVBRY1I3ZHZCQjRCdW9NOUdmamhNNU5FcXJDVzlXZXJ3VEpCaVM5cU14Yzc1c0RpTVc2c3Q4SnhVbWx3TzMyUlN5SWdWbUJGblRlZzRaRExGdGtjMzI1M29KQ0hlSUF5cWZfY3dqdDd1Mk16WldZUHdScGo1WTl2NWctc3V0RlFwZzZqQTY5QllHSVV4M21iVHY5VTNfZlJJQWFVY9IBjAJBVV95cUxQa25SdDJjem94UFMzQWQ4VTZmVUVveTNZbEgyLWJVdmRCdEVXRHpWSjdHZ1JuUU9lek56eTZsVFhWeVQ5VHZudWI0ZXVqTENNdHhuWWlfdFYwNWE5YjcxWXR6b1k2aWNzLXBsaFpfOXZxcTJUNnRZVU43dWE1clBlVGd2S3gteXp0TUllWGhJRmJrSHBTM2ZfT2pQRGdSV2o5dlVibVdFSkViZ09NOVNweVJMRXFGS0pmb1QxdHBZNmtBX3lKdnk5dlZrdWc2VzBlX3MyLUpvcjVXeURabWZDX1ozT3J4Y2pmdGdKZFNJeHR4bTRPSi1XU3FxRFFzbl9jQTl6UUF0bWI1NThu?oc=5</t>
+  </si>
+  <si>
     <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQQ3hUMDdhc1ZEcHp1a0dtb3dTbE13d1duR3pUX0dWLTJqbzZfYmlIYl9Id2M3Yy1CdmNtUk1qam1xRnc2NTNJRDk3UXF2TzJGYVNWY3YwXzRYSVlDZ05uQ1c4blY4V2d6XzNzc2JRckdJVE0zSWNnNXJPY3NhODN4b1hYcFhiQUl4UGJ1VkNDWGIwZms?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOZmRINGh0SkZxTDRTeWVFSUswUnhZNGxjZllYYURKbWFkVHhMSnZMd1VMamRUTzBnYmVOSWY5Q3lxaDNmOGd2T0VmeTRyZm9UZ1VHRTJRWTRLei1tbXZ5VUhKMFRRbmNrVTNIc21Ia2QwOUkwS1RCM29faVZoNHMtS084X3R4RTdJcGtjb2ZZT0RuOFNkMkZ1MzRCQXN3Y1BvcXkzNHl0dDVHUHM3dHBVTHpWLTNoTnRVVHcwVHJQQ0QxbmJKQVZST29ReDhFRVZvbUU4N1lJYXRpVWdRSHNFbjFxT0libDRTeUtWMXVwRUY3MlprRWJGajNDQ2N4MFlVeUZUVVhB0gGLAkFVX3lxTE5lazJSTmpvZjRob3FrYTgtZE12SVZrYjk1U0tRdjQxOXNfbzQyRlF6RFduNU5CdjdON1hsWExlOWZRU1lzemdnNUt4eDN6TU8tMTV6WUNaSHdQRTdBYUdQQ1BfZlU5WFF4UzE1T1h1VENhXzdiMTVEWTZTSDJvdXRFNFJSMlAyZE51emx5WU8yRUZDd0FJTmFVbjhUV2NYSkVMWGJ6Z3BFOEMyZEFhMjFZcDlpb2RQajF2ZUltWV9FYUM3MU9VeWJyVVZMMllWeGNKOVktTUhfSlExWTVBMmpwSlN5M3VqWGFXZ1prVWlDdUd1MWd5bEdxeFpwUTllazJ1bmdkVUF5UGJqWQ?oc=5</t>
+  </si>
+  <si>
     <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOZmRINGh0SkZxTDRTeWVFSUswUnhZNGxjZllYYURKbWFkVHhMSnZMd1VMamRUTzBnYmVOSWY5Q3lxaDNmOGd2T0VmeTRyZm9UZ1VHRTJRWTRLei1tbXZ5VUhKMFRRbmNrVTNIc21Ia2QwOUkwS1RCM29faVZoNHMtS084X3R4RTdJcGtjb2ZZT0RuOFNkMkZ1MzRCQXN3Y1BvcXkzNHl0dDVHUHM3dHBVTHpWLTNoTnRVVHcwVHJQQ0QxbmJKQVZST29ReDhFRVZvbUU4N1lJYXRpVWdRSHNFbjFxT0libDRTeUtWMXVwRUY3MlprRWJGajNDQ2N4MFlVeUZUVVhB0gGLAkFVX3lxTE5lazJSTmpvZjRob3FrYTgtZE12SVZrYjk1U0tRdjQxOXNfbzQyRlF6RFduNU5CdjdON1hsWExlOWZRU1lzemdnNUt4eDN6TU8tMTV6WUNaSHdQRTdBYUdQQ1BfZlU5WFF4UzE1T1h1VENhXzdiMTVEWTZTSDJvdXRFNFJSMlAyZE51emx5WU8yRUZDd0FJTmFVbjhUV2NYSkVMWGJ6Z3BFOEMyZEFhMjFZcDlpb2RQajF2ZUltWV9FYUM3MU9VeWJyVVZMMllWeGNKOVktTUhfSlExWTVBMmpwSlN5M3VqWGFXZ1prVWlDdUd1MWd5bEdxeFpwUTllazJ1bmdkVUF5UGJqWQ?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNcnFWMDE5UEt1ODh4cm9JS3lZdlpIOUptaUY5U25tUWVxd25NTGJiNFA4WTdyVUNvRzlob3M4bVpOczc5czVRaXA5V1RQc0h6SXpRUXVuRTlXSjJveGNJbWw5ZDRYUzRoLVQ1UjB1YXVqZzBvUlFyb29Oa1JVT3h4N1pFc1hfNExPUmFVTml6QlB0eEJW?oc=5</t>
   </si>
   <si>
@@ -1201,10 +1465,19 @@
     <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPVFRDQXk2WVcwQVhLTmljT1B4akFGM3ozQlBvc3QyOHJua1BfT1hxRnFJY212eFowWTVTdVBmTHN6d2REcXc5VGVuUmw1LWsxNWxOeW82UzBPaVQ3azZfQVNSb0pUTHFqTHdGVWJXS2Z5YmVSbXZJSXd4dzdTamNXdUtqMTRwVDV4MF9acHJFX1pTZ19NVVNvLWdNb1Y1d0FzZlN2dWVMamlvVlNCN01ZS2MxZDh1M250d2tsNEVpc2NYRUJXcE9KYk0yd1FHU3BiNUtFOENRdWZ4ZHdsR0l2cFRFMEpKTGYtaUk4dmhuRjhyaVU3RDYxbUpCUzjSAZACQVVfeXFMTmxJSVphakhMc1dSdUhqdDJFZW00OTIwT0NRNndiZGNtLWROVW1NZFFHWHhTMzVYb3N6aHRBV1NObF94cEVSeHZMOWpPTW1oVXdGeDloRU9uSWpIUXNldU1qY2lUM3dNWnhwMUNESWVTUy1SNGYzZkM0Nk1ORE9zQkNkdzc1MnJpUldVTnhKeUsycE1rcGdwMi1SN3F4bkZUdHZGNUJWT1RLeS1ZMFJUVkdmOXpHcnpId0N2QW9oOEVsbkYyVU9xbUtnTEVBdW1kNnlOY2wwVGVUY1dCc3N5WkQ5ZTBRUTFKSndYUU4zYVU2aUc1cUlsLUt4d3B6OTZ4Xzl0cC0tMFAwQ0hwM2JWUC0?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNNFJLRzNtTGZtU1ZCaVUxbGR1QUhBMzV5eFVUT2w4TWZVZnNfYmNMX1IydEVyYnhGT3ZJcDZMaG85R0RUUU9LaEsxT0hyYTFEcy1lNmVTMTA4TWlTbzJ2NmJNbTdxTXZQeUVsczJGMTdSZVlYVHlwblhqeG53UzZ5QkhsMVFyTWRORUQtOUNJMXFBSzJiNkZGQjJSZ1lvcWdfUHFTN1duQjJvcWVyMEZIZE01OGMyakhIQk5WbkROZlpIaDg5UHJRLWdEWVVSRlN4N21hNlhvemlncnlCZlNsM1BvYlJrX2hnUEpmREFCT1pzWS14YmtLMzNHWk1ndnN1NVE5YUdaajNmelBLZEViNEFHNHdjbFhqZEHSAbQCQVVfeXFMTXBsTHJ3d1N1RXh4WFdBdjAtMVFYcEJTV2xwd0xHZERGQVlHNXNvcW5hYmdpN09Wd1ljMjR4RjNSRWMxMl8xMmN5TzN2XzQzUDhCdlJ2WjdNSklzMG1yRzI5YnRnRDFhYWo3Wi1wOEdNbHE4UElzU2FGN3Z2b29XX0Z0bXBDczQzbE1oRE9zVjk1VG9OMzZSNlhsbjlFZUp4em84bGxJSTJyRG8yOWlvUkxPZkhVT0picHVCXzRRX2dhY1VTTWlJcUFYRnVBQzV0ck10YkktYXVpSE5uNm40U1lneGt5c0p5VUNzYnl0NEpqWmVLUE5UcWxOT1BJbnFDZmJRSG9XaTYyMXhqT3dhekhSUDBLSnh6dGxBNFNNYzktYTdZMmxmZm13bXhDd2x3Y0tvWkM?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQQ3pvU201R2JPZEJPWTQyNzZSdTJJbV9jM0IzbUFBYzZxcEp3Y1U2T0xoNGJYMk4xRkY0Uk9ybUtSZTllX1dxVFc4b2tKMVBqWktiTjh5THhoeC1GUWJpZkh4RnVZQVVOeDBwWGtyTVBCSjBsQ1dxZWxRMjRaT3pkcDZKMFhaWTRSMS1JUjlKZy1kOTM2TllVV0NQMjJZMTVN0gGkAUFVX3lxTE5Nb3ZabTd1SnBUT0l5alV6UEdnV1ZCaDdnVWstTXRYYnJseXpPMDhMM0VIVDNGRHd4cWpnQkx6SlVhek9XOGhWUndJeGZPbUI0MzNQY3BxOXFMb1cyVENMYzB6a3liYlFnVVRFZ3h4bjlSRVZ5TU5DbzNqc2RZVURBYkZYT3d0NS1jWWU0ZmJGNk8tSWRKRkJUZWpGRmczLUJzRTNG?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNNFJLRzNtTGZtU1ZCaVUxbGR1QUhBMzV5eFVUT2w4TWZVZnNfYmNMX1IydEVyYnhGT3ZJcDZMaG85R0RUUU9LaEsxT0hyYTFEcy1lNmVTMTA4TWlTbzJ2NmJNbTdxTXZQeUVsczJGMTdSZVlYVHlwblhqeG53UzZ5QkhsMVFyTWRORUQtOUNJMXFBSzJiNkZGQjJSZ1lvcWdfUHFTN1duQjJvcWVyMEZIZE01OGMyakhIQk5WbkROZlpIaDg5UHJRLWdEWVVSRlN4N21hNlhvemlncnlCZlNsM1BvYlJrX2hnUEpmREFCT1pzWS14YmtLMzNHWk1ndnN1NVE5YUdaajNmelBLZEViNEFHNHdjbFhqZEHSAbQCQVVfeXFMTXBsTHJ3d1N1RXh4WFdBdjAtMVFYcEJTV2xwd0xHZERGQVlHNXNvcW5hYmdpN09Wd1ljMjR4RjNSRWMxMl8xMmN5TzN2XzQzUDhCdlJ2WjdNSklzMG1yRzI5YnRnRDFhYWo3Wi1wOEdNbHE4UElzU2FGN3Z2b29XX0Z0bXBDczQzbE1oRE9zVjk1VG9OMzZSNlhsbjlFZUp4em84bGxJSTJyRG8yOWlvUkxPZkhVT0picHVCXzRRX2dhY1VTTWlJcUFYRnVBQzV0ck10YkktYXVpSE5uNm40U1lneGt5c0p5VUNzYnl0NEpqWmVLUE5UcWxOT1BJbnFDZmJRSG9XaTYyMXhqT3dhekhSUDBLSnh6dGxBNFNNYzktYTdZMmxmZm13bXhDd2x3Y0tvWkM?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQSmlvdlUzeHJlOVhEOTBjQVN5TlhCWkNmaUNEQnczelA1YWVHXzJ1ZHZkM2JKcWdCNzdKYkViRnQyaFpldFB5MGQ4SU54WDVoVGNlbWdRQzJhM0hvRGFaaF9MR3lxUWhSbGJUTFNKcHVmQjJ4MjlibnNuaGNVcXVaVE1aa0stdmFzYmxvTnlmc1hwMFdQUDJGVkVuS2Y4NTgydk9zQlZsU2l0OXA2NjUzZnk3SnpDOUx6RjItNE9EYWlscDBlR19XV1pIdEgxVF9XT2RWMHItMmdEeHlqdmdfYzh1X0dIT2lLNjlvR2RsRWhDZ25iMWVGbTNzaUtQZy1STHfSAZwCQVVfeXFMTXRiNGt6QnJSZDJ3NXItNWZ1enZWUkZmMEhPSm5pNWpLT2hSLXdLWnBzOTFLcVdzM3Q2SWZ1UWpzdU13NjVDNUR6S2o5N1BhOWdlYWEyVDh2bGVqTE1LR19KUnFaUFJEVWZhTlZ4Z3RwV3J2U1I3VmtReVVaTGxMTldfeEZmclhOby1iaFpVU2ZjOUJqRERwNFlMNVdzbDVFX3BQWmg1YjNhY0hrQWJ4UW53Z0lRTWlLWFEyWm5Jck5qX3ROSXVqZUxtTHM3WDk2TDJzUDJUN21VTjkxamZMRUd2Unl3emJEaGJxejJPdFViSkNWbTRudzNRUmE4bFg4a1JaLURLa0lQakk0U0kyRFFwV0ZlRHBtZ3VNc1Q?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxObFJ5amljVE9jSVpXcTh3b1pqaXNPWWp3QkFjZkFPT25VRk9KbDczbno3VFFlZnZkc2RURl9PdXVxOXNCV2lYdGZHYmVmYmoyLTl6TWJsNjYzLVJwOEoyWmM0TU1zYTJld24wdUJTcHE5RzhXdlk5VTE4WVpWQWpYS3R5REo4aURzZ0tkMTA2WGd1Y1dQdWFrTy1zZHZueWhlb1gwYXc0dWhjZ05Oc0tlQVpCR2pta2E4MU1vTTVFUW0yRDZDcWN5Z3g2RUYtUjdfWFdDc3Z1czBRMkYzVFcwV1pUUEU?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQajg4Z0F1TkdHLTRxTG9Sd2tUTXBxWDNyaWo4a1RuTXFZUHNVaDM2XzRvNDZWZS1ZRXVNaGRFc0hiaVVsaUU3NHdtNTVUbXRVbVZReGJPaEVzVzdZSHNweWdrVmhpQVV1REVfcmpSeDlFeGhZNjFEb2huNTlpZkVTMlhpbVRPZEh1OXdhLWxmdnBRNURlV2dYemhVenJheTZLZkZhMU93NXVVX0pobC1VNFhoN2FrNG1XZUl5MG9iNFQ?oc=5</t>
@@ -1228,30 +1501,33 @@
     <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSlFESU01MVJsb3l4c2RqRHh3UHVHcHZjcEhSUldGYmZLZmNnOC14NUh2a1dFZUlkZ000STZVcEt5a3RVellXTWQ1SFF1YjZlLTVvRTdBbVhvX2FMc0I5dEhMamZJajJvOW1hWFFPd3ZvdGZlNE90M0Z1VGpKN2NZZVVwS083dWJJb3VaUGZtQWw4eFNYOWhFSWh3VExoRi1ZSGJMOGNUYUxhV3JQbE1KalphcWw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
+  </si>
+  <si>
+    <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNQ0VEeWtCQWV2VXlEekdmTTBNNWdRVTNNVEd0Vmt6QkM4UGItcWQwOFZhZFNHNGJIOWhpWGhVeFFxTFRFV3lHeTdIOFF5aDltV0hWUURZM1dsQmFfVmFvTU1JdGJ5U09wVktadWhJWUNMdnllQVJXOU4zZS1SdDVqdk5OOGJqc0hDNFVUa3ZkZ2dQNXZkMDdlbVh3RXlHSnh5N1J4a2VLYU1SR3N5czFVQ3BfZW5wQmZtY0Y4RmctWU5BbjhGU2hvSVRLdjdLWV9pcUZSZXRqYXR1am1tNll5VXR4bmtCZlR1blhXUFl1V1VqU3pGUG9jbtIBjAJBVV95cUxQWXZ3bFpiSDN6eWVxM2ZTckYwcUpSRExJc2ZYVUtONWhLYnJBX0JMZ2lUTFJkRzFKZmZUQ0R5OFVBM3pkZzlWdldJc0tPZ2E0R3JGd0JkUElqOTJDSmdmbWlzRjJrWXZIQ0pnMHgwb1lVekpVWTRiMHZIdHpnUXhyTURpeDV5X0NHbFFXTnFYN3hQbDYwVG0yQUFGTFM2a2tIRFMyQU93WG95LTExWUlJbkRsQ1RYcC04UXYzYmtXNFNxbDctWmN6RFVZWWtNbEFFQVF1N2lDd1NGVFBzR3BJUkpWR2FvLXZoQnR6V1Mzc1NMNHNtRkFmalRrd1FMT3lWY2VhT3RzRkkxXzdC?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPczRONEpvSjI3TmpVWEdqVnNtUG1LeFBjSjc2X0ZfR2RQaVcxN1J6ZDBheFcwVHNPZGcyelI3RUFsWEp1YXBQcDFacFJjSkVXVWRCZ3ZhMzdZRmtvOVBHckJjWDlhdlV4NUF3anRJR21qN0RqV1dhRFlLQ2lIVm40NnRSNlBXMDNWZlB0dkhMWW1zOXRkOUJyRmVBaENseXYyREtzUlRxUkJsTUJ1eUJPQWs0aW5hdU96LXU2ejVkMlJNZERnZXRTUk9ydXB0UURFX3dvVkJ5Qm9SUDFFUXBuTzBn0gHnAUFVX3lxTE5wZFNHdzdvOWxRLWQtOWtrcUFzZi0ydEFMXzF0YUZOa3AwQjlNUjFablhQRTdwR2J5Qzh5WDZ3UEZ4QTZSc2MwbHB6TnM0WTduMjduVnM2RnRTY0JQR1ZtWTB0QThMaXNVQlZQV2xENVBZTXV6ZHQxVGNTNDF1ZGpxbU9BeEFxMGZrUVNIdVNJeUpjcmVXcm5pemM2SHRUR0duN0hKWjVlNzR4bDFsWVRKTjhmbTJoQlM1a2RheHVSc0N5MkNucmFhdnkzYUFHby1Qb3R0TE56dHBMNUoyVnhTa01IU3liWQ?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQM3I2ZXJMVkpqT0RPRGhtVm5LZjVPZnBZTGh4NnBCZTZqajZ1dGY5VGM1MGdKMno1aHdSbERqSEVLWEUyQWctYUtFcl9aVW9jR0RMYWF5aWxQemtRRnhWMEZHTUNyNG0wQVowaFNIUi1zdF9vNFVhTEF3eUVwNFU3UEVYNWdoaUtUUE1FeGFTQkhweG5SOTJzdjMwUm9keGhxcEg5Tk9KbS1mR0h1TDAxbUV4YU9LbmRQOGJIQ0ZkUEx3Z3JMSHBSRGNDWdIB5gFBVV95cUxOVVl6Ujl1cW5wU3A0OXB6dG9jYV9PaHpYbWdhcDBpNm9Ud0NrYUd5YWhkZEQyZVhUNWMxMjgtZEptdDNPUmUtSGp6c3VRMDRYMzdBN3ZuWHhORlotWThuZ2c5MlFaQzl0LXJIbGthTm5yS2J5UWdMWFJiSGFFUjdzQlhmNm9abnlUT1NQc3N2dEVMQ3VIbWh2c1hiSGRCR2todGpUMTNkR2dqdUpWT040RlBIQXZudnV2RnhPaEpOaUtEZmxhcXR5YWw1cE1IRjVibGUwdndBS0JVa0dRZDZQM1VvM0tNdw?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNOWpHQlNpRUdaU1ZWSzBzd3EzM2I3cmZXdzd4aUNrMjlnbWJPZkNNbVVGYXRrX2VPUjJxcEt5ZUJha3lyOS1VODQtTmV5d3NFdU80ME01eFg5X2dWZ25GT0Vhdl9TbVJBZ1RkaEJBZHh3aXNpNEMweEJEM3NuUmxRLWMzQWdUOEFkUUlKbm1PR1FyWVNMSGppa3VOZ2JUQy1wTl9sdkRpT0xhdWNaclNBdmxycEZnTUU0dHJvVVdsbWRaeDc2V1ZHb3dNMmNucmpuTzRkdDRzaERIY093NW81MnpDM0diSHRTbkE?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQM3I2ZXJMVkpqT0RPRGhtVm5LZjVPZnBZTGh4NnBCZTZqajZ1dGY5VGM1MGdKMno1aHdSbERqSEVLWEUyQWctYUtFcl9aVW9jR0RMYWF5aWxQemtRRnhWMEZHTUNyNG0wQVowaFNIUi1zdF9vNFVhTEF3eUVwNFU3UEVYNWdoaUtUUE1FeGFTQkhweG5SOTJzdjMwUm9keGhxcEg5Tk9KbS1mR0h1TDAxbUV4YU9LbmRQOGJIQ0ZkUEx3Z3JMSHBSRGNDWdIB5gFBVV95cUxOVVl6Ujl1cW5wU3A0OXB6dG9jYV9PaHpYbWdhcDBpNm9Ud0NrYUd5YWhkZEQyZVhUNWMxMjgtZEptdDNPUmUtSGp6c3VRMDRYMzdBN3ZuWHhORlotWThuZ2c5MlFaQzl0LXJIbGthTm5yS2J5UWdMWFJiSGFFUjdzQlhmNm9abnlUT1NQc3N2dEVMQ3VIbWh2c1hiSGRCR2todGpUMTNkR2dqdUpWT040RlBIQXZudnV2RnhPaEpOaUtEZmxhcXR5YWw1cE1IRjVibGUwdndBS0JVa0dRZDZQM1VvM0tNdw?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNUnRxaERnUnRKcEkxaWZ2cHlsZFRuQkRtMXpDcWZxdU1NNk05VERuZV9CQVhPbXI3Y1d1RGFPMGF0ZGsyamNvZEhFTkQzQWdUSzVNVjg1U0JNQ29WTVRxTldKNWEwX2sybGE5TXhfcU5BUEJ4YVU3MmhFdnpGb0JzV0c2ck1mcGZnc2RVLTd0MEtzZktlQXVzRTN4bVZEa1JOTnlMa0VYWGtkYVJIdURz?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSlFESU01MVJsb3l4c2RqRHh3UHVHcHZjcEhSUldGYmZLZmNnOC14NUh2a1dFZUlkZ000STZVcEt5a3RVellXTWQ1SFF1YjZlLTVvRTdBbVhvX2FMc0I5dEhMamZJajJvOW1hWFFPd3ZvdGZlNE90M0Z1VGpKN2NZZVVwS083dWJJb3VaUGZtQWw4eFNYOWhFSWh3VExoRi1ZSGJMOGNUYUxhV3JQbE1KalphcWw?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
-  </si>
-  <si>
-    <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNQ0VEeWtCQWV2VXlEekdmTTBNNWdRVTNNVEd0Vmt6QkM4UGItcWQwOFZhZFNHNGJIOWhpWGhVeFFxTFRFV3lHeTdIOFF5aDltV0hWUURZM1dsQmFfVmFvTU1JdGJ5U09wVktadWhJWUNMdnllQVJXOU4zZS1SdDVqdk5OOGJqc0hDNFVUa3ZkZ2dQNXZkMDdlbVh3RXlHSnh5N1J4a2VLYU1SR3N5czFVQ3BfZW5wQmZtY0Y4RmctWU5BbjhGU2hvSVRLdjdLWV9pcUZSZXRqYXR1am1tNll5VXR4bmtCZlR1blhXUFl1V1VqU3pGUG9jbtIBjAJBVV95cUxQWXZ3bFpiSDN6eWVxM2ZTckYwcUpSRExJc2ZYVUtONWhLYnJBX0JMZ2lUTFJkRzFKZmZUQ0R5OFVBM3pkZzlWdldJc0tPZ2E0R3JGd0JkUElqOTJDSmdmbWlzRjJrWXZIQ0pnMHgwb1lVekpVWTRiMHZIdHpnUXhyTURpeDV5X0NHbFFXTnFYN3hQbDYwVG0yQUFGTFM2a2tIRFMyQU93WG95LTExWUlJbkRsQ1RYcC04UXYzYmtXNFNxbDctWmN6RFVZWWtNbEFFQVF1N2lDd1NGVFBzR3BJUkpWR2FvLXZoQnR6V1Mzc1NMNHNtRkFmalRrd1FMT3lWY2VhT3RzRkkxXzdC?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPemdoRDc3Um9SMTVlNm1zNEhLTFlLNzNZNzZkbHlOOVB2V1pLVkY2eHZYdTllVXozMGQtbVlQQmlwRUFFclVqR1UyMnUwT19fX3BrcGQ0bTNWVlUyX29MdkhRdC1wY0huNENONDR3ZEJOaHdwcDJqWXNKN2tFdE1QOXB6Q1Rqa0NfOXBHbGROUjlkNTAyX2JDdzhhZ3lTdGQtdUdUNDdrMHdiYlV5T0ExdUd6bWRBY1VfMXBPaE5GdEd0RWFfNGc?oc=5</t>
   </si>
   <si>
@@ -1264,10 +1540,16 @@
     <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOMWJRUzdtRlZyMGg3cnFZYVBRZzZQVGExREJVZGxOZk03d3IxbVZfREhIQmRIMTcwM0RhV0VITzl5MkdIbVNEd0ppLS1TUGpLVmF2dzJ6bTdyeU15Vms5SzlGU3MtZ0l2aUlWSzdTYk13OGxOVjQ3akNucUdmLV9yeXZjcjdYLVJyWnl5a25scDBxWnVRSlg5VFZ3TkVlS0pzU3ZXM2RZZTdrbjZ4Q2dub1FraTNwVzd5M0FObGo3dUEzYmlwdFd3T256anIweVZFUkt2VWFOeUN6SkFBQ1QxQ19GQkF4NE0yMHpvWUZTRVdjZ21BYnZlVkFBWnlwRElSeTB6M0xvVGXSAY4CQVVfeXFMTzJyUHA2bWVUTnc2WDBiUkJzWVdRWUNobktMNEQ1SVBnb0kxSFh1SlMzejA4VEhfRTEtRDBfb0N4dkVLbkZkMVVEakZOaENacG1vdDNVck15LVNCdU5IMUJ2b2pnV2RGd1JKMVBmemk0bGpHTTVMQlJ0LTE0Rmw5TjVDVVkyV3o3X0pveThGc283dzlDMnlWZXAzUkJhMUllRnF5bVpSSS16N0hPMGFhQjh3cVRVWFRLT1JxQ3JkaU8wX2ZwaUthalFqNkRITU5YdnU3LWZlaTBhSTJrd1FMNndPY3llbG1nSXJFWTJUVUpZTW5idVpNVVVwTU9qV1lqM3d5UDFrZjcwaTVmbE5B?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVkVKVlhVU1d2Tk9ITl84dEtTVHBMTF92RDJLa0JNTFJhRVljR2syeFBUQVJnV0EteVN5eG1zVVBuMldzOUVNSzZ4M0s3cWY2NXhTa05zNklVcVRIU0FOSGJSajVRM2Y0QzRLQk1yUHprM3NPRXA3dm9qQXVCNHRVa204OE82V3NBU0FLcF9HeU0yR0tQN0tWNmkxcjZBaHVsc05iZjg4Qy1tU1VSNmxPNHhrdXZJaV81YlBvc1JNalLSAcABQVVfeXFMTmtFbWJiYWI5d19VS21uUEx6Q09oeUs3bjFVdDBtbFdoZmNsZDBJUlZhdHhEUlFOMmVFSmdSbXZRX3c3YXFzVWtRcldzR00zU19PNWx5X053QUM3N2N6UVRwcVNtek1qeV95a0tsQ2Y1TGpnQWRDYXBGTDZLVlppd1BYeGh6LUlZVmtQQkw4dmhERlRza3UxZGg1VXdKRkEwT0R4eXZlN2tDdEdLUWxGQjE3ekh1eWR6Skg2eGNIM3lU?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
@@ -1285,15 +1567,15 @@
     <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRWU1YmM4clFjLXhocUloOFB3QWpFRVVrTWg1ajdkLWluRGEydUJ1VXo1cmU0djVzU01DU04yTmJGTm1BZ2VQaVdWTl9ITVFtVE91U1NEVnM3STdERkkxd3VBS3AtZXliVmdnNFFTNEp3WlJXcTdaTG5LX3NhMFdLU3NLNHZJTHRCVW5hLVlDLTRqakJZTS1POEcyOXpnWC12VVJPSS1ZZk9WSXowS0JqeGczUGNQTkFZYWRiQ3RKSk9RanJVR2FHRQ?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVkVKVlhVU1d2Tk9ITl84dEtTVHBMTF92RDJLa0JNTFJhRVljR2syeFBUQVJnV0EteVN5eG1zVVBuMldzOUVNSzZ4M0s3cWY2NXhTa05zNklVcVRIU0FOSGJSajVRM2Y0QzRLQk1yUHprM3NPRXA3dm9qQXVCNHRVa204OE82V3NBU0FLcF9HeU0yR0tQN0tWNmkxcjZBaHVsc05iZjg4Qy1tU1VSNmxPNHhrdXZJaV81YlBvc1JNalLSAcABQVVfeXFMTmtFbWJiYWI5d19VS21uUEx6Q09oeUs3bjFVdDBtbFdoZmNsZDBJUlZhdHhEUlFOMmVFSmdSbXZRX3c3YXFzVWtRcldzR00zU19PNWx5X053QUM3N2N6UVRwcVNtek1qeV95a0tsQ2Y1TGpnQWRDYXBGTDZLVlppd1BYeGh6LUlZVmtQQkw4dmhERlRza3UxZGg1VXdKRkEwT0R4eXZlN2tDdEdLUWxGQjE3ekh1eWR6Skg2eGNIM3lU?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPV3JMcmxKczJ0SUVEa0xWa016eEQ1NXhSTFpiYXRZOFpxMjlMMXpjOWx4dzZzVXJiRC00UmhGWVFrQjN2ZmFOU0lmWmUzSUtWOEJSX2VxVXRldW1HcXdBN2ZydVRpb09FNDEwbTJtYnRYQjM3eG55cTZaRW9GOURaRDJZUk5QTDVZS2hxeUVhemtkS2U3VnQtT09nc1dnRkhTU3NzMlpRS3ZYZkROWExud0szRG7SAbQBQVVfeXFMTXJvM0I0SEZhNldLZ3RRWmdhWnFwS0JicnhBOGZPTDZJdlJyR3ZLQ3BYTkNWZWhybzdxVEstR3duOXZFWHdVVWI1ZlAtYVl2T2hZejhfZXAwS2hPekMxbGp6X2UxUk05eWdUajNPWU80cENHRkFySDVkTmRBbExyLUFqMjZtYUEyQmVtTV9sU3RjU2RHeXFPQ3ZyTkJOalZDblRid05OTFRSNWc4dkc2Qm1HMkNy?oc=5</t>
   </si>
   <si>
+    <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+  </si>
+  <si>
+    <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+  </si>
+  <si>
     <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
   </si>
   <si>
@@ -1312,16 +1594,19 @@
     <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZllZb2c2OS12UW5RLU9YQWJyclk5dEtzdHhwNDFybVVnOTJ3LW5sTC0wM1NoTm9mNEN4eDIwYWFUTGFsTnYxQld0MHVtdGFYV0JWTVBaM3JiU3hhQkRMV0RxbWZwbENoNE1MaVUyZGYwd3RmOUJFVU41eUlMVG15a3BNWEZ5akdJWWVvcGtxTW9LdEtGUXE0ckVrSG5NYjBLaVRxTXgxaGp3dw?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNVllVbkwzWi1PdVRWcmQ4VjJEd0lwREZXdnBNSHBFcDFEWnctSEtqZVVEVk9WNHZxQzZYSGxwOU1aSkhQX3dtLTRxZGxabzNfZlJtRWhrVTlGYnpoYkdqRFM4SE1CTmw1QTh0eEhfSXEyaF9wMVlUUU04aFR1VG1heGQ3cjdWZ2EtYm9GVTZyZzQxNUwwUTV1c3ZRNTJycmwzSjFIZHc4T25mM3JLUmUxd09FeHNIT0o5UWowMVJIX0NOZk81SmJxMGJqMWlpamE5UFlVS0ZwZExUNGRUVU9CbVJfRFgzUVdaRDRqMExnRjRjSmJLSmJoQUNzaFpKMDFtYXg5eEZ0WkYzM0RoUnk2NGdsTWZ1Z9IBmwJBVV95cUxPMEtpSWotNUdlNkNuSjl5U2x4YkhzTWNxeUlBZzk1UWNOaWZxQjhMenJvVVh0SHpBNjVNdWM4c2hWWVpWeVA1X2c2V2FLSHY5RFNGN05hMkFVOXBsdnlyUFFmTTJyeHRqY08tV2lQVDdQZUctOTlwV1d3N2JJRVlyU2thcmVzbmpsNXZsdzhFQjFkLWNIQmVUblNXNDVTZXV3eHN0M0ZOUmFYazBKWF9IdmVMVW9UTThDckZlbkVERy1RNGV5SmFySWFmMFVWSy1aNjd6Z2Q5RWsyTk1jU1lSdWhQWlc3R1NhZDdLY1RqTDBDeXRaX0kyN3RBeTloc0o2OFhRdXJTLWtibDRJS29ITzd4WEFJQXNVbVhR?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMVA5RW15YWg0b1ZqdVltdnJETFVFcW82bjJ3TmJQUXRMM01uMFpJTUliTUVkczFXVm9kdGlZdnBlR3NTR1FWRGlOck5VOFZTTC1UaEFhQmozd0EzZllJamY2RHBKeXBsTGFTMWl6QUVzRHBqWDdXaTRkamxhQzRaUG9DSFpnQllQUUtaMFpIR0tJYTNmQmJTVnN2cDNiNGtmZUlHdVg0bi1lNTZrY2JfbmpOM24wTlNKTkxGNFhZU20waDAzLTdGNDRsSm1oSVI1N3QyTHlpazNlY2tYRzQwTGFYNA?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNVllVbkwzWi1PdVRWcmQ4VjJEd0lwREZXdnBNSHBFcDFEWnctSEtqZVVEVk9WNHZxQzZYSGxwOU1aSkhQX3dtLTRxZGxabzNfZlJtRWhrVTlGYnpoYkdqRFM4SE1CTmw1QTh0eEhfSXEyaF9wMVlUUU04aFR1VG1heGQ3cjdWZ2EtYm9GVTZyZzQxNUwwUTV1c3ZRNTJycmwzSjFIZHc4T25mM3JLUmUxd09FeHNIT0o5UWowMVJIX0NOZk81SmJxMGJqMWlpamE5UFlVS0ZwZExUNGRUVU9CbVJfRFgzUVdaRDRqMExnRjRjSmJLSmJoQUNzaFpKMDFtYXg5eEZ0WkYzM0RoUnk2NGdsTWZ1Z9IBmwJBVV95cUxPMEtpSWotNUdlNkNuSjl5U2x4YkhzTWNxeUlBZzk1UWNOaWZxQjhMenJvVVh0SHpBNjVNdWM4c2hWWVpWeVA1X2c2V2FLSHY5RFNGN05hMkFVOXBsdnlyUFFmTTJyeHRqY08tV2lQVDdQZUctOTlwV1d3N2JJRVlyU2thcmVzbmpsNXZsdzhFQjFkLWNIQmVUblNXNDVTZXV3eHN0M0ZOUmFYazBKWF9IdmVMVW9UTThDckZlbkVERy1RNGV5SmFySWFmMFVWSy1aNjd6Z2Q5RWsyTk1jU1lSdWhQWlc3R1NhZDdLY1RqTDBDeXRaX0kyN3RBeTloc0o2OFhRdXJTLWtibDRJS29ITzd4WEFJQXNVbVhR?oc=5</t>
-  </si>
-  <si>
-    <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-  </si>
-  <si>
-    <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+    <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVDhlQmp2WFB1ZVZYS1Y1TzZEWkxhcWlpLUFEMXd2eXdELVRzSkVZSW5BR19rMlJTenpPS2d1Z2l1V2Z5VWxlRmpJaW1wZjJOem9fVjNMSlVKTFhZQTc0R05PYkxzbjRoVFFSVWt4aE16Y0JDM3prbVFLUUNscFpiZzdIRWw4TGRlWE1qbUwwQnJ5TmxsaTRZbXlzcGNnblhEOTJXZzVudTNHdw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSTN2aW1qSHhkQlJ2aHJNcHltQWxFaVlMZGk3MUNYdWk5YVRxdDc1WkNoQVQ0QjFUMHdERjNhd3kyOUNFbnJSVmdJd3psenZSS21Rb01DY1RLX2lTdkFqaHAzZ0RUekVFZU1zek1jRUotOWJ6T2dyQlN6QjFrRHY1Z0F2enRCUUtHS05TV3lMc1djQlJCeXlxdEhjWWloUGZhZjRMeDlseHVSUjAtS2NZWHdzY2czdm1USS13b213QXJtNHJPbnVldnhoNGNrNUk0bnZTTld4cy1KRUFoYVBnYVVxeWZoS2doUFRyMEtPRmlNZUhPLU43VmlFVUczelVoLXpYa0xYYkRSM3BWdnFPWk1sb9IBmAJBVV95cUxOWnZBMkpVRVNrOXFCcVAzczdmZEw4d1JrX1FvYkFXMXh6Y042dTdpQlhCVVQwLUNwZHF3YWVuU3ZidFl1eFM2Uk1HT2s3djZnWFYzMWl6NHlaYkpnRW9HSE9JWjBVWVpiY1FHbjVzLXBlbkNON09MYWVCenNVdXNPZXBlNE9BX2ZiZ1paendNOUVQeEp4SWZ6Umx3cXVCUGdyRFpmTWZ2M0Z2YlFIakNzc0lQelBoNVFWRmMzdnFJTmlGZVptMFFhSVNoZHkxM1lpQUIzUDZ0YTdJdVlOQlBrTWJhUExyblBRdklJMU5JV1g0ZmdCZ1pVWUx0YzJaUmdRX2tSYWNjWXZudnRJUGZ3cU9BX2VNVGxl?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
@@ -1342,51 +1627,48 @@
     <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSTN2aW1qSHhkQlJ2aHJNcHltQWxFaVlMZGk3MUNYdWk5YVRxdDc1WkNoQVQ0QjFUMHdERjNhd3kyOUNFbnJSVmdJd3psenZSS21Rb01DY1RLX2lTdkFqaHAzZ0RUekVFZU1zek1jRUotOWJ6T2dyQlN6QjFrRHY1Z0F2enRCUUtHS05TV3lMc1djQlJCeXlxdEhjWWloUGZhZjRMeDlseHVSUjAtS2NZWHdzY2czdm1USS13b213QXJtNHJPbnVldnhoNGNrNUk0bnZTTld4cy1KRUFoYVBnYVVxeWZoS2doUFRyMEtPRmlNZUhPLU43VmlFVUczelVoLXpYa0xYYkRSM3BWdnFPWk1sb9IBmAJBVV95cUxOWnZBMkpVRVNrOXFCcVAzczdmZEw4d1JrX1FvYkFXMXh6Y042dTdpQlhCVVQwLUNwZHF3YWVuU3ZidFl1eFM2Uk1HT2s3djZnWFYzMWl6NHlaYkpnRW9HSE9JWjBVWVpiY1FHbjVzLXBlbkNON09MYWVCenNVdXNPZXBlNE9BX2ZiZ1paendNOUVQeEp4SWZ6Umx3cXVCUGdyRFpmTWZ2M0Z2YlFIakNzc0lQelBoNVFWRmMzdnFJTmlGZVptMFFhSVNoZHkxM1lpQUIzUDZ0YTdJdVlOQlBrTWJhUExyblBRdklJMU5JV1g0ZmdCZ1pVWUx0YzJaUmdRX2tSYWNjWXZudnRJUGZ3cU9BX2VNVGxl?oc=5</t>
-  </si>
-  <si>
     <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVDhlQmp2WFB1ZVZYS1Y1TzZEWkxhcWlpLUFEMXd2eXdELVRzSkVZSW5BR19rMlJTenpPS2d1Z2l1V2Z5VWxlRmpJaW1wZjJOem9fVjNMSlVKTFhZQTc0R05PYkxzbjRoVFFSVWt4aE16Y0JDM3prbVFLUUNscFpiZzdIRWw4TGRlWE1qbUwwQnJ5TmxsaTRZbXlzcGNnblhEOTJXZzVudTNHdw?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPcjJHT1RUMjN1bnRiNExKMlc0T2xKY3dGWTBCaWt2QW9YaEZnV19yMl9uai0xd3oxWFFkclZCb0RUSVZiRzNoQW9PYThKR2tBV0VwSzJyOU1Ya0Z3RE1LZ1N3MXhYY1JqWkRoU25IQ0RxQXJ3cE9ZMDdrcV9JTlY3X1hyZkNkN2lRMGhENGRFcmlrNHJqTnFoanhyZmJEeEFvWGV6bkJrM3dISGpHaG9DOW9JUWNCcFJIaGppa3cwTHB2MklnVk9HNWZwUk5Gek5pY1BwVldLb2VCUkhrc0dv0gHnAUFVX3lxTFBVcWZtM3c5N3VLVFZ0VFJhb0xSLTZLVjVWdE1qWW1Jd1B1bGtEUkphZnlTNjVCaVJUdHNlYngtRVhtempvSjM3V0puMTMzZGVGejhuZm9nVkxRR3QtQ25mRFVjQUNvbGFBbkZqdG9pQzFVSzhDUmtWODZMQWYzWjVZRjJzdjlxN2FLX3daclVDNnNsall0eGRrTzNIb00weHNHMDNwM0pBQk4wM0lTQm5yX3BQRUlfNm5YYVNxcTdOeTRCc09kMUpGSWFxR01yWDczLXFGaWw2d3FNbk92RjBWQ2tvdVBwbw?oc=5</t>
   </si>
   <si>
+    <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQzdnLVlLd2xJOHFWaGxaMzE5UVFSUWNRSGotUU1QRTNnaGxjQV9CN3RxVzBvZGU5aUxrdGpiQ2hVTkpqMEVGS0xad0JwVWhVNDdiZWt1eF9OZVNqRE9RRHRFTGVmbmFPWDhNWVlHR0xjV2xsR2ZCd0JrcVNmaGdneWxibjJjdkhsMnNwWThGVlhiX0Jfanc1YVpZOUZqUUttZm9kbDlaNHEweHJpU3B1Y18xRzdieWd1enN3eHVEZ0lUbm5sLW1j0gHMAUFVX3lxTFB6djRKRmdOdXpUVDFzSWY1MUNpTlAya3VreEZfM196VENfYWhVZ1g3RUJveVlOY0ItV1RlellpRTJPaXJWdVdYdTFwRUtST2lCdlBTbVM2REFvYVpZODEyWm8zTGpkSXNESl9xdTI3OEdmbndpZjIyNmFudWFYTFozOWozTEdvWERVQmJTMUc5T2RDWU1lSDhSSk1iLXRiMTFoLVoxRDFwckRmXzRKcGF0SDNHd1I3MVpyOFNHc0ZVcjBmVFV1bnVXdXVJNQ?oc=5</t>
   </si>
   <si>
-    <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
-  </si>
-  <si>
     <t>https://www.alertabogota.com/noticias/local</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQV190TVQ0UHhYOWIxUGNuYTdTaWNLbW5xWUtBVFMtUEl4cmUtNmlTYzQ1QnNVUElkUXZfSFJ2MlgybzVjcFNTbXdDX2FWbDV1cWZ5WnpLR1Q4MXZGNGttTDhLWTJtNXlkenc3X01sdUlXbEh5X2dwRzJ6Vk1rWWRlZXNEVVpPMHJTS05QM0NsdkZGVm9jUjd5VG1aekdjdG1abE9OVXFQZTdDakxvN2pka0tkNWFuQUpVS3pMZGZxMDFqcUJRdWVyaGF2Uk9DWERYREozQ19fS01tNzNhUzZBOXIyOVBfazFjak1wbjN1U2FjOTk2YmhrSzM2eW54Qi1lUFRtQkpCTHRJSDJvcUxLTUhSSjdUeFkwNlE2SmFZS1dfU3JaM1NtRi1GR0xfRU5RZFE?oc=5</t>
+  </si>
+  <si>
     <t>https://www.diarioadn.co/seccion/actualidad</t>
   </si>
   <si>
     <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS18wNnQtbks1R2xqVWJPWG9ubE5wWGREQURGMy1PRi0tUVN1ZWxrMG1Na1BmRTA4aUlob2hwbEdnSTh1ZllTaXgwOERJX29kUy1UaUFRV2lOd2V4enp2bUE2QnBIRmpvbi1GNVpIN2dWRE1FS3BaV2hENFA1RlVRVmdRbVdUVDdNNi1hdUNVcjVmVXllZldCNU1pMGRZZ3E1X2NRdUwwbXV6RUJKUHBLUUdycHktb3JnMzdpNndJdDhLTmotQTdEVEtsZ1ozUWo20gHWAUFVX3lxTE1PRnZubjVMelJsTDBXR3RSWllXcmhNOUtIaEh1SkxpSnY2eUViQkRVZG5CMjRUV01YbHN6bTV0eVNwa2xxYk9KdTR0NnIyTmVEel9OQzgwUWFDMjVvNnY5WGZJcjRkM2VQT2ItRWRTQ0ROTjhMNkgycGN4S3l6WS0yNm1SSTB0Yk01X2U0R195b2I5NWNXZWhZcUxQbUltX1VXZHZEQnhmWktOdm5EeERnTm5UZkxxdy1EZndIQ3BNUnhHbjRGaXFlLU8xSzEwdHdTLW15VEE?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQbmd3SVJpUGFScGlabzdNY0J1UkV6S3RjMTBBX1g4S0ptY2hCR0pxTnY0RTcyYzZXM2NXcVZobXRCN1UteGYtMmFmclpBTDktOTdoLVN1UllpNGlNYXhsb1UyNzdBR1E5LTVLYXU0S0pSQTV5dGdUMDVfeUNvSDF0S0VNTWJDaTV3RTRLdWJZNE9MOTlyZi1NTFU2Y20yWjZLcVVFdDBOYUpkUW9NRUlBTDcweXNjR1V6c1RIZDZiYWtIZzV2aFhMT083MVBpaDdmQnZlMzVtM3lHSjNnV1JEMUlFcEM0UU9kNmIyeWVnUGJUeXdBMkHSAfsBQVVfeXFMTlpVazJZT3NxeHRwWllQd3dFM0ZsTDBEMldFRVFYTnZoZ2tmWkx6dzAtZVNzUnh2TWFtRXQ4RWtfWlA0eWkwQTNJeWlXWkF2NXRsUlRXd3RmREJRbmZjRTRneUREeUZ4ZzVHVmpCTXQ0d3dYZjVucnhMSzAzQ3BKZ2EyYzNna1VOdVNRbm1ua0pFRFBQb0dkMEdsbklyZ1BSTjhhdWpOT25zT1Q3b0hZMEhjRGQwNHRBZ3M5M29Jc1dIWkkzY2Y3TXdwWnRyeDVyYzJleXlyZExNY2N6Z290WFFScHJpVEhpdTNKTDNBenBpUjBXamd0ZWt5dGM?oc=5</t>
   </si>
   <si>
+    <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQa0s1c0hqMDkzOFJDMUtjbjhPcWw1NXhYSWtVMFRfeXhZcDVSYmJfUEtOTXRIN0FvaE5tZ0ViWWNCV18wOENXWXJiMThtX1Vvc0NLU1NHSVpiS1ZrS3hlY3RtaWdwdHFvelR0RVRuQjNISHFwMXFwaEhFcjNmazdyVjlVTGV0Njh0aU9Fczg4aVlHaE5CUkRPS0ZVaDVkdGtnZjhhT1R4em1RVlRLZ3dBbHVoSTNoTGlWQWgtRkpnM1RvSHc3eTRmdG13V0xteVlOaFM2SWFaWHpKdkNfYkh1Snl5UkRzcWhodEFuZUMxbHc1b0Fp0gGIAkFVX3lxTE5CRjlRbHFUdVRNYjV3aHhCeVNHalc2NE5XTkFrT2F6d21FQzR4RFZITFJxemdta29RTS1teWpNVFpHbWgwaXBIZENYNTk0OXVDLWliNW9nRmhubkZoQTVkSkpjOWZuSlJKN29XMEp0REp2RERWVDZYM1dIbnpOVUc1QmN2ZnlpRU45NDdGUnhPXzgyYmQ5WGlfb2g5ZElNVDJ0cGlGY2FEbHdnM1lyVUFNT19wOWFYOUFjZzRXX1M3MEdZa29adGE5RXM4eXJ5NWVhVFhmY0JFWjdXQk9NRVc0NDM1SVJWWmh6Y2p1VzRZSWRreURoYlNkTW5nal8tQ29PYnBZY0Z1Rg?oc=5</t>
   </si>
   <si>
-    <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
+    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPWHZpSkpIdjZKRXllSDdtTHd5dGw0LW9kaC1QUTFLRXJnYkNraHJvVkRMYzZlbzJkaURkWDJhUk1OQUlydkk0YXczaEZLWnhoV3JhT2xFbFJwRXpEYVA3MUtYR0t2MzE3N0xKcVVFVjdhNS1fbm1LU2NFVkc2d1ZOZ3JLNUl1aU05UFZEODR4dWYwNFk5RnJBXzdhTmNuZmVqZUNmYmlwU3BweWRzX1ZhQjRGVm1QaGx2aDc3V0Q4UlZheWg4ZlJoTTZoTU5GRnYwYURuVHA1UkpLSElMNHRTajhyUEZUOG1OUDNCVEpLVUJrZ0F4TGlqVHdFaU5Eemc2MlhNb2Rn0gGLAkFVX3lxTE9OVm9vTnJlSlp0anZ1bEx6T1lwYjMySWUxNHpwT18xU21IQnlQcUVMN0JlX0F1TVhwM0thcWdUdWVCMVFYSm02YmpxMTF0a3BXR29rNVVXN3BqMi1CdUlteW9uRVZJNFB4cWMxdDIxRnRVcW50NktsZmUzSTg5V3FZTGxvTkdQcWFodHd5SjFIWmFwVkZKaUp5UnAtMkxUTkN3V08zSkNJRklXYTV6TnhNMGM2UGRhRkNFRnFoNnVudThXWnpXbHJnZUg0bndtVWs5TlFnU2FkOGNZY2hvS1FhaE5sNldRdm9PTmVESmtObDZkblFRMWhBODNfMEdmVVhrUG4yQ2ZXSHB1aw?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWHBSeDA5d3p2OEN1Q1lGMHl6dEpxc002ckFoQ2NfS2xfNndBZWV2Nl92Rk03NTZaUmtPenpFSG51T1dpQWNsTlRiVmVBc0xzUUJHUEQ1RG0wMTgxaEIxQ3pCT0pzY1VxQ2ZTZTA1TF96UWtJYy1hTkZBdnliTzc4Y2N0VEtMM0VOdUFmZ080OVFiNkVKb0lkUTN3OTdQcGptYVpHWmdGbGpjTnBaelZn?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPWHZpSkpIdjZKRXllSDdtTHd5dGw0LW9kaC1QUTFLRXJnYkNraHJvVkRMYzZlbzJkaURkWDJhUk1OQUlydkk0YXczaEZLWnhoV3JhT2xFbFJwRXpEYVA3MUtYR0t2MzE3N0xKcVVFVjdhNS1fbm1LU2NFVkc2d1ZOZ3JLNUl1aU05UFZEODR4dWYwNFk5RnJBXzdhTmNuZmVqZUNmYmlwU3BweWRzX1ZhQjRGVm1QaGx2aDc3V0Q4UlZheWg4ZlJoTTZoTU5GRnYwYURuVHA1UkpLSElMNHRTajhyUEZUOG1OUDNCVEpLVUJrZ0F4TGlqVHdFaU5Eemc2MlhNb2Rn0gGLAkFVX3lxTE9OVm9vTnJlSlp0anZ1bEx6T1lwYjMySWUxNHpwT18xU21IQnlQcUVMN0JlX0F1TVhwM0thcWdUdWVCMVFYSm02YmpxMTF0a3BXR29rNVVXN3BqMi1CdUlteW9uRVZJNFB4cWMxdDIxRnRVcW50NktsZmUzSTg5V3FZTGxvTkdQcWFodHd5SjFIWmFwVkZKaUp5UnAtMkxUTkN3V08zSkNJRklXYTV6TnhNMGM2UGRhRkNFRnFoNnVudThXWnpXbHJnZUg0bndtVWs5TlFnU2FkOGNZY2hvS1FhaE5sNldRdm9PTmVESmtObDZkblFRMWhBODNfMEdmVVhrUG4yQ2ZXSHB1aw?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPNFFpY29QRl9XdnlhQmdkZGpwZ3NCSDlqSkdtMHJXdU5ZTzhUd01JZUV1MVItMGZWZmd5R19nY2l5V3lQVW5TdjdicGprb0pXaG10aDdPWkw1NTJTM2NOTUtKQThuUS1KMUlWX1kwQmZDR1RaSnloU25HVllwRGh2UHRRZ0dGTDZ1UnFxRkF0eVhiS3JKdW1YVUp6WDlDb2Vobi1EaUU0aG1fQXN4QWwzQ09fVml4YTIzUUxQZFFOaGdtU3BzSHNzcWhYbEVvSHc0SUZkbGE3Q1lYVnBwZ3ctTkZabzQ?oc=5</t>
   </si>
   <si>
@@ -1399,9 +1681,15 @@
     <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNTGNKT1ZIVC1RXzM0MUt3T2prd20zVjVOaG45cEg2eHJiRTVYQnhPRTQwX1VlVEF1VmV6WVNuTWIwMXFzbEw2cC1tRzl2ME11YXh2QUdoSE41dlNzQlZDMXhWM3ByZE40R3lhMVVoLXJRQ0dENHJZcVBZeEtJbDExZFo0NkRoSTFZSm5XVkJrVmZkZ2RRU2VST1FvWVlwMm1QM21tSjNXNjJsdGxjTmZqSkk5d3dDMjhETzZFM2x1V3pGNnNUeWFGVVNBZWwwU2EtdVdnN0gyMlIzX0I3LVF3V2h4TE7SAfgBQVVfeXFMT0NMSnh2NDNyM2N6NkNvc2FRLVdYS2xHRnh6cGlSLUpWOTQyeUs5NkphOHhDMTFrT09uSDlETHoxbXFvYk45el84eGMzal9JbTExU0RjdXczcDRkcHNoR1YtZ1VyUUlnU0ljU3JwWFhIZXloeGI3bWhpOThQRjdJUTJ3QS16UXlLN3hrZHFRMFotTXhTQzhtNk1rQTZkQ0haR016U0JPVWM3RUFwb0JFSW1naEFtWUU4S0NSSXZWUjJjMjNWb1QzSWNpSkdSM1JYUGRjcXNRSjBZRzZWR3E2ekNEemxIalhqVWlZQ25acWEwdGU2OTlHRXM?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZTVQT2p4UFNyUjFyYnV1M2xEMXgyQVpqZE9OazBzUjJ2bmw3T09zMGpGY0JxcXRaSGNCVkFGbEtsaEVrekk1dDF2VHFLT3UtYTF3WmFHd2hBTVVZYkZDSG10ZlNRQVBrd0ljSjRWSmI5VGkyMG1qMVpOZV9IY1FtNWpod0VKVklxR3loT0dOOFFXQU5iUlgxb04xUFlfNk9Xb1hjNkFlNmltQlRVdEc5LQ?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVGV3a0tQeW5uLVpJdlBBT3Rrc0NrUm9Va3pHY3NYMko1d1N4bjUzdjVYZ3ZjZWZpQ0xYak0yQVNLdFRsVXJxbnJMSVJVT3ZyaEZ4ZEZIU01RWVoyUHd6Q0hiNFdCMElNeXExYXVrQVJaQU8tN0RUMC0xZERQdFZ2aWo0UXQtZTZ5VmN6NE9YSjlhYUVGd01ycDBCaC1RMEhUcmk5TTdEekozS3g5Ry02SEVTOWprUdIBygFBVV95cUxQMlJDNFNLREl3U2ZaeXVGYy1GS2NmWlVydW1DX24wRE9NOVhBbzhqNWNzMmhTNEdTa0JFa281R1FVRUFfdjlUXzd2Nl8xTGxMb3JIaUVxOG1DTTBwRlluV1B3QVF6QTI1cEd1TTlVQlJiVWJkLWFFRFo1RlVsQjRMS2ZmTDhpUTY3bGdfRzlXWmliT2NybEFPcnRfaWJpX3UtazA0ekRpOFpOeU93TGNsOTV6Ynp3VkhKRnVPcmswemZHYnZNQUxrWHNn?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQazQzUk15LVJiV2RfaHdjdEJiYXRoNWhJWDRaZ3FBOGRwSWpCMS1QSFo0SzUxYnUtWDJKUElQLXY0Q1pmUmZmdGZFeUlyQmY2UnVkZjB6SkhCb3dkUnNKNEFUYndwaFF5R1l0d1cwN1lOMEFwaVdUTnhOYVAzU2VGck1xcm9fNnhJTGtjRUpOd2NDdGdvZVJkNzluRV9XVmRoenZNendGa0RVaWdVYWhPM3pYYVBsT2k3a1BRS05XNkViVzjSAdcBQVVfeXFMTVgydDBnaXIwSVBWQXRzZFlLWGkxa2x1TzBMNV9oZ1JyNzY1cWxaVjhJVHp2TDlOQ2o3LUpTLVl1aFV4RlZLYV9zbTVVM0t1eXJLQnZYaV8ydFBCSWl6WXBhajlLUlpESjlOWEFIbXZWMy1qREd0a0JXQ2lpelJqbEM3Z2dCNXFrYVhyajQ1cUNxMVpBWDJ6RzlVSFRydlgwazdIM3JxR29qUGVydFR2ZFNieWdxZ09Pal9nSFJwYVlKcE93OVFsUnczY3ZwLXhlLUIyNXQ2NUU?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQazQzUk15LVJiV2RfaHdjdEJiYXRoNWhJWDRaZ3FBOGRwSWpCMS1QSFo0SzUxYnUtWDJKUElQLXY0Q1pmUmZmdGZFeUlyQmY2UnVkZjB6SkhCb3dkUnNKNEFUYndwaFF5R1l0d1cwN1lOMEFwaVdUTnhOYVAzU2VGck1xcm9fNnhJTGtjRUpOd2NDdGdvZVJkNzluRV9XVmRoenZNendGa0RVaWdVYWhPM3pYYVBsT2k3a1BRS05XNkViVzg?oc=5</t>
   </si>
   <si>
@@ -1420,15 +1708,18 @@
     <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTVZGRXZlSDMzdUlmSHU1Z21OY2ZCM1pVVUR1OGoyTFpuXzVnZmIzaXg4bml1NlFrcGEyN0lTb1o1V0FYeTlaeWNtM0c5TW9IUVZBaDBLR053MVpiN1hXa3lDWWNub2ZDVzlhWUZkUDNkZWd2b09oMnhKWWRTVzlhdHBtOE1IaUVWNjNyellzUVdoM3h4X1lweVdrMmRLQUhFa1NtMi03NFRvcm9wemtuMTlHNURGLTBTanZpNkxzam9zT3FfbzVzVldXYVJrRXdQZFl0cVFRU3NDMEF3X2I2ctIB5gFBVV95cUxNdFowTkZuMEcyRGV5QXRtbFRCX1VpM19uWGs4dGFZUGpCUzNpNGxmTEFfVHdLREw0X3R4b2NyZHNuejNmMl9mUlR2QlFscFRyME9NUmpPZy1zQ2JZdmcyV0hnREl6UTBEdlVSUlBDNlVoeDNzSndNNms2ZUZrc0FUbzdKenBIampNNTJub3FzLWRSQlB1bkhIaE5sMnFYcGd2SlpHdngtOVJ4dEZid0VEMHV4MklTT0NBRVZONGtsaXBja0VZT3pCbXhYcXVpUG9XcjVpRDRKQWpCajA1c3Q1bUx2bGpWUQ?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n0gHeAUFVX3lxTE5ELS1vYi1fLWZ3THVvOFJJNmZ0QjlxWXRDZ2FQSVh1bXZkM2V2d2d6dEg0WkRvd2xZM1NYdFh5RzZDbjh0Y0VSVlJFTGNFYW5ydmdYcmtxMnFIZ24ydEhYZUJBZDI1Qmpxc0pldFZreWpFblQyZEo3UFUzcFFfRk10VEN1WHAwcWg3MWNVLU1zSC1vY2pQREVWLUVMbzQ5cUdITEhOeGVSSFgxRGpFNFJ3UGhndmVVMWVIdU11RlZ3RUppWFR4dTJ3UXhLVE4ydThUaFhsMXFFRURsUHRVZw?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPc1FBT3Q2R0VBVVZ6bHE4OVhSQzRMX1hNSkp5WE1vTmRnemJKZWR2eU9sVVA5WWJUWXY4VDJmSWQ2MW81eHQ4V2NfN0hVUkh2cEFyb0hiMEszZzVCUkZWYnAxLURNNlR6MlNnT3pkamVUeWRzZTU0TDBlN1ZMNzUyYWxaZjBDZVd3NkdKUFFYWTJHc1cyWmlFLXdTWE5xZUpwNFQ4X2VUelpid21UVWlkSUdfWjVNZEp3dFHSAc4BQVVfeXFMTnN6MlF5T1FyR3pzdnhqaXVrb2FZMHdZSV8wMVNXUVdyZkxzSVBSWW9lN0MyLXJPN0FnRkl1aGtGd0IxUGxpZ1B5X1FGWk1ybzhHSXVBOGc0MndXMnRkMm9nXzFuUThiSzBqWEF1WWVhcGROcF81U1ZXMDZiRzZLOUNNdmZyNnBlbkI1d09vZEtDSGxidFg5VS04bTBhdXZzZHFfTExXYXJMN2lNc3lSWndzdUlSYVR6aTE1d1FTamQxYXRfdjAyVlNoX3UyQ1E?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQUTFWOU5YN2xQeER4OVd5Vmp5VVRmWFRnb3pZczAwck54RUljT3RTMnMwVUdkVmN3TWQ1S0N6ZldRQWQ1VTUwcDFsRXQ2ZGNoQzhpOG1mNGRkZ1JhQnFad1lNc1V1aFQxbEZaM2dzbzRIYWEzQXpVVDVYRXRPZGhqc29STVI0VkhPQVc0bVZHWURGTnhOQjBvekhwUS1VaXdEQlRZRm90NkhrN3N3blMzadIBtgFBVV95cUxQcXNDNmNEOUd2ZmhpVTJYR0xMSEFHZ2RnV3ZTa0h6eFRZYVdiTDJEbzdlVWRjRXNSV0thc0NiVUdGUzduZDk3T3YyVzNNRWtiUVJhemFNVk9tUFJMZGtuN0pjeHJwUnpBelRvblRtd1hSSFREZXlFa1hjUjZKSmFQWjJfOGtZWWRZdHdBTy1aV21wUnJhdDBIc19GMEFVbk9jamRVVUttSlBwRjNxX2hnSWtaTGZ3dw?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPTm5hZnc3OEdNMzBqWWNibDNQeUJfaGs4ZDI4R2tZSFRmRWpXQ1lJXzk1VzE2RnNyWTdCbjhNcHJUbmpQc3dVVWlNanRQZjZScjdRc3FVSWN2TjRCOTUyNWRsRzlOT3k2LUZzR0Q4OHFTb0dOQmNuU05rdGc2VUJlX3F4bHlQSUF4a1liR2hnYkpFdHZPeGFSLWtnVDJYZi02Y01LbllmSnhaaTU4SmhHQktVXzU4SHpuUWF6M0wwaWtFNDc3NWlhMmNnclBPY1lSSXo1MC1HR2t4UlAtYlZmdTY5S2ZZaHM2RGM2YXVmdWFMVlc3aWx4UmlSRDI2WDZPOXfSAYcCQVVfeXFMTzdzYmVXMDdMT3JkU3RDQW9acXR1VmROSW1peklfZ1JzQUVKdXNmWmRNaUllVFg1M3hGUEZlWjN0TzR6aVRsQW9IZVhsTUJiTVU5QUNvaXBzTTVKbGNwcWU0am1HRmJObWlJZkRvUjUzekFUcEdCdzNWSzg0YmJKelRrb0Jfc1hGNkVvTGFHMlRlVEFXUmNBbVF1czR4R1lzUXhDSWhheGRDZ2ZQdlVOTURkNjV5TjNGMjBYdkFGcmpqUENjR2lvUEJ4TmpqMklreVFZbnZ0ZGpMNTljWXFuUzF5UWs2VmR5QkZwb0pMWFp5aWF5UWNGdWQ0czJYUjRFNWRvd1JYZjQ?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQUTFWOU5YN2xQeER4OVd5Vmp5VVRmWFRnb3pZczAwck54RUljT3RTMnMwVUdkVmN3TWQ1S0N6ZldRQWQ1VTUwcDFsRXQ2ZGNoQzhpOG1mNGRkZ1JhQnFad1lNc1V1aFQxbEZaM2dzbzRIYWEzQXpVVDVYRXRPZGhqc29STVI0VkhPQVc0bVZHWURGTnhOQjBvekhwUS1VaXdEQlRZRm90NkhrN3N3blMzadIBtgFBVV95cUxQcXNDNmNEOUd2ZmhpVTJYR0xMSEFHZ2RnV3ZTa0h6eFRZYVdiTDJEbzdlVWRjRXNSV0thc0NiVUdGUzduZDk3T3YyVzNNRWtiUVJhemFNVk9tUFJMZGtuN0pjeHJwUnpBelRvblRtd1hSSFREZXlFa1hjUjZKSmFQWjJfOGtZWWRZdHdBTy1aV21wUnJhdDBIc19GMEFVbk9jamRVVUttSlBwRjNxX2hnSWtaTGZ3dw?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOckVuZWpkQV9QTnd6UzZmSXdvNl9xX3plZHNIRkV1X2liZTJmYjRHY05uVDc5M09nekFlMDVwVS01WWtsZmstN1VtZkc3M0E5d0xGd1lRMzh5c0Qtc09iei1pVmdSekozWUVLenM5YVRtTms0R3BJdEZocU9YVE5wUEo0UVdLRnQ3cENPWm1ETmhsbjFULThLTVRKanQwSTVvM2hCQW5VODlJejZkRkpYUHpzREpEeDY1M29UaV82cUZQVFp6OEpmRVlxRTBzQzFUcWlPbTVWOVQwSG9LVF9KcGhiejZzTWt2S05KYzdyeDgzbThZMmhkdUNQZTBBdGNHN2RletIBnwJBVV95cUxPOTVVOXMyRFBNN21yQnZ5RHkzMTZOMVYybU0xXzNzczIycm95cHdBcEFKc0d0VVlLT25PYWJkVDhnbUVMdlQwTHktNlJqNG9EeXFDQ1RSaG51Tnc4ZXlsWXpVYzZSZWl1MXVRQVdabXI5ZTRUYXdQblUzWmN5NEE3VW1PRF8yNWdHcjVsdXZ3STF2cUJlenZHbTluZkpKYzRvSlhDZVlNVWdnVjBqZEFuSHpuQnNwdUVMMjBkMm5JNUZVZkFfOHFUMHFpeEdLWGFzZ0Q0V0pZdzdrMXdpUkRsRVZQRVppU3hnTXZlU05GRWZlZ3hKUnBKdFlWdy02cXJRdE1YWUFsSDRZTXctSDRhSkRMMV95QlRPUkJIVV92Yw?oc=5</t>
   </si>
   <si>
@@ -1444,12 +1735,12 @@
     <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOOTZUMTFEd3FHU3FvYjlxT2c1M0FVNktocG9QV2Z3YV9LYlNIUU9jNGlqZW03SEVoZk9MVkJZc2VLWGVBOE42UnFZSlI3Mk1sZEJLSUhYSHZYaFByanlMMVR1SnJHeVpoRHppVGRRTWZZMmxkNkpBQXlaWXNkR2h2by1najVOd1gzS09hdmRrY1VWbUdMaExobHREblpVdldVU2pCSnNMcER1Q1htcWhsVw?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdjc0b3pDbXMxTXJHLTlMN1B3T1FRNG4zQm9ZekVxUUphdkJsOXkwQmNLYy1KUVVwQmR4UkEtOWpMWjgyQkduazN1cVh1SktyY2hqTEp6VGNNLTY4bUtYM2Q1enpMQmRGcVI5aV95ci1Lb1FTT0hlRE1mbEQxWUNfNDRUTEdTQlRZQzItM2sxNkp6UFppYjFMVVlweEM?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZGtNeVVBeHQta1Zhc2Z5YVpZR09qcnJZdnZCOGJ1TGdwbEktWVQ1UElPWmI2bEFEZUlOUGI5Z1J5U053TlBHcHkxclNnYlA2VU8zaWMwN3ZXdW9kdW1wTEJ5akcwcC1kZXk1eFZnQTlNT3JsUnRlRGNwTFpuNFZ4SnowUW5qQnhacGxHSTlCUXdRWDBXRjdHQUd1RGtkUjFJOXZhNmZkWXdfd0I3WGdYcWllRThlRkR4LXdQa1JNbDBlN2pyOUtJSU1zbGhob1cxUWhjeE03aXVJYWpLaTh4QmpyZGpXOVQ4dHJURUd2MWdtb01wd3hISTladGdKbDV1NmfSAZwCQVVfeXFMTmlvd2VmT04wQVNQWEh2LVQ3WXF6M0hZZU4wa3RKa3dUMEU3c3NPQmhONUoxbGNQNnJPR1dsUWp3d3pVT19vM1JoUnZNTWZIR1hWcjZXYXBNcVQ5OVN4dGR2S2dfbXZWclFFeU9GNUM2eEY3OWR5OWo5OUZTeXVSMWhKTHV0VGx6RFc4eVktSGFXdGJwa0FNWTd4b3hyakQxRWNJMXlOUjhiaEhtbXZhWkhDUmZ3ZVVTNGNfTEdUZjl3Z3VPT0VwVjZ5OHBOT0tEVmlZbTFKVUtXcU5JaWN0MnVpNWFLdmVtZTlaQV9Cd0Y3RUc3eXI1R3hrNnRXVnZELVliZTRrVUNaYXNsdFJ1Q2ZkRFpRSnhYcjl3NGE?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdjc0b3pDbXMxTXJHLTlMN1B3T1FRNG4zQm9ZekVxUUphdkJsOXkwQmNLYy1KUVVwQmR4UkEtOWpMWjgyQkduazN1cVh1SktyY2hqTEp6VGNNLTY4bUtYM2Q1enpMQmRGcVI5aV95ci1Lb1FTT0hlRE1mbEQxWUNfNDRUTEdTQlRZQzItM2sxNkp6UFppYjFMVVlweEM?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOVzdMSEFIR2ZQbHZXX0RrN1RXakRobFRlMTFXbG9vSUtLUzl2VGxwbFhvUmlPZ1FmUjZVYVZPcmREdlhPNExPSnZIUjRfOEpfRDhveEJmdlVxcDh6QThJUzNFcHk0TEtVdnVHZ2trbHFjVlFhemxxbEtfQnlqVVRyTVI0MTVCN0VKVE0xQmxRSTdBT3I3N1ZfeVJqSlFEdmFlck53ZlhYSURrUHZma25BQWVHMWhIbFZBb3dvbmtjSHZad0NVa0VxTWE0aFBpb1ZpSXRwRl9pMFJrN1k0T0JGb01zRQ?oc=5</t>
   </si>
   <si>
@@ -1459,12 +1750,18 @@
     <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxONFV6MExpS1dkLVVGbVJSbkZmVDVFdGNUeDU2T3FkTlE5Nk9MaHh0Mjl3UWlwbDE2N1lmcEI0djNPTTJrQ0FEQ0p3ZmlwZ2UzeGk4MlhGbXhMYncycFdWNlJhaVNuN2J6TFhUaUprelZ2NHJtbzZIOE5GUFNiZWxJN180cXJiUjZ0SFNFN1c1bWg3dWZhOHptaGpQMm0xMmZLZjFiRWxmb08zRDJ0eTR1X3daUjh4WDR6Z19LZFJSdm93SFlKZFHSAdoBQVVfeXFMUHc2bFczYWNlZjRFNnRldVZ0aUFuakFMcDNjZWo5Tkh2X1FYY0ExSFg0blE2RFNkaDVKN0hIMjNXX3lMWHBvTFZYdGpyeDYzdkp6dHBjSkY5ajQ4TU84ZmVMTTR0SlRMZTNPMG9PV1gySEFYNlF0SmN4Z2RnZElOXzNicGw4bC1KLTBMQjAzQnN2OWRqNTBWU3hYNXpQNjZmSmE5dW9GR1FJQ0I3MUtLS3lzdjJBdVUyUVdWOERzTkt2ZlN6ZnBIMVVFZ291cXBfRFd4QUlxV0lwclE?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQUHU3TUU3MGxQWVkzVUQzOW1sQlZWV1hyYm1BNVRFTTJudzF6LUhvSXV1RXRWUFNTZXFRaHFqMFJPS1FvS19lNWVlUGxrRjNoYlVtN2tKeXlPRUpaajZZZlJpZzZHRFpURUVoRkdUSnp6X1kzT2hvdkVsaldUNTAxdmxnZlhRcUZNZTA0OWY2ZXBpTUE0SDB0QVZPaU5ZSVc4NlAwS0VUVVMzSEZ2MjVXYnB2OTlocHJkUWNXbXZ6U1HSAdQBQVVfeXFMTXNRdlRzM1RhNnNzMVJpUjIwcGpwbW5YRzY3Rno5UEJLZERScGk2eTBZdDdRVDBheEtlcExReDg5SXhpVTR6RzhmRWtJQkhSbmFWZkVEaGtMMzhicWhDb1B1cmZUOThOWGZuYWxhbWZPQlBGdkVtS2N5ZG41Uk0xXy1DeDl5YzdPVElacHk4LWlPV3dNSWtyMG5QcTljUThlQVEyTDNtRU1xb1MyaWNXNTF4M2QtVk11bWRFRlNIZTlpSEV3by1KYjA5czdmNFVZU1RpUG8?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFh6ZDVETFROR255WTE1dm1uNXhtaXg4aGNjOUtZblZDbU9RbnFhLU81Z29yVDZzeG1HcFpjeS12UFJNX1lSaXRRVWIyWUFyWkMyaDJobmNReFhjRzREcTFBTGFsX3RwNDRnUHhydUtWdEcyR0VFeVRXUlg5c0hJZlhydURCVG0zcmd0SkNVbk5qak8tbkJGWnducXNZV1hOUFEtSHRWbmVvOFRXSFM4aG5zbU9SOWJ2Y1RTRGNB0gHSAUFVX3lxTE5jTVU1LW82UDhqRVdjVnNNQ29LZXpEdTM1a2NiRlNUaVBBUnVCZ25hamlJM3RiZW9DNzBMYWNBanJaemVuaEdzUUMyOFljN0t3SU1ac0ZRNnBLWm1LNjAycG8yUFRTZllRWVIwTWV0dTN2TTM3WEt5ZWNNWFlia2VvMFdnNEZtMTlDSWhwX1ZLc3hCTDlvT20zd3ZJUEE2UVJVc1Z3bGpnOENxSWNYcExDX0hiaGxTMnE2dXBSaEJnRE9Od2VQdk1vQmVCUy1PdjlSZw?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPQnZ5RGlTQzl5ZXdNM0tERWdMSXVqS1FkSVFYcS1JZE9BYVNHSzduZTlmTks3OURGVk1QZjc3NmctbWN2d3hMQXREaVY5UWRhM3paZmRfUFI5MjFob0hkelFvaGoyYWVxdC1KRDNsTWVvZU9sanIzbEFrWjNzUDVfdTYxV3E1UHRVTll3cm5KR05XZkl3SHlmUHZnZFZsUUFsXzF3Y01GdWRDSm93aEM5TlhZRmhhYlloWmVZczVGaXJkbkpCeExUNV9TRU9wQ25fVEZWOXZMellIOEnSAe8BQVVfeXFMTkVrcGVHbldsS0t0LXJDR3dKaUt6UHEzclhuUG15SVp3R3lRWWtySzlzbXA2ZWRNdXJpcXlBVnhZbVVVVVc5WkMtY2d6ODctOTQ0TFN2ZF9HZkJHSXlzZUpWZjBRUUNvUC1jV0p5am9yYnFWVXVVU3haclJzM0lfcWxiTEh5YnA1QUtIR0RIWEVHdlRHRXBtb0ZydFBsSDVoZVBjYTVvZ2otZzNmelpXbERNTzFLR0JNLWl5NjIyWTliNFpSNE5ndHpwMlRXRHplbUZ6UFI1Um5ORmtZWnVCeDdmYUxXWTJRd19KMG84UnM?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcl8yMC0tR0ZJZXk3NW9tdGs1TTFMTXQ4Z3pkamhhZDFmbURaTWRWc3dvMXhLTUF1WlJaQ25kZmF5eU4wQUNuMy1OQ1FKM3NFOFZrblZKMzlxNWowSjd2a2EySTZsVzNEWTNHZmtqd3ZBU2ozMFFEZ29LdF8wb0Nvb2UzZzQyNzFWdlBwVTZ4RF80cmxwd2NoZVdXNDhlOGxVMENaSnA1T0gzRFJrOE1nRFJaekZ6allTdnc?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNOHZRdHo4NTlxNUgtRl95X2V2MGJBSDQ2RXlncFQyb1FET1o2UV83MmtZc2ZMRG41aXNCeWxiNUVhWnJ2ajY4WDRzb25OWm5ZcU0xWlJKN2Q2VnZlTUprVzh5QWJNb2xaUnByMmFLN1V3bkpQLU9ZbGVsQUtvUWFSbERMek81aEhPMFZzdXZ3dElzLWQxcW9kRi1xTWRnN0pKSzBKNEw2aUVMaElQZHBHcVh3?oc=5</t>
   </si>
   <si>
@@ -1474,34 +1771,34 @@
     <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcl8yMC0tR0ZJZXk3NW9tdGs1TTFMTXQ4Z3pkamhhZDFmbURaTWRWc3dvMXhLTUF1WlJaQ25kZmF5eU4wQUNuMy1OQ1FKM3NFOFZrblZKMzlxNWowSjd2a2EySTZsVzNEWTNHZmtqd3ZBU2ozMFFEZ29LdF8wb0Nvb2UzZzQyNzFWdlBwVTZ4RF80cmxwd2NoZVdXNDhlOGxVMENaSnA1T0gzRFJrOE1nRFJaekZ6allTdnc?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNOG5Za2d6dXAtQzZJMDZoYlhieUtZb3I0OXh4QlFIeWNoRkIwMGxlUmFCUkpjZ0FyeThvYVprUEFpQXpQc3hfOVJfcmZOdk81QlhCTGFSeVlieUstcDR2NkozUGlEUnJ1WHRrUVh2WFRZQklfR3ZxM19UWmlka3B1OG5xY2tKMkJONGJuVkhyeHh1RTdhbUJ1cktib9IBmwFBVV95cUxQVmRGQnY2UkxUaTI2OTNUNzdOSTNoX1FmUE82azZ5c21GdjZHcUU5dEh1SVFDVTJ4M24tM3pfbUVEVUxTUEhRblFYTS1oenhXMU9SYm1GS2dHN25yQi1CeVlPcnoxdU9ocF80QzN1clQzcEJKS0JHc3d5dllCdVlmWE5CQ2c2Qk9na1hianI1ekNaSXQtSjB3X2padw?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcDl2Z1NjUWM5d3VaOUZWRjNWZld1QngyQWlmbGFnelB5ZU4tNGJISm5KXy1aN01uWERNaVQzUGJmSWJFeVNxSjVTLVhRYU92dEVia1F2TVhvQUxmdVdvd3BRLUZLLWdYNkg3eUNKd1NhTGlwZGpVazdZOW9OU2RBLXhYYk5qcUpmSm55QkxRem55MUxQYmZjVUJSSThyU01XbGQyTTlyQnU5cFJTNnVmNXpvMGY4ZGVjZGFzXzVhVXAzZ2PSAdcBQVVfeXFMTUJvMXgzWXo2cnlEaEtYNnFCN0xHb2ZrZlp0YS1fV0gzbl9PanE4RDFNLTNMN1FZcU9kak55S2M2OEd2d3ZmU2RPYjRZWDlmR3NmUWxDNEQ2am9jTlB2SzI3SG9KQ3c2NHU0OWxJYkRYdWRMUTh3ZEs4ZjgwTGdnanA2S1RxYmlxRFVmNnRKTGMxVWwzSzczRTd1ZFFEYVJWd3ljbmVKU1l0VjZnZ2QwbnN0SmozVEV0cTJzbC1yQ3g0SUthMEk1aDhzeF9MWENqRFgzbTNPYWM?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPajQ0NUdTQzVVQ21yQTBXYjhlc1o3NDA3aXRMaEhIWHVPN1ZOQVN5UHZ4OU1Ma1RGdlVlU3VkczhiVHkxbEJPdUxKeHY5RUgzQ0NNTlZMNkJjSl9oeVBQREZ3ek02QXd6UlhDeE9NMDlJdEJMb3ljclhaeEZVTEhDOEg0Y3hSdU9hUWlFaXlmbXJKWGFXQXNxS0k1Z0tlanBHZjlNY2h4T0JHYU5ObXh3TUdOU0ZkMkplNTZn?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQak9ISWpvdmIxWlZSNUlZQ2p1ZDA5SDRYaWJWNFhFcDVyb1dlUm1PZ2VycTk5WFpPc1NOQlg4SWx4TDlsWTFSbm15RDY5X2hNSUlWaDJ5NElNVW9ZckctMFFZS1pzaDlTMzJyT2hsWDRQTnNBeXdRVDJ3cWxST3BfaVoyNnFMdEl2SkRZd3hTdm9OZFVKbFdBbUdGdzhtaDRhZE5EdzdPYmo5RTJCSWo5U3NXbUlVZ2V1TUZ4U0JjT0JmOGg5UG1tXzhGbVk?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTjN2Wkl1aXB1Wi1DX25OQnZ6amUwVGhLenJTU0VQZkpwZW5zVUxwbEFZZFI4bG4yMS1Qa2J6MWtaYjRLODBfSVNaNktKbWljNVRMSU1uckx2ZXhyVWZ1QlJmeWVvcjVLQWE5cC1lclVkcDNFMlBnMWk1dFF3VVdEaW91ZEFGdG1JU2tRcHk3VGtnOER4MDRjRWQwUzlRUXBRTC10WGg3VkRfcHlVSkFvTUxyekwwMVRVdjRlQ3kzd2tZd2EwZGVZ?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNVmlPaF9SMDVfSXIxa05XNjBTd0NscTdOYTh4SEtlRU9QZGItVjN3S0Uza3BCbklvdzd3YlYxeHdGWVVIWXpxc1AzLVF4TzVzUlV1WlVjNjhvQnAwUkRJaURBZ2FqeDhpb0Z5d2d6bVN1Y3hNVE5IakpNUk83X1FLVUJTdG5MbkZHaWJCLXlfQ3pWMkVrUi1zdUk0Tkp6SDZTVDVvUUVLY1FoOEhnU1JieXplX1B1eDJ1VTZRMjZoNlZGUXVtU0VRZTV5eFE4S25yUXEtVTUwb3pTVlo3V045bjNvdENRaWlJWllpMTFjTnVCMVBSdlE0Z1gtU3pBRk1scWhCaU1PRdIBjAJBVV95cUxPc1E4TmdZZzgyZU5xVUZoeHI3eE03YUc3b2RKNzk1M0w2YXE1UVl1a0ttcWZ2WEh1bzdGU3czNmNNbXc5bnZHX2NhWWY4b1NQVTNfV2ktX2Y5TE5uVHp5VnBneWlMQXhQR0ZoUWs1Z2xBU25FNW5xZFlMQ1FGQWk2QVVud2w4NkU5N2ZNOTVfUGptaVkzR0hYUEhjVHUzN2ZuY0Nkdmo2NDc5Y05zVjcxU1liTU1aRjIzeXB6ZkJabHZTNko5ZXpxY1RoNWdjWGJER05HSmdyclJKYVJUOXAtSlRoU21qbU5lQkxVZEJYTUtJS252Q000bVJzVEFuWGtGMEhKWm9Pd2JCVjk3?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOdDBneDZDSVFGTEdLQVVyWWJrazBhb2R3ZzZWb051Rkd0MjhKWU5MWFdCVVhNV1JVMlczeDl5elhqLTl5Y19aczFZNmNrV2xKMFdjV0NTWE1RMHplTU9PbzJDWXd4TkNjX0ZrQ2o2ZXRSYVRJT3RKZU1xUG5odGFjYm1BeXJfSkF5WDB1SEZLRWJjSzdKemRXbWFVWGZsaHVONXFkM0RPSWZ0VmRRN2NwenoxRUNrOFhPbmExeUVrUXRXczVfem1iaXdjSTBIR0FoUFpRYUswN3ZFYUlGNFpJZXp1UjJ3bUt0UEVuNnEtSm5sVzFt?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPajQ0NUdTQzVVQ21yQTBXYjhlc1o3NDA3aXRMaEhIWHVPN1ZOQVN5UHZ4OU1Ma1RGdlVlU3VkczhiVHkxbEJPdUxKeHY5RUgzQ0NNTlZMNkJjSl9oeVBQREZ3ek02QXd6UlhDeE9NMDlJdEJMb3ljclhaeEZVTEhDOEg0Y3hSdU9hUWlFaXlmbXJKWGFXQXNxS0k1Z0tlanBHZjlNY2h4T0JHYU5ObXh3TUdOU0ZkMkplNTZn?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQak9ISWpvdmIxWlZSNUlZQ2p1ZDA5SDRYaWJWNFhFcDVyb1dlUm1PZ2VycTk5WFpPc1NOQlg4SWx4TDlsWTFSbm15RDY5X2hNSUlWaDJ5NElNVW9ZckctMFFZS1pzaDlTMzJyT2hsWDRQTnNBeXdRVDJ3cWxST3BfaVoyNnFMdEl2SkRZd3hTdm9OZFVKbFdBbUdGdzhtaDRhZE5EdzdPYmo5RTJCSWo5U3NXbUlVZ2V1TUZ4U0JjT0JmOGg5UG1tXzhGbVk?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPZnFRNm1qalphMGhIaGdYT0hVWUFDUlZmbENKeGd2ZkkyaHNkRzlXU1ZleWtsamdoNzdZRFkxWXpwTU04RFQ0VWZScUlxWkFMcklPVTJEVEZ2UDhMNVdUdTVOQl8tdF9NTlZVYzA4YmFWbkpCNV9Xdkpod2FvcW44cEcxTUJPWlBCT3lqQ3VKZUpUZ3pkVG90a1U5bmpaYmoxc1lsRlVQNUt5ZFlNNnhiUnMwR2xITm94Ym5LXzJLVWJHazRtN1FPd2xLWdIB5gFBVV95cUxORGdBSHFILTcyZm5VVTVEOFFsQzB5bTV4aUdWT280QXUwREctNC05OG1qbE5oazJQZ3N1NENlM0J0Y1hwSFYyN1UyaU15dTk5Ty0wVTdJNmQ0dDYtTlhnYk9pMTRRRlRpYmw1d3Y5Z2lmWm9tR1pUMTAtZWNhQ244SVBPMm1DLXVmQTZvQ1U1ejkyRHlqU2hOLWxfeGFfaXZJbUQ2N2tEbmplSXhkYmxqUUdDQWYwdGNYVVFBN1JyZm5MMTJRTFlmNHhxajg4UGxnUTNySDNrWUJmaXNqUGJhdkFIRFY0QQ?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdEpCWHhRQ0JwdHNjV1BoWnNrWk4xWnFFbUQ0QzY2dU1XZk5TWHNyVk9NTlJlaVZ2MTlFVDk3MzNVWHFxWUFZQ3A0UVZHYzhPWUROMi0xWE5OOHpLZEhIVThRalhrOEN1MEE3U2RVRV94bDJpbjRiaUdBbWtfWnlaZ3RydVFtQTdQM3RVSE1qVWRoX0tXanBqQlNqX3RrWVVDMmpzc05JdmlJblFhSTZrazNKb0ltVEh6bGhudjlWQ1VZcjlRZllSWHBGaW01Nmd2dEdTelNRN3g?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNVmlPaF9SMDVfSXIxa05XNjBTd0NscTdOYTh4SEtlRU9QZGItVjN3S0Uza3BCbklvdzd3YlYxeHdGWVVIWXpxc1AzLVF4TzVzUlV1WlVjNjhvQnAwUkRJaURBZ2FqeDhpb0Z5d2d6bVN1Y3hNVE5IakpNUk83X1FLVUJTdG5MbkZHaWJCLXlfQ3pWMkVrUi1zdUk0Tkp6SDZTVDVvUUVLY1FoOEhnU1JieXplX1B1eDJ1VTZRMjZoNlZGUXVtU0VRZTV5eFE4S25yUXEtVTUwb3pTVlo3V045bjNvdENRaWlJWllpMTFjTnVCMVBSdlE0Z1gtU3pBRk1scWhCaU1PRdIBjAJBVV95cUxPc1E4TmdZZzgyZU5xVUZoeHI3eE03YUc3b2RKNzk1M0w2YXE1UVl1a0ttcWZ2WEh1bzdGU3czNmNNbXc5bnZHX2NhWWY4b1NQVTNfV2ktX2Y5TE5uVHp5VnBneWlMQXhQR0ZoUWs1Z2xBU25FNW5xZFlMQ1FGQWk2QVVud2w4NkU5N2ZNOTVfUGptaVkzR0hYUEhjVHUzN2ZuY0Nkdmo2NDc5Y05zVjcxU1liTU1aRjIzeXB6ZkJabHZTNko5ZXpxY1RoNWdjWGJER05HSmdyclJKYVJUOXAtSlRoU21qbU5lQkxVZEJYTUtJS252Q000bVJzVEFuWGtGMEhKWm9Pd2JCVjk3?oc=5</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTjN2Wkl1aXB1Wi1DX25OQnZ6amUwVGhLenJTU0VQZkpwZW5zVUxwbEFZZFI4bG4yMS1Qa2J6MWtaYjRLODBfSVNaNktKbWljNVRMSU1uckx2ZXhyVWZ1QlJmeWVvcjVLQWE5cC1lclVkcDNFMlBnMWk1dFF3VVdEaW91ZEFGdG1JU2tRcHk3VGtnOER4MDRjRWQwUzlRUXBRTC10WGg3VkRfcHlVSkFvTUxyekwwMVRVdjRlQ3kzd2tZd2EwZGVZ?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNSmpSM1NzR3NJZ3plTzQtYTRZTVl2LWdBTjhWVDllTTJNdnJ5RGhoaTFEUFZZQlBCTGRFV2Y2TGplcFhjSU5fd3R6ZU5QZjFqR3dVYXIxc0VPX2xLaTlqOFZhRFNEaXhsdjlnMXNUc2IzdmZjUVlWNzRVRVhlS3hCeUdaLURhamxTUmhKcGRQVGJEVWZHbjQ4OGR5aExLQy05YXFqbllEcno4SW5kcXd6MlFVd0Y3VDNERW5reUFZZThQa2RwNUFBN3FILXZ3d3VqeEdIMW5Zc3Q5V3FEeW9vRGotM1gxbklRVHh3TNIB8gFBVV95cUxNT2Y1YlNyMWZCemZJLUdUMEYxSmw1REY1UjM3WDJiaXloZG9CdERtUEp1djV0bTBUNW45WlFCSTRVSjExOG56UlJZNmZHZFV1N01ZcEJvdGtOMHJNMUpIWDBWSTJTWUFZNDFPY1RUS1ZybnVLWldUSTRRaWM5WDRyckFBYjdnTk9HUGhqZllBZ0VBSDNDRzlWR2hZVGdBNTFBZnZHUThEc1E3c1NLbmZfb09wTGtXcFNVVVp2LVhZeTFjN0NWU2lBLVQtLWNJSU1LQVB3OTNUMlBuTWt6Q1laZTNVRG9XWkpFTmpwX2NmcG5hZw?oc=5</t>
@@ -1510,9 +1807,6 @@
     <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOaExPYlVrMlVVdGdIczJldER1T2U1V1EzS212dGl1eFFDbmpRUlpRdXFuWVh1RXFESWNpV0hRVDhkLUtJN05lN05sakZzUHdLdnpCWWNwNFgzOUNiSDVpSF90eHAxTnNIbTBwUEdieUkyaE9yNEYydVUzOHhjRFA5aEQ0X0p1MVV6Ry1yZkZWbVM3NkxBNHZ1M3FjRURwQmo3VDhKVEplLWo3ZlRBRm9FZy1CVHktY21WQ0JLZ2lQT3JtNVFzQ0ZsU2Via9IB3wFBVV95cUxOc2hOSmFjNGU0ZVlCN0NfYWdoMzJldjlscGZQLWdzY01PYTVrSW5QMzZOek9VTFdRbXk0ZGU1RVo0OEZsUzRpbS1sUGVnanF4YUFIZ1F6Ni1rVjRPT1NDOHdFZzJKcUhBampxal84MnFnMW5vSG9tNzFxVVNZelA1cnN4b2lqN0RhYUkzamVMMGVUMXNmQ3FLTmhXdlhKWC1kdDE4LURLQ3FKWDMweUc0eUh6eVBiWjlnb3VQdTNhNTlmaEhCWGw0RDdCX2tVRnRaRDhfZUM0eUxjanpBY2Jn?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPNzltbTBsa2trTDhUaW13ZEx3VVVCNWJYWUdMMzRiN3RJZnlaSlpSczNiTGVDT3JhcTd3YWZtV1lfdW5RT1JxY21FU0JqZlJyUVAwd2c2RWViQ09tb1BQbjkzVHItRUpnaWtWZjc3cEQ0QjdaWTJXaUI0UGY4c2c0Vmpzay1EVVgzX2RUMndFcXZkU25ZMFEzM1ZHbjc1UEdQQU9TNzc5TGVLRkFCdG0ybEpZdHc2VktRaVF4YTVCcTFLZk5ITnpWLVItMU5CbzZqV1lMMGxoNEN1VlRzdjc00gHzAUFVX3lxTE5Talh5Y09PR1RuSzhlOTZUbHNVRENDMlpXbE5rTGdZQ3ozUVFjM0p5V2VmcE1FQzVKdkZwc2p3SEl3SVhBT2NuajQzOWlkazF5UHZDQzg3VGFySHNtRDh6Wkx4bEhGdFdjZGFGVkxhZ2xZNjRLM3FZdGYxZVdSVDZNUURCckQ4NExUYXRpdHJHRHo4Sk9qUjh5djMwdm8xYjFpcVNmd083NXR6bUQwWE04V2FWek83U0xGdHY4LXBkbFlSZEhaTWktNmtkaHYxVDlFbXhrYXFDRXdid3hRSk1uVktwQ1NETFZrRW5xMFI4Y1oxWQ?oc=5</t>
   </si>
   <si>
@@ -1522,6 +1816,9 @@
     <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOVWdJWWtTdmZkcUY3QUM1ZmJJZTdkRnZvVlgtbkpsZS1aa2Y3SkZLMG5XWjlURkhBZzRFRTM0VTZab2FzWFBKM0pNYktVVl9KckdZaVdXTGRpMDRVZ0FPMmU1bmhsQk9NT3VWZjdkSnk1Qnc5bTZGN29vMWhzRkREOURQMzJhNVhXajdPaXlGVnhLNU9WeXBveVBidFVpblZweW9iamtzR2Y1UG5VX3BHX3VaQmpJcHdodmRNa0xkWmd4ZlgtUUHSAdoBQVVfeXFMTmUzalpBM2J2NHFmV185akVudW9XQVVqWDVNMi02cDBDdFBnXzFWMnNSb1J5SF9sMElVcl84WnQwTVdtMURQRm00TTZoc1BCZnJ5NGlqcWdjQUFtRGNiTlZia0tPVy1rZGR6dy1RVDI3Y21XMEZPV19KQXhFYVIwY0lDdHlrMU9sVldSQ2F6X0x2RnFXbVNRXzNsRUwzM1JwMVBsR0stdmRUU1M4bGJJVEllZm1heGNlMVdTQ1lRZUt1V3EtS09LUnV2QzFjSDltRHY0VGZROU40N2c?oc=5</t>
   </si>
   <si>
+    <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
+  </si>
+  <si>
     <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPek9JX1dudlVEb3diN3BlNW1WMUpBeEJydXlwN2tVUGNNZW5UY1hnOFNOWFI3dGtvRkR5aUJPZDN0QmlhcEtBM3phTWc1TWVBSUxMU0ZJa2s2OHM5OVZzZU52dHJudkI4R3RIUnZTVlZmRzYtS0locnVibkE5OUZocHVOSkFlckY1NHJzZDFTUmFYXzhQQlhPS3BLRV8tV0NCbFUwZnEyRjVVOFJnOTV4MGpvSlNBdE9GSUhKT0FiU2VEcENOVHpFVHVXODRtOEVwaEJiatIB2gFBVV95cUxQWlNEOG1VT0ZwSXJOT0Z0eDh1b1FYeE0tdnVFUVdVdHBrWGE0QlA0a05MRmQ1MmxmaEZ3X2pfRk1ESEQwV013ZWczWVRNVmVKWElJLTkwMWxMOXRQTjZXVWtWUU9ZMjViYnZRcE96VWU5Nm82VzByVXNaVU1wRzJCN3BBeTFoMm9DdFVKM2VYY0szaGJvV3FTZlRoNWhUWldmVjhueGpVc2p5bEhhV2t1MjNyUVhwYnI3VmNXYktxYVdJeDdFWF84VmZvcGpoVGY4dk93UTVIcFZ5dw?oc=5</t>
   </si>
   <si>
@@ -1540,19 +1837,25 @@
     <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzExajdsZFN2UGduQnZXWjhydHdUNGNwZkJjQ1J0ZUR5cm96M01feHZIcFpQTGFpZWM0d0ZyVmhmVjRFWVRnaVhydHJkUU4yT3NYel9ZNm5tVGFLVXZKRHRXTFRkUzlubGx5eE9WVGgxRTg2SElBaGN3cW4tZ2hzRU9KdG51ZElRaGFablhHbTlzNTBEUEd1RmdCNExkOUFiVS1MUFBkOURYV004M3lhbzB0VlZYazBPVG8wOXBmYl9ldzNLUFE?oc=5</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
-  </si>
-  <si>
     <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNZ2cwYjk5Rk9ZV0p2c2paOHI1M2djamFCOExGYUFfTHpKTGIzOURhNFBQLUtBRDRhcGRmZ1ZxR3lnVkd5cTJYSFBjYkJlWkVnRFBIaFAxS0dIekZfREJHSGRtdE9hejRaaFJxZDlDaVJDZ09PVy1yOTVLZ2doQ0dqZ0RqeXRiLVhqdTQ4dGEwRUZoUTRXUmRNTFJEbTF6RUxKSy03NEdILTk3WWlia1lLTDlibVZ2UjJrMnhHeWhLVER3VkxPaDZyR1V3cEZhN3JTcDZCZtIB2gFBVV95cUxNeWo0TGhMNjdxTmFxeS01NlNpRm8yOVBDSklySlBaaWlPTTFyN1RZY2tBUHpGNG54T1cwMGY1akw0QVplT0hDdS1OLU9ZTXV1VnpBeFJMeHlWT3hDRGFxX3dGeVZQclZPbnlLeFhkejhIUFExdGZ3a0MxOVFOTnNBTE81YTRLemN2VnhsUlc5a1d5SUFSSk1ra3NJMTFodzZjcnlPYnhiNnljZHdLWXdtTXBwck1EaC0xRU5DUTQxWWJqNi14WVA3NmoxX19Ual9saEthZVBhSUFsQQ?oc=5</t>
   </si>
   <si>
+    <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
+  </si>
+  <si>
+    <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+  </si>
+  <si>
+    <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+  </si>
+  <si>
+    <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
+  </si>
+  <si>
+    <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
+  </si>
+  <si>
     <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
-  </si>
-  <si>
-    <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
-  </si>
-  <si>
-    <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
   </si>
   <si>
     <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
@@ -1571,9 +1874,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -1637,13 +1937,12 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1939,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1976,25 +2275,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="D2" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E2" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="F2" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G2" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>331</v>
+        <v>383</v>
+      </c>
+      <c r="I2" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2002,28 +2304,28 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="D3" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E3" t="s">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="F3" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G3" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="I3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2031,28 +2333,28 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="D4" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E4" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="F4" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G4" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="I4" t="s">
-        <v>510</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2060,260 +2362,260 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="D5" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E5" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="F5" t="s">
-        <v>321</v>
+        <v>374</v>
       </c>
       <c r="G5" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="I5" t="s">
-        <v>511</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E6" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="F6" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G6" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>335</v>
+        <v>387</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="D7" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E7" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F7" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G7" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
       <c r="D8" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="E8" t="s">
-        <v>312</v>
+        <v>364</v>
       </c>
       <c r="F8" t="s">
-        <v>319</v>
+        <v>375</v>
       </c>
       <c r="G8" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>337</v>
+        <v>389</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="D9" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="E9" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F9" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G9" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="I9" t="s">
-        <v>512</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="D10" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E10" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="F10" t="s">
-        <v>319</v>
+        <v>374</v>
       </c>
       <c r="G10" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>339</v>
+        <v>391</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="D11" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E11" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F11" t="s">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="G11" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>340</v>
+        <v>392</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="D12" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E12" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F12" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G12" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="I12" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="D13" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E13" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="F13" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G13" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2321,57 +2623,57 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="D14" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E14" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F14" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G14" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="D15" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E15" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="F15" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G15" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2379,86 +2681,86 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>252</v>
+        <v>300</v>
       </c>
       <c r="D16" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E16" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="F16" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G16" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="I16" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>301</v>
       </c>
       <c r="D17" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E17" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F17" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G17" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>346</v>
+        <v>398</v>
       </c>
       <c r="I17" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="D18" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E18" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F18" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="G18" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>347</v>
+        <v>399</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2466,28 +2768,28 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="D19" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E19" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="F19" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G19" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>348</v>
+        <v>400</v>
       </c>
       <c r="I19" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2495,28 +2797,28 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="D20" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E20" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F20" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="G20" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2524,28 +2826,28 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="D21" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E21" t="s">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="F21" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G21" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2553,28 +2855,28 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="D22" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E22" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="F22" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G22" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>351</v>
+        <v>403</v>
       </c>
       <c r="I22" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2582,28 +2884,28 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="D23" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E23" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="F23" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G23" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>352</v>
+        <v>404</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2611,947 +2913,950 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>307</v>
       </c>
       <c r="D24" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E24" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F24" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G24" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>353</v>
+        <v>405</v>
       </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="D25" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E25" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F25" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G25" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>354</v>
+        <v>406</v>
       </c>
       <c r="I25" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="D26" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E26" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="F26" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G26" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="I26" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="D27" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E27" t="s">
-        <v>311</v>
+        <v>366</v>
       </c>
       <c r="F27" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G27" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I27" t="s">
-        <v>91</v>
+        <v>408</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="D28" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E28" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F28" t="s">
-        <v>320</v>
+        <v>374</v>
       </c>
       <c r="G28" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="I28" t="s">
-        <v>92</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="D29" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E29" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="F29" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G29" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>358</v>
+        <v>410</v>
       </c>
       <c r="I29" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="D30" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="F30" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G30" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>359</v>
+        <v>411</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="D31" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E31" t="s">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G31" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="I31" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="D32" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E32" t="s">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="F32" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G32" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>361</v>
+        <v>413</v>
       </c>
       <c r="I32" t="s">
-        <v>96</v>
+        <v>612</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="D33" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E33" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="F33" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G33" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>362</v>
+        <v>414</v>
       </c>
       <c r="I33" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D34" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E34" t="s">
-        <v>311</v>
+        <v>366</v>
       </c>
       <c r="F34" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G34" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>363</v>
+        <v>415</v>
       </c>
       <c r="I34" t="s">
-        <v>98</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="D35" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E35" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="F35" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="G35" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>364</v>
+        <v>416</v>
       </c>
       <c r="I35" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="D36" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E36" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F36" t="s">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="G36" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>365</v>
+        <v>417</v>
+      </c>
+      <c r="I36" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>257</v>
+        <v>312</v>
       </c>
       <c r="D37" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E37" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F37" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G37" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>366</v>
+        <v>418</v>
       </c>
       <c r="I37" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="D38" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E38" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="F38" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="G38" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
       <c r="I38" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="D39" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E39" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F39" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="G39" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>368</v>
+        <v>420</v>
       </c>
       <c r="I39" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E40" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F40" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="G40" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="I40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E41" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F41" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G41" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="I41" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="D42" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E42" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="F42" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G42" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>371</v>
+        <v>423</v>
       </c>
       <c r="I42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="D43" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E43" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F43" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G43" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="I43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E44" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F44" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G44" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>373</v>
+        <v>425</v>
       </c>
       <c r="I44" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E45" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F45" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G45" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>374</v>
+        <v>426</v>
       </c>
       <c r="I45" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E46" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="F46" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G46" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>375</v>
+        <v>427</v>
       </c>
       <c r="I46" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E47" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F47" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G47" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>376</v>
+        <v>428</v>
       </c>
       <c r="I47" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E48" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="F48" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G48" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>377</v>
+        <v>429</v>
       </c>
       <c r="I48" t="s">
-        <v>513</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E49" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F49" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G49" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>378</v>
+        <v>430</v>
       </c>
       <c r="I49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E50" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F50" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G50" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>379</v>
+        <v>431</v>
       </c>
       <c r="I50" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>319</v>
       </c>
       <c r="D51" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E51" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F51" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G51" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>380</v>
+        <v>432</v>
       </c>
       <c r="I51" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="D52" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E52" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F52" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G52" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>381</v>
+        <v>433</v>
       </c>
       <c r="I52" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C53" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E53" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="F53" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G53" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>382</v>
+        <v>434</v>
+      </c>
+      <c r="I53" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="D54" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E54" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="F54" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G54" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="I54" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C55" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="D55" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E55" t="s">
-        <v>313</v>
+        <v>367</v>
       </c>
       <c r="F55" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G55" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>384</v>
+        <v>436</v>
       </c>
       <c r="I55" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
         <v>120</v>
       </c>
       <c r="C56" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E56" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F56" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G56" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>385</v>
+        <v>437</v>
       </c>
       <c r="I56" t="s">
         <v>120</v>
@@ -3559,3486 +3864,3474 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="D57" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E57" t="s">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="F57" t="s">
-        <v>321</v>
+        <v>371</v>
       </c>
       <c r="G57" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>386</v>
+        <v>438</v>
       </c>
       <c r="I57" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="D58" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E58" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F58" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G58" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>387</v>
+        <v>439</v>
+      </c>
+      <c r="I58" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C59" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="D59" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E59" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F59" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G59" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>388</v>
+        <v>440</v>
+      </c>
+      <c r="I59" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>279</v>
+        <v>321</v>
       </c>
       <c r="D60" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E60" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="F60" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G60" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>389</v>
+        <v>441</v>
+      </c>
+      <c r="I60" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>271</v>
+        <v>322</v>
       </c>
       <c r="D61" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E61" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="F61" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G61" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>390</v>
+        <v>442</v>
       </c>
       <c r="I61" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D62" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E62" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F62" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="G62" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>391</v>
+        <v>443</v>
       </c>
       <c r="I62" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C63" t="s">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="D63" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E63" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F63" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G63" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>392</v>
+        <v>444</v>
       </c>
       <c r="I63" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C64" t="s">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="D64" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E64" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F64" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G64" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>393</v>
+        <v>445</v>
       </c>
       <c r="I64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
       <c r="D65" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E65" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F65" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G65" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>394</v>
+        <v>446</v>
+      </c>
+      <c r="I65" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D66" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E66" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F66" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="G66" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="I66" t="s">
-        <v>130</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="D67" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E67" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="F67" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G67" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>396</v>
+        <v>448</v>
       </c>
       <c r="I67" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C68" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D68" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E68" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="F68" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G68" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>397</v>
+        <v>449</v>
       </c>
       <c r="I68" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="D69" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E69" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F69" t="s">
-        <v>322</v>
+        <v>377</v>
       </c>
       <c r="G69" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>398</v>
+        <v>450</v>
       </c>
       <c r="I69" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B70" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C70" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="D70" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E70" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="F70" t="s">
-        <v>319</v>
+        <v>377</v>
       </c>
       <c r="G70" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>399</v>
+        <v>451</v>
       </c>
       <c r="I70" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C71" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="D71" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E71" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F71" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G71" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>400</v>
+        <v>452</v>
       </c>
       <c r="I71" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C72" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="D72" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E72" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F72" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G72" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>401</v>
+        <v>453</v>
       </c>
       <c r="I72" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C73" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="D73" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E73" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F73" t="s">
-        <v>322</v>
+        <v>377</v>
       </c>
       <c r="G73" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="I73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
-        <v>247</v>
+        <v>325</v>
       </c>
       <c r="D74" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E74" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F74" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G74" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>403</v>
+        <v>455</v>
+      </c>
+      <c r="I74" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C75" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="D75" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E75" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F75" t="s">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="G75" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>404</v>
+        <v>456</v>
       </c>
       <c r="I75" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C76" t="s">
-        <v>272</v>
+        <v>327</v>
       </c>
       <c r="D76" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E76" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F76" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G76" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="I76" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C77" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="D77" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E77" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F77" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
       <c r="G77" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>406</v>
+        <v>458</v>
       </c>
       <c r="I77" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C78" t="s">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="D78" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E78" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F78" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G78" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>407</v>
+        <v>459</v>
       </c>
       <c r="I78" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B79" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C79" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="D79" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E79" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="F79" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G79" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>408</v>
+        <v>460</v>
       </c>
       <c r="I79" t="s">
-        <v>143</v>
+        <v>614</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C80" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="D80" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E80" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F80" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G80" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>409</v>
+        <v>461</v>
       </c>
       <c r="I80" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C81" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="D81" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E81" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F81" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G81" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>410</v>
+        <v>462</v>
+      </c>
+      <c r="I81" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C82" t="s">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="D82" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E82" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="F82" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G82" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>411</v>
+        <v>463</v>
       </c>
       <c r="I82" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C83" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D83" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E83" t="s">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="F83" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G83" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="I83" t="s">
-        <v>147</v>
+        <v>464</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C84" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="D84" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E84" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F84" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G84" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>413</v>
+        <v>465</v>
+      </c>
+      <c r="I84" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="D85" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E85" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="F85" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G85" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>414</v>
+        <v>466</v>
       </c>
       <c r="I85" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B86" t="s">
         <v>150</v>
       </c>
       <c r="C86" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="D86" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E86" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F86" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G86" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>415</v>
+        <v>467</v>
+      </c>
+      <c r="I86" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>252</v>
+        <v>330</v>
       </c>
       <c r="D87" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E87" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F87" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G87" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>416</v>
+        <v>468</v>
       </c>
       <c r="I87" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
-        <v>251</v>
+        <v>322</v>
       </c>
       <c r="D88" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="E88" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
       <c r="F88" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G88" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>417</v>
+        <v>469</v>
       </c>
       <c r="I88" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C89" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="D89" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E89" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F89" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G89" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>418</v>
+        <v>470</v>
       </c>
       <c r="I89" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C90" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="D90" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E90" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F90" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="G90" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>419</v>
+        <v>471</v>
       </c>
       <c r="I90" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C91" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="D91" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E91" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F91" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G91" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>420</v>
+        <v>472</v>
       </c>
       <c r="I91" t="s">
-        <v>514</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C92" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="D92" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E92" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F92" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G92" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I92" t="s">
-        <v>515</v>
+        <v>473</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C93" t="s">
-        <v>285</v>
+        <v>328</v>
       </c>
       <c r="D93" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E93" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F93" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G93" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>422</v>
+        <v>474</v>
       </c>
       <c r="I93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C94" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D94" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E94" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F94" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G94" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="I94" t="s">
-        <v>158</v>
+        <v>475</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C95" t="s">
-        <v>247</v>
+        <v>332</v>
       </c>
       <c r="D95" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E95" t="s">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="F95" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G95" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>424</v>
+        <v>476</v>
       </c>
       <c r="I95" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C96" t="s">
-        <v>257</v>
+        <v>328</v>
       </c>
       <c r="D96" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E96" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F96" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G96" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="I96" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C97" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="D97" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E97" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="F97" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G97" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C98" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="D98" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E98" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F98" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="G98" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>427</v>
+        <v>479</v>
       </c>
       <c r="I98" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C99" t="s">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="D99" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E99" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F99" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G99" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>428</v>
+        <v>480</v>
       </c>
       <c r="I99" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C100" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="D100" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E100" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F100" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="G100" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>429</v>
+        <v>481</v>
       </c>
       <c r="I100" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C101" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D101" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E101" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F101" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G101" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="I101" t="s">
-        <v>165</v>
+        <v>482</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B102" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C102" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D102" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E102" t="s">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="F102" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G102" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="I102" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B103" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C103" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D103" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E103" t="s">
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="F103" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="G103" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>432</v>
+        <v>484</v>
       </c>
       <c r="I103" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C104" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="D104" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E104" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F104" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G104" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>433</v>
+        <v>485</v>
       </c>
       <c r="I104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C105" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="D105" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E105" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F105" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G105" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>434</v>
+        <v>486</v>
+      </c>
+      <c r="I105" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B106" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C106" t="s">
-        <v>247</v>
+        <v>335</v>
       </c>
       <c r="D106" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E106" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="F106" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G106" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>435</v>
+        <v>487</v>
+      </c>
+      <c r="I106" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C107" t="s">
-        <v>247</v>
+        <v>336</v>
       </c>
       <c r="D107" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E107" t="s">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="F107" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G107" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>436</v>
+        <v>488</v>
       </c>
       <c r="I107" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C108" t="s">
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="D108" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E108" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F108" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G108" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>437</v>
+        <v>489</v>
       </c>
       <c r="I108" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C109" t="s">
-        <v>247</v>
+        <v>322</v>
       </c>
       <c r="D109" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E109" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="F109" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G109" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>438</v>
+        <v>490</v>
       </c>
       <c r="I109" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B110" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C110" t="s">
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="D110" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E110" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F110" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G110" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>439</v>
+        <v>491</v>
       </c>
       <c r="I110" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B111" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C111" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="D111" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E111" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F111" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G111" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="I111" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B112" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C112" t="s">
-        <v>247</v>
+        <v>334</v>
       </c>
       <c r="D112" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E112" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F112" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G112" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>441</v>
+        <v>493</v>
+      </c>
+      <c r="I112" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B113" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C113" t="s">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="D113" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E113" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F113" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G113" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="I113" t="s">
-        <v>177</v>
+        <v>494</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B114" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C114" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="D114" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E114" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F114" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G114" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>443</v>
+        <v>495</v>
+      </c>
+      <c r="I114" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B115" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C115" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D115" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E115" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F115" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G115" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>444</v>
+        <v>496</v>
       </c>
       <c r="I115" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B116" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C116" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="D116" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E116" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F116" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G116" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="I116" t="s">
-        <v>180</v>
+        <v>497</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C117" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="D117" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E117" t="s">
-        <v>315</v>
+        <v>362</v>
       </c>
       <c r="F117" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G117" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>446</v>
+        <v>498</v>
       </c>
       <c r="I117" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B118" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C118" t="s">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="D118" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E118" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F118" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="G118" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>447</v>
+        <v>499</v>
       </c>
       <c r="I118" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B119" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C119" t="s">
-        <v>247</v>
+        <v>338</v>
       </c>
       <c r="D119" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E119" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F119" t="s">
-        <v>319</v>
+        <v>379</v>
       </c>
       <c r="G119" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>448</v>
+        <v>500</v>
+      </c>
+      <c r="I119" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B120" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C120" t="s">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="D120" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E120" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F120" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G120" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>449</v>
+        <v>501</v>
+      </c>
+      <c r="I120" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B121" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C121" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="D121" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E121" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="F121" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G121" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>450</v>
+        <v>502</v>
       </c>
       <c r="I121" t="s">
-        <v>516</v>
+        <v>186</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B122" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C122" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="D122" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E122" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F122" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G122" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>451</v>
+        <v>503</v>
+      </c>
+      <c r="I122" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C123" t="s">
-        <v>271</v>
+        <v>339</v>
       </c>
       <c r="D123" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E123" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F123" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G123" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>452</v>
+        <v>504</v>
       </c>
       <c r="I123" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B124" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C124" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D124" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E124" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F124" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G124" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="I124" t="s">
-        <v>188</v>
+        <v>505</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B125" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C125" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="D125" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E125" t="s">
-        <v>316</v>
+        <v>369</v>
       </c>
       <c r="F125" t="s">
-        <v>326</v>
+        <v>373</v>
       </c>
       <c r="G125" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>454</v>
+        <v>506</v>
+      </c>
+      <c r="I125" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B126" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C126" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D126" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E126" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F126" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G126" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="I126" t="s">
-        <v>190</v>
+        <v>507</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B127" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C127" t="s">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="D127" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E127" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="F127" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G127" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>456</v>
+        <v>508</v>
       </c>
       <c r="I127" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B128" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C128" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="D128" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E128" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="F128" t="s">
-        <v>328</v>
+        <v>372</v>
       </c>
       <c r="G128" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>457</v>
+        <v>509</v>
       </c>
       <c r="I128" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B129" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C129" t="s">
         <v>295</v>
       </c>
       <c r="D129" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E129" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="F129" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G129" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>458</v>
+        <v>510</v>
       </c>
       <c r="I129" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B130" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C130" t="s">
-        <v>271</v>
+        <v>340</v>
       </c>
       <c r="D130" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E130" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F130" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G130" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>459</v>
+        <v>511</v>
       </c>
       <c r="I130" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B131" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C131" t="s">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="D131" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E131" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F131" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G131" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>460</v>
+        <v>512</v>
       </c>
       <c r="I131" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B132" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C132" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="D132" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="E132" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F132" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G132" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>461</v>
+        <v>513</v>
       </c>
       <c r="I132" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B133" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C133" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="D133" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E133" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F133" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G133" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>462</v>
+        <v>514</v>
       </c>
       <c r="I133" t="s">
-        <v>197</v>
+        <v>615</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B134" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C134" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="D134" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="E134" t="s">
-        <v>310</v>
+        <v>364</v>
       </c>
       <c r="F134" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G134" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>463</v>
+        <v>515</v>
       </c>
       <c r="I134" t="s">
-        <v>198</v>
+        <v>616</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B135" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C135" t="s">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="D135" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E135" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F135" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G135" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>464</v>
+        <v>516</v>
       </c>
       <c r="I135" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B136" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C136" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="D136" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E136" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F136" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G136" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>465</v>
+        <v>517</v>
       </c>
       <c r="I136" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B137" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C137" t="s">
-        <v>271</v>
+        <v>331</v>
       </c>
       <c r="D137" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E137" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F137" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G137" t="s">
-        <v>329</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="I137" t="s">
-        <v>201</v>
+        <v>381</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B138" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C138" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="D138" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E138" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="F138" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G138" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="I138" t="s">
-        <v>202</v>
+        <v>518</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B139" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C139" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D139" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E139" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F139" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G139" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="I139" t="s">
-        <v>203</v>
+        <v>519</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B140" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C140" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="D140" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E140" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F140" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G140" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="I140" t="s">
-        <v>204</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B141" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C141" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="D141" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E141" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="F141" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G141" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="I141" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B142" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C142" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="D142" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E142" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F142" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G142" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>471</v>
+        <v>522</v>
       </c>
       <c r="I142" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B143" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C143" t="s">
-        <v>252</v>
+        <v>342</v>
       </c>
       <c r="D143" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E143" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="F143" t="s">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="G143" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>472</v>
+        <v>523</v>
       </c>
       <c r="I143" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B144" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C144" t="s">
-        <v>278</v>
+        <v>343</v>
       </c>
       <c r="D144" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E144" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F144" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="G144" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="I144" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B145" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C145" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="D145" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E145" t="s">
-        <v>316</v>
+        <v>366</v>
       </c>
       <c r="F145" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G145" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>474</v>
+        <v>525</v>
       </c>
       <c r="I145" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B146" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C146" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="D146" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E146" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="F146" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G146" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="I146" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B147" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C147" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="D147" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E147" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="F147" t="s">
-        <v>319</v>
+        <v>375</v>
       </c>
       <c r="G147" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="I147" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B148" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C148" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="D148" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E148" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G148" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>477</v>
+        <v>528</v>
       </c>
       <c r="I148" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B149" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C149" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D149" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E149" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F149" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="G149" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>478</v>
+        <v>529</v>
       </c>
       <c r="I149" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B150" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="D150" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E150" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F150" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="G150" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>479</v>
+        <v>530</v>
       </c>
       <c r="I150" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B151" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C151" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D151" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E151" t="s">
-        <v>317</v>
+        <v>364</v>
       </c>
       <c r="F151" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G151" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>480</v>
+        <v>531</v>
       </c>
       <c r="I151" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B152" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C152" t="s">
-        <v>251</v>
+        <v>344</v>
       </c>
       <c r="D152" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="E152" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G152" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>481</v>
+        <v>532</v>
       </c>
       <c r="I152" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B153" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C153" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D153" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E153" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F153" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G153" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>482</v>
+        <v>533</v>
       </c>
       <c r="I153" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B154" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C154" t="s">
-        <v>270</v>
+        <v>328</v>
       </c>
       <c r="D154" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E154" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F154" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="G154" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="I154" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B155" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C155" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="D155" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E155" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F155" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G155" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="I155" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B156" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C156" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="D156" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E156" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F156" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G156" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="I156" t="s">
-        <v>220</v>
+        <v>536</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B157" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C157" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D157" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E157" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="F157" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G157" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="I157" t="s">
-        <v>221</v>
+        <v>537</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B158" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C158" t="s">
-        <v>257</v>
+        <v>345</v>
       </c>
       <c r="D158" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E158" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>487</v>
+        <v>538</v>
       </c>
       <c r="I158" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B159" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C159" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D159" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E159" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F159" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G159" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="I159" t="s">
-        <v>223</v>
+        <v>539</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B160" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C160" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="D160" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E160" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F160" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G160" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>489</v>
+        <v>540</v>
       </c>
       <c r="I160" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B161" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C161" t="s">
-        <v>260</v>
+        <v>346</v>
       </c>
       <c r="D161" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E161" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F161" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="G161" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="I161" t="s">
-        <v>225</v>
+        <v>541</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B162" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C162" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="D162" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E162" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F162" t="s">
-        <v>326</v>
+        <v>372</v>
       </c>
       <c r="G162" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>491</v>
+        <v>542</v>
       </c>
       <c r="I162" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B163" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C163" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D163" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E163" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="F163" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
       <c r="G163" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>492</v>
+        <v>543</v>
       </c>
       <c r="I163" t="s">
-        <v>227</v>
+        <v>617</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B164" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C164" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D164" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E164" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="F164" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="G164" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="I164" t="s">
-        <v>228</v>
+        <v>544</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B165" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C165" t="s">
-        <v>255</v>
+        <v>344</v>
       </c>
       <c r="D165" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E165" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="F165" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G165" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>494</v>
+        <v>545</v>
       </c>
       <c r="I165" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B166" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C166" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="D166" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E166" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F166" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G166" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>495</v>
+        <v>546</v>
       </c>
       <c r="I166" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B167" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C167" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="D167" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E167" t="s">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="F167" t="s">
-        <v>319</v>
+        <v>379</v>
       </c>
       <c r="G167" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="I167" t="s">
-        <v>231</v>
+        <v>547</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B168" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C168" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="D168" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E168" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F168" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G168" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>497</v>
+        <v>548</v>
       </c>
       <c r="I168" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B169" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C169" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="D169" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E169" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F169" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G169" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>498</v>
+        <v>549</v>
       </c>
       <c r="I169" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B170" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C170" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="D170" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E170" t="s">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F170" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G170" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>499</v>
+        <v>550</v>
       </c>
       <c r="I170" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B171" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C171" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="D171" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E171" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="F171" t="s">
-        <v>322</v>
+        <v>380</v>
       </c>
       <c r="G171" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>500</v>
+        <v>551</v>
       </c>
       <c r="I171" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B172" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C172" t="s">
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="D172" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E172" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F172" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G172" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>501</v>
+        <v>552</v>
       </c>
       <c r="I172" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B173" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C173" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D173" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E173" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F173" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G173" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>502</v>
+        <v>553</v>
       </c>
       <c r="I173" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B174" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C174" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D174" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E174" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F174" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G174" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="I174" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B175" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C175" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D175" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E175" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F175" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="G175" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>504</v>
+        <v>555</v>
       </c>
       <c r="I175" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B176" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C176" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="D176" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E176" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="F176" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="G176" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>505</v>
+        <v>556</v>
       </c>
       <c r="I176" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B177" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C177" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="D177" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E177" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F177" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G177" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>506</v>
+        <v>557</v>
       </c>
       <c r="I177" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B178" t="s">
         <v>242</v>
       </c>
       <c r="C178" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="D178" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E178" t="s">
-        <v>315</v>
+        <v>365</v>
       </c>
       <c r="F178" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="G178" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>507</v>
+        <v>558</v>
       </c>
       <c r="I178" t="s">
         <v>242</v>
@@ -7046,28 +7339,28 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B179" t="s">
         <v>243</v>
       </c>
       <c r="C179" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="D179" t="s">
-        <v>308</v>
+        <v>361</v>
       </c>
       <c r="E179" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="F179" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="G179" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>508</v>
+        <v>559</v>
       </c>
       <c r="I179" t="s">
         <v>243</v>
@@ -7075,77 +7368,1394 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B180" t="s">
         <v>244</v>
       </c>
       <c r="C180" t="s">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="D180" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E180" t="s">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="F180" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G180" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>509</v>
+        <v>560</v>
       </c>
       <c r="I180" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:9">
-      <c r="A181" s="3">
-        <v>46037</v>
+      <c r="A181" t="s">
+        <v>55</v>
       </c>
       <c r="B181" t="s">
         <v>245</v>
       </c>
       <c r="C181" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="D181" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="E181" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="F181" t="s">
-        <v>322</v>
+        <v>372</v>
       </c>
       <c r="G181" t="s">
-        <v>329</v>
+        <v>381</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="I181" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="182" spans="1:9">
-      <c r="A182" s="3">
-        <v>46054</v>
+      <c r="A182" t="s">
+        <v>55</v>
       </c>
       <c r="B182" t="s">
         <v>246</v>
       </c>
       <c r="C182" t="s">
+        <v>328</v>
+      </c>
+      <c r="D182" t="s">
+        <v>360</v>
+      </c>
+      <c r="E182" t="s">
+        <v>365</v>
+      </c>
+      <c r="F182" t="s">
+        <v>371</v>
+      </c>
+      <c r="G182" t="s">
+        <v>381</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I182" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" t="s">
+        <v>55</v>
+      </c>
+      <c r="B183" t="s">
         <v>247</v>
       </c>
-      <c r="D182" t="s">
-        <v>308</v>
-      </c>
-      <c r="E182" t="s">
-        <v>314</v>
-      </c>
-      <c r="F182" t="s">
-        <v>322</v>
-      </c>
-      <c r="G182" t="s">
-        <v>329</v>
+      <c r="C183" t="s">
+        <v>313</v>
+      </c>
+      <c r="D183" t="s">
+        <v>360</v>
+      </c>
+      <c r="E183" t="s">
+        <v>364</v>
+      </c>
+      <c r="F183" t="s">
+        <v>372</v>
+      </c>
+      <c r="G183" t="s">
+        <v>381</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="I183" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" t="s">
+        <v>55</v>
+      </c>
+      <c r="B184" t="s">
+        <v>245</v>
+      </c>
+      <c r="C184" t="s">
+        <v>290</v>
+      </c>
+      <c r="D184" t="s">
+        <v>360</v>
+      </c>
+      <c r="E184" t="s">
+        <v>364</v>
+      </c>
+      <c r="F184" t="s">
+        <v>372</v>
+      </c>
+      <c r="G184" t="s">
+        <v>381</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="I184" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" t="s">
+        <v>56</v>
+      </c>
+      <c r="B185" t="s">
+        <v>248</v>
+      </c>
+      <c r="C185" t="s">
+        <v>290</v>
+      </c>
+      <c r="D185" t="s">
+        <v>360</v>
+      </c>
+      <c r="E185" t="s">
+        <v>364</v>
+      </c>
+      <c r="F185" t="s">
+        <v>372</v>
+      </c>
+      <c r="G185" t="s">
+        <v>381</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I185" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" t="s">
+        <v>57</v>
+      </c>
+      <c r="B186" t="s">
+        <v>86</v>
+      </c>
+      <c r="C186" t="s">
+        <v>300</v>
+      </c>
+      <c r="D186" t="s">
+        <v>360</v>
+      </c>
+      <c r="E186" t="s">
+        <v>363</v>
+      </c>
+      <c r="F186" t="s">
+        <v>373</v>
+      </c>
+      <c r="G186" t="s">
+        <v>382</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="I186" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" t="s">
+        <v>57</v>
+      </c>
+      <c r="B187" t="s">
+        <v>249</v>
+      </c>
+      <c r="C187" t="s">
+        <v>328</v>
+      </c>
+      <c r="D187" t="s">
+        <v>360</v>
+      </c>
+      <c r="E187" t="s">
+        <v>364</v>
+      </c>
+      <c r="F187" t="s">
+        <v>372</v>
+      </c>
+      <c r="G187" t="s">
+        <v>381</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="I187" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" t="s">
+        <v>58</v>
+      </c>
+      <c r="B188" t="s">
+        <v>250</v>
+      </c>
+      <c r="C188" t="s">
+        <v>295</v>
+      </c>
+      <c r="D188" t="s">
+        <v>360</v>
+      </c>
+      <c r="E188" t="s">
+        <v>365</v>
+      </c>
+      <c r="F188" t="s">
+        <v>371</v>
+      </c>
+      <c r="G188" t="s">
+        <v>381</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I188" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" t="s">
+        <v>58</v>
+      </c>
+      <c r="B189" t="s">
+        <v>251</v>
+      </c>
+      <c r="C189" t="s">
+        <v>296</v>
+      </c>
+      <c r="D189" t="s">
+        <v>360</v>
+      </c>
+      <c r="E189" t="s">
+        <v>366</v>
+      </c>
+      <c r="F189" t="s">
+        <v>377</v>
+      </c>
+      <c r="G189" t="s">
+        <v>381</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="I189" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" t="s">
+        <v>59</v>
+      </c>
+      <c r="B190" t="s">
+        <v>252</v>
+      </c>
+      <c r="C190" t="s">
+        <v>302</v>
+      </c>
+      <c r="D190" t="s">
+        <v>360</v>
+      </c>
+      <c r="E190" t="s">
+        <v>365</v>
+      </c>
+      <c r="F190" t="s">
+        <v>374</v>
+      </c>
+      <c r="G190" t="s">
+        <v>381</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="I190" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" t="s">
+        <v>59</v>
+      </c>
+      <c r="B191" t="s">
+        <v>253</v>
+      </c>
+      <c r="C191" t="s">
+        <v>350</v>
+      </c>
+      <c r="D191" t="s">
+        <v>360</v>
+      </c>
+      <c r="E191" t="s">
+        <v>368</v>
+      </c>
+      <c r="F191" t="s">
+        <v>372</v>
+      </c>
+      <c r="G191" t="s">
+        <v>381</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="I191" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" t="s">
+        <v>60</v>
+      </c>
+      <c r="B192" t="s">
+        <v>254</v>
+      </c>
+      <c r="C192" t="s">
+        <v>293</v>
+      </c>
+      <c r="D192" t="s">
+        <v>360</v>
+      </c>
+      <c r="E192" t="s">
+        <v>362</v>
+      </c>
+      <c r="F192" t="s">
+        <v>373</v>
+      </c>
+      <c r="G192" t="s">
+        <v>382</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I192" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" t="s">
+        <v>61</v>
+      </c>
+      <c r="B193" t="s">
+        <v>255</v>
+      </c>
+      <c r="C193" t="s">
+        <v>351</v>
+      </c>
+      <c r="D193" t="s">
+        <v>360</v>
+      </c>
+      <c r="E193" t="s">
+        <v>365</v>
+      </c>
+      <c r="F193" t="s">
+        <v>371</v>
+      </c>
+      <c r="G193" t="s">
+        <v>381</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="I193" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" t="s">
+        <v>61</v>
+      </c>
+      <c r="B194" t="s">
+        <v>256</v>
+      </c>
+      <c r="C194" t="s">
+        <v>295</v>
+      </c>
+      <c r="D194" t="s">
+        <v>360</v>
+      </c>
+      <c r="E194" t="s">
+        <v>365</v>
+      </c>
+      <c r="F194" t="s">
+        <v>371</v>
+      </c>
+      <c r="G194" t="s">
+        <v>381</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I194" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" t="s">
+        <v>62</v>
+      </c>
+      <c r="B195" t="s">
+        <v>257</v>
+      </c>
+      <c r="C195" t="s">
+        <v>352</v>
+      </c>
+      <c r="D195" t="s">
+        <v>360</v>
+      </c>
+      <c r="E195" t="s">
+        <v>365</v>
+      </c>
+      <c r="F195" t="s">
+        <v>371</v>
+      </c>
+      <c r="G195" t="s">
+        <v>381</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="I195" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" t="s">
+        <v>63</v>
+      </c>
+      <c r="B196" t="s">
+        <v>258</v>
+      </c>
+      <c r="C196" t="s">
+        <v>323</v>
+      </c>
+      <c r="D196" t="s">
+        <v>360</v>
+      </c>
+      <c r="E196" t="s">
+        <v>365</v>
+      </c>
+      <c r="F196" t="s">
+        <v>377</v>
+      </c>
+      <c r="G196" t="s">
+        <v>381</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="I196" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" t="s">
+        <v>64</v>
+      </c>
+      <c r="B197" t="s">
+        <v>259</v>
+      </c>
+      <c r="C197" t="s">
+        <v>353</v>
+      </c>
+      <c r="D197" t="s">
+        <v>360</v>
+      </c>
+      <c r="E197" t="s">
+        <v>369</v>
+      </c>
+      <c r="F197" t="s">
+        <v>372</v>
+      </c>
+      <c r="G197" t="s">
+        <v>381</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="I197" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" t="s">
+        <v>64</v>
+      </c>
+      <c r="B198" t="s">
+        <v>259</v>
+      </c>
+      <c r="C198" t="s">
+        <v>353</v>
+      </c>
+      <c r="D198" t="s">
+        <v>360</v>
+      </c>
+      <c r="E198" t="s">
+        <v>369</v>
+      </c>
+      <c r="F198" t="s">
+        <v>372</v>
+      </c>
+      <c r="G198" t="s">
+        <v>381</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="I198" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" t="s">
+        <v>65</v>
+      </c>
+      <c r="B199" t="s">
+        <v>260</v>
+      </c>
+      <c r="C199" t="s">
+        <v>291</v>
+      </c>
+      <c r="D199" t="s">
+        <v>361</v>
+      </c>
+      <c r="E199" t="s">
+        <v>364</v>
+      </c>
+      <c r="F199" t="s">
+        <v>371</v>
+      </c>
+      <c r="G199" t="s">
+        <v>381</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="I199" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" t="s">
+        <v>66</v>
+      </c>
+      <c r="B200" t="s">
+        <v>261</v>
+      </c>
+      <c r="C200" t="s">
+        <v>347</v>
+      </c>
+      <c r="D200" t="s">
+        <v>360</v>
+      </c>
+      <c r="E200" t="s">
+        <v>364</v>
+      </c>
+      <c r="F200" t="s">
+        <v>372</v>
+      </c>
+      <c r="G200" t="s">
+        <v>381</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="I200" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" t="s">
+        <v>67</v>
+      </c>
+      <c r="B201" t="s">
+        <v>262</v>
+      </c>
+      <c r="C201" t="s">
+        <v>336</v>
+      </c>
+      <c r="D201" t="s">
+        <v>360</v>
+      </c>
+      <c r="E201" t="s">
+        <v>363</v>
+      </c>
+      <c r="F201" t="s">
+        <v>372</v>
+      </c>
+      <c r="G201" t="s">
+        <v>381</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="I201" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" t="s">
+        <v>67</v>
+      </c>
+      <c r="B202" t="s">
+        <v>263</v>
+      </c>
+      <c r="C202" t="s">
+        <v>325</v>
+      </c>
+      <c r="D202" t="s">
+        <v>360</v>
+      </c>
+      <c r="E202" t="s">
+        <v>365</v>
+      </c>
+      <c r="F202" t="s">
+        <v>371</v>
+      </c>
+      <c r="G202" t="s">
+        <v>381</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="I202" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" t="s">
+        <v>67</v>
+      </c>
+      <c r="B203" t="s">
+        <v>264</v>
+      </c>
+      <c r="C203" t="s">
+        <v>296</v>
+      </c>
+      <c r="D203" t="s">
+        <v>360</v>
+      </c>
+      <c r="E203" t="s">
+        <v>365</v>
+      </c>
+      <c r="F203" t="s">
+        <v>371</v>
+      </c>
+      <c r="G203" t="s">
+        <v>381</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="I203" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="s">
+        <v>67</v>
+      </c>
+      <c r="B204" t="s">
+        <v>265</v>
+      </c>
+      <c r="C204" t="s">
+        <v>323</v>
+      </c>
+      <c r="D204" t="s">
+        <v>360</v>
+      </c>
+      <c r="E204" t="s">
+        <v>364</v>
+      </c>
+      <c r="F204" t="s">
+        <v>371</v>
+      </c>
+      <c r="G204" t="s">
+        <v>381</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="I204" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="s">
+        <v>67</v>
+      </c>
+      <c r="B205" t="s">
+        <v>266</v>
+      </c>
+      <c r="C205" t="s">
+        <v>316</v>
+      </c>
+      <c r="D205" t="s">
+        <v>360</v>
+      </c>
+      <c r="E205" t="s">
+        <v>365</v>
+      </c>
+      <c r="F205" t="s">
+        <v>373</v>
+      </c>
+      <c r="G205" t="s">
+        <v>382</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="I205" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="s">
+        <v>67</v>
+      </c>
+      <c r="B206" t="s">
+        <v>267</v>
+      </c>
+      <c r="C206" t="s">
+        <v>290</v>
+      </c>
+      <c r="D206" t="s">
+        <v>360</v>
+      </c>
+      <c r="E206" t="s">
+        <v>365</v>
+      </c>
+      <c r="F206" t="s">
+        <v>373</v>
+      </c>
+      <c r="G206" t="s">
+        <v>382</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="I206" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="s">
+        <v>68</v>
+      </c>
+      <c r="B207" t="s">
+        <v>268</v>
+      </c>
+      <c r="C207" t="s">
+        <v>293</v>
+      </c>
+      <c r="D207" t="s">
+        <v>360</v>
+      </c>
+      <c r="E207" t="s">
+        <v>365</v>
+      </c>
+      <c r="F207" t="s">
+        <v>373</v>
+      </c>
+      <c r="G207" t="s">
+        <v>382</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="I207" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="s">
+        <v>68</v>
+      </c>
+      <c r="B208" t="s">
+        <v>269</v>
+      </c>
+      <c r="C208" t="s">
+        <v>354</v>
+      </c>
+      <c r="D208" t="s">
+        <v>360</v>
+      </c>
+      <c r="E208" t="s">
+        <v>365</v>
+      </c>
+      <c r="F208" t="s">
+        <v>379</v>
+      </c>
+      <c r="G208" t="s">
+        <v>381</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="I208" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" t="s">
+        <v>68</v>
+      </c>
+      <c r="B209" t="s">
+        <v>270</v>
+      </c>
+      <c r="C209" t="s">
+        <v>355</v>
+      </c>
+      <c r="D209" t="s">
+        <v>360</v>
+      </c>
+      <c r="E209" t="s">
+        <v>365</v>
+      </c>
+      <c r="F209" t="s">
+        <v>372</v>
+      </c>
+      <c r="G209" t="s">
+        <v>381</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="I209" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" t="s">
+        <v>68</v>
+      </c>
+      <c r="B210" t="s">
+        <v>271</v>
+      </c>
+      <c r="C210" t="s">
+        <v>313</v>
+      </c>
+      <c r="D210" t="s">
+        <v>360</v>
+      </c>
+      <c r="E210" t="s">
+        <v>363</v>
+      </c>
+      <c r="F210" t="s">
+        <v>373</v>
+      </c>
+      <c r="G210" t="s">
+        <v>382</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="I210" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" t="s">
+        <v>68</v>
+      </c>
+      <c r="B211" t="s">
+        <v>272</v>
+      </c>
+      <c r="C211" t="s">
+        <v>334</v>
+      </c>
+      <c r="D211" t="s">
+        <v>360</v>
+      </c>
+      <c r="E211" t="s">
+        <v>364</v>
+      </c>
+      <c r="F211" t="s">
+        <v>372</v>
+      </c>
+      <c r="G211" t="s">
+        <v>381</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="I211" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" t="s">
+        <v>68</v>
+      </c>
+      <c r="B212" t="s">
+        <v>273</v>
+      </c>
+      <c r="C212" t="s">
+        <v>338</v>
+      </c>
+      <c r="D212" t="s">
+        <v>360</v>
+      </c>
+      <c r="E212" t="s">
+        <v>365</v>
+      </c>
+      <c r="F212" t="s">
+        <v>379</v>
+      </c>
+      <c r="G212" t="s">
+        <v>381</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="I212" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" t="s">
+        <v>68</v>
+      </c>
+      <c r="B213" t="s">
+        <v>274</v>
+      </c>
+      <c r="C213" t="s">
+        <v>345</v>
+      </c>
+      <c r="D213" t="s">
+        <v>360</v>
+      </c>
+      <c r="E213" t="s">
+        <v>363</v>
+      </c>
+      <c r="F213" t="s">
+        <v>373</v>
+      </c>
+      <c r="G213" t="s">
+        <v>382</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="I213" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" t="s">
+        <v>69</v>
+      </c>
+      <c r="B214" t="s">
+        <v>275</v>
+      </c>
+      <c r="C214" t="s">
+        <v>295</v>
+      </c>
+      <c r="D214" t="s">
+        <v>360</v>
+      </c>
+      <c r="E214" t="s">
+        <v>365</v>
+      </c>
+      <c r="F214" t="s">
+        <v>371</v>
+      </c>
+      <c r="G214" t="s">
+        <v>381</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="I214" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" t="s">
+        <v>69</v>
+      </c>
+      <c r="B215" t="s">
+        <v>276</v>
+      </c>
+      <c r="C215" t="s">
+        <v>328</v>
+      </c>
+      <c r="D215" t="s">
+        <v>360</v>
+      </c>
+      <c r="E215" t="s">
+        <v>364</v>
+      </c>
+      <c r="F215" t="s">
+        <v>371</v>
+      </c>
+      <c r="G215" t="s">
+        <v>381</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="I215" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" t="s">
+        <v>69</v>
+      </c>
+      <c r="B216" t="s">
+        <v>277</v>
+      </c>
+      <c r="C216" t="s">
+        <v>353</v>
+      </c>
+      <c r="D216" t="s">
+        <v>360</v>
+      </c>
+      <c r="E216" t="s">
+        <v>364</v>
+      </c>
+      <c r="F216" t="s">
+        <v>372</v>
+      </c>
+      <c r="G216" t="s">
+        <v>381</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="I216" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" t="s">
+        <v>70</v>
+      </c>
+      <c r="B217" t="s">
+        <v>278</v>
+      </c>
+      <c r="C217" t="s">
+        <v>347</v>
+      </c>
+      <c r="D217" t="s">
+        <v>360</v>
+      </c>
+      <c r="E217" t="s">
+        <v>364</v>
+      </c>
+      <c r="F217" t="s">
+        <v>372</v>
+      </c>
+      <c r="G217" t="s">
+        <v>381</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="I217" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" t="s">
+        <v>70</v>
+      </c>
+      <c r="B218" t="s">
+        <v>279</v>
+      </c>
+      <c r="C218" t="s">
+        <v>355</v>
+      </c>
+      <c r="D218" t="s">
+        <v>360</v>
+      </c>
+      <c r="E218" t="s">
+        <v>365</v>
+      </c>
+      <c r="F218" t="s">
+        <v>372</v>
+      </c>
+      <c r="G218" t="s">
+        <v>381</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="I218" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" t="s">
+        <v>70</v>
+      </c>
+      <c r="B219" t="s">
+        <v>280</v>
+      </c>
+      <c r="C219" t="s">
+        <v>290</v>
+      </c>
+      <c r="D219" t="s">
+        <v>360</v>
+      </c>
+      <c r="E219" t="s">
+        <v>365</v>
+      </c>
+      <c r="F219" t="s">
+        <v>372</v>
+      </c>
+      <c r="G219" t="s">
+        <v>381</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="I219" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" t="s">
+        <v>71</v>
+      </c>
+      <c r="B220" t="s">
+        <v>281</v>
+      </c>
+      <c r="C220" t="s">
+        <v>295</v>
+      </c>
+      <c r="D220" t="s">
+        <v>360</v>
+      </c>
+      <c r="E220" t="s">
+        <v>365</v>
+      </c>
+      <c r="F220" t="s">
+        <v>373</v>
+      </c>
+      <c r="G220" t="s">
+        <v>382</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="I220" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" t="s">
+        <v>71</v>
+      </c>
+      <c r="B221" t="s">
+        <v>282</v>
+      </c>
+      <c r="C221" t="s">
+        <v>356</v>
+      </c>
+      <c r="D221" t="s">
+        <v>360</v>
+      </c>
+      <c r="E221" t="s">
+        <v>365</v>
+      </c>
+      <c r="F221" t="s">
+        <v>372</v>
+      </c>
+      <c r="G221" t="s">
+        <v>381</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="I221" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" t="s">
+        <v>71</v>
+      </c>
+      <c r="B222" t="s">
+        <v>283</v>
+      </c>
+      <c r="C222" t="s">
+        <v>357</v>
+      </c>
+      <c r="D222" t="s">
+        <v>360</v>
+      </c>
+      <c r="E222" t="s">
+        <v>364</v>
+      </c>
+      <c r="F222" t="s">
+        <v>372</v>
+      </c>
+      <c r="G222" t="s">
+        <v>381</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="I222" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" t="s">
+        <v>71</v>
+      </c>
+      <c r="B223" t="s">
+        <v>284</v>
+      </c>
+      <c r="C223" t="s">
+        <v>298</v>
+      </c>
+      <c r="D223" t="s">
+        <v>360</v>
+      </c>
+      <c r="E223" t="s">
+        <v>365</v>
+      </c>
+      <c r="F223" t="s">
+        <v>372</v>
+      </c>
+      <c r="G223" t="s">
+        <v>381</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="I223" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" t="s">
+        <v>71</v>
+      </c>
+      <c r="B224" t="s">
+        <v>285</v>
+      </c>
+      <c r="C224" t="s">
+        <v>358</v>
+      </c>
+      <c r="D224" t="s">
+        <v>360</v>
+      </c>
+      <c r="E224" t="s">
+        <v>365</v>
+      </c>
+      <c r="F224" t="s">
+        <v>372</v>
+      </c>
+      <c r="G224" t="s">
+        <v>381</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="I224" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" t="s">
+        <v>71</v>
+      </c>
+      <c r="B225" t="s">
+        <v>286</v>
+      </c>
+      <c r="C225" t="s">
+        <v>295</v>
+      </c>
+      <c r="D225" t="s">
+        <v>360</v>
+      </c>
+      <c r="E225" t="s">
+        <v>365</v>
+      </c>
+      <c r="F225" t="s">
+        <v>372</v>
+      </c>
+      <c r="G225" t="s">
+        <v>381</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="I225" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" t="s">
+        <v>71</v>
+      </c>
+      <c r="B226" t="s">
+        <v>287</v>
+      </c>
+      <c r="C226" t="s">
+        <v>359</v>
+      </c>
+      <c r="D226" t="s">
+        <v>360</v>
+      </c>
+      <c r="E226" t="s">
+        <v>363</v>
+      </c>
+      <c r="F226" t="s">
+        <v>371</v>
+      </c>
+      <c r="G226" t="s">
+        <v>381</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="I226" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" t="s">
+        <v>71</v>
+      </c>
+      <c r="B227" t="s">
+        <v>288</v>
+      </c>
+      <c r="C227" t="s">
+        <v>296</v>
+      </c>
+      <c r="D227" t="s">
+        <v>360</v>
+      </c>
+      <c r="E227" t="s">
+        <v>365</v>
+      </c>
+      <c r="F227" t="s">
+        <v>372</v>
+      </c>
+      <c r="G227" t="s">
+        <v>381</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="I227" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -7285,50 +8895,96 @@
     <hyperlink ref="H134" r:id="rId133"/>
     <hyperlink ref="H135" r:id="rId134"/>
     <hyperlink ref="H136" r:id="rId135"/>
-    <hyperlink ref="H137" r:id="rId136"/>
-    <hyperlink ref="H138" r:id="rId137"/>
-    <hyperlink ref="H139" r:id="rId138"/>
-    <hyperlink ref="H140" r:id="rId139"/>
-    <hyperlink ref="H141" r:id="rId140"/>
-    <hyperlink ref="H142" r:id="rId141"/>
-    <hyperlink ref="H143" r:id="rId142"/>
-    <hyperlink ref="H144" r:id="rId143"/>
-    <hyperlink ref="H145" r:id="rId144"/>
-    <hyperlink ref="H146" r:id="rId145"/>
-    <hyperlink ref="H147" r:id="rId146"/>
-    <hyperlink ref="H148" r:id="rId147"/>
-    <hyperlink ref="H149" r:id="rId148"/>
-    <hyperlink ref="H150" r:id="rId149"/>
-    <hyperlink ref="H151" r:id="rId150"/>
-    <hyperlink ref="H152" r:id="rId151"/>
-    <hyperlink ref="H153" r:id="rId152"/>
-    <hyperlink ref="H154" r:id="rId153"/>
-    <hyperlink ref="H155" r:id="rId154"/>
-    <hyperlink ref="H156" r:id="rId155"/>
-    <hyperlink ref="H157" r:id="rId156"/>
-    <hyperlink ref="H158" r:id="rId157"/>
-    <hyperlink ref="H159" r:id="rId158"/>
-    <hyperlink ref="H160" r:id="rId159"/>
-    <hyperlink ref="H161" r:id="rId160"/>
-    <hyperlink ref="H162" r:id="rId161"/>
-    <hyperlink ref="H163" r:id="rId162"/>
-    <hyperlink ref="H164" r:id="rId163"/>
-    <hyperlink ref="H165" r:id="rId164"/>
-    <hyperlink ref="H166" r:id="rId165"/>
-    <hyperlink ref="H167" r:id="rId166"/>
-    <hyperlink ref="H168" r:id="rId167"/>
-    <hyperlink ref="H169" r:id="rId168"/>
-    <hyperlink ref="H170" r:id="rId169"/>
-    <hyperlink ref="H171" r:id="rId170"/>
-    <hyperlink ref="H172" r:id="rId171"/>
-    <hyperlink ref="H173" r:id="rId172"/>
-    <hyperlink ref="H174" r:id="rId173"/>
-    <hyperlink ref="H175" r:id="rId174"/>
-    <hyperlink ref="H176" r:id="rId175"/>
-    <hyperlink ref="H177" r:id="rId176"/>
-    <hyperlink ref="H178" r:id="rId177"/>
-    <hyperlink ref="H179" r:id="rId178"/>
-    <hyperlink ref="H180" r:id="rId179"/>
+    <hyperlink ref="H138" r:id="rId136"/>
+    <hyperlink ref="H139" r:id="rId137"/>
+    <hyperlink ref="H140" r:id="rId138"/>
+    <hyperlink ref="H141" r:id="rId139"/>
+    <hyperlink ref="H142" r:id="rId140"/>
+    <hyperlink ref="H143" r:id="rId141"/>
+    <hyperlink ref="H144" r:id="rId142"/>
+    <hyperlink ref="H145" r:id="rId143"/>
+    <hyperlink ref="H146" r:id="rId144"/>
+    <hyperlink ref="H147" r:id="rId145"/>
+    <hyperlink ref="H148" r:id="rId146"/>
+    <hyperlink ref="H149" r:id="rId147"/>
+    <hyperlink ref="H150" r:id="rId148"/>
+    <hyperlink ref="H151" r:id="rId149"/>
+    <hyperlink ref="H152" r:id="rId150"/>
+    <hyperlink ref="H153" r:id="rId151"/>
+    <hyperlink ref="H154" r:id="rId152"/>
+    <hyperlink ref="H155" r:id="rId153"/>
+    <hyperlink ref="H156" r:id="rId154"/>
+    <hyperlink ref="H157" r:id="rId155"/>
+    <hyperlink ref="H158" r:id="rId156"/>
+    <hyperlink ref="H159" r:id="rId157"/>
+    <hyperlink ref="H160" r:id="rId158"/>
+    <hyperlink ref="H161" r:id="rId159"/>
+    <hyperlink ref="H162" r:id="rId160"/>
+    <hyperlink ref="H163" r:id="rId161"/>
+    <hyperlink ref="H164" r:id="rId162"/>
+    <hyperlink ref="H165" r:id="rId163"/>
+    <hyperlink ref="H166" r:id="rId164"/>
+    <hyperlink ref="H167" r:id="rId165"/>
+    <hyperlink ref="H168" r:id="rId166"/>
+    <hyperlink ref="H169" r:id="rId167"/>
+    <hyperlink ref="H170" r:id="rId168"/>
+    <hyperlink ref="H171" r:id="rId169"/>
+    <hyperlink ref="H172" r:id="rId170"/>
+    <hyperlink ref="H173" r:id="rId171"/>
+    <hyperlink ref="H174" r:id="rId172"/>
+    <hyperlink ref="H175" r:id="rId173"/>
+    <hyperlink ref="H176" r:id="rId174"/>
+    <hyperlink ref="H177" r:id="rId175"/>
+    <hyperlink ref="H178" r:id="rId176"/>
+    <hyperlink ref="H179" r:id="rId177"/>
+    <hyperlink ref="H180" r:id="rId178"/>
+    <hyperlink ref="H181" r:id="rId179"/>
+    <hyperlink ref="H182" r:id="rId180"/>
+    <hyperlink ref="H183" r:id="rId181"/>
+    <hyperlink ref="H184" r:id="rId182"/>
+    <hyperlink ref="H185" r:id="rId183"/>
+    <hyperlink ref="H186" r:id="rId184"/>
+    <hyperlink ref="H187" r:id="rId185"/>
+    <hyperlink ref="H188" r:id="rId186"/>
+    <hyperlink ref="H189" r:id="rId187"/>
+    <hyperlink ref="H190" r:id="rId188"/>
+    <hyperlink ref="H191" r:id="rId189"/>
+    <hyperlink ref="H192" r:id="rId190"/>
+    <hyperlink ref="H193" r:id="rId191"/>
+    <hyperlink ref="H194" r:id="rId192"/>
+    <hyperlink ref="H195" r:id="rId193"/>
+    <hyperlink ref="H196" r:id="rId194"/>
+    <hyperlink ref="H197" r:id="rId195"/>
+    <hyperlink ref="H198" r:id="rId196"/>
+    <hyperlink ref="H199" r:id="rId197"/>
+    <hyperlink ref="H200" r:id="rId198"/>
+    <hyperlink ref="H201" r:id="rId199"/>
+    <hyperlink ref="H202" r:id="rId200"/>
+    <hyperlink ref="H203" r:id="rId201"/>
+    <hyperlink ref="H204" r:id="rId202"/>
+    <hyperlink ref="H205" r:id="rId203"/>
+    <hyperlink ref="H206" r:id="rId204"/>
+    <hyperlink ref="H207" r:id="rId205"/>
+    <hyperlink ref="H208" r:id="rId206"/>
+    <hyperlink ref="H209" r:id="rId207"/>
+    <hyperlink ref="H210" r:id="rId208"/>
+    <hyperlink ref="H211" r:id="rId209"/>
+    <hyperlink ref="H212" r:id="rId210"/>
+    <hyperlink ref="H213" r:id="rId211"/>
+    <hyperlink ref="H214" r:id="rId212"/>
+    <hyperlink ref="H215" r:id="rId213"/>
+    <hyperlink ref="H216" r:id="rId214"/>
+    <hyperlink ref="H217" r:id="rId215"/>
+    <hyperlink ref="H218" r:id="rId216"/>
+    <hyperlink ref="H219" r:id="rId217"/>
+    <hyperlink ref="H220" r:id="rId218"/>
+    <hyperlink ref="H221" r:id="rId219"/>
+    <hyperlink ref="H222" r:id="rId220"/>
+    <hyperlink ref="H223" r:id="rId221"/>
+    <hyperlink ref="H224" r:id="rId222"/>
+    <hyperlink ref="H225" r:id="rId223"/>
+    <hyperlink ref="H226" r:id="rId224"/>
+    <hyperlink ref="H227" r:id="rId225"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="618">
   <si>
     <t>fecha</t>
   </si>
@@ -2324,9 +2324,6 @@
       <c r="H3" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="I3" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
@@ -2411,9 +2408,6 @@
       <c r="H6" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="I6" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
@@ -2440,9 +2434,6 @@
       <c r="H7" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="I7" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
@@ -2469,9 +2460,6 @@
       <c r="H8" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I8" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
@@ -2498,9 +2486,6 @@
       <c r="H9" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="I9" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
@@ -2527,9 +2512,6 @@
       <c r="H10" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="I10" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
@@ -2556,9 +2538,6 @@
       <c r="H11" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="I11" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
@@ -2585,9 +2564,6 @@
       <c r="H12" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="I12" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
@@ -2614,9 +2590,6 @@
       <c r="H13" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="I13" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
@@ -2643,9 +2616,6 @@
       <c r="H14" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="I14" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
@@ -2672,9 +2642,6 @@
       <c r="H15" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="I15" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
@@ -2701,9 +2668,6 @@
       <c r="H16" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="I16" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
@@ -2730,9 +2694,6 @@
       <c r="H17" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="I17" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
@@ -2759,9 +2720,6 @@
       <c r="H18" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="I18" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
@@ -2788,9 +2746,6 @@
       <c r="H19" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="I19" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
@@ -2817,9 +2772,6 @@
       <c r="H20" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="I20" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
@@ -2846,9 +2798,6 @@
       <c r="H21" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="I21" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
@@ -2875,9 +2824,6 @@
       <c r="H22" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="I22" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
@@ -2904,9 +2850,6 @@
       <c r="H23" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="I23" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
@@ -2933,9 +2876,6 @@
       <c r="H24" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="I24" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
@@ -2962,9 +2902,6 @@
       <c r="H25" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="I25" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
@@ -2991,9 +2928,6 @@
       <c r="H26" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="I26" t="s">
-        <v>96</v>
-      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
@@ -3075,9 +3009,6 @@
       <c r="H29" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="I29" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
@@ -3104,9 +3035,6 @@
       <c r="H30" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="I30" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
@@ -3133,9 +3061,6 @@
       <c r="H31" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="I31" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
@@ -3191,9 +3116,6 @@
       <c r="H33" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="I33" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
@@ -3249,9 +3171,6 @@
       <c r="H35" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="I35" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
@@ -3278,9 +3197,6 @@
       <c r="H36" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="I36" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
@@ -3307,9 +3223,6 @@
       <c r="H37" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="I37" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
@@ -3336,9 +3249,6 @@
       <c r="H38" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="I38" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
@@ -3365,9 +3275,6 @@
       <c r="H39" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="I39" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
@@ -3394,9 +3301,6 @@
       <c r="H40" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="I40" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
@@ -3423,9 +3327,6 @@
       <c r="H41" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="I41" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
@@ -3452,9 +3353,6 @@
       <c r="H42" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="I42" t="s">
-        <v>110</v>
-      </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
@@ -3481,9 +3379,6 @@
       <c r="H43" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="I43" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
@@ -3510,9 +3405,6 @@
       <c r="H44" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="I44" t="s">
-        <v>112</v>
-      </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
@@ -3539,9 +3431,6 @@
       <c r="H45" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="I45" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
@@ -3568,9 +3457,6 @@
       <c r="H46" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="I46" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
@@ -3597,9 +3483,6 @@
       <c r="H47" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="I47" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
@@ -3626,11 +3509,8 @@
       <c r="H48" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="I48" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>21</v>
       </c>
@@ -3655,11 +3535,8 @@
       <c r="H49" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="I49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -3684,11 +3561,8 @@
       <c r="H50" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="I50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -3713,11 +3587,8 @@
       <c r="H51" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="I51" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -3742,11 +3613,8 @@
       <c r="H52" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="I52" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -3771,11 +3639,8 @@
       <c r="H53" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="I53" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -3800,11 +3665,8 @@
       <c r="H54" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="I54" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -3829,11 +3691,8 @@
       <c r="H55" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="I55" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -3858,11 +3717,8 @@
       <c r="H56" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="I56" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -3887,11 +3743,8 @@
       <c r="H57" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="I57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -3916,11 +3769,8 @@
       <c r="H58" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="I58" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -3945,11 +3795,8 @@
       <c r="H59" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="I59" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -3974,11 +3821,8 @@
       <c r="H60" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="I60" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -4003,11 +3847,8 @@
       <c r="H61" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="I61" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -4032,11 +3873,8 @@
       <c r="H62" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="I62" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -4061,11 +3899,8 @@
       <c r="H63" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="I63" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -4089,9 +3924,6 @@
       </c>
       <c r="H64" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="I64" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4119,9 +3951,6 @@
       <c r="H65" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="I65" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
@@ -4174,9 +4003,6 @@
       <c r="H67" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="I67" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
@@ -4203,9 +4029,6 @@
       <c r="H68" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="I68" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
@@ -4232,9 +4055,6 @@
       <c r="H69" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="I69" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
@@ -4261,9 +4081,6 @@
       <c r="H70" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="I70" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
@@ -4290,9 +4107,6 @@
       <c r="H71" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="I71" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
@@ -4319,9 +4133,6 @@
       <c r="H72" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="I72" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
@@ -4348,9 +4159,6 @@
       <c r="H73" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="I73" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
@@ -4377,9 +4185,6 @@
       <c r="H74" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="I74" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
@@ -4406,9 +4211,6 @@
       <c r="H75" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="I75" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
@@ -4435,9 +4237,6 @@
       <c r="H76" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="I76" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
@@ -4464,9 +4263,6 @@
       <c r="H77" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="I77" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
@@ -4493,9 +4289,6 @@
       <c r="H78" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="I78" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
@@ -4551,11 +4344,8 @@
       <c r="H80" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="I80" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -4580,11 +4370,8 @@
       <c r="H81" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="I81" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -4609,11 +4396,8 @@
       <c r="H82" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="I82" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>31</v>
       </c>
@@ -4639,7 +4423,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>31</v>
       </c>
@@ -4664,11 +4448,8 @@
       <c r="H84" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="I84" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>31</v>
       </c>
@@ -4693,11 +4474,8 @@
       <c r="H85" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="I85" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>31</v>
       </c>
@@ -4722,11 +4500,8 @@
       <c r="H86" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="I86" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>31</v>
       </c>
@@ -4751,11 +4526,8 @@
       <c r="H87" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="I87" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>31</v>
       </c>
@@ -4780,11 +4552,8 @@
       <c r="H88" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="I88" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>32</v>
       </c>
@@ -4809,11 +4578,8 @@
       <c r="H89" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="I89" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>32</v>
       </c>
@@ -4838,11 +4604,8 @@
       <c r="H90" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="I90" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>32</v>
       </c>
@@ -4867,11 +4630,8 @@
       <c r="H91" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="I91" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>32</v>
       </c>
@@ -4897,7 +4657,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>32</v>
       </c>
@@ -4922,11 +4682,8 @@
       <c r="H93" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I93" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
         <v>32</v>
       </c>
@@ -4952,7 +4709,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>32</v>
       </c>
@@ -4977,11 +4734,8 @@
       <c r="H95" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="I95" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9">
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>33</v>
       </c>
@@ -5006,11 +4760,8 @@
       <c r="H96" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="I96" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9">
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>33</v>
       </c>
@@ -5036,7 +4787,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -5061,11 +4812,8 @@
       <c r="H98" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="I98" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -5090,11 +4838,8 @@
       <c r="H99" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="I99" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
         <v>34</v>
       </c>
@@ -5119,11 +4864,8 @@
       <c r="H100" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="I100" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9">
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -5149,7 +4891,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
         <v>35</v>
       </c>
@@ -5174,11 +4916,8 @@
       <c r="H102" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="I102" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
         <v>35</v>
       </c>
@@ -5203,11 +4942,8 @@
       <c r="H103" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="I103" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -5232,11 +4968,8 @@
       <c r="H104" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="I104" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
         <v>35</v>
       </c>
@@ -5261,11 +4994,8 @@
       <c r="H105" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="I105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
         <v>36</v>
       </c>
@@ -5290,11 +5020,8 @@
       <c r="H106" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="I106" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
         <v>36</v>
       </c>
@@ -5319,11 +5046,8 @@
       <c r="H107" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="I107" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>36</v>
       </c>
@@ -5348,11 +5072,8 @@
       <c r="H108" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="I108" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>36</v>
       </c>
@@ -5377,11 +5098,8 @@
       <c r="H109" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="I109" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>36</v>
       </c>
@@ -5406,11 +5124,8 @@
       <c r="H110" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="I110" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9">
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>36</v>
       </c>
@@ -5435,11 +5150,8 @@
       <c r="H111" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="I111" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>36</v>
       </c>
@@ -5464,11 +5176,8 @@
       <c r="H112" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="I112" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9">
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" t="s">
         <v>36</v>
       </c>
@@ -5494,7 +5203,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:8">
       <c r="A114" t="s">
         <v>37</v>
       </c>
@@ -5519,11 +5228,8 @@
       <c r="H114" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="I114" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9">
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
         <v>37</v>
       </c>
@@ -5548,11 +5254,8 @@
       <c r="H115" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="I115" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9">
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116" t="s">
         <v>37</v>
       </c>
@@ -5578,7 +5281,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
         <v>37</v>
       </c>
@@ -5603,11 +5306,8 @@
       <c r="H117" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="I117" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9">
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -5632,11 +5332,8 @@
       <c r="H118" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="I118" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9">
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119" t="s">
         <v>37</v>
       </c>
@@ -5661,11 +5358,8 @@
       <c r="H119" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="I119" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9">
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" t="s">
         <v>37</v>
       </c>
@@ -5690,11 +5384,8 @@
       <c r="H120" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="I120" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9">
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" t="s">
         <v>37</v>
       </c>
@@ -5719,11 +5410,8 @@
       <c r="H121" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="I121" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9">
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" t="s">
         <v>37</v>
       </c>
@@ -5748,11 +5436,8 @@
       <c r="H122" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="I122" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9">
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
         <v>38</v>
       </c>
@@ -5777,11 +5462,8 @@
       <c r="H123" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="I123" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9">
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
         <v>39</v>
       </c>
@@ -5807,7 +5489,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -5832,11 +5514,8 @@
       <c r="H125" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="I125" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9">
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -5862,7 +5541,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
         <v>41</v>
       </c>
@@ -5887,11 +5566,8 @@
       <c r="H127" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="I127" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
         <v>41</v>
       </c>
@@ -5915,9 +5591,6 @@
       </c>
       <c r="H128" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="I128" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -5945,9 +5618,6 @@
       <c r="H129" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="I129" t="s">
-        <v>194</v>
-      </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
@@ -5974,9 +5644,6 @@
       <c r="H130" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="I130" t="s">
-        <v>195</v>
-      </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
@@ -6003,9 +5670,6 @@
       <c r="H131" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="I131" t="s">
-        <v>196</v>
-      </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
@@ -6032,9 +5696,6 @@
       <c r="H132" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="I132" t="s">
-        <v>197</v>
-      </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
@@ -6119,9 +5780,6 @@
       <c r="H135" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="I135" t="s">
-        <v>200</v>
-      </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
@@ -6148,9 +5806,6 @@
       <c r="H136" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="I136" t="s">
-        <v>201</v>
-      </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
@@ -6278,9 +5933,6 @@
       <c r="H141" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="I141" t="s">
-        <v>206</v>
-      </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
@@ -6307,9 +5959,6 @@
       <c r="H142" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="I142" t="s">
-        <v>207</v>
-      </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
@@ -6336,9 +5985,6 @@
       <c r="H143" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="I143" t="s">
-        <v>208</v>
-      </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
@@ -6365,11 +6011,8 @@
       <c r="H144" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="I144" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" t="s">
         <v>43</v>
       </c>
@@ -6394,11 +6037,8 @@
       <c r="H145" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="I145" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9">
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" t="s">
         <v>43</v>
       </c>
@@ -6423,11 +6063,8 @@
       <c r="H146" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="I146" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9">
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" t="s">
         <v>43</v>
       </c>
@@ -6452,11 +6089,8 @@
       <c r="H147" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="I147" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9">
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" t="s">
         <v>44</v>
       </c>
@@ -6481,11 +6115,8 @@
       <c r="H148" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="I148" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9">
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" t="s">
         <v>44</v>
       </c>
@@ -6510,11 +6141,8 @@
       <c r="H149" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="I149" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9">
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" t="s">
         <v>44</v>
       </c>
@@ -6539,11 +6167,8 @@
       <c r="H150" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="I150" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9">
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" t="s">
         <v>44</v>
       </c>
@@ -6568,11 +6193,8 @@
       <c r="H151" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="I151" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9">
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" t="s">
         <v>44</v>
       </c>
@@ -6597,11 +6219,8 @@
       <c r="H152" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="I152" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9">
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" t="s">
         <v>44</v>
       </c>
@@ -6626,11 +6245,8 @@
       <c r="H153" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="I153" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9">
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" t="s">
         <v>44</v>
       </c>
@@ -6655,11 +6271,8 @@
       <c r="H154" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="I154" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9">
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155" t="s">
         <v>44</v>
       </c>
@@ -6684,11 +6297,8 @@
       <c r="H155" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="I155" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9">
+    </row>
+    <row r="156" spans="1:8">
       <c r="A156" t="s">
         <v>44</v>
       </c>
@@ -6714,7 +6324,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:8">
       <c r="A157" t="s">
         <v>44</v>
       </c>
@@ -6740,7 +6350,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:8">
       <c r="A158" t="s">
         <v>44</v>
       </c>
@@ -6765,11 +6375,8 @@
       <c r="H158" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="I158" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9">
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" t="s">
         <v>45</v>
       </c>
@@ -6795,7 +6402,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:8">
       <c r="A160" t="s">
         <v>45</v>
       </c>
@@ -6819,9 +6426,6 @@
       </c>
       <c r="H160" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="I160" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -6875,9 +6479,6 @@
       <c r="H162" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="I162" t="s">
-        <v>227</v>
-      </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
@@ -6959,9 +6560,6 @@
       <c r="H165" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="I165" t="s">
-        <v>230</v>
-      </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
@@ -6988,9 +6586,6 @@
       <c r="H166" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="I166" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
@@ -7043,9 +6638,6 @@
       <c r="H168" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="I168" t="s">
-        <v>233</v>
-      </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
@@ -7072,9 +6664,6 @@
       <c r="H169" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="I169" t="s">
-        <v>234</v>
-      </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
@@ -7101,9 +6690,6 @@
       <c r="H170" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="I170" t="s">
-        <v>235</v>
-      </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
@@ -7130,9 +6716,6 @@
       <c r="H171" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="I171" t="s">
-        <v>236</v>
-      </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
@@ -7159,9 +6742,6 @@
       <c r="H172" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="I172" t="s">
-        <v>237</v>
-      </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
@@ -7188,9 +6768,6 @@
       <c r="H173" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="I173" t="s">
-        <v>238</v>
-      </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
@@ -7217,9 +6794,6 @@
       <c r="H174" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="I174" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
@@ -7246,9 +6820,6 @@
       <c r="H175" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="I175" t="s">
-        <v>240</v>
-      </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
@@ -7275,11 +6846,8 @@
       <c r="H176" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="I176" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9">
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" t="s">
         <v>54</v>
       </c>
@@ -7304,11 +6872,8 @@
       <c r="H177" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="I177" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9">
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" t="s">
         <v>54</v>
       </c>
@@ -7333,11 +6898,8 @@
       <c r="H178" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="I178" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9">
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>54</v>
       </c>
@@ -7362,11 +6924,8 @@
       <c r="H179" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="I179" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9">
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" t="s">
         <v>55</v>
       </c>
@@ -7391,11 +6950,8 @@
       <c r="H180" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="I180" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9">
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" t="s">
         <v>55</v>
       </c>
@@ -7420,11 +6976,8 @@
       <c r="H181" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="I181" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9">
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182" t="s">
         <v>55</v>
       </c>
@@ -7449,11 +7002,8 @@
       <c r="H182" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="I182" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9">
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" t="s">
         <v>55</v>
       </c>
@@ -7478,11 +7028,8 @@
       <c r="H183" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="I183" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9">
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" t="s">
         <v>55</v>
       </c>
@@ -7507,11 +7054,8 @@
       <c r="H184" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="I184" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9">
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
         <v>56</v>
       </c>
@@ -7536,11 +7080,8 @@
       <c r="H185" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="I185" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9">
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" t="s">
         <v>57</v>
       </c>
@@ -7565,11 +7106,8 @@
       <c r="H186" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="I186" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9">
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" t="s">
         <v>57</v>
       </c>
@@ -7594,11 +7132,8 @@
       <c r="H187" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="I187" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9">
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" t="s">
         <v>58</v>
       </c>
@@ -7623,11 +7158,8 @@
       <c r="H188" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="I188" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9">
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" t="s">
         <v>58</v>
       </c>
@@ -7652,11 +7184,8 @@
       <c r="H189" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="I189" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9">
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" t="s">
         <v>59</v>
       </c>
@@ -7681,11 +7210,8 @@
       <c r="H190" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="I190" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9">
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" t="s">
         <v>59</v>
       </c>
@@ -7710,11 +7236,8 @@
       <c r="H191" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="I191" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9">
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" t="s">
         <v>60</v>
       </c>
@@ -7739,11 +7262,8 @@
       <c r="H192" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="I192" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9">
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" t="s">
         <v>61</v>
       </c>
@@ -7768,11 +7288,8 @@
       <c r="H193" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="I193" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9">
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" t="s">
         <v>61</v>
       </c>
@@ -7797,11 +7314,8 @@
       <c r="H194" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="I194" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9">
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" t="s">
         <v>62</v>
       </c>
@@ -7826,11 +7340,8 @@
       <c r="H195" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="I195" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9">
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" t="s">
         <v>63</v>
       </c>
@@ -7855,11 +7366,8 @@
       <c r="H196" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="I196" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9">
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197" t="s">
         <v>64</v>
       </c>
@@ -7884,11 +7392,8 @@
       <c r="H197" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="I197" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9">
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198" t="s">
         <v>64</v>
       </c>
@@ -7913,11 +7418,8 @@
       <c r="H198" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="I198" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9">
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" t="s">
         <v>65</v>
       </c>
@@ -7942,11 +7444,8 @@
       <c r="H199" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="I199" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9">
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" t="s">
         <v>66</v>
       </c>
@@ -7971,11 +7470,8 @@
       <c r="H200" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="I200" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9">
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" t="s">
         <v>67</v>
       </c>
@@ -8000,11 +7496,8 @@
       <c r="H201" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="I201" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9">
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202" t="s">
         <v>67</v>
       </c>
@@ -8029,11 +7522,8 @@
       <c r="H202" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="I202" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9">
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203" t="s">
         <v>67</v>
       </c>
@@ -8058,11 +7548,8 @@
       <c r="H203" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="I203" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9">
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204" t="s">
         <v>67</v>
       </c>
@@ -8087,11 +7574,8 @@
       <c r="H204" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="I204" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9">
+    </row>
+    <row r="205" spans="1:8">
       <c r="A205" t="s">
         <v>67</v>
       </c>
@@ -8116,11 +7600,8 @@
       <c r="H205" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="I205" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9">
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206" t="s">
         <v>67</v>
       </c>
@@ -8145,11 +7626,8 @@
       <c r="H206" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="I206" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9">
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207" t="s">
         <v>68</v>
       </c>
@@ -8174,11 +7652,8 @@
       <c r="H207" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="I207" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9">
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208" t="s">
         <v>68</v>
       </c>
@@ -8203,11 +7678,8 @@
       <c r="H208" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="I208" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9">
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209" t="s">
         <v>68</v>
       </c>
@@ -8232,11 +7704,8 @@
       <c r="H209" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="I209" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9">
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210" t="s">
         <v>68</v>
       </c>
@@ -8261,11 +7730,8 @@
       <c r="H210" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="I210" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9">
+    </row>
+    <row r="211" spans="1:8">
       <c r="A211" t="s">
         <v>68</v>
       </c>
@@ -8290,11 +7756,8 @@
       <c r="H211" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="I211" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9">
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212" t="s">
         <v>68</v>
       </c>
@@ -8319,11 +7782,8 @@
       <c r="H212" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="I212" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9">
+    </row>
+    <row r="213" spans="1:8">
       <c r="A213" t="s">
         <v>68</v>
       </c>
@@ -8348,11 +7808,8 @@
       <c r="H213" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="I213" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9">
+    </row>
+    <row r="214" spans="1:8">
       <c r="A214" t="s">
         <v>69</v>
       </c>
@@ -8377,11 +7834,8 @@
       <c r="H214" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="I214" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9">
+    </row>
+    <row r="215" spans="1:8">
       <c r="A215" t="s">
         <v>69</v>
       </c>
@@ -8406,11 +7860,8 @@
       <c r="H215" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="I215" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9">
+    </row>
+    <row r="216" spans="1:8">
       <c r="A216" t="s">
         <v>69</v>
       </c>
@@ -8435,11 +7886,8 @@
       <c r="H216" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="I216" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9">
+    </row>
+    <row r="217" spans="1:8">
       <c r="A217" t="s">
         <v>70</v>
       </c>
@@ -8464,11 +7912,8 @@
       <c r="H217" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="I217" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9">
+    </row>
+    <row r="218" spans="1:8">
       <c r="A218" t="s">
         <v>70</v>
       </c>
@@ -8493,11 +7938,8 @@
       <c r="H218" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="I218" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9">
+    </row>
+    <row r="219" spans="1:8">
       <c r="A219" t="s">
         <v>70</v>
       </c>
@@ -8522,11 +7964,8 @@
       <c r="H219" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="I219" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9">
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220" t="s">
         <v>71</v>
       </c>
@@ -8551,11 +7990,8 @@
       <c r="H220" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="I220" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9">
+    </row>
+    <row r="221" spans="1:8">
       <c r="A221" t="s">
         <v>71</v>
       </c>
@@ -8580,11 +8016,8 @@
       <c r="H221" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="I221" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9">
+    </row>
+    <row r="222" spans="1:8">
       <c r="A222" t="s">
         <v>71</v>
       </c>
@@ -8609,11 +8042,8 @@
       <c r="H222" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="I222" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9">
+    </row>
+    <row r="223" spans="1:8">
       <c r="A223" t="s">
         <v>71</v>
       </c>
@@ -8638,11 +8068,8 @@
       <c r="H223" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="I223" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9">
+    </row>
+    <row r="224" spans="1:8">
       <c r="A224" t="s">
         <v>71</v>
       </c>
@@ -8667,11 +8094,8 @@
       <c r="H224" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="I224" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9">
+    </row>
+    <row r="225" spans="1:8">
       <c r="A225" t="s">
         <v>71</v>
       </c>
@@ -8696,11 +8120,8 @@
       <c r="H225" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="I225" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9">
+    </row>
+    <row r="226" spans="1:8">
       <c r="A226" t="s">
         <v>71</v>
       </c>
@@ -8725,11 +8146,8 @@
       <c r="H226" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="I226" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9">
+    </row>
+    <row r="227" spans="1:8">
       <c r="A227" t="s">
         <v>71</v>
       </c>
@@ -8753,9 +8171,6 @@
       </c>
       <c r="H227" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="I227" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I239"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
+          <t>Cómo ir al pueblo con el 'secreto de la eterna juventud' en Colombia: tiene dulce patrimonio famoso - Pulzo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,29 +599,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/cultura</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOZ0VibTZNeVU2TTdrbm83V0NTVUw0Yjg4S0lNdE16d3BwUzRZMnd0YzlTUk1DLWRHV01PX0EtMWM2S2h3SGlhbjZpSzVJemlCYXZnY1FoU0FJZlVOcFIwNG1nU1dBNUlUa0pHOXZ1S1BBREJEaXBZV0VNWHhrWnFxMmFjRkszYzFtNnR3Q29qX3lWTGUxbWVDRkpUMzRkc0djSXVISVZpZndkbV9GZk1HYVd5VXpwczd2c3kyWG1TNjNLUmdYZnlB0gHMAUFVX3lxTE5CdUhhV0VXTUlUWHBjQjVJMml1c200d0FVV214WkZiVERpODg1Q0VTZmxBU2lqT0lrc0YyajhTZUhIRWJZTHZoNkRLUzZfNTk5amZ1SnhhSU5KbVBfdk9CeGpQTzVodTMwTFh6ZElWcFVsZmN5cS1LblBGandid3VocVlVaHBoNVpzbGJrNThhMVBEYS1pM1Y5ZlktVDZYYkw0bklmOGQ4X01Za3RtYzdselVRMXZtRjZWSjVlV283eXhKT0QxdU9XN0lJQw?oc=5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>“Boom” de deudores jóvenes: más tarjetas, más riesgo; así es la nueva cara del crédito en Colombia - ELTIEMPO.COM</t>
+          <t>Colombia recibió a jóvenes latinoamericanos para reflexionar sobre el futuro de la democracia en la era digital - Organización de Estados Iberoamericanos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Organización de Estados Iberoamericanos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,7 +642,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQSldNa3RSdGU3cW1YdzJGc2JTYks2Yzc0Sl9lSTZvZF9WblJOa0ZMVFVoSkpCejAtM2NmZHhEbjFHWEI4bUh3cHJOWFktV0hkeWxqZ3BvNDhMWERyQ1BRdUpPVmJjdjBvZG1TWTRjMm9QWmsyMlFvOG56Sm1TaUdWYnhYZVRaX3Y1T1V3ZkFGdnIydncxUjV2dzhsSWVyaHlWcmNERlJpeUVxZXVDdmczZFZDRnYyWmlaUXIyRXM3anB5UTVzdFprWG9vTTNkcUNDMmNLUk5EbC1FQzhVTmVOTVd4YjBrXy0za015dzNZU2tld9IB9wFBVV95cUxNXy1zRWx4U1U2cFNiWjZ1d1pJWFpxS1hiMzdHbVVqV1ZaV01yT0k3V2FBVEhDSHZkTExnOFZmM1ZsLURvV0gtbE1qRllwYVcyaEZMLTItNGY5dU82QUMzdVNYaFlYbUhhMDloRll3dVFjY3B6eUk3VUFRaWFkaHVRXzQ0RGVZdWgzWUY3R1RPMlNvY3ZBbWJEYnY3NUNoSHZGTTI0bXdwWE5HYkFBejMxc1FOb2l0ajdsQkdidXUxcHhOUzlraXFDd1NteXhHeTBQaUpodE5WV1lkcXJyT0FVUi1rcGk2eUdPaWZmWmZGVlFBZ3BDaktn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNa1hCWjNMbE5tMHQ0LU1MTm9kTWRNcVJ4WHVSeml4TW5SYmlzTndaVW55aDlGcmNxdm1vdnZjdlJmeGt4bVc4SGRybElQSnl4dXdiUVNvVW4tMVMwMFFZakNvYURvMlNoM1h2MG9TZUhZZDl1c3V4eldmSExNWUlqdE1CYzBGR3QzOXpobXBBZWRUcWJwclJULVVISndXTEU0akNmNk5SVUlFQzhHQmM0ZW9aZVNLQkl4aFBfQTBsaGNxcWd5d0tiVUhXM042dE43VW1pUkhaclR1aEVlak1YckwtMnB4RmJPcnJKc3F0aFZ5N2NE?oc=5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -702,7 +698,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -717,27 +713,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
@@ -749,102 +745,106 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+          <t>https://www.diarioadn.co/seccion/cultura</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jóvenes habitantes de calle serán guardianes de Bogotá: se capacitarán en temas de reciclaje - Bogota.gov.co</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZTlVbXhUR0VMSmF3NDJXWVlwWmwyYzBISlQ0MVRNSUdOSWQwcThFZWt3eTBJUmpRMVl1YkVDR3NSa0FEWEpqdVJfWnlNcHA4SWhpai05OHo0czdBVF8wTnlLVGRfVEpzeEc4NDhXcGlEaThvcDlHdXJIZ01INDlaN1lad2tubHVWM0Z0ZFlEOGV0dmhESjNmZDJPMFlJY01ETHBNUmhlOWtJZkNaUkRkQnowdHd3Wlp2MlE?oc=5</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alcaldía conecta a estudiantes con universidades y oportunidades de financiación - Alcaldía de Armenia</t>
+          <t>“Boom” de deudores jóvenes: más tarjetas, más riesgo; así es la nueva cara del crédito en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alcaldía de Armenia</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSGNJLWNiT0JsQlpPUmVWSjJDZE82M2pOVGtLNkozcXFjdU5pa1pMaENkbFQ3c3dmSGc2X1dtdy1KM0txRUlaMjNvZEY3T19lNmZmWk1wZllDdWhqelEzd3ludXhRRnlVZG9OU09xLTlyLUUzTWE2LTFGcURsWmVFeWNxc3lLY05hWFZsR1FwTTFGZl9ZeURESE1HTkoxbWhhMVp2TWg3bklENzFsakRkdUlIQXAwT1pUZlVDMTBqMlBYS1JxQ3BzeGZ2VmF6ZU12c24xVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQSldNa3RSdGU3cW1YdzJGc2JTYks2Yzc0Sl9lSTZvZF9WblJOa0ZMVFVoSkpCejAtM2NmZHhEbjFHWEI4bUh3cHJOWFktV0hkeWxqZ3BvNDhMWERyQ1BRdUpPVmJjdjBvZG1TWTRjMm9QWmsyMlFvOG56Sm1TaUdWYnhYZVRaX3Y1T1V3ZkFGdnIydncxUjV2dzhsSWVyaHlWcmNERlJpeUVxZXVDdmczZFZDRnYyWmlaUXIyRXM3anB5UTVzdFprWG9vTTNkcUNDMmNLUk5EbC1FQzhVTmVOTVd4YjBrXy0za015dzNZU2tld9IB9wFBVV95cUxNXy1zRWx4U1U2cFNiWjZ1d1pJWFpxS1hiMzdHbVVqV1ZaV01yT0k3V2FBVEhDSHZkTExnOFZmM1ZsLURvV0gtbE1qRllwYVcyaEZMLTItNGY5dU82QUMzdVNYaFlYbUhhMDloRll3dVFjY3B6eUk3VUFRaWFkaHVRXzQ0RGVZdWgzWUY3R1RPMlNvY3ZBbWJEYnY3NUNoSHZGTTI0bXdwWE5HYkFBejMxc1FOb2l0ajdsQkdidXUxcHhOUzlraXFDd1NteXhHeTBQaUpodE5WV1lkcXJyT0FVUi1rcGk2eUdPaWZmWmZGVlFBZ3BDaktn?oc=5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
+          <t>En el oriente de Cali tenían a dos adolescentes que serían reclutados por la estructura criminal 'Jacobo Arenas': los iban a llevar al Cauca - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxPUDNwLXRyY3FHY2JlX0luT0d3UzBjSXpGZFBsRFptUnBFUTZRbVJLWUhWQmpVVzhlc1pVMEMtSjhCR2NvRFNocGtCZkZ3MDFxbEFJci10bmZtdGdFS0R5WGtnMU1lOTJxSXBpSVQtMlRKSGtWaWpmWE0tbzdqNHF2RVpYQ0UwUmYtVlMxMFJmZGpReHZhWm1uYUFKQmtIbjRsS2FUdzFDcFVidlQ1cjBuR0RkUTB1YUVhN0hQNTdELVdQYy1lcDZ5a09YUllmLUVFck1DemFsX2hSOVVjZEZhZm5XY2FWYjFXblNmenZxb0JrUVVvT3pHRW5PUlhKZEVuUlZSSklUMGpmZ0hxX2VZaURuamxFeW_SAZcCQVVfeXFMT1AzcC10cmNxR2NiZV9Jbk9Hd1MwY0l6RmRQbERabVJwRVE2UW1SS1lIVkJqVVc4ZXNaVTBDLUo4Qkdjb0RTaHBrQmZGdzAxcWxBSXItdG5mbXRnRUtEeVhrZzFNZTkycUlwaUlULTJUSkhrVmlqZlhNLW83ajRxdkVaWENFMFJmLVZTMTBSZmRqUXh2YVptbmFBSkJrSG40bEthVHcxQ3BVYnZUNXIwbkdEZFEwdWFFYTdIUDU3RC1XUGMtZXA2eWtPWFJZZi1FRXJNQ3phbF9oUjlVY2RGYWZuV2NhVmIxV25TZnp2cW9Ca1FVb096R0VuT1JYSmRFblJWUkpJVDBqZmdIcV9lWWlEbmpsRXlv?oc=5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -925,12 +925,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>En el oriente de Cali tenían a dos adolescentes que serían reclutados por la estructura criminal 'Jacobo Arenas': los iban a llevar al Cauca - ELTIEMPO.COM</t>
+          <t>Plan en Bogotá busca convertir a jóvenes habitantes de calle en promotores ambientales - Periodismo Público</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Periodismo Público</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -940,22 +940,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxPUDNwLXRyY3FHY2JlX0luT0d3UzBjSXpGZFBsRFptUnBFUTZRbVJLWUhWQmpVVzhlc1pVMEMtSjhCR2NvRFNocGtCZkZ3MDFxbEFJci10bmZtdGdFS0R5WGtnMU1lOTJxSXBpSVQtMlRKSGtWaWpmWE0tbzdqNHF2RVpYQ0UwUmYtVlMxMFJmZGpReHZhWm1uYUFKQmtIbjRsS2FUdzFDcFVidlQ1cjBuR0RkUTB1YUVhN0hQNTdELVdQYy1lcDZ5a09YUllmLUVFck1DemFsX2hSOVVjZEZhZm5XY2FWYjFXblNmenZxb0JrUVVvT3pHRW5PUlhKZEVuUlZSSklUMGpmZ0hxX2VZaURuamxFeW_SAZcCQVVfeXFMT1AzcC10cmNxR2NiZV9Jbk9Hd1MwY0l6RmRQbERabVJwRVE2UW1SS1lIVkJqVVc4ZXNaVTBDLUo4Qkdjb0RTaHBrQmZGdzAxcWxBSXItdG5mbXRnRUtEeVhrZzFNZTkycUlwaUlULTJUSkhrVmlqZlhNLW83ajRxdkVaWENFMFJmLVZTMTBSZmRqUXh2YVptbmFBSkJrSG40bEthVHcxQ3BVYnZUNXIwbkdEZFEwdWFFYTdIUDU3RC1XUGMtZXA2eWtPWFJZZi1FRXJNQ3phbF9oUjlVY2RGYWZuV2NhVmIxV25TZnp2cW9Ca1FVb096R0VuT1JYSmRFblJWUkpJVDBqZmdIcV9lWWlEbmpsRXlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNYjhpNDNHdXpiRVI4Uk56Tlk0dlZQbVZUa0RvN1VMTW9ubU1vTDI3Q3R1WW1nUDYyUzRkM0NubGN0dXBvY0xWRVdwaW9qQzQyc3NSLU9FRV91OGh1bnVvanhrcmFpdVl6amdvNnpQamNQMFktX0hPdUl2SkNnbFI3WFNSakhyQVpSOGt5elZGcGc4blNici10bXpmTHM0TlIxNUdBT2x3YkMyb3lvT044aXRNWDg1Z0E?oc=5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -968,12 +968,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Plan en Bogotá busca convertir a jóvenes habitantes de calle en promotores ambientales - Periodismo Público</t>
+          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Periodismo Público</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNYjhpNDNHdXpiRVI4Uk56Tlk0dlZQbVZUa0RvN1VMTW9ubU1vTDI3Q3R1WW1nUDYyUzRkM0NubGN0dXBvY0xWRVdwaW9qQzQyc3NSLU9FRV91OGh1bnVvanhrcmFpdVl6amdvNnpQamNQMFktX0hPdUl2SkNnbFI3WFNSakhyQVpSOGt5elZGcGc4blNici10bXpmTHM0TlIxNUdBT2x3YkMyb3lvT044aXRNWDg1Z0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1006,17 +1006,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños - Yahoo</t>
+          <t>Alcaldía conecta a estudiantes con universidades y oportunidades de financiación - Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNaV96T3o5U1J0ZnloNEVVajBYWVktU3BzNFV5Y1ZpbmdOQmhCSE5ONTRneUxtdDJESjZ0SDRfMjNYOUpZTUZjZlF0elAzTzdTMXlndExqMzZRQS1FNUhoRjRUU05SZ1dHR0V4SkJ2bHZzNlphN094aERlTnk5a29LYldYcWVMYW1tYTdsQjN5Y0g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSGNJLWNiT0JsQlpPUmVWSjJDZE82M2pOVGtLNkozcXFjdU5pa1pMaENkbFQ3c3dmSGc2X1dtdy1KM0txRUlaMjNvZEY3T19lNmZmWk1wZllDdWhqelEzd3ludXhRRnlVZG9OU09xLTlyLUUzTWE2LTFGcURsWmVFeWNxc3lLY05hWFZsR1FwTTFGZl9ZeURESE1HTkoxbWhhMVp2TWg3bklENzFsakRkdUlIQXAwT1pUZlVDMTBqMlBYS1JxQ3BzeGZ2VmF6ZU12c24xVw?oc=5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1049,17 +1049,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Elecciones 2026: 70% de los jóvenes en Colombia todavía no saben por quién votar a la Presidencia, según encuesta | El Colombiano - El Colombiano</t>
+          <t>Jóvenes habitantes de calle serán guardianes de Bogotá: se capacitarán en temas de reciclaje - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZlNPMmVNZ0lHTEh6bFpBTjJqUzZXdU11czVXbDBYeTNhS2k5ODRJejhtU2NQRDZqd3p4eFMxOEVLSWl3UUU1RmNicy1ZVnItc2FiWHBnTlJVd3c2SUlUSzAyQVBQYTlZc2VaUUlIOXBtSFp4UDY1TWlfcHdNQjVSVmUzTldUUGxqbzVDY0tsb29mOEo2S3FlNXVWWXpHd2FtM3dYNzN1QjhwUUd4YnN3adIBtgFBVV95cUxPb2Z2OW1VRWVkVU90ZUpaanJ4NklTejBBaUNSQ2MzTERhb1JZZEJHY1lYeUhydmVkelB5cGVDRTliNHVHV1JEc0dlQURNbWJmVElfdUhwMzNhREh5WnQwMkgzVFZqTElNNkUxMzdYYVlhbDZEemhpNmFScHUzM3JVc3ZQOXAxQU1HRXJpU3FxQTNhSFZnb21qZHl4ejJ5a2VNbFNPLVJ6Wk1qeEt6amhzc1Q2aTNUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZTlVbXhUR0VMSmF3NDJXWVlwWmwyYzBISlQ0MVRNSUdOSWQwcThFZWt3eTBJUmpRMVl1YkVDR3NSa0FEWEpqdVJfWnlNcHA4SWhpai05OHo0czdBVF8wTnlLVGRfVEpzeEc4NDhXcGlEaThvcDlHdXJIZ01INDlaN1lad2tubHVWM0Z0ZFlEOGV0dmhESjNmZDJPMFlJY01ETHBNUmhlOWtJZkNaUkRkQnowdHd3Wlp2MlE?oc=5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños | El Colombiano - El Colombiano</t>
+          <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños - Yahoo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQSDhDeEZJVVh5SGI1Zk1iekZWQnhDbVctZnVUYzhqQ2E1aWJRS1VCeHVkNGw0ZWpPQm1Eci1LcDdFWGZXU181dHk1R29RRC1QeXZuWFNSYXhLUjhubTBBRnQ1T01zV2VpZEw2VHBzYkNFbWVrdFlFNWtKX0p4a0N2dlV2aXBBX29hWlpyVk9jR0lOVzJ1WmIwRW9lTkQ4THBxSkhiNTlZa9IBrAFBVV95cUxNWjh0d2x2QVNiM0Y2WXNZeXYyZm1mUEkxOG9LMjBjcWVhbjVwMjlvdUtLOVNJVk5ZNTR3dkd4RW9GVGMwZ19GUEhPckRrdGVFZVVSN2ZDaWFGbDZUX2d2dDJMQm4zNkZmYkYzbjVEbWJRcTJLaVktR19CN2pYNzkzaTRPdW9OeW5IVzFGWU9fbnpTeWM5ODZ2MHdNa0dXVFM2QXFzQS0wRnRrNXVa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNaV96T3o5U1J0ZnloNEVVajBYWVktU3BzNFV5Y1ZpbmdOQmhCSE5ONTRneUxtdDJESjZ0SDRfMjNYOUpZTUZjZlF0elAzTzdTMXlndExqMzZRQS1FNUhoRjRUU05SZ1dHR0V4SkJ2bHZzNlphN094aERlTnk5a29LYldYcWVMYW1tYTdsQjN5Y0g?oc=5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jóvenes en Colombia están eligiendo las carreras universitarias teniendo en cuenta la demanda: conozca cuáles son - Portafolio.co</t>
+          <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portafolio.co</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNTmo1b3RtV2pFUnA5UXRpTUJyOE5NM3VWMkotNkppc0tCMXlyMWI5d3A0T08tcllCMGtvWHoyVWtlbjRnM2ZZV1piaTdabXJWV1ZLS2dXWm4zV2NFb2Z6NnplSXRsV0tjSHMtNWVUU0VfNjN0a3lycjBOTHd2bk5qT1pUQ2dCTWphbzlOX1d1Ylg5bXI2Ml9pQXFSa2lYQjZFRUZDaDlOdlpTRENVZHJ5dkRSOGVIV0ZhdUJIUGxUeGRFVnl1R2fSAcsBQVVfeXFMUHBoR2RJZDlxTW9Jc1VTYk1SR3ViZi1EUmpOenBYLXAzUDhaM3gtaV95T2dwaDZ4cjdJRVhNdjZfSmZWLXFaclBfc1ktWnJGVndfTmE1aFM0M2pFZUcxbDdQdEpOQmEtVThvdmVEd3dSOUNiWlpGaF9oOVNxTUN5UURsZVRDb2w4WUZPZTlPNi03S1V1ZGh2RHZ0ZlFpc0k0R3RXQVlNTkNJbUxNVk9NSnlmUHVmRlE0UEFYN1NzT0NRT0tobGZYcDNkWGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQSDhDeEZJVVh5SGI1Zk1iekZWQnhDbVctZnVUYzhqQ2E1aWJRS1VCeHVkNGw0ZWpPQm1Eci1LcDdFWGZXU181dHk1R29RRC1QeXZuWFNSYXhLUjhubTBBRnQ1T01zV2VpZEw2VHBzYkNFbWVrdFlFNWtKX0p4a0N2dlV2aXBBX29hWlpyVk9jR0lOVzJ1WmIwRW9lTkQ4THBxSkhiNTlZa9IBrAFBVV95cUxNWjh0d2x2QVNiM0Y2WXNZeXYyZm1mUEkxOG9LMjBjcWVhbjVwMjlvdUtLOVNJVk5ZNTR3dkd4RW9GVGMwZ19GUEhPckRrdGVFZVVSN2ZDaWFGbDZUX2d2dDJMQm4zNkZmYkYzbjVEbWJRcTJLaVktR19CN2pYNzkzaTRPdW9OeW5IVzFGWU9fbnpTeWM5ODZ2MHdNa0dXVFM2QXFzQS0wRnRrNXVa?oc=5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace - Bogota.gov.co</t>
+          <t>Jóvenes en Colombia están eligiendo las carreras universitarias teniendo en cuenta la demanda: conozca cuáles son - Portafolio.co</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>Portafolio.co</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOGlJcXNqT09nb1VFRXJYa3RTckd5Vklkb3RwSXJvNlV0cml2aDQ5ckhveDdJYVhRZzJfVHBSYmlGTTRhV2lLODQ4Zk52SmFBVDhCXzFuVTh5U2pfM2tOVWRLZGRQN0kwRUcyUGI2UXhhOWVTUGoxcjRTVmFFVHZsX3prZ2F5NThtaE5ZX1lYcGNMMkpNdVBxUjNmMHJtVXlNTndsZ09LdjRRaE1JeW9EWS0xMXR5NGJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNTmo1b3RtV2pFUnA5UXRpTUJyOE5NM3VWMkotNkppc0tCMXlyMWI5d3A0T08tcllCMGtvWHoyVWtlbjRnM2ZZV1piaTdabXJWV1ZLS2dXWm4zV2NFb2Z6NnplSXRsV0tjSHMtNWVUU0VfNjN0a3lycjBOTHd2bk5qT1pUQ2dCTWphbzlOX1d1Ylg5bXI2Ml9pQXFSa2lYQjZFRUZDaDlOdlpTRENVZHJ5dkRSOGVIV0ZhdUJIUGxUeGRFVnl1R2fSAcsBQVVfeXFMUHBoR2RJZDlxTW9Jc1VTYk1SR3ViZi1EUmpOenBYLXAzUDhaM3gtaV95T2dwaDZ4cjdJRVhNdjZfSmZWLXFaclBfc1ktWnJGVndfTmE1aFM0M2pFZUcxbDdQdEpOQmEtVThvdmVEd3dSOUNiWlpGaF9oOVNxTUN5UURsZVRDb2w4WUZPZTlPNi03S1V1ZGh2RHZ0ZlFpc0k0R3RXQVlNTkNJbUxNVk9NSnlmUHVmRlE0UEFYN1NzT0NRT0tobGZYcDNkWGM?oc=5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1221,17 +1221,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Carreras académicas más elegidas por los jóvenes en Colombia este 2026: tecnología y salud son algunas - ELTIEMPO.COM</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1241,22 +1241,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNbG9GRW1GYVhUNWlIWDJ0eHdlNHdvenBSeW80MFF6aThCWi0xcUZmN2VlTnoyY3dVdjZaRDJocENhQnRrMGdfa3Y4Z2diS0F2RU9lTXdyUkM4a1pESnB4Qzc5bFJXeEZfYTZfWFRHV0lFVTU2M3daMFpWUk53OU5wR1luNXFoejNYc0xBb2kwZHhqck9obW1DaGtUR1Z5bWdKa2ZGQmFWaGRBNTRITXBpNF84NVBDTGtiZkc3WlJ6bkxSc1RRZklrUUhaaXdGNXFHOU82eDR3M2prcUstMHZQZ0xKSdIB6AFBVV95cUxOb3lzVlp1cU5CN3lTU0F4bm1aVk1SeENCd2JIQzI5aXhaZGJfWUlhWXBpSnQ2NjhGZFlOY2NrbzYwdWdZOVZfVF9vUE5zYVhSaGtPbjd1WVVRNUZBYjlVZkVTZW13ZWZrbld6SjNDN1FtU2M1M2F5REtidFFuTzByV2g0TDBUOFp0Wms1Sm5IV2plTHp4UkpDMjJSMWdaRExXVE5uSmx0VzZXR2VlVDkxTWY0SE1TRVU1QVZLMGV3eUp0andRVm8zOW4zTFdvdWlxd2dldVAtOTVDU0xCVy1TQmQ2SUJtd1Fr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOGlJcXNqT09nb1VFRXJYa3RTckd5Vklkb3RwSXJvNlV0cml2aDQ5ckhveDdJYVhRZzJfVHBSYmlGTTRhV2lLODQ4Zk52SmFBVDhCXzFuVTh5U2pfM2tOVWRLZGRQN0kwRUcyUGI2UXhhOWVTUGoxcjRTVmFFVHZsX3prZ2F5NThtaE5ZX1lYcGNMMkpNdVBxUjNmMHJtVXlNTndsZ09LdjRRaE1JeW9EWS0xMXR5NGJZ?oc=5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1264,17 +1264,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
+          <t>Elecciones 2026: 70% de los jóvenes en Colombia todavía no saben por quién votar a la Presidencia, según encuesta | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bogota.alerta.com.co</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1284,22 +1284,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOblktRDZRdDlQREx0SWFrYjhnWkoxMmY3MHJJcEJCQU9lbDcwUi1wTFAtVTVySlhnbG9LNGtpd2NHZ05VQ1p0cFpqNkdiU05ENWlISEZUQV9aNExDb3NUUHU1MkduSHJ5LUlsUlhYR0FOMkRvVXloSW1PS1RZZzV3T3VUU1EyQWdGMWhmQTF4a1ZXV0ZlRFRvdDVQcVgyN1ZyakZoeEZuZXpGbG53ZzVfdG5oQ01lajJo0gG8AUFVX3lxTE45S1pNZFFOTUdlajl3elgyYkNGZ01TVGxaRjVPMENmQ2Qwek1GQUhGcVNSSURsN01uM1FYSTR4R2J5U29LSVRWbElNc3hOaUo4V09MdG82SnhHWUFMd1hqTU5DWTFtWmJOZEZqUFRjUmtaZUs4YXQyWjdMZjVyS0J6Q1FNbHBfNENodDRGQ3VZNGVwY2RTS1YzekN4UkwtakV4TlFPYzU5WFA3aGJmd01YOHpfQUNiZ21xSTJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZlNPMmVNZ0lHTEh6bFpBTjJqUzZXdU11czVXbDBYeTNhS2k5ODRJejhtU2NQRDZqd3p4eFMxOEVLSWl3UUU1RmNicy1ZVnItc2FiWHBnTlJVd3c2SUlUSzAyQVBQYTlZc2VaUUlIOXBtSFp4UDY1TWlfcHdNQjVSVmUzTldUUGxqbzVDY0tsb29mOEo2S3FlNXVWWXpHd2FtM3dYNzN1QjhwUUd4YnN3adIBtgFBVV95cUxPb2Z2OW1VRWVkVU90ZUpaanJ4NklTejBBaUNSQ2MzTERhb1JZZEJHY1lYeUhydmVkelB5cGVDRTliNHVHV1JEc0dlQURNbWJmVElfdUhwMzNhREh5WnQwMkgzVFZqTElNNkUxMzdYYVlhbDZEemhpNmFScHUzM3JVc3ZQOXAxQU1HRXJpU3FxQTNhSFZnb21qZHl4ejJ5a2VNbFNPLVJ6Wk1qeEt6amhzc1Q2aTNUdw?oc=5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Colegios en Colombia implementarán cátedra obligatoria de protección animal y biodiversidad - Senado.gov.co</t>
+          <t>Carreras académicas más elegidas por los jóvenes en Colombia este 2026: tecnología y salud son algunas - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Senado.gov.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPdkRscDEzLTMzYnhsa2M2N2JfZ3M4ampEZzM5ZVFDRm9aSHBySC1idWljUS1BbW8yVjlUcmF4YW9NNVA2M0dzblQ3aGo3emV5RTFnc1ZkclFHWF9XVDBubmU2Q0lpQmJCTzFiUTNOMnNIdm90NmJua0RwNlNuZXJ1bDIweU95akZQWmFNcmFfT2sxNG1Qb3BDU3hyQmJsT3hqQVlHZnBGb2RNUnJBS201YzV6SFVRR21IX0U3eHNSZEo3MFNuZmVPakgwZGEzVlFYTGJZcEg0dGtSdFpvMnU3TExoMzIxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNbG9GRW1GYVhUNWlIWDJ0eHdlNHdvenBSeW80MFF6aThCWi0xcUZmN2VlTnoyY3dVdjZaRDJocENhQnRrMGdfa3Y4Z2diS0F2RU9lTXdyUkM4a1pESnB4Qzc5bFJXeEZfYTZfWFRHV0lFVTU2M3daMFpWUk53OU5wR1luNXFoejNYc0xBb2kwZHhqck9obW1DaGtUR1Z5bWdKa2ZGQmFWaGRBNTRITXBpNF84NVBDTGtiZkc3WlJ6bkxSc1RRZklrUUhaaXdGNXFHOU82eDR3M2prcUstMHZQZ0xKSdIB6AFBVV95cUxOb3lzVlp1cU5CN3lTU0F4bm1aVk1SeENCd2JIQzI5aXhaZGJfWUlhWXBpSnQ2NjhGZFlOY2NrbzYwdWdZOVZfVF9vUE5zYVhSaGtPbjd1WVVRNUZBYjlVZkVTZW13ZWZrbld6SjNDN1FtU2M1M2F5REtidFFuTzByV2g0TDBUOFp0Wms1Sm5IV2plTHp4UkpDMjJSMWdaRExXVE5uSmx0VzZXR2VlVDkxTWY0SE1TRVU1QVZLMGV3eUp0andRVm8zOW4zTFdvdWlxd2dldVAtOTVDU0xCVy1TQmQ2SUJtd1Fr?oc=5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1350,17 +1350,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Estudiantes de Cali pajarearon en el Orquideorama durante la Colombia Birdfair - cali.gov.co</t>
+          <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cali.gov.co</t>
+          <t>bogota.alerta.com.co</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQV0NTeVBLODFJYjFsQkJVWHdNRXdLc3h4S1VGdlpQaFhZNVZGYnU5SXp4R3ZfbEFReGFxRW15X2dienNBV1l3SlFMSEZqUW81bXZBLUgwQkdIX2RHcTNpOTZSaWZoekdubkVUSHV3OEp2V05hV1VzaGh0SFRmXzctb2JWbHprWmFuRVI1TTRVcmJCRlc0X3dIMk96dXNEaG5HQjN3S1JnYnh0eVVteEZXQ25reWwtY04xREZoby1YSXg1clgyY194bHpLOHNCVk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOblktRDZRdDlQREx0SWFrYjhnWkoxMmY3MHJJcEJCQU9lbDcwUi1wTFAtVTVySlhnbG9LNGtpd2NHZ05VQ1p0cFpqNkdiU05ENWlISEZUQV9aNExDb3NUUHU1MkduSHJ5LUlsUlhYR0FOMkRvVXloSW1PS1RZZzV3T3VUU1EyQWdGMWhmQTF4a1ZXV0ZlRFRvdDVQcVgyN1ZyakZoeEZuZXpGbG53ZzVfdG5oQ01lajJo0gG8AUFVX3lxTE45S1pNZFFOTUdlajl3elgyYkNGZ01TVGxaRjVPMENmQ2Qwek1GQUhGcVNSSURsN01uM1FYSTR4R2J5U29LSVRWbElNc3hOaUo4V09MdG82SnhHWUFMd1hqTU5DWTFtWmJOZEZqUFRjUmtaZUs4YXQyWjdMZjVyS0J6Q1FNbHBfNENodDRGQ3VZNGVwY2RTS1YzekN4UkwtakV4TlFPYzU5WFA3aGJmd01YOHpfQUNiZ21xSTJp?oc=5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1393,17 +1393,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>¡Batacazo de Juventud en Quito! Eliminó a Universidad Católica y clasificó en la CONMEBOL Libertadores - ESPN Colombia</t>
+          <t>Colegios en Colombia implementarán cátedra obligatoria de protección animal y biodiversidad - Senado.gov.co</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ESPN Colombia</t>
+          <t>Senado.gov.co</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPMmtfdmViQkxLOGhpUFB4eWZyM3ZvM3ROYXBfNEgydVpnbHlQc1A5ZVVXVml2dTk5ZGdtVkhkVmhoOFZOWTRhN0VETnVNZnJNOE1mYTRIdmthTUpTQmxsSVlkS3RZOXk1eU93SGdpc09IZ1dDTVJqQmxpTHZsMVJoRllyTkJaOE9pZW13ZXk0eWoyWTFoX0JZemdiWDBPZXloSTZTNUswTVd4Ni1PUXJwTUpzMExYQU1zV0Z2NzBRNGhfYzczOUpBc3E2RVEtcHdqMjJVLUdzSklSQ0NaRGlrRjBtQUlxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPdkRscDEzLTMzYnhsa2M2N2JfZ3M4ampEZzM5ZVFDRm9aSHBySC1idWljUS1BbW8yVjlUcmF4YW9NNVA2M0dzblQ3aGo3emV5RTFnc1ZkclFHWF9XVDBubmU2Q0lpQmJCTzFiUTNOMnNIdm90NmJua0RwNlNuZXJ1bDIweU95akZQWmFNcmFfT2sxNG1Qb3BDU3hyQmJsT3hqQVlHZnBGb2RNUnJBS201YzV6SFVRR21IX0U3eHNSZEo3MFNuZmVPakgwZGEzVlFYTGJZcEg0dGtSdFpvMnU3TExoMzIxZw?oc=5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1436,17 +1436,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estadounidense inadmitido en Cartagena por delitos sexuales contra menores de edad - Caracol Radio</t>
+          <t>347 mil nuevos estudiantes acceden a educación superior sin endeudarse en Colombia - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxObHNKT2otaW5sc28xYzd6a3JNYWlVUVRNaHpuSFJhVjZVSl9oVzlOSnUybk5BRG9rdkJSUlpuQlZFTEpqU01TS3I2OHZ6YmR6UXREYlZzRGdQYVk3VThUZGVUUVpidGVYLVltNzVlVHkzR0toMTNNMzlobWtXSEU5eVMtQWdleUNzZkowSHZITk5xbVVwOEozT0RNZHZobGhUTEpEd05GWUY3N2NfY0xoQllpTHlCZF8t0gHMAUFVX3lxTE1wR2F2Q19MNDlFY1M4cVFwTDhGMGFJdGZubU9CSmJJZllVYjlyWU1fLUJXYl8wRGgzRjhRNlpDcGk2dWJEbEc2V1VqY3J3d0E1R3l3YllSNkN1d2FGelE2TmN3M3k2aWlwR3A0YzFCTC1YNTV1UzFVX2J3amFwaExsWFpTN2RSZHNfMFp5Z0NENS1tTFQyTHN3Sm9zMGlqWDRITHpyLUdUQlV1bm56UENZRTV1alFFTVZGZERlRE42TzUxdWJpQ25tNVgzbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPN0NyT3lmemVDZlhGaDdEclNPMlNacF9ZOTFVTDI1cG55cnV5UW4yZDRaSDVpOVBBWW0xd0p4SkU1eEJYdEJDemtYWl9BX1EwOWFlSUJ4azhkNXliNE5sengyZ0hGMEtYamxCRmRjYmF5U1NNbzdBeVh6THhVOVFqYk12dmR6WVJSel9GRGxpZFNoN3F5NmhveDh1UFk1Rm1BUWZKckhFVmpnaEd5MXZWTlNzMWhPR0x2S1daTjdrLTVsWFF0RDBtYkd3UzdTTGVPV21QdHZrUjgwOFJTaVdRVXdURFo2UQ?oc=5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1479,17 +1479,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Defensoría del Pueblo exige cese inmediato del reclutamiento forzado de niñas, niños y adolescentes en Colombia - Defensoría del Pueblo de Colombia</t>
+          <t>Estudiantes de Cali pajarearon en el Orquideorama durante la Colombia Birdfair - cali.gov.co</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Defensoría del Pueblo de Colombia</t>
+          <t>cali.gov.co</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOOXBhbnlhY2EtSG5ZSHlTVlJ0U01WUDBnSlJlWFBGajVCZld5TUpmVW9MLWRxZE1IeVI0eGlBVGhnbWVaQV9MWUQtclg1Y2F6eGZqamxsSzFQMWRJV3MtSExwT2lyd24xY1k5RnBHUTJ0eFdmd1VrMXU5ank5dDZkLVJ3MjM3Q01lREZFc081Q3JqTHBITk9MMmJiYjFtS2MzRTg5S05ZOFk0M29hNHRsbV85NHgwMWl3WE1SRVdPeEgwVWp4b21wdElhUUNFZy05eUJLbFBfQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQV0NTeVBLODFJYjFsQkJVWHdNRXdLc3h4S1VGdlpQaFhZNVZGYnU5SXp4R3ZfbEFReGFxRW15X2dienNBV1l3SlFMSEZqUW81bXZBLUgwQkdIX2RHcTNpOTZSaWZoekdubkVUSHV3OEp2V05hV1VzaGh0SFRmXzctb2JWbHprWmFuRVI1TTRVcmJCRlc0X3dIMk96dXNEaG5HQjN3S1JnYnh0eVVteEZXQ25reWwtY04xREZoby1YSXg1clgyY194bHpLOHNCVk0?oc=5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1522,32 +1522,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
+          <t>¡Batacazo de Juventud en Quito! Eliminó a Universidad Católica y clasificó en la CONMEBOL Libertadores - ESPN Colombia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>ESPN Colombia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPMmtfdmViQkxLOGhpUFB4eWZyM3ZvM3ROYXBfNEgydVpnbHlQc1A5ZVVXVml2dTk5ZGdtVkhkVmhoOFZOWTRhN0VETnVNZnJNOE1mYTRIdmthTUpTQmxsSVlkS3RZOXk1eU93SGdpc09IZ1dDTVJqQmxpTHZsMVJoRllyTkJaOE9pZW13ZXk0eWoyWTFoX0JZemdiWDBPZXloSTZTNUswTVd4Ni1PUXJwTUpzMExYQU1zV0Z2NzBRNGhfYzczOUpBc3E2RVEtcHdqMjJVLUdzSklSQ0NaRGlrRjBtQUlxZw?oc=5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1565,17 +1565,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Estas son las reconocidas universidades acreditadas en Colombia de las que se están saliendo los estudiantes: subió la deserción, según el Ministerio de Educación - Infobae</t>
+          <t>Estadounidense inadmitido en Cartagena por delitos sexuales contra menores de edad - Caracol Radio</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNdURDZWdBYVZGbjVuWGh6ZmFMdUY2bjcyc1hLWWxKSnl2dVVSMjRvNGFkZmN5aGgyVlFSUzhUb29lOTg5MWFFY3F0RFM5Y3NtTHZyY0hrcnExYjJjWE9NRkJhbTVwTnZYRElXckIwSDEtM20zeHpkX1pBdGJ0bXhjenY0bUVWSkNNREFKM3FlMDVnT2pqdXdBY0lSSDI3MUJIOFl6Umk3SWdCeU1fYk9TZkVEODJ4dHZoOEdNQVFueHBlVUxNLUNpdUY4YWVWLUpMRER4bkNQek5fWC1Mamk4Ymp1NF9mN3JDWmFIV25hNUpydndyeXNoTUt0QXRxcTBZMHVybk0yNEhfeWdhc3pYadIBqwJBVV95cUxPVTVQb2JnXzBJTkFYNUNOZ1YxeTBJU1Z3bTkxb3Nkak5HdVZ5N0Qwb284LXBwRDZNakVfM0RsR0JOWllycENEYVlLQTV2cW52Ymdpa0NGOHB4d1pVNjFXU0VESEQ3OUR2Mmhrck1uU2NKT2oweEYxT3R3MmNzVzFobVZPUnFGT3paeVA5NzV1cmFQeHYwT2htdmQzc0x0Y1hCUWJGOUdoVHV5elNKa3VWZ0xIaHY2OGJXY3VOR1NuTkFXYzh2QnhWSmxnMFVFRUdxaThzZFBxTHlxNHRyTUpMSHNGRUFCeS1XUXlkMVlUd0hhY3RfWkJXZmN0UzdEYWdyOWR2WGFialRYdTAwUEp2OUkyRFZQcjNWcTgzNndlNEl3RHljMElWTkxvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxObHNKT2otaW5sc28xYzd6a3JNYWlVUVRNaHpuSFJhVjZVSl9oVzlOSnUybk5BRG9rdkJSUlpuQlZFTEpqU01TS3I2OHZ6YmR6UXREYlZzRGdQYVk3VThUZGVUUVpidGVYLVltNzVlVHkzR0toMTNNMzlobWtXSEU5eVMtQWdleUNzZkowSHZITk5xbVVwOEozT0RNZHZobGhUTEpEd05GWUY3N2NfY0xoQllpTHlCZF8t0gHMAUFVX3lxTE1wR2F2Q19MNDlFY1M4cVFwTDhGMGFJdGZubU9CSmJJZllVYjlyWU1fLUJXYl8wRGgzRjhRNlpDcGk2dWJEbEc2V1VqY3J3d0E1R3l3YllSNkN1d2FGelE2TmN3M3k2aWlwR3A0YzFCTC1YNTV1UzFVX2J3amFwaExsWFpTN2RSZHNfMFp5Z0NENS1tTFQyTHN3Sm9zMGlqWDRITHpyLUdUQlV1bm56UENZRTV1alFFTVZGZERlRE42TzUxdWJpQ25tNVgzbw?oc=5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
+          <t>Defensoría del Pueblo exige cese inmediato del reclutamiento forzado de niñas, niños y adolescentes en Colombia - Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1643,14 +1643,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOOXBhbnlhY2EtSG5ZSHlTVlJ0U01WUDBnSlJlWFBGajVCZld5TUpmVW9MLWRxZE1IeVI0eGlBVGhnbWVaQV9MWUQtclg1Y2F6eGZqamxsSzFQMWRJV3MtSExwT2lyd24xY1k5RnBHUTJ0eFdmd1VrMXU5ank5dDZkLVJ3MjM3Q01lREZFc081Q3JqTHBITk9MMmJiYjFtS2MzRTg5S05ZOFk0M29hNHRsbV85NHgwMWl3WE1SRVdPeEgwVWp4b21wdElhUUNFZy05eUJLbFBfQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1660,12 +1656,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
+          <t>Infancias en la guerra: el reclutamiento vuelve a aumentar en Colombia y así es el negocio que hay detrás - CAMBIO Colombia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>CAMBIO Colombia</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1675,12 +1671,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1690,7 +1686,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPWTRzcnA4QnE0QS1RSF92WnBRbVRLM3c5cVFRcVlOQ2VhXzRSa1NLalZpNHRNME0zc2Nid3BzeU1Kb0xIdTFMYlZqQ2llVUotWS12bHY3bEtoZEY1M29GM0JWM1BHYXBVZmY0UEN4czNtRHBIQ09uZmYzYmlLQ2IzcV85QXJNbXpvajZ3YWtnX0FHU3pyTjV5d3RTNUJiSW9wODJJTy1jUHV6M241cFRtM3JIdnVIZjZaRjdtNlUzWmF6ZUM2MFVLaGIzMWc0WjNKZldCcmthdm1OWi1Rb1ZCR1NyQTV2M3gxeUFoTHAweWJIMElBQjdIbEthRlZaR2VUTmJ4Zjl4OW0?oc=5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1703,27 +1699,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Cada dos días es reclutado un menor de edad en Colombia: en 2025, 40 % fueron niñas, dice la Defensoría - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1733,14 +1729,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQcDdFdmtDc2pySXhNZEtwcTVsTk9ZS1JDSEtHSGl0YXk3dEhNQ1V6dlBmYXZBUTBfNnBqaVR5TUFfNVdSemdFdE1hVDhHVV9TSUhaVnR3d0IzanJIbGhjb1B4aS04djYwWnp6YS1NekYtb1YyWWlkekhEZjV5TmhfbWhHNmswWlpqT1JTTl95NWV5eWd3ajhYTEpiaXJIRldnX0pqT3hRVnRMSEJGQW9OTlpFRWkxRGxESV83QkdCVGx3LUJySVR4TEs1TGFNM0pxVEY2OEdUQ2VSbjh1ckVud1BldVhHdXI0c1h1R0ZvX09YVm53d1HSAfsBQVVfeXFMTTRod3NmNUxMSDhrc29tdzR2RFMyVFpfWmh3b01yNVVRR1ZPQnl6Q0ZZQ3VMc2x6UXhpaHAwVzhQWjdPZ294YnRNMXNVQUdrVnp4VFFIZVowRHdEVm4wR0J4NGpzVjlDWkpBMmU4R0p5UUNTREZOWGlGNDBXS3N4RkJvNDlfQTYzd2FDUEVsUE5WdGF6NU4zVzM1MnVlVDQ4SVIxZDRaTmNZd1RpMWxvelpPUm0xZlBkZDhfanp5WVotbjZxTjJydE45NGRCeTk2c1RzcnZGVUhzakxWRjBNZVMwN2tFUlFQMXVTUWF4SHRFdWs1SUE1dmZWMVk?oc=5</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1750,12 +1742,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>En Colombia, cada 48 horas reclutan a un niño, niña o adolescente - Caracol Radio</t>
+          <t>Colombia: El reclutamiento de niños por grupos armados se cuadruplicó en cinco años | Noticias ONU - UN News</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>UN News</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1765,7 +1757,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1780,7 +1772,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPZ3FnbG5UcDl2dElHc2tndjRGZHFfTEtwSzZXTm00TEtwbkprdnJLQ2dmZ2RiTjdLbURnelZWYUZRQ0Z6QXVCMWxla3VTVTM3NDVnTTZ1amJ1dGRvVGdzbW5Fc3E3ZkFlOUhpRlVnbnRSZWowdVNDM1FrSkhQbEc5eVlLQkw3RTlVem9sX1haX2ZfUVM3TndFNXpoUDF5S2_SAbMBQVVfeXFMTTVGUDR6b3R0QVlKZTlDRGh6Um9kbE1qNjA1OUctWTRVRWgyQ1R5QkdEYmUtS3JVbWtGcjRzTXBxSXFGNTdiQkdyMU16VER0OHJKUEViVWRMUExfQ05neHJRbERGcDdQU3VmYnVXbnBiWVJXSFZCdlZqVng3NXg3RWdGWFFiUXZwZGo0dW95bGhxdmpqLUs1X3BJcWVIV0YycHl1dDZLUU5mdDIybWxvZVJKZzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9wSzZjZVpFS1l3NGk2RTY1NlEweXZQcGhjaG9VRm11d0Y4U2xkLVBCYzhoY1o5dmJmQ1g2UE5wR2cxckxPZEowdnpnZkdDT2tyTWRfcmlXYw?oc=5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1793,12 +1785,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Colombia está perdiendo a sus niños en la guerra - EL PAÍS</t>
+          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EL PAÍS</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1808,22 +1800,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPc0p4UDhDd3FDTi1IQUUwUzRzd3dTTHE4cEZuSUp5cTY5dDRUMFRiSHlEUk5naU1ZZUctWEFGODlhLWowNmNuSkE0eUcxZlI1dzJJaU93N1pUaXFid3RjdkNHeHhJbmpQel9CM3hQaUdXUFBVZ2hlQjR0WnZ6emI3TERNZmF3RC1laFpwWjZzSlp4X1QyUmdvTHVZQmYxempldUHSAbYBQVVfeXFMTVBPN1dRZWxmb3pMMFM2TmdwMmlhTVVqTHVmWDdOdDlqWGUtQmRzODdFYmdVSHlYT295Z0tCSmJhOGlFUFJXVG9pd24yMDRUTUJRR25XZkxYeWc3TUpqNF90d28wdDEwTlRGOHNOaTVqbTNtbmxUUkxtSkdTOGtCajljY29LOTJ3TGMtNU5jZXZ1RnBnRTl4UHRLZ1A5MGFiVUFnQ3h2SzFEV2V1S3dKcW5URmQ0anc?oc=5</t>
+          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -1836,12 +1828,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Enfoque Internacional - Niños soldado en Colombia: 'Tiktok es una red muy usual para el reclutamiento' - RFI</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1851,12 +1843,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1866,7 +1858,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPSXVVRUV0NTJIWUpLRjctUXJwTkZ5bnR2clhrc0JQSzVseXZnY0VZSWZoVFRTblJGNFQ4TWxWZ2kxaUxIckxxVTdORGE5ZGdXU0ZsOUVvSWYxWEtobWhNbjB2THg5NGxidFNMcnNFWmNtR251WVZSTHc4ajB5NkZkdFQ4YUpTa0MwVDlHUzV5QWhCUjh3b0xTdnNweFpEb21LT2VUMWJOQWJHT1lQWThRV2Z5a0U2RWtTOHN3R2VMWFNjemMwdUhUdE9RU29NZ2xZSnBzbTluY0pRa1E?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1879,12 +1871,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
+          <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Unicef</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1894,12 +1886,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1909,14 +1901,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOaE5BNl9aTGdKUjlkdW1BaGZOUnNCSTFLYXBRcGdGamVqR2xlazBGZmhjYjBxYUxYa1BfZ2t3NDZpOS14eWRmbFFIWkFfLUMzSVdFQV9oRGNXeUlycl9CMkJjc0R3MVBIcnVtVk5BcERONnJnVFBpckFCQWNKaGlhbFVCUjhyQTlSb24tSElRYWJyQ1FELVdTMlhRQ3BmeDJXMlNKMnRhdm91RjVxMTFOOVpuMkF6SFdQSUs1TFU5LVgxN1JMSWQ3X1piT0lXN3FI?oc=5</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1926,17 +1914,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>En el Día de las Manos Rojas, la Defensoría del Pueblo alza la voz contra el reclutamiento de niñas, niños y adolescentes - Defensoría del Pueblo de Colombia</t>
+          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Defensoría del Pueblo de Colombia</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1946,7 +1934,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1956,7 +1944,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOeEM0U1NNTGdPenhCTGZmZ0l6ZkxXdWppZHJXM1FfaGFqUHFRc2JvUDJqUDBwUVdFenh5QWhlbi1JSV85UmNRVE1mcjdxNkNQWVNnSFZBem9MLTdnX2paeFFZZ1N3TjZPZlZjSUdrOEZWRTM1bXF6SVJFdHNCaW0xQzM1ZE1pdFFENXB2OENSRFNTZkd5OXdsYzZpcDg2X3FWaFRDa0NLT2w2Z1ptUXVXalBQSzN5UXFOMktuVWJtS050YzRReGx4YmFuZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1969,12 +1957,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Infancias en la guerra: el reclutamiento vuelve a aumentar en Colombia y así es el negocio que hay detrás - CAMBIO Colombia</t>
+          <t>En el Día de las Manos Rojas, la Defensoría del Pueblo alza la voz contra el reclutamiento de niñas, niños y adolescentes - Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAMBIO Colombia</t>
+          <t>Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1999,7 +1987,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPWTRzcnA4QnE0QS1RSF92WnBRbVRLM3c5cVFRcVlOQ2VhXzRSa1NLalZpNHRNME0zc2Nid3BzeU1Kb0xIdTFMYlZqQ2llVUotWS12bHY3bEtoZEY1M29GM0JWM1BHYXBVZmY0UEN4czNtRHBIQ09uZmYzYmlLQ2IzcV85QXJNbXpvajZ3YWtnX0FHU3pyTjV5d3RTNUJiSW9wODJJTy1jUHV6M241cFRtM3JIdnVIZjZaRjdtNlUzWmF6ZUM2MFVLaGIzMWc0WjNKZldCcmthdm1OWi1Rb1ZCR1NyQTV2M3gxeUFoTHAweWJIMElBQjdIbEthRlZaR2VUTmJ4Zjl4OW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOeEM0U1NNTGdPenhCTGZmZ0l6ZkxXdWppZHJXM1FfaGFqUHFRc2JvUDJqUDBwUVdFenh5QWhlbi1JSV85UmNRVE1mcjdxNkNQWVNnSFZBem9MLTdnX2paeFFZZ1N3TjZPZlZjSUdrOEZWRTM1bXF6SVJFdHNCaW0xQzM1ZE1pdFFENXB2OENSRFNTZkd5OXdsYzZpcDg2X3FWaFRDa0NLT2w2Z1ptUXVXalBQSzN5UXFOMktuVWJtS050YzRReGx4YmFuZw?oc=5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -2012,27 +2000,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Unicef</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2042,10 +2030,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOaE5BNl9aTGdKUjlkdW1BaGZOUnNCSTFLYXBRcGdGamVqR2xlazBGZmhjYjBxYUxYa1BfZ2t3NDZpOS14eWRmbFFIWkFfLUMzSVdFQV9oRGNXeUlycl9CMkJjc0R3MVBIcnVtVk5BcERONnJnVFBpckFCQWNKaGlhbFVCUjhyQTlSb24tSElRYWJyQ1FELVdTMlhRQ3BmeDJXMlNKMnRhdm91RjVxMTFOOVpuMkF6SFdQSUs1TFU5LVgxN1JMSWQ3X1piT0lXN3FI?oc=5</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2055,7 +2047,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
+          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2085,10 +2077,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2098,12 +2094,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
+          <t>Estas son las reconocidas universidades acreditadas en Colombia de las que se están saliendo los estudiantes: subió la deserción, según el Ministerio de Educación - Infobae</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2118,17 +2114,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNdURDZWdBYVZGbjVuWGh6ZmFMdUY2bjcyc1hLWWxKSnl2dVVSMjRvNGFkZmN5aGgyVlFSUzhUb29lOTg5MWFFY3F0RFM5Y3NtTHZyY0hrcnExYjJjWE9NRkJhbTVwTnZYRElXckIwSDEtM20zeHpkX1pBdGJ0bXhjenY0bUVWSkNNREFKM3FlMDVnT2pqdXdBY0lSSDI3MUJIOFl6Umk3SWdCeU1fYk9TZkVEODJ4dHZoOEdNQVFueHBlVUxNLUNpdUY4YWVWLUpMRER4bkNQek5fWC1Mamk4Ymp1NF9mN3JDWmFIV25hNUpydndyeXNoTUt0QXRxcTBZMHVybk0yNEhfeWdhc3pYadIBqwJBVV95cUxPVTVQb2JnXzBJTkFYNUNOZ1YxeTBJU1Z3bTkxb3Nkak5HdVZ5N0Qwb284LXBwRDZNakVfM0RsR0JOWllycENEYVlLQTV2cW52Ymdpa0NGOHB4d1pVNjFXU0VESEQ3OUR2Mmhrck1uU2NKT2oweEYxT3R3MmNzVzFobVZPUnFGT3paeVA5NzV1cmFQeHYwT2htdmQzc0x0Y1hCUWJGOUdoVHV5elNKa3VWZ0xIaHY2OGJXY3VOR1NuTkFXYzh2QnhWSmxnMFVFRUdxaThzZFBxTHlxNHRyTUpMSHNGRUFCeS1XUXlkMVlUd0hhY3RfWkJXZmN0UzdEYWdyOWR2WGFialRYdTAwUEp2OUkyRFZQcjNWcTgzNndlNEl3RHljMElWTkxvOA?oc=5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2141,12 +2137,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Colombia: El reclutamiento de niños por grupos armados se cuadruplicó en cinco años | Noticias ONU - UN News</t>
+          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UN News</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2156,12 +2152,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2171,10 +2167,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9wSzZjZVpFS1l3NGk2RTY1NlEweXZQcGhjaG9VRm11d0Y4U2xkLVBCYzhoY1o5dmJmQ1g2UE5wR2cxckxPZEowdnpnZkdDT2tyTWRfcmlXYw?oc=5</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cada dos días es reclutado un menor de edad en Colombia: en 2025, 40 % fueron niñas, dice la Defensoría - ELTIEMPO.COM</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQcDdFdmtDc2pySXhNZEtwcTVsTk9ZS1JDSEtHSGl0YXk3dEhNQ1V6dlBmYXZBUTBfNnBqaVR5TUFfNVdSemdFdE1hVDhHVV9TSUhaVnR3d0IzanJIbGhjb1B4aS04djYwWnp6YS1NekYtb1YyWWlkekhEZjV5TmhfbWhHNmswWlpqT1JTTl95NWV5eWd3ajhYTEpiaXJIRldnX0pqT3hRVnRMSEJGQW9OTlpFRWkxRGxESV83QkdCVGx3LUJySVR4TEs1TGFNM0pxVEY2OEdUQ2VSbjh1ckVud1BldVhHdXI0c1h1R0ZvX09YVm53d1HSAfsBQVVfeXFMTTRod3NmNUxMSDhrc29tdzR2RFMyVFpfWmh3b01yNVVRR1ZPQnl6Q0ZZQ3VMc2x6UXhpaHAwVzhQWjdPZ294YnRNMXNVQUdrVnp4VFFIZVowRHdEVm4wR0J4NGpzVjlDWkpBMmU4R0p5UUNTREZOWGlGNDBXS3N4RkJvNDlfQTYzd2FDUEVsUE5WdGF6NU4zVzM1MnVlVDQ4SVIxZDRaTmNZd1RpMWxvelpPUm0xZlBkZDhfanp5WVotbjZxTjJydE45NGRCeTk2c1RzcnZGVUhzakxWRjBNZVMwN2tFUlFQMXVTUWF4SHRFdWs1SUE1dmZWMVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2222,17 +2222,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
+          <t>Colombia está perdiendo a sus niños en la guerra - EL PAÍS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Unicef</t>
+          <t>EL PAÍS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQMWdqbWZUSHduQkx2Y3F4VEJZTkxKS0ZBbExLVHZTc21KbmNoQ2Y3cHNJTWJhWlZ0dWNFalJQcUxIQXNWOTQtc1JCY2VVOTdlaXpESnhGRzdwVmlEODJEOHdDXzY4d0Z6RGpqTHJ3eWR1TVl0MDY0S1Y2VU9GNkVfWUlwX0N2MzBYYmFMX0xWQ0RBeGN4Q1p4LU9UTW9GM3hTb0pwOWRxcWJvNEg0UjVpQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPc0p4UDhDd3FDTi1IQUUwUzRzd3dTTHE4cEZuSUp5cTY5dDRUMFRiSHlEUk5naU1ZZUctWEFGODlhLWowNmNuSkE0eUcxZlI1dzJJaU93N1pUaXFid3RjdkNHeHhJbmpQel9CM3hQaUdXUFBVZ2hlQjR0WnZ6emI3TERNZmF3RC1laFpwWjZzSlp4X1QyUmdvTHVZQmYxempldUHSAbYBQVVfeXFMTVBPN1dRZWxmb3pMMFM2TmdwMmlhTVVqTHVmWDdOdDlqWGUtQmRzODdFYmdVSHlYT295Z0tCSmJhOGlFUFJXVG9pd24yMDRUTUJRR25XZkxYeWc3TUpqNF90d28wdDEwTlRGOHNOaTVqbTNtbmxUUkxtSkdTOGtCajljY29LOTJ3TGMtNU5jZXZ1RnBnRTl4UHRLZ1A5MGFiVUFnQ3h2SzFEV2V1S3dKcW5URmQ0anc?oc=5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2265,17 +2265,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>¿Le apasiona el aviturismo? Programe su visita a Cali para el Colombia Birdfair, una iniciativa de conservación con foco en la infancia y la juventud - ELTIEMPO.COM</t>
+          <t>En Colombia, cada 48 horas reclutan a un niño, niña o adolescente - Caracol Radio</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPdHFDVmxhT0NQQkxpakdYUjREMjVIcllPbHZuTFh6OHVDN0hGWDE1YVIwbmFoNW5ESEFELVluZHJSLUg2MVJ1cWpOaEtvcXMyY0Jpb2tVcVYteFBCSXZhQWh4c1dtVjFFVS14d0Z1OWtSY1Ewd0JqNGZlVjRxeGwweF9WLWg5a20tZF94eXBuaGxTVHdxc1Rfa0c3TUxKTXFxMjlVdXY5N3hwUzJGUURfczY5Ulc0bTQ2NFJWZWJ4SXhfZmZhYUl5ekJhRDFObDFNdVZMYVBURVM2ZXNPVEVhMER0UUJYTTRwTUFWMlM0cFN4alNEYm9MbUQ4ZVhoRlNYSUpzSjI3bjdobmNGajdiVUNqMkJjbmxfTFo1XzZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPZ3FnbG5UcDl2dElHc2tndjRGZHFfTEtwSzZXTm00TEtwbkprdnJLQ2dmZ2RiTjdLbURnelZWYUZRQ0Z6QXVCMWxla3VTVTM3NDVnTTZ1amJ1dGRvVGdzbW5Fc3E3ZkFlOUhpRlVnbnRSZWowdVNDM1FrSkhQbEc5eVlLQkw3RTlVem9sX1haX2ZfUVM3TndFNXpoUDF5S2_SAbMBQVVfeXFMTTVGUDR6b3R0QVlKZTlDRGh6Um9kbE1qNjA1OUctWTRVRWgyQ1R5QkdEYmUtS3JVbWtGcjRzTXBxSXFGNTdiQkdyMU16VER0OHJKUEViVWRMUExfQ05neHJRbERGcDdQU3VmYnVXbnBiWVJXSFZCdlZqVng3NXg3RWdGWFFiUXZwZGo0dW95bGhxdmpqLUs1X3BJcWVIV0YycHl1dDZLUU5mdDIybWxvZVJKZzQ?oc=5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2308,17 +2308,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tres jóvenes indígenas ingresan a la Universidad Nacional - Radio Nacional de Colombia</t>
+          <t>Enfoque Internacional - Niños soldado en Colombia: 'Tiktok es una red muy usual para el reclutamiento' - RFI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Radio Nacional de Colombia</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNbTQxeVdtTWhaUkVLeXYtdDJuMVVZSnpKWS1RWWRXakNLbDY2ZngwZTAtZE5rOWpXd1g5WmFHajN3enpCRnVxcDdoZnBBbzI0RG5fcWVTVWFnUlAwcGhDdHQ0ZEZ3emN5MFlVMXVYcTBaWHZzNldXd0JYOEROZ1lPYWZBeWpyRE50ZFpHTlZ6RHh3d1lEdWQ2NXJMek1HaTlRY3ZIWHZGb03SAawBQVVfeXFMTkZ2NUNGdldMTWJkb2d4MEI2SDNxSjlXbGlWZ2tucVI4OU0yWWhVWTNYMjBWT3hjZWdNNFFvdDBrLThoYU5wMUhOOXoyMTMzRm15R3NMbmRoSi1PMEZDRF9IcmRpTlhuVDZVbDZtS0ZJX0dQcVhRSFlIdk80MkZKd0RyNFNRWFdBT1JYdkxiVGVORnk5c2F4aUs4VWNiR055NW9rdEFyaVIxNHZTRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPSXVVRUV0NTJIWUpLRjctUXJwTkZ5bnR2clhrc0JQSzVseXZnY0VZSWZoVFRTblJGNFQ4TWxWZ2kxaUxIckxxVTdORGE5ZGdXU0ZsOUVvSWYxWEtobWhNbjB2THg5NGxidFNMcnNFWmNtR251WVZSTHc4ajB5NkZkdFQ4YUpTa0MwVDlHUzV5QWhCUjh3b0xTdnNweFpEb21LT2VUMWJOQWJHT1lQWThRV2Z5a0U2RWtTOHN3R2VMWFNjemMwdUhUdE9RU29NZ2xZSnBzbTluY0pRa1E?oc=5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Adolescentes colombianos pasan en promedio 2,2 horas al día socializando en internet: Universidad de los Andes - UNIMINUTO Radio</t>
+          <t>¿Le apasiona el aviturismo? Programe su visita a Cali para el Colombia Birdfair, una iniciativa de conservación con foco en la infancia y la juventud - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNIMINUTO Radio</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOeEVEUlI0ZFJoQ1BYTGdrMWRkekxsZldhWUxQc3dlREt1LVo3djhaU0trUnZlMVlfcl9FdGJDbkRVWndzd3ZnbjJnTURaZnplZ3dQSDZFckN2cG9EWjRWa1ZON1JFZ0Z1WlY4MmZ2b2FsdEFEWjZqZmpnSXdSZVg1Wk9xZEZSb1BCOUVuVDI5QWFsM3dTQUh6VjZDUnBfQlRJNG5ZdHVQUF9fZUpUYlJVTG0tYjJucGdvMFRIZDNXSlRJNGZIWHlaTk13dllWWFhFRWZXaHdVbVZQVmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPdHFDVmxhT0NQQkxpakdYUjREMjVIcllPbHZuTFh6OHVDN0hGWDE1YVIwbmFoNW5ESEFELVluZHJSLUg2MVJ1cWpOaEtvcXMyY0Jpb2tVcVYteFBCSXZhQWh4c1dtVjFFVS14d0Z1OWtSY1Ewd0JqNGZlVjRxeGwweF9WLWg5a20tZF94eXBuaGxTVHdxc1Rfa0c3TUxKTXFxMjlVdXY5N3hwUzJGUURfczY5Ulc0bTQ2NFJWZWJ4SXhfZmZhYUl5ekJhRDFObDFNdVZMYVBURVM2ZXNPVEVhMER0UUJYTTRwTUFWMlM0cFN4alNEYm9MbUQ4ZVhoRlNYSUpzSjI3bjdobmNGajdiVUNqMkJjbmxfTFo1XzZn?oc=5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2394,17 +2394,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>¿Quién es Jacques Leveugle? El francés acusado de abusar de 89 niños en 9 países, incluido Colombia - Semana.com</t>
+          <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semana.com</t>
+          <t>Unicef</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNZDJsMDBhWUFjNkxEVUhYU0U5WHFQVXdSbEJLaFVuTGtDSk9HZkRrSGQxVUZ3Z0xOLVVTU3hQUlNYUjFYWFlJb01aTmtHVkFMV1dlQWJEeEVkeEtSOElWSmVKMjBiTklHZ3JYQVhKbGNPTThMcWhMS3ZOSHdUWi1aZkdhekFfVVBFSHdlMFB0U1VjbDd6SVptN1RUc2R2LV95VmE4ZVNpaXlsd0tlb1NVQnN2dnRYdHN5eUQ0aHRzcDg3WmxVVGRUNmkxY3V2Y0NnVU14Tm9VajZhUdIB3wFBVV95cUxOSmJsYkNUNDRZdEItbXNLcWY1SVVZQmJRMjYyOFkzNzNieHlBc2xGSmVPX0pGWkUxbmt0aDJhNVJOWVJGbTJCSkJqa2FNTmJGRG1FWExMWjZTNEFPVDhtQVkwQzZTU3lIYnZZendkX2hLdFlWLVVDN3JGOVBDdVlzeERNRC1OazFtUEUyR0MtVTlUOGRTTUhXRTFVNlo0VXBJZUUtY0ZQNW04cVBVcUxLdmQzTEdmc1hmWW9Hc1Z0VnFRME5kQ3JQSlVERjN5bFRCbzhRSTZLNUpHemoxMDlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQMWdqbWZUSHduQkx2Y3F4VEJZTkxKS0ZBbExLVHZTc21KbmNoQ2Y3cHNJTWJhWlZ0dWNFalJQcUxIQXNWOTQtc1JCY2VVOTdlaXpESnhGRzdwVmlEODJEOHdDXzY4d0Z6RGpqTHJ3eWR1TVl0MDY0S1Y2VU9GNkVfWUlwX0N2MzBYYmFMX0xWQ0RBeGN4Q1p4LU9UTW9GM3hTb0pwOWRxcWJvNEg0UjVpQw?oc=5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2437,17 +2437,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>¿Le apasiona el aviturismo? Programe su visita a Cali para el Colombia Birdfair, una iniciativa de conservación con foco en la infancia y la juventud - ELTIEMPO.COM</t>
+          <t>Adolescentes colombianos pasan en promedio 2,2 horas al día socializando en internet: Universidad de los Andes - UNIMINUTO Radio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>UNIMINUTO Radio</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPdHFDVmxhT0NQQkxpakdYUjREMjVIcllPbHZuTFh6OHVDN0hGWDE1YVIwbmFoNW5ESEFELVluZHJSLUg2MVJ1cWpOaEtvcXMyY0Jpb2tVcVYteFBCSXZhQWh4c1dtVjFFVS14d0Z1OWtSY1Ewd0JqNGZlVjRxeGwweF9WLWg5a20tZF94eXBuaGxTVHdxc1Rfa0c3TUxKTXFxMjlVdXY5N3hwUzJGUURfczY5Ulc0bTQ2NFJWZWJ4SXhfZmZhYUl5ekJhRDFObDFNdVZMYVBURVM2ZXNPVEVhMER0UUJYTTRwTUFWMlM0cFN4alNEYm9MbUQ4ZVhoRlNYSUpzSjI3bjdobmNGajdiVUNqMkJjbmxfTFo1XzZn0gGjAkFVX3lxTE9jQ2hLRkFKNnVWckhPbjNnOHdCN1JIMTVVLUo1a2VQNmxpWWxUbDY5TV96eWZQYWxpcEJ4cUEySFZCS2NLaFFVWGFOT0lrd3ZiYzN0Y1JJcVI3VFFCdnRZcksxR2ljell6anVfOHY1ejRrcE1rdUcwLVRCenVrVVJrazRwNzJFc3ZWV0JFVWNfVm9lRjAyV1plVkIxV3BpMmdURG1iemZhX1hnNkp0UHNDZ3VZOHRLVXJ6UEFKOXVfVTVlR1prMGtOZ2RYN0E3czREcDZxYkwwb2hQZExQVDNVT01RTk9QemhnS1NiaU5ld3FsalNFbWVrUWFxOE11aW9iWWx2ajBPblQ5UDAzZG1DVloxWS1RN0lxOWkxbVg1SEN3NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOeEVEUlI0ZFJoQ1BYTGdrMWRkekxsZldhWUxQc3dlREt1LVo3djhaU0trUnZlMVlfcl9FdGJDbkRVWndzd3ZnbjJnTURaZnplZ3dQSDZFckN2cG9EWjRWa1ZON1JFZ0Z1WlY4MmZ2b2FsdEFEWjZqZmpnSXdSZVg1Wk9xZEZSb1BCOUVuVDI5QWFsM3dTQUh6VjZDUnBfQlRJNG5ZdHVQUF9fZUpUYlJVTG0tYjJucGdvMFRIZDNXSlRJNGZIWHlaTk13dllWWFhFRWZXaHdVbVZQVmM?oc=5</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2480,17 +2480,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Exclusivo: 13,8 millones de niños, niñas y adolescentes en Colombia crecen entre conflicto, migración y crisis climática, según nuevo informe - ELTIEMPO.COM</t>
+          <t>Tres jóvenes indígenas ingresan a la Universidad Nacional - Radio Nacional de Colombia</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Radio Nacional de Colombia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNOTlaVExIaU54TkxnMFIzY3lBUjdvN0dTOVVMc3lvVENfU2VhY2tGTlNFYWdOcnJUdjdYdk9rdWRSOFRueVh4TW92NnVZSkg2TmI1WENFZFVXLTVVaEFDcTdpNWdxdmtiU3dpQ1RhTTg0N0NEakhucUd4bFh4aHoyRGlIaXRUS2d0YmdHZlpRNU95RndEUmFBRVZkTGpBMllkTWZQVVRORzVWb3Y1UHhELUZhVV9JWk5MbnI0eExucHVCdVV5dHJhcl9vVXJRdGM5WVRnR19xbXZXajlJbS1Ja2ZhdFlCOVM3cWJ0N0NBNTVtd9IB9wFBVV95cUxOM0RDc3lsTDZIdlNxaVZxcUxvN0gxRF8xQzc0czJfRUJGZmpmVlFyb2pMVC1fZ0ZNazJMZjdJd1laTDFEcDJubnAyQ05OOXdXSmRrU09vRUZpdFNaT21aOWtoajFTSDlnWkpKVWo4VVVZU1NTLVlvNzRTQXdFZXl1ekNqSmtsU0twWmx1YmQwSV83VkhqZFQ3TW9ILUxBb1Z4SlZWSUhYQWtDTlhJRHhZSmJRaTNzWXJyMDBXZGQydUx0anFQMGZWMmxGSE84ZzVkVmNENHQtdDJfLXlDV09kb0VuOVYzSVdJenVBa1p2Nzkydkw5eEtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNbTQxeVdtTWhaUkVLeXYtdDJuMVVZSnpKWS1RWWRXakNLbDY2ZngwZTAtZE5rOWpXd1g5WmFHajN3enpCRnVxcDdoZnBBbzI0RG5fcWVTVWFnUlAwcGhDdHQ0ZEZ3emN5MFlVMXVYcTBaWHZzNldXd0JYOEROZ1lPYWZBeWpyRE50ZFpHTlZ6RHh3d1lEdWQ2NXJMek1HaTlRY3ZIWHZGb03SAawBQVVfeXFMTkZ2NUNGdldMTWJkb2d4MEI2SDNxSjlXbGlWZ2tucVI4OU0yWWhVWTNYMjBWT3hjZWdNNFFvdDBrLThoYU5wMUhOOXoyMTMzRm15R3NMbmRoSi1PMEZDRF9IcmRpTlhuVDZVbDZtS0ZJX0dQcVhRSFlIdk80MkZKd0RyNFNRWFdBT1JYdkxiVGVORnk5c2F4aUs4VWNiR055NW9rdEFyaVIxNHZTRQ?oc=5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2523,12 +2523,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Contraloría alerta que más de 1 millón 200 mil niños no tienen acceso al PAE en Colombia - ELTIEMPO.COM</t>
+          <t>¿Le apasiona el aviturismo? Programe su visita a Cali para el Colombia Birdfair, una iniciativa de conservación con foco en la infancia y la juventud - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQTzdCMmlSTHhPT3dIM29QaWkybFplRjN1T1BuM05SU2VEdUZuY0dPdk5seUhSSmpyQ0VHbnlIV05NaFFoTFMzSUx2QlBZLXVlaC1pSi1nd25QNjh0azk2MWpNMUV0bjhsSzktZmF1MnVsZTRFZnB2YmZ6azc5cU9oVGE4WlU3WXZwZnRwcW85aF9iVEl0dWplT3pCTkczS013Y0IwZHkxTFpRd1RMc1JySTdxX0ZoSjh0TS0tNldtVUxTUXhRc3l2Rm55RWN3VHU0ZkxQSE1XODEyVEhs0gHiAUFVX3lxTFB4RmYtelFvZ3FuNlpTaXhpN1BPcm94ODh3c3U0c0kxUmVRcVlMOFU2MWpUVmtzdUt2VGtDQzB4QmR4Y1h2b2hxc2lNNld1SXhOM2ZqY1piQnJsT19uc3ZzZnVuUEVzRGoxdGQwTkNvdFVSdUljR1BSNnJla1FBSHhNNnZTUTVzX1AyekVranZCWHR0WDZpTnBYNVlxRl9LU0ExazZrdGhFa1hQcEpXSGcxTEJIVmU3SHROODgzaURZQWh5QUxwSjRUcEhLbTlwNlBCVFpVNk12bjc4am4xQnp0dnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPdHFDVmxhT0NQQkxpakdYUjREMjVIcllPbHZuTFh6OHVDN0hGWDE1YVIwbmFoNW5ESEFELVluZHJSLUg2MVJ1cWpOaEtvcXMyY0Jpb2tVcVYteFBCSXZhQWh4c1dtVjFFVS14d0Z1OWtSY1Ewd0JqNGZlVjRxeGwweF9WLWg5a20tZF94eXBuaGxTVHdxc1Rfa0c3TUxKTXFxMjlVdXY5N3hwUzJGUURfczY5Ulc0bTQ2NFJWZWJ4SXhfZmZhYUl5ekJhRDFObDFNdVZMYVBURVM2ZXNPVEVhMER0UUJYTTRwTUFWMlM0cFN4alNEYm9MbUQ4ZVhoRlNYSUpzSjI3bjdobmNGajdiVUNqMkJjbmxfTFo1XzZn0gGjAkFVX3lxTE9jQ2hLRkFKNnVWckhPbjNnOHdCN1JIMTVVLUo1a2VQNmxpWWxUbDY5TV96eWZQYWxpcEJ4cUEySFZCS2NLaFFVWGFOT0lrd3ZiYzN0Y1JJcVI3VFFCdnRZcksxR2ljell6anVfOHY1ejRrcE1rdUcwLVRCenVrVVJrazRwNzJFc3ZWV0JFVWNfVm9lRjAyV1plVkIxV3BpMmdURG1iemZhX1hnNkp0UHNDZ3VZOHRLVXJ6UEFKOXVfVTVlR1prMGtOZ2RYN0E3czREcDZxYkwwb2hQZExQVDNVT01RTk9QemhnS1NiaU5ld3FsalNFbWVrUWFxOE11aW9iWWx2ajBPblQ5UDAzZG1DVloxWS1RN0lxOWkxbVg1SEN3NA?oc=5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2566,17 +2566,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>El uso de redes sociales por grupos armados para reclutar jóvenes crece en Colombia, México y Ucrania - WIRED</t>
+          <t>Exclusivo: 13,8 millones de niños, niñas y adolescentes en Colombia crecen entre conflicto, migración y crisis climática, según nuevo informe - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WIRED</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNc0lDNjdNaXRmRDJJcFNCazB3OGpPLTdFS0JjV3FyS1F4dFFuV3RXMTA2S25UOTh0NWt0VE1IV2g2V1R4TDVPWGlmMXB3ZHVTWkhzb1loOWpCd0xUZnFlSFZFeWd5ZmxnQ1pKWFVRdTAwOTlCWWZINjBPMVdrYWxsejBIWl9XVi1UVHp1LXNaRVRMdms4QVZpWGxOSWdfLVBTeWQ5YUR1RmwzRlo0enJOT1ZmN3R1Y3RaX3B1cjlmUGZYckdPTndtQ3hUcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNOTlaVExIaU54TkxnMFIzY3lBUjdvN0dTOVVMc3lvVENfU2VhY2tGTlNFYWdOcnJUdjdYdk9rdWRSOFRueVh4TW92NnVZSkg2TmI1WENFZFVXLTVVaEFDcTdpNWdxdmtiU3dpQ1RhTTg0N0NEakhucUd4bFh4aHoyRGlIaXRUS2d0YmdHZlpRNU95RndEUmFBRVZkTGpBMllkTWZQVVRORzVWb3Y1UHhELUZhVV9JWk5MbnI0eExucHVCdVV5dHJhcl9vVXJRdGM5WVRnR19xbXZXajlJbS1Ja2ZhdFlCOVM3cWJ0N0NBNTVtd9IB9wFBVV95cUxOM0RDc3lsTDZIdlNxaVZxcUxvN0gxRF8xQzc0czJfRUJGZmpmVlFyb2pMVC1fZ0ZNazJMZjdJd1laTDFEcDJubnAyQ05OOXdXSmRrU09vRUZpdFNaT21aOWtoajFTSDlnWkpKVWo4VVVZU1NTLVlvNzRTQXdFZXl1ekNqSmtsU0twWmx1YmQwSV83VkhqZFQ3TW9ILUxBb1Z4SlZWSUhYQWtDTlhJRHhZSmJRaTNzWXJyMDBXZGQydUx0anFQMGZWMmxGSE84ZzVkVmNENHQtdDJfLXlDV09kb0VuOVYzSVdJenVBa1p2Nzkydkw5eEtF?oc=5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2609,17 +2609,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Prosperidad Social: los pagos de Colombia Mayor, Renta Ciudadana y Jóvenes en paz de febrero - ELTIEMPO.COM</t>
+          <t>¿Quién es Jacques Leveugle? El francés acusado de abusar de 89 niños en 9 países, incluido Colombia - Semana.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Semana.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNcFpBUFJrVWpUNDlkMW5BMlhDMjhCd1NZZUNockVmUHF2bl9JR3JYcGJLUmlKdldIZnRyQ1RjLVRqWUNSX25PWGo1ZVZpWmhXa3JkNC1ZVVJ6RzVSdi14NDFJbk9sejBoQ3V3SWpsTHN6N0xPRTFjYndYX2M5LUN4dmZKNDJueTJjT2pBT1hhY0ZfTkt2Sy1COVJmU0JzQkFvUGZrZnJwMGhWUGRNTl9jODR5bEtvRHVCYVBHdFdaWURfX1I4UVE2YXNodE9tWUZUYUd5djZjZk50MXpZcHA5YXlXbEV4VjTSAewBQVVfeXFMT3BxZFg1YTJmSmNTbkhTdHZmeVR5VE5XT3NpSk5sajdMRUlrWnpaa2ctZXMzcHI2ZFRaSnB0WnBqa25VOVlWVTExems4bDVmU21xVmdEcEV5RkZvZzQyVU1JWkZodm9TQmtwRUZOTWtjbTRzSXhHWDBIdDJ0blpPQ1dpbGFFdVhyOHpjUkYxSDQyXy1weDdYcjJMVTlKeDhNWVAtcTBXRUQxS3p1M25uZnVhMlc5YUt4VmUyZ3hKODd2ZUxhOGM3TXBCSXB3ZmRKN3FCLXVxX01oNkhCVGc5WV9IRFR2MUE2SzZick8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNZDJsMDBhWUFjNkxEVUhYU0U5WHFQVXdSbEJLaFVuTGtDSk9HZkRrSGQxVUZ3Z0xOLVVTU3hQUlNYUjFYWFlJb01aTmtHVkFMV1dlQWJEeEVkeEtSOElWSmVKMjBiTklHZ3JYQVhKbGNPTThMcWhMS3ZOSHdUWi1aZkdhekFfVVBFSHdlMFB0U1VjbDd6SVptN1RUc2R2LV95VmE4ZVNpaXlsd0tlb1NVQnN2dnRYdHN5eUQ0aHRzcDg3WmxVVGRUNmkxY3V2Y0NnVU14Tm9VajZhUdIB3wFBVV95cUxOSmJsYkNUNDRZdEItbXNLcWY1SVVZQmJRMjYyOFkzNzNieHlBc2xGSmVPX0pGWkUxbmt0aDJhNVJOWVJGbTJCSkJqa2FNTmJGRG1FWExMWjZTNEFPVDhtQVkwQzZTU3lIYnZZendkX2hLdFlWLVVDN3JGOVBDdVlzeERNRC1OazFtUEUyR0MtVTlUOGRTTUhXRTFVNlo0VXBJZUUtY0ZQNW04cVBVcUxLdmQzTEdmc1hmWW9Hc1Z0VnFRME5kQ3JQSlVERjN5bFRCbzhRSTZLNUpHemoxMDlB?oc=5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2652,17 +2652,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sin querer queriendo, el consejero local de Juventud de la localidad de Engativá, Andrés Felipe Acosta Vásquez, terminó haciéndose famoso por su forma de hablar similar a la del jefe de Estado, algo que hacen con naturalidad comediante reconocidos com - facebook.com</t>
+          <t>Contraloría alerta que más de 1 millón 200 mil niños no tienen acceso al PAE en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNT2xGLXFXTDE2NXZsYWF0SmMxRkUyQ21GRUVsUGM5NC1DUnJOUDBJRUJIM0VkUmQ3a1YzRUV2b01TSUExalEtYUdnbHlrcWc2Ni1BZFZaWnpKVk91M2RYb01EYkNCejdpTUM1VHVweS1ia29ENy1nc2s4V2xTUG1XUGgzLVp3dUVaZlhUa2FDM3NEd2l2T3R2MGdYZi1BMjN1cXRuNHhYaHZSOTBEeDkzd1ZXa0VHd0hhLUxiaXROVzdic1N3XzhVQXFyZGtOZ1ZVMnVMa0dhT1dKbmx3WTNvdGhWUTBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQTzdCMmlSTHhPT3dIM29QaWkybFplRjN1T1BuM05SU2VEdUZuY0dPdk5seUhSSmpyQ0VHbnlIV05NaFFoTFMzSUx2QlBZLXVlaC1pSi1nd25QNjh0azk2MWpNMUV0bjhsSzktZmF1MnVsZTRFZnB2YmZ6azc5cU9oVGE4WlU3WXZwZnRwcW85aF9iVEl0dWplT3pCTkczS013Y0IwZHkxTFpRd1RMc1JySTdxX0ZoSjh0TS0tNldtVUxTUXhRc3l2Rm55RWN3VHU0ZkxQSE1XODEyVEhs0gHiAUFVX3lxTFB4RmYtelFvZ3FuNlpTaXhpN1BPcm94ODh3c3U0c0kxUmVRcVlMOFU2MWpUVmtzdUt2VGtDQzB4QmR4Y1h2b2hxc2lNNld1SXhOM2ZqY1piQnJsT19uc3ZzZnVuUEVzRGoxdGQwTkNvdFVSdUljR1BSNnJla1FBSHhNNnZTUTVzX1AyekVranZCWHR0WDZpTnBYNVlxRl9LU0ExazZrdGhFa1hQcEpXSGcxTEJIVmU3SHROODgzaURZQWh5QUxwSjRUcEhLbTlwNlBCVFpVNk12bjc4am4xQnp0dnc?oc=5</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2695,17 +2695,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jóvenes colombianos dan sus primeros pasos para convertirse en pilotos militares - Fuerza Aeroespacial Colombiana</t>
+          <t>El uso de redes sociales por grupos armados para reclutar jóvenes crece en Colombia, México y Ucrania - WIRED</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fuerza Aeroespacial Colombiana</t>
+          <t>WIRED</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPV2ZoS2txM1NrTDg2Zl9yRGJhaGk5QjJjZnlRZmJWRjNQTi1ETWo1bURhb3hyaWV1YzBDSzRoTVJWb0NOcGdVeTZ2M3ZkMC1OZThFMEM5RXMwaXdZOXdXVkpZS1FfU1Q5dXdxSGZKZ3hrbjJ1NFNwZWQ4NWJINldQQTM1Vll0cU05Z3dhSC15dDVFXzZVOXc1dDBpUFhySkJVYjdTUTZBWUdBWmNDdlB3a1VxU2pqdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNc0lDNjdNaXRmRDJJcFNCazB3OGpPLTdFS0JjV3FyS1F4dFFuV3RXMTA2S25UOTh0NWt0VE1IV2g2V1R4TDVPWGlmMXB3ZHVTWkhzb1loOWpCd0xUZnFlSFZFeWd5ZmxnQ1pKWFVRdTAwOTlCWWZINjBPMVdrYWxsejBIWl9XVi1UVHp1LXNaRVRMdms4QVZpWGxOSWdfLVBTeWQ5YUR1RmwzRlo0enJOT1ZmN3R1Y3RaX3B1cjlmUGZYckdPTndtQ3hUcw?oc=5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2738,17 +2738,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Viajes con menores de edad en Colombia cambian este 2026: esto dice la nueva ley - La FM</t>
+          <t>Sin querer queriendo, el consejero local de Juventud de la localidad de Engativá, Andrés Felipe Acosta Vásquez, terminó haciéndose famoso por su forma de hablar similar a la del jefe de Estado, algo que hacen con naturalidad comediante reconocidos com - facebook.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>La FM</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNy16bzc2dktiRGkyeXN3blBBRzZ3WjNxek9QX3hqV0o0dlZfNUtvd3ZMR1pvcEJXSndIU0lyMDZCb0hQa3R6WXVBTnZmOVNTU0xqN2Z5OF9UWUVuRDRzOUNrajNwbXkzUGJnRU44LTJYdEdQSEJJcDZOLUJqSG5DaG5MdVhyejh30gGIAUFVX3lxTE9CMGNNcjFpQzFVSzNhN3pzSF81anVxX2dfX0tFODRCVGFEN1ViUkV6OU9ldU1sbm0xd2xkLVdKZUtkX1ZZNDF6Ti1sNWNfTVlVeHdxQ2dET0hIMm1YQ1d5eG4xMVdEdmUyVll5SlRUYkVZZlU3X012aFRSRVEtdFg5UVdDMUI5elg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNT2xGLXFXTDE2NXZsYWF0SmMxRkUyQ21GRUVsUGM5NC1DUnJOUDBJRUJIM0VkUmQ3a1YzRUV2b01TSUExalEtYUdnbHlrcWc2Ni1BZFZaWnpKVk91M2RYb01EYkNCejdpTUM1VHVweS1ia29ENy1nc2s4V2xTUG1XUGgzLVp3dUVaZlhUa2FDM3NEd2l2T3R2MGdYZi1BMjN1cXRuNHhYaHZSOTBEeDkzd1ZXa0VHd0hhLUxiaXROVzdic1N3XzhVQXFyZGtOZ1ZVMnVMa0dhT1dKbmx3WTNvdGhWUTBoUQ?oc=5</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2781,17 +2781,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Más de 800 colegios privados han cerrado en Colombia desde 2020 y el panorama parece empeorar - bloomberglinea.com</t>
+          <t>Prosperidad Social: los pagos de Colombia Mayor, Renta Ciudadana y Jóvenes en paz de febrero - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bloomberglinea.com</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQMUlhLWE5ZzVjSzRUNEF0Z0kyTFNsb0d4dnh0aEpXUXNVbmxHYTRhZFJPX0llWXRZdFpkbnNGeEFmZWdzY3dEUWJLbDdDb0wxcGNyMFJKQ3ZJR0xwN28tMGhrVDhRV1dGUlpSa0g3LUlEQlcyajd6MEtqV2oxakJkYVFSdmxEUmI1NlJVcXhFQ01RRXRYdGU5RHpRbnp0STVsWERmZkhpVnVPc3NUU0hYZzZBS2ZUUkRyQldrRXlMVDVSQ05Jc3hLQ0pEWWVrTkNRR09FRDVPTFhMQnA1TTRCRWpB0gH2AUFVX3lxTE5NZGlCQjUyZDktS2RmeEdqbzkydjZfckZjNlJBa00xa3E2bTREbXB6eE1zVnZFdGtFOEdLdC1ZTFlSSDl3cDBlZTM1VDNSQ2o2UThxeFhVU3J1UTF5Yzk5OWQzSkFsQUl4NmN6LVRVbm96VWRVd0IxTXhIdGIyVDhXczZSUTJ6YnBXYnB1LW1NMlBybnQteGFOeC1uX2JOUkRGU0JCY1VRVGltcTFiZWxCa052a3hFRnU3WVptR1V3d2oyMWRVMmpHT1d3Wjh1eThwanIzc0NWVjFqNlF1TUdlN2psdkdhSnIyZWxtUC0xR2pVdGRtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNcFpBUFJrVWpUNDlkMW5BMlhDMjhCd1NZZUNockVmUHF2bl9JR3JYcGJLUmlKdldIZnRyQ1RjLVRqWUNSX25PWGo1ZVZpWmhXa3JkNC1ZVVJ6RzVSdi14NDFJbk9sejBoQ3V3SWpsTHN6N0xPRTFjYndYX2M5LUN4dmZKNDJueTJjT2pBT1hhY0ZfTkt2Sy1COVJmU0JzQkFvUGZrZnJwMGhWUGRNTl9jODR5bEtvRHVCYVBHdFdaWURfX1I4UVE2YXNodE9tWUZUYUd5djZjZk50MXpZcHA5YXlXbEV4VjTSAewBQVVfeXFMT3BxZFg1YTJmSmNTbkhTdHZmeVR5VE5XT3NpSk5sajdMRUlrWnpaa2ctZXMzcHI2ZFRaSnB0WnBqa25VOVlWVTExems4bDVmU21xVmdEcEV5RkZvZzQyVU1JWkZodm9TQmtwRUZOTWtjbTRzSXhHWDBIdDJ0blpPQ1dpbGFFdVhyOHpjUkYxSDQyXy1weDdYcjJMVTlKeDhNWVAtcTBXRUQxS3p1M25uZnVhMlc5YUt4VmUyZ3hKODd2ZUxhOGM3TXBCSXB3ZmRKN3FCLXVxX01oNkhCVGc5WV9IRFR2MUE2SzZick8?oc=5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2824,17 +2824,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos - integracionsocial.gov.co</t>
+          <t>Jóvenes colombianos dan sus primeros pasos para convertirse en pilotos militares - Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>integracionsocial.gov.co</t>
+          <t>Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxNMzJhelJqNkVVMlpLUDNKMjlBazI0c3ZIemxfRE1oRFdFWjh4WWRxbTJScTV4QWF1ZG1ZOHFvWmJ2Si1iUzlOQ3NPUVVaTmV0ZVZSOWxSanhWd1hkSHFlUmYyUnZQaHJFdUZNNDFqZm9GQ1IyeVhfUENReEg3RHNMQlZYd0Q2emw3dXh4ODdIUVozU09lVks4VU90ODhNTjNLVmxNbGlMV0k4WXFNdURHaVpCSjlPUTJOdllnNVJ0VVVPOVN4OEo4djBkamJvSjE1Ny0yMFVNdGRxYU1zTlJEaU1PTTMxbDZkVGxxNWlscnBicEwxN20wX2VmdzRqdE43bUUxdkZuSVZRMG5GZmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPV2ZoS2txM1NrTDg2Zl9yRGJhaGk5QjJjZnlRZmJWRjNQTi1ETWo1bURhb3hyaWV1YzBDSzRoTVJWb0NOcGdVeTZ2M3ZkMC1OZThFMEM5RXMwaXdZOXdXVkpZS1FfU1Q5dXdxSGZKZ3hrbjJ1NFNwZWQ4NWJINldQQTM1Vll0cU05Z3dhSC15dDVFXzZVOXc1dDBpUFhySkJVYjdTUTZBWUdBWmNDdlB3a1VxU2pqdw?oc=5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2867,17 +2867,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Solo 13 de cada 100 estudiantes en Colombia alcanza los aprendizajes básicos y la mitad no llega a grado once: Advierten consecuencias 'catastróficas' - ELTIEMPO.COM</t>
+          <t>Viajes con menores de edad en Colombia cambian este 2026: esto dice la nueva ley - La FM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>La FM</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNNE9BSllXSG53VWU5clFlTjBXanVlUEswSmdVVkxCeDJCS0NtNzQ5cTJPckc3ZDNDXzdHWnZLZnFSakwyV29kTXcxZWxvN1pWdzNMOURXTDd1aHRVM195V0pMaGd3N2xSNWs5MXVwWE5Qa2hoVFN6aHNaRlhNT2RuVFhDSi1GWXc3TkE0V2pzd2RkV3o5TFc1MmJfZ3pCOWtocVR1YmlNdThWVEdsSFZDSnpiQ1N3TVFxYXhOX3l0WUtZWWVOOU5fc3hIdm0wZEhHUGtCWVpReGdtZzd5U1VIWTRYU1g5bVZHSUtjRDJnbk5BeGEwRDBRRkVINDAyQkowcUYzM1ZDZ1dPTms3Yng3Z3ZBQWhGa21VT0pOeDVEU2rSAaYCQVVfeXFMUHlhLVdiMUJtOXNBVldTaVRacEo4V3JtYm9QODhHdlhBY3pfQnlQMW5vbWhYa1hHLS1nVGZ1dHRqSkh1b0VjaEhRcVVSTmlpREdEZ0VOMWE5ZjU2Vk8ySG0tQ19acTZwcHYxelg0NDZmMDI0NFpvTTZvNTFqVTBVb3dYSjhQYjNPSUE1aXN1LThzaHVweW1XRWxYTUN0VFlXV3RuZV9JcXZWeDNwUWtQLVhjMWx5UjdiMXdzTlB3TGw1TjJNbElNX2FYOHdhb1ltWXA4bUY3SmwzelBHSkdVNnpyanl1QzQtbDJYc0JkdElCODFLaUlnemhOWjV1UkhnVFVEVzVaVjlvajFWd0FOOTlob3B5NmZHaWVtR3ZPeDRXVEQxMmxR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNy16bzc2dktiRGkyeXN3blBBRzZ3WjNxek9QX3hqV0o0dlZfNUtvd3ZMR1pvcEJXSndIU0lyMDZCb0hQa3R6WXVBTnZmOVNTU0xqN2Z5OF9UWUVuRDRzOUNrajNwbXkzUGJnRU44LTJYdEdQSEJJcDZOLUJqSG5DaG5MdVhyejh30gGIAUFVX3lxTE9CMGNNcjFpQzFVSzNhN3pzSF81anVxX2dfX0tFODRCVGFEN1ViUkV6OU9ldU1sbm0xd2xkLVdKZUtkX1ZZNDF6Ti1sNWNfTVlVeHdxQ2dET0hIMm1YQ1d5eG4xMVdEdmUyVll5SlRUYkVZZlU3X012aFRSRVEtdFg5UVdDMUI5elg?oc=5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2910,17 +2910,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos - integracionsocial.gov.co</t>
+          <t>Más de 800 colegios privados han cerrado en Colombia desde 2020 y el panorama parece empeorar - bloomberglinea.com</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>integracionsocial.gov.co</t>
+          <t>bloomberglinea.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2930,22 +2930,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQRE5KUVBWM2tVV3FSR0E5OWYzZTdfWm0ybU50TzVFNUNlRkFmazZtVzdiZlVTSXFQMTQzajNpYlduWUtfaXZIRWdUVHRBeHVvM1FzQ1o2cEYzRjZIa1ZiZFU0azlXa2dZaXU0X19EdjR1YTIxRmVEVnpXUmotT1JtMGln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQMUlhLWE5ZzVjSzRUNEF0Z0kyTFNsb0d4dnh0aEpXUXNVbmxHYTRhZFJPX0llWXRZdFpkbnNGeEFmZWdzY3dEUWJLbDdDb0wxcGNyMFJKQ3ZJR0xwN28tMGhrVDhRV1dGUlpSa0g3LUlEQlcyajd6MEtqV2oxakJkYVFSdmxEUmI1NlJVcXhFQ01RRXRYdGU5RHpRbnp0STVsWERmZkhpVnVPc3NUU0hYZzZBS2ZUUkRyQldrRXlMVDVSQ05Jc3hLQ0pEWWVrTkNRR09FRDVPTFhMQnA1TTRCRWpB0gH2AUFVX3lxTE5NZGlCQjUyZDktS2RmeEdqbzkydjZfckZjNlJBa00xa3E2bTREbXB6eE1zVnZFdGtFOEdLdC1ZTFlSSDl3cDBlZTM1VDNSQ2o2UThxeFhVU3J1UTF5Yzk5OWQzSkFsQUl4NmN6LVRVbm96VWRVd0IxTXhIdGIyVDhXczZSUTJ6YnBXYnB1LW1NMlBybnQteGFOeC1uX2JOUkRGU0JCY1VRVGltcTFiZWxCa052a3hFRnU3WVptR1V3d2oyMWRVMmpHT1d3Wjh1eThwanIzc0NWVjFqNlF1TUdlN2psdkdhSnIyZWxtUC0xR2pVdGRtUQ?oc=5</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rafael Uribe Uribe da la bienvenida a sus nuevos consejeros de juventud 2026-2029 - Bogota.gov.co</t>
+          <t>¡Participa! Convocatoria de Jóvenes con Oportunidades con más de 12.000 cupos - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxORkNNZDdHbmU1YjF1bnNSM05ZaXU1V29qek5lUDNTN01FT092N0VnY0syVDBqZ05sdHQxazYyNm5GeTFZaERsdnNiM3V5ZHdhWXRnMDhJWHJWc3lzZFlBWWpaM1ZuWl9lRXF2RG1xSjBOU19fcEN6LURTQVA0cW9kT0FRRmNEcUpwRmJKdm96T2EtaFN0NlhaOXkzTVozSTBlN1A4akUzV2xkeW0xNHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOMkc2STM2aDJ1Vi1qSF9fM1pZNkxoSmJlbDBLMEtmTk1vYmNZdG1sTjNkcXI3M2t1dGVyT3lrdmdDSEJjU2k5TE9VZ2otVDVqeE1qcm1LbDd6WG9zdlllVk1RaDFvMVEtTHNoNmg4UGhscEFlSVBhX0V1ZWIyRWdIR2tXOVZjeHJaWFp3Ukh6dDBNd19ZVzFyQTM1WjloblNBNlhEU01iRURUeFZRX0ZsSVJyV0hONUR1WUE?oc=5</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>La Universidad Católica de Colombia recibe estudiantes de intercambio internacional para el semestre 2026-1 - Universidad Católica De Colombia</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos - integracionsocial.gov.co</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Universidad Católica De Colombia</t>
+          <t>integracionsocial.gov.co</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQOHNQN09kUklZS1ZDZGFvYmtNMzNWczQ4QXU2eXB1eWdlRnZyU2ExUnVlSzRPdnZOU0hRLTctMnNsNWttZ0ZlNmlBeEZabW9PZ1hkd1p2NElQbkRSWjFva1EyMmdtS2l4eVZ1Q1dZNGlaVGZiSFRFblh3VFllWVpkY3hRZFlNdkNXdmE3LUZQc1daZ1FZZTdrLUQxTURaWDFubVR2YTVOMzZKalNDeVBwajluc0RobVFfZzJVQXJrVVp2QU9zR2ltcWxUVmloZTFCN2U1NHRDOG1XcC1q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQRE5KUVBWM2tVV3FSR0E5OWYzZTdfWm0ybU50TzVFNUNlRkFmazZtVzdiZlVTSXFQMTQzajNpYlduWUtfaXZIRWdUVHRBeHVvM1FzQ1o2cEYzRjZIa1ZiZFU0azlXa2dZaXU0X19EdjR1YTIxRmVEVnpXUmotT1JtMGln?oc=5</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3039,17 +3039,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Juventud que honra la patria - policia.gov.co</t>
+          <t>La Universidad Católica de Colombia recibe estudiantes de intercambio internacional para el semestre 2026-1 - Universidad Católica De Colombia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>policia.gov.co</t>
+          <t>Universidad Católica De Colombia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1GT0lYblBCXzFacFBoWjdCTzNrUGxhT25ROVVMc3RhOGUzVk5VdTVHdlU3aC1OcnREYmxuUHE0QlFYcnZLblh2THpaVFRtLUJWRXpudFg2QWxmN1VRVi1pSUVEUXRNUDlJQlZ3MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQOHNQN09kUklZS1ZDZGFvYmtNMzNWczQ4QXU2eXB1eWdlRnZyU2ExUnVlSzRPdnZOU0hRLTctMnNsNWttZ0ZlNmlBeEZabW9PZ1hkd1p2NElQbkRSWjFva1EyMmdtS2l4eVZ1Q1dZNGlaVGZiSFRFblh3VFllWVpkY3hRZFlNdkNXdmE3LUZQc1daZ1FZZTdrLUQxTURaWDFubVR2YTVOMzZKalNDeVBwajluc0RobVFfZzJVQXJrVVp2QU9zR2ltcWxUVmloZTFCN2U1NHRDOG1XcC1q?oc=5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3082,17 +3082,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tratado START, niños en Colombia y España, Gaza... Las noticias del jueves - UN News</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos - integracionsocial.gov.co</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UN News</t>
+          <t>integracionsocial.gov.co</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3102,22 +3102,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA3d21fTnBoQS1hakduX0ExZXJSUlZzcmlneHN5TFJUQW1WMjI4dU1CWV9vN21QaWNLX0JZcjJ1UElINTFfTXFYbWI0bWxRNkpXUGdMaTZYWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxNMzJhelJqNkVVMlpLUDNKMjlBazI0c3ZIemxfRE1oRFdFWjh4WWRxbTJScTV4QWF1ZG1ZOHFvWmJ2Si1iUzlOQ3NPUVVaTmV0ZVZSOWxSanhWd1hkSHFlUmYyUnZQaHJFdUZNNDFqZm9GQ1IyeVhfUENReEg3RHNMQlZYd0Q2emw3dXh4ODdIUVozU09lVks4VU90ODhNTjNLVmxNbGlMV0k4WXFNdURHaVpCSjlPUTJOdllnNVJ0VVVPOVN4OEo4djBkamJvSjE1Ny0yMFVNdGRxYU1zTlJEaU1PTTMxbDZkVGxxNWlscnBicEwxN20wX2VmdzRqdE43bUUxdkZuSVZRMG5GZmc?oc=5</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -3125,17 +3125,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Estas son las universidades bogotanas que más han perdido estudiantes en los últimos 4 años - Portafolio.co</t>
+          <t>Solo 13 de cada 100 estudiantes en Colombia alcanza los aprendizajes básicos y la mitad no llega a grado once: Advierten consecuencias 'catastróficas' - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portafolio.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3145,22 +3145,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTlRkZkdaSEtLcWdXRDJqS0xGa2ZuMFdISTVSUm5pR2NvWFZaeG9ZQXlNdVFLMmpmbWd0Nzh3cUcwaEtNbUpVdnJhSkdNNk9WSXNYU1dfcHZ4R3FXSG1yY2twX3d2N1ktWHgxN2FrdmgwRVRmTkZhZWVUWDk5SzB4R3ZzaWVJNmZRSDRyY0wyd3ctS2VNUWI5SU9raXItRW5PUElJMDVuTHh3LVdYQlB4ZXJQSHNjVmpmdWtaN0RNRm5ZeXZqd0RxOFdsNjZSYzdxNE95NmFvYWJEd9IB3wFBVV95cUxPa0V1SER3OUR4QlMzUVFScDZPQmlsbXdjOHBuSHlHS2pjZkw3N3l2NE9XNU1xU0gzNkJvNGNGV0oxTVczaTdjWm5jUlAzSjVpMkJEVm9zOFpXQ3NKMDA2aXE3S3pXVU1PYml6NTB1eUR0dEdseTJhNFZLeWxTTWhqOTJNaW5tQ09kTjduLThpX3FKbEFvTnRaY3F4UVhpOW1NYmtNbXFRaTVaVVA1S1pMeTRGRU94VVllcDIyYlVjYU5pemxnUDRsSlVuZnM4NmpmRDE5emw2RVdHdTRMMmZr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNNE9BSllXSG53VWU5clFlTjBXanVlUEswSmdVVkxCeDJCS0NtNzQ5cTJPckc3ZDNDXzdHWnZLZnFSakwyV29kTXcxZWxvN1pWdzNMOURXTDd1aHRVM195V0pMaGd3N2xSNWs5MXVwWE5Qa2hoVFN6aHNaRlhNT2RuVFhDSi1GWXc3TkE0V2pzd2RkV3o5TFc1MmJfZ3pCOWtocVR1YmlNdThWVEdsSFZDSnpiQ1N3TVFxYXhOX3l0WUtZWWVOOU5fc3hIdm0wZEhHUGtCWVpReGdtZzd5U1VIWTRYU1g5bVZHSUtjRDJnbk5BeGEwRDBRRkVINDAyQkowcUYzM1ZDZ1dPTms3Yng3Z3ZBQWhGa21VT0pOeDVEU2rSAaYCQVVfeXFMUHlhLVdiMUJtOXNBVldTaVRacEo4V3JtYm9QODhHdlhBY3pfQnlQMW5vbWhYa1hHLS1nVGZ1dHRqSkh1b0VjaEhRcVVSTmlpREdEZ0VOMWE5ZjU2Vk8ySG0tQ19acTZwcHYxelg0NDZmMDI0NFpvTTZvNTFqVTBVb3dYSjhQYjNPSUE1aXN1LThzaHVweW1XRWxYTUN0VFlXV3RuZV9JcXZWeDNwUWtQLVhjMWx5UjdiMXdzTlB3TGw1TjJNbElNX2FYOHdhb1ltWXA4bUY3SmwzelBHSkdVNnpyanl1QzQtbDJYc0JkdElCODFLaUlnemhOWjV1UkhnVFVEVzVaVjlvajFWd0FOOTlob3B5NmZHaWVtR3ZPeDRXVEQxMmxR?oc=5</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3168,17 +3168,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Rafael Uribe Uribe da la bienvenida a sus nuevos consejeros de juventud 2026-2029 - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxORkNNZDdHbmU1YjF1bnNSM05ZaXU1V29qek5lUDNTN01FT092N0VnY0syVDBqZ05sdHQxazYyNm5GeTFZaERsdnNiM3V5ZHdhWXRnMDhJWHJWc3lzZFlBWWpaM1ZuWl9lRXF2RG1xSjBOU19fcEN6LURTQVA0cW9kT0FRRmNEcUpwRmJKdm96T2EtaFN0NlhaOXkzTVozSTBlN1A4akUzV2xkeW0xNHc?oc=5</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Tratado START, niños en Colombia y España, Gaza... Las noticias del jueves - UN News</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>UN News</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3231,22 +3231,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA3d21fTnBoQS1hakduX0ExZXJSUlZzcmlneHN5TFJUQW1WMjI4dU1CWV9vN21QaWNLX0JZcjJ1UElINTFfTXFYbWI0bWxRNkpXUGdMaTZYWQ?oc=5</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3254,17 +3254,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
+          <t>Juventud que honra la patria - policia.gov.co</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>policia.gov.co</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1GT0lYblBCXzFacFBoWjdCTzNrUGxhT25ROVVMc3RhOGUzVk5VdTVHdlU3aC1OcnREYmxuUHE0QlFYcnZLblh2THpaVFRtLUJWRXpudFg2QWxmN1VRVi1pSUVEUXRNUDlJQlZ3MA?oc=5</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3297,17 +3297,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>“Ahora que estamos un poco más viejos, queremos ser un ejemplo para la juventud”: Camilo Villegas, golfista colombiano - UNIMINUTO Radio</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UNIMINUTO Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPOFJRNk52Mkx1Q2hFTm5oQV9UUFlLYkVlMjZEanRsN0hnQU9xRTJTR08tQTl2MVYzQTFMWkRuYXJFcG4zbk5iYWE0clBva0dWVXFlMmt5NTQxTUhtamwzazlacC1HdXZjRkRFVW03U3ZNVVdGTEZHY0JHalFaVXJwLXpZRVpIYm1FcWhkUWVyY29Ud1Rzb1NDUG1UczFJdXNJNnh5MkpPbU5WTDFnV3hmcjBTbXpTcndtNnotMmNqNzdEYXJLSEM1cTA3U0F1ZzctQy1tMUhjc28wcU9kT04wc053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3340,17 +3340,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Menores de edad en Colombia pueden viajar sin permiso de ambos padres en 2026: en estos casos aplica - Eluniversal.com.co</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eluniversal.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNUkViVng5bVFEQmo3RnFIQXA5dWV6b0czWnJnaC0zRkc2QWx4dUJsZGZ1cXp3R2RfazFVeGdQZUU3Y1dvWUhlQ2o3NlVIaWlMamJNLXNUdlBzeFIyaFJSSVBoZEotTjRiNjRyUFV4Q1FEWFgxWGIyVGtRbUdrQl9mc0dzNXZlejhIelR3WkwwSDFGTzBydll5M1RHZm9YcmFId2NrMVF5eUczbW82bVU4X3p4dTliaTNRcWYwTlI0UG90b2hDUHYyTkhlbGRoelMzVGh3OGhLQnlPanNiOEgxTWlrYklBZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3383,17 +3383,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>El discurso oficial planteó retos para la juventud y riesgos en la frontera mientras la reorganización de redes criminales se traslada al sur del continente - facebook.com</t>
+          <t>Estas son las universidades bogotanas que más han perdido estudiantes en los últimos 4 años - Portafolio.co</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Portafolio.co</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3403,22 +3403,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdlNPUVI5dDdwZ3B3eHdpemJIa1VFMnh0STBza3hUb3lzVGxYQS1JRHpya21SSHF3RXdBcjROYUptREtXVlJWdjR6dWNhWDd2akZmVVhpdGJjNHlITnZDeVRlRzFHR2xpcV9adWVXS3huM1R5ZUpOVnlYX1FKd3U4WXc4eXFaVlpQT2kwZHlKOTI0U0QtdlQ1STNBM1RhTkhOMVE3SlJRNHJ3VzB5YXdoNVFyT2RIWGhWY0dnaVcwWFNVVHZ2ekVSVTd0S3Rxc1VVRUNkdmgxUm41X3ZsLW9JVG9QRnR0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTlRkZkdaSEtLcWdXRDJqS0xGa2ZuMFdISTVSUm5pR2NvWFZaeG9ZQXlNdVFLMmpmbWd0Nzh3cUcwaEtNbUpVdnJhSkdNNk9WSXNYU1dfcHZ4R3FXSG1yY2twX3d2N1ktWHgxN2FrdmgwRVRmTkZhZWVUWDk5SzB4R3ZzaWVJNmZRSDRyY0wyd3ctS2VNUWI5SU9raXItRW5PUElJMDVuTHh3LVdYQlB4ZXJQSHNjVmpmdWtaN0RNRm5ZeXZqd0RxOFdsNjZSYzdxNE95NmFvYWJEd9IB3wFBVV95cUxPa0V1SER3OUR4QlMzUVFScDZPQmlsbXdjOHBuSHlHS2pjZkw3N3l2NE9XNU1xU0gzNkJvNGNGV0oxTVczaTdjWm5jUlAzSjVpMkJEVm9zOFpXQ3NKMDA2aXE3S3pXVU1PYml6NTB1eUR0dEdseTJhNFZLeWxTTWhqOTJNaW5tQ09kTjduLThpX3FKbEFvTnRaY3F4UVhpOW1NYmtNbXFRaTVaVVA1S1pMeTRGRU94VVllcDIyYlVjYU5pemxnUDRsSlVuZnM4NmpmRDE5emw2RVdHdTRMMmZr?oc=5</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3426,17 +3426,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Google y Colombia ofrecerán 20 mil becas para jóvenes en inteligencia artificial y ciberseguridad - Radio Nacional de Colombia</t>
+          <t>“Ahora que estamos un poco más viejos, queremos ser un ejemplo para la juventud”: Camilo Villegas, golfista colombiano - UNIMINUTO Radio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Radio Nacional de Colombia</t>
+          <t>UNIMINUTO Radio</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNLXpWa2dvSjF2b21RNzQyN2EwdS1tR1FidXFzaEtSWVJ5eDRQWlE0cUJzWmExdWRYcmR3dlo2VXJDV2cwejJoa29JUVhIVEtPcFZjRlp6eHgtZkhsV2JwamkzY3RDREdlZi1BeUlPeGF6d1Zsd2lPS29mQVlrdVk2b2RNMlJVVHcxbENaaUdyRWVCWmdacl9QNTF6X3doWjY5bHliMzJsa3RwazRwWW1kbkNObzJWWUI3eTNYRdIBwAFBVV95cUxNbk1SdEsyOEFxQV91a1RYSm81bUhTdVgxSjdEeG1FVEY1V09pX2hPU29kRnNaMEhwZjB6WnZfSTFfb0tnTWMzdWtLZTlHbVh3emZRckpRblhveE5xVnY5dzRCMzlMZ2dPWmk5cHJHMzNVVzRlTkVtMjd4Znpuall4V2dVUy1EbWNMM1lJdTlrLTVkU1ZNQWdhUER5MGdHbjhXQno0cE44WW1ZdS1md2JaOEc0aFF5c29iUVVFbUw2Z3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPOFJRNk52Mkx1Q2hFTm5oQV9UUFlLYkVlMjZEanRsN0hnQU9xRTJTR08tQTl2MVYzQTFMWkRuYXJFcG4zbk5iYWE0clBva0dWVXFlMmt5NTQxTUhtamwzazlacC1HdXZjRkRFVW03U3ZNVVdGTEZHY0JHalFaVXJwLXpZRVpIYm1FcWhkUWVyY29Ud1Rzb1NDUG1UczFJdXNJNnh5MkpPbU5WTDFnV3hmcjBTbXpTcndtNnotMmNqNzdEYXJLSEM1cTA3U0F1ZzctQy1tMUhjc28wcU9kT04wc053?oc=5</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3469,17 +3469,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
+          <t>Menores de edad en Colombia pueden viajar sin permiso de ambos padres en 2026: en estos casos aplica - Eluniversal.com.co</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Eluniversal.com.co</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNUkViVng5bVFEQmo3RnFIQXA5dWV6b0czWnJnaC0zRkc2QWx4dUJsZGZ1cXp3R2RfazFVeGdQZUU3Y1dvWUhlQ2o3NlVIaWlMamJNLXNUdlBzeFIyaFJSSVBoZEotTjRiNjRyUFV4Q1FEWFgxWGIyVGtRbUdrQl9mc0dzNXZlejhIelR3WkwwSDFGTzBydll5M1RHZm9YcmFId2NrMVF5eUczbW82bVU4X3p4dTliaTNRcWYwTlI0UG90b2hDUHYyTkhlbGRoelMzVGh3OGhLQnlPanNiOEgxTWlrYklBZw?oc=5</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3512,17 +3512,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sacerdote condenado en Colombia por abusar a menor vive impune en Perú: está “rodeado de niños” - Noticias Caracol</t>
+          <t>El discurso oficial planteó retos para la juventud y riesgos en la frontera mientras la reorganización de redes criminales se traslada al sur del continente - facebook.com</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPQ2tlTHBMcEM0YjFYcmZ2aXNrTXZraE9Yd29VQ0pwczNjWnFiWUE3VkY3M2VEX0Yxa3I1WHRKT0w0dE1fREtWcDFHTXV0S2FZZHhWLWdSRXpmUWIwUEVOVm9NdklDRi1zU2dDc2I3X3BvM21tVFdlc3NHQVBjMnZPck1RTHNTOVJpN1JYWnJYRnFoOVFJaG5HVldZYWIxaHZVaFUwS08xdXdwTjhxZ0wwX1VpdWwwV1lidTFSblRBTEx6ZlRmeTNraGNHOEdQdTVtT2pmdjNHUWtQYTk4b2fSAesBQVVfeXFMT183RG10VmZJeVFaa1pRc3NqcEE1bFd3MUU1Y3l6ZEIyOTZnNFVvRWw1NlhzTmMzdm15LWFLZGczN0doUzA0Y0dZcGRrZ2JnOEdGNUFLYWlvZmpWMUxLOTRsclBLWmY2TTkyRUdwaFZjREJXZlNHNXlqNkRRMXc2NUIzODJKcWVDWmJIc3FOQy1ZYXJkT1VCZjdXMmFmYkF5TGhFek13VWNBTWdFZ3QyYjdpRDlsN2tnSDYwSjV3SDQ3MXVhOU1vQm9qR1ZZdTNJOUxMRURKaC1RdndoajNCbmdINlB6bDZqUDVEMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdlNPUVI5dDdwZ3B3eHdpemJIa1VFMnh0STBza3hUb3lzVGxYQS1JRHpya21SSHF3RXdBcjROYUptREtXVlJWdjR6dWNhWDd2akZmVVhpdGJjNHlITnZDeVRlRzFHR2xpcV9adWVXS3huM1R5ZUpOVnlYX1FKd3U4WXc4eXFaVlpQT2kwZHlKOTI0U0QtdlQ1STNBM1RhTkhOMVE3SlJRNHJ3VzB5YXdoNVFyT2RIWGhWY0dnaVcwWFNVVHZ2ekVSVTd0S3Rxc1VVRUNkdmgxUm41X3ZsLW9JVG9QRnR0QQ?oc=5</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3555,17 +3555,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>¿Cuáles universidades en Colombia ganaron y perdieron más estudiantes en 2025?: aquí el listado - La FM</t>
+          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>La FM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3580,17 +3580,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNeWdma2NDUFpvSzNlS2hSLV9tY2hxeGJ1VXNnTUFxRVJ3M3dkYnFsRU1COGtVdW41Vmt2a05laUJtMmE5WHlLNlBFNUNzMjJxSXRfam5YV0J5cndmT3l6SXNfUjZ2WFdtdWFaMHNLb0JtQk94WFdjVG5zVWJJQ2VQSEowclQzOW9YZ3FwcnZUY1MxZkY1b0hWUlk5ZlNVTFnSAZ8BQVVfeXFMT3JGVXFySEYwOWJwT21FMXp2bkFHR3MwZHFTRDVmTndleFlJOTBjRi1oVzZBejJyejNsMlNNa1NoNnF3TTVnX1BZSjRUOF9ObGs0eW9BNzAwYl9qallvRmpwMmZ4SnByVmotNHhoU0pTY2hIZEZiT3gtcmVWb1ZhdUtWUzRGX2JfVl96Mm1KYk9nTXhEaUE2cmdtdy1fc25n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3598,12 +3598,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3641,17 +3641,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>La ley colombiana que permite que un menor de edad salga del país sin la autorización de ambos padres: ¿en qué casos aplica? - ELTIEMPO.COM</t>
+          <t>Sacerdote condenado en Colombia por abusar a menor vive impune en Perú: está “rodeado de niños” - Noticias Caracol</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPdUc1dGVMTXJvN3c2c29yMVA3aHRBVV9sRlZRdmJqM25wUzhpNC1kSzQ4U2VEU0ZfRVY1ZUJjM0JRT282b3dkUVlpVFZNN2lEc21yNUl0Yk1qZXRvNmppdGQzazdGcHI4YTZ0Z2NlX25leFhUSjlCOXNUSnV0azRwS19lUlJtODEwcDJRd0Vic2s2R05idWp4d2ZkWWZqMTlFcmtwUzlwU0tvMHRWcDEzR2REMTdEbXVabm9lVUtQWWRjUy1vazc1SXpWZ1dqOERIbHN3TGhZYm9GajJOSy1ES3NqX2RqYTJCVl9ZZHFFSkJ1WTRmVVhEYnpB0gH_AUFVX3lxTFBUOEp4NTVxaTM4dW9UX215aDV4ak5UY0N4MzVzYjZCTWtmUU5XRWxOMDBlRXZnVTl0NXpFQW5yNlFIRTM3NmU3dXlQNTRoUk1IWnBnMjRuRGxsTExnRTVrR2xkNG93R2s1RXMwdFN0TmtTWG12ZEFWQ3NobWxjMDdtYXZBUE5rZFZvd1NWQlExMWVPVTV6VVlzQmJqclZmX0tzbzg2NGQ0ZFVWelgya3MwcExUTHEtUWl2S09Dd2JHYTNYZ3VnZjVhSm9UbXFtOVdzbTNUdExLekFHekI4XzhzTndGcjYwNWZxeVV1aWkxdEZaa0w4YlIwenV3WVBaYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPQ2tlTHBMcEM0YjFYcmZ2aXNrTXZraE9Yd29VQ0pwczNjWnFiWUE3VkY3M2VEX0Yxa3I1WHRKT0w0dE1fREtWcDFHTXV0S2FZZHhWLWdSRXpmUWIwUEVOVm9NdklDRi1zU2dDc2I3X3BvM21tVFdlc3NHQVBjMnZPck1RTHNTOVJpN1JYWnJYRnFoOVFJaG5HVldZYWIxaHZVaFUwS08xdXdwTjhxZ0wwX1VpdWwwV1lidTFSblRBTEx6ZlRmeTNraGNHOEdQdTVtT2pmdjNHUWtQYTk4b2fSAesBQVVfeXFMT183RG10VmZJeVFaa1pRc3NqcEE1bFd3MUU1Y3l6ZEIyOTZnNFVvRWw1NlhzTmMzdm15LWFLZGczN0doUzA0Y0dZcGRrZ2JnOEdGNUFLYWlvZmpWMUxLOTRsclBLWmY2TTkyRUdwaFZjREJXZlNHNXlqNkRRMXc2NUIzODJKcWVDWmJIc3FOQy1ZYXJkT1VCZjdXMmFmYkF5TGhFek13VWNBTWdFZ3QyYjdpRDlsN2tnSDYwSjV3SDQ3MXVhOU1vQm9qR1ZZdTNJOUxMRURKaC1RdndoajNCbmdINlB6bDZqUDVEMA?oc=5</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3684,17 +3684,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>'Los jóvenes son apáticos a la política porque no les han cumplido; los invito a quedarse en Colombia'. - Portafolio.co</t>
+          <t>Google y Colombia ofrecerán 20 mil becas para jóvenes en inteligencia artificial y ciberseguridad - Radio Nacional de Colombia</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portafolio.co</t>
+          <t>Radio Nacional de Colombia</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPTFB4Z1ZGMHU2Q2hKcjVObjFEYV90WnpaU0dIc1hQODNtN05SaC16Nnl3Ny1hNV9VRWxma0tyTzhlNFJ1ZURzMV9JdkhUMnNKQU16ZUEtV3VYQVp4RlduMkpIdXFSY09Pak4wZWEzM0pmS19lZ1dpSVZseFp5X0JuWnZCWFk0VXlaeUtyS19GNGlNOHE0LUEwblJkZnF2dkxnTV9hN3lEcDZhaTZZeXdKS3lOYkxLSFhhRUhsOVFMamRjYzhJSXMwZF9rSHBMSXhmUGUzekhTbGVySWJSNzBjLUQ0djHSAeoBQVVfeXFMTUFTM3Zpb3M1Z2lPdUlVd1llQU5FWmVrSWE5a01jZklSRDJpQkFIZ3VEVXJndkZmQXBVSUVDNGFnSHJrX0lvQS1DcTc5MEYzWEZMZkFrRFFSUTZfeXkySkdOUEdLZnJGdTl2NENNSGxtS3FfZHNhR210UVJxRG5wUkxtTzlnVURPZXdhVmh6UnktNFZtYWxicXp0S0NaSlh5akxuNnp1WlJhYjM5RkJEX1ZDelFJQkpZbjhiNFpibDNaem5HNll0elNrTGdqTU5mbld6VVJ4MkpqS2F1TmpZZHRCTnJTSlVGUDVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNLXpWa2dvSjF2b21RNzQyN2EwdS1tR1FidXFzaEtSWVJ5eDRQWlE0cUJzWmExdWRYcmR3dlo2VXJDV2cwejJoa29JUVhIVEtPcFZjRlp6eHgtZkhsV2JwamkzY3RDREdlZi1BeUlPeGF6d1Zsd2lPS29mQVlrdVk2b2RNMlJVVHcxbENaaUdyRWVCWmdacl9QNTF6X3doWjY5bHliMzJsa3RwazRwWW1kbkNObzJWWUI3eTNYRdIBwAFBVV95cUxNbk1SdEsyOEFxQV91a1RYSm81bUhTdVgxSjdEeG1FVEY1V09pX2hPU29kRnNaMEhwZjB6WnZfSTFfb0tnTWMzdWtLZTlHbVh3emZRckpRblhveE5xVnY5dzRCMzlMZ2dPWmk5cHJHMzNVVzRlTkVtMjd4Znpuall4V2dVUy1EbWNMM1lJdTlrLTVkU1ZNQWdhUER5MGdHbjhXQno0cE44WW1ZdS1md2JaOEc0aFF5c29iUVVFbUw2Z3E?oc=5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3727,17 +3727,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>16 colegios y guarderías han cerrado en Medellín desde 2023: caída de nacimientos sería una de las causas | El Colombiano - El Colombiano</t>
+          <t>¿Cuáles universidades en Colombia ganaron y perdieron más estudiantes en 2025?: aquí el listado - La FM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>La FM</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNUhQeTlqb0hCbnZUSVk0dzJBZ1V0OFJWSEM2MkNBMlBPYzFKRmRWWk5NRjBHX0tBS1dsWll4d1cyNGRQTmNScjVuYkprcGYxcXlhV0lDanpZbXNNeXZmS1NUb0RXTnVXTXlVOWdjWXpQYlhhSk53WFZiSU8xREtkYUlNWTluby0tYzBuMTR2NW5VSEJFRWlDazQ2clZvZ9IBowFBVV95cUxNQW5kQnBqdDYyWldMcXhiWXNZcU1rc0NBMzh2UURMZkZhZ0JtSXhFNklCMnpDdkQ5ak5sY3I5aVlXWV9sWTVpbDFLNjAwaGtsMHl3bFVXSS03ZEs5RS16WmF0aUZudnpCZzNIdko0WFg5UC0zRnB2TnZrQ1JYOWJqak90OVNzS3RiUVV0QWNRUWdudzR4b2hPbWlKZTJQU2M3RnRv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNeWdma2NDUFpvSzNlS2hSLV9tY2hxeGJ1VXNnTUFxRVJ3M3dkYnFsRU1COGtVdW41Vmt2a05laUJtMmE5WHlLNlBFNUNzMjJxSXRfam5YV0J5cndmT3l6SXNfUjZ2WFdtdWFaMHNLb0JtQk94WFdjVG5zVWJJQ2VQSEowclQzOW9YZ3FwcnZUY1MxZkY1b0hWUlk5ZlNVTFnSAZ8BQVVfeXFMT3JGVXFySEYwOWJwT21FMXp2bkFHR3MwZHFTRDVmTndleFlJOTBjRi1oVzZBejJyejNsMlNNa1NoNnF3TTVnX1BZSjRUOF9ObGs0eW9BNzAwYl9qallvRmpwMmZ4SnByVmotNHhoU0pTY2hIZEZiT3gtcmVWb1ZhdUtWUzRGX2JfVl96Mm1KYk9nTXhEaUE2cmdtdy1fc25n?oc=5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3770,17 +3770,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Los motivos detrás del cierre de 16 colegios en Medellín en los últimos tres años | El Colombiano - El Colombiano</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUU5vYUFOTGVaS2lNNl9wTTZXMnc5Sm9tWVRkTVpxV3RER3NCbklwQVdHV1NFdGNJNVNOTzFhS2YwbEV4akZtVG5VSzFaakppZVl4dDN1RE10WE1oVlZjRlc3Sl85M3VTR0d0RFZNUFNSdXM2anltc0d2V2VGU0IyZThIOU1DdGRSZGJtakExUkbSAZYBQVVfeXFMTzVHWUpWb0Y3a2h3Z1d1T0Njbk9vaWdCdHZCTmZkelEyM2Rmb3JQQXJGZE5LLXBpM1hjbWVuM2RoUS1KSktYMnVKSHAxaVRzcU4yQlNxMFpKVWRIM1loWk5CZ1Q0TEJScTU3Z1RTUmVmbW53OEk4STJrVmlIWi1NcERkNng3VFFQM1Z5OGU5SlpfX0ZFTUVR?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3813,17 +3813,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>¡Anote! Prosperidad Social revela fechas de pagos de Renta Ciudadana, Colombia Mayor, IVA y programas para jóvenes | El Colombiano - El Colombiano</t>
+          <t>La ley colombiana que permite que un menor de edad salga del país sin la autorización de ambos padres: ¿en qué casos aplica? - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOVY3YjlmWmt4SnctbF9Hd3IzZzZSMWNpaC1YWTZkNVdEcnhyb256VFFZRTFiLWtULUdSREVQRGJmREhORmJQbFpubkY5NkViZEVfMEp5ck5GQWppTmhfTHVmWEU0eGlMTUN5NVhNTjlJNnpRR0wwVUQ1ZUlIODBCeDVvN3RuYkpKSzVCOGhfRFNCVUNJaERDYmZUaUlZMmxPWVJSOUdwTWhETmM4MGpVVUsxS0dHTU1tLXlzQ3dKS29FNTBJakFCT3F1WlJueWprU19KVGNDaFA4SjjSAeABQVVfeXFMT0lSMjYwM3VVcFQ0c3ZSdXczQldoczBwajdIWENEYU8zeVRIU1JtNnpJQUw3MklYbUNjWTVHS3Vfd3I4UzNzcmRGbDVXU0tDbG5jaGZ5MklUcENJc2htRFdZcGI1c0JIeGxfSFhQOEI3WHNrR21faHRZa21ZME5rVjVvVDd0MXlLVHlxNG43X0RYWDA2ZV9hUHlqeHVSQnRRbXdBQnFDRVc0YjRWQ2J3eWUzQmtaUjl6RmFVMEoza1dEUnZRWEZuakRhY0N6ZVNQSzRXQk5ZVVo2TlpnWmlwZ00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxPdUc1dGVMTXJvN3c2c29yMVA3aHRBVV9sRlZRdmJqM25wUzhpNC1kSzQ4U2VEU0ZfRVY1ZUJjM0JRT282b3dkUVlpVFZNN2lEc21yNUl0Yk1qZXRvNmppdGQzazdGcHI4YTZ0Z2NlX25leFhUSjlCOXNUSnV0azRwS19lUlJtODEwcDJRd0Vic2s2R05idWp4d2ZkWWZqMTlFcmtwUzlwU0tvMHRWcDEzR2REMTdEbXVabm9lVUtQWWRjUy1vazc1SXpWZ1dqOERIbHN3TGhZYm9GajJOSy1ES3NqX2RqYTJCVl9ZZHFFSkJ1WTRmVVhEYnpB0gH_AUFVX3lxTFBUOEp4NTVxaTM4dW9UX215aDV4ak5UY0N4MzVzYjZCTWtmUU5XRWxOMDBlRXZnVTl0NXpFQW5yNlFIRTM3NmU3dXlQNTRoUk1IWnBnMjRuRGxsTExnRTVrR2xkNG93R2s1RXMwdFN0TmtTWG12ZEFWQ3NobWxjMDdtYXZBUE5rZFZvd1NWQlExMWVPVTV6VVlzQmJqclZmX0tzbzg2NGQ0ZFVWelgya3MwcExUTHEtUWl2S09Dd2JHYTNYZ3VnZjVhSm9UbXFtOVdzbTNUdExLekFHekI4XzhzTndGcjYwNWZxeVV1aWkxdEZaa0w4YlIwenV3WVBaYw?oc=5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>En San Cristóbal se fortalece la participación juvenil con la instalación del Consejo Local de Juventud - Bogota.gov.co</t>
+          <t>16 colegios y guarderías han cerrado en Medellín desde 2023: caída de nacimientos sería una de las causas | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3876,22 +3876,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT0NxRk9zUGZMNzd0TG80N0lKaGwtZlpGSmpKMzVsZW5VU3haNHJ5Z0lZZFlPVFI4U05kQ0VRQjBERGIwMkVUUEgyVVlGR192R0w2TTMxa0h4MHNHMHBDRVBFa0paVmdwdWg1b003X3ljMU9qb3RuQTNXT3hMQnY5MWJrS0p6amV2bW10cGpwOUxsV2hzekRnd0ZNQ1g5YWdLeWZPd1pWem14aTRW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNUhQeTlqb0hCbnZUSVk0dzJBZ1V0OFJWSEM2MkNBMlBPYzFKRmRWWk5NRjBHX0tBS1dsWll4d1cyNGRQTmNScjVuYkprcGYxcXlhV0lDanpZbXNNeXZmS1NUb0RXTnVXTXlVOWdjWXpQYlhhSk53WFZiSU8xREtkYUlNWTluby0tYzBuMTR2NW5VSEJFRWlDazQ2clZvZ9IBowFBVV95cUxNQW5kQnBqdDYyWldMcXhiWXNZcU1rc0NBMzh2UURMZkZhZ0JtSXhFNklCMnpDdkQ5ak5sY3I5aVlXWV9sWTVpbDFLNjAwaGtsMHl3bFVXSS03ZEs5RS16WmF0aUZudnpCZzNIdko0WFg5UC0zRnB2TnZrQ1JYOWJqak90OVNzS3RiUVV0QWNRUWdudzR4b2hPbWlKZTJQU2M3RnRv?oc=5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3899,17 +3899,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>La Fundación Inter Miami CF y Royal Caribbean inspiran a jóvenes talentos en Medellín, Colombia, durante la cuarta Clínica Internacional de Fútbol Juvenil - Inter Miami CF</t>
+          <t>'Los jóvenes son apáticos a la política porque no les han cumplido; los invito a quedarse en Colombia'. - Portafolio.co</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Portafolio.co</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxQVVZ0LWJZWktJWHZaR0lvT1p2VDdsRTdMSGVQLUttZGVuNF9oVm1pRUZvWlE5U0JKVUVqTmxUMl96SUVkX054bHpmUEozQ3VjSk1YUlFuUlhIcDZfWWxwRVBKX2dFbUxxODRCRFVNek14OVY1RnFNTFcyLXoyM1R0dTB1azhSMTRhcmRKdm85aGdvQzBMNi1BYVlZQklOUzBZb3huM3E1QnE1ODJQbTR1LTB2clJraDNVUjlNdVBPRUtJdGhYOGoxdm83SVBtWVlCcGU4WWtBby1XNFVOMGVtWk5nOGYwSWhzSzVkRE5ZdmRlcjB3YWh5aU1zQi1IdjlvUTlfallRb216Si1TamFmTGRwOERNX2VH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPTFB4Z1ZGMHU2Q2hKcjVObjFEYV90WnpaU0dIc1hQODNtN05SaC16Nnl3Ny1hNV9VRWxma0tyTzhlNFJ1ZURzMV9JdkhUMnNKQU16ZUEtV3VYQVp4RlduMkpIdXFSY09Pak4wZWEzM0pmS19lZ1dpSVZseFp5X0JuWnZCWFk0VXlaeUtyS19GNGlNOHE0LUEwblJkZnF2dkxnTV9hN3lEcDZhaTZZeXdKS3lOYkxLSFhhRUhsOVFMamRjYzhJSXMwZF9rSHBMSXhmUGUzekhTbGVySWJSNzBjLUQ0djHSAeoBQVVfeXFMTUFTM3Zpb3M1Z2lPdUlVd1llQU5FWmVrSWE5a01jZklSRDJpQkFIZ3VEVXJndkZmQXBVSUVDNGFnSHJrX0lvQS1DcTc5MEYzWEZMZkFrRFFSUTZfeXkySkdOUEdLZnJGdTl2NENNSGxtS3FfZHNhR210UVJxRG5wUkxtTzlnVURPZXdhVmh6UnktNFZtYWxicXp0S0NaSlh5akxuNnp1WlJhYjM5RkJEX1ZDelFJQkpZbjhiNFpibDNaem5HNll0elNrTGdqTU5mbld6VVJ4MkpqS2F1TmpZZHRCTnJTSlVGUDVR?oc=5</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3942,17 +3942,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Llega el fin de polémica norma en los colegios: no podrán impedir el ingreso de estudiantes aunque incumpla... - redmas.com.co</t>
+          <t>Los motivos detrás del cierre de 16 colegios en Medellín en los últimos tres años | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQa0Q4WmNWV1NnY0hxOGhTRDB4Q0tyNW9VLTNFaTBIU2ZIN1ZRQ1R3LURaR0YwSHplWW5ZcGxDUnNvbXJyNFdWQmNtc0FPUnMzdnhxMkExbTVTdzlOTmQ0RGp0UG11RWRrZldGcnNlM0xPclh2MkozOW4yallGNm5JU0xBVHBhYUlPU0cxamI4NHVNcEMzbnhHZGp0aFpvQ0QyOGJUbzRqd3k4a3ppNXpJSDUxNl9JODgwOXVTNFdFWWhfendmeVQwS192X0ktMnFKVHNJMlR3X3dXUXRDZExHcUFqQndNd2R5RWFtWVZSRGRlTGM1Y2NiUEhkaTjSAYICQVVfeXFMTnFIaUUyVDJYOU9aOHJ1MnZ4ZlFMN3JDdkxTR1NoaTI1Uko0MzVJbFI5aWdpaUhfdDlYeVFrRE1tV2JkX21SaFJCVEtMc3IxMG1EUWZwakZZSlRPZ2JiLUtJLXpwSHAxb2EtUy1nejFRcWRxdFBNX29KV0ExMzNHTUZZQXpGQXFwRHVfSG5sX0FpclBoSHhwa1RidndpMFoxT2JiV0hLb3plSmFUZ05UdmxVb1Q5QkFDUmV3VUR3eWlQTFI3OFdNSjh5NFEzNnJzQzBpdnZ4TVhUSU91T3BROEFLTThBZkVKbU1KUU0xUURDaG5ObWR1UC1GSlZ4N0JLdzhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUU5vYUFOTGVaS2lNNl9wTTZXMnc5Sm9tWVRkTVpxV3RER3NCbklwQVdHV1NFdGNJNVNOTzFhS2YwbEV4akZtVG5VSzFaakppZVl4dDN1RE10WE1oVlZjRlc3Sl85M3VTR0d0RFZNUFNSdXM2anltc0d2V2VGU0IyZThIOU1DdGRSZGJtakExUkbSAZYBQVVfeXFMTzVHWUpWb0Y3a2h3Z1d1T0Njbk9vaWdCdHZCTmZkelEyM2Rmb3JQQXJGZE5LLXBpM1hjbWVuM2RoUS1KSktYMnVKSHAxaVRzcU4yQlNxMFpKVWRIM1loWk5CZ1Q0TEJScTU3Z1RTUmVmbW53OEk4STJrVmlIWi1NcERkNng3VFFQM1Z5OGU5SlpfX0ZFTUVR?oc=5</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3985,17 +3985,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alerta nacional: Niñas y adolescentes fueron las principales víctimas de delitos sexuales en 2025 - Publimetro Colombia</t>
+          <t>La Fundación Inter Miami CF y Royal Caribbean inspiran a jóvenes talentos en Medellín, Colombia, durante la cuarta Clínica Internacional de Fútbol Juvenil - Inter Miami CF</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Publimetro Colombia</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNDJzNU02WjZVRFlSSDlrcGRZQVh5eXowNnR3S0tJVUtwbE9Qb3h6dnN4UkhyTG92WWtrMVlIaXB4RXpFcHVFU2RybTRVM1JyaVJPU05WbDJEeHpiZ3JCTGw2WkRoY0JmM2kzTndoWkUwcVVmeDBKckhUSDlfMkhRMk1qeHJDd3JadWdTdndkZ1diRFJVdGdLcG9QbENyVmpZY3FxeG5qdEF0dWdqenZRQ25qNUdlMnpuem9MRTRsYXpZMzJFMVg3MWN3ZTl2OHk0eUdURzBqN25tS28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAJBVV95cUxQVVZ0LWJZWktJWHZaR0lvT1p2VDdsRTdMSGVQLUttZGVuNF9oVm1pRUZvWlE5U0JKVUVqTmxUMl96SUVkX054bHpmUEozQ3VjSk1YUlFuUlhIcDZfWWxwRVBKX2dFbUxxODRCRFVNek14OVY1RnFNTFcyLXoyM1R0dTB1azhSMTRhcmRKdm85aGdvQzBMNi1BYVlZQklOUzBZb3huM3E1QnE1ODJQbTR1LTB2clJraDNVUjlNdVBPRUtJdGhYOGoxdm83SVBtWVlCcGU4WWtBby1XNFVOMGVtWk5nOGYwSWhzSzVkRE5ZdmRlcjB3YWh5aU1zQi1IdjlvUTlfallRb216Si1TamFmTGRwOERNX2VH?oc=5</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4028,17 +4028,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Indepaz advierte que cada 48 horas reclutan a un menor de edad en Colombia - Asuntos Legales</t>
+          <t>En San Cristóbal se fortalece la participación juvenil con la instalación del Consejo Local de Juventud - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Asuntos Legales</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzZRdHpsR0ppR0ZOcHpRQkM3X0xRYUpQQXZTYmNSMkVPVTY0eHEzeUNXVXYyNFE2SVpaNDNOSG1aajZrUWdFZW9KQU5xS1ZsWjAzaGt0Q2tuUHRzanNCMmQ5OW5CaVhuSmo1bFZsTGR4OEtrTHJGNFR1RlVJZm8yQzNvYThsdDFhQnNKcHZnTi1GN2pYbEFibzdkcV9VT0lsUUdldi10ZUVTRWd4bVdoOE1OcUxyMnFpRlB6OU9kNUxLVHFvcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPT0NxRk9zUGZMNzd0TG80N0lKaGwtZlpGSmpKMzVsZW5VU3haNHJ5Z0lZZFlPVFI4U05kQ0VRQjBERGIwMkVUUEgyVVlGR192R0w2TTMxa0h4MHNHMHBDRVBFa0paVmdwdWg1b003X3ljMU9qb3RuQTNXT3hMQnY5MWJrS0p6amV2bW10cGpwOUxsV2hzekRnd0ZNQ1g5YWdLeWZPd1pWem14aTRW?oc=5</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4071,17 +4071,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UNAD se consolida como la universidad con más estudiantes matriculados en Colombia - Noticias UNAD</t>
+          <t>¡Anote! Prosperidad Social revela fechas de pagos de Renta Ciudadana, Colombia Mayor, IVA y programas para jóvenes | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Noticias UNAD</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPRXI2ZFJ2VWhVRVI2MVBYUG1mbEZ5YjQzR1JuTVZwQ0QyMS1UbXl0aFdxX3hvNGVzTm1rMjNPTDAwUXFCVmtZZk43WkdyZUd3cXZkMjdxdE1acTczWmRmZVNyT05vcjFUUW5oZmRGVFFpeFozZjc4T2Jnb0JzNDVOVHVyS0liak56NzVZUEQ3anF1TlFOVVdkYWhJNTU1RmhtckJGWGlTN2xzem5NZTA2WFZ2bmE3c25ScndCeTZ1OWpxYVlLd0NaQUg2a3lvdjlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOVY3YjlmWmt4SnctbF9Hd3IzZzZSMWNpaC1YWTZkNVdEcnhyb256VFFZRTFiLWtULUdSREVQRGJmREhORmJQbFpubkY5NkViZEVfMEp5ck5GQWppTmhfTHVmWEU0eGlMTUN5NVhNTjlJNnpRR0wwVUQ1ZUlIODBCeDVvN3RuYkpKSzVCOGhfRFNCVUNJaERDYmZUaUlZMmxPWVJSOUdwTWhETmM4MGpVVUsxS0dHTU1tLXlzQ3dKS29FNTBJakFCT3F1WlJueWprU19KVGNDaFA4SjjSAeABQVVfeXFMT0lSMjYwM3VVcFQ0c3ZSdXczQldoczBwajdIWENEYU8zeVRIU1JtNnpJQUw3MklYbUNjWTVHS3Vfd3I4UzNzcmRGbDVXU0tDbG5jaGZ5MklUcENJc2htRFdZcGI1c0JIeGxfSFhQOEI3WHNrR21faHRZa21ZME5rVjVvVDd0MXlLVHlxNG43X0RYWDA2ZV9hUHlqeHVSQnRRbXdBQnFDRVc0YjRWQ2J3eWUzQmtaUjl6RmFVMEoza1dEUnZRWEZuakRhY0N6ZVNQSzRXQk5ZVVo2TlpnWmlwZ00?oc=5</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4114,17 +4114,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
+          <t>Llega el fin de polémica norma en los colegios: no podrán impedir el ingreso de estudiantes aunque incumpla... - redmas.com.co</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQa0Q4WmNWV1NnY0hxOGhTRDB4Q0tyNW9VLTNFaTBIU2ZIN1ZRQ1R3LURaR0YwSHplWW5ZcGxDUnNvbXJyNFdWQmNtc0FPUnMzdnhxMkExbTVTdzlOTmQ0RGp0UG11RWRrZldGcnNlM0xPclh2MkozOW4yallGNm5JU0xBVHBhYUlPU0cxamI4NHVNcEMzbnhHZGp0aFpvQ0QyOGJUbzRqd3k4a3ppNXpJSDUxNl9JODgwOXVTNFdFWWhfendmeVQwS192X0ktMnFKVHNJMlR3X3dXUXRDZExHcUFqQndNd2R5RWFtWVZSRGRlTGM1Y2NiUEhkaTjSAYICQVVfeXFMTnFIaUUyVDJYOU9aOHJ1MnZ4ZlFMN3JDdkxTR1NoaTI1Uko0MzVJbFI5aWdpaUhfdDlYeVFrRE1tV2JkX21SaFJCVEtMc3IxMG1EUWZwakZZSlRPZ2JiLUtJLXpwSHAxb2EtUy1nejFRcWRxdFBNX29KV0ExMzNHTUZZQXpGQXFwRHVfSG5sX0FpclBoSHhwa1RidndpMFoxT2JiV0hLb3plSmFUZ05UdmxVb1Q5QkFDUmV3VUR3eWlQTFI3OFdNSjh5NFEzNnJzQzBpdnZ4TVhUSU91T3BROEFLTThBZkVKbU1KUU0xUURDaG5ObWR1UC1GSlZ4N0JLdzhB?oc=5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4157,17 +4157,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>Alerta nacional: Niñas y adolescentes fueron las principales víctimas de delitos sexuales en 2025 - Publimetro Colombia</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Publimetro Colombia</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4192,29 +4192,25 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNDJzNU02WjZVRFlSSDlrcGRZQVh5eXowNnR3S0tJVUtwbE9Qb3h6dnN4UkhyTG92WWtrMVlIaXB4RXpFcHVFU2RybTRVM1JyaVJPU05WbDJEeHpiZ3JCTGw2WkRoY0JmM2kzTndoWkUwcVVmeDBKckhUSDlfMkhRMk1qeHJDd3JadWdTdndkZ1diRFJVdGdLcG9QbENyVmpZY3FxeG5qdEF0dWdqenZRQ25qNUdlMnpuem9MRTRsYXpZMzJFMVg3MWN3ZTl2OHk0eUdURzBqN25tS28?oc=5</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
+          <t>UNAD se consolida como la universidad con más estudiantes matriculados en Colombia - Noticias UNAD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Noticias UNAD</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4239,7 +4235,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPRXI2ZFJ2VWhVRVI2MVBYUG1mbEZ5YjQzR1JuTVZwQ0QyMS1UbXl0aFdxX3hvNGVzTm1rMjNPTDAwUXFCVmtZZk43WkdyZUd3cXZkMjdxdE1acTczWmRmZVNyT05vcjFUUW5oZmRGVFFpeFozZjc4T2Jnb0JzNDVOVHVyS0liak56NzVZUEQ3anF1TlFOVVdkYWhJNTU1RmhtckJGWGlTN2xzem5NZTA2WFZ2bmE3c25ScndCeTZ1OWpxYVlLd0NaQUg2a3lvdjlR?oc=5</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4247,17 +4243,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
+          <t>Indepaz advierte que cada 48 horas reclutan a un menor de edad en Colombia - Asuntos Legales</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Asuntos Legales</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4272,7 +4268,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4282,7 +4278,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzZRdHpsR0ppR0ZOcHpRQkM3X0xRYUpQQXZTYmNSMkVPVTY0eHEzeUNXVXYyNFE2SVpaNDNOSG1aajZrUWdFZW9KQU5xS1ZsWjAzaGt0Q2tuUHRzanNCMmQ5OW5CaVhuSmo1bFZsTGR4OEtrTHJGNFR1RlVJZm8yQzNvYThsdDFhQnNKcHZnTi1GN2pYbEFibzdkcV9VT0lsUUdldi10ZUVTRWd4bVdoOE1OcUxyMnFpRlB6OU9kNUxLVHFvcGc?oc=5</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4290,17 +4286,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ni los Andes, ni la Javeriana ni la Nacional: estas son las universidades que más ganaron y más perdieron estudiantes en los últimos años en Colombia - ELTIEMPO.COM</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4310,12 +4306,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4325,25 +4321,29 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNY3BFT0Fldks3R3kyOWVGMTN3YmJ1bzFFbkJJMDZFLW5UZ3NXS3JBa3c4ek5SMGpFNE9aS2Q4WWdxWHlfN0o3SlhMWmJBT2xBXzU0eU9nX01fOU5USkFMSExZazg5dHJHNWFWVFVqOVVQQnBpUmFBWmVLcW4wQjE5ZjhqNlRKU1pDNmtLT0NBMFFNdlp4NUtYOHhMM1NEVmxudW1vQUxEblpyNmRhRHJJU2o0cm9zaC04WUczZVlEeVlaQUtVdG9VaEkybWxyTERsZ3RDSkk3OV90NXBxanRqSXlrOXdIR3ZvWXRiUTV2VjFYRUJibFoxQXl4VjZyZXdNQ29NXzU1Um5wQ2c3YzRvRjNZSFNzX2d5T29uMUlwXzHSAaYCQVVfeXFMUFNQLW9PWGhtWUo1UHVwZ1k0eVkxNnlXLXJGUWwtN2VpSUZQZlFBZTNhMzNtN3JzMGF5eUhKSTE3ZXpPbEJ0X0g0Y0NkMTdJNTFJTWFYLXB4eXRHek9NSWRpRzlkWTZsNkxxckRuWXRjVTdxc3pQOEQwR0tIMmF4ZElLekdOOWlRNTJONGxId2FhNXdCVzhxZHZFM2xwVXZvRklDWXFlNEtTTExoa3hkQWE2dGVETU9NLUdXVHBiOVRzUFhwdWJlWUdyN2h5NnExLTdVQzRLRDdhaTNuMTVxSmp1T3pickQxRWNNQ2dDVHR5UlpFZ3dudVc3TDVsbEtTOWtVRXVZa1dlcENoNExOQ3BQNDhmcS12ZThFMElheGlBUlhxeU53?oc=5</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>🔎 Uribe alerta sobre 1.157 jóvenes asesinados en gobierno Petro. ¿Preocupación real o politización? #Seguridad #Juventud #Colombia - facebook.com</t>
+          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOLWFUcUtpZ0pFLUNNVXI1YzgzZENRM2tBVlV5Z01XTEsyZTZJQnBPTFFNeVlaeXpzaTRGZmZlN1YxOGVqMnIxaF81NDc3c0tlTkZldTRaREZwNmo2MmZla3lZbXhzYjhyZnk0bHgtM1ZuT3F2THU0ejVOd3o4eGtpWlpjLWhNVlNzX1lPdkJlWGVsNWFuZlVVRWNyZlJsclJYWHh5MExVOEtzSGRzNjl5VmhDeFRIWlhMYTd1RS1QUFhFbllKY2FmNXB6V2lmZ2lRLUdXU3NsU1BpWFpCWUo3LUZMcHE1bGNFZlIw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4376,17 +4376,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Maestra de español une estudiantes de NC y Colombia - quepasamedia.com</t>
+          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>quepasamedia.com</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOcktHWlBuS2xxaGNjWURCYmVSZ3pyNUxTSEVscTlFblUyTWROTkQtczU2UjdtOUlCb1dDMWdMbTIwRi12SFM5Y3RVTFVBbDZULU5lTk0zcGV0bG9IQUVlX0Nja05TeHpMaTJZLXRjbkhJTkx0Mk42X1I1OVg1bndidExIdTdpQUxodU01RmNjcWhvVllTS3JEd1M5aTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4419,17 +4419,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fundación Marina Orth celebra 20 años transformando la educación de miles de jóvenes en Colombia - Caracol Radio</t>
+          <t>Ni los Andes, ni la Javeriana ni la Nacional: estas son las universidades que más ganaron y más perdieron estudiantes en los últimos años en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZ1dFSEpLY2JtUkxkZzhsMlpxdE9HQ01QUHBGZ1RsM0U4NXFSQzlXV3FZWW51blk0QzdpVllrQVpmcHRxQzYxaXlpa3JpbHE5SHJhWjJRZGdHbnVleGhuV0VfQkdQbWZzVnAybmEzUXpFT0p3S3doMlJNR1g4b3Bib3ZaVWN0OE1LMU9fUi15czVHb0h1YnAwamtFRW5EamdMemdQTHBfcWVHUWU2ME9wMTFxTEpjS3BfeWRjY01hbzJZNmlCUGo2UzF4b9IB3wFBVV95cUxPM3ladUtkX3NFSHk5Y3RfbWhCZl9ENWRVWGNlWFlLUFpxOTlhRlNYTTAwM0FRRXU1TWVZTk1KRC1RNTlHcmpKd3lDaUttelRza2RGVmhxQWxuZ2VmZThMSDRsWVFONzFNdk15NnIxZ1FjMzVNbl83d2RzUFV2eUJvblppSmR6TWRoVVp5Q3BLWHdBbkVweU5WSWg1QVQ3M1htZnJOQ2VfTjZ4OXZhd2RoN3RheXFfWXBrSWlVWWx3allFZVlUVlRxY0hJd21PMkRMcll3RkctR2diS181UWg4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxNY3BFT0Fldks3R3kyOWVGMTN3YmJ1bzFFbkJJMDZFLW5UZ3NXS3JBa3c4ek5SMGpFNE9aS2Q4WWdxWHlfN0o3SlhMWmJBT2xBXzU0eU9nX01fOU5USkFMSExZazg5dHJHNWFWVFVqOVVQQnBpUmFBWmVLcW4wQjE5ZjhqNlRKU1pDNmtLT0NBMFFNdlp4NUtYOHhMM1NEVmxudW1vQUxEblpyNmRhRHJJU2o0cm9zaC04WUczZVlEeVlaQUtVdG9VaEkybWxyTERsZ3RDSkk3OV90NXBxanRqSXlrOXdIR3ZvWXRiUTV2VjFYRUJibFoxQXl4VjZyZXdNQ29NXzU1Um5wQ2c3YzRvRjNZSFNzX2d5T29uMUlwXzHSAaYCQVVfeXFMUFNQLW9PWGhtWUo1UHVwZ1k0eVkxNnlXLXJGUWwtN2VpSUZQZlFBZTNhMzNtN3JzMGF5eUhKSTE3ZXpPbEJ0X0g0Y0NkMTdJNTFJTWFYLXB4eXRHek9NSWRpRzlkWTZsNkxxckRuWXRjVTdxc3pQOEQwR0tIMmF4ZElLekdOOWlRNTJONGxId2FhNXdCVzhxZHZFM2xwVXZvRklDWXFlNEtTTExoa3hkQWE2dGVETU9NLUdXVHBiOVRzUFhwdWJlWUdyN2h5NnExLTdVQzRLRDdhaTNuMTVxSmp1T3pickQxRWNNQ2dDVHR5UlpFZ3dudVc3TDVsbEtTOWtVRXVZa1dlcENoNExOQ3BQNDhmcS12ZThFMElheGlBUlhxeU53?oc=5</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4462,17 +4462,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Plataformas digitales de movilidad refuerzan medidas de seguridad para adolescentes - Hora 13 Noticias</t>
+          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hora 13 Noticias</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBZSnJnMGRCcWhkUTNheVhzeEFtUEhBcGpibjVvQ1Z2bzZkN1FwQjR3MHRqN2N3dmx4M25YdmpROGhYVmtpOFhsZEJ2Y3B1cHRrWXBRZVNLdHlabl91dHRwQlVBYnZLUm1qMmtGU1B2TmUxcFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZ1dFSEpLY2JtUkxkZzhsMlpxdE9HQ01QUHBGZ1RsM0U4NXFSQzlXV3FZWW51blk0QzdpVllrQVpmcHRxQzYxaXlpa3JpbHE5SHJhWjJRZGdHbnVleGhuV0VfQkdQbWZzVnAybmEzUXpFT0p3S3doMlJNR1g4b3Bib3ZaVWN0OE1LMU9fUi15czVHb0h1YnAwamtFRW5EamdMemdQTHBfcWVHUWU2ME9wMTFxTEpjS3BfeWRjY01hbzJZNmlCUGo2UzF4bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZ1dFSEpLY2JtUkxkZzhsMlpxdE9HQ01QUHBGZ1RsM0U4NXFSQzlXV3FZWW51blk0QzdpVllrQVpmcHRxQzYxaXlpa3JpbHE5SHJhWjJRZGdHbnVleGhuV0VfQkdQbWZzVnAybmEzUXpFT0p3S3doMlJNR1g4b3Bib3ZaVWN0OE1LMU9fUi15czVHb0h1YnAwamtFRW5EamdMemdQTHBfcWVHUWU2ME9wMTFxTEpjS3BfeWRjY01hbzJZNmlCUGo2UzF4b9IB3wFBVV95cUxPM3ladUtkX3NFSHk5Y3RfbWhCZl9ENWRVWGNlWFlLUFpxOTlhRlNYTTAwM0FRRXU1TWVZTk1KRC1RNTlHcmpKd3lDaUttelRza2RGVmhxQWxuZ2VmZThMSDRsWVFONzFNdk15NnIxZ1FjMzVNbl83d2RzUFV2eUJvblppSmR6TWRoVVp5Q3BLWHdBbkVweU5WSWg1QVQ3M1htZnJOQ2VfTjZ4OXZhd2RoN3RheXFfWXBrSWlVWWx3allFZVlUVlRxY0hJd21PMkRMcll3RkctR2diS181UWg4?oc=5</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4553,12 +4553,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>Plataformas digitales de movilidad refuerzan medidas de seguridad para adolescentes - Hora 13 Noticias</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Hora 13 Noticias</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4568,22 +4568,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBZSnJnMGRCcWhkUTNheVhzeEFtUEhBcGpibjVvQ1Z2bzZkN1FwQjR3MHRqN2N3dmx4M25YdmpROGhYVmtpOFhsZEJ2Y3B1cHRrWXBRZVNLdHlabl91dHRwQlVBYnZLUm1qMmtGU1B2TmUxcFE?oc=5</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -4591,17 +4591,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Estos son los programas de educación superior que la candidata Paloma Valencia propone revivir para los jóvenes en Colombia - ELTIEMPO.COM</t>
+          <t>Fundación Marina Orth celebra 20 años transformando la educación de miles de jóvenes en Colombia - Caracol Radio</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQbFBTcllrWjJwdEJlbnJRN3Fpa2I5U2V6NTJiRWpfRlNqY0J0ODNPS2cyZEllM1c3V2pvUWtKWXM2endVdFR5WHhzQU5fdHZ5OTBfN3lXaFBqRzdHb0lhb3RON3ZJNTUyTXFDN3IzVE54d0hkMHNuUUNkbGhLanMxWUNkZG1YYzJ5dUNRMXhRbVZELUZLOG1ZMTl2eVUtcUxDMWdkYndPUWpVb25RUFFpb1NzWHk3cVh3d0JPSWhpYzBhVWFfaWp5YkxOUS1sWUNvXzBNWXhRS2VlcGt4YVRIX2VjYzk4RzBmeHBXVzBLOHFuQTJrOGRjc2Z4QXB6TS1oMEM4N0t3SXk5YzlOaEtPdS1iVVY4RGNILXpHVXlyNjV2TWfSAagCQVVfeXFMTmRvRUNOVGpWeUQxZUtaN1UtTjlOMjBLTmZpbHN5cmZVRzRpeFE1QlcyTFdjN0xtQVNuLVJzREdTc2ZYRWpVMFl5dXg2SG1HenR0NE9WNklvZkEwYk1VaTRPNTJHbC0xRG1lcDZfRG1XLW1sZHJLcVIzd1pSektGUUNTbFZFWlN6VWMxTF9rbGV0bC0tdUNmaWJpUjRSX1VUM0podFloLWt0dlI5WllVeDRyWV9PUGswZE5oV2dzbXRkY1FjeERRRkJzTkpVcVV1LVBhazVoQWtCbGJVSy1nUFZyQ0dacER5RG1aOWJmWFFHalpBUkxiV3RBZ045X05tWHd4Y2hoWGJDLS1EcDhYOHBnNGVlWEpiUGNwQmhoeUJ5M0NoTU9zSGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOZ1dFSEpLY2JtUkxkZzhsMlpxdE9HQ01QUHBGZ1RsM0U4NXFSQzlXV3FZWW51blk0QzdpVllrQVpmcHRxQzYxaXlpa3JpbHE5SHJhWjJRZGdHbnVleGhuV0VfQkdQbWZzVnAybmEzUXpFT0p3S3doMlJNR1g4b3Bib3ZaVWN0OE1LMU9fUi15czVHb0h1YnAwamtFRW5EamdMemdQTHBfcWVHUWU2ME9wMTFxTEpjS3BfeWRjY01hbzJZNmlCUGo2UzF4bw?oc=5</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -4634,17 +4634,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Inició el calendario escolar 2026 para los estudiantes de Cali establecido en la Resolución No. 4143.0.21.0. 06508 del 31 de octubre de 2025 - cali.gov.co</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>cali.gov.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4654,22 +4654,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNWlRsbG45VUtFQ04wZTVnTUpVVENFbU9kZkxiNTd4c3RPTUR3bmRJSF9ZR3k1U3NjN1BKN3RBbF9Nc0dqUzBmZDZweE1mOUZxb2s2REgyR19VZ1NiZi1VLUFUTTFyUUE1RDN6bDdKN1ZtNkQ4bjV6R3lJZTJtT2JRdzJWUGo2TTFDLVpEWkpGZWVYaWZBbTdQaFljSHVYOHhCY1JCdEVQOC1xSGlZWDN0QUJCY1BRVjFienNpNzEyOWpzc1ZfNG5fanItY3B1SkktMFZaRUxZcDQ0T0J3d3hUVFZ6c2hhbTR6YUdJZVhxanlBb2twY1JfSHhLNWxvSlNLN2dBLWlRd3Rvbm1FYmFQeEZlTEYwdG4zQzVJ?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4677,17 +4677,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Reconocidos colegios de Colombia no abrieron sus puertas en 2026 tras años de historia: se despiden de estu... - redmas.com.co</t>
+          <t>Maestra de español une estudiantes de NC y Colombia - quepasamedia.com</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>quepasamedia.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPUzRTZldvRkIxRnROTWFON1RxYjhpb0V3a0psY0lFYUVMYlVCb1dPSVUyRzlMOENOTENqeWF4MUtiT181bDJ1TnZuQ0dSYU1yZEljZVR1Qm5pYldRNjhVV0lndy1qSWpNZkFTWVBRY1I3ZHZCQjRCdW9NOUdmamhNNU5FcXJDVzlXZXJ3VEpCaVM5cU14Yzc1c0RpTVc2c3Q4SnhVbWx3TzMyUlN5SWdWbUJGblRlZzRaRExGdGtjMzI1M29KQ0hlSUF5cWZfY3dqdDd1Mk16WldZUHdScGo1WTl2NWctc3V0RlFwZzZqQTY5QllHSVV4M21iVHY5VTNfZlJJQWFVY9IBjAJBVV95cUxQa25SdDJjem94UFMzQWQ4VTZmVUVveTNZbEgyLWJVdmRCdEVXRHpWSjdHZ1JuUU9lek56eTZsVFhWeVQ5VHZudWI0ZXVqTENNdHhuWWlfdFYwNWE5YjcxWXR6b1k2aWNzLXBsaFpfOXZxcTJUNnRZVU43dWE1clBlVGd2S3gteXp0TUllWGhJRmJrSHBTM2ZfT2pQRGdSV2o5dlVibVdFSkViZ09NOVNweVJMRXFGS0pmb1QxdHBZNmtBX3lKdnk5dlZrdWc2VzBlX3MyLUpvcjVXeURabWZDX1ozT3J4Y2pmdGdKZFNJeHR4bTRPSi1XU3FxRFFzbl9jQTl6UUF0bWI1NThu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOcktHWlBuS2xxaGNjWURCYmVSZ3pyNUxTSEVscTlFblUyTWROTkQtczU2UjdtOUlCb1dDMWdMbTIwRi12SFM5Y3RVTFVBbDZULU5lTk0zcGV0bG9IQUVlX0Nja05TeHpMaTJZLXRjbkhJTkx0Mk42X1I1OVg1bndidExIdTdpQUxodU01RmNjcWhvVllTS3JEd1M5aTE?oc=5</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -4720,17 +4720,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>🔎 Uribe alerta sobre 1.157 jóvenes asesinados en gobierno Petro. ¿Preocupación real o politización? #Seguridad #Juventud #Colombia - facebook.com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4740,22 +4740,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOLWFUcUtpZ0pFLUNNVXI1YzgzZENRM2tBVlV5Z01XTEsyZTZJQnBPTFFNeVlaeXpzaTRGZmZlN1YxOGVqMnIxaF81NDc3c0tlTkZldTRaREZwNmo2MmZla3lZbXhzYjhyZnk0bHgtM1ZuT3F2THU0ejVOd3o4eGtpWlpjLWhNVlNzX1lPdkJlWGVsNWFuZlVVRWNyZlJsclJYWHh5MExVOEtzSGRzNjl5VmhDeFRIWlhMYTd1RS1QUFhFbllKY2FmNXB6V2lmZ2lRLUdXU3NsU1BpWFpCWUo3LUZMcHE1bGNFZlIw?oc=5</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4768,12 +4768,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IEEE. Del campo de batalla a la construcción de la paz: el papel de las autoridades en la desmovilización y reinserción de las niñas soldados en la Colombia del futuro - Ministerio de Defensa</t>
+          <t>Estos son los programas de educación superior que la candidata Paloma Valencia propone revivir para los jóvenes en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ministerio de Defensa</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQQ3hUMDdhc1ZEcHp1a0dtb3dTbE13d1duR3pUX0dWLTJqbzZfYmlIYl9Id2M3Yy1CdmNtUk1qam1xRnc2NTNJRDk3UXF2TzJGYVNWY3YwXzRYSVlDZ05uQ1c4blY4V2d6XzNzc2JRckdJVE0zSWNnNXJPY3NhODN4b1hYcFhiQUl4UGJ1VkNDWGIwZms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQbFBTcllrWjJwdEJlbnJRN3Fpa2I5U2V6NTJiRWpfRlNqY0J0ODNPS2cyZEllM1c3V2pvUWtKWXM2endVdFR5WHhzQU5fdHZ5OTBfN3lXaFBqRzdHb0lhb3RON3ZJNTUyTXFDN3IzVE54d0hkMHNuUUNkbGhLanMxWUNkZG1YYzJ5dUNRMXhRbVZELUZLOG1ZMTl2eVUtcUxDMWdkYndPUWpVb25RUFFpb1NzWHk3cVh3d0JPSWhpYzBhVWFfaWp5YkxOUS1sWUNvXzBNWXhRS2VlcGt4YVRIX2VjYzk4RzBmeHBXVzBLOHFuQTJrOGRjc2Z4QXB6TS1oMEM4N0t3SXk5YzlOaEtPdS1iVVY4RGNILXpHVXlyNjV2TWfSAagCQVVfeXFMTmRvRUNOVGpWeUQxZUtaN1UtTjlOMjBLTmZpbHN5cmZVRzRpeFE1QlcyTFdjN0xtQVNuLVJzREdTc2ZYRWpVMFl5dXg2SG1HenR0NE9WNklvZkEwYk1VaTRPNTJHbC0xRG1lcDZfRG1XLW1sZHJLcVIzd1pSektGUUNTbFZFWlN6VWMxTF9rbGV0bC0tdUNmaWJpUjRSX1VUM0podFloLWt0dlI5WllVeDRyWV9PUGswZE5oV2dzbXRkY1FjeERRRkJzTkpVcVV1LVBhazVoQWtCbGJVSy1nUFZyQ0dacER5RG1aOWJmWFFHalpBUkxiV3RBZ045X05tWHd4Y2hoWGJDLS1EcDhYOHBnNGVlWEpiUGNwQmhoeUJ5M0NoTU9zSGg?oc=5</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>En Japón estudiantes colombianos podrán estudiar lengua y cultura de ese país con becas de intercambio del ICETEX y el gobierno del Japón. - icetex.gov.co</t>
+          <t>Reconocidos colegios de Colombia no abrieron sus puertas en 2026 tras años de historia: se despiden de estu... - redmas.com.co</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>icetex.gov.co</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOR3VLZkYwT0EzdC1YZkZFSktLdlFzRGZfVDQwWlE2Vlc2SkY3WmJaZkxvLXU3dVhZd0l5VHl5ZVRwMkw5NGdpTDdYODYyc096ZnhTNkd1V3NGNkdaZjZxM3hicHg2V3kyU0dvLVV0bkpRTWtQZTQ5eGtOY3BXNWxpSnhCZWJtWmtZelFKSlJfUmJfYmxHdlRKY2F0aUxrNXhRQ3MwREtFeHdzcFd3eWgwV1RMclVNckxTSm5qSjVwMVZzS0tEYzlleTFlalhlRzlOLUFmSjRpbTZWLXJsMlNzQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPUzRTZldvRkIxRnROTWFON1RxYjhpb0V3a0psY0lFYUVMYlVCb1dPSVUyRzlMOENOTENqeWF4MUtiT181bDJ1TnZuQ0dSYU1yZEljZVR1Qm5pYldRNjhVV0lndy1qSWpNZkFTWVBRY1I3ZHZCQjRCdW9NOUdmamhNNU5FcXJDVzlXZXJ3VEpCaVM5cU14Yzc1c0RpTVc2c3Q4SnhVbWx3TzMyUlN5SWdWbUJGblRlZzRaRExGdGtjMzI1M29KQ0hlSUF5cWZfY3dqdDd1Mk16WldZUHdScGo1WTl2NWctc3V0RlFwZzZqQTY5QllHSVV4M21iVHY5VTNfZlJJQWFVY9IBjAJBVV95cUxQa25SdDJjem94UFMzQWQ4VTZmVUVveTNZbEgyLWJVdmRCdEVXRHpWSjdHZ1JuUU9lek56eTZsVFhWeVQ5VHZudWI0ZXVqTENNdHhuWWlfdFYwNWE5YjcxWXR6b1k2aWNzLXBsaFpfOXZxcTJUNnRZVU43dWE1clBlVGd2S3gteXp0TUllWGhJRmJrSHBTM2ZfT2pQRGdSV2o5dlVibVdFSkViZ09NOVNweVJMRXFGS0pmb1QxdHBZNmtBX3lKdnk5dlZrdWc2VzBlX3MyLUpvcjVXeURabWZDX1ozT3J4Y2pmdGdKZFNJeHR4bTRPSi1XU3FxRFFzbl9jQTl6UUF0bWI1NThu?oc=5</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -4892,17 +4892,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ley aprieta a los estudiantes por el uso de celulares en los colegios: profesores podrán revisar el disposi... - redmas.com.co</t>
+          <t>IEEE. Del campo de batalla a la construcción de la paz: el papel de las autoridades en la desmovilización y reinserción de las niñas soldados en la Colombia del futuro - Ministerio de Defensa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Ministerio de Defensa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOZmRINGh0SkZxTDRTeWVFSUswUnhZNGxjZllYYURKbWFkVHhMSnZMd1VMamRUTzBnYmVOSWY5Q3lxaDNmOGd2T0VmeTRyZm9UZ1VHRTJRWTRLei1tbXZ5VUhKMFRRbmNrVTNIc21Ia2QwOUkwS1RCM29faVZoNHMtS084X3R4RTdJcGtjb2ZZT0RuOFNkMkZ1MzRCQXN3Y1BvcXkzNHl0dDVHUHM3dHBVTHpWLTNoTnRVVHcwVHJQQ0QxbmJKQVZST29ReDhFRVZvbUU4N1lJYXRpVWdRSHNFbjFxT0libDRTeUtWMXVwRUY3MlprRWJGajNDQ2N4MFlVeUZUVVhB0gGLAkFVX3lxTE5lazJSTmpvZjRob3FrYTgtZE12SVZrYjk1U0tRdjQxOXNfbzQyRlF6RFduNU5CdjdON1hsWExlOWZRU1lzemdnNUt4eDN6TU8tMTV6WUNaSHdQRTdBYUdQQ1BfZlU5WFF4UzE1T1h1VENhXzdiMTVEWTZTSDJvdXRFNFJSMlAyZE51emx5WU8yRUZDd0FJTmFVbjhUV2NYSkVMWGJ6Z3BFOEMyZEFhMjFZcDlpb2RQajF2ZUltWV9FYUM3MU9VeWJyVVZMMllWeGNKOVktTUhfSlExWTVBMmpwSlN5M3VqWGFXZ1prVWlDdUd1MWd5bEdxeFpwUTllazJ1bmdkVUF5UGJqWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQQ3hUMDdhc1ZEcHp1a0dtb3dTbE13d1duR3pUX0dWLTJqbzZfYmlIYl9Id2M3Yy1CdmNtUk1qam1xRnc2NTNJRDk3UXF2TzJGYVNWY3YwXzRYSVlDZ05uQ1c4blY4V2d6XzNzc2JRckdJVE0zSWNnNXJPY3NhODN4b1hYcFhiQUl4UGJ1VkNDWGIwZms?oc=5</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -4935,17 +4935,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>En Japón estudiantes colombianos podrán estudiar lengua y cultura de ese país con becas de intercambio del ICETEX y el gobierno del Japón. - icetex.gov.co</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>icetex.gov.co</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOR3VLZkYwT0EzdC1YZkZFSktLdlFzRGZfVDQwWlE2Vlc2SkY3WmJaZkxvLXU3dVhZd0l5VHl5ZVRwMkw5NGdpTDdYODYyc096ZnhTNkd1V3NGNkdaZjZxM3hicHg2V3kyU0dvLVV0bkpRTWtQZTQ5eGtOY3BXNWxpSnhCZWJtWmtZelFKSlJfUmJfYmxHdlRKY2F0aUxrNXhRQ3MwREtFeHdzcFd3eWgwV1RMclVNckxTSm5qSjVwMVZzS0tEYzlleTFlalhlRzlOLUFmSjRpbTZWLXJsMlNzQg?oc=5</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Posesionados 51 consejeros de juventudes en Santa Marta - Caracol Radio</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNcnFWMDE5UEt1ODh4cm9JS3lZdlpIOUptaUY5U25tUWVxd25NTGJiNFA4WTdyVUNvRzlob3M4bVpOczc5czVRaXA5V1RQc0h6SXpRUXVuRTlXSjJveGNJbWw5ZDRYUzRoLVQ1UjB1YXVqZzBvUlFyb29Oa1JVT3h4N1pFc1hfNExPUmFVTml6QlB0eEJW?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5021,17 +5021,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Inició el calendario escolar 2026 para los estudiantes de Cali establecido en la Resolución No. 4143.0.21.0. 06508 del 31 de octubre de 2025 - cali.gov.co</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>cali.gov.co</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNWlRsbG45VUtFQ04wZTVnTUpVVENFbU9kZkxiNTd4c3RPTUR3bmRJSF9ZR3k1U3NjN1BKN3RBbF9Nc0dqUzBmZDZweE1mOUZxb2s2REgyR19VZ1NiZi1VLUFUTTFyUUE1RDN6bDdKN1ZtNkQ4bjV6R3lJZTJtT2JRdzJWUGo2TTFDLVpEWkpGZWVYaWZBbTdQaFljSHVYOHhCY1JCdEVQOC1xSGlZWDN0QUJCY1BRVjFienNpNzEyOWpzc1ZfNG5fanItY3B1SkktMFZaRUxZcDQ0T0J3d3hUVFZ6c2hhbTR6YUdJZVhxanlBb2twY1JfSHhLNWxvSlNLN2dBLWlRd3Rvbm1FYmFQeEZlTEYwdG4zQzVJ?oc=5</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -5064,17 +5064,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>El verdadero poder de la juventud se construye desde la educación inicial: Colombia reafirma su apuesta por la educación como derecho a lo largo de la vida - Ministerio de Educación Nacional</t>
+          <t>Posesionados 51 consejeros de juventudes en Santa Marta - Caracol Radio</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Santa Marta</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgJBVV95cUxNeHU1SkQzQW85ZV9qM1doX2oyREFMdHZMOWYtWDl4dlliQzFvWVA2WWRZeWliUXpENWo5SU1BTUdyZmpSUndBUnNHczBDYmU1YTFrZUhIUVVUenYtTzM2a1JBbzZRZ1lRZmE2amhrQlNWMmw4QjVqcGo5dnozZENRZ2k3Qy1nUzBMNS1ZdWZObXhyd1FDejJOeGd3TVVGSmYxZDBSWE8xTEthbmtsWkRkS3cxT0lpRHlaTkJqclI4U2k1ejhzajAtRUY2T3pZdjBVUWlmdmVWM1VSUGlhbzhtRU9Md0xXYTljeTF6UWJ6R1VOcVh2WWZTWjdxejV6cDQ3NjNEN29NTU5nU3BnZ3ZpV1hZRWlaN21OTnVRdi0zSU5aYTNfZEVtaC1pNi1yZG1zdnBsM3JmWEYwd1hMY3NxMnM4WVdSQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNcnFWMDE5UEt1ODh4cm9JS3lZdlpIOUptaUY5U25tUWVxd25NTGJiNFA4WTdyVUNvRzlob3M4bVpOczc5czVRaXA5V1RQc0h6SXpRUXVuRTlXSjJveGNJbWw5ZDRYUzRoLVQ1UjB1YXVqZzBvUlFyb29Oa1JVT3h4N1pFc1hfNExPUmFVTml6QlB0eEJW0gGoAUFVX3lxTE9EMHhyaTBzdjFKSW5vbjY0X1BfV3FnNHlaSUFsaXJXSW5SVzg2aTIxMF9ORFhZX1ZHZU9WRmloSmJNeFFTUFNNck1ITDlGZUIzVXk1UWlLUnJsVWxjaHpRMTMweHVENi0wVk11cUhkNXp3Tzh5RUNHWVN0YU56RlpDamlLcDJ1cWF5YnRuTEZNeS11S0MwUmFHOWZ3MGFBYWxCekxIcmNodQ?oc=5</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5107,17 +5107,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ponen freno a polémica norma en colegios: Ley prohíbe que impidan el ingreso a estudiantes que incumplan re... - redmas.com.co</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOVzlCMkZDa0JoRmRTQWgzRXM0SUY1ZlBNdGJRNFdoRF9UVGxTd20wbHNMWFJ2YmpSSndHY2QydW9QYzRRQVZyeG14eElnc29xZDlMTTFuYjdTa3hNNUxhX1E3OWEzX1h1SloyWkJFbG02V0N6WFVYdHlDMEthVTNEVFVKWVVfb3c1MEF3dGIxSmhBQUt2Z3pQU21VdnVuaTJlTHB6dEhmekdOaVFZWkxKQXZDSlNkWGozbU9Gc2g3YWpLbS1Xd3p6X2pjaDhSejJBR0ZZdVU3LTM3VDVxS2tFRVhMQkFwNXRJY0dJLUhNRkdCU3lxSXB6b2pReWtvd9IBgwJBVV95cUxPejJlVWNtREtHdllUakMyUm85WHh2NHpXMVk0NVh0S3FTYmk4S242MzlWcEtZcDZQbGFuMDNIVENWaW9aNFpTaExNU2d4cU5OQnN3X3FlRW9xSzRpc2twNEdqc2NWcTZsRTdfVF94elB6cnNPc3U5V1p2TmhDa0JQM2ZFUDQxbDU4d0d1bkpnSlhWT3p2Q2pzbm5OeElFV0JydzRjaDZqVERJRk91TG1rZFVMT0hDQkhNTmtCMVZrY3VSc0o0YzNwTHEyUlJMVlJLZDh1WGZhM1ZOWWdUbHRkeWhKT0VfTWFBWk9STDBJZlRwN2VabTVkdnhwWW9KMWxMSEtj?oc=5</t>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -5150,17 +5150,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Causas de la crisis colegios privados en Colombia - Radio Nacional de Colombia</t>
+          <t>Ley aprieta a los estudiantes por el uso de celulares en los colegios: profesores podrán revisar el disposi... - redmas.com.co</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Radio Nacional de Colombia</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQQ3pvU201R2JPZEJPWTQyNzZSdTJJbV9jM0IzbUFBYzZxcEp3Y1U2T0xoNGJYMk4xRkY0Uk9ybUtSZTllX1dxVFc4b2tKMVBqWktiTjh5THhoeC1GUWJpZkh4RnVZQVVOeDBwWGtyTVBCSjBsQ1dxZWxRMjRaT3pkcDZKMFhaWTRSMS1JUjlKZy1kOTM2TllVV0NQMjJZMTVN0gGkAUFVX3lxTE5Nb3ZabTd1SnBUT0l5alV6UEdnV1ZCaDdnVWstTXRYYnJseXpPMDhMM0VIVDNGRHd4cWpnQkx6SlVhek9XOGhWUndJeGZPbUI0MzNQY3BxOXFMb1cyVENMYzB6a3liYlFnVVRFZ3h4bjlSRVZ5TU5DbzNqc2RZVURBYkZYT3d0NS1jWWU0ZmJGNk8tSWRKRkJUZWpGRmczLUJzRTNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOZmRINGh0SkZxTDRTeWVFSUswUnhZNGxjZllYYURKbWFkVHhMSnZMd1VMamRUTzBnYmVOSWY5Q3lxaDNmOGd2T0VmeTRyZm9UZ1VHRTJRWTRLei1tbXZ5VUhKMFRRbmNrVTNIc21Ia2QwOUkwS1RCM29faVZoNHMtS084X3R4RTdJcGtjb2ZZT0RuOFNkMkZ1MzRCQXN3Y1BvcXkzNHl0dDVHUHM3dHBVTHpWLTNoTnRVVHcwVHJQQ0QxbmJKQVZST29ReDhFRVZvbUU4N1lJYXRpVWdRSHNFbjFxT0libDRTeUtWMXVwRUY3MlprRWJGajNDQ2N4MFlVeUZUVVhB0gGLAkFVX3lxTE5lazJSTmpvZjRob3FrYTgtZE12SVZrYjk1U0tRdjQxOXNfbzQyRlF6RFduNU5CdjdON1hsWExlOWZRU1lzemdnNUt4eDN6TU8tMTV6WUNaSHdQRTdBYUdQQ1BfZlU5WFF4UzE1T1h1VENhXzdiMTVEWTZTSDJvdXRFNFJSMlAyZE51emx5WU8yRUZDd0FJTmFVbjhUV2NYSkVMWGJ6Z3BFOEMyZEFhMjFZcDlpb2RQajF2ZUltWV9FYUM3MU9VeWJyVVZMMllWeGNKOVktTUhfSlExWTVBMmpwSlN5M3VqWGFXZ1prVWlDdUd1MWd5bEdxeFpwUTllazJ1bmdkVUF5UGJqWQ?oc=5</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5193,32 +5193,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Estados Unidos reclama a Colombia ante ONU el incremento de reclutamiento de menores de edad - El Espectador</t>
+          <t>Posesionados 51 consejeros de juventudes en Santa Marta - Caracol Radio</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Santa Marta</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPVFRDQXk2WVcwQVhLTmljT1B4akFGM3ozQlBvc3QyOHJua1BfT1hxRnFJY212eFowWTVTdVBmTHN6d2REcXc5VGVuUmw1LWsxNWxOeW82UzBPaVQ3azZfQVNSb0pUTHFqTHdGVWJXS2Z5YmVSbXZJSXd4dzdTamNXdUtqMTRwVDV4MF9acHJFX1pTZ19NVVNvLWdNb1Y1d0FzZlN2dWVMamlvVlNCN01ZS2MxZDh1M250d2tsNEVpc2NYRUJXcE9KYk0yd1FHU3BiNUtFOENRdWZ4ZHdsR0l2cFRFMEpKTGYtaUk4dmhuRjhyaVU3RDYxbUpCUzjSAZACQVVfeXFMTmxJSVphakhMc1dSdUhqdDJFZW00OTIwT0NRNndiZGNtLWROVW1NZFFHWHhTMzVYb3N6aHRBV1NObF94cEVSeHZMOWpPTW1oVXdGeDloRU9uSWpIUXNldU1qY2lUM3dNWnhwMUNESWVTUy1SNGYzZkM0Nk1ORE9zQkNkdzc1MnJpUldVTnhKeUsycE1rcGdwMi1SN3F4bkZUdHZGNUJWT1RLeS1ZMFJUVkdmOXpHcnpId0N2QW9oOEVsbkYyVU9xbUtnTEVBdW1kNnlOY2wwVGVUY1dCc3N5WkQ5ZTBRUTFKSndYUU4zYVU2aUc1cUlsLUt4d3B6OTZ4Xzl0cC0tMFAwQ0hwM2JWUC0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNcnFWMDE5UEt1ODh4cm9JS3lZdlpIOUptaUY5U25tUWVxd25NTGJiNFA4WTdyVUNvRzlob3M4bVpOczc5czVRaXA5V1RQc0h6SXpRUXVuRTlXSjJveGNJbWw5ZDRYUzRoLVQ1UjB1YXVqZzBvUlFyb29Oa1JVT3h4N1pFc1hfNExPUmFVTml6QlB0eEJW?oc=5</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -5236,17 +5236,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Estados Unidos hizo llamado de atención a Colombia ante la ONU por aumento de reclutamiento de menores de edad:“Dudas sobre impunidad al terrorismo” - Infobae</t>
+          <t>El verdadero poder de la juventud se construye desde la educación inicial: Colombia reafirma su apuesta por la educación como derecho a lo largo de la vida - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNNFJLRzNtTGZtU1ZCaVUxbGR1QUhBMzV5eFVUT2w4TWZVZnNfYmNMX1IydEVyYnhGT3ZJcDZMaG85R0RUUU9LaEsxT0hyYTFEcy1lNmVTMTA4TWlTbzJ2NmJNbTdxTXZQeUVsczJGMTdSZVlYVHlwblhqeG53UzZ5QkhsMVFyTWRORUQtOUNJMXFBSzJiNkZGQjJSZ1lvcWdfUHFTN1duQjJvcWVyMEZIZE01OGMyakhIQk5WbkROZlpIaDg5UHJRLWdEWVVSRlN4N21hNlhvemlncnlCZlNsM1BvYlJrX2hnUEpmREFCT1pzWS14YmtLMzNHWk1ndnN1NVE5YUdaajNmelBLZEViNEFHNHdjbFhqZEHSAbQCQVVfeXFMTXBsTHJ3d1N1RXh4WFdBdjAtMVFYcEJTV2xwd0xHZERGQVlHNXNvcW5hYmdpN09Wd1ljMjR4RjNSRWMxMl8xMmN5TzN2XzQzUDhCdlJ2WjdNSklzMG1yRzI5YnRnRDFhYWo3Wi1wOEdNbHE4UElzU2FGN3Z2b29XX0Z0bXBDczQzbE1oRE9zVjk1VG9OMzZSNlhsbjlFZUp4em84bGxJSTJyRG8yOWlvUkxPZkhVT0picHVCXzRRX2dhY1VTTWlJcUFYRnVBQzV0ck10YkktYXVpSE5uNm40U1lneGt5c0p5VUNzYnl0NEpqWmVLUE5UcWxOT1BJbnFDZmJRSG9XaTYyMXhqT3dhekhSUDBLSnh6dGxBNFNNYzktYTdZMmxmZm13bXhDd2x3Y0tvWkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgJBVV95cUxNeHU1SkQzQW85ZV9qM1doX2oyREFMdHZMOWYtWDl4dlliQzFvWVA2WWRZeWliUXpENWo5SU1BTUdyZmpSUndBUnNHczBDYmU1YTFrZUhIUVVUenYtTzM2a1JBbzZRZ1lRZmE2amhrQlNWMmw4QjVqcGo5dnozZENRZ2k3Qy1nUzBMNS1ZdWZObXhyd1FDejJOeGd3TVVGSmYxZDBSWE8xTEthbmtsWkRkS3cxT0lpRHlaTkJqclI4U2k1ejhzajAtRUY2T3pZdjBVUWlmdmVWM1VSUGlhbzhtRU9Md0xXYTljeTF6UWJ6R1VOcVh2WWZTWjdxejV6cDQ3NjNEN29NTU5nU3BnZ3ZpV1hZRWlaN21OTnVRdi0zSU5aYTNfZEVtaC1pNi1yZG1zdnBsM3JmWEYwd1hMY3NxMnM4WVdSQQ?oc=5</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -5279,12 +5279,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad - Infobae</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQSmlvdlUzeHJlOVhEOTBjQVN5TlhCWkNmaUNEQnczelA1YWVHXzJ1ZHZkM2JKcWdCNzdKYkViRnQyaFpldFB5MGQ4SU54WDVoVGNlbWdRQzJhM0hvRGFaaF9MR3lxUWhSbGJUTFNKcHVmQjJ4MjlibnNuaGNVcXVaVE1aa0stdmFzYmxvTnlmc1hwMFdQUDJGVkVuS2Y4NTgydk9zQlZsU2l0OXA2NjUzZnk3SnpDOUx6RjItNE9EYWlscDBlR19XV1pIdEgxVF9XT2RWMHItMmdEeHlqdmdfYzh1X0dIT2lLNjlvR2RsRWhDZ25iMWVGbTNzaUtQZy1STHfSAZwCQVVfeXFMTXRiNGt6QnJSZDJ3NXItNWZ1enZWUkZmMEhPSm5pNWpLT2hSLXdLWnBzOTFLcVdzM3Q2SWZ1UWpzdU13NjVDNUR6S2o5N1BhOWdlYWEyVDh2bGVqTE1LR19KUnFaUFJEVWZhTlZ4Z3RwV3J2U1I3VmtReVVaTGxMTldfeEZmclhOby1iaFpVU2ZjOUJqRERwNFlMNVdzbDVFX3BQWmg1YjNhY0hrQWJ4UW53Z0lRTWlLWFEyWm5Jck5qX3ROSXVqZUxtTHM3WDk2TDJzUDJUN21VTjkxamZMRUd2Unl3emJEaGJxejJPdFViSkNWbTRudzNRUmE4bFg4a1JaLURLa0lQakk0U0kyRFFwV0ZlRHBtZ3VNc1Q?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5322,17 +5322,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>⚽ Santa Fe propone torneo sub-23 para dar oportunidades a jóvenes y futbolistas sin club. #Fútbol #Juventud #Colombia - Facebook</t>
+          <t>Ponen freno a polémica norma en colegios: Ley prohíbe que impidan el ingreso a estudiantes que incumplan re... - redmas.com.co</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxObFJ5amljVE9jSVpXcTh3b1pqaXNPWWp3QkFjZkFPT25VRk9KbDczbno3VFFlZnZkc2RURl9PdXVxOXNCV2lYdGZHYmVmYmoyLTl6TWJsNjYzLVJwOEoyWmM0TU1zYTJld24wdUJTcHE5RzhXdlk5VTE4WVpWQWpYS3R5REo4aURzZ0tkMTA2WGd1Y1dQdWFrTy1zZHZueWhlb1gwYXc0dWhjZ05Oc0tlQVpCR2pta2E4MU1vTTVFUW0yRDZDcWN5Z3g2RUYtUjdfWFdDc3Z1czBRMkYzVFcwV1pUUEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOVzlCMkZDa0JoRmRTQWgzRXM0SUY1ZlBNdGJRNFdoRF9UVGxTd20wbHNMWFJ2YmpSSndHY2QydW9QYzRRQVZyeG14eElnc29xZDlMTTFuYjdTa3hNNUxhX1E3OWEzX1h1SloyWkJFbG02V0N6WFVYdHlDMEthVTNEVFVKWVVfb3c1MEF3dGIxSmhBQUt2Z3pQU21VdnVuaTJlTHB6dEhmekdOaVFZWkxKQXZDSlNkWGozbU9Gc2g3YWpLbS1Xd3p6X2pjaDhSejJBR0ZZdVU3LTM3VDVxS2tFRVhMQkFwNXRJY0dJLUhNRkdCU3lxSXB6b2pReWtvd9IBgwJBVV95cUxPejJlVWNtREtHdllUakMyUm85WHh2NHpXMVk0NVh0S3FTYmk4S242MzlWcEtZcDZQbGFuMDNIVENWaW9aNFpTaExNU2d4cU5OQnN3X3FlRW9xSzRpc2twNEdqc2NWcTZsRTdfVF94elB6cnNPc3U5V1p2TmhDa0JQM2ZFUDQxbDU4d0d1bkpnSlhWT3p2Q2pzbm5OeElFV0JydzRjaDZqVERJRk91TG1rZFVMT0hDQkhNTmtCMVZrY3VSc0o0YzNwTHEyUlJMVlJLZDh1WGZhM1ZOWWdUbHRkeWhKT0VfTWFBWk9STDBJZlRwN2VabTVkdnhwWW9KMWxMSEtj?oc=5</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -5365,27 +5365,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>¿Qué está pasando con los colegios privados en Colombia? - Ministerio de Educación Nacional</t>
+          <t>Estados Unidos reclama a Colombia ante ONU el incremento de reclutamiento de menores de edad - El Espectador</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPR1N5MGEzQ0xqcVF5cVd3TUJXVGJ0Um9kSElKTXVWbDc4Q1FEdTBrbjI0TmJ5OFFNZFRseXQwYmhEYTNvM2dNWUlfaU1WMnFEb0luTEdadTJ4VmFuZ1h1eHM0T0ZPQ1BGRlhlQlpEZGJtRklRbXhtVE8xMVVFUGZESjRIYXBVVF9DTUJOcVRMZExSSkZVbmdTQzVOZG01aUIzT1VjamFsUFJrZVZ4aHFJNlZEUWNqVHBiZUpQSjZ4NHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPVFRDQXk2WVcwQVhLTmljT1B4akFGM3ozQlBvc3QyOHJua1BfT1hxRnFJY212eFowWTVTdVBmTHN6d2REcXc5VGVuUmw1LWsxNWxOeW82UzBPaVQ3azZfQVNSb0pUTHFqTHdGVWJXS2Z5YmVSbXZJSXd4dzdTamNXdUtqMTRwVDV4MF9acHJFX1pTZ19NVVNvLWdNb1Y1d0FzZlN2dWVMamlvVlNCN01ZS2MxZDh1M250d2tsNEVpc2NYRUJXcE9KYk0yd1FHU3BiNUtFOENRdWZ4ZHdsR0l2cFRFMEpKTGYtaUk4dmhuRjhyaVU3RDYxbUpCUzjSAZACQVVfeXFMTmxJSVphakhMc1dSdUhqdDJFZW00OTIwT0NRNndiZGNtLWROVW1NZFFHWHhTMzVYb3N6aHRBV1NObF94cEVSeHZMOWpPTW1oVXdGeDloRU9uSWpIUXNldU1qY2lUM3dNWnhwMUNESWVTUy1SNGYzZkM0Nk1ORE9zQkNkdzc1MnJpUldVTnhKeUsycE1rcGdwMi1SN3F4bkZUdHZGNUJWT1RLeS1ZMFJUVkdmOXpHcnpId0N2QW9oOEVsbkYyVU9xbUtnTEVBdW1kNnlOY2wwVGVUY1dCc3N5WkQ5ZTBRUTFKSndYUU4zYVU2aUc1cUlsLUt4d3B6OTZ4Xzl0cC0tMFAwQ0hwM2JWUC0?oc=5</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -5408,17 +5408,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Más de 220 menores de edad fueron rescatados tras estar abandonados en Bogotá en 2025 - Caracol Radio</t>
+          <t>¿Qué es Uber Teens? La opción de viaje para jóvenes suma nuevas funciones de seguridad y ya supera los 186.000 trayectos en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5433,17 +5433,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOalk3YjJZcTBJakNTakdzSVVMcWZOWmFVM09BaWpMWFVUYnMzVER4QzRNTmNJUURGUWZ6Mmw2YjhMcDhPenR4VzRaQXlpUTRUc3pUcnhjUkxCZVZ4b0REQ3lBZnU5d0pYWV9CNWd0Q29ZLXNpWWxMeTl0WG4tNmNTT2xNYW53OUIwNXhQUnlIQXNSWWxEcUt4Yk15UWZwa3IzZnBBbW5vZ1VBYlp6dmZWR1FaZWE2azFHSVk3dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxQVW1feUZub2lVOGJPZGZMUkN2RGtVWWVTbUNWRDZzVDdZNnhnY1RJREpOTHlNaFc1dUFCYjhYS0R2eXkwUDRzMVB1Q1IybUZPRk5hSXBJejZFNkRIMFhlZUZvVzl4Y0trcXFyMEhOMUlaX1EwWVB5eHpuclAtSmVLdmU0TWNvUjgtcXFVMERFRUlXY1JTbm1hRzNOM21ER0pKZWRlWmpiTXdSQkhxb01JeTEwZmpDakZ1YXVQYmoxMUJOMGlMWDRVYUVtR3BqRmNSUnF0cWdUUFRPR2Y4MFJ0NkVXSXlLLXZXaXluZ1NCXzg2UUdZM2owVVRHbG0xOU1LamZ5bDM1UmJ1WWgzSFM3QVhjRlRyUUnSAZwCQVVfeXFMTlFibFFIZVp1S2h5cFVPMTAwbG0wSVRJZDlWX29WZU5QWU9feXZGYmdmbnNKRHd1Sk56NFlLZmIzUUJyZG0tY05xRXI0dVo1QVlJdzNES1dITUlfSHVSbTY5Qmx5X0Zpa3Z3ZFpzZlBOUlFYZ0NNSXRteTg2a2E3eUhnTUFmWDlUZ0ZKSXUtamNZWUJ2S1o4bjlYZ3R6UWtHbnpRY0VFSzY5clJwSjZqZkpvb3UyV0FaczVrRHZ4SElvdWFoeUJXYzF5ZEwzVVBOY29JVmtTNkQxT0dSREdlNFlRakdhRTdweHBGQThMWTF6QnF4N29SeUcweFdEa1JLekk3OWhBLXRWY1h0TVl0MXIwOU16SnlHWHRRZVc?oc=5</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -5451,17 +5451,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Se acaban los castigos para estudiantes en colegios: Corte Constitucional pone contra las cuerdas a los rec... - redmas.com.co</t>
+          <t>Causas de la crisis colegios privados en Colombia - Radio Nacional de Colombia</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Radio Nacional de Colombia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPeUdyQjFZLUJGUHR0WTBwSldBTGJtRHFmU2NJNkJWT0tBMzlNTFJ6RWpTekQxRVUyX2phUHE4dzFwbTBQZ3Q3SHE1QllpQUN0Q1BJdGpVQjVGWmNrX25wVGZhLUhfei1weWVPbnloMEczS0Y0YXNUN1otS1MxQVQxaE5SMldWdkVvV2xvTEx5VlY3V25WNmYyVnFsM1ZZcFUwb2dYa0FBbkcwUjZGempNelNEUFdsNk9BbFNHOVVfRUR2UEs5RFd1OFJYSVpzM2NSb0NRZUYzRHJRSzJfelFreE5IaHU1T3pZdktHeWtQUHRNMGd3c1FiaDhfTXJwTF9PME42elZja9IBjAJBVV95cUxOTlRtWDJiVkhqc0tmcHpDUkFGSVA1bHFTdlJIbkZBUElBNnRvWjV0bEhXaVhhakpJUEtUZ0xGeGNVV09HWTNPUzl5S0Y4bzZiQmJNc0o4VkdnYmJRSHRGQlJadmxyNFNuNk9GZUpURHlnWlEzbTh3VzFHZ1pBMWZ5WHNEZm9ubkYzUU1KTGdOdGNLbHpJTDlRNENZNTRISG9sT29kQ0RjRTFRNDNUSUtsY3p0dFRhLThoX3lxU2Y2RXFoMmVtSXB3eVRuT3p6ZG5NVk1zRmlENFVZa1gyRmJQNHhpMGFXRFNtOVZ3YUh3QmFZaXVWY2Etd2I3SFBWZk45aE12dkE3WEJwdEg1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQQ3pvU201R2JPZEJPWTQyNzZSdTJJbV9jM0IzbUFBYzZxcEp3Y1U2T0xoNGJYMk4xRkY0Uk9ybUtSZTllX1dxVFc4b2tKMVBqWktiTjh5THhoeC1GUWJpZkh4RnVZQVVOeDBwWGtyTVBCSjBsQ1dxZWxRMjRaT3pkcDZKMFhaWTRSMS1JUjlKZy1kOTM2TllVV0NQMjJZMTVN0gGkAUFVX3lxTE5Nb3ZabTd1SnBUT0l5alV6UEdnV1ZCaDdnVWstTXRYYnJseXpPMDhMM0VIVDNGRHd4cWpnQkx6SlVhek9XOGhWUndJeGZPbUI0MzNQY3BxOXFMb1cyVENMYzB6a3liYlFnVVRFZ3h4bjlSRVZ5TU5DbzNqc2RZVURBYkZYT3d0NS1jWWU0ZmJGNk8tSWRKRkJUZWpGRmczLUJzRTNG?oc=5</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5494,17 +5494,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Aunque las cifras bajaron frente a 2024, cientos de niños y adolescentes, muchos de ellos indígenas, fueron reclutados por grupos armados en zonas de alta vulnerabilidad - facebook.com</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPWWtnRGpyNFl6cVhWWGhFRjhDYVFfZnR6Q0JrclZhRXF1NUxCMEZjbWRneExlUGNoN2RoTk1uUjdiRVBJVmoydVdmRzdJX3BDRExySmxxZ2dITkhUT0tZRzRDQ3NvcWI3LW5za0NyaGVoNzN0NjY3Xzdna2daS2RuRmtYS1dwUmUxclBpdURNRmR0Y3JOeU1DWXFFUEpXLVlqSGtzWUs5Mm9ib29RLUxHaDVQMEc0WkJyWkF2UV9abFB6NkZmSkh6NEE4VVhyR21tdV96bDNIRnhCWk1WVFluVFMzeHQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQSmlvdlUzeHJlOVhEOTBjQVN5TlhCWkNmaUNEQnczelA1YWVHXzJ1ZHZkM2JKcWdCNzdKYkViRnQyaFpldFB5MGQ4SU54WDVoVGNlbWdRQzJhM0hvRGFaaF9MR3lxUWhSbGJUTFNKcHVmQjJ4MjlibnNuaGNVcXVaVE1aa0stdmFzYmxvTnlmc1hwMFdQUDJGVkVuS2Y4NTgydk9zQlZsU2l0OXA2NjUzZnk3SnpDOUx6RjItNE9EYWlscDBlR19XV1pIdEgxVF9XT2RWMHItMmdEeHlqdmdfYzh1X0dIT2lLNjlvR2RsRWhDZ25iMWVGbTNzaUtQZy1STHfSAZwCQVVfeXFMTXRiNGt6QnJSZDJ3NXItNWZ1enZWUkZmMEhPSm5pNWpLT2hSLXdLWnBzOTFLcVdzM3Q2SWZ1UWpzdU13NjVDNUR6S2o5N1BhOWdlYWEyVDh2bGVqTE1LR19KUnFaUFJEVWZhTlZ4Z3RwV3J2U1I3VmtReVVaTGxMTldfeEZmclhOby1iaFpVU2ZjOUJqRERwNFlMNVdzbDVFX3BQWmg1YjNhY0hrQWJ4UW53Z0lRTWlLWFEyWm5Jck5qX3ROSXVqZUxtTHM3WDk2TDJzUDJUN21VTjkxamZMRUd2Unl3emJEaGJxejJPdFViSkNWbTRudzNRUmE4bFg4a1JaLURLa0lQakk0U0kyRFFwV0ZlRHBtZ3VNc1Q?oc=5</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -5537,17 +5537,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>¿Qué está pasando con los colegios privados en Colombia? - El Nuevo Siglo</t>
+          <t>Estados Unidos hizo llamado de atención a Colombia ante la ONU por aumento de reclutamiento de menores de edad:“Dudas sobre impunidad al terrorismo” - Infobae</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>El Nuevo Siglo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZzZTLXZVaUFVM043V2MtUHZGUFRWVktvSjF2d0c5cUNrbzg1MThzdW1mUVhIeTV5ZW8xak9obGxzMjJTRXVYVG93R2V3OGVqWjBNQnRoNWxVMXBEMWR2eHIxb1pyOFllWEZxem8wSTQ2aktzVTNndUNMU2szeHJKWTNDWlFWbDVtNEwyckF4ajF6WlhjTC02bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNNFJLRzNtTGZtU1ZCaVUxbGR1QUhBMzV5eFVUT2w4TWZVZnNfYmNMX1IydEVyYnhGT3ZJcDZMaG85R0RUUU9LaEsxT0hyYTFEcy1lNmVTMTA4TWlTbzJ2NmJNbTdxTXZQeUVsczJGMTdSZVlYVHlwblhqeG53UzZ5QkhsMVFyTWRORUQtOUNJMXFBSzJiNkZGQjJSZ1lvcWdfUHFTN1duQjJvcWVyMEZIZE01OGMyakhIQk5WbkROZlpIaDg5UHJRLWdEWVVSRlN4N21hNlhvemlncnlCZlNsM1BvYlJrX2hnUEpmREFCT1pzWS14YmtLMzNHWk1ndnN1NVE5YUdaajNmelBLZEViNEFHNHdjbFhqZEHSAbQCQVVfeXFMTXBsTHJ3d1N1RXh4WFdBdjAtMVFYcEJTV2xwd0xHZERGQVlHNXNvcW5hYmdpN09Wd1ljMjR4RjNSRWMxMl8xMmN5TzN2XzQzUDhCdlJ2WjdNSklzMG1yRzI5YnRnRDFhYWo3Wi1wOEdNbHE4UElzU2FGN3Z2b29XX0Z0bXBDczQzbE1oRE9zVjk1VG9OMzZSNlhsbjlFZUp4em84bGxJSTJyRG8yOWlvUkxPZkhVT0picHVCXzRRX2dhY1VTTWlJcUFYRnVBQzV0ck10YkktYXVpSE5uNm40U1lneGt5c0p5VUNzYnl0NEpqWmVLUE5UcWxOT1BJbnFDZmJRSG9XaTYyMXhqT3dhekhSUDBLSnh6dGxBNFNNYzktYTdZMmxmZm13bXhDd2x3Y0tvWkM?oc=5</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -5585,12 +5585,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Colombia presentó avances en la protección de la niñez y la adolescencia ante el Comité de los Derechos del Niño - Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Aunque las cifras bajaron frente a 2024, cientos de niños y adolescentes, muchos de ellos indígenas, fueron reclutados por grupos armados en zonas de alta vulnerabilidad - facebook.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQajg4Z0F1TkdHLTRxTG9Sd2tUTXBxWDNyaWo4a1RuTXFZUHNVaDM2XzRvNDZWZS1ZRXVNaGRFc0hiaVVsaUU3NHdtNTVUbXRVbVZReGJPaEVzVzdZSHNweWdrVmhpQVV1REVfcmpSeDlFeGhZNjFEb2huNTlpZkVTMlhpbVRPZEh1OXdhLWxmdnBRNURlV2dYemhVenJheTZLZkZhMU93NXVVX0pobC1VNFhoN2FrNG1XZUl5MG9iNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPWWtnRGpyNFl6cVhWWGhFRjhDYVFfZnR6Q0JrclZhRXF1NUxCMEZjbWRneExlUGNoN2RoTk1uUjdiRVBJVmoydVdmRzdJX3BDRExySmxxZ2dITkhUT0tZRzRDQ3NvcWI3LW5za0NyaGVoNzN0NjY3Xzdna2daS2RuRmtYS1dwUmUxclBpdURNRmR0Y3JOeU1DWXFFUEpXLVlqSGtzWUs5Mm9ib29RLUxHaDVQMEc0WkJyWkF2UV9abFB6NkZmSkh6NEE4VVhyR21tdV96bDNIRnhCWk1WVFluVFMzeHQ?oc=5</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -5628,12 +5628,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Se acaban los castigos para estudiantes en colegios: Corte Constitucional pone contra las cuerdas a los rec... - redmas.com.co</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPeUdyQjFZLUJGUHR0WTBwSldBTGJtRHFmU2NJNkJWT0tBMzlNTFJ6RWpTekQxRVUyX2phUHE4dzFwbTBQZ3Q3SHE1QllpQUN0Q1BJdGpVQjVGWmNrX25wVGZhLUhfei1weWVPbnloMEczS0Y0YXNUN1otS1MxQVQxaE5SMldWdkVvV2xvTEx5VlY3V25WNmYyVnFsM1ZZcFUwb2dYa0FBbkcwUjZGempNelNEUFdsNk9BbFNHOVVfRUR2UEs5RFd1OFJYSVpzM2NSb0NRZUYzRHJRSzJfelFreE5IaHU1T3pZdktHeWtQUHRNMGd3c1FiaDhfTXJwTF9PME42elZja9IBjAJBVV95cUxOTlRtWDJiVkhqc0tmcHpDUkFGSVA1bHFTdlJIbkZBUElBNnRvWjV0bEhXaVhhakpJUEtUZ0xGeGNVV09HWTNPUzl5S0Y4bzZiQmJNc0o4VkdnYmJRSHRGQlJadmxyNFNuNk9GZUpURHlnWlEzbTh3VzFHZ1pBMWZ5WHNEZm9ubkYzUU1KTGdOdGNLbHpJTDlRNENZNTRISG9sT29kQ0RjRTFRNDNUSUtsY3p0dFRhLThoX3lxU2Y2RXFoMmVtSXB3eVRuT3p6ZG5NVk1zRmlENFVZa1gyRmJQNHhpMGFXRFNtOVZ3YUh3QmFZaXVWY2Etd2I3SFBWZk45aE12dkE3WEJwdEg1?oc=5</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -5666,17 +5666,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
+          <t>Colombia presentó avances en la protección de la niñez y la adolescencia ante el Comité de los Derechos del Niño - Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQajg4Z0F1TkdHLTRxTG9Sd2tUTXBxWDNyaWo4a1RuTXFZUHNVaDM2XzRvNDZWZS1ZRXVNaGRFc0hiaVVsaUU3NHdtNTVUbXRVbVZReGJPaEVzVzdZSHNweWdrVmhpQVV1REVfcmpSeDlFeGhZNjFEb2huNTlpZkVTMlhpbVRPZEh1OXdhLWxmdnBRNURlV2dYemhVenJheTZLZkZhMU93NXVVX0pobC1VNFhoN2FrNG1XZUl5MG9iNFQ?oc=5</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5709,17 +5709,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>La deserción escolar le cuesta a Colombia $2,8 billones al año: casi el 40% de los estudiantes abandona las aulas - Publimetro Colombia</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Publimetro Colombia</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNOWpHQlNpRUdaU1ZWSzBzd3EzM2I3cmZXdzd4aUNrMjlnbWJPZkNNbVVGYXRrX2VPUjJxcEt5ZUJha3lyOS1VODQtTmV5d3NFdU80ME01eFg5X2dWZ25GT0Vhdl9TbVJBZ1RkaEJBZHh3aXNpNEMweEJEM3NuUmxRLWMzQWdUOEFkUUlKbm1PR1FyWVNMSGppa3VOZ2JUQy1wTl9sdkRpT0xhdWNaclNBdmxycEZnTUU0dHJvVVdsbWRaeDc2V1ZHb3dNMmNucmpuTzRkdDRzaERIY093NW81MnpDM0diSHRTbkE?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -5752,17 +5752,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Consejos Locales de Juventud en Bogotá: 21 jóvenes se posesionaron en Tunjuelito - Bogota.gov.co</t>
+          <t>Más de 220 menores de edad fueron rescatados tras estar abandonados en Bogotá en 2025 - Caracol Radio</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNUnRxaERnUnRKcEkxaWZ2cHlsZFRuQkRtMXpDcWZxdU1NNk05VERuZV9CQVhPbXI3Y1d1RGFPMGF0ZGsyamNvZEhFTkQzQWdUSzVNVjg1U0JNQ29WTVRxTldKNWEwX2sybGE5TXhfcU5BUEJ4YVU3MmhFdnpGb0JzV0c2ck1mcGZnc2RVLTd0MEtzZktlQXVzRTN4bVZEa1JOTnlMa0VYWGtkYVJIdURz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOalk3YjJZcTBJakNTakdzSVVMcWZOWmFVM09BaWpMWFVUYnMzVER4QzRNTmNJUURGUWZ6Mmw2YjhMcDhPenR4VzRaQXlpUTRUc3pUcnhjUkxCZVZ4b0REQ3lBZnU5d0pYWV9CNWd0Q29ZLXNpWWxMeTl0WG4tNmNTT2xNYW53OUIwNXhQUnlIQXNSWWxEcUt4Yk15UWZwa3IzZnBBbW5vZ1VBYlp6dmZWR1FaZWE2azFHSVk3dQ?oc=5</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -5795,17 +5795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Se posesionaron los consejeros de juventud electos en el Distrito de Barranquilla - ELHERALDO.CO</t>
+          <t>¿Qué está pasando con los colegios privados en Colombia? - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ELHERALDO.CO</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQM3I2ZXJMVkpqT0RPRGhtVm5LZjVPZnBZTGh4NnBCZTZqajZ1dGY5VGM1MGdKMno1aHdSbERqSEVLWEUyQWctYUtFcl9aVW9jR0RMYWF5aWxQemtRRnhWMEZHTUNyNG0wQVowaFNIUi1zdF9vNFVhTEF3eUVwNFU3UEVYNWdoaUtUUE1FeGFTQkhweG5SOTJzdjMwUm9keGhxcEg5Tk9KbS1mR0h1TDAxbUV4YU9LbmRQOGJIQ0ZkUEx3Z3JMSHBSRGNDWdIB5gFBVV95cUxOVVl6Ujl1cW5wU3A0OXB6dG9jYV9PaHpYbWdhcDBpNm9Ud0NrYUd5YWhkZEQyZVhUNWMxMjgtZEptdDNPUmUtSGp6c3VRMDRYMzdBN3ZuWHhORlotWThuZ2c5MlFaQzl0LXJIbGthTm5yS2J5UWdMWFJiSGFFUjdzQlhmNm9abnlUT1NQc3N2dEVMQ3VIbWh2c1hiSGRCR2todGpUMTNkR2dqdUpWT040RlBIQXZudnV2RnhPaEpOaUtEZmxhcXR5YWw1cE1IRjVibGUwdndBS0JVa0dRZDZQM1VvM0tNdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPR1N5MGEzQ0xqcVF5cVd3TUJXVGJ0Um9kSElKTXVWbDc4Q1FEdTBrbjI0TmJ5OFFNZFRseXQwYmhEYTNvM2dNWUlfaU1WMnFEb0luTEdadTJ4VmFuZ1h1eHM0T0ZPQ1BGRlhlQlpEZGJtRklRbXhtVE8xMVVFUGZESjRIYXBVVF9DTUJOcVRMZExSSkZVbmdTQzVOZG01aUIzT1VjamFsUFJrZVZ4aHFJNlZEUWNqVHBiZUpQSjZ4NHo?oc=5</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -5838,17 +5838,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>¿Dónde estudian los genios de Colombia? Estos son los únicos colegios del país con calificación AAA+ - Portafolio.co</t>
+          <t>⚽ Santa Fe propone torneo sub-23 para dar oportunidades a jóvenes y futbolistas sin club. #Fútbol #Juventud #Colombia - Facebook</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portafolio.co</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPczRONEpvSjI3TmpVWEdqVnNtUG1LeFBjSjc2X0ZfR2RQaVcxN1J6ZDBheFcwVHNPZGcyelI3RUFsWEp1YXBQcDFacFJjSkVXVWRCZ3ZhMzdZRmtvOVBHckJjWDlhdlV4NUF3anRJR21qN0RqV1dhRFlLQ2lIVm40NnRSNlBXMDNWZlB0dkhMWW1zOXRkOUJyRmVBaENseXYyREtzUlRxUkJsTUJ1eUJPQWs0aW5hdU96LXU2ejVkMlJNZERnZXRTUk9ydXB0UURFX3dvVkJ5Qm9SUDFFUXBuTzBn0gHnAUFVX3lxTE5wZFNHdzdvOWxRLWQtOWtrcUFzZi0ydEFMXzF0YUZOa3AwQjlNUjFablhQRTdwR2J5Qzh5WDZ3UEZ4QTZSc2MwbHB6TnM0WTduMjduVnM2RnRTY0JQR1ZtWTB0QThMaXNVQlZQV2xENVBZTXV6ZHQxVGNTNDF1ZGpxbU9BeEFxMGZrUVNIdVNJeUpjcmVXcm5pemM2SHRUR0duN0hKWjVlNzR4bDFsWVRKTjhmbTJoQlM1a2RheHVSc0N5MkNucmFhdnkzYUFHby1Qb3R0TE56dHBMNUoyVnhTa01IU3liWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxObFJ5amljVE9jSVpXcTh3b1pqaXNPWWp3QkFjZkFPT25VRk9KbDczbno3VFFlZnZkc2RURl9PdXVxOXNCV2lYdGZHYmVmYmoyLTl6TWJsNjYzLVJwOEoyWmM0TU1zYTJld24wdUJTcHE5RzhXdlk5VTE4WVpWQWpYS3R5REo4aURzZ0tkMTA2WGd1Y1dQdWFrTy1zZHZueWhlb1gwYXc0dWhjZ05Oc0tlQVpCR2pta2E4MU1vTTVFUW0yRDZDcWN5Z3g2RUYtUjdfWFdDc3Z1czBRMkYzVFcwV1pUUEU?oc=5</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5881,17 +5881,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Medicina Legal confirma la muerte de cuatro menores de edad por los enfrentamientos entre disidencias en Guaviare - EL PAÍS</t>
+          <t>¿Qué está pasando con los colegios privados en Colombia? - El Nuevo Siglo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EL PAÍS</t>
+          <t>El Nuevo Siglo</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNQ0VEeWtCQWV2VXlEekdmTTBNNWdRVTNNVEd0Vmt6QkM4UGItcWQwOFZhZFNHNGJIOWhpWGhVeFFxTFRFV3lHeTdIOFF5aDltV0hWUURZM1dsQmFfVmFvTU1JdGJ5U09wVktadWhJWUNMdnllQVJXOU4zZS1SdDVqdk5OOGJqc0hDNFVUa3ZkZ2dQNXZkMDdlbVh3RXlHSnh5N1J4a2VLYU1SR3N5czFVQ3BfZW5wQmZtY0Y4RmctWU5BbjhGU2hvSVRLdjdLWV9pcUZSZXRqYXR1am1tNll5VXR4bmtCZlR1blhXUFl1V1VqU3pGUG9jbtIBjAJBVV95cUxQWXZ3bFpiSDN6eWVxM2ZTckYwcUpSRExJc2ZYVUtONWhLYnJBX0JMZ2lUTFJkRzFKZmZUQ0R5OFVBM3pkZzlWdldJc0tPZ2E0R3JGd0JkUElqOTJDSmdmbWlzRjJrWXZIQ0pnMHgwb1lVekpVWTRiMHZIdHpnUXhyTURpeDV5X0NHbFFXTnFYN3hQbDYwVG0yQUFGTFM2a2tIRFMyQU93WG95LTExWUlJbkRsQ1RYcC04UXYzYmtXNFNxbDctWmN6RFVZWWtNbEFFQVF1N2lDd1NGVFBzR3BJUkpWR2FvLXZoQnR6V1Mzc1NMNHNtRkFmalRrd1FMT3lWY2VhT3RzRkkxXzdC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZzZTLXZVaUFVM043V2MtUHZGUFRWVktvSjF2d0c5cUNrbzg1MThzdW1mUVhIeTV5ZW8xak9obGxzMjJTRXVYVG93R2V3OGVqWjBNQnRoNWxVMXBEMWR2eHIxb1pyOFllWEZxem8wSTQ2aktzVTNndUNMU2szeHJKWTNDWlFWbDVtNEwyckF4ajF6WlhjTC02bA?oc=5</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>Imposición de boinas: jóvenes construyen un futuro sólido al servicio de Colombia - Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSlFESU01MVJsb3l4c2RqRHh3UHVHcHZjcEhSUldGYmZLZmNnOC14NUh2a1dFZUlkZ000STZVcEt5a3RVellXTWQ1SFF1YjZlLTVvRTdBbVhvX2FMc0I5dEhMamZJajJvOW1hWFFPd3ZvdGZlNE90M0Z1VGpKN2NZZVVwS083dWJJb3VaUGZtQWw4eFNYOWhFSWh3VExoRi1ZSGJMOGNUYUxhV3JQbE1KalphcWw?oc=5</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
+          <t>Consejos Locales de Juventud en Bogotá: 21 jóvenes se posesionaron en Tunjuelito - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5987,22 +5987,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNUnRxaERnUnRKcEkxaWZ2cHlsZFRuQkRtMXpDcWZxdU1NNk05VERuZV9CQVhPbXI3Y1d1RGFPMGF0ZGsyamNvZEhFTkQzQWdUSzVNVjg1U0JNQ29WTVRxTldKNWEwX2sybGE5TXhfcU5BUEJ4YVU3MmhFdnpGb0JzV0c2ck1mcGZnc2RVLTd0MEtzZktlQXVzRTN4bVZEa1JOTnlMa0VYWGtkYVJIdURz?oc=5</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -6015,12 +6015,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Imposición de boinas: jóvenes construyen un futuro sólido al servicio de Colombia - Fuerza Aeroespacial Colombiana</t>
+          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fuerza Aeroespacial Colombiana</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSlFESU01MVJsb3l4c2RqRHh3UHVHcHZjcEhSUldGYmZLZmNnOC14NUh2a1dFZUlkZ000STZVcEt5a3RVellXTWQ1SFF1YjZlLTVvRTdBbVhvX2FMc0I5dEhMamZJajJvOW1hWFFPd3ZvdGZlNE90M0Z1VGpKN2NZZVVwS083dWJJb3VaUGZtQWw4eFNYOWhFSWh3VExoRi1ZSGJMOGNUYUxhV3JQbE1KalphcWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -6053,17 +6053,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>La industria del éxito temprano está dañando a los jóvenes en Colombia - La Silla Vacía</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>La Silla Vacía</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPemdoRDc3Um9SMTVlNm1zNEhLTFlLNzNZNzZkbHlOOVB2V1pLVkY2eHZYdTllVXozMGQtbVlQQmlwRUFFclVqR1UyMnUwT19fX3BrcGQ0bTNWVlUyX29MdkhRdC1wY0huNENONDR3ZEJOaHdwcDJqWXNKN2tFdE1QOXB6Q1Rqa0NfOXBHbGROUjlkNTAyX2JDdzhhZ3lTdGQtdUdUNDdrMHdiYlV5T0ExdUd6bWRBY1VfMXBPaE5GdEd0RWFfNGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -6096,12 +6096,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -6139,17 +6139,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Casas de Juventud lanzan convocatorias para semilleros y talleres gratis en artes, deporte y cultura urbana en Bogotá ¡Aquí detalles! - Bogota.gov.co</t>
+          <t>La deserción escolar le cuesta a Colombia $2,8 billones al año: casi el 40% de los estudiantes abandona las aulas - Publimetro Colombia</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>Publimetro Colombia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6159,22 +6159,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPQVRjdEY5Qzd0YUktckFJT2NWYVZmdEc3dEthdVExQ3lub0VCM3QyMXhqNnlZaUctQkRPWkY4bzhPbWE2X3BNU2FYMHg5ZzhPMVpWLVVnelNkTWdXV09PS3VwSmZpZXZ2a09pT0JUX3VraXhXMGdnUFhnbnJWXzlOdkJaRzBUYl8tQXE0dURYSE9NV2R2REViOFcyeUF4cFFRRXNJM0thTWxDX1lLWmJwWTUtZkJxWUpRWEpPTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNOWpHQlNpRUdaU1ZWSzBzd3EzM2I3cmZXdzd4aUNrMjlnbWJPZkNNbVVGYXRrX2VPUjJxcEt5ZUJha3lyOS1VODQtTmV5d3NFdU80ME01eFg5X2dWZ25GT0Vhdl9TbVJBZ1RkaEJBZHh3aXNpNEMweEJEM3NuUmxRLWMzQWdUOEFkUUlKbm1PR1FyWVNMSGppa3VOZ2JUQy1wTl9sdkRpT0xhdWNaclNBdmxycEZnTUU0dHJvVVdsbWRaeDc2V1ZHb3dNMmNucmpuTzRkdDRzaERIY093NW81MnpDM0diSHRTbkE?oc=5</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -6182,17 +6182,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>Se posesionaron los consejeros de juventud electos en el Distrito de Barranquilla - ELHERALDO.CO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>ELHERALDO.CO</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQM3I2ZXJMVkpqT0RPRGhtVm5LZjVPZnBZTGh4NnBCZTZqajZ1dGY5VGM1MGdKMno1aHdSbERqSEVLWEUyQWctYUtFcl9aVW9jR0RMYWF5aWxQemtRRnhWMEZHTUNyNG0wQVowaFNIUi1zdF9vNFVhTEF3eUVwNFU3UEVYNWdoaUtUUE1FeGFTQkhweG5SOTJzdjMwUm9keGhxcEg5Tk9KbS1mR0h1TDAxbUV4YU9LbmRQOGJIQ0ZkUEx3Z3JMSHBSRGNDWdIB5gFBVV95cUxOVVl6Ujl1cW5wU3A0OXB6dG9jYV9PaHpYbWdhcDBpNm9Ud0NrYUd5YWhkZEQyZVhUNWMxMjgtZEptdDNPUmUtSGp6c3VRMDRYMzdBN3ZuWHhORlotWThuZ2c5MlFaQzl0LXJIbGthTm5yS2J5UWdMWFJiSGFFUjdzQlhmNm9abnlUT1NQc3N2dEVMQ3VIbWh2c1hiSGRCR2todGpUMTNkR2dqdUpWT040RlBIQXZudnV2RnhPaEpOaUtEZmxhcXR5YWw1cE1IRjVibGUwdndBS0JVa0dRZDZQM1VvM0tNdw?oc=5</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -6225,17 +6225,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Menos estudiantes, cierre de colegios y menor fuerza laboral: el efecto dominó que causaría la caída de los nacimientos en Colombia - ELTIEMPO.COM</t>
+          <t>¿Dónde estudian los genios de Colombia? Estos son los únicos colegios del país con calificación AAA+ - Portafolio.co</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Portafolio.co</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOMWJRUzdtRlZyMGg3cnFZYVBRZzZQVGExREJVZGxOZk03d3IxbVZfREhIQmRIMTcwM0RhV0VITzl5MkdIbVNEd0ppLS1TUGpLVmF2dzJ6bTdyeU15Vms5SzlGU3MtZ0l2aUlWSzdTYk13OGxOVjQ3akNucUdmLV9yeXZjcjdYLVJyWnl5a25scDBxWnVRSlg5VFZ3TkVlS0pzU3ZXM2RZZTdrbjZ4Q2dub1FraTNwVzd5M0FObGo3dUEzYmlwdFd3T256anIweVZFUkt2VWFOeUN6SkFBQ1QxQ19GQkF4NE0yMHpvWUZTRVdjZ21BYnZlVkFBWnlwRElSeTB6M0xvVGXSAY4CQVVfeXFMTzJyUHA2bWVUTnc2WDBiUkJzWVdRWUNobktMNEQ1SVBnb0kxSFh1SlMzejA4VEhfRTEtRDBfb0N4dkVLbkZkMVVEakZOaENacG1vdDNVck15LVNCdU5IMUJ2b2pnV2RGd1JKMVBmemk0bGpHTTVMQlJ0LTE0Rmw5TjVDVVkyV3o3X0pveThGc283dzlDMnlWZXAzUkJhMUllRnF5bVpSSS16N0hPMGFhQjh3cVRVWFRLT1JxQ3JkaU8wX2ZwaUthalFqNkRITU5YdnU3LWZlaTBhSTJrd1FMNndPY3llbG1nSXJFWTJUVUpZTW5idVpNVVVwTU9qV1lqM3d5UDFrZjcwaTVmbE5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPczRONEpvSjI3TmpVWEdqVnNtUG1LeFBjSjc2X0ZfR2RQaVcxN1J6ZDBheFcwVHNPZGcyelI3RUFsWEp1YXBQcDFacFJjSkVXVWRCZ3ZhMzdZRmtvOVBHckJjWDlhdlV4NUF3anRJR21qN0RqV1dhRFlLQ2lIVm40NnRSNlBXMDNWZlB0dkhMWW1zOXRkOUJyRmVBaENseXYyREtzUlRxUkJsTUJ1eUJPQWs0aW5hdU96LXU2ejVkMlJNZERnZXRTUk9ydXB0UURFX3dvVkJ5Qm9SUDFFUXBuTzBn0gHnAUFVX3lxTE5wZFNHdzdvOWxRLWQtOWtrcUFzZi0ydEFMXzF0YUZOa3AwQjlNUjFablhQRTdwR2J5Qzh5WDZ3UEZ4QTZSc2MwbHB6TnM0WTduMjduVnM2RnRTY0JQR1ZtWTB0QThMaXNVQlZQV2xENVBZTXV6ZHQxVGNTNDF1ZGpxbU9BeEFxMGZrUVNIdVNJeUpjcmVXcm5pemM2SHRUR0duN0hKWjVlNzR4bDFsWVRKTjhmbTJoQlM1a2RheHVSc0N5MkNucmFhdnkzYUFHby1Qb3R0TE56dHBMNUoyVnhTa01IU3liWQ?oc=5</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -6268,27 +6268,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
+          <t>Medicina Legal confirma la muerte de cuatro menores de edad por los enfrentamientos entre disidencias en Guaviare - EL PAÍS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>EL PAÍS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNQ0VEeWtCQWV2VXlEekdmTTBNNWdRVTNNVEd0Vmt6QkM4UGItcWQwOFZhZFNHNGJIOWhpWGhVeFFxTFRFV3lHeTdIOFF5aDltV0hWUURZM1dsQmFfVmFvTU1JdGJ5U09wVktadWhJWUNMdnllQVJXOU4zZS1SdDVqdk5OOGJqc0hDNFVUa3ZkZ2dQNXZkMDdlbVh3RXlHSnh5N1J4a2VLYU1SR3N5czFVQ3BfZW5wQmZtY0Y4RmctWU5BbjhGU2hvSVRLdjdLWV9pcUZSZXRqYXR1am1tNll5VXR4bmtCZlR1blhXUFl1V1VqU3pGUG9jbtIBjAJBVV95cUxQWXZ3bFpiSDN6eWVxM2ZTckYwcUpSRExJc2ZYVUtONWhLYnJBX0JMZ2lUTFJkRzFKZmZUQ0R5OFVBM3pkZzlWdldJc0tPZ2E0R3JGd0JkUElqOTJDSmdmbWlzRjJrWXZIQ0pnMHgwb1lVekpVWTRiMHZIdHpnUXhyTURpeDV5X0NHbFFXTnFYN3hQbDYwVG0yQUFGTFM2a2tIRFMyQU93WG95LTExWUlJbkRsQ1RYcC04UXYzYmtXNFNxbDctWmN6RFVZWWtNbEFFQVF1N2lDd1NGVFBzR3BJUkpWR2FvLXZoQnR6V1Mzc1NMNHNtRkFmalRrd1FMT3lWY2VhT3RzRkkxXzdC?oc=5</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -6311,17 +6311,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
+          <t>La industria del éxito temprano está dañando a los jóvenes en Colombia - La Silla Vacía</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPemdoRDc3Um9SMTVlNm1zNEhLTFlLNzNZNzZkbHlOOVB2V1pLVkY2eHZYdTllVXozMGQtbVlQQmlwRUFFclVqR1UyMnUwT19fX3BrcGQ0bTNWVlUyX29MdkhRdC1wY0huNENONDR3ZEJOaHdwcDJqWXNKN2tFdE1QOXB6Q1Rqa0NfOXBHbGROUjlkNTAyX2JDdzhhZ3lTdGQtdUdUNDdrMHdiYlV5T0ExdUd6bWRBY1VfMXBPaE5GdEd0RWFfNGc?oc=5</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -6354,17 +6354,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6389,29 +6389,25 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>En los últimos cinco años nivel nacional han cerrado las puertas más de 800 colegios - LaRepublica.co</t>
+          <t>Casas de Juventud lanzan convocatorias para semilleros y talleres gratis en artes, deporte y cultura urbana en Bogotá ¡Aquí detalles! - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LaRepublica.co</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6421,22 +6417,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVkVKVlhVU1d2Tk9ITl84dEtTVHBMTF92RDJLa0JNTFJhRVljR2syeFBUQVJnV0EteVN5eG1zVVBuMldzOUVNSzZ4M0s3cWY2NXhTa05zNklVcVRIU0FOSGJSajVRM2Y0QzRLQk1yUHprM3NPRXA3dm9qQXVCNHRVa204OE82V3NBU0FLcF9HeU0yR0tQN0tWNmkxcjZBaHVsc05iZjg4Qy1tU1VSNmxPNHhrdXZJaV81YlBvc1JNalLSAcABQVVfeXFMTmtFbWJiYWI5d19VS21uUEx6Q09oeUs3bjFVdDBtbFdoZmNsZDBJUlZhdHhEUlFOMmVFSmdSbXZRX3c3YXFzVWtRcldzR00zU19PNWx5X053QUM3N2N6UVRwcVNtek1qeV95a0tsQ2Y1TGpnQWRDYXBGTDZLVlppd1BYeGh6LUlZVmtQQkw4dmhERlRza3UxZGg1VXdKRkEwT0R4eXZlN2tDdEdLUWxGQjE3ekh1eWR6Skg2eGNIM3lU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPQVRjdEY5Qzd0YUktckFJT2NWYVZmdEc3dEthdVExQ3lub0VCM3QyMXhqNnlZaUctQkRPWkY4bzhPbWE2X3BNU2FYMHg5ZzhPMVpWLVVnelNkTWdXV09PS3VwSmZpZXZ2a09pT0JUX3VraXhXMGdnUFhnbnJWXzlOdkJaRzBUYl8tQXE0dURYSE9NV2R2REViOFcyeUF4cFFRRXNJM0thTWxDX1lLWmJwWTUtZkJxWUpRWEpPTA?oc=5</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -6444,17 +6440,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6469,17 +6465,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU0gGGAkFVX3lxTE9kVTNSLWtRcmp3VzFBcXViWi1BSWVxdF9YaERoMFpoZkM5bFNjV1pBcVRqS1FRLXdlMTUtcjRYcVpveUhRNWFwQ0VDblBnZW1TME9STnhpWW9DanJvVXlqTVloLUU2ZTAtMENhU2lDV1hMLTYyNXJfU1htMHlmSzBkUnlGamd5cXlfOXlJV2ZmWUMzVUlKamlQa2VmZnVDVkcyR2pVZkx3VEk3aTFqYk51dk5paVhheURPQ0NQcVI0NkFYMXFwbml0bU85WmpINnNMUWpfZnVnbE1BNnRxQnozUUNnNGwtWXN3R1FBczNBZzVVeEQxSEZPeE5rMEd0Y3NVbVRiSHc?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -6487,22 +6483,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6512,7 +6508,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6522,7 +6518,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -6530,17 +6526,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
+          <t>Menos estudiantes, cierre de colegios y menor fuerza laboral: el efecto dominó que causaría la caída de los nacimientos en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6555,7 +6551,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6565,7 +6561,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOMWJRUzdtRlZyMGg3cnFZYVBRZzZQVGExREJVZGxOZk03d3IxbVZfREhIQmRIMTcwM0RhV0VITzl5MkdIbVNEd0ppLS1TUGpLVmF2dzJ6bTdyeU15Vms5SzlGU3MtZ0l2aUlWSzdTYk13OGxOVjQ3akNucUdmLV9yeXZjcjdYLVJyWnl5a25scDBxWnVRSlg5VFZ3TkVlS0pzU3ZXM2RZZTdrbjZ4Q2dub1FraTNwVzd5M0FObGo3dUEzYmlwdFd3T256anIweVZFUkt2VWFOeUN6SkFBQ1QxQ19GQkF4NE0yMHpvWUZTRVdjZ21BYnZlVkFBWnlwRElSeTB6M0xvVGXSAY4CQVVfeXFMTzJyUHA2bWVUTnc2WDBiUkJzWVdRWUNobktMNEQ1SVBnb0kxSFh1SlMzejA4VEhfRTEtRDBfb0N4dkVLbkZkMVVEakZOaENacG1vdDNVck15LVNCdU5IMUJ2b2pnV2RGd1JKMVBmemk0bGpHTTVMQlJ0LTE0Rmw5TjVDVVkyV3o3X0pveThGc283dzlDMnlWZXAzUkJhMUllRnF5bVpSSS16N0hPMGFhQjh3cVRVWFRLT1JxQ3JkaU8wX2ZwaUthalFqNkRITU5YdnU3LWZlaTBhSTJrd1FMNndPY3llbG1nSXJFWTJUVUpZTW5idVpNVVVwTU9qV1lqM3d5UDFrZjcwaTVmbE5B?oc=5</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -6578,12 +6574,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cambió el calendario en colegios en Colombia: esas son las nuevas fechas de vacaciones - La FM</t>
+          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>La FM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6598,7 +6594,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6608,7 +6604,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPV3JMcmxKczJ0SUVEa0xWa016eEQ1NXhSTFpiYXRZOFpxMjlMMXpjOWx4dzZzVXJiRC00UmhGWVFrQjN2ZmFOU0lmWmUzSUtWOEJSX2VxVXRldW1HcXdBN2ZydVRpb09FNDEwbTJtYnRYQjM3eG55cTZaRW9GOURaRDJZUk5QTDVZS2hxeUVhemtkS2U3VnQtT09nc1dnRkhTU3NzMlpRS3ZYZkROWExud0szRG7SAbQBQVVfeXFMTXJvM0I0SEZhNldLZ3RRWmdhWnFwS0JicnhBOGZPTDZJdlJyR3ZLQ3BYTkNWZWhybzdxVEstR3duOXZFWHdVVWI1ZlAtYVl2T2hZejhfZXAwS2hPekMxbGp6X2UxUk05eWdUajNPWU80cENHRkFySDVkTmRBbExyLUFqMjZtYUEyQmVtTV9sU3RjU2RHeXFPQ3ZyTkJOalZDblRid05OTFRSNWc4dkc2Qm1HMkNy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -6621,12 +6617,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Día Internacional de la Educación 2026 celebra el poder de la juventud - UNESCO</t>
+          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6641,7 +6637,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6651,7 +6647,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRWU1YmM4clFjLXhocUloOFB3QWpFRVVrTWg1ajdkLWluRGEydUJ1VXo1cmU0djVzU01DU04yTmJGTm1BZ2VQaVdWTl9ITVFtVE91U1NEVnM3STdERkkxd3VBS3AtZXliVmdnNFFTNEp3WlJXcTdaTG5LX3NhMFdLU3NLNHZJTHRCVW5hLVlDLTRqakJZTS1POEcyOXpnWC12VVJPSS1ZZk9WSXowS0JqeGczUGNQTkFZYWRiQ3RKSk9RanJVR2FHRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU0gGGAkFVX3lxTE9kVTNSLWtRcmp3VzFBcXViWi1BSWVxdF9YaERoMFpoZkM5bFNjV1pBcVRqS1FRLXdlMTUtcjRYcVpveUhRNWFwQ0VDblBnZW1TME9STnhpWW9DanJvVXlqTVloLUU2ZTAtMENhU2lDV1hMLTYyNXJfU1htMHlmSzBkUnlGamd5cXlfOXlJV2ZmWUMzVUlKamlQa2VmZnVDVkcyR2pVZkx3VEk3aTFqYk51dk5paVhheURPQ0NQcVI0NkFYMXFwbml0bU85WmpINnNMUWpfZnVnbE1BNnRxQnozUUNnNGwtWXN3R1FBczNBZzVVeEQxSEZPeE5rMEd0Y3NVbVRiSHc?oc=5</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -6664,12 +6660,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>En los últimos cinco años nivel nacional han cerrado las puertas más de 800 colegios - LaRepublica.co</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>LaRepublica.co</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6694,29 +6690,25 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVkVKVlhVU1d2Tk9ITl84dEtTVHBMTF92RDJLa0JNTFJhRVljR2syeFBUQVJnV0EteVN5eG1zVVBuMldzOUVNSzZ4M0s3cWY2NXhTa05zNklVcVRIU0FOSGJSajVRM2Y0QzRLQk1yUHprM3NPRXA3dm9qQXVCNHRVa204OE82V3NBU0FLcF9HeU0yR0tQN0tWNmkxcjZBaHVsc05iZjg4Qy1tU1VSNmxPNHhrdXZJaV81YlBvc1JNalLSAcABQVVfeXFMTmtFbWJiYWI5d19VS21uUEx6Q09oeUs3bjFVdDBtbFdoZmNsZDBJUlZhdHhEUlFOMmVFSmdSbXZRX3c3YXFzVWtRcldzR00zU19PNWx5X053QUM3N2N6UVRwcVNtek1qeV95a0tsQ2Y1TGpnQWRDYXBGTDZLVlppd1BYeGh6LUlZVmtQQkw4dmhERlRza3UxZGg1VXdKRkEwT0R4eXZlN2tDdEdLUWxGQjE3ekh1eWR6Skg2eGNIM3lU?oc=5</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Colombia lista para los Juegos de Invierno de la Juventud 2026 - EL INFORMADOR - Santa Marta, Colombia</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EL INFORMADOR - Santa Marta, Colombia</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6731,7 +6723,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6741,25 +6733,29 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNT0x5eFk2VFI4TjZyS0I4Wk55RzNuZFl6R3lWTlNOWlVEVFNSUFp3d3hTeU1mUU9JN1hWdHgyYkloUE1xVGctblpGZVZsOHI4cVZLdlZmRnQtZklkOWsyaUlsM0lLRkRxZ2F6dTIzdmRyQ0UwQW82X0djWkpiRDBrUVFVYUt4ZkF4dS1VOWRkbjIwbXBIRERpcVBBcm9OLXlKVUswSHItY0hEYzF3dGw4ZVBFdjZHcmQ4YUJnYWo3OTU3OU12dEtOYVlOZVBCY1Z5Y1VSSzM5WmVpUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/vida</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Actividades en Bogotá para niños y adolescentes gratis en enero - Colombia.com</t>
+          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Colombia.com</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6769,22 +6765,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdVdPZUt4NUl4bDJxN1NGSkJoMlJmSGdickotNUVPdHlPN1czS3dXUEFnbEtUY2szR0drY3ZWZkxFcEVaOXFtUF9VNDlRcVNST0RycnlkSHp3YWJ0SGd6V0ZPVWs2TWt1UHBYQWI4ajNkQnYxNEhsOWo0YjB1a3NIQ3k5SXRCNDZHZkZ6Rm1hdDkxZFc2UlU5amp0bElHOEhjSl9pVFhqOS1hSlNOWHp5VEtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU?oc=5</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -6792,17 +6788,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Jóvenes creen en democracia, pero ven barreras para incidir y participar: las claves de nueva encuesta de percepción de Cifras y Conceptos - ELTIEMPO.COM</t>
+          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6812,12 +6808,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6827,7 +6823,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNVllVbkwzWi1PdVRWcmQ4VjJEd0lwREZXdnBNSHBFcDFEWnctSEtqZVVEVk9WNHZxQzZYSGxwOU1aSkhQX3dtLTRxZGxabzNfZlJtRWhrVTlGYnpoYkdqRFM4SE1CTmw1QTh0eEhfSXEyaF9wMVlUUU04aFR1VG1heGQ3cjdWZ2EtYm9GVTZyZzQxNUwwUTV1c3ZRNTJycmwzSjFIZHc4T25mM3JLUmUxd09FeHNIT0o5UWowMVJIX0NOZk81SmJxMGJqMWlpamE5UFlVS0ZwZExUNGRUVU9CbVJfRFgzUVdaRDRqMExnRjRjSmJLSmJoQUNzaFpKMDFtYXg5eEZ0WkYzM0RoUnk2NGdsTWZ1Z9IBmwJBVV95cUxPMEtpSWotNUdlNkNuSjl5U2x4YkhzTWNxeUlBZzk1UWNOaWZxQjhMenJvVVh0SHpBNjVNdWM4c2hWWVpWeVA1X2c2V2FLSHY5RFNGN05hMkFVOXBsdnlyUFFmTTJyeHRqY08tV2lQVDdQZUctOTlwV1d3N2JJRVlyU2thcmVzbmpsNXZsdzhFQjFkLWNIQmVUblNXNDVTZXV3eHN0M0ZOUmFYazBKWF9IdmVMVW9UTThDckZlbkVERy1RNGV5SmFySWFmMFVWSy1aNjd6Z2Q5RWsyTk1jU1lSdWhQWlc3R1NhZDdLY1RqTDBDeXRaX0kyN3RBeTloc0o2OFhRdXJTLWtibDRJS29ITzd4WEFJQXNVbVhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6835,17 +6831,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Armenia posesionó a los nuevos Consejeros Municipales de Juventud para el periodo 2026–2029 - Alcaldía de Armenia</t>
+          <t>Cambió el calendario en colegios en Colombia: esas son las nuevas fechas de vacaciones - La FM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Alcaldía de Armenia</t>
+          <t>La FM</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6855,12 +6851,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6870,7 +6866,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMVA5RW15YWg0b1ZqdVltdnJETFVFcW82bjJ3TmJQUXRMM01uMFpJTUliTUVkczFXVm9kdGlZdnBlR3NTR1FWRGlOck5VOFZTTC1UaEFhQmozd0EzZllJamY2RHBKeXBsTGFTMWl6QUVzRHBqWDdXaTRkamxhQzRaUG9DSFpnQllQUUtaMFpIR0tJYTNmQmJTVnN2cDNiNGtmZUlHdVg0bi1lNTZrY2JfbmpOM24wTlNKTkxGNFhZU20waDAzLTdGNDRsSm1oSVI1N3QyTHlpazNlY2tYRzQwTGFYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPV3JMcmxKczJ0SUVEa0xWa016eEQ1NXhSTFpiYXRZOFpxMjlMMXpjOWx4dzZzVXJiRC00UmhGWVFrQjN2ZmFOU0lmWmUzSUtWOEJSX2VxVXRldW1HcXdBN2ZydVRpb09FNDEwbTJtYnRYQjM3eG55cTZaRW9GOURaRDJZUk5QTDVZS2hxeUVhemtkS2U3VnQtT09nc1dnRkhTU3NzMlpRS3ZYZkROWExud0szRG7SAbQBQVVfeXFMTXJvM0I0SEZhNldLZ3RRWmdhWnFwS0JicnhBOGZPTDZJdlJyR3ZLQ3BYTkNWZWhybzdxVEstR3duOXZFWHdVVWI1ZlAtYVl2T2hZejhfZXAwS2hPekMxbGp6X2UxUk05eWdUajNPWU80cENHRkFySDVkTmRBbExyLUFqMjZtYUEyQmVtTV9sU3RjU2RHeXFPQ3ZyTkJOalZDblRid05OTFRSNWc4dkc2Qm1HMkNy?oc=5</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -6878,17 +6874,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Crisis en la educación privada de Bogotá: en lo que va del 2026 han cerrado 35 colegios - Portafolio.co</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portafolio.co</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6903,35 +6899,39 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ29TeFBiMWZnaUctc2xlYmJhZ1hkcVZIc3A0WDFDTkpMR2R0ZlJzTlVBT0hKNjZweDJTZ2Z1WEFEcUZKYnpwS1hPZlNyTUpMU0hLOUpIc2NRVktESEotTFV4cjJwbzZnQWY3YlNVdXpRb0pET2VTck56Z1p5OEpUS2ljZWh4UVBCeDBSRXV3S2xERUxaekZMeDNXTDNUVXc5WmpfRktuXzd6UGNGeF9ZUU9NM1NuLUnSAbwBQVVfeXFMT2U4aTE3VGM2SFl3VXE3VlVrOHpYaGhNRFVzM2RwS0xBYkdDVE1nQ0RnbUdUc2FwRGRzdUtGdzA2MlNLZ1dZekhKMFZ2LVd2bm1GQnhWMzZtUkxkV2FBUFpjclhFaHZMSUp4QWhpVEstUHdqcGk5LXFvd0Z5dEJOS3FhXzg2aTcxX3dEY2Zvb2RpUXFlMmdtOTlmS3Jlbk9rX3FHWGkzYzNMWHIxNjlEUmpnUnpoN0t3cGxfMGU?oc=5</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Colegios serán más estrictos en 2026: Eliminan la ley que amparaba a los estudiantes en esta situación - redmas.com.co</t>
+          <t>Día Internacional de la Educación 2026 celebra el poder de la juventud - UNESCO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNSGx6SGg2V3AxTDZ1SkRMemhiTXV6eVE2T1NudWQxRm8yU09lQmpucEMzdzhsVm80enc2SGZYN2ZWa2o4WmdaZWJ5WThNS2JwOFBSVnJ1TkdjRE10M2tkQk1zc3hJUE91d0ZNQXVCcVVFaUk2TEhsNGNFMDJwanVsM1R2Tm9KdG9kNVpVNWI3d244U1JWenRlcXBEVlRrWmtUclVZdWQ5SzRVMFNLbnJxT3libE5UQk1xSlBLYW9pS2cxb3hyVXdVVzExbFlKcWJsTkRzTGhGQjI4M3MzeU5wYzB2MkZZQdIB6wFBVV95cUxOaXVlcUFwUUNqbS1CTURNUGZrUktkZ1phUkxOYUswaF9GbkZZc3p4SGpaZ0FWOExhaWhadHowMHd6SUM5RUNNVGZZanJrMVd1VUoybG84elg0Z3cwcGdiYmJUVjZrZDd2TXcxMEF3YUNCbzNxd0l6QXpSUUZDV3NDczAwOU10RXcyVGVrVk9yczh1Q1FoVG0tRXY1cjFBNmg3VFlrRDZCWElFSTBJbGhjampvMnZCTDNidGljWC1BU2VFR0dqUVBkVkVMLVBINUZkMVQ1UXVnaFBpQzNiMTdtcjQ1Y1NUdmxweGZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRWU1YmM4clFjLXhocUloOFB3QWpFRVVrTWg1ajdkLWluRGEydUJ1VXo1cmU0djVzU01DU04yTmJGTm1BZ2VQaVdWTl9ITVFtVE91U1NEVnM3STdERkkxd3VBS3AtZXliVmdnNFFTNEp3WlJXcTdaTG5LX3NhMFdLU3NLNHZJTHRCVW5hLVlDLTRqakJZTS1POEcyOXpnWC12VVJPSS1ZZk9WSXowS0JqeGczUGNQTkFZYWRiQ3RKSk9RanJVR2FHRQ?oc=5</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -6969,12 +6969,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Crisis en la educación privada de Bogotá: en lo que va del 2026 han cerrado 35 colegios - Portafolio.co</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Portafolio.co</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ29TeFBiMWZnaUctc2xlYmJhZ1hkcVZIc3A0WDFDTkpMR2R0ZlJzTlVBT0hKNjZweDJTZ2Z1WEFEcUZKYnpwS1hPZlNyTUpMU0hLOUpIc2NRVktESEotTFV4cjJwbzZnQWY3YlNVdXpRb0pET2VTck56Z1p5OEpUS2ljZWh4UVBCeDBSRXV3S2xERUxaekZMeDNXTDNUVXc5WmpfRktuXzd6UGNGeF9ZUU9NM1NuLUnSAbwBQVVfeXFMT2U4aTE3VGM2SFl3VXE3VlVrOHpYaGhNRFVzM2RwS0xBYkdDVE1nQ0RnbUdUc2FwRGRzdUtGdzA2MlNLZ1dZekhKMFZ2LVd2bm1GQnhWMzZtUkxkV2FBUFpjclhFaHZMSUp4QWhpVEstUHdqcGk5LXFvd0Z5dEJOS3FhXzg2aTcxX3dEY2Zvb2RpUXFlMmdtOTlmS3Jlbk9rX3FHWGkzYzNMWHIxNjlEUmpnUnpoN0t3cGxfMGU?oc=5</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -7012,12 +7012,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Jóvenes creen en democracia, pero ven barreras para incidir y participar: las claves de nueva encuesta de percepción de Cifras y Conceptos - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNVllVbkwzWi1PdVRWcmQ4VjJEd0lwREZXdnBNSHBFcDFEWnctSEtqZVVEVk9WNHZxQzZYSGxwOU1aSkhQX3dtLTRxZGxabzNfZlJtRWhrVTlGYnpoYkdqRFM4SE1CTmw1QTh0eEhfSXEyaF9wMVlUUU04aFR1VG1heGQ3cjdWZ2EtYm9GVTZyZzQxNUwwUTV1c3ZRNTJycmwzSjFIZHc4T25mM3JLUmUxd09FeHNIT0o5UWowMVJIX0NOZk81SmJxMGJqMWlpamE5UFlVS0ZwZExUNGRUVU9CbVJfRFgzUVdaRDRqMExnRjRjSmJLSmJoQUNzaFpKMDFtYXg5eEZ0WkYzM0RoUnk2NGdsTWZ1Z9IBmwJBVV95cUxPMEtpSWotNUdlNkNuSjl5U2x4YkhzTWNxeUlBZzk1UWNOaWZxQjhMenJvVVh0SHpBNjVNdWM4c2hWWVpWeVA1X2c2V2FLSHY5RFNGN05hMkFVOXBsdnlyUFFmTTJyeHRqY08tV2lQVDdQZUctOTlwV1d3N2JJRVlyU2thcmVzbmpsNXZsdzhFQjFkLWNIQmVUblNXNDVTZXV3eHN0M0ZOUmFYazBKWF9IdmVMVW9UTThDckZlbkVERy1RNGV5SmFySWFmMFVWSy1aNjd6Z2Q5RWsyTk1jU1lSdWhQWlc3R1NhZDdLY1RqTDBDeXRaX0kyN3RBeTloc0o2OFhRdXJTLWtibDRJS29ITzd4WEFJQXNVbVhR?oc=5</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -7055,12 +7055,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Colegios serán más estrictos en 2026: Eliminan la ley que amparaba a los estudiantes en esta situación - redmas.com.co</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNSGx6SGg2V3AxTDZ1SkRMemhiTXV6eVE2T1NudWQxRm8yU09lQmpucEMzdzhsVm80enc2SGZYN2ZWa2o4WmdaZWJ5WThNS2JwOFBSVnJ1TkdjRE10M2tkQk1zc3hJUE91d0ZNQXVCcVVFaUk2TEhsNGNFMDJwanVsM1R2Tm9KdG9kNVpVNWI3d244U1JWenRlcXBEVlRrWmtUclVZdWQ5SzRVMFNLbnJxT3libE5UQk1xSlBLYW9pS2cxb3hyVXdVVzExbFlKcWJsTkRzTGhGQjI4M3MzeU5wYzB2MkZZQdIB6wFBVV95cUxOaXVlcUFwUUNqbS1CTURNUGZrUktkZ1phUkxOYUswaF9GbkZZc3p4SGpaZ0FWOExhaWhadHowMHd6SUM5RUNNVGZZanJrMVd1VUoybG84elg0Z3cwcGdiYmJUVjZrZDd2TXcxMEF3YUNCbzNxd0l6QXpSUUZDV3NDczAwOU10RXcyVGVrVk9yczh1Q1FoVG0tRXY1cjFBNmg3VFlrRDZCWElFSTBJbGhjampvMnZCTDNidGljWC1BU2VFR0dqUVBkVkVMLVBINUZkMVQ1UXVnaFBpQzNiMTdtcjQ1Y1NUdmxweGZv?oc=5</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -7098,12 +7098,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Abierta convocatoria para estudiantes quienes recibirán $2 millones mensuales por ir a la universidad</t>
+          <t>Colombia lista para los Juegos de Invierno de la Juventud 2026 - EL INFORMADOR - Santa Marta, Colombia</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>icetex.gov.co</t>
+          <t>EL INFORMADOR - Santa Marta, Colombia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Santa Marta</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -7126,7 +7126,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNT0x5eFk2VFI4TjZyS0I4Wk55RzNuZFl6R3lWTlNOWlVEVFNSUFp3d3hTeU1mUU9JN1hWdHgyYkloUE1xVGctblpGZVZsOHI4cVZLdlZmRnQtZklkOWsyaUlsM0lLRkRxZ2F6dTIzdmRyQ0UwQW82X0djWkpiRDBrUVFVYUt4ZkF4dS1VOWRkbjIwbXBIRERpcVBBcm9OLXlKVUswSHItY0hEYzF3dGw4ZVBFdjZHcmQ4YUJnYWo3OTU3OU12dEtOYVlOZVBCY1Z5Y1VSSzM5WmVpUQ?oc=5</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -7137,12 +7141,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>80 adolescentes vinculadas a Bienestar Familiar reciben formación en salud menstrual - Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Armenia posesionó a los nuevos Consejeros Municipales de Juventud para el periodo 2026–2029 - Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7152,12 +7156,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -7167,7 +7171,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZllZb2c2OS12UW5RLU9YQWJyclk5dEtzdHhwNDFybVVnOTJ3LW5sTC0wM1NoTm9mNEN4eDIwYWFUTGFsTnYxQld0MHVtdGFYV0JWTVBaM3JiU3hhQkRMV0RxbWZwbENoNE1MaVUyZGYwd3RmOUJFVU41eUlMVG15a3BNWEZ5akdJWWVvcGtxTW9LdEtGUXE0ckVrSG5NYjBLaVRxTXgxaGp3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMVA5RW15YWg0b1ZqdVltdnJETFVFcW82bjJ3TmJQUXRMM01uMFpJTUliTUVkczFXVm9kdGlZdnBlR3NTR1FWRGlOck5VOFZTTC1UaEFhQmozd0EzZllJamY2RHBKeXBsTGFTMWl6QUVzRHBqWDdXaTRkamxhQzRaUG9DSFpnQllQUUtaMFpIR0tJYTNmQmJTVnN2cDNiNGtmZUlHdVg0bi1lNTZrY2JfbmpOM24wTlNKTkxGNFhZU20waDAzLTdGNDRsSm1oSVI1N3QyTHlpazNlY2tYRzQwTGFYNA?oc=5</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -7175,17 +7179,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IDIPRON abre inscripciones a talleres gratuitos para niños y jóvenes en Bogotá - City Tv</t>
+          <t>Actividades en Bogotá para niños y adolescentes gratis en enero - Colombia.com</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>City Tv</t>
+          <t>Colombia.com</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7195,7 +7199,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7210,7 +7214,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPcjJHT1RUMjN1bnRiNExKMlc0T2xKY3dGWTBCaWt2QW9YaEZnV19yMl9uai0xd3oxWFFkclZCb0RUSVZiRzNoQW9PYThKR2tBV0VwSzJyOU1Ya0Z3RE1LZ1N3MXhYY1JqWkRoU25IQ0RxQXJ3cE9ZMDdrcV9JTlY3X1hyZkNkN2lRMGhENGRFcmlrNHJqTnFoanhyZmJEeEFvWGV6bkJrM3dISGpHaG9DOW9JUWNCcFJIaGppa3cwTHB2MklnVk9HNWZwUk5Gek5pY1BwVldLb2VCUkhrc0dv0gHnAUFVX3lxTFBVcWZtM3c5N3VLVFZ0VFJhb0xSLTZLVjVWdE1qWW1Jd1B1bGtEUkphZnlTNjVCaVJUdHNlYngtRVhtempvSjM3V0puMTMzZGVGejhuZm9nVkxRR3QtQ25mRFVjQUNvbGFBbkZqdG9pQzFVSzhDUmtWODZMQWYzWjVZRjJzdjlxN2FLX3daclVDNnNsall0eGRrTzNIb00weHNHMDNwM0pBQk4wM0lTQm5yX3BQRUlfNm5YYVNxcTdOeTRCc09kMUpGSWFxR01yWDczLXFGaWw2d3FNbk92RjBWQ2tvdVBwbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdVdPZUt4NUl4bDJxN1NGSkJoMlJmSGdickotNUVPdHlPN1czS3dXUEFnbEtUY2szR0drY3ZWZkxFcEVaOXFtUF9VNDlRcVNST0RycnlkSHp3YWJ0SGd6V0ZPVWs2TWt1UHBYQWI4ajNkQnYxNEhsOWo0YjB1a3NIQ3k5SXRCNDZHZkZ6Rm1hdDkxZFc2UlU5amp0bElHOEhjSl9pVFhqOS1hSlNOWHp5VEtn?oc=5</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -7218,17 +7222,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>80 adolescentes vinculadas a Bienestar Familiar reciben formación en salud menstrual - Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7238,12 +7242,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7253,7 +7257,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZllZb2c2OS12UW5RLU9YQWJyclk5dEtzdHhwNDFybVVnOTJ3LW5sTC0wM1NoTm9mNEN4eDIwYWFUTGFsTnYxQld0MHVtdGFYV0JWTVBaM3JiU3hhQkRMV0RxbWZwbENoNE1MaVUyZGYwd3RmOUJFVU41eUlMVG15a3BNWEZ5akdJWWVvcGtxTW9LdEtGUXE0ckVrSG5NYjBLaVRxTXgxaGp3dw?oc=5</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -7261,17 +7265,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Abierta convocatoria para estudiantes quienes recibirán $2 millones mensuales por ir a la universidad</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>icetex.gov.co</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7294,27 +7298,23 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
-        </is>
-      </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Así inicia el calendario escolar 2026 - Ministerio de Educación Nacional</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVDhlQmp2WFB1ZVZYS1Y1TzZEWkxhcWlpLUFEMXd2eXdELVRzSkVZSW5BR19rMlJTenpPS2d1Z2l1V2Z5VWxlRmpJaW1wZjJOem9fVjNMSlVKTFhZQTc0R05PYkxzbjRoVFFSVWt4aE16Y0JDM3prbVFLUUNscFpiZzdIRWw4TGRlWE1qbUwwQnJ5TmxsaTRZbXlzcGNnblhEOTJXZzVudTNHdw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -7347,17 +7347,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>La crisis de los colegios privados no se detiene: 35 instituciones cerraron en Bogotá para la vigencia 2026, ya van más de 400 en seis años - ELTIEMPO.COM</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7367,22 +7367,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSTN2aW1qSHhkQlJ2aHJNcHltQWxFaVlMZGk3MUNYdWk5YVRxdDc1WkNoQVQ0QjFUMHdERjNhd3kyOUNFbnJSVmdJd3psenZSS21Rb01DY1RLX2lTdkFqaHAzZ0RUekVFZU1zek1jRUotOWJ6T2dyQlN6QjFrRHY1Z0F2enRCUUtHS05TV3lMc1djQlJCeXlxdEhjWWloUGZhZjRMeDlseHVSUjAtS2NZWHdzY2czdm1USS13b213QXJtNHJPbnVldnhoNGNrNUk0bnZTTld4cy1KRUFoYVBnYVVxeWZoS2doUFRyMEtPRmlNZUhPLU43VmlFVUczelVoLXpYa0xYYkRSM3BWdnFPWk1sb9IBmAJBVV95cUxOWnZBMkpVRVNrOXFCcVAzczdmZEw4d1JrX1FvYkFXMXh6Y042dTdpQlhCVVQwLUNwZHF3YWVuU3ZidFl1eFM2Uk1HT2s3djZnWFYzMWl6NHlaYkpnRW9HSE9JWjBVWVpiY1FHbjVzLXBlbkNON09MYWVCenNVdXNPZXBlNE9BX2ZiZ1paendNOUVQeEp4SWZ6Umx3cXVCUGdyRFpmTWZ2M0Z2YlFIakNzc0lQelBoNVFWRmMzdnFJTmlGZVptMFFhSVNoZHkxM1lpQUIzUDZ0YTdJdVlOQlBrTWJhUExyblBRdklJMU5JV1g0ZmdCZ1pVWUx0YzJaUmdRX2tSYWNjWXZudnRJUGZ3cU9BX2VNVGxl?oc=5</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -7390,12 +7390,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7410,22 +7410,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7453,22 +7453,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Estudio advierte sobre el uso de pantallas en menores de edad; ¿deben niños y adolescentes estar expuestos a ellas? - elpais.com.co</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>elpais.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNODE5UmhRcnUwTnJXb3B0aVNXMXRod0lXQmtTcWZoODdYVHJtTzVObER5UEpiSnBCbTJIaDJUN3lONnZEbkdNaXdvMmxvX3hNTVp5dGtrUld5NUVrZVBsampEenEyakpxQWJOYldrdUhPeWM5UVFUVk1IbDl3VEw5cEF1MnNRSnNrUnVkRnpTcDhiOUdUSzUwNGRjVHdKamsxeklBVzl0dzZSZ05FRFpuXzBySWVYY1o5YjBjbXg1MlRSUVlGaWtaeTQwM2ZrQzhIMHFlY2VFM0xVY0NiWFZ4Q2ZYczlVd1JGTHNadmZn0gHzAUFVX3lxTE1rQ2pPNXZMVm5rc0FVdExOa0xJVl96TEJIRmZTXzhfQ3hoY21NaTRHalNUM1JsMHMyZ1Q1bVNSNlpzdmkwS1BhWE54ZXlnVG9rdzlBczZaMlFfeUxBc0ZZQmQ5NUo0WThLVW9XNlZkeGxiOF80Rkh6S3hvV21yczVReWtOVlltNlV4dXl0QjhueDJKZ1lBaGpvTUJwQlc5NkV0OWp2UDc3VGgtYWpEcTdRb05WQkRsRWZ1WlhTcjBIeUJPM2ZHZDhSQndRM194T2dXeVRTSDBxRXBqLXhGd2g5UkVoQnlMeElsVUhuUm5jbS1VYw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -7524,12 +7524,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
+          <t>Así inicia el calendario escolar 2026 - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVDhlQmp2WFB1ZVZYS1Y1TzZEWkxhcWlpLUFEMXd2eXdELVRzSkVZSW5BR19rMlJTenpPS2d1Z2l1V2Z5VWxlRmpJaW1wZjJOem9fVjNMSlVKTFhZQTc0R05PYkxzbjRoVFFSVWt4aE16Y0JDM3prbVFLUUNscFpiZzdIRWw4TGRlWE1qbUwwQnJ5TmxsaTRZbXlzcGNnblhEOTJXZzVudTNHdw?oc=5</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Confirman cambio académico en los colegios para 2026: Estudiantes estrenarán nueva asignatura por ley en Co... - redmas.com.co</t>
+          <t>La crisis de los colegios privados no se detiene: 35 instituciones cerraron en Bogotá para la vigencia 2026, ya van más de 400 en seis años - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7587,17 +7587,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOOUFOa2tMOGxIRnZxRkV4d1NjaXRZdzZBc25VdGhZM002c2JLQVhORmZQRjVXeUNPbVNSaVFlRzBvb3FTc0RWajcwRkM0OGNyZi1ocHNuR2Q3dkRZbUIzSEdtSzBYcUNsNEF3Nzc0S1hOT2ZHMnZOTnZJdXgyQmIyWnhlNmdOZkU2alBTTnNhaWNnZGE4d2ltUDBOZGtZUFRRN0RGbXljUGRMLUZzbl9FdTBDXzk2di13Zk52MDR0T3I5QXlaNlo2bWNqalVtLWp4Ri1uNWZSNG5yVnJaalZiRDN0cFprNVpwOVdkRDVn0gHzAUFVX3lxTFBPb1BUb3RCTHdMbjhXcTdmUF9GSDVkUFJqd1JxZXhkR0w1cXRUUTl2NXVSN3dQOFRTWk80eEhudmN1bHJmT29HeFRMSWU0dlJnbkU1QkJpbkM5M2hmYW14c19JNTZ4dWV5eEFWcFBISXNYenlWN2ZFMVZLV19EUmVFNHBwQU9aeU5ORS1Oc0ItNElXV29MV3hjRzdVMHY5SmJSM2hPRmg0LTNheXBWRmJmcEdsa1ZMZEg4LXZtQmZBeml2QnRQS002RzQ4NmgtTjRRbHJ4QWpVcEhTMVdGdTNFTkVoSnhVVkpXWUhxaDR3VGQxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSTN2aW1qSHhkQlJ2aHJNcHltQWxFaVlMZGk3MUNYdWk5YVRxdDc1WkNoQVQ0QjFUMHdERjNhd3kyOUNFbnJSVmdJd3psenZSS21Rb01DY1RLX2lTdkFqaHAzZ0RUekVFZU1zek1jRUotOWJ6T2dyQlN6QjFrRHY1Z0F2enRCUUtHS05TV3lMc1djQlJCeXlxdEhjWWloUGZhZjRMeDlseHVSUjAtS2NZWHdzY2czdm1USS13b213QXJtNHJPbnVldnhoNGNrNUk0bnZTTld4cy1KRUFoYVBnYVVxeWZoS2doUFRyMEtPRmlNZUhPLU43VmlFVUczelVoLXpYa0xYYkRSM3BWdnFPWk1sb9IBmAJBVV95cUxOWnZBMkpVRVNrOXFCcVAzczdmZEw4d1JrX1FvYkFXMXh6Y042dTdpQlhCVVQwLUNwZHF3YWVuU3ZidFl1eFM2Uk1HT2s3djZnWFYzMWl6NHlaYkpnRW9HSE9JWjBVWVpiY1FHbjVzLXBlbkNON09MYWVCenNVdXNPZXBlNE9BX2ZiZ1paendNOUVQeEp4SWZ6Umx3cXVCUGdyRFpmTWZ2M0Z2YlFIakNzc0lQelBoNVFWRmMzdnFJTmlGZVptMFFhSVNoZHkxM1lpQUIzUDZ0YTdJdVlOQlBrTWJhUExyblBRdklJMU5JV1g0ZmdCZ1pVWUx0YzJaUmdRX2tSYWNjWXZudnRJUGZ3cU9BX2VNVGxl?oc=5</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -7610,12 +7610,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Los jóvenes creen en la democracia, pero ven retos en su funcionamiento en Colombia: estudio de Cifras y Conceptos - ELTIEMPO.COM</t>
+          <t>IDIPRON abre inscripciones a talleres gratuitos para niños y jóvenes en Bogotá - City Tv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>City Tv</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7625,22 +7625,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPNjZKLUxUTlYxcm5RdlpaWk5mYjg4cmo4OGhFNkx1TWViYjZpV2VpN1JDdWgtckFxN05TVF9MbU9IVGQwNjI4WFlDajhjMjFEZl83SExwLVNoazBrcHVQMHhiVm51NGRnSkZBUGR1ejZibmJvRHhwbUMwVVQzUlFVZjRqWUh2ZzRVeDl1VFBfMFRYTlgxbmZzTjY5ODRPS0xPR25WSFF0aVpEQ0RVMnpaMVRGcjlyQVdYbkVQMjdNVm44QXR3TmQ0aC1WdkluVGF0WHNaY2RUXzRFbV9pTER4RjZoUFQxVUd3c1lZblM2cUZid3Bhc2FMOHhJc0RZVGZJbEF3YmowSUgySEHSAZACQVVfeXFMUGF5NGVXT2o3YWt3YmZwUG9GTXRpTFhYanhCR28wcWQ4LUJrd2kyRW43NTlZcklraXhCRlFFSXBxY0I0VFJoWllWZVBmNGczQW43UEZjSWl2d1hLWk15TlFNX1k3TUZGUkxMcy1PQWkyWFJWNTVvdHU1MHdhWWY3UkUwd0VRUklHTVkzQnFzaGtSZmdLWk9TblZhMmpWdU5Rc0thNXdzeHJKaGFqbEgzNUpYVzU0MEUtYkZjTEVtNElsYXV1MFY1djl2bDFMcGZ1VTBqaGYyV1UtMnZ1T2RVbGJFeHk0VDQyTGxmbnJLOU5ZVjhkZ2hBMlFxRFdkdkFLaXhBbUNqVEFVa21iNy1uang?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPcjJHT1RUMjN1bnRiNExKMlc0T2xKY3dGWTBCaWt2QW9YaEZnV19yMl9uai0xd3oxWFFkclZCb0RUSVZiRzNoQW9PYThKR2tBV0VwSzJyOU1Ya0Z3RE1LZ1N3MXhYY1JqWkRoU25IQ0RxQXJ3cE9ZMDdrcV9JTlY3X1hyZkNkN2lRMGhENGRFcmlrNHJqTnFoanhyZmJEeEFvWGV6bkJrM3dISGpHaG9DOW9JUWNCcFJIaGppa3cwTHB2MklnVk9HNWZwUk5Gek5pY1BwVldLb2VCUkhrc0dv0gHnAUFVX3lxTFBVcWZtM3c5N3VLVFZ0VFJhb0xSLTZLVjVWdE1qWW1Jd1B1bGtEUkphZnlTNjVCaVJUdHNlYngtRVhtempvSjM3V0puMTMzZGVGejhuZm9nVkxRR3QtQ25mRFVjQUNvbGFBbkZqdG9pQzFVSzhDUmtWODZMQWYzWjVZRjJzdjlxN2FLX3daclVDNnNsall0eGRrTzNIb00weHNHMDNwM0pBQk4wM0lTQm5yX3BQRUlfNm5YYVNxcTdOeTRCc09kMUpGSWFxR01yWDczLXFGaWw2d3FNbk92RjBWQ2tvdVBwbw?oc=5</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -7648,12 +7648,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7673,17 +7673,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -7691,17 +7691,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>La lista de útiles escolares que está prohibido pedir en los colegios de Colombia - ELTIEMPO.COM</t>
+          <t>Estudio advierte sobre el uso de pantallas en menores de edad; ¿deben niños y adolescentes estar expuestos a ellas? - elpais.com.co</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>elpais.com.co</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQzdnLVlLd2xJOHFWaGxaMzE5UVFSUWNRSGotUU1QRTNnaGxjQV9CN3RxVzBvZGU5aUxrdGpiQ2hVTkpqMEVGS0xad0JwVWhVNDdiZWt1eF9OZVNqRE9RRHRFTGVmbmFPWDhNWVlHR0xjV2xsR2ZCd0JrcVNmaGdneWxibjJjdkhsMnNwWThGVlhiX0Jfanc1YVpZOUZqUUttZm9kbDlaNHEweHJpU3B1Y18xRzdieWd1enN3eHVEZ0lUbm5sLW1j0gHMAUFVX3lxTFB6djRKRmdOdXpUVDFzSWY1MUNpTlAya3VreEZfM196VENfYWhVZ1g3RUJveVlOY0ItV1RlellpRTJPaXJWdVdYdTFwRUtST2lCdlBTbVM2REFvYVpZODEyWm8zTGpkSXNESl9xdTI3OEdmbndpZjIyNmFudWFYTFozOWozTEdvWERVQmJTMUc5T2RDWU1lSDhSSk1iLXRiMTFoLVoxRDFwckRmXzRKcGF0SDNHd1I3MVpyOFNHc0ZVcjBmVFV1bnVXdXVJNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNODE5UmhRcnUwTnJXb3B0aVNXMXRod0lXQmtTcWZoODdYVHJtTzVObER5UEpiSnBCbTJIaDJUN3lONnZEbkdNaXdvMmxvX3hNTVp5dGtrUld5NUVrZVBsampEenEyakpxQWJOYldrdUhPeWM5UVFUVk1IbDl3VEw5cEF1MnNRSnNrUnVkRnpTcDhiOUdUSzUwNGRjVHdKamsxeklBVzl0dzZSZ05FRFpuXzBySWVYY1o5YjBjbXg1MlRSUVlGaWtaeTQwM2ZrQzhIMHFlY2VFM0xVY0NiWFZ4Q2ZYczlVd1JGTHNadmZn0gHzAUFVX3lxTE1rQ2pPNXZMVm5rc0FVdExOa0xJVl96TEJIRmZTXzhfQ3hoY21NaTRHalNUM1JsMHMyZ1Q1bVNSNlpzdmkwS1BhWE54ZXlnVG9rdzlBczZaMlFfeUxBc0ZZQmQ5NUo0WThLVW9XNlZkeGxiOF80Rkh6S3hvV21yczVReWtOVlltNlV4dXl0QjhueDJKZ1lBaGpvTUJwQlc5NkV0OWp2UDc3VGgtYWpEcTdRb05WQkRsRWZ1WlhTcjBIeUJPM2ZHZDhSQndRM194T2dXeVRTSDBxRXBqLXhGd2g5UkVoQnlMeElsVUhuUm5jbS1VYw?oc=5</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -7734,17 +7734,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Medellín tiene nuevo Consejo Distrital de Juventud: este martes se posesionaron sus 23 integrantes | El Colombiano - El Colombiano</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUjhnNlN4LXZ6YjM1V2xra3dtSUhLTERUemk5YlI5QlNKR0R4NmZLWTRwZTFRNnB3ZzNNejZoWktZdnVHQnZBWjZuY1otQTNBeFg3cWRnLTBpeW5KU2FOcFZLODdsUVYwSTR3Nl85eklDVXowVWloSVRZeEpOTnkySl9jeThrdUNCQW1mXy0ycnNNRktaSHZ6cWlwVjRpSE5ESDdKb0hvQ25tdmlJdzNR0gG0AUFVX3lxTE5LZ1VUZm1rYUdOUUNXSnpHOFN6MjlxWHYzNjhkZnlYWXpUNFdhczNZRzlkTTltbmJNOS12b3RoV2lNVjhkZUtRbmtaVloxSWVlRUhCNnJ6N09iaElvbkNLQTdVYUp0cWMwZS1YMXdKX0toX1FxdFk4NlJKbkwwT1A3MXU3VDc3LUJnWDZhd0l6dDk0ME9Hb2xwQzhxZm5DM2ttU3F6ei1KYzEwZ3JRR0JRX1JFUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -7777,17 +7777,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Confirman cambio académico en los colegios para 2026: Estudiantes estrenarán nueva asignatura por ley en Co... - redmas.com.co</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7797,22 +7797,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOOUFOa2tMOGxIRnZxRkV4d1NjaXRZdzZBc25VdGhZM002c2JLQVhORmZQRjVXeUNPbVNSaVFlRzBvb3FTc0RWajcwRkM0OGNyZi1ocHNuR2Q3dkRZbUIzSEdtSzBYcUNsNEF3Nzc0S1hOT2ZHMnZOTnZJdXgyQmIyWnhlNmdOZkU2alBTTnNhaWNnZGE4d2ltUDBOZGtZUFRRN0RGbXljUGRMLUZzbl9FdTBDXzk2di13Zk52MDR0T3I5QXlaNlo2bWNqalVtLWp4Ri1uNWZSNG5yVnJaalZiRDN0cFprNVpwOVdkRDVn0gHzAUFVX3lxTFBPb1BUb3RCTHdMbjhXcTdmUF9GSDVkUFJqd1JxZXhkR0w1cXRUUTl2NXVSN3dQOFRTWk80eEhudmN1bHJmT29HeFRMSWU0dlJnbkU1QkJpbkM5M2hmYW14c19JNTZ4dWV5eEFWcFBISXNYenlWN2ZFMVZLV19EUmVFNHBwQU9aeU5ORS1Oc0ItNElXV29MV3hjRzdVMHY5SmJSM2hPRmg0LTNheXBWRmJmcEdsa1ZMZEg4LXZtQmZBeml2QnRQS002RzQ4NmgtTjRRbHJ4QWpVcEhTMVdGdTNFTkVoSnhVVkpXWUhxaDR3VGQxQQ?oc=5</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -7820,17 +7820,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PTIES: La apuesta del Gobierno Nacional para llevar educación superior digna a más de 27.000 jóvenes en las regiones más remotas de Colombia - Ministerio de Educación Nacional</t>
+          <t>Los jóvenes creen en la democracia, pero ven retos en su funcionamiento en Colombia: estudio de Cifras y Conceptos - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQV190TVQ0UHhYOWIxUGNuYTdTaWNLbW5xWUtBVFMtUEl4cmUtNmlTYzQ1QnNVUElkUXZfSFJ2MlgybzVjcFNTbXdDX2FWbDV1cWZ5WnpLR1Q4MXZGNGttTDhLWTJtNXlkenc3X01sdUlXbEh5X2dwRzJ6Vk1rWWRlZXNEVVpPMHJTS05QM0NsdkZGVm9jUjd5VG1aekdjdG1abE9OVXFQZTdDakxvN2pka0tkNWFuQUpVS3pMZGZxMDFqcUJRdWVyaGF2Uk9DWERYREozQ19fS01tNzNhUzZBOXIyOVBfazFjak1wbjN1U2FjOTk2YmhrSzM2eW54Qi1lUFRtQkpCTHRJSDJvcUxLTUhSSjdUeFkwNlE2SmFZS1dfU3JaM1NtRi1GR0xfRU5RZFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPNjZKLUxUTlYxcm5RdlpaWk5mYjg4cmo4OGhFNkx1TWViYjZpV2VpN1JDdWgtckFxN05TVF9MbU9IVGQwNjI4WFlDajhjMjFEZl83SExwLVNoazBrcHVQMHhiVm51NGRnSkZBUGR1ejZibmJvRHhwbUMwVVQzUlFVZjRqWUh2ZzRVeDl1VFBfMFRYTlgxbmZzTjY5ODRPS0xPR25WSFF0aVpEQ0RVMnpaMVRGcjlyQVdYbkVQMjdNVm44QXR3TmQ0aC1WdkluVGF0WHNaY2RUXzRFbV9pTER4RjZoUFQxVUd3c1lZblM2cUZid3Bhc2FMOHhJc0RZVGZJbEF3YmowSUgySEHSAZACQVVfeXFMUGF5NGVXT2o3YWt3YmZwUG9GTXRpTFhYanhCR28wcWQ4LUJrd2kyRW43NTlZcklraXhCRlFFSXBxY0I0VFJoWllWZVBmNGczQW43UEZjSWl2d1hLWk15TlFNX1k3TUZGUkxMcy1PQWkyWFJWNTVvdHU1MHdhWWY3UkUwd0VRUklHTVkzQnFzaGtSZmdLWk9TblZhMmpWdU5Rc0thNXdzeHJKaGFqbEgzNUpYVzU0MEUtYkZjTEVtNElsYXV1MFY1djl2bDFMcGZ1VTBqaGYyV1UtMnZ1T2RVbGJFeHk0VDQyTGxmbnJLOU5ZVjhkZ2hBMlFxRFdkdkFLaXhBbUNqVEFVa21iNy1uang?oc=5</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -7863,17 +7863,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7898,29 +7898,25 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
+          <t>PTIES: La apuesta del Gobierno Nacional para llevar educación superior digna a más de 27.000 jóvenes en las regiones más remotas de Colombia - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7930,12 +7926,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7945,7 +7941,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQV190TVQ0UHhYOWIxUGNuYTdTaWNLbW5xWUtBVFMtUEl4cmUtNmlTYzQ1QnNVUElkUXZfSFJ2MlgybzVjcFNTbXdDX2FWbDV1cWZ5WnpLR1Q4MXZGNGttTDhLWTJtNXlkenc3X01sdUlXbEh5X2dwRzJ6Vk1rWWRlZXNEVVpPMHJTS05QM0NsdkZGVm9jUjd5VG1aekdjdG1abE9OVXFQZTdDakxvN2pka0tkNWFuQUpVS3pMZGZxMDFqcUJRdWVyaGF2Uk9DWERYREozQ19fS01tNzNhUzZBOXIyOVBfazFjak1wbjN1U2FjOTk2YmhrSzM2eW54Qi1lUFRtQkpCTHRJSDJvcUxLTUhSSjdUeFkwNlE2SmFZS1dfU3JaM1NtRi1GR0xfRU5RZFE?oc=5</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -7953,17 +7949,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Una generación que ora: el encuentro juvenil que revela otra cara de la juventud colombiana - elpais.com.co</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>elpais.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7973,12 +7969,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7988,7 +7984,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS18wNnQtbks1R2xqVWJPWG9ubE5wWGREQURGMy1PRi0tUVN1ZWxrMG1Na1BmRTA4aUlob2hwbEdnSTh1ZllTaXgwOERJX29kUy1UaUFRV2lOd2V4enp2bUE2QnBIRmpvbi1GNVpIN2dWRE1FS3BaV2hENFA1RlVRVmdRbVdUVDdNNi1hdUNVcjVmVXllZldCNU1pMGRZZ3E1X2NRdUwwbXV6RUJKUHBLUUdycHktb3JnMzdpNndJdDhLTmotQTdEVEtsZ1ozUWo20gHWAUFVX3lxTE1PRnZubjVMelJsTDBXR3RSWllXcmhNOUtIaEh1SkxpSnY2eUViQkRVZG5CMjRUV01YbHN6bTV0eVNwa2xxYk9KdTR0NnIyTmVEel9OQzgwUWFDMjVvNnY5WGZJcjRkM2VQT2ItRWRTQ0ROTjhMNkgycGN4S3l6WS0yNm1SSTB0Yk01X2U0R195b2I5NWNXZWhZcUxQbUltX1VXZHZEQnhmWktOdm5EeERnTm5UZkxxdy1EZndIQ3BNUnhHbjRGaXFlLU8xSzEwdHdTLW15VEE?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -7996,17 +7992,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tumban común norma para entrar a los colegios de Colombia: ley prohíbe que les exijan a sus estudiantes una... - redmas.com.co</t>
+          <t>La lista de útiles escolares que está prohibido pedir en los colegios de Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8031,7 +8027,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQbmd3SVJpUGFScGlabzdNY0J1UkV6S3RjMTBBX1g4S0ptY2hCR0pxTnY0RTcyYzZXM2NXcVZobXRCN1UteGYtMmFmclpBTDktOTdoLVN1UllpNGlNYXhsb1UyNzdBR1E5LTVLYXU0S0pSQTV5dGdUMDVfeUNvSDF0S0VNTWJDaTV3RTRLdWJZNE9MOTlyZi1NTFU2Y20yWjZLcVVFdDBOYUpkUW9NRUlBTDcweXNjR1V6c1RIZDZiYWtIZzV2aFhMT083MVBpaDdmQnZlMzVtM3lHSjNnV1JEMUlFcEM0UU9kNmIyeWVnUGJUeXdBMkHSAfsBQVVfeXFMTlpVazJZT3NxeHRwWllQd3dFM0ZsTDBEMldFRVFYTnZoZ2tmWkx6dzAtZVNzUnh2TWFtRXQ4RWtfWlA0eWkwQTNJeWlXWkF2NXRsUlRXd3RmREJRbmZjRTRneUREeUZ4ZzVHVmpCTXQ0d3dYZjVucnhMSzAzQ3BKZ2EyYzNna1VOdVNRbm1ua0pFRFBQb0dkMEdsbklyZ1BSTjhhdWpOT25zT1Q3b0hZMEhjRGQwNHRBZ3M5M29Jc1dIWkkzY2Y3TXdwWnRyeDVyYzJleXlyZExNY2N6Z290WFFScHJpVEhpdTNKTDNBenBpUjBXamd0ZWt5dGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQzdnLVlLd2xJOHFWaGxaMzE5UVFSUWNRSGotUU1QRTNnaGxjQV9CN3RxVzBvZGU5aUxrdGpiQ2hVTkpqMEVGS0xad0JwVWhVNDdiZWt1eF9OZVNqRE9RRHRFTGVmbmFPWDhNWVlHR0xjV2xsR2ZCd0JrcVNmaGdneWxibjJjdkhsMnNwWThGVlhiX0Jfanc1YVpZOUZqUUttZm9kbDlaNHEweHJpU3B1Y18xRzdieWd1enN3eHVEZ0lUbm5sLW1j0gHMAUFVX3lxTFB6djRKRmdOdXpUVDFzSWY1MUNpTlAya3VreEZfM196VENfYWhVZ1g3RUJveVlOY0ItV1RlellpRTJPaXJWdVdYdTFwRUtST2lCdlBTbVM2REFvYVpZODEyWm8zTGpkSXNESl9xdTI3OEdmbndpZjIyNmFudWFYTFozOWozTEdvWERVQmJTMUc5T2RDWU1lSDhSSk1iLXRiMTFoLVoxRDFwckRmXzRKcGF0SDNHd1I3MVpyOFNHc0ZVcjBmVFV1bnVXdXVJNQ?oc=5</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -8039,17 +8035,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+          <t>Medellín tiene nuevo Consejo Distrital de Juventud: este martes se posesionaron sus 23 integrantes | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8059,12 +8055,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -8074,7 +8070,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUjhnNlN4LXZ6YjM1V2xra3dtSUhLTERUemk5YlI5QlNKR0R4NmZLWTRwZTFRNnB3ZzNNejZoWktZdnVHQnZBWjZuY1otQTNBeFg3cWRnLTBpeW5KU2FOcFZLODdsUVYwSTR3Nl85eklDVXowVWloSVRZeEpOTnkySl9jeThrdUNCQW1mXy0ycnNNRktaSHZ6cWlwVjRpSE5ESDdKb0hvQ25tdmlJdzNR0gG0AUFVX3lxTE5LZ1VUZm1rYUdOUUNXSnpHOFN6MjlxWHYzNjhkZnlYWXpUNFdhczNZRzlkTTltbmJNOS12b3RoV2lNVjhkZUtRbmtaVloxSWVlRUhCNnJ6N09iaElvbkNLQTdVYUp0cWMwZS1YMXdKX0toX1FxdFk4NlJKbkwwT1A3MXU3VDc3LUJnWDZhd0l6dDk0ME9Hb2xwQzhxZm5DM2ttU3F6ei1KYzEwZ3JRR0JRX1JFUA?oc=5</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -8082,17 +8078,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>¿Por qué ahora la rebeldía de los jóvenes está en la derecha política? | El Colombiano - El Colombiano</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8107,17 +8103,17 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNX0hZTUdNcFNvMEhnMk1nVF92WlA2UUlHT3o4bjdVOHZzRWJRSEp5NEtwUl9fNFJiNDZxVWVmZjVfVTBUajVGZk5nd01FVEJWa1ZRZFphVTVVcERyY3RmRldkelhpdTU0UTNRRWItc3lDMUFHTEJ2MlJzLUFJSWVoWW9WR1dERTMwUUpCdDZRX2tkd2ZBa3pLSFd4Q1J6dEZoalJmTnJ3TElRTG94Y3BSMzd6LUFNa0Zh0gG-AUFVX3lxTFBnYU0xVTI2SVY1cDNXQlRQVjZqWmRUN285Sm1MdWNybTZlZXJCb0t3NXZMaFdIMVlOV3pDd1dWUllGRHdRRFhLWE40WjM3NDIyVlhXamdiNVZ0blZxamM2YlNSdFcxdUFadEpzZGQzZkJmaHdpczZMU3VmekJ0ZEVtaFBBYmN6a0QtdGxGQlJqMG1SUjU0RFdMTlo5UXNBQ0RwbE1WVkptZzVKTnY4Q3E5MFlneEVnWU5rd0dqZUE?oc=5</t>
+          <t>https://www.alertabogota.com/noticias/local</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -8125,17 +8121,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Confirmado el calendario escolar 2026 para alumnos y docentes en Colombia: cuándo habrá vacaciones, puentes y - AS Colombia</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AS Colombia</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8145,12 +8141,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -8160,25 +8156,29 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQa0s1c0hqMDkzOFJDMUtjbjhPcWw1NXhYSWtVMFRfeXhZcDVSYmJfUEtOTXRIN0FvaE5tZ0ViWWNCV18wOENXWXJiMThtX1Vvc0NLU1NHSVpiS1ZrS3hlY3RtaWdwdHFvelR0RVRuQjNISHFwMXFwaEhFcjNmazdyVjlVTGV0Njh0aU9Fczg4aVlHaE5CUkRPS0ZVaDVkdGtnZjhhT1R4em1RVlRLZ3dBbHVoSTNoTGlWQWgtRkpnM1RvSHc3eTRmdG13V0xteVlOaFM2SWFaWHpKdkNfYkh1Snl5UkRzcWhodEFuZUMxbHc1b0Fp0gGIAkFVX3lxTE5CRjlRbHFUdVRNYjV3aHhCeVNHalc2NE5XTkFrT2F6d21FQzR4RFZITFJxemdta29RTS1teWpNVFpHbWgwaXBIZENYNTk0OXVDLWliNW9nRmhubkZoQTVkSkpjOWZuSlJKN29XMEp0REp2RERWVDZYM1dIbnpOVUc1QmN2ZnlpRU45NDdGUnhPXzgyYmQ5WGlfb2g5ZElNVDJ0cGlGY2FEbHdnM1lyVUFNT19wOWFYOUFjZzRXX1M3MEdZa29adGE5RXM4eXJ5NWVhVFhmY0JFWjdXQk9NRVc0NDM1SVJWWmh6Y2p1VzRZSWRreURoYlNkTW5nal8tQ29PYnBZY0Z1Rg?oc=5</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Menos ninis, mismas preguntas: ¿Qué hay detrás de la reducción de jóvenes que ni estudian ni trabajan en Colombia? - ELTIEMPO.COM</t>
+          <t>Madre denuncia a Karina García por grabar a su hija menor de edad sin autorización durante una transmisión en vivo</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPWHZpSkpIdjZKRXllSDdtTHd5dGw0LW9kaC1QUTFLRXJnYkNraHJvVkRMYzZlbzJkaURkWDJhUk1OQUlydkk0YXczaEZLWnhoV3JhT2xFbFJwRXpEYVA3MUtYR0t2MzE3N0xKcVVFVjdhNS1fbm1LU2NFVkc2d1ZOZ3JLNUl1aU05UFZEODR4dWYwNFk5RnJBXzdhTmNuZmVqZUNmYmlwU3BweWRzX1ZhQjRGVm1QaGx2aDc3V0Q4UlZheWg4ZlJoTTZoTU5GRnYwYURuVHA1UkpLSElMNHRTajhyUEZUOG1OUDNCVEpLVUJrZ0F4TGlqVHdFaU5Eemc2MlhNb2Rn0gGLAkFVX3lxTE9OVm9vTnJlSlp0anZ1bEx6T1lwYjMySWUxNHpwT18xU21IQnlQcUVMN0JlX0F1TVhwM0thcWdUdWVCMVFYSm02YmpxMTF0a3BXR29rNVVXN3BqMi1CdUlteW9uRVZJNFB4cWMxdDIxRnRVcW50NktsZmUzSTg5V3FZTGxvTkdQcWFodHd5SjFIWmFwVkZKaUp5UnAtMkxUTkN3V08zSkNJRklXYTV6TnhNMGM2UGRhRkNFRnFoNnVudThXWnpXbHJnZUg0bndtVWs5TlFnU2FkOGNZY2hvS1FhaE5sNldRdm9PTmVESmtObDZkblFRMWhBODNfMEdmVVhrUG4yQ2ZXSHB1aw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/12/madre-denuncia-a-karina-garcia-por-grabar-a-su-hija-menor-de-edad-sin-autorizacion-durante-una-transmision-en-vivo/</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -8211,17 +8211,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Colombia promueve estrategia de prevención de castigo físico en niños - Prensa Latina</t>
+          <t>Una generación que ora: el encuentro juvenil que revela otra cara de la juventud colombiana - elpais.com.co</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Prensa Latina</t>
+          <t>elpais.com.co</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWHBSeDA5d3p2OEN1Q1lGMHl6dEpxc002ckFoQ2NfS2xfNndBZWV2Nl92Rk03NTZaUmtPenpFSG51T1dpQWNsTlRiVmVBc0xzUUJHUEQ1RG0wMTgxaEIxQ3pCT0pzY1VxQ2ZTZTA1TF96UWtJYy1hTkZBdnliTzc4Y2N0VEtMM0VOdUFmZ080OVFiNkVKb0lkUTN3OTdQcGptYVpHWmdGbGpjTnBaelZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS18wNnQtbks1R2xqVWJPWG9ubE5wWGREQURGMy1PRi0tUVN1ZWxrMG1Na1BmRTA4aUlob2hwbEdnSTh1ZllTaXgwOERJX29kUy1UaUFRV2lOd2V4enp2bUE2QnBIRmpvbi1GNVpIN2dWRE1FS3BaV2hENFA1RlVRVmdRbVdUVDdNNi1hdUNVcjVmVXllZldCNU1pMGRZZ3E1X2NRdUwwbXV6RUJKUHBLUUdycHktb3JnMzdpNndJdDhLTmotQTdEVEtsZ1ozUWo20gHWAUFVX3lxTE1PRnZubjVMelJsTDBXR3RSWllXcmhNOUtIaEh1SkxpSnY2eUViQkRVZG5CMjRUV01YbHN6bTV0eVNwa2xxYk9KdTR0NnIyTmVEel9OQzgwUWFDMjVvNnY5WGZJcjRkM2VQT2ItRWRTQ0ROTjhMNkgycGN4S3l6WS0yNm1SSTB0Yk01X2U0R195b2I5NWNXZWhZcUxQbUltX1VXZHZEQnhmWktOdm5EeERnTm5UZkxxdy1EZndIQ3BNUnhHbjRGaXFlLU8xSzEwdHdTLW15VEE?oc=5</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -8254,17 +8254,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>17 son menores de edad y los casos se concentran en Montería y otros 16 municipios, según autoridades de salud - facebook.com</t>
+          <t>Tumban común norma para entrar a los colegios de Colombia: ley prohíbe que les exijan a sus estudiantes una... - redmas.com.co</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Montería</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPNFFpY29QRl9XdnlhQmdkZGpwZ3NCSDlqSkdtMHJXdU5ZTzhUd01JZUV1MVItMGZWZmd5R19nY2l5V3lQVW5TdjdicGprb0pXaG10aDdPWkw1NTJTM2NOTUtKQThuUS1KMUlWX1kwQmZDR1RaSnloU25HVllwRGh2UHRRZ0dGTDZ1UnFxRkF0eVhiS3JKdW1YVUp6WDlDb2Vobi1EaUU0aG1fQXN4QWwzQ09fVml4YTIzUUxQZFFOaGdtU3BzSHNzcWhYbEVvSHc0SUZkbGE3Q1lYVnBwZ3ctTkZabzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQbmd3SVJpUGFScGlabzdNY0J1UkV6S3RjMTBBX1g4S0ptY2hCR0pxTnY0RTcyYzZXM2NXcVZobXRCN1UteGYtMmFmclpBTDktOTdoLVN1UllpNGlNYXhsb1UyNzdBR1E5LTVLYXU0S0pSQTV5dGdUMDVfeUNvSDF0S0VNTWJDaTV3RTRLdWJZNE9MOTlyZi1NTFU2Y20yWjZLcVVFdDBOYUpkUW9NRUlBTDcweXNjR1V6c1RIZDZiYWtIZzV2aFhMT083MVBpaDdmQnZlMzVtM3lHSjNnV1JEMUlFcEM0UU9kNmIyeWVnUGJUeXdBMkHSAfsBQVVfeXFMTlpVazJZT3NxeHRwWllQd3dFM0ZsTDBEMldFRVFYTnZoZ2tmWkx6dzAtZVNzUnh2TWFtRXQ4RWtfWlA0eWkwQTNJeWlXWkF2NXRsUlRXd3RmREJRbmZjRTRneUREeUZ4ZzVHVmpCTXQ0d3dYZjVucnhMSzAzQ3BKZ2EyYzNna1VOdVNRbm1ua0pFRFBQb0dkMEdsbklyZ1BSTjhhdWpOT25zT1Q3b0hZMEhjRGQwNHRBZ3M5M29Jc1dIWkkzY2Y3TXdwWnRyeDVyYzJleXlyZExNY2N6Z290WFFScHJpVEhpdTNKTDNBenBpUjBXamd0ZWt5dGM?oc=5</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -8297,17 +8297,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>¿Cómo tramitar desde el exterior la salida de Colombia de un menor de edad? - Colexret</t>
+          <t>Confirmado el calendario escolar 2026 para alumnos y docentes en Colombia: cuándo habrá vacaciones, puentes y - AS Colombia</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Colexret</t>
+          <t>AS Colombia</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQc2xwX2xRNkc0anc2UGJqSEp0NGJrWGljRTVKUFJuTVFxVXJRTDRpdlFZTkd0eU9iU180X3RjUElYaUlUT25nVXU0NURtdzRCTTBqUkQ4UGUyUmJUQV9BdzBlRmNLNmxYa2xVVVlHMWZBVVN0SHZVOHVqazd2Rk9TcERwdnlwYWV3QTJPUVJQV2gxU1pJbFI0VW16TWlxN0NsOUpQd0cxNTh6QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQa0s1c0hqMDkzOFJDMUtjbjhPcWw1NXhYSWtVMFRfeXhZcDVSYmJfUEtOTXRIN0FvaE5tZ0ViWWNCV18wOENXWXJiMThtX1Vvc0NLU1NHSVpiS1ZrS3hlY3RtaWdwdHFvelR0RVRuQjNISHFwMXFwaEhFcjNmazdyVjlVTGV0Njh0aU9Fczg4aVlHaE5CUkRPS0ZVaDVkdGtnZjhhT1R4em1RVlRLZ3dBbHVoSTNoTGlWQWgtRkpnM1RvSHc3eTRmdG13V0xteVlOaFM2SWFaWHpKdkNfYkh1Snl5UkRzcWhodEFuZUMxbHc1b0Fp0gGIAkFVX3lxTE5CRjlRbHFUdVRNYjV3aHhCeVNHalc2NE5XTkFrT2F6d21FQzR4RFZITFJxemdta29RTS1teWpNVFpHbWgwaXBIZENYNTk0OXVDLWliNW9nRmhubkZoQTVkSkpjOWZuSlJKN29XMEp0REp2RERWVDZYM1dIbnpOVUc1QmN2ZnlpRU45NDdGUnhPXzgyYmQ5WGlfb2g5ZElNVDJ0cGlGY2FEbHdnM1lyVUFNT19wOWFYOUFjZzRXX1M3MEdZa29adGE5RXM4eXJ5NWVhVFhmY0JFWjdXQk9NRVc0NDM1SVJWWmh6Y2p1VzRZSWRreURoYlNkTW5nal8tQ29PYnBZY0Z1Rg?oc=5</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -8340,17 +8340,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Confirman cambio en las vacaciones de los colegios en 2026: Bogotá reajusta el descanso de los estudiantes - redmas.com.co</t>
+          <t>¿Por qué ahora la rebeldía de los jóvenes está en la derecha política? | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8360,22 +8360,22 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQb0NOTFo5Z0Z1V0ZCaHIxY0NiRHFwZWJHWVJaNGpWR0J0MUhFVTlIMlowdUVJWnNkTWdCSXQydm9kVTBvT2JLT1AzeVd2VTdxY1dVZzNFOXlTbXlBR1dzR3lfRG5fZzdRZUExbkU5bVlpU2pYRW9RWmNGWGZDMTA0S1p3UXNfdEsyQi1YS09oVGtnMVhxU0lueXdldW93aUwyaW5QNVJiT002dHZ0NzZkMmtQSWdBMUZRak1vSUdrakJtVHNTanI1RFVEeGJBdkxXcDdORDRzT3R5bHJaS1lrWlczaTBhczUyOFBVZ1VlOVVqUnFJdDl1ZmZ0djhFcHRLMUHSAYcCQVVfeXFMTXlGMTBtM3g4cnFEalRJNjA3SkxVOUhKRmlwWjhJTnFQOGtKRFdJNzhaSGcwS0czOEF4RmlBbHZYcF9wU2lsNVR1T2EtNUtsTVBmZlpYcTJLY2gxc3Y2Yk1XMXRFV1NLVU9nZDA2Rm1mWEVTUVZfSktaVy01WTc3Q2VXU09EbG1hZ3lhSUltVjUtXzAzZVpuZWpjMFNqX3lOUzNoVnltaVoxMnY4MGNfV0wzblE5Tk1GSXhfeFc3QzhLMVkzX2FsRUQtQnZYNEYtcVp0VTh6Yl93TEJNQ0RMMVlIUWp1Q3hrZ1hxaFJ6QlZQeVU1YmhwZHFiUE9BSVR4S1ZTbWNWSzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNX0hZTUdNcFNvMEhnMk1nVF92WlA2UUlHT3o4bjdVOHZzRWJRSEp5NEtwUl9fNFJiNDZxVWVmZjVfVTBUajVGZk5nd01FVEJWa1ZRZFphVTVVcERyY3RmRldkelhpdTU0UTNRRWItc3lDMUFHTEJ2MlJzLUFJSWVoWW9WR1dERTMwUUpCdDZRX2tkd2ZBa3pLSFd4Q1J6dEZoalJmTnJ3TElRTG94Y3BSMzd6LUFNa0Zh0gG-AUFVX3lxTFBnYU0xVTI2SVY1cDNXQlRQVjZqWmRUN285Sm1MdWNybTZlZXJCb0t3NXZMaFdIMVlOV3pDd1dWUllGRHdRRFhLWE40WjM3NDIyVlhXamdiNVZ0blZxamM2YlNSdFcxdUFadEpzZGQzZkJmaHdpczZMU3VmekJ0ZEVtaFBBYmN6a0QtdGxGQlJqMG1SUjU0RFdMTlo5UXNBQ0RwbE1WVkptZzVKTnY4Q3E5MFlneEVnWU5rd0dqZUE?oc=5</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -8383,17 +8383,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Petro refuerza su apoyo a los estudiantes de las universidades públicas con miras a las elecciones - EL PAÍS</t>
+          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>EL PAÍS</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNTGNKT1ZIVC1RXzM0MUt3T2prd20zVjVOaG45cEg2eHJiRTVYQnhPRTQwX1VlVEF1VmV6WVNuTWIwMXFzbEw2cC1tRzl2ME11YXh2QUdoSE41dlNzQlZDMXhWM3ByZE40R3lhMVVoLXJRQ0dENHJZcVBZeEtJbDExZFo0NkRoSTFZSm5XVkJrVmZkZ2RRU2VST1FvWVlwMm1QM21tSjNXNjJsdGxjTmZqSkk5d3dDMjhETzZFM2x1V3pGNnNUeWFGVVNBZWwwU2EtdVdnN0gyMlIzX0I3LVF3V2h4TE7SAfgBQVVfeXFMT0NMSnh2NDNyM2N6NkNvc2FRLVdYS2xHRnh6cGlSLUpWOTQyeUs5NkphOHhDMTFrT09uSDlETHoxbXFvYk45el84eGMzal9JbTExU0RjdXczcDRkcHNoR1YtZ1VyUUlnU0ljU3JwWFhIZXloeGI3bWhpOThQRjdJUTJ3QS16UXlLN3hrZHFRMFotTXhTQzhtNk1rQTZkQ0haR016U0JPVWM3RUFwb0JFSW1naEFtWUU4S0NSSXZWUjJjMjNWb1QzSWNpSkdSM1JYUGRjcXNRSjBZRzZWR3E2ekNEemxIalhqVWlZQ25acWEwdGU2OTlHRXM?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -8426,17 +8426,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>¿Cuándo inician las clases en los colegios distritales de Bogotá este 2026? Fechas y más - Bogota.gov.co</t>
+          <t>Colombia promueve estrategia de prevención de castigo físico en niños - Prensa Latina</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>Prensa Latina</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8446,22 +8446,22 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZTVQT2p4UFNyUjFyYnV1M2xEMXgyQVpqZE9OazBzUjJ2bmw3T09zMGpGY0JxcXRaSGNCVkFGbEtsaEVrekk1dDF2VHFLT3UtYTF3WmFHd2hBTVVZYkZDSG10ZlNRQVBrd0ljSjRWSmI5VGkyMG1qMVpOZV9IY1FtNWpod0VKVklxR3loT0dOOFFXQU5iUlgxb04xUFlfNk9Xb1hjNkFlNmltQlRVdEc5LQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWHBSeDA5d3p2OEN1Q1lGMHl6dEpxc002ckFoQ2NfS2xfNndBZWV2Nl92Rk03NTZaUmtPenpFSG51T1dpQWNsTlRiVmVBc0xzUUJHUEQ1RG0wMTgxaEIxQ3pCT0pzY1VxQ2ZTZTA1TF96UWtJYy1hTkZBdnliTzc4Y2N0VEtMM0VOdUFmZ080OVFiNkVKb0lkUTN3OTdQcGptYVpHWmdGbGpjTnBaelZn?oc=5</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -8469,32 +8469,32 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>¿Cuándo entran a clases los colegios públicos y distritales en enero de 2026? - El Espectador</t>
+          <t>Menos ninis, mismas preguntas: ¿Qué hay detrás de la reducción de jóvenes que ni estudian ni trabajan en Colombia? - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVGV3a0tQeW5uLVpJdlBBT3Rrc0NrUm9Va3pHY3NYMko1d1N4bjUzdjVYZ3ZjZWZpQ0xYak0yQVNLdFRsVXJxbnJMSVJVT3ZyaEZ4ZEZIU01RWVoyUHd6Q0hiNFdCMElNeXExYXVrQVJaQU8tN0RUMC0xZERQdFZ2aWo0UXQtZTZ5VmN6NE9YSjlhYUVGd01ycDBCaC1RMEhUcmk5TTdEekozS3g5Ry02SEVTOWprUdIBygFBVV95cUxQMlJDNFNLREl3U2ZaeXVGYy1GS2NmWlVydW1DX24wRE9NOVhBbzhqNWNzMmhTNEdTa0JFa281R1FVRUFfdjlUXzd2Nl8xTGxMb3JIaUVxOG1DTTBwRlluV1B3QVF6QTI1cEd1TTlVQlJiVWJkLWFFRFo1RlVsQjRMS2ZmTDhpUTY3bGdfRzlXWmliT2NybEFPcnRfaWJpX3UtazA0ekRpOFpOeU93TGNsOTV6Ynp3VkhKRnVPcmswemZHYnZNQUxrWHNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPWHZpSkpIdjZKRXllSDdtTHd5dGw0LW9kaC1QUTFLRXJnYkNraHJvVkRMYzZlbzJkaURkWDJhUk1OQUlydkk0YXczaEZLWnhoV3JhT2xFbFJwRXpEYVA3MUtYR0t2MzE3N0xKcVVFVjdhNS1fbm1LU2NFVkc2d1ZOZ3JLNUl1aU05UFZEODR4dWYwNFk5RnJBXzdhTmNuZmVqZUNmYmlwU3BweWRzX1ZhQjRGVm1QaGx2aDc3V0Q4UlZheWg4ZlJoTTZoTU5GRnYwYURuVHA1UkpLSElMNHRTajhyUEZUOG1OUDNCVEpLVUJrZ0F4TGlqVHdFaU5Eemc2MlhNb2Rn0gGLAkFVX3lxTE9OVm9vTnJlSlp0anZ1bEx6T1lwYjMySWUxNHpwT18xU21IQnlQcUVMN0JlX0F1TVhwM0thcWdUdWVCMVFYSm02YmpxMTF0a3BXR29rNVVXN3BqMi1CdUlteW9uRVZJNFB4cWMxdDIxRnRVcW50NktsZmUzSTg5V3FZTGxvTkdQcWFodHd5SjFIWmFwVkZKaUp5UnAtMkxUTkN3V08zSkNJRklXYTV6TnhNMGM2UGRhRkNFRnFoNnVudThXWnpXbHJnZUg0bndtVWs5TlFnU2FkOGNZY2hvS1FhaE5sNldRdm9PTmVESmtObDZkblFRMWhBODNfMEdmVVhrUG4yQ2ZXSHB1aw?oc=5</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -8512,22 +8512,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Niños colombianos pasan 8.9 horas diarias frente a pantallas: qué efectos hay en su salud - El Espectador</t>
+          <t>17 son menores de edad y los casos se concentran en Montería y otros 16 municipios, según autoridades de salud - facebook.com</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Montería</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZkRQZ0I3REZBYkZoNlVha2RNQ3F6dmlSYU5hTTBBOGkzMlBSM2xXV0RsMFRKcy1XRG1xWWNmQk5mUWE3ci1BMGZpNGZHeHFjcDBmdGQxb1cwNG95V0R0RVNodGlYcXFFcHRLdWU3bWgtSC1vV2YwTE5wVVpBejlZd2ZmRENoVTl4cDNnNWQwUDBxRFlIak83MjRYelRLRVdodS1wNnRLeC1wS1ViT2Y2SDhOSmdYZ0taY3BDNmxYMUpuUdIB1gFBVV95cUxOTUtIYTlOYUdmTHVzRmZWQVNGRkVsdDk3cEg4bDlRaXhVRUZyd2tBOHFXUWplMUtQYUpRX29LbDZNOHhDcXc4OHQ0OTVNS1I3cElDR1RRNFliRXA0UjV0Y1kzbmdzRzFVSnNYUlZUeEN4OEt1SnZDbXRzQ1hycHoxRTE1RlZzNk5BR1o2LTBTTWZka01pR2oycmV1MWlZY2ZoSjVvRlBvMWVLODJMbnFaZ251aU0zWGZqWHkwX1lMTEZCaC04ZEQwZTNTaU1ycktSUDhuRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPNFFpY29QRl9XdnlhQmdkZGpwZ3NCSDlqSkdtMHJXdU5ZTzhUd01JZUV1MVItMGZWZmd5R19nY2l5V3lQVW5TdjdicGprb0pXaG10aDdPWkw1NTJTM2NOTUtKQThuUS1KMUlWX1kwQmZDR1RaSnloU25HVllwRGh2UHRRZ0dGTDZ1UnFxRkF0eVhiS3JKdW1YVUp6WDlDb2Vobi1EaUU0aG1fQXN4QWwzQ09fVml4YTIzUUxQZFFOaGdtU3BzSHNzcWhYbEVvSHc0SUZkbGE3Q1lYVnBwZ3ctTkZabzQ?oc=5</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -8555,17 +8555,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Más de 1.400 personas han resultado quemadas con pólvora en Colombia: 30% son menores de edad - Caracol Radio</t>
+          <t>17 son menores de edad y los casos se concentran en Montería y otros 16 municipios, según autoridades de salud - facebook.com</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Montería</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQazQzUk15LVJiV2RfaHdjdEJiYXRoNWhJWDRaZ3FBOGRwSWpCMS1QSFo0SzUxYnUtWDJKUElQLXY0Q1pmUmZmdGZFeUlyQmY2UnVkZjB6SkhCb3dkUnNKNEFUYndwaFF5R1l0d1cwN1lOMEFwaVdUTnhOYVAzU2VGck1xcm9fNnhJTGtjRUpOd2NDdGdvZVJkNzluRV9XVmRoenZNendGa0RVaWdVYWhPM3pYYVBsT2k3a1BRS05XNkViVzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPeEpXeWtVQzkwUGphTTk2Tm9yUExYcHhEdHJfQVR2TERWYmlmbmpUQ29sZkRCd2k2bV9JLWc5WDJSMUR6azNPb3ZLNWExQk9EYkVmLWREbmpWTXRHSWRMbnowQTdSRFFVUU4tUzlHTkE2S0lXbjVuNmRKVHptUkNXRTJwZjk3VUhMN2ZKdTd2ajBNOXRuVjZrcmFDbENzNXFFM1F1XzZLZVlqNXQwQTE4Tk5raGdCLUljQVF4NWljZXpTLXBqTWYwVnhPUWRHWFpoR1k3ajA2SWwydzVZdFJ0UGxDRWlhdw?oc=5</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -8598,17 +8598,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Más de 1.400 personas han resultado quemadas con pólvora en Colombia: 30% son menores de edad - Caracol Radio</t>
+          <t>¿Cómo tramitar desde el exterior la salida de Colombia de un menor de edad? - Colexret</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Colexret</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQazQzUk15LVJiV2RfaHdjdEJiYXRoNWhJWDRaZ3FBOGRwSWpCMS1QSFo0SzUxYnUtWDJKUElQLXY0Q1pmUmZmdGZFeUlyQmY2UnVkZjB6SkhCb3dkUnNKNEFUYndwaFF5R1l0d1cwN1lOMEFwaVdUTnhOYVAzU2VGck1xcm9fNnhJTGtjRUpOd2NDdGdvZVJkNzluRV9XVmRoenZNendGa0RVaWdVYWhPM3pYYVBsT2k3a1BRS05XNkViVzjSAdcBQVVfeXFMTVgydDBnaXIwSVBWQXRzZFlLWGkxa2x1TzBMNV9oZ1JyNzY1cWxaVjhJVHp2TDlOQ2o3LUpTLVl1aFV4RlZLYV9zbTVVM0t1eXJLQnZYaV8ydFBCSWl6WXBhajlLUlpESjlOWEFIbXZWMy1qREd0a0JXQ2lpelJqbEM3Z2dCNXFrYVhyajQ1cUNxMVpBWDJ6RzlVSFRydlgwazdIM3JxR29qUGVydFR2ZFNieWdxZ09Pal9nSFJwYVlKcE93OVFsUnczY3ZwLXhlLUIyNXQ2NUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQc2xwX2xRNkc0anc2UGJqSEp0NGJrWGljRTVKUFJuTVFxVXJRTDRpdlFZTkd0eU9iU180X3RjUElYaUlUT25nVXU0NURtdzRCTTBqUkQ4UGUyUmJUQV9BdzBlRmNLNmxYa2xVVVlHMWZBVVN0SHZVOHVqazd2Rk9TcERwdnlwYWV3QTJPUVJQV2gxU1pJbFI0VW16TWlxN0NsOUpQd0cxNTh6QQ?oc=5</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -8641,17 +8641,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Cuándo es la semana de receso escolar en Colombia 2026: Fechas oficiales Ministerio de Educación - Caracol Radio</t>
+          <t>Confirman cambio en las vacaciones de los colegios en 2026: Bogotá reajusta el descanso de los estudiantes - redmas.com.co</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQb0NOTFo5Z0Z1V0ZCaHIxY0NiRHFwZWJHWVJaNGpWR0J0MUhFVTlIMlowdUVJWnNkTWdCSXQydm9kVTBvT2JLT1AzeVd2VTdxY1dVZzNFOXlTbXlBR1dzR3lfRG5fZzdRZUExbkU5bVlpU2pYRW9RWmNGWGZDMTA0S1p3UXNfdEsyQi1YS09oVGtnMVhxU0lueXdldW93aUwyaW5QNVJiT002dHZ0NzZkMmtQSWdBMUZRak1vSUdrakJtVHNTanI1RFVEeGJBdkxXcDdORDRzT3R5bHJaS1lrWlczaTBhczUyOFBVZ1VlOVVqUnFJdDl1ZmZ0djhFcHRLMUHSAYcCQVVfeXFMTXlGMTBtM3g4cnFEalRJNjA3SkxVOUhKRmlwWjhJTnFQOGtKRFdJNzhaSGcwS0czOEF4RmlBbHZYcF9wU2lsNVR1T2EtNUtsTVBmZlpYcTJLY2gxc3Y2Yk1XMXRFV1NLVU9nZDA2Rm1mWEVTUVZfSktaVy01WTc3Q2VXU09EbG1hZ3lhSUltVjUtXzAzZVpuZWpjMFNqX3lOUzNoVnltaVoxMnY4MGNfV0wzblE5Tk1GSXhfeFc3QzhLMVkzX2FsRUQtQnZYNEYtcVp0VTh6Yl93TEJNQ0RMMVlIUWp1Q3hrZ1hxaFJ6QlZQeVU1YmhwZHFiUE9BSVR4S1ZTbWNWSzA?oc=5</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -8684,17 +8684,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
+          <t>¿Cuándo inician las clases en los colegios distritales de Bogotá este 2026? Fechas y más - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8704,22 +8704,22 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZTVQT2p4UFNyUjFyYnV1M2xEMXgyQVpqZE9OazBzUjJ2bmw3T09zMGpGY0JxcXRaSGNCVkFGbEtsaEVrekk1dDF2VHFLT3UtYTF3WmFHd2hBTVVZYkZDSG10ZlNRQVBrd0ljSjRWSmI5VGkyMG1qMVpOZV9IY1FtNWpod0VKVklxR3loT0dOOFFXQU5iUlgxb04xUFlfNk9Xb1hjNkFlNmltQlRVdEc5LQ?oc=5</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -8727,17 +8727,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Estudiantes ganan la batalla: les pagarán $2 millones mensuales en sus prácticas desde 2026 si cumplen esta... - redmas.com.co</t>
+          <t>Petro refuerza su apoyo a los estudiantes de las universidades públicas con miras a las elecciones - EL PAÍS</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>EL PAÍS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNN2FROTMzTUQ2cEpiMGhTeDdSbFNqajFoeV9hdy1KOWt1QTdia3A1QzNvbmJuYjJiUFJpSDNaWWRoVGEyMzZKcG1NZHZBOGxFa21WaE5mYUVPOWV5Qko0bkktU3Ezb1JwbjRLUUlwT0pjSkxxUVpZRktYTl9FdDFvZnp1TGhoNTExM1p5NEFDQWR5UEdQYVFoNFZ3YnRyZDUyRWg2VkR4RHNRM0VkS0FNWk1JZG5ydzI3SkZEbmdTczJNNmZHRFZjTERJVHA4aS1FOHFWb0NQVmZnZmgtUjJfTFhxRUx3TWVBUjJQMU5wb0w2ZjVTdHREUdIB_gFBVV95cUxOOVRnWEQwY2RpZkVWLUxFeGpwdElDRzAwNktMOWxYdThYR2l3Vm4yQVNfUVRfeDl3cDJqejNJNTVTYXh5UW9WdVlDbmd5aDFKYXEwVkZfc2JRVDRoZ004Qm5mSG55dHdSb3RKbjR6VWZPQmgzdGo1TmpUM3RucG9rUlVaZjN2dXZrZDZuenNFQWFNX3FJRmhpOWFzanUtY19xT3J3N1JVNkxpalB1NFR5cmFsZG5lTmQ1U0M3Vld4NEtxTHEzcVRmNnUzZGxkei1wZWxZazdVSGpZS3E4TUlsR3lHYThaWnlwVFJmTnpIVTZvY2xLZ1RoMDQyRmVlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNTGNKT1ZIVC1RXzM0MUt3T2prd20zVjVOaG45cEg2eHJiRTVYQnhPRTQwX1VlVEF1VmV6WVNuTWIwMXFzbEw2cC1tRzl2ME11YXh2QUdoSE41dlNzQlZDMXhWM3ByZE40R3lhMVVoLXJRQ0dENHJZcVBZeEtJbDExZFo0NkRoSTFZSm5XVkJrVmZkZ2RRU2VST1FvWVlwMm1QM21tSjNXNjJsdGxjTmZqSkk5d3dDMjhETzZFM2x1V3pGNnNUeWFGVVNBZWwwU2EtdVdnN0gyMlIzX0I3LVF3V2h4TE7SAfgBQVVfeXFMT0NMSnh2NDNyM2N6NkNvc2FRLVdYS2xHRnh6cGlSLUpWOTQyeUs5NkphOHhDMTFrT09uSDlETHoxbXFvYk45el84eGMzal9JbTExU0RjdXczcDRkcHNoR1YtZ1VyUUlnU0ljU3JwWFhIZXloeGI3bWhpOThQRjdJUTJ3QS16UXlLN3hrZHFRMFotTXhTQzhtNk1rQTZkQ0haR016U0JPVWM3RUFwb0JFSW1naEFtWUU4S0NSSXZWUjJjMjNWb1QzSWNpSkdSM1JYUGRjcXNRSjBZRzZWR3E2ekNEemxIalhqVWlZQ25acWEwdGU2OTlHRXM?oc=5</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -8770,22 +8770,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Cierran sus puertas: estos son los prestigiosos colegios de Colombia que ya no funcionarán en 2026 - Semana.com</t>
+          <t>¿Cuándo entran a clases los colegios públicos y distritales en enero de 2026? - El Espectador</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Semana.com</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTVZGRXZlSDMzdUlmSHU1Z21OY2ZCM1pVVUR1OGoyTFpuXzVnZmIzaXg4bml1NlFrcGEyN0lTb1o1V0FYeTlaeWNtM0c5TW9IUVZBaDBLR053MVpiN1hXa3lDWWNub2ZDVzlhWUZkUDNkZWd2b09oMnhKWWRTVzlhdHBtOE1IaUVWNjNyellzUVdoM3h4X1lweVdrMmRLQUhFa1NtMi03NFRvcm9wemtuMTlHNURGLTBTanZpNkxzam9zT3FfbzVzVldXYVJrRXdQZFl0cVFRU3NDMEF3X2I2ctIB5gFBVV95cUxNdFowTkZuMEcyRGV5QXRtbFRCX1VpM19uWGs4dGFZUGpCUzNpNGxmTEFfVHdLREw0X3R4b2NyZHNuejNmMl9mUlR2QlFscFRyME9NUmpPZy1zQ2JZdmcyV0hnREl6UTBEdlVSUlBDNlVoeDNzSndNNms2ZUZrc0FUbzdKenBIampNNTJub3FzLWRSQlB1bkhIaE5sMnFYcGd2SlpHdngtOVJ4dEZid0VEMHV4MklTT0NBRVZONGtsaXBja0VZT3pCbXhYcXVpUG9XcjVpRDRKQWpCajA1c3Q1bUx2bGpWUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVGV3a0tQeW5uLVpJdlBBT3Rrc0NrUm9Va3pHY3NYMko1d1N4bjUzdjVYZ3ZjZWZpQ0xYak0yQVNLdFRsVXJxbnJMSVJVT3ZyaEZ4ZEZIU01RWVoyUHd6Q0hiNFdCMElNeXExYXVrQVJaQU8tN0RUMC0xZERQdFZ2aWo0UXQtZTZ5VmN6NE9YSjlhYUVGd01ycDBCaC1RMEhUcmk5TTdEekozS3g5Ry02SEVTOWprUdIBygFBVV95cUxQMlJDNFNLREl3U2ZaeXVGYy1GS2NmWlVydW1DX24wRE9NOVhBbzhqNWNzMmhTNEdTa0JFa281R1FVRUFfdjlUXzd2Nl8xTGxMb3JIaUVxOG1DTTBwRlluV1B3QVF6QTI1cEd1TTlVQlJiVWJkLWFFRFo1RlVsQjRMS2ZmTDhpUTY3bGdfRzlXWmliT2NybEFPcnRfaWJpX3UtazA0ekRpOFpOeU93TGNsOTV6Ynp3VkhKRnVPcmswemZHYnZNQUxrWHNn?oc=5</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -8813,27 +8813,27 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cuándo es la semana de receso escolar en Colombia 2026: Fechas oficiales Ministerio de Educación - Caracol Radio</t>
+          <t>Niños colombianos pasan 8.9 horas diarias frente a pantallas: qué efectos hay en su salud - El Espectador</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n0gHeAUFVX3lxTE5ELS1vYi1fLWZ3THVvOFJJNmZ0QjlxWXRDZ2FQSVh1bXZkM2V2d2d6dEg0WkRvd2xZM1NYdFh5RzZDbjh0Y0VSVlJFTGNFYW5ydmdYcmtxMnFIZ24ydEhYZUJBZDI1Qmpxc0pldFZreWpFblQyZEo3UFUzcFFfRk10VEN1WHAwcWg3MWNVLU1zSC1vY2pQREVWLUVMbzQ5cUdITEhOeGVSSFgxRGpFNFJ3UGhndmVVMWVIdU11RlZ3RUppWFR4dTJ3UXhLVE4ydThUaFhsMXFFRURsUHRVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZkRQZ0I3REZBYkZoNlVha2RNQ3F6dmlSYU5hTTBBOGkzMlBSM2xXV0RsMFRKcy1XRG1xWWNmQk5mUWE3ci1BMGZpNGZHeHFjcDBmdGQxb1cwNG95V0R0RVNodGlYcXFFcHRLdWU3bWgtSC1vV2YwTE5wVVpBejlZd2ZmRENoVTl4cDNnNWQwUDBxRFlIak83MjRYelRLRVdodS1wNnRLeC1wS1ViT2Y2SDhOSmdYZ0taY3BDNmxYMUpuUdIB1gFBVV95cUxOTUtIYTlOYUdmTHVzRmZWQVNGRkVsdDk3cEg4bDlRaXhVRUZyd2tBOHFXUWplMUtQYUpRX29LbDZNOHhDcXc4OHQ0OTVNS1I3cElDR1RRNFliRXA0UjV0Y1kzbmdzRzFVSnNYUlZUeEN4OEt1SnZDbXRzQ1hycHoxRTE1RlZzNk5BR1o2LTBTTWZka01pR2oycmV1MWlZY2ZoSjVvRlBvMWVLODJMbnFaZ251aU0zWGZqWHkwX1lMTEZCaC04ZEQwZTNTaU1ycktSUDhuRVRR?oc=5</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -8856,12 +8856,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Calendario escolar 2026 en Colombia: fechas de matrículas, inicio de clases y recesos - Caracol Radio</t>
+          <t>Más de 1.400 personas han resultado quemadas con pólvora en Colombia: 30% son menores de edad - Caracol Radio</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPc1FBT3Q2R0VBVVZ6bHE4OVhSQzRMX1hNSkp5WE1vTmRnemJKZWR2eU9sVVA5WWJUWXY4VDJmSWQ2MW81eHQ4V2NfN0hVUkh2cEFyb0hiMEszZzVCUkZWYnAxLURNNlR6MlNnT3pkamVUeWRzZTU0TDBlN1ZMNzUyYWxaZjBDZVd3NkdKUFFYWTJHc1cyWmlFLXdTWE5xZUpwNFQ4X2VUelpid21UVWlkSUdfWjVNZEp3dFHSAc4BQVVfeXFMTnN6MlF5T1FyR3pzdnhqaXVrb2FZMHdZSV8wMVNXUVdyZkxzSVBSWW9lN0MyLXJPN0FnRkl1aGtGd0IxUGxpZ1B5X1FGWk1ybzhHSXVBOGc0MndXMnRkMm9nXzFuUThiSzBqWEF1WWVhcGROcF81U1ZXMDZiRzZLOUNNdmZyNnBlbkI1d09vZEtDSGxidFg5VS04bTBhdXZzZHFfTExXYXJMN2lNc3lSWndzdUlSYVR6aTE1d1FTamQxYXRfdjAyVlNoX3UyQ1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQazQzUk15LVJiV2RfaHdjdEJiYXRoNWhJWDRaZ3FBOGRwSWpCMS1QSFo0SzUxYnUtWDJKUElQLXY0Q1pmUmZmdGZFeUlyQmY2UnVkZjB6SkhCb3dkUnNKNEFUYndwaFF5R1l0d1cwN1lOMEFwaVdUTnhOYVAzU2VGck1xcm9fNnhJTGtjRUpOd2NDdGdvZVJkNzluRV9XVmRoenZNendGa0RVaWdVYWhPM3pYYVBsT2k3a1BRS05XNkViVzg?oc=5</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -8899,17 +8899,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
+          <t>Más de 1.400 personas han resultado quemadas con pólvora en Colombia: 30% son menores de edad - Caracol Radio</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>bogota.alerta.com.co</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8919,22 +8919,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQUTFWOU5YN2xQeER4OVd5Vmp5VVRmWFRnb3pZczAwck54RUljT3RTMnMwVUdkVmN3TWQ1S0N6ZldRQWQ1VTUwcDFsRXQ2ZGNoQzhpOG1mNGRkZ1JhQnFad1lNc1V1aFQxbEZaM2dzbzRIYWEzQXpVVDVYRXRPZGhqc29STVI0VkhPQVc0bVZHWURGTnhOQjBvekhwUS1VaXdEQlRZRm90NkhrN3N3blMzadIBtgFBVV95cUxQcXNDNmNEOUd2ZmhpVTJYR0xMSEFHZ2RnV3ZTa0h6eFRZYVdiTDJEbzdlVWRjRXNSV0thc0NiVUdGUzduZDk3T3YyVzNNRWtiUVJhemFNVk9tUFJMZGtuN0pjeHJwUnpBelRvblRtd1hSSFREZXlFa1hjUjZKSmFQWjJfOGtZWWRZdHdBTy1aV21wUnJhdDBIc19GMEFVbk9jamRVVUttSlBwRjNxX2hnSWtaTGZ3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQazQzUk15LVJiV2RfaHdjdEJiYXRoNWhJWDRaZ3FBOGRwSWpCMS1QSFo0SzUxYnUtWDJKUElQLXY0Q1pmUmZmdGZFeUlyQmY2UnVkZjB6SkhCb3dkUnNKNEFUYndwaFF5R1l0d1cwN1lOMEFwaVdUTnhOYVAzU2VGck1xcm9fNnhJTGtjRUpOd2NDdGdvZVJkNzluRV9XVmRoenZNendGa0RVaWdVYWhPM3pYYVBsT2k3a1BRS05XNkViVzjSAdcBQVVfeXFMTVgydDBnaXIwSVBWQXRzZFlLWGkxa2x1TzBMNV9oZ1JyNzY1cWxaVjhJVHp2TDlOQ2o3LUpTLVl1aFV4RlZLYV9zbTVVM0t1eXJLQnZYaV8ydFBCSWl6WXBhajlLUlpESjlOWEFIbXZWMy1qREd0a0JXQ2lpelJqbEM3Z2dCNXFrYVhyajQ1cUNxMVpBWDJ6RzlVSFRydlgwazdIM3JxR29qUGVydFR2ZFNieWdxZ09Pal9nSFJwYVlKcE93OVFsUnczY3ZwLXhlLUIyNXQ2NUU?oc=5</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -8942,17 +8942,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Reputados colegios de Colombia estarán cerrados en 2026: no pudieron sobrevivir a realidad con sus estudian... - redmas.com.co</t>
+          <t>Cierran sus puertas: estos son los prestigiosos colegios de Colombia que ya no funcionarán en 2026 - Semana.com</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Semana.com</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPTm5hZnc3OEdNMzBqWWNibDNQeUJfaGs4ZDI4R2tZSFRmRWpXQ1lJXzk1VzE2RnNyWTdCbjhNcHJUbmpQc3dVVWlNanRQZjZScjdRc3FVSWN2TjRCOTUyNWRsRzlOT3k2LUZzR0Q4OHFTb0dOQmNuU05rdGc2VUJlX3F4bHlQSUF4a1liR2hnYkpFdHZPeGFSLWtnVDJYZi02Y01LbllmSnhaaTU4SmhHQktVXzU4SHpuUWF6M0wwaWtFNDc3NWlhMmNnclBPY1lSSXo1MC1HR2t4UlAtYlZmdTY5S2ZZaHM2RGM2YXVmdWFMVlc3aWx4UmlSRDI2WDZPOXfSAYcCQVVfeXFMTzdzYmVXMDdMT3JkU3RDQW9acXR1VmROSW1peklfZ1JzQUVKdXNmWmRNaUllVFg1M3hGUEZlWjN0TzR6aVRsQW9IZVhsTUJiTVU5QUNvaXBzTTVKbGNwcWU0am1HRmJObWlJZkRvUjUzekFUcEdCdzNWSzg0YmJKelRrb0Jfc1hGNkVvTGFHMlRlVEFXUmNBbVF1czR4R1lzUXhDSWhheGRDZ2ZQdlVOTURkNjV5TjNGMjBYdkFGcmpqUENjR2lvUEJ4TmpqMklreVFZbnZ0ZGpMNTljWXFuUzF5UWs2VmR5QkZwb0pMWFp5aWF5UWNGdWQ0czJYUjRFNWRvd1JYZjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTVZGRXZlSDMzdUlmSHU1Z21OY2ZCM1pVVUR1OGoyTFpuXzVnZmIzaXg4bml1NlFrcGEyN0lTb1o1V0FYeTlaeWNtM0c5TW9IUVZBaDBLR053MVpiN1hXa3lDWWNub2ZDVzlhWUZkUDNkZWd2b09oMnhKWWRTVzlhdHBtOE1IaUVWNjNyellzUVdoM3h4X1lweVdrMmRLQUhFa1NtMi03NFRvcm9wemtuMTlHNURGLTBTanZpNkxzam9zT3FfbzVzVldXYVJrRXdQZFl0cVFRU3NDMEF3X2I2ctIB5gFBVV95cUxNdFowTkZuMEcyRGV5QXRtbFRCX1VpM19uWGs4dGFZUGpCUzNpNGxmTEFfVHdLREw0X3R4b2NyZHNuejNmMl9mUlR2QlFscFRyME9NUmpPZy1zQ2JZdmcyV0hnREl6UTBEdlVSUlBDNlVoeDNzSndNNms2ZUZrc0FUbzdKenBIampNNTJub3FzLWRSQlB1bkhIaE5sMnFYcGd2SlpHdngtOVJ4dEZid0VEMHV4MklTT0NBRVZONGtsaXBja0VZT3pCbXhYcXVpUG9XcjVpRDRKQWpCajA1c3Q1bUx2bGpWUQ?oc=5</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -8985,17 +8985,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Gobierno anuncia pago del internado médico desde 2026 tras presión de estudiantes | El Colombiano - El Colombiano</t>
+          <t>Cuándo es la semana de receso escolar en Colombia 2026: Fechas oficiales Ministerio de Educación - Caracol Radio</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNbG1sVGlTX1IwblVKTmFzQ3lSSElQN2lTV1hmZUlfekhvak0ySWtlX3BVZElvQVVTd3lWVVZGb0NBM2ZHUlRsczZuNHBfSm05azhmZzkxT2RqdzNHSldkSVA4RmRNZEVWajlSUkN1Uk42OUx2X0JoY0dwcTloZ193M25WbWI4dlJxU2xMbmVxUHR6U2djdmVwNUJrWG5jekg5dnpicFhTYVBWbWtfZFlPSHpR0gG3AUFVX3lxTFBKOElRX3lGT3VpVlVVLUpyWEU5QmhOQk1DQVhQTjlYZ3JhVGpHQ0J1RG1NblNXRWNhM253cVJpLWRIWUZBLWpHVUF6VDN2Rkw4MExjeVE3cU5XUGVGVlRSaFYtUVA3TE5mUHBRa0daWVBfZkNid0JEdTNzUUR1eHlrYmpJU2hJX0tBSmxkdjJURFVoTnhOZEhJdW8wbDZkS3U5cGU1cWRwVWJZSk5pd3ZpWUtRS2YyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n0gHeAUFVX3lxTE5ELS1vYi1fLWZ3THVvOFJJNmZ0QjlxWXRDZ2FQSVh1bXZkM2V2d2d6dEg0WkRvd2xZM1NYdFh5RzZDbjh0Y0VSVlJFTGNFYW5ydmdYcmtxMnFIZ24ydEhYZUJBZDI1Qmpxc0pldFZreWpFblQyZEo3UFUzcFFfRk10VEN1WHAwcWg3MWNVLU1zSC1vY2pQREVWLUVMbzQ5cUdITEhOeGVSSFgxRGpFNFJ3UGhndmVVMWVIdU11RlZ3RUppWFR4dTJ3UXhLVE4ydThUaFhsMXFFRURsUHRVZw?oc=5</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -9028,17 +9028,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Estudiantes de Medicina anunciaron protesta y Gustavo Petro les respondió: habría plantón en 17 ciudades - Infobae</t>
+          <t>Cuándo es la semana de receso escolar en Colombia 2026: Fechas oficiales Ministerio de Educación - Caracol Radio</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOckVuZWpkQV9QTnd6UzZmSXdvNl9xX3plZHNIRkV1X2liZTJmYjRHY05uVDc5M09nekFlMDVwVS01WWtsZmstN1VtZkc3M0E5d0xGd1lRMzh5c0Qtc09iei1pVmdSekozWUVLenM5YVRtTms0R3BJdEZocU9YVE5wUEo0UVdLRnQ3cENPWm1ETmhsbjFULThLTVRKanQwSTVvM2hCQW5VODlJejZkRkpYUHpzREpEeDY1M29UaV82cUZQVFp6OEpmRVlxRTBzQzFUcWlPbTVWOVQwSG9LVF9KcGhiejZzTWt2S05KYzdyeDgzbThZMmhkdUNQZTBBdGNHN2RletIBnwJBVV95cUxPOTVVOXMyRFBNN21yQnZ5RHkzMTZOMVYybU0xXzNzczIycm95cHdBcEFKc0d0VVlLT25PYWJkVDhnbUVMdlQwTHktNlJqNG9EeXFDQ1RSaG51Tnc4ZXlsWXpVYzZSZWl1MXVRQVdabXI5ZTRUYXdQblUzWmN5NEE3VW1PRF8yNWdHcjVsdXZ3STF2cUJlenZHbTluZkpKYzRvSlhDZVlNVWdnVjBqZEFuSHpuQnNwdUVMMjBkMm5JNUZVZkFfOHFUMHFpeEdLWGFzZ0Q0V0pZdzdrMXdpUkRsRVZQRVppU3hnTXZlU05GRWZlZ3hKUnBKdFlWdy02cXJRdE1YWUFsSDRZTXctSDRhSkRMMV95QlRPUkJIVV92Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n?oc=5</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -9071,17 +9071,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Medellín registrará la tasa más baja de embarazos adolescentes de los últimos 13 años: la capital de Antioquia presentó una reducción del 2% - ELTIEMPO.COM</t>
+          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxNRXlYVlpUSkI1V1NiNG5KYjJsWnVTeHFUakcyTFAzaUxmZFlEa2YxblZfTTZUTVUyaUxnQUloWE1WbVlJb0o4U0p3TXR3WTAwQUpCb1MyNS1hVmJzUFA0eWp3RkQtaDd6OVZLaXhMZktWa1hKUmw0LVRQUjlaYmxGY0U0eEhFXzZ5N0VXV05UMkVySUNTd2xfblhnOUVqLUpoZ0otSGFtUTZTa0RGODROZmVQT182Wm5fZHRWMTVKY2xZZ0dPRlBjS3BJeXozTnp4M25VZm4xSXVuVmZJVkV6VEE4azFXRndhZzVGSWJ4R3hBRkl0WG5wSW9XNjRNT0pyZU8xanIzY2FsY3Nrcmd6aGRxSVFRajc1YXBTONIBogJBVV95cUxNNVdna2hOTVozcTFOcjA4RUx3X2lZWnc0X1YzSlBNV24xTVRUNklwazZOdzFVdVJhT3pxSVp2RjBQS2pNb1RBN2NhNWtpOHl6R094R2x2bFBXdl9DaXNFR2pNc0FlRHdSSnM3UW9ZWW9VTmtpU3ZENmVIVjgwSGZHSnRRTVlHbFp0Z1dPdlU1OFVQLVVDU1AxZG8wR2VGNlc2b2U0RUdseHllZ2xIVi1QbENDbFFXTmdmbTZmS3NRWGtqYU4xRWc1ZkwtMW5XTzB2aVNONkZmNzVYRmcyVUFZZmdfbW5LYkZnREN2YjVVcU5kX1ZxVzVoMUFiUDc5c1dJaHF5UDA3a2ZaUUpZd3htUC1Damh0cks4VlhBQ1VvRllUQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -9114,17 +9114,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Un hombre detenido por captar a adolescentes venezolanas para explotarlas en Colombia - El Nacional</t>
+          <t>Estudiantes ganan la batalla: les pagarán $2 millones mensuales en sus prácticas desde 2026 si cumplen esta... - redmas.com.co</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>El Nacional</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNcG9Zc05RT3pEbE5KNzlQYnIxcTlJbVZrUW1SSHQ2aGRRcnZ0SndSLUxWX0dCc01Wam5ieXJFUzNDcmJxRDBBNE5LY00zcGh2eVN5T0RHQlhjeVNUNWY4WWdxckZwVUFhNEtQRjNFZHRjS3JNQ1RlQ0wxRU01aGRxZWlDRFIxT0QtV1dKa3V3em0ydGthSlRJSTFNaXAtenB0SmNUemI2WnVjb2FfSzdLYmNEVHJHblNkQ1RGc3NB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNN2FROTMzTUQ2cEpiMGhTeDdSbFNqajFoeV9hdy1KOWt1QTdia3A1QzNvbmJuYjJiUFJpSDNaWWRoVGEyMzZKcG1NZHZBOGxFa21WaE5mYUVPOWV5Qko0bkktU3Ezb1JwbjRLUUlwT0pjSkxxUVpZRktYTl9FdDFvZnp1TGhoNTExM1p5NEFDQWR5UEdQYVFoNFZ3YnRyZDUyRWg2VkR4RHNRM0VkS0FNWk1JZG5ydzI3SkZEbmdTczJNNmZHRFZjTERJVHA4aS1FOHFWb0NQVmZnZmgtUjJfTFhxRUx3TWVBUjJQMU5wb0w2ZjVTdHREUdIB_gFBVV95cUxOOVRnWEQwY2RpZkVWLUxFeGpwdElDRzAwNktMOWxYdThYR2l3Vm4yQVNfUVRfeDl3cDJqejNJNTVTYXh5UW9WdVlDbmd5aDFKYXEwVkZfc2JRVDRoZ004Qm5mSG55dHdSb3RKbjR6VWZPQmgzdGo1TmpUM3RucG9rUlVaZjN2dXZrZDZuenNFQWFNX3FJRmhpOWFzanUtY19xT3J3N1JVNkxpalB1NFR5cmFsZG5lTmQ1U0M3Vld4NEtxTHEzcVRmNnUzZGxkei1wZWxZazdVSGpZS3E4TUlsR3lHYThaWnlwVFJmTnpIVTZvY2xLZ1RoMDQyRmVlQQ?oc=5</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -9157,17 +9157,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Cali recibe el JamCam Colombia 2025 con más de 2.000 jóvenes scouts de la Región Interamericana - cali.gov.co</t>
+          <t>Calendario escolar 2026 en Colombia: fechas de matrículas, inicio de clases y recesos - Caracol Radio</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>cali.gov.co</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLUNFeUZzUm1qREJBbnpQX0J4WTREQmRIVlVYblhFS2J4UnoyVXJZamoyLUJ6Z25pLUpSMUFLQmxjRVFNWUUyMXFkY0RKUU1vcVR1Q196d0RBRW9aemg5SDh0VWhlSllYZHVwdVF5d0Nrb3NadjhrMjlPX3YxVm9FUkE3VVAxRVU2X05vQlg1RXgxY2JzbFlQMUN2aXROZEZ4QXVleFdRMUY5eDRzUDFubktQR0JhTTZBcVB5TXBJd3h3eTYzS3dEZjA0UUhGYVVTazBxVzBLT1VmVzIzQk10enJIOTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPc1FBT3Q2R0VBVVZ6bHE4OVhSQzRMX1hNSkp5WE1vTmRnemJKZWR2eU9sVVA5WWJUWXY4VDJmSWQ2MW81eHQ4V2NfN0hVUkh2cEFyb0hiMEszZzVCUkZWYnAxLURNNlR6MlNnT3pkamVUeWRzZTU0TDBlN1ZMNzUyYWxaZjBDZVd3NkdKUFFYWTJHc1cyWmlFLXdTWE5xZUpwNFQ4X2VUelpid21UVWlkSUdfWjVNZEp3dFHSAc4BQVVfeXFMTnN6MlF5T1FyR3pzdnhqaXVrb2FZMHdZSV8wMVNXUVdyZkxzSVBSWW9lN0MyLXJPN0FnRkl1aGtGd0IxUGxpZ1B5X1FGWk1ybzhHSXVBOGc0MndXMnRkMm9nXzFuUThiSzBqWEF1WWVhcGROcF81U1ZXMDZiRzZLOUNNdmZyNnBlbkI1d09vZEtDSGxidFg5VS04bTBhdXZzZHFfTExXYXJMN2lNc3lSWndzdUlSYVR6aTE1d1FTamQxYXRfdjAyVlNoX3UyQ1E?oc=5</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -9200,17 +9200,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Balance de gestión 2025 evidenció avances en la participación juvenil en Bogotá - Bogota.gov.co</t>
+          <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>bogota.alerta.com.co</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOOTZUMTFEd3FHU3FvYjlxT2c1M0FVNktocG9QV2Z3YV9LYlNIUU9jNGlqZW03SEVoZk9MVkJZc2VLWGVBOE42UnFZSlI3Mk1sZEJLSUhYSHZYaFByanlMMVR1SnJHeVpoRHppVGRRTWZZMmxkNkpBQXlaWXNkR2h2by1najVOd1gzS09hdmRrY1VWbUdMaExobHREblpVdldVU2pCSnNMcER1Q1htcWhsVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQUTFWOU5YN2xQeER4OVd5Vmp5VVRmWFRnb3pZczAwck54RUljT3RTMnMwVUdkVmN3TWQ1S0N6ZldRQWQ1VTUwcDFsRXQ2ZGNoQzhpOG1mNGRkZ1JhQnFad1lNc1V1aFQxbEZaM2dzbzRIYWEzQXpVVDVYRXRPZGhqc29STVI0VkhPQVc0bVZHWURGTnhOQjBvekhwUS1VaXdEQlRZRm90NkhrN3N3blMzadIBtgFBVV95cUxQcXNDNmNEOUd2ZmhpVTJYR0xMSEFHZ2RnV3ZTa0h6eFRZYVdiTDJEbzdlVWRjRXNSV0thc0NiVUdGUzduZDk3T3YyVzNNRWtiUVJhemFNVk9tUFJMZGtuN0pjeHJwUnpBelRvblRtd1hSSFREZXlFa1hjUjZKSmFQWjJfOGtZWWRZdHdBTy1aV21wUnJhdDBIc19GMEFVbk9jamRVVUttSlBwRjNxX2hnSWtaTGZ3dw?oc=5</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -9243,17 +9243,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Consejeros de juventud deben ser posesionados antes del 19 de enero - lanacion.com.co</t>
+          <t>Reputados colegios de Colombia estarán cerrados en 2026: no pudieron sobrevivir a realidad con sus estudian... - redmas.com.co</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>lanacion.com.co</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdjc0b3pDbXMxTXJHLTlMN1B3T1FRNG4zQm9ZekVxUUphdkJsOXkwQmNLYy1KUVVwQmR4UkEtOWpMWjgyQkduazN1cVh1SktyY2hqTEp6VGNNLTY4bUtYM2Q1enpMQmRGcVI5aV95ci1Lb1FTT0hlRE1mbEQxWUNfNDRUTEdTQlRZQzItM2sxNkp6UFppYjFMVVlweEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPTm5hZnc3OEdNMzBqWWNibDNQeUJfaGs4ZDI4R2tZSFRmRWpXQ1lJXzk1VzE2RnNyWTdCbjhNcHJUbmpQc3dVVWlNanRQZjZScjdRc3FVSWN2TjRCOTUyNWRsRzlOT3k2LUZzR0Q4OHFTb0dOQmNuU05rdGc2VUJlX3F4bHlQSUF4a1liR2hnYkpFdHZPeGFSLWtnVDJYZi02Y01LbllmSnhaaTU4SmhHQktVXzU4SHpuUWF6M0wwaWtFNDc3NWlhMmNnclBPY1lSSXo1MC1HR2t4UlAtYlZmdTY5S2ZZaHM2RGM2YXVmdWFMVlc3aWx4UmlSRDI2WDZPOXfSAYcCQVVfeXFMTzdzYmVXMDdMT3JkU3RDQW9acXR1VmROSW1peklfZ1JzQUVKdXNmWmRNaUllVFg1M3hGUEZlWjN0TzR6aVRsQW9IZVhsTUJiTVU5QUNvaXBzTTVKbGNwcWU0am1HRmJObWlJZkRvUjUzekFUcEdCdzNWSzg0YmJKelRrb0Jfc1hGNkVvTGFHMlRlVEFXUmNBbVF1czR4R1lzUXhDSWhheGRDZ2ZQdlVOTURkNjV5TjNGMjBYdkFGcmpqUENjR2lvUEJ4TmpqMklreVFZbnZ0ZGpMNTljWXFuUzF5UWs2VmR5QkZwb0pMWFp5aWF5UWNGdWQ0czJYUjRFNWRvd1JYZjQ?oc=5</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -9286,17 +9286,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Accidente de estudiantes del Liceo Antioqueño: bus iba con el 97% de su capacidad, sin cinturones y con fallas graves de seguridad - Infobae</t>
+          <t>Medellín registrará la tasa más baja de embarazos adolescentes de los últimos 13 años: la capital de Antioquia presentó una reducción del 2% - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZGtNeVVBeHQta1Zhc2Z5YVpZR09qcnJZdnZCOGJ1TGdwbEktWVQ1UElPWmI2bEFEZUlOUGI5Z1J5U053TlBHcHkxclNnYlA2VU8zaWMwN3ZXdW9kdW1wTEJ5akcwcC1kZXk1eFZnQTlNT3JsUnRlRGNwTFpuNFZ4SnowUW5qQnhacGxHSTlCUXdRWDBXRjdHQUd1RGtkUjFJOXZhNmZkWXdfd0I3WGdYcWllRThlRkR4LXdQa1JNbDBlN2pyOUtJSU1zbGhob1cxUWhjeE03aXVJYWpLaTh4QmpyZGpXOVQ4dHJURUd2MWdtb01wd3hISTladGdKbDV1NmfSAZwCQVVfeXFMTmlvd2VmT04wQVNQWEh2LVQ3WXF6M0hZZU4wa3RKa3dUMEU3c3NPQmhONUoxbGNQNnJPR1dsUWp3d3pVT19vM1JoUnZNTWZIR1hWcjZXYXBNcVQ5OVN4dGR2S2dfbXZWclFFeU9GNUM2eEY3OWR5OWo5OUZTeXVSMWhKTHV0VGx6RFc4eVktSGFXdGJwa0FNWTd4b3hyakQxRWNJMXlOUjhiaEhtbXZhWkhDUmZ3ZVVTNGNfTEdUZjl3Z3VPT0VwVjZ5OHBOT0tEVmlZbTFKVUtXcU5JaWN0MnVpNWFLdmVtZTlaQV9Cd0Y3RUc3eXI1R3hrNnRXVnZELVliZTRrVUNaYXNsdFJ1Q2ZkRFpRSnhYcjl3NGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxNRXlYVlpUSkI1V1NiNG5KYjJsWnVTeHFUakcyTFAzaUxmZFlEa2YxblZfTTZUTVUyaUxnQUloWE1WbVlJb0o4U0p3TXR3WTAwQUpCb1MyNS1hVmJzUFA0eWp3RkQtaDd6OVZLaXhMZktWa1hKUmw0LVRQUjlaYmxGY0U0eEhFXzZ5N0VXV05UMkVySUNTd2xfblhnOUVqLUpoZ0otSGFtUTZTa0RGODROZmVQT182Wm5fZHRWMTVKY2xZZ0dPRlBjS3BJeXozTnp4M25VZm4xSXVuVmZJVkV6VEE4azFXRndhZzVGSWJ4R3hBRkl0WG5wSW9XNjRNT0pyZU8xanIzY2FsY3Nrcmd6aGRxSVFRajc1YXBTONIBogJBVV95cUxNNVdna2hOTVozcTFOcjA4RUx3X2lZWnc0X1YzSlBNV24xTVRUNklwazZOdzFVdVJhT3pxSVp2RjBQS2pNb1RBN2NhNWtpOHl6R094R2x2bFBXdl9DaXNFR2pNc0FlRHdSSnM3UW9ZWW9VTmtpU3ZENmVIVjgwSGZHSnRRTVlHbFp0Z1dPdlU1OFVQLVVDU1AxZG8wR2VGNlc2b2U0RUdseHllZ2xIVi1QbENDbFFXTmdmbTZmS3NRWGtqYU4xRWc1ZkwtMW5XTzB2aVNONkZmNzVYRmcyVUFZZmdfbW5LYkZnREN2YjVVcU5kX1ZxVzVoMUFiUDc5c1dJaHF5UDA3a2ZaUUpZd3htUC1Damh0cks4VlhBQ1VvRllUQQ?oc=5</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -9329,17 +9329,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Criar en la era digital: ¿cómo acompañar a niñas, niños y adolescentes en un mundo lleno de pantallas? - Crónica del Quindio</t>
+          <t>Estudiantes de Medicina anunciaron protesta y Gustavo Petro les respondió: habría plantón en 17 ciudades - Infobae</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Crónica del Quindio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOVzdMSEFIR2ZQbHZXX0RrN1RXakRobFRlMTFXbG9vSUtLUzl2VGxwbFhvUmlPZ1FmUjZVYVZPcmREdlhPNExPSnZIUjRfOEpfRDhveEJmdlVxcDh6QThJUzNFcHk0TEtVdnVHZ2trbHFjVlFhemxxbEtfQnlqVVRyTVI0MTVCN0VKVE0xQmxRSTdBT3I3N1ZfeVJqSlFEdmFlck53ZlhYSURrUHZma25BQWVHMWhIbFZBb3dvbmtjSHZad0NVa0VxTWE0aFBpb1ZpSXRwRl9pMFJrN1k0T0JGb01zRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOckVuZWpkQV9QTnd6UzZmSXdvNl9xX3plZHNIRkV1X2liZTJmYjRHY05uVDc5M09nekFlMDVwVS01WWtsZmstN1VtZkc3M0E5d0xGd1lRMzh5c0Qtc09iei1pVmdSekozWUVLenM5YVRtTms0R3BJdEZocU9YVE5wUEo0UVdLRnQ3cENPWm1ETmhsbjFULThLTVRKanQwSTVvM2hCQW5VODlJejZkRkpYUHpzREpEeDY1M29UaV82cUZQVFp6OEpmRVlxRTBzQzFUcWlPbTVWOVQwSG9LVF9KcGhiejZzTWt2S05KYzdyeDgzbThZMmhkdUNQZTBBdGNHN2RletIBnwJBVV95cUxPOTVVOXMyRFBNN21yQnZ5RHkzMTZOMVYybU0xXzNzczIycm95cHdBcEFKc0d0VVlLT25PYWJkVDhnbUVMdlQwTHktNlJqNG9EeXFDQ1RSaG51Tnc4ZXlsWXpVYzZSZWl1MXVRQVdabXI5ZTRUYXdQblUzWmN5NEE3VW1PRF8yNWdHcjVsdXZ3STF2cUJlenZHbTluZkpKYzRvSlhDZVlNVWdnVjBqZEFuSHpuQnNwdUVMMjBkMm5JNUZVZkFfOHFUMHFpeEdLWGFzZ0Q0V0pZdzdrMXdpUkRsRVZQRVppU3hnTXZlU05GRWZlZ3hKUnBKdFlWdy02cXJRdE1YWUFsSDRZTXctSDRhSkRMMV95QlRPUkJIVV92Yw?oc=5</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -9372,17 +9372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Rescatan en Medellín a tres niños de 2, 5 y 6 años, que estaban solos en casa: olía a quemado - Noticias Caracol</t>
+          <t>Gobierno anuncia pago del internado médico desde 2026 tras presión de estudiantes | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQLWdxTEctb1h1RElseVVGUEZrMENDUEVGNVNvLVFoZ3JHVE9TeTlVOXVNMDl6dlRCcmZPdE5FeVp3MkRTMTV1b1J1Q3JnZWc0MVVaTFNzSkVIQUZfY0hITzdkSTdFdDA1Z2d3MEs1QTlRaklqbG5XajlmY2FsVzdtTEQ1NlVzQUlsaUxxdDRZVkhWVTdaSFlLZ1g3cjhsT0lEQ3RXeWVHb3JIcS1hb1g0Y3BmZHd1SDFxNEVzTEt4M1VMdW5uOVV0Z1plR0pSNWR4dHfSAd8BQVVfeXFMTTFCSzBmLUIxZGhtSzR4X0xTVm1UWTJWYVVXa2JBbDRrcnRWVy1lR3d3V1lnUEl0b3Q0YVhNdVRjRmdROUFqMVYtZFJQQW04ZGNTOS1wVFp6ZDl4dUc0OTdKenhQa0Q3TXF6UFdCZF9lbHdGRXB2X0RCcXR2QzN0NmVDUW1OYUVGNTl4cWNQT1JOaFZlcUFJSzV1NDh3akdwckE5endyVldnRjVBUGUtODJBbGRuTUJfNkVZd25XRWJMSDRvaE83OUZ1XzlZbENNTEJEUjF6Y0ZGb1NSTEw0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNbG1sVGlTX1IwblVKTmFzQ3lSSElQN2lTV1hmZUlfekhvak0ySWtlX3BVZElvQVVTd3lWVVZGb0NBM2ZHUlRsczZuNHBfSm05azhmZzkxT2RqdzNHSldkSVA4RmRNZEVWajlSUkN1Uk42OUx2X0JoY0dwcTloZ193M25WbWI4dlJxU2xMbmVxUHR6U2djdmVwNUJrWG5jekg5dnpicFhTYVBWbWtfZFlPSHpR0gG3AUFVX3lxTFBKOElRX3lGT3VpVlVVLUpyWEU5QmhOQk1DQVhQTjlYZ3JhVGpHQ0J1RG1NblNXRWNhM253cVJpLWRIWUZBLWpHVUF6VDN2Rkw4MExjeVE3cU5XUGVGVlRSaFYtUVA3TE5mUHBRa0daWVBfZkNid0JEdTNzUUR1eHlrYmpJU2hJX0tBSmxkdjJURFVoTnhOZEhJdW8wbDZkS3U5cGU1cWRwVWJZSk5pd3ZpWUtRS2YyZw?oc=5</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -9415,17 +9415,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>“Todos los jóvenes deben saber que Colombia es un país rico en cultura”: Martín Elías Junior - WRadio</t>
+          <t>Cali recibe el JamCam Colombia 2025 con más de 2.000 jóvenes scouts de la Región Interamericana - cali.gov.co</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>WRadio</t>
+          <t>cali.gov.co</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQUHU3TUU3MGxQWVkzVUQzOW1sQlZWV1hyYm1BNVRFTTJudzF6LUhvSXV1RXRWUFNTZXFRaHFqMFJPS1FvS19lNWVlUGxrRjNoYlVtN2tKeXlPRUpaajZZZlJpZzZHRFpURUVoRkdUSnp6X1kzT2hvdkVsaldUNTAxdmxnZlhRcUZNZTA0OWY2ZXBpTUE0SDB0QVZPaU5ZSVc4NlAwS0VUVVMzSEZ2MjVXYnB2OTlocHJkUWNXbXZ6U1HSAdQBQVVfeXFMTXNRdlRzM1RhNnNzMVJpUjIwcGpwbW5YRzY3Rno5UEJLZERScGk2eTBZdDdRVDBheEtlcExReDg5SXhpVTR6RzhmRWtJQkhSbmFWZkVEaGtMMzhicWhDb1B1cmZUOThOWGZuYWxhbWZPQlBGdkVtS2N5ZG41Uk0xXy1DeDl5YzdPVElacHk4LWlPV3dNSWtyMG5QcTljUThlQVEyTDNtRU1xb1MyaWNXNTF4M2QtVk11bWRFRlNIZTlpSEV3by1KYjA5czdmNFVZU1RpUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLUNFeUZzUm1qREJBbnpQX0J4WTREQmRIVlVYblhFS2J4UnoyVXJZamoyLUJ6Z25pLUpSMUFLQmxjRVFNWUUyMXFkY0RKUU1vcVR1Q196d0RBRW9aemg5SDh0VWhlSllYZHVwdVF5d0Nrb3NadjhrMjlPX3YxVm9FUkE3VVAxRVU2X05vQlg1RXgxY2JzbFlQMUN2aXROZEZ4QXVleFdRMUY5eDRzUDFubktQR0JhTTZBcVB5TXBJd3h3eTYzS3dEZjA0UUhGYVVTazBxVzBLT1VmVzIzQk10enJIOTc?oc=5</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -9458,17 +9458,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>“Todos los jóvenes deben saber que Colombia es un país rico en cultura”: Martín Elías Junior - WRadio</t>
+          <t>Un hombre detenido por captar a adolescentes venezolanas para explotarlas en Colombia - El Nacional</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>WRadio</t>
+          <t>El Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxONFV6MExpS1dkLVVGbVJSbkZmVDVFdGNUeDU2T3FkTlE5Nk9MaHh0Mjl3UWlwbDE2N1lmcEI0djNPTTJrQ0FEQ0p3ZmlwZ2UzeGk4MlhGbXhMYncycFdWNlJhaVNuN2J6TFhUaUprelZ2NHJtbzZIOE5GUFNiZWxJN180cXJiUjZ0SFNFN1c1bWg3dWZhOHptaGpQMm0xMmZLZjFiRWxmb08zRDJ0eTR1X3daUjh4WDR6Z19LZFJSdm93SFlKZFHSAdoBQVVfeXFMUHc2bFczYWNlZjRFNnRldVZ0aUFuakFMcDNjZWo5Tkh2X1FYY0ExSFg0blE2RFNkaDVKN0hIMjNXX3lMWHBvTFZYdGpyeDYzdkp6dHBjSkY5ajQ4TU84ZmVMTTR0SlRMZTNPMG9PV1gySEFYNlF0SmN4Z2RnZElOXzNicGw4bC1KLTBMQjAzQnN2OWRqNTBWU3hYNXpQNjZmSmE5dW9GR1FJQ0I3MUtLS3lzdjJBdVUyUVdWOERzTkt2ZlN6ZnBIMVVFZ291cXBfRFd4QUlxV0lwclE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNcG9Zc05RT3pEbE5KNzlQYnIxcTlJbVZrUW1SSHQ2aGRRcnZ0SndSLUxWX0dCc01Wam5ieXJFUzNDcmJxRDBBNE5LY00zcGh2eVN5T0RHQlhjeVNUNWY4WWdxckZwVUFhNEtQRjNFZHRjS3JNQ1RlQ0wxRU01aGRxZWlDRFIxT0QtV1dKa3V3em0ydGthSlRJSTFNaXAtenB0SmNUemI2WnVjb2FfSzdLYmNEVHJHblNkQ1RGc3NB?oc=5</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -9501,42 +9501,42 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>¿El alemán será materia obligatoria en colegios públicos? Esto dice el Mineducación - El Espectador</t>
+          <t>Balance de gestión 2025 evidenció avances en la participación juvenil en Bogotá - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFh6ZDVETFROR255WTE1dm1uNXhtaXg4aGNjOUtZblZDbU9RbnFhLU81Z29yVDZzeG1HcFpjeS12UFJNX1lSaXRRVWIyWUFyWkMyaDJobmNReFhjRzREcTFBTGFsX3RwNDRnUHhydUtWdEcyR0VFeVRXUlg5c0hJZlhydURCVG0zcmd0SkNVbk5qak8tbkJGWnducXNZV1hOUFEtSHRWbmVvOFRXSFM4aG5zbU9SOWJ2Y1RTRGNB0gHSAUFVX3lxTE5jTVU1LW82UDhqRVdjVnNNQ29LZXpEdTM1a2NiRlNUaVBBUnVCZ25hamlJM3RiZW9DNzBMYWNBanJaemVuaEdzUUMyOFljN0t3SU1ac0ZRNnBLWm1LNjAycG8yUFRTZllRWVIwTWV0dTN2TTM3WEt5ZWNNWFlia2VvMFdnNEZtMTlDSWhwX1ZLc3hCTDlvT20zd3ZJUEE2UVJVc1Z3bGpnOENxSWNYcExDX0hiaGxTMnE2dXBSaEJnRE9Od2VQdk1vQmVCUy1PdjlSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOOTZUMTFEd3FHU3FvYjlxT2c1M0FVNktocG9QV2Z3YV9LYlNIUU9jNGlqZW03SEVoZk9MVkJZc2VLWGVBOE42UnFZSlI3Mk1sZEJLSUhYSHZYaFByanlMMVR1SnJHeVpoRHppVGRRTWZZMmxkNkpBQXlaWXNkR2h2by1najVOd1gzS09hdmRrY1VWbUdMaExobHREblpVdldVU2pCSnNMcER1Q1htcWhsVw?oc=5</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -9544,17 +9544,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ni matemáticas, ni inglés: esta es la nueva asignatura obligatoria en los colegios a partir de 2026 - AS Colombia</t>
+          <t>Consejeros de juventud deben ser posesionados antes del 19 de enero - lanacion.com.co</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>AS Colombia</t>
+          <t>lanacion.com.co</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPQnZ5RGlTQzl5ZXdNM0tERWdMSXVqS1FkSVFYcS1JZE9BYVNHSzduZTlmTks3OURGVk1QZjc3NmctbWN2d3hMQXREaVY5UWRhM3paZmRfUFI5MjFob0hkelFvaGoyYWVxdC1KRDNsTWVvZU9sanIzbEFrWjNzUDVfdTYxV3E1UHRVTll3cm5KR05XZkl3SHlmUHZnZFZsUUFsXzF3Y01GdWRDSm93aEM5TlhZRmhhYlloWmVZczVGaXJkbkpCeExUNV9TRU9wQ25fVEZWOXZMellIOEnSAe8BQVVfeXFMTkVrcGVHbldsS0t0LXJDR3dKaUt6UHEzclhuUG15SVp3R3lRWWtySzlzbXA2ZWRNdXJpcXlBVnhZbVVVVVc5WkMtY2d6ODctOTQ0TFN2ZF9HZkJHSXlzZUpWZjBRUUNvUC1jV0p5am9yYnFWVXVVU3haclJzM0lfcWxiTEh5YnA1QUtIR0RIWEVHdlRHRXBtb0ZydFBsSDVoZVBjYTVvZ2otZzNmelpXbERNTzFLR0JNLWl5NjIyWTliNFpSNE5ndHpwMlRXRHplbUZ6UFI1Um5ORmtZWnVCeDdmYUxXWTJRd19KMG84UnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdjc0b3pDbXMxTXJHLTlMN1B3T1FRNG4zQm9ZekVxUUphdkJsOXkwQmNLYy1KUVVwQmR4UkEtOWpMWjgyQkduazN1cVh1SktyY2hqTEp6VGNNLTY4bUtYM2Q1enpMQmRGcVI5aV95ci1Lb1FTT0hlRE1mbEQxWUNfNDRUTEdTQlRZQzItM2sxNkp6UFppYjFMVVlweEM?oc=5</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -9587,17 +9587,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Más de 64.000 estudiantes se matricularon en programas en línea - Noticias UNAD</t>
+          <t>Accidente de estudiantes del Liceo Antioqueño: bus iba con el 97% de su capacidad, sin cinturones y con fallas graves de seguridad - Infobae</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Noticias UNAD</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNOHZRdHo4NTlxNUgtRl95X2V2MGJBSDQ2RXlncFQyb1FET1o2UV83MmtZc2ZMRG41aXNCeWxiNUVhWnJ2ajY4WDRzb25OWm5ZcU0xWlJKN2Q2VnZlTUprVzh5QWJNb2xaUnByMmFLN1V3bkpQLU9ZbGVsQUtvUWFSbERMek81aEhPMFZzdXZ3dElzLWQxcW9kRi1xTWRnN0pKSzBKNEw2aUVMaElQZHBHcVh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZGtNeVVBeHQta1Zhc2Z5YVpZR09qcnJZdnZCOGJ1TGdwbEktWVQ1UElPWmI2bEFEZUlOUGI5Z1J5U053TlBHcHkxclNnYlA2VU8zaWMwN3ZXdW9kdW1wTEJ5akcwcC1kZXk1eFZnQTlNT3JsUnRlRGNwTFpuNFZ4SnowUW5qQnhacGxHSTlCUXdRWDBXRjdHQUd1RGtkUjFJOXZhNmZkWXdfd0I3WGdYcWllRThlRkR4LXdQa1JNbDBlN2pyOUtJSU1zbGhob1cxUWhjeE03aXVJYWpLaTh4QmpyZGpXOVQ4dHJURUd2MWdtb01wd3hISTladGdKbDV1NmfSAZwCQVVfeXFMTmlvd2VmT04wQVNQWEh2LVQ3WXF6M0hZZU4wa3RKa3dUMEU3c3NPQmhONUoxbGNQNnJPR1dsUWp3d3pVT19vM1JoUnZNTWZIR1hWcjZXYXBNcVQ5OVN4dGR2S2dfbXZWclFFeU9GNUM2eEY3OWR5OWo5OUZTeXVSMWhKTHV0VGx6RFc4eVktSGFXdGJwa0FNWTd4b3hyakQxRWNJMXlOUjhiaEhtbXZhWkhDUmZ3ZVVTNGNfTEdUZjl3Z3VPT0VwVjZ5OHBOT0tEVmlZbTFKVUtXcU5JaWN0MnVpNWFLdmVtZTlaQV9Cd0Y3RUc3eXI1R3hrNnRXVnZELVliZTRrVUNaYXNsdFJ1Q2ZkRFpRSnhYcjl3NGE?oc=5</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -9630,17 +9630,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Colombia fortalece la respuesta institucional frente a la niñez y adolescencia migrante - Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Criar en la era digital: ¿cómo acompañar a niñas, niños y adolescentes en un mundo lleno de pantallas? - Crónica del Quindio</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Crónica del Quindio</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcl8yMC0tR0ZJZXk3NW9tdGs1TTFMTXQ4Z3pkamhhZDFmbURaTWRWc3dvMXhLTUF1WlJaQ25kZmF5eU4wQUNuMy1OQ1FKM3NFOFZrblZKMzlxNWowSjd2a2EySTZsVzNEWTNHZmtqd3ZBU2ozMFFEZ29LdF8wb0Nvb2UzZzQyNzFWdlBwVTZ4RF80cmxwd2NoZVdXNDhlOGxVMENaSnA1T0gzRFJrOE1nRFJaekZ6allTdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOVzdMSEFIR2ZQbHZXX0RrN1RXakRobFRlMTFXbG9vSUtLUzl2VGxwbFhvUmlPZ1FmUjZVYVZPcmREdlhPNExPSnZIUjRfOEpfRDhveEJmdlVxcDh6QThJUzNFcHk0TEtVdnVHZ2trbHFjVlFhemxxbEtfQnlqVVRyTVI0MTVCN0VKVE0xQmxRSTdBT3I3N1ZfeVJqSlFEdmFlck53ZlhYSURrUHZma25BQWVHMWhIbFZBb3dvbmtjSHZad0NVa0VxTWE0aFBpb1ZpSXRwRl9pMFJrN1k0T0JGb01zRQ?oc=5</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -9673,17 +9673,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Bogotá presenta el primer estudio sobre dinámicas de niños y jóvenes en condición de calle - Caracol Radio</t>
+          <t>Rescatan en Medellín a tres niños de 2, 5 y 6 años, que estaban solos en casa: olía a quemado - Noticias Caracol</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9698,17 +9698,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcDl2Z1NjUWM5d3VaOUZWRjNWZld1QngyQWlmbGFnelB5ZU4tNGJISm5KXy1aN01uWERNaVQzUGJmSWJFeVNxSjVTLVhRYU92dEVia1F2TVhvQUxmdVdvd3BRLUZLLWdYNkg3eUNKd1NhTGlwZGpVazdZOW9OU2RBLXhYYk5qcUpmSm55QkxRem55MUxQYmZjVUJSSThyU01XbGQyTTlyQnU5cFJTNnVmNXpvMGY4ZGVjZGFzXzVhVXAzZ2PSAdcBQVVfeXFMTUJvMXgzWXo2cnlEaEtYNnFCN0xHb2ZrZlp0YS1fV0gzbl9PanE4RDFNLTNMN1FZcU9kak55S2M2OEd2d3ZmU2RPYjRZWDlmR3NmUWxDNEQ2am9jTlB2SzI3SG9KQ3c2NHU0OWxJYkRYdWRMUTh3ZEs4ZjgwTGdnanA2S1RxYmlxRFVmNnRKTGMxVWwzSzczRTd1ZFFEYVJWd3ljbmVKU1l0VjZnZ2QwbnN0SmozVEV0cTJzbC1yQ3g0SUthMEk1aDhzeF9MWENqRFgzbTNPYWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQLWdxTEctb1h1RElseVVGUEZrMENDUEVGNVNvLVFoZ3JHVE9TeTlVOXVNMDl6dlRCcmZPdE5FeVp3MkRTMTV1b1J1Q3JnZWc0MVVaTFNzSkVIQUZfY0hITzdkSTdFdDA1Z2d3MEs1QTlRaklqbG5XajlmY2FsVzdtTEQ1NlVzQUlsaUxxdDRZVkhWVTdaSFlLZ1g3cjhsT0lEQ3RXeWVHb3JIcS1hb1g0Y3BmZHd1SDFxNEVzTEt4M1VMdW5uOVV0Z1plR0pSNWR4dHfSAd8BQVVfeXFMTTFCSzBmLUIxZGhtSzR4X0xTVm1UWTJWYVVXa2JBbDRrcnRWVy1lR3d3V1lnUEl0b3Q0YVhNdVRjRmdROUFqMVYtZFJQQW04ZGNTOS1wVFp6ZDl4dUc0OTdKenhQa0Q3TXF6UFdCZF9lbHdGRXB2X0RCcXR2QzN0NmVDUW1OYUVGNTl4cWNQT1JOaFZlcUFJSzV1NDh3akdwckE5endyVldnRjVBUGUtODJBbGRuTUJfNkVZd25XRWJMSDRvaE83OUZ1XzlZbENNTEJEUjF6Y0ZGb1NSTEw0dw?oc=5</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -9716,17 +9716,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Bogotá también abraza en Navidad a jóvenes vulnerables y en riesgo de calle - La FM</t>
+          <t>“Todos los jóvenes deben saber que Colombia es un país rico en cultura”: Martín Elías Junior - WRadio</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>La FM</t>
+          <t>WRadio</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9736,22 +9736,22 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNOG5Za2d6dXAtQzZJMDZoYlhieUtZb3I0OXh4QlFIeWNoRkIwMGxlUmFCUkpjZ0FyeThvYVprUEFpQXpQc3hfOVJfcmZOdk81QlhCTGFSeVlieUstcDR2NkozUGlEUnJ1WHRrUVh2WFRZQklfR3ZxM19UWmlka3B1OG5xY2tKMkJONGJuVkhyeHh1RTdhbUJ1cktib9IBmwFBVV95cUxQVmRGQnY2UkxUaTI2OTNUNzdOSTNoX1FmUE82azZ5c21GdjZHcUU5dEh1SVFDVTJ4M24tM3pfbUVEVUxTUEhRblFYTS1oenhXMU9SYm1GS2dHN25yQi1CeVlPcnoxdU9ocF80QzN1clQzcEJKS0JHc3d5dllCdVlmWE5CQ2c2Qk9na1hianI1ekNaSXQtSjB3X2padw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxONFV6MExpS1dkLVVGbVJSbkZmVDVFdGNUeDU2T3FkTlE5Nk9MaHh0Mjl3UWlwbDE2N1lmcEI0djNPTTJrQ0FEQ0p3ZmlwZ2UzeGk4MlhGbXhMYncycFdWNlJhaVNuN2J6TFhUaUprelZ2NHJtbzZIOE5GUFNiZWxJN180cXJiUjZ0SFNFN1c1bWg3dWZhOHptaGpQMm0xMmZLZjFiRWxmb08zRDJ0eTR1X3daUjh4WDR6Z19LZFJSdm93SFlKZFHSAdoBQVVfeXFMUHc2bFczYWNlZjRFNnRldVZ0aUFuakFMcDNjZWo5Tkh2X1FYY0ExSFg0blE2RFNkaDVKN0hIMjNXX3lMWHBvTFZYdGpyeDYzdkp6dHBjSkY5ajQ4TU84ZmVMTTR0SlRMZTNPMG9PV1gySEFYNlF0SmN4Z2RnZElOXzNicGw4bC1KLTBMQjAzQnN2OWRqNTBWU3hYNXpQNjZmSmE5dW9GR1FJQ0I3MUtLS3lzdjJBdVUyUVdWOERzTkt2ZlN6ZnBIMVVFZ291cXBfRFd4QUlxV0lwclE?oc=5</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -9759,17 +9759,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
+          <t>“Todos los jóvenes deben saber que Colombia es un país rico en cultura”: Martín Elías Junior - WRadio</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>WRadio</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQUHU3TUU3MGxQWVkzVUQzOW1sQlZWV1hyYm1BNVRFTTJudzF6LUhvSXV1RXRWUFNTZXFRaHFqMFJPS1FvS19lNWVlUGxrRjNoYlVtN2tKeXlPRUpaajZZZlJpZzZHRFpURUVoRkdUSnp6X1kzT2hvdkVsaldUNTAxdmxnZlhRcUZNZTA0OWY2ZXBpTUE0SDB0QVZPaU5ZSVc4NlAwS0VUVVMzSEZ2MjVXYnB2OTlocHJkUWNXbXZ6U1HSAdQBQVVfeXFMTXNRdlRzM1RhNnNzMVJpUjIwcGpwbW5YRzY3Rno5UEJLZERScGk2eTBZdDdRVDBheEtlcExReDg5SXhpVTR6RzhmRWtJQkhSbmFWZkVEaGtMMzhicWhDb1B1cmZUOThOWGZuYWxhbWZPQlBGdkVtS2N5ZG41Uk0xXy1DeDl5YzdPVElacHk4LWlPV3dNSWtyMG5QcTljUThlQVEyTDNtRU1xb1MyaWNXNTF4M2QtVk11bWRFRlNIZTlpSEV3by1KYjA5czdmNFVZU1RpUG8?oc=5</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -9802,27 +9802,27 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>30 quemados con pólvora en el Valle del Cauca y no ha terminado diciembre: 12 de ellos son niños y adolescentes; piden a la población mayor conciencia - ELTIEMPO.COM</t>
+          <t>¿El alemán será materia obligatoria en colegios públicos? Esto dice el Mineducación - El Espectador</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOZGZFRWYzbUs0eWpFUVdsRnUtMXNTVmpIR0hlcU9FbXcyQkxIek92Qk02TVlMNGgyeUxBRkkycHpVeHBwREZvZlhJRXUteWl5aFc3X1dSMjlpbmJwLUtsN0FQR2FkbzVVaVRQNHBpdjNfUWhQaUIycXZmUUN5N1kxbnNQY1BqbWZmOWU2YjAzUnRQNkF3eUJVUEg3TlRTd1F5WWZHVkZaVnhpNW1hSl9SbEpBR1RweEVtSFM0QWotcEJ3aHotT1pGTTBXbDhrOEdHLXRLd2hQcEV4aXQtQ2lULVNKQ0xNaXF0ZkktOEZUaVpyczRoZ3ZuZEtKc3F2bW15eWpCall6WVRGUTBpRHNxWHpOZEtJSTc1bk5pOV9HRFHSAaYCQVVfeXFMTnFJd1RaMUdoeDcydmdqWXRFSmFzRUd0b2FaUHFMVld4VDlyQkVRemtUVFZTVEVoWHdyRHpILXpFU0VVeklITTVMVGx1dElFYmY1WXFEX0NrN29zMDcxcTJfMFExMHVxV0ZfUE93cGQ3QW5jemNaT2VlS2MwME1DVTNnR0NwbWdPaDZQRDQxelBMUXZhREc1aG1DQ09BMkRFR3MwanZiWThJVlExUkhmMmlDVnhTTnI5N3RpUDlFanBsblJ3NktFVVR4QXV1WWo4NUNFaHUxNkU1VXgyMmIwTmd4SXpGSFQzejluLXRPYTdPV2JkN2NMWkNLUjZNOWdyU0JJTzN2WmZUeHM2WUN4aWR2TU1LT2tvbjVHRkNpM05Eb1hEaldB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFh6ZDVETFROR255WTE1dm1uNXhtaXg4aGNjOUtZblZDbU9RbnFhLU81Z29yVDZzeG1HcFpjeS12UFJNX1lSaXRRVWIyWUFyWkMyaDJobmNReFhjRzREcTFBTGFsX3RwNDRnUHhydUtWdEcyR0VFeVRXUlg5c0hJZlhydURCVG0zcmd0SkNVbk5qak8tbkJGWnducXNZV1hOUFEtSHRWbmVvOFRXSFM4aG5zbU9SOWJ2Y1RTRGNB0gHSAUFVX3lxTE5jTVU1LW82UDhqRVdjVnNNQ29LZXpEdTM1a2NiRlNUaVBBUnVCZ25hamlJM3RiZW9DNzBMYWNBanJaemVuaEdzUUMyOFljN0t3SU1ac0ZRNnBLWm1LNjAycG8yUFRTZllRWVIwTWV0dTN2TTM3WEt5ZWNNWFlia2VvMFdnNEZtMTlDSWhwX1ZLc3hCTDlvT20zd3ZJUEE2UVJVc1Z3bGpnOENxSWNYcExDX0hiaGxTMnE2dXBSaEJnRE9Od2VQdk1vQmVCUy1PdjlSZw?oc=5</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -9845,17 +9845,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IDIPRON alerta sobre niños y jóvenes en riesgo de habitar calle en Bogotá - City Tv</t>
+          <t>Ni matemáticas, ni inglés: esta es la nueva asignatura obligatoria en los colegios a partir de 2026 - AS Colombia</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>City Tv</t>
+          <t>AS Colombia</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -9865,22 +9865,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdEpCWHhRQ0JwdHNjV1BoWnNrWk4xWnFFbUQ0QzY2dU1XZk5TWHNyVk9NTlJlaVZ2MTlFVDk3MzNVWHFxWUFZQ3A0UVZHYzhPWUROMi0xWE5OOHpLZEhIVThRalhrOEN1MEE3U2RVRV94bDJpbjRiaUdBbWtfWnlaZ3RydVFtQTdQM3RVSE1qVWRoX0tXanBqQlNqX3RrWVVDMmpzc05JdmlJblFhSTZrazNKb0ltVEh6bGhudjlWQ1VZcjlRZllSWHBGaW01Nmd2dEdTelNRN3g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPQnZ5RGlTQzl5ZXdNM0tERWdMSXVqS1FkSVFYcS1JZE9BYVNHSzduZTlmTks3OURGVk1QZjc3NmctbWN2d3hMQXREaVY5UWRhM3paZmRfUFI5MjFob0hkelFvaGoyYWVxdC1KRDNsTWVvZU9sanIzbEFrWjNzUDVfdTYxV3E1UHRVTll3cm5KR05XZkl3SHlmUHZnZFZsUUFsXzF3Y01GdWRDSm93aEM5TlhZRmhhYlloWmVZczVGaXJkbkpCeExUNV9TRU9wQ25fVEZWOXZMellIOEnSAe8BQVVfeXFMTkVrcGVHbldsS0t0LXJDR3dKaUt6UHEzclhuUG15SVp3R3lRWWtySzlzbXA2ZWRNdXJpcXlBVnhZbVVVVVc5WkMtY2d6ODctOTQ0TFN2ZF9HZkJHSXlzZUpWZjBRUUNvUC1jV0p5am9yYnFWVXVVU3haclJzM0lfcWxiTEh5YnA1QUtIR0RIWEVHdlRHRXBtb0ZydFBsSDVoZVBjYTVvZ2otZzNmelpXbERNTzFLR0JNLWl5NjIyWTliNFpSNE5ndHpwMlRXRHplbUZ6UFI1Um5ORmtZWnVCeDdmYUxXWTJRd19KMG84UnM?oc=5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -9888,17 +9888,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Barranquilla será sede de la Asamblea Nacional de Juventudes 2025 desde este viernes - ELHERALDO.CO</t>
+          <t>Más de 64.000 estudiantes se matricularon en programas en línea - Noticias UNAD</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ELHERALDO.CO</t>
+          <t>Noticias UNAD</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPZnFRNm1qalphMGhIaGdYT0hVWUFDUlZmbENKeGd2ZkkyaHNkRzlXU1ZleWtsamdoNzdZRFkxWXpwTU04RFQ0VWZScUlxWkFMcklPVTJEVEZ2UDhMNVdUdTVOQl8tdF9NTlZVYzA4YmFWbkpCNV9Xdkpod2FvcW44cEcxTUJPWlBCT3lqQ3VKZUpUZ3pkVG90a1U5bmpaYmoxc1lsRlVQNUt5ZFlNNnhiUnMwR2xITm94Ym5LXzJLVWJHazRtN1FPd2xLWdIB5gFBVV95cUxORGdBSHFILTcyZm5VVTVEOFFsQzB5bTV4aUdWT280QXUwREctNC05OG1qbE5oazJQZ3N1NENlM0J0Y1hwSFYyN1UyaU15dTk5Ty0wVTdJNmQ0dDYtTlhnYk9pMTRRRlRpYmw1d3Y5Z2lmWm9tR1pUMTAtZWNhQ244SVBPMm1DLXVmQTZvQ1U1ejkyRHlqU2hOLWxfeGFfaXZJbUQ2N2tEbmplSXhkYmxqUUdDQWYwdGNYVVFBN1JyZm5MMTJRTFlmNHhxajg4UGxnUTNySDNrWUJmaXNqUGJhdkFIRFY0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNOHZRdHo4NTlxNUgtRl95X2V2MGJBSDQ2RXlncFQyb1FET1o2UV83MmtZc2ZMRG41aXNCeWxiNUVhWnJ2ajY4WDRzb25OWm5ZcU0xWlJKN2Q2VnZlTUprVzh5QWJNb2xaUnByMmFLN1V3bkpQLU9ZbGVsQUtvUWFSbERMek81aEhPMFZzdXZ3dElzLWQxcW9kRi1xTWRnN0pKSzBKNEw2aUVMaElQZHBHcVh3?oc=5</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -9931,17 +9931,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Colombia y Alemania se unen para que más estudiantes aprendan alemán en los colegios públicos - Ministerio de Educación Nacional</t>
+          <t>Colombia fortalece la respuesta institucional frente a la niñez y adolescencia migrante - Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOdDBneDZDSVFGTEdLQVVyWWJrazBhb2R3ZzZWb051Rkd0MjhKWU5MWFdCVVhNV1JVMlczeDl5elhqLTl5Y19aczFZNmNrV2xKMFdjV0NTWE1RMHplTU9PbzJDWXd4TkNjX0ZrQ2o2ZXRSYVRJT3RKZU1xUG5odGFjYm1BeXJfSkF5WDB1SEZLRWJjSzdKemRXbWFVWGZsaHVONXFkM0RPSWZ0VmRRN2NwenoxRUNrOFhPbmExeUVrUXRXczVfem1iaXdjSTBIR0FoUFpRYUswN3ZFYUlGNFpJZXp1UjJ3bUt0UEVuNnEtSm5sVzFt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcl8yMC0tR0ZJZXk3NW9tdGs1TTFMTXQ4Z3pkamhhZDFmbURaTWRWc3dvMXhLTUF1WlJaQ25kZmF5eU4wQUNuMy1OQ1FKM3NFOFZrblZKMzlxNWowSjd2a2EySTZsVzNEWTNHZmtqd3ZBU2ozMFFEZ29LdF8wb0Nvb2UzZzQyNzFWdlBwVTZ4RF80cmxwd2NoZVdXNDhlOGxVMENaSnA1T0gzRFJrOE1nRFJaekZ6allTdnc?oc=5</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -9974,17 +9974,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>El mapa de riesgo de la niñez: estudio del Idipron revela la grave situación de los menores en contexto de calle en Bogotá - Semana.com</t>
+          <t>Bogotá también abraza en Navidad a jóvenes vulnerables y en riesgo de calle - La FM</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Semana.com</t>
+          <t>La FM</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNVmlPaF9SMDVfSXIxa05XNjBTd0NscTdOYTh4SEtlRU9QZGItVjN3S0Uza3BCbklvdzd3YlYxeHdGWVVIWXpxc1AzLVF4TzVzUlV1WlVjNjhvQnAwUkRJaURBZ2FqeDhpb0Z5d2d6bVN1Y3hNVE5IakpNUk83X1FLVUJTdG5MbkZHaWJCLXlfQ3pWMkVrUi1zdUk0Tkp6SDZTVDVvUUVLY1FoOEhnU1JieXplX1B1eDJ1VTZRMjZoNlZGUXVtU0VRZTV5eFE4S25yUXEtVTUwb3pTVlo3V045bjNvdENRaWlJWllpMTFjTnVCMVBSdlE0Z1gtU3pBRk1scWhCaU1PRdIBjAJBVV95cUxPc1E4TmdZZzgyZU5xVUZoeHI3eE03YUc3b2RKNzk1M0w2YXE1UVl1a0ttcWZ2WEh1bzdGU3czNmNNbXc5bnZHX2NhWWY4b1NQVTNfV2ktX2Y5TE5uVHp5VnBneWlMQXhQR0ZoUWs1Z2xBU25FNW5xZFlMQ1FGQWk2QVVud2w4NkU5N2ZNOTVfUGptaVkzR0hYUEhjVHUzN2ZuY0Nkdmo2NDc5Y05zVjcxU1liTU1aRjIzeXB6ZkJabHZTNko5ZXpxY1RoNWdjWGJER05HSmdyclJKYVJUOXAtSlRoU21qbU5lQkxVZEJYTUtJS252Q000bVJzVEFuWGtGMEhKWm9Pd2JCVjk3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNOG5Za2d6dXAtQzZJMDZoYlhieUtZb3I0OXh4QlFIeWNoRkIwMGxlUmFCUkpjZ0FyeThvYVprUEFpQXpQc3hfOVJfcmZOdk81QlhCTGFSeVlieUstcDR2NkozUGlEUnJ1WHRrUVh2WFRZQklfR3ZxM19UWmlka3B1OG5xY2tKMkJONGJuVkhyeHh1RTdhbUJ1cktib9IBmwFBVV95cUxQVmRGQnY2UkxUaTI2OTNUNzdOSTNoX1FmUE82azZ5c21GdjZHcUU5dEh1SVFDVTJ4M24tM3pfbUVEVUxTUEhRblFYTS1oenhXMU9SYm1GS2dHN25yQi1CeVlPcnoxdU9ocF80QzN1clQzcEJKS0JHc3d5dllCdVlmWE5CQ2c2Qk9na1hianI1ekNaSXQtSjB3X2padw?oc=5</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -10017,17 +10017,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Colombia conmemora una década de la Resolución 2250 con un diálogo nacional sobre juventudes, paz y seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10037,12 +10037,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTjN2Wkl1aXB1Wi1DX25OQnZ6amUwVGhLenJTU0VQZkpwZW5zVUxwbEFZZFI4bG4yMS1Qa2J6MWtaYjRLODBfSVNaNktKbWljNVRMSU1uckx2ZXhyVWZ1QlJmeWVvcjVLQWE5cC1lclVkcDNFMlBnMWk1dFF3VVdEaW91ZEFGdG1JU2tRcHk3VGtnOER4MDRjRWQwUzlRUXBRTC10WGg3VkRfcHlVSkFvTUxyekwwMVRVdjRlQ3kzd2tZd2EwZGVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -10060,17 +10060,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Barranquilla será escenario de la Asamblea Nacional de Juventudes: 2.000 participantes de todo el país - notasdeactualidad.com</t>
+          <t>30 quemados con pólvora en el Valle del Cauca y no ha terminado diciembre: 12 de ellos son niños y adolescentes; piden a la población mayor conciencia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>notasdeactualidad.com</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQak9ISWpvdmIxWlZSNUlZQ2p1ZDA5SDRYaWJWNFhFcDVyb1dlUm1PZ2VycTk5WFpPc1NOQlg4SWx4TDlsWTFSbm15RDY5X2hNSUlWaDJ5NElNVW9ZckctMFFZS1pzaDlTMzJyT2hsWDRQTnNBeXdRVDJ3cWxST3BfaVoyNnFMdEl2SkRZd3hTdm9OZFVKbFdBbUdGdzhtaDRhZE5EdzdPYmo5RTJCSWo5U3NXbUlVZ2V1TUZ4U0JjT0JmOGg5UG1tXzhGbVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOZGZFRWYzbUs0eWpFUVdsRnUtMXNTVmpIR0hlcU9FbXcyQkxIek92Qk02TVlMNGgyeUxBRkkycHpVeHBwREZvZlhJRXUteWl5aFc3X1dSMjlpbmJwLUtsN0FQR2FkbzVVaVRQNHBpdjNfUWhQaUIycXZmUUN5N1kxbnNQY1BqbWZmOWU2YjAzUnRQNkF3eUJVUEg3TlRTd1F5WWZHVkZaVnhpNW1hSl9SbEpBR1RweEVtSFM0QWotcEJ3aHotT1pGTTBXbDhrOEdHLXRLd2hQcEV4aXQtQ2lULVNKQ0xNaXF0ZkktOEZUaVpyczRoZ3ZuZEtKc3F2bW15eWpCall6WVRGUTBpRHNxWHpOZEtJSTc1bk5pOV9HRFHSAaYCQVVfeXFMTnFJd1RaMUdoeDcydmdqWXRFSmFzRUd0b2FaUHFMVld4VDlyQkVRemtUVFZTVEVoWHdyRHpILXpFU0VVeklITTVMVGx1dElFYmY1WXFEX0NrN29zMDcxcTJfMFExMHVxV0ZfUE93cGQ3QW5jemNaT2VlS2MwME1DVTNnR0NwbWdPaDZQRDQxelBMUXZhREc1aG1DQ09BMkRFR3MwanZiWThJVlExUkhmMmlDVnhTTnI5N3RpUDlFanBsblJ3NktFVVR4QXV1WWo4NUNFaHUxNkU1VXgyMmIwTmd4SXpGSFQzejluLXRPYTdPV2JkN2NMWkNLUjZNOWdyU0JJTzN2WmZUeHM2WUN4aWR2TU1LT2tvbjVHRkNpM05Eb1hEaldB?oc=5</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -10103,17 +10103,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Bogotá presenta por primera vez un estudio Georreferenciado de los Contextos de Calle de la Niñez y la Adolescencia - Bogota.gov.co</t>
+          <t>Bogotá presenta el primer estudio sobre dinámicas de niños y jóvenes en condición de calle - Caracol Radio</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPajQ0NUdTQzVVQ21yQTBXYjhlc1o3NDA3aXRMaEhIWHVPN1ZOQVN5UHZ4OU1Ma1RGdlVlU3VkczhiVHkxbEJPdUxKeHY5RUgzQ0NNTlZMNkJjSl9oeVBQREZ3ek02QXd6UlhDeE9NMDlJdEJMb3ljclhaeEZVTEhDOEg0Y3hSdU9hUWlFaXlmbXJKWGFXQXNxS0k1Z0tlanBHZjlNY2h4T0JHYU5ObXh3TUdOU0ZkMkplNTZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcDl2Z1NjUWM5d3VaOUZWRjNWZld1QngyQWlmbGFnelB5ZU4tNGJISm5KXy1aN01uWERNaVQzUGJmSWJFeVNxSjVTLVhRYU92dEVia1F2TVhvQUxmdVdvd3BRLUZLLWdYNkg3eUNKd1NhTGlwZGpVazdZOW9OU2RBLXhYYk5qcUpmSm55QkxRem55MUxQYmZjVUJSSThyU01XbGQyTTlyQnU5cFJTNnVmNXpvMGY4ZGVjZGFzXzVhVXAzZ2PSAdcBQVVfeXFMTUJvMXgzWXo2cnlEaEtYNnFCN0xHb2ZrZlp0YS1fV0gzbl9PanE4RDFNLTNMN1FZcU9kak55S2M2OEd2d3ZmU2RPYjRZWDlmR3NmUWxDNEQ2am9jTlB2SzI3SG9KQ3c2NHU0OWxJYkRYdWRMUTh3ZEs4ZjgwTGdnanA2S1RxYmlxRFVmNnRKTGMxVWwzSzczRTd1ZFFEYVJWd3ljbmVKU1l0VjZnZ2QwbnN0SmozVEV0cTJzbC1yQ3g0SUthMEk1aDhzeF9MWENqRFgzbTNPYWM?oc=5</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -10146,17 +10146,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Ley 30 beneficia a estudiantes, pero ¿soluciona el problema estructural de la educación en Colombia? - WRadio</t>
+          <t>Bogotá presenta por primera vez un estudio Georreferenciado de los Contextos de Calle de la Niñez y la Adolescencia - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>WRadio</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10166,22 +10166,22 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOaExPYlVrMlVVdGdIczJldER1T2U1V1EzS212dGl1eFFDbmpRUlpRdXFuWVh1RXFESWNpV0hRVDhkLUtJN05lN05sakZzUHdLdnpCWWNwNFgzOUNiSDVpSF90eHAxTnNIbTBwUEdieUkyaE9yNEYydVUzOHhjRFA5aEQ0X0p1MVV6Ry1yZkZWbVM3NkxBNHZ1M3FjRURwQmo3VDhKVEplLWo3ZlRBRm9FZy1CVHktY21WQ0JLZ2lQT3JtNVFzQ0ZsU2Via9IB3wFBVV95cUxOc2hOSmFjNGU0ZVlCN0NfYWdoMzJldjlscGZQLWdzY01PYTVrSW5QMzZOek9VTFdRbXk0ZGU1RVo0OEZsUzRpbS1sUGVnanF4YUFIZ1F6Ni1rVjRPT1NDOHdFZzJKcUhBampxal84MnFnMW5vSG9tNzFxVVNZelA1cnN4b2lqN0RhYUkzamVMMGVUMXNmQ3FLTmhXdlhKWC1kdDE4LURLQ3FKWDMweUc0eUh6eVBiWjlnb3VQdTNhNTlmaEhCWGw0RDdCX2tVRnRaRDhfZUM0eUxjanpBY2Jn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPajQ0NUdTQzVVQ21yQTBXYjhlc1o3NDA3aXRMaEhIWHVPN1ZOQVN5UHZ4OU1Ma1RGdlVlU3VkczhiVHkxbEJPdUxKeHY5RUgzQ0NNTlZMNkJjSl9oeVBQREZ3ek02QXd6UlhDeE9NMDlJdEJMb3ljclhaeEZVTEhDOEg0Y3hSdU9hUWlFaXlmbXJKWGFXQXNxS0k1Z0tlanBHZjlNY2h4T0JHYU5ObXh3TUdOU0ZkMkplNTZn?oc=5</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -10189,17 +10189,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Colegios endurecen las reglas en 2026: Llega el fin de la ley que respaldaba a los estudiantes en este caso - redmas.com.co</t>
+          <t>Colombia y Alemania se unen para que más estudiantes aprendan alemán en los colegios públicos - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNSmpSM1NzR3NJZ3plTzQtYTRZTVl2LWdBTjhWVDllTTJNdnJ5RGhoaTFEUFZZQlBCTGRFV2Y2TGplcFhjSU5fd3R6ZU5QZjFqR3dVYXIxc0VPX2xLaTlqOFZhRFNEaXhsdjlnMXNUc2IzdmZjUVlWNzRVRVhlS3hCeUdaLURhamxTUmhKcGRQVGJEVWZHbjQ4OGR5aExLQy05YXFqbllEcno4SW5kcXd6MlFVd0Y3VDNERW5reUFZZThQa2RwNUFBN3FILXZ3d3VqeEdIMW5Zc3Q5V3FEeW9vRGotM1gxbklRVHh3TNIB8gFBVV95cUxNT2Y1YlNyMWZCemZJLUdUMEYxSmw1REY1UjM3WDJiaXloZG9CdERtUEp1djV0bTBUNW45WlFCSTRVSjExOG56UlJZNmZHZFV1N01ZcEJvdGtOMHJNMUpIWDBWSTJTWUFZNDFPY1RUS1ZybnVLWldUSTRRaWM5WDRyckFBYjdnTk9HUGhqZllBZ0VBSDNDRzlWR2hZVGdBNTFBZnZHUThEc1E3c1NLbmZfb09wTGtXcFNVVVp2LVhZeTFjN0NWU2lBLVQtLWNJSU1LQVB3OTNUMlBuTWt6Q1laZTNVRG9XWkpFTmpwX2NmcG5hZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOdDBneDZDSVFGTEdLQVVyWWJrazBhb2R3ZzZWb051Rkd0MjhKWU5MWFdCVVhNV1JVMlczeDl5elhqLTl5Y19aczFZNmNrV2xKMFdjV0NTWE1RMHplTU9PbzJDWXd4TkNjX0ZrQ2o2ZXRSYVRJT3RKZU1xUG5odGFjYm1BeXJfSkF5WDB1SEZLRWJjSzdKemRXbWFVWGZsaHVONXFkM0RPSWZ0VmRRN2NwenoxRUNrOFhPbmExeUVrUXRXczVfem1iaXdjSTBIR0FoUFpRYUswN3ZFYUlGNFpJZXp1UjJ3bUt0UEVuNnEtSm5sVzFt?oc=5</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -10232,17 +10232,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
+          <t>IDIPRON alerta sobre niños y jóvenes en riesgo de habitar calle en Bogotá - City Tv</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>City Tv</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10252,22 +10252,22 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdEpCWHhRQ0JwdHNjV1BoWnNrWk4xWnFFbUQ0QzY2dU1XZk5TWHNyVk9NTlJlaVZ2MTlFVDk3MzNVWHFxWUFZQ3A0UVZHYzhPWUROMi0xWE5OOHpLZEhIVThRalhrOEN1MEE3U2RVRV94bDJpbjRiaUdBbWtfWnlaZ3RydVFtQTdQM3RVSE1qVWRoX0tXanBqQlNqX3RrWVVDMmpzc05JdmlJblFhSTZrazNKb0ltVEh6bGhudjlWQ1VZcjlRZllSWHBGaW01Nmd2dEdTelNRN3g?oc=5</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -10275,17 +10275,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Colombia reporta 185 casos de niños quemados por pólvora, un crecimiento del 9% frente al 2024 - Caracol Radio</t>
+          <t>Barranquilla será sede de la Asamblea Nacional de Juventudes 2025 desde este viernes - ELHERALDO.CO</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>ELHERALDO.CO</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOVWdJWWtTdmZkcUY3QUM1ZmJJZTdkRnZvVlgtbkpsZS1aa2Y3SkZLMG5XWjlURkhBZzRFRTM0VTZab2FzWFBKM0pNYktVVl9KckdZaVdXTGRpMDRVZ0FPMmU1bmhsQk9NT3VWZjdkSnk1Qnc5bTZGN29vMWhzRkREOURQMzJhNVhXajdPaXlGVnhLNU9WeXBveVBidFVpblZweW9iamtzR2Y1UG5VX3BHX3VaQmpJcHdodmRNa0xkWmd4ZlgtUUHSAdoBQVVfeXFMTmUzalpBM2J2NHFmV185akVudW9XQVVqWDVNMi02cDBDdFBnXzFWMnNSb1J5SF9sMElVcl84WnQwTVdtMURQRm00TTZoc1BCZnJ5NGlqcWdjQUFtRGNiTlZia0tPVy1rZGR6dy1RVDI3Y21XMEZPV19KQXhFYVIwY0lDdHlrMU9sVldSQ2F6X0x2RnFXbVNRXzNsRUwzM1JwMVBsR0stdmRUU1M4bGJJVEllZm1heGNlMVdTQ1lRZUt1V3EtS09LUnV2QzFjSDltRHY0VGZROU40N2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPZnFRNm1qalphMGhIaGdYT0hVWUFDUlZmbENKeGd2ZkkyaHNkRzlXU1ZleWtsamdoNzdZRFkxWXpwTU04RFQ0VWZScUlxWkFMcklPVTJEVEZ2UDhMNVdUdTVOQl8tdF9NTlZVYzA4YmFWbkpCNV9Xdkpod2FvcW44cEcxTUJPWlBCT3lqQ3VKZUpUZ3pkVG90a1U5bmpaYmoxc1lsRlVQNUt5ZFlNNnhiUnMwR2xITm94Ym5LXzJLVWJHazRtN1FPd2xLWdIB5gFBVV95cUxORGdBSHFILTcyZm5VVTVEOFFsQzB5bTV4aUdWT280QXUwREctNC05OG1qbE5oazJQZ3N1NENlM0J0Y1hwSFYyN1UyaU15dTk5Ty0wVTdJNmQ0dDYtTlhnYk9pMTRRRlRpYmw1d3Y5Z2lmWm9tR1pUMTAtZWNhQ244SVBPMm1DLXVmQTZvQ1U1ejkyRHlqU2hOLWxfeGFfaXZJbUQ2N2tEbmplSXhkYmxqUUdDQWYwdGNYVVFBN1JyZm5MMTJRTFlmNHhxajg4UGxnUTNySDNrWUJmaXNqUGJhdkFIRFY0QQ?oc=5</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -10318,17 +10318,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Colombia recoge aportes clave de jóvenes migrantes para el Primer Plan de Acción Nacional de Juventud, Paz y Seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>El mapa de riesgo de la niñez: estudio del Idipron revela la grave situación de los menores en contexto de calle en Bogotá - Semana.com</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>Semana.com</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10338,22 +10338,22 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQb2FIenFRUjRjWTdVdHhwUWVLcDU3SHVBLTF4WGdDbDdvdEhuaFhXWkF3TndUeGxTMVVaZWt3dHZsUFF1ZWxFR0hJNWNPMkhpRWhZaVNvUFVIVW5zRUlhS2toYUUyM2wzTnVLRGxBdnNJSG9ISlBteXdMS3AtVEM5blJqbXFlYVo2M0ZKY2w2SXBKOEd2QnIyUHgzX0ZFcEtBUWh5X3V5SkNoWkZyUE9pRkM5TENhdzFhaW1QTlhvUXNmQ2FRVTBzLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNVmlPaF9SMDVfSXIxa05XNjBTd0NscTdOYTh4SEtlRU9QZGItVjN3S0Uza3BCbklvdzd3YlYxeHdGWVVIWXpxc1AzLVF4TzVzUlV1WlVjNjhvQnAwUkRJaURBZ2FqeDhpb0Z5d2d6bVN1Y3hNVE5IakpNUk83X1FLVUJTdG5MbkZHaWJCLXlfQ3pWMkVrUi1zdUk0Tkp6SDZTVDVvUUVLY1FoOEhnU1JieXplX1B1eDJ1VTZRMjZoNlZGUXVtU0VRZTV5eFE4S25yUXEtVTUwb3pTVlo3V045bjNvdENRaWlJWllpMTFjTnVCMVBSdlE0Z1gtU3pBRk1scWhCaU1PRdIBjAJBVV95cUxPc1E4TmdZZzgyZU5xVUZoeHI3eE03YUc3b2RKNzk1M0w2YXE1UVl1a0ttcWZ2WEh1bzdGU3czNmNNbXc5bnZHX2NhWWY4b1NQVTNfV2ktX2Y5TE5uVHp5VnBneWlMQXhQR0ZoUWs1Z2xBU25FNW5xZFlMQ1FGQWk2QVVud2w4NkU5N2ZNOTVfUGptaVkzR0hYUEhjVHUzN2ZuY0Nkdmo2NDc5Y05zVjcxU1liTU1aRjIzeXB6ZkJabHZTNko5ZXpxY1RoNWdjWGJER05HSmdyclJKYVJUOXAtSlRoU21qbU5lQkxVZEJYTUtJS252Q000bVJzVEFuWGtGMEhKWm9Pd2JCVjk3?oc=5</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -10361,17 +10361,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Los estudiantes a los que los colegios en Colombia no podrán negar el cupo a pesar de esta situación - AS Colombia</t>
+          <t>Colombia conmemora una década de la Resolución 2250 con un diálogo nacional sobre juventudes, paz y seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>AS Colombia</t>
+          <t>Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPNzltbTBsa2trTDhUaW13ZEx3VVVCNWJYWUdMMzRiN3RJZnlaSlpSczNiTGVDT3JhcTd3YWZtV1lfdW5RT1JxY21FU0JqZlJyUVAwd2c2RWViQ09tb1BQbjkzVHItRUpnaWtWZjc3cEQ0QjdaWTJXaUI0UGY4c2c0Vmpzay1EVVgzX2RUMndFcXZkU25ZMFEzM1ZHbjc1UEdQQU9TNzc5TGVLRkFCdG0ybEpZdHc2VktRaVF4YTVCcTFLZk5ITnpWLVItMU5CbzZqV1lMMGxoNEN1VlRzdjc00gHzAUFVX3lxTE5Talh5Y09PR1RuSzhlOTZUbHNVRENDMlpXbE5rTGdZQ3ozUVFjM0p5V2VmcE1FQzVKdkZwc2p3SEl3SVhBT2NuajQzOWlkazF5UHZDQzg3VGFySHNtRDh6Wkx4bEhGdFdjZGFGVkxhZ2xZNjRLM3FZdGYxZVdSVDZNUURCckQ4NExUYXRpdHJHRHo4Sk9qUjh5djMwdm8xYjFpcVNmd083NXR6bUQwWE04V2FWek83U0xGdHY4LXBkbFlSZEhaTWktNmtkaHYxVDlFbXhrYXFDRXdid3hRSk1uVktwQ1NETFZrRW5xMFI4Y1oxWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTjN2Wkl1aXB1Wi1DX25OQnZ6amUwVGhLenJTU0VQZkpwZW5zVUxwbEFZZFI4bG4yMS1Qa2J6MWtaYjRLODBfSVNaNktKbWljNVRMSU1uckx2ZXhyVWZ1QlJmeWVvcjVLQWE5cC1lclVkcDNFMlBnMWk1dFF3VVdEaW91ZEFGdG1JU2tRcHk3VGtnOER4MDRjRWQwUzlRUXBRTC10WGg3VkRfcHlVSkFvTUxyekwwMVRVdjRlQ3kzd2tZd2EwZGVZ?oc=5</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -10404,17 +10404,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>La chispa que está moviendo a Colombia: jóvenes que ya no sueñan con el futuro, lo construyen - ELTIEMPO.COM</t>
+          <t>Barranquilla será escenario de la Asamblea Nacional de Juventudes: 2.000 participantes de todo el país - notasdeactualidad.com</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>notasdeactualidad.com</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNZ2cwYjk5Rk9ZV0p2c2paOHI1M2djamFCOExGYUFfTHpKTGIzOURhNFBQLUtBRDRhcGRmZ1ZxR3lnVkd5cTJYSFBjYkJlWkVnRFBIaFAxS0dIekZfREJHSGRtdE9hejRaaFJxZDlDaVJDZ09PVy1yOTVLZ2doQ0dqZ0RqeXRiLVhqdTQ4dGEwRUZoUTRXUmRNTFJEbTF6RUxKSy03NEdILTk3WWlia1lLTDlibVZ2UjJrMnhHeWhLVER3VkxPaDZyR1V3cEZhN3JTcDZCZtIB2gFBVV95cUxNeWo0TGhMNjdxTmFxeS01NlNpRm8yOVBDSklySlBaaWlPTTFyN1RZY2tBUHpGNG54T1cwMGY1akw0QVplT0hDdS1OLU9ZTXV1VnpBeFJMeHlWT3hDRGFxX3dGeVZQclZPbnlLeFhkejhIUFExdGZ3a0MxOVFOTnNBTE81YTRLemN2VnhsUlc5a1d5SUFSSk1ra3NJMTFodzZjcnlPYnhiNnljZHdLWXdtTXBwck1EaC0xRU5DUTQxWWJqNi14WVA3NmoxX19Ual9saEthZVBhSUFsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQak9ISWpvdmIxWlZSNUlZQ2p1ZDA5SDRYaWJWNFhFcDVyb1dlUm1PZ2VycTk5WFpPc1NOQlg4SWx4TDlsWTFSbm15RDY5X2hNSUlWaDJ5NElNVW9ZckctMFFZS1pzaDlTMzJyT2hsWDRQTnNBeXdRVDJ3cWxST3BfaVoyNnFMdEl2SkRZd3hTdm9OZFVKbFdBbUdGdzhtaDRhZE5EdzdPYmo5RTJCSWo5U3NXbUlVZ2V1TUZ4U0JjT0JmOGg5UG1tXzhGbVk?oc=5</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -10447,17 +10447,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Jóvenes del Atlántico gritan “¡No más bullyng!” a través del arte - Gobernación del Atlántico</t>
+          <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Gobernación del Atlántico</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzExajdsZFN2UGduQnZXWjhydHdUNGNwZkJjQ1J0ZUR5cm96M01feHZIcFpQTGFpZWM0d0ZyVmhmVjRFWVRnaVhydHJkUU4yT3NYel9ZNm5tVGFLVXZKRHRXTFRkUzlubGx5eE9WVGgxRTg2SElBaGN3cW4tZ2hzRU9KdG51ZElRaGFablhHbTlzNTBEUEd1RmdCNExkOUFiVS1MUFBkOURYV004M3lhbzB0VlZYazBPVG8wOXBmYl9ldzNLUFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -10490,17 +10490,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
+          <t>Ley 30 beneficia a estudiantes, pero ¿soluciona el problema estructural de la educación en Colombia? - WRadio</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>WRadio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOaExPYlVrMlVVdGdIczJldER1T2U1V1EzS212dGl1eFFDbmpRUlpRdXFuWVh1RXFESWNpV0hRVDhkLUtJN05lN05sakZzUHdLdnpCWWNwNFgzOUNiSDVpSF90eHAxTnNIbTBwUEdieUkyaE9yNEYydVUzOHhjRFA5aEQ0X0p1MVV6Ry1yZkZWbVM3NkxBNHZ1M3FjRURwQmo3VDhKVEplLWo3ZlRBRm9FZy1CVHktY21WQ0JLZ2lQT3JtNVFzQ0ZsU2Via9IB3wFBVV95cUxOc2hOSmFjNGU0ZVlCN0NfYWdoMzJldjlscGZQLWdzY01PYTVrSW5QMzZOek9VTFdRbXk0ZGU1RVo0OEZsUzRpbS1sUGVnanF4YUFIZ1F6Ni1rVjRPT1NDOHdFZzJKcUhBampxal84MnFnMW5vSG9tNzFxVVNZelA1cnN4b2lqN0RhYUkzamVMMGVUMXNmQ3FLTmhXdlhKWC1kdDE4LURLQ3FKWDMweUc0eUh6eVBiWjlnb3VQdTNhNTlmaEhCWGw0RDdCX2tVRnRaRDhfZUM0eUxjanpBY2Jn?oc=5</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -10533,17 +10533,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Luto en Colombia: accidente de autobús deja sin vida a su conductor y 16 adolescentes en Antioquia - France 24</t>
+          <t>Colegios endurecen las reglas en 2026: Llega el fin de la ley que respaldaba a los estudiantes en este caso - redmas.com.co</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>France 24</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNazV1YUNZc0xtelFRTklmUlVWSy0ySGtiWjUxa2tkaVdnWGlZc3Z5TkxXZ1UyM0NhY21ycktySlVRcW1wSGRnTkVhblctZUU4UVBVX3h3U0Nkc3NPRzNZOHZhY0FRa3hWcmQwbGk3X01hcHd4V2xfNjV1WG5yQ2Uwdm9IQkdZakE3VTdkN1ZnUFNIdzNTWW9qR2xNekxmeVpBbFpVODhMS0ZkdFZ3ZVdmRE5EU1pjV18taloxQTBwVHQ4S3J0dGRHNWZvNTRMMm1lM29waHl2aFJoaXZCamdZZURHSDY2bDNrWEIyaFdiU20?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNSmpSM1NzR3NJZ3plTzQtYTRZTVl2LWdBTjhWVDllTTJNdnJ5RGhoaTFEUFZZQlBCTGRFV2Y2TGplcFhjSU5fd3R6ZU5QZjFqR3dVYXIxc0VPX2xLaTlqOFZhRFNEaXhsdjlnMXNUc2IzdmZjUVlWNzRVRVhlS3hCeUdaLURhamxTUmhKcGRQVGJEVWZHbjQ4OGR5aExLQy05YXFqbllEcno4SW5kcXd6MlFVd0Y3VDNERW5reUFZZThQa2RwNUFBN3FILXZ3d3VqeEdIMW5Zc3Q5V3FEeW9vRGotM1gxbklRVHh3TNIB8gFBVV95cUxNT2Y1YlNyMWZCemZJLUdUMEYxSmw1REY1UjM3WDJiaXloZG9CdERtUEp1djV0bTBUNW45WlFCSTRVSjExOG56UlJZNmZHZFV1N01ZcEJvdGtOMHJNMUpIWDBWSTJTWUFZNDFPY1RUS1ZybnVLWldUSTRRaWM5WDRyckFBYjdnTk9HUGhqZllBZ0VBSDNDRzlWR2hZVGdBNTFBZnZHUThEc1E3c1NLbmZfb09wTGtXcFNVVVp2LVhZeTFjN0NWU2lBLVQtLWNJSU1LQVB3OTNUMlBuTWt6Q1laZTNVRG9XWkpFTmpwX2NmcG5hZw?oc=5</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -10576,17 +10576,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Hay menos ninis: Colombia registró en octubre la cifra más baja en ocho años de jóvenes que no estudian ni trabajan | El Colombiano - El Colombiano</t>
+          <t>Los estudiantes a los que los colegios en Colombia no podrán negar el cupo a pesar de esta situación - AS Colombia</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>AS Colombia</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNeXdDVC1IaXVDTFZXeUplRzF2Mzh1TUdheFNsUnQzX2RwVWxyTVhtd1VNRTdoSjNQRkxTeERVbjlVQUhOSUZHNWNweFlnTkFCdGZVRElaSkFJcmJnRzNlaWxZMS1oRUE2cmFENmJ6eXVPSW15VVhPWUxfTXMzWm96d195blNmMlJzeWRtVC1rU054ak1mUDJoM2ZCV1NoMjMtc1Z6MGpwZUMtSlE0MEExcDlZNDRMMnZFeVBYbHo1VnpBMkJIWWdLaVVMcDNFaWJlbDM4UzdQN3QyTTFOOEM0dFBiRVc5am9IQmFsTmJNRXNUMEtTT3fSAfsBQVVfeXFMT084RXRRYzZzaWIxM01iN0IwSFpBSXp6cEZ6eVFPOV9RVG1UVXBXdVByYTE1TDVqXzU0azZUZFRrbEI3LVJ3YzVqSndlbndlYThsRWN3Zm9JbXFuSmRuY1BFMEd4SFh3WWN4ZElwVy1ZQnBhb3ByUlMybUx6WGp2QjcwM3pqa0ZMdkZtQ2RONlE0OExEN1h4QzJjQVlnelRzU2psT1BSVUNNdUpmWDJKbURmVDhZdWI3UnUtNzRONVFzMWV6djZtb0R5b1o1VUJyTVI1MlRMTUhTRmNoX2liZHdMY3dDVjFfQ21XSGJVWTRBcFgxanlyRGpCNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPNzltbTBsa2trTDhUaW13ZEx3VVVCNWJYWUdMMzRiN3RJZnlaSlpSczNiTGVDT3JhcTd3YWZtV1lfdW5RT1JxY21FU0JqZlJyUVAwd2c2RWViQ09tb1BQbjkzVHItRUpnaWtWZjc3cEQ0QjdaWTJXaUI0UGY4c2c0Vmpzay1EVVgzX2RUMndFcXZkU25ZMFEzM1ZHbjc1UEdQQU9TNzc5TGVLRkFCdG0ybEpZdHc2VktRaVF4YTVCcTFLZk5ITnpWLVItMU5CbzZqV1lMMGxoNEN1VlRzdjc00gHzAUFVX3lxTE5Talh5Y09PR1RuSzhlOTZUbHNVRENDMlpXbE5rTGdZQ3ozUVFjM0p5V2VmcE1FQzVKdkZwc2p3SEl3SVhBT2NuajQzOWlkazF5UHZDQzg3VGFySHNtRDh6Wkx4bEhGdFdjZGFGVkxhZ2xZNjRLM3FZdGYxZVdSVDZNUURCckQ4NExUYXRpdHJHRHo4Sk9qUjh5djMwdm8xYjFpcVNmd083NXR6bUQwWE04V2FWek83U0xGdHY4LXBkbFlSZEhaTWktNmtkaHYxVDlFbXhrYXFDRXdid3hRSk1uVktwQ1NETFZrRW5xMFI4Y1oxWQ?oc=5</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -10619,17 +10619,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Tragedia en Antioquia: 17 adolescentes mueren al caer micro a un precipicio en Colombia - El Litoral</t>
+          <t>Colombia recoge aportes clave de jóvenes migrantes para el Primer Plan de Acción Nacional de Juventud, Paz y Seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>El Litoral</t>
+          <t>Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPek9JX1dudlVEb3diN3BlNW1WMUpBeEJydXlwN2tVUGNNZW5UY1hnOFNOWFI3dGtvRkR5aUJPZDN0QmlhcEtBM3phTWc1TWVBSUxMU0ZJa2s2OHM5OVZzZU52dHJudkI4R3RIUnZTVlZmRzYtS0locnVibkE5OUZocHVOSkFlckY1NHJzZDFTUmFYXzhQQlhPS3BLRV8tV0NCbFUwZnEyRjVVOFJnOTV4MGpvSlNBdE9GSUhKT0FiU2VEcENOVHpFVHVXODRtOEVwaEJiatIB2gFBVV95cUxQWlNEOG1VT0ZwSXJOT0Z0eDh1b1FYeE0tdnVFUVdVdHBrWGE0QlA0a05MRmQ1MmxmaEZ3X2pfRk1ESEQwV013ZWczWVRNVmVKWElJLTkwMWxMOXRQTjZXVWtWUU9ZMjViYnZRcE96VWU5Nm82VzByVXNaVU1wRzJCN3BBeTFoMm9DdFVKM2VYY0szaGJvV3FTZlRoNWhUWldmVjhueGpVc2p5bEhhV2t1MjNyUVhwYnI3VmNXYktxYVdJeDdFWF84VmZvcGpoVGY4dk93UTVIcFZ5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQb2FIenFRUjRjWTdVdHhwUWVLcDU3SHVBLTF4WGdDbDdvdEhuaFhXWkF3TndUeGxTMVVaZWt3dHZsUFF1ZWxFR0hJNWNPMkhpRWhZaVNvUFVIVW5zRUlhS2toYUUyM2wzTnVLRGxBdnNJSG9ISlBteXdMS3AtVEM5blJqbXFlYVo2M0ZKY2w2SXBKOEd2QnIyUHgzX0ZFcEtBUWh5X3V5SkNoWkZyUE9pRkM5TENhdzFhaW1QTlhvUXNmQ2FRVTBzLQ?oc=5</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -10662,17 +10662,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
+          <t>Colombia reporta 185 casos de niños quemados por pólvora, un crecimiento del 9% frente al 2024 - Caracol Radio</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -10687,17 +10687,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOVWdJWWtTdmZkcUY3QUM1ZmJJZTdkRnZvVlgtbkpsZS1aa2Y3SkZLMG5XWjlURkhBZzRFRTM0VTZab2FzWFBKM0pNYktVVl9KckdZaVdXTGRpMDRVZ0FPMmU1bmhsQk9NT3VWZjdkSnk1Qnc5bTZGN29vMWhzRkREOURQMzJhNVhXajdPaXlGVnhLNU9WeXBveVBidFVpblZweW9iamtzR2Y1UG5VX3BHX3VaQmpJcHdodmRNa0xkWmd4ZlgtUUHSAdoBQVVfeXFMTmUzalpBM2J2NHFmV185akVudW9XQVVqWDVNMi02cDBDdFBnXzFWMnNSb1J5SF9sMElVcl84WnQwTVdtMURQRm00TTZoc1BCZnJ5NGlqcWdjQUFtRGNiTlZia0tPVy1rZGR6dy1RVDI3Y21XMEZPV19KQXhFYVIwY0lDdHlrMU9sVldSQ2F6X0x2RnFXbVNRXzNsRUwzM1JwMVBsR0stdmRUU1M4bGJJVEllZm1heGNlMVdTQ1lRZUt1V3EtS09LUnV2QzFjSDltRHY0VGZROU40N2c?oc=5</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -10710,40 +10710,341 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
+          <t>Hay menos ninis: Colombia registró en octubre la cifra más baja en ocho años de jóvenes que no estudian ni trabajan | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>El Colombiano</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNeXdDVC1IaXVDTFZXeUplRzF2Mzh1TUdheFNsUnQzX2RwVWxyTVhtd1VNRTdoSjNQRkxTeERVbjlVQUhOSUZHNWNweFlnTkFCdGZVRElaSkFJcmJnRzNlaWxZMS1oRUE2cmFENmJ6eXVPSW15VVhPWUxfTXMzWm96d195blNmMlJzeWRtVC1rU054ak1mUDJoM2ZCV1NoMjMtc1Z6MGpwZUMtSlE0MEExcDlZNDRMMnZFeVBYbHo1VnpBMkJIWWdLaVVMcDNFaWJlbDM4UzdQN3QyTTFOOEM0dFBiRVc5am9IQmFsTmJNRXNUMEtTT3fSAfsBQVVfeXFMT084RXRRYzZzaWIxM01iN0IwSFpBSXp6cEZ6eVFPOV9RVG1UVXBXdVByYTE1TDVqXzU0azZUZFRrbEI3LVJ3YzVqSndlbndlYThsRWN3Zm9JbXFuSmRuY1BFMEd4SFh3WWN4ZElwVy1ZQnBhb3ByUlMybUx6WGp2QjcwM3pqa0ZMdkZtQ2RONlE0OExEN1h4QzJjQVlnelRzU2psT1BSVUNNdUpmWDJKbURmVDhZdWI3UnUtNzRONVFzMWV6djZtb0R5b1o1VUJyTVI1MlRMTUhTRmNoX2liZHdMY3dDVjFfQ21XSGJVWTRBcFgxanlyRGpCNTA?oc=5</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Luto en Colombia: accidente de autobús deja sin vida a su conductor y 16 adolescentes en Antioquia - France 24</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>France 24</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNazV1YUNZc0xtelFRTklmUlVWSy0ySGtiWjUxa2tkaVdnWGlZc3Z5TkxXZ1UyM0NhY21ycktySlVRcW1wSGRnTkVhblctZUU4UVBVX3h3U0Nkc3NPRzNZOHZhY0FRa3hWcmQwbGk3X01hcHd4V2xfNjV1WG5yQ2Uwdm9IQkdZakE3VTdkN1ZnUFNIdzNTWW9qR2xNekxmeVpBbFpVODhMS0ZkdFZ3ZVdmRE5EU1pjV18taloxQTBwVHQ4S3J0dGRHNWZvNTRMMm1lM29waHl2aFJoaXZCamdZZURHSDY2bDNrWEIyaFdiU20?oc=5</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
           <t>Mueren 16 niños al caer un autobús escolar por un barranco en Colombia - Euronews.com</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Euronews.com</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>gratuito</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
         <is>
           <t>Educación</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQamJCNDY1QWhwX0hOTE9LMzJMNW1CU2V0Skc5NEkyOUcwazUzbjhEQkt2aU1ha1FrN3VIOUlIQjZSdEJFVUJrWUZWNFlHZUFOTHlnNm93VUkxdk4tWlNpcWJUU1oydjg5WTNGSktZcTBZT2tSOXN1TzlpcVlNYVNZc2owUzU1SDdoRmxURXY4ZzlLclZTS0o0b2RTN1I?oc=5</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Jóvenes del Atlántico gritan “¡No más bullyng!” a través del arte - Gobernación del Atlántico</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Gobernación del Atlántico</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Política pública</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Sin identificar</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzExajdsZFN2UGduQnZXWjhydHdUNGNwZkJjQ1J0ZUR5cm96M01feHZIcFpQTGFpZWM0d0ZyVmhmVjRFWVRnaVhydHJkUU4yT3NYel9ZNm5tVGFLVXZKRHRXTFRkUzlubGx5eE9WVGgxRTg2SElBaGN3cW4tZ2hzRU9KdG51ZElRaGFablhHbTlzNTBEUEd1RmdCNExkOUFiVS1MUFBkOURYV004M3lhbzB0VlZYazBPVG8wOXBmYl9ldzNLUFE?oc=5</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>La chispa que está moviendo a Colombia: jóvenes que ya no sueñan con el futuro, lo construyen - ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNZ2cwYjk5Rk9ZV0p2c2paOHI1M2djamFCOExGYUFfTHpKTGIzOURhNFBQLUtBRDRhcGRmZ1ZxR3lnVkd5cTJYSFBjYkJlWkVnRFBIaFAxS0dIekZfREJHSGRtdE9hejRaaFJxZDlDaVJDZ09PVy1yOTVLZ2doQ0dqZ0RqeXRiLVhqdTQ4dGEwRUZoUTRXUmRNTFJEbTF6RUxKSy03NEdILTk3WWlia1lLTDlibVZ2UjJrMnhHeWhLVER3VkxPaDZyR1V3cEZhN3JTcDZCZtIB2gFBVV95cUxNeWo0TGhMNjdxTmFxeS01NlNpRm8yOVBDSklySlBaaWlPTTFyN1RZY2tBUHpGNG54T1cwMGY1akw0QVplT0hDdS1OLU9ZTXV1VnpBeFJMeHlWT3hDRGFxX3dGeVZQclZPbnlLeFhkejhIUFExdGZ3a0MxOVFOTnNBTE81YTRLemN2VnhsUlc5a1d5SUFSSk1ra3NJMTFodzZjcnlPYnhiNnljZHdLWXdtTXBwck1EaC0xRU5DUTQxWWJqNi14WVA3NmoxX19Ual9saEthZVBhSUFsQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Tragedia en Antioquia: 17 adolescentes mueren al caer micro a un precipicio en Colombia - El Litoral</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>El Litoral</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>gratuito</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPek9JX1dudlVEb3diN3BlNW1WMUpBeEJydXlwN2tVUGNNZW5UY1hnOFNOWFI3dGtvRkR5aUJPZDN0QmlhcEtBM3phTWc1TWVBSUxMU0ZJa2s2OHM5OVZzZU52dHJudkI4R3RIUnZTVlZmRzYtS0locnVibkE5OUZocHVOSkFlckY1NHJzZDFTUmFYXzhQQlhPS3BLRV8tV0NCbFUwZnEyRjVVOFJnOTV4MGpvSlNBdE9GSUhKT0FiU2VEcENOVHpFVHVXODRtOEVwaEJiatIB2gFBVV95cUxQWlNEOG1VT0ZwSXJOT0Z0eDh1b1FYeE0tdnVFUVdVdHBrWGE0QlA0a05MRmQ1MmxmaEZ3X2pfRk1ESEQwV013ZWczWVRNVmVKWElJLTkwMWxMOXRQTjZXVWtWUU9ZMjViYnZRcE96VWU5Nm82VzByVXNaVU1wRzJCN3BBeTFoMm9DdFVKM2VYY0szaGJvV3FTZlRoNWhUWldmVjhueGpVc2p5bEhhV2t1MjNyUVhwYnI3VmNXYktxYVdJeDdFWF84VmZvcGpoVGY4dk93UTVIcFZ5dw?oc=5</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -526,27 +526,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>¿Menos ninis o menos jóvenes?, una alerta silenciosa en Colombia - laopinion.co</t>
+          <t>Alerta en San Gil por intoxicación de estudiantes; ya se había presentado un caso similar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>laopinion.co</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -556,10 +556,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZjZOSnNfRFhRSE9mRDhqQ0ZTY0E5WThhbXJFamJjemRjUGxCa3BXOVdVUVFkZzNYV1hQazQtR2JVYUZTUE80Wi1OWHlhMkpTOWlyZUhmaTFMX0U2YWxiOTBZMndIQl9IcDRIQXdmWkNCcEU1LTJTQTNQQ0tTSy03VnZvVG0xOGZyaHpYV0xlT2VKWEpIaXl3b1ZyUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/alerta-en-san-gil-por-intoxicacion-de-estudiantes-ya-se-habia-presentado-un-caso-similar/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tres estudiantes de un colegio de San Gil, Santander, se intoxicaron con clonazepam. Hace una semana ya se había presentado un caso similar.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,27 +573,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alerta en San Gil por intoxicación de estudiantes; ya se había presentado un caso similar</t>
+          <t>¿Menos ninis o menos jóvenes?, una alerta silenciosa en Colombia - laopinion.co</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>laopinion.co</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,14 +603,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/alerta-en-san-gil-por-intoxicacion-de-estudiantes-ya-se-habia-presentado-un-caso-similar/</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Tres estudiantes de un colegio de San Gil, Santander, se intoxicaron con clonazepam. Hace una semana ya se había presentado un caso similar.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZjZOSnNfRFhRSE9mRDhqQ0ZTY0E5WThhbXJFamJjemRjUGxCa3BXOVdVUVFkZzNYV1hQazQtR2JVYUZTUE80Wi1OWHlhMkpTOWlyZUhmaTFMX0U2YWxiOTBZMndIQl9IcDRIQXdmWkNCcEU1LTJTQTNQQ0tTSy03VnZvVG0xOGZyaHpYV0xlT2VKWEpIaXl3b1ZyUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Funcionaria del Inpec fue capturada con un arma en evento de Álvaro Uribe y Paloma Valencia: así lo narró la candidata presidencial</t>
+          <t>Rival uruguayo para Medellín: Juventud de Las Piedras se clasificó - Futbolred</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Futbolred</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -689,14 +689,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/27/funcionaria-del-inpec-fue-capturada-con-un-arma-en-evento-de-alvaro-uribe-y-paloma-valencia-asi-lo-narro-la-candidata-presidencial/</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Tras un procedimiento de registro a la mujer de 30 años, identificada como Mónica Fernanda Joven Urbano, se le encontró al interior de un bolso un arma de fuego tipo pistola, al parecer calibre 25 mm, con un cargador y cinco cartuchos para la misma,...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPeF9nZVdzMW5xd0dVSmZFaXJkT2dKM2h1SWVUYUNHSkl0Q1hYbmFQTGd6NjM1dno0cUpYWS1wNGduR0ZFUVpnenhHaVhOQkRxT3ltSlV2NUEtZFAwZmNISWxkcUlYWmtMbWJJZzJzZHhSM0lqeURjUkFZV2JDSlpNM215OXo2aUZidEhOTVh3X0RqaHVPOU5tV3ltS2plMV9kc1ZXUTBieUVrYVVFTGVNRnFyRHFsbExxdUhnRVhaaW41bDhKU05WajFnemh2NTd0SEd6MFFYRnJaUXJONjBGQlFGc1doQ05h0gHoAUFVX3lxTE94X2dlV3MxbnF3R1VKZkVpcmRPZ0ozaHVJZVRhQ0dKSXRDWFhuYVBMZ3o2MzV2ejRxSlhZLXA0Z25HRkVRWmd6eEdpWE5CRHFPeW1KVXY1QS1kUDBmY0hJbGRxSVhaa0xtYklnMnNkeFIzSWp5RGNSQVlXYkNKWk0zbXk5ejZpRmJ0SE5NWHdfRGpodU85Tm1XeW1LamUxX2RzVldRMGJ5RWthVUVMZU1GcXJEcWxsTHF1SGdFWFppbjVsOEpTTlZqMWd6aHY1N3RIR3owUVhGclpRck42MEZCUUZzV2hDTmE?oc=5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -706,12 +702,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Juventud de Uruguay, próximo rival de Independiente Medellín en Copa Libertadores | El Colombiano - El Colombiano</t>
+          <t>Funcionaria del Inpec fue capturada con un arma en evento de Álvaro Uribe y Paloma Valencia: así lo narró la candidata presidencial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -721,12 +717,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -736,10 +732,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVjRIRXEySDlDYkx2ZWRCcTJDcjlfWHh4U1ZwRE4waUk0U0VjZEdnX2lFVkxTbzNIcVNCbTRpSXZDT0k4aU5UQ01ESGdrVXVsV0JmRmtFZ0pFOUFaYXZ5M2pmTlFyOWw5S3ZUYTNSLUZZUjZPRVY2UWdURUVHSllWLTdISHhxZ0JudF91ZWhKbGYwUnJEamIwdXQ1MnNJS000NEtSbE1pSmV5eVFjNDhpdV9LREpRdkk0Vkl1SExnXzltWFZFeE5WVktteEnSAdIBQVVfeXFMT2ZHQzZJMDNFdEJhYVBPSmpwSFl1eGhzSlFrSWZQYmdzX0JMdkxXaXgzSTkzVi1xMmtuVUV4Szg5UUV4WFhPMVhsUG1zOC1BOUlSdGdXMk1lWllmQjQzcDZlZGFlZHRfbzR4bHhZaVJsYlEzdVRXeW9fTDRJeTVWVG1pbkw2cXJGb0RRckJxRGF3QXJaYlU4Z2tXNlYxUG1rVUtKZ01HalZpUWFiOXFHWW43UFh5Y3lLZWt0QlRUVU1pN3F6Z1I4TnpSeG4wbU1oQnNn?oc=5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/02/27/funcionaria-del-inpec-fue-capturada-con-un-arma-en-evento-de-alvaro-uribe-y-paloma-valencia-asi-lo-narro-la-candidata-presidencial/</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Tras un procedimiento de registro a la mujer de 30 años, identificada como Mónica Fernanda Joven Urbano, se le encontró al interior de un bolso un arma de fuego tipo pistola, al parecer calibre 25 mm, con un cargador y cinco cartuchos para la misma,...</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rival uruguayo para Medellín: Juventud de Las Piedras se clasificó - Futbolred</t>
+          <t>Juventud de Uruguay, próximo rival de Independiente Medellín en Copa Libertadores | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Futbolred</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPeF9nZVdzMW5xd0dVSmZFaXJkT2dKM2h1SWVUYUNHSkl0Q1hYbmFQTGd6NjM1dno0cUpYWS1wNGduR0ZFUVpnenhHaVhOQkRxT3ltSlV2NUEtZFAwZmNISWxkcUlYWmtMbWJJZzJzZHhSM0lqeURjUkFZV2JDSlpNM215OXo2aUZidEhOTVh3X0RqaHVPOU5tV3ltS2plMV9kc1ZXUTBieUVrYVVFTGVNRnFyRHFsbExxdUhnRVhaaW41bDhKU05WajFnemh2NTd0SEd6MFFYRnJaUXJONjBGQlFGc1doQ05h0gHoAUFVX3lxTE94X2dlV3MxbnF3R1VKZkVpcmRPZ0ozaHVJZVRhQ0dKSXRDWFhuYVBMZ3o2MzV2ejRxSlhZLXA0Z25HRkVRWmd6eEdpWE5CRHFPeW1KVXY1QS1kUDBmY0hJbGRxSVhaa0xtYklnMnNkeFIzSWp5RGNSQVlXYkNKWk0zbXk5ejZpRmJ0SE5NWHdfRGpodU85Tm1XeW1LamUxX2RzVldRMGJ5RWthVUVMZU1GcXJEcWxsTHF1SGdFWFppbjVsOEpTTlZqMWd6aHY1N3RIR3owUVhGclpRck42MEZCUUZzV2hDTmE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVjRIRXEySDlDYkx2ZWRCcTJDcjlfWHh4U1ZwRE4waUk0U0VjZEdnX2lFVkxTbzNIcVNCbTRpSXZDT0k4aU5UQ01ESGdrVXVsV0JmRmtFZ0pFOUFaYXZ5M2pmTlFyOWw5S3ZUYTNSLUZZUjZPRVY2UWdURUVHSllWLTdISHhxZ0JudF91ZWhKbGYwUnJEamIwdXQ1MnNJS000NEtSbE1pSmV5eVFjNDhpdV9LREpRdkk0Vkl1SExnXzltWFZFeE5WVktteEnSAdIBQVVfeXFMT2ZHQzZJMDNFdEJhYVBPSmpwSFl1eGhzSlFrSWZQYmdzX0JMdkxXaXgzSTkzVi1xMmtuVUV4Szg5UUV4WFhPMVhsUG1zOC1BOUlSdGdXMk1lWllmQjQzcDZlZGFlZHRfbzR4bHhZaVJsYlEzdVRXeW9fTDRJeTVWVG1pbkw2cXJGb0RRckJxRGF3QXJaYlU4Z2tXNlYxUG1rVUtKZ01HalZpUWFiOXFHWW43UFh5Y3lLZWt0QlRUVU1pN3F6Z1I4TnpSeG4wbU1oQnNn?oc=5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quién es María Julissa, la ‘influencer’ que estaría vinculada con alias El Mencho: lleva seis meses viviendo en Colombia</t>
+          <t>Video viral en redes sociales evidenciaría la falta de atención en hospital Meissen de Bogotá: “Lleva una hora gritando y no lo ayudan”</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1026,27 +1026,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/25/quien-es-maria-julissa-la-influencer-que-estaria-vinculada-con-alias-el-mencho-lleva-seis-meses-viviendo-en-colombia/</t>
+          <t>https://www.infobae.com/colombia/2026/02/25/video-viral-en-redes-sociales-evidenciaria-la-falta-de-atencion-en-hospital-meissen-de-bogota-lleva-una-hora-gritando-y-no-lo-ayudan/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>La joven creadora de contenido rechazó su vinculación con el operativo que dio de baja al líder del Cartel Jalisco Nueva Generación</t>
+          <t>En el clip se observa a un joven llorando por un dolor intenso en el abdomen, mientras el personal médico pasa a su lado con aparente indiferencia</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Video viral en redes sociales evidenciaría la falta de atención en hospital Meissen de Bogotá: “Lleva una hora gritando y no lo ayudan”</t>
+          <t>Identifican al taxista que recogió a Diana Ospina: es muy joven y con antecedentes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1073,29 +1073,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/25/video-viral-en-redes-sociales-evidenciaria-la-falta-de-atencion-en-hospital-meissen-de-bogota-lleva-una-hora-gritando-y-no-lo-ayudan/</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>En el clip se observa a un joven llorando por un dolor intenso en el abdomen, mientras el personal médico pasa a su lado con aparente indiferencia</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/identifican-taxista-que-secuestraron-diana-ospina-nombre-PP5065588</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1105,12 +1101,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Identifican al taxista que recogió a Diana Ospina: es muy joven y con antecedentes</t>
+          <t>Salud pública: la maternidad adolescente, factor que multiplica la pobreza - AmCham Colombia – Cámara de Comercio Colombo Americana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>AmCham Colombia – Cámara de Comercio Colombo Americana</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1120,12 +1116,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1135,7 +1131,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/identifican-taxista-que-secuestraron-diana-ospina-nombre-PP5065588</t>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxQS1h3cmhKMXdhZUtFa2ZBeWhYVkxWd19KalVSZ29zQlhqVmtvUEF3QmdiMXZNVjJWYkZ6SjBuVFNQblMzQTh5MVhwazRTOVlvbVRqTGl2cVowVXNjcmwtSFVwTl83blJZSGJ2cVo1VTUybzRhOFdmNEYtdzZvcjdrR2J1NWY0TGlXSUMtWmRETS1qTUM4endWckp2bnc4azdaWExlTk5wOG1kLUNTbHpPNUZCcG9wb1lWRHNBWTdqYUhOQUg4V09QX3RLUGRMNnNLcEdQN1Z4am56SGRHU2V2TWpJZzZTZm40cHFobXg4YTA2UXJOUVNSTXdGM0lFWmFoazdObEI4bWdwZXdEaHNtNV9XRGE5bE9rSnYzUHdPalRiYS1u?oc=5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1148,12 +1144,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Salud pública: la maternidad adolescente, factor que multiplica la pobreza - AmCham Colombia – Cámara de Comercio Colombo Americana</t>
+          <t>De perder una beca universitaria a la adicción digital: así afecta el celular a niños y adolescentes en Colombia - Pulzo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AmCham Colombia – Cámara de Comercio Colombo Americana</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1163,7 +1159,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1178,7 +1174,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxQS1h3cmhKMXdhZUtFa2ZBeWhYVkxWd19KalVSZ29zQlhqVmtvUEF3QmdiMXZNVjJWYkZ6SjBuVFNQblMzQTh5MVhwazRTOVlvbVRqTGl2cVowVXNjcmwtSFVwTl83blJZSGJ2cVo1VTUybzRhOFdmNEYtdzZvcjdrR2J1NWY0TGlXSUMtWmRETS1qTUM4endWckp2bnc4azdaWExlTk5wOG1kLUNTbHpPNUZCcG9wb1lWRHNBWTdqYUhOQUg4V09QX3RLUGRMNnNLcEdQN1Z4am56SGRHU2V2TWpJZzZTZm40cHFobXg4YTA2UXJOUVNSTXdGM0lFWmFoazdObEI4bWdwZXdEaHNtNV9XRGE5bE9rSnYzUHdPalRiYS1u?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOenBPdUJMa1NWeWktbjQyUmoxQkY3Y0lUcFhfTko5bnRnYmVjTk5FZ29pTzBhSlpuYXVaQTdBVlA2OVRERmxLLXY5dDNPQm1yY3cyeDh3V0M1OUFOckZIaUc4enI4S05GQTdIQkRiR0Vwc24xVEs1MGdOa2lJUXlCMi1uSGctS3U5WkRjcWY1d3JVSXJNQnpQLVFXUUt2WVMxYVB1clVzNWtPZU95anRSeGFhVW5kM3VNdTZyZ3RXUjRvR1BnNHNVWVI1UEHSAdIBQVVfeXFMT3E3Y2k0bVlzQ2RwYkRSY0NQZXJHMUtHbHB3YmtBYTlnZTFUejQzZWhhMUdmRmFqMGhCOGFrWlVRazhBdnIwTGx6NHAweXBZLXFRVmZkYjlGd3BOQkhEY3M0Y3NDdFBzYjlwMHZOZDBwLVJOSklkT2phZGNnNHNhN3ExYzA5czhTSjBYMWFxcE5NT3pVRVQtR0ZIcU1fWURXN21nendTTG1PcDE1WkowanAweG9GZHZFc0lnaWtxb1ZGR1FrZ0J0VUdldFBNeDVtNEJB?oc=5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1191,12 +1187,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>De perder una beca universitaria a la adicción digital: así afecta el celular a niños y adolescentes en Colombia - Pulzo</t>
+          <t>Quién es María Julissa, la ‘influencer’ que estaría vinculada con alias El Mencho: lleva seis meses viviendo en Colombia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1221,10 +1217,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOenBPdUJMa1NWeWktbjQyUmoxQkY3Y0lUcFhfTko5bnRnYmVjTk5FZ29pTzBhSlpuYXVaQTdBVlA2OVRERmxLLXY5dDNPQm1yY3cyeDh3V0M1OUFOckZIaUc4enI4S05GQTdIQkRiR0Vwc24xVEs1MGdOa2lJUXlCMi1uSGctS3U5WkRjcWY1d3JVSXJNQnpQLVFXUUt2WVMxYVB1clVzNWtPZU95anRSeGFhVW5kM3VNdTZyZ3RXUjRvR1BnNHNVWVI1UEHSAdIBQVVfeXFMT3E3Y2k0bVlzQ2RwYkRSY0NQZXJHMUtHbHB3YmtBYTlnZTFUejQzZWhhMUdmRmFqMGhCOGFrWlVRazhBdnIwTGx6NHAweXBZLXFRVmZkYjlGd3BOQkhEY3M0Y3NDdFBzYjlwMHZOZDBwLVJOSklkT2phZGNnNHNhN3ExYzA5czhTSjBYMWFxcE5NT3pVRVQtR0ZIcU1fWURXN21nendTTG1PcDE1WkowanAweG9GZHZFc0lnaWtxb1ZGR1FrZ0J0VUdldFBNeDVtNEJB?oc=5</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/02/25/quien-es-maria-julissa-la-influencer-que-estaria-vinculada-con-alias-el-mencho-lleva-seis-meses-viviendo-en-colombia/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>La joven creadora de contenido rechazó su vinculación con el operativo que dio de baja al líder del Cartel Jalisco Nueva Generación</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>La juventud colombiana en 2026: entre la esperanza y el cansancio - El Espectador</t>
+          <t>Estudiante de 14 años murió tras riña con arma blanca a la salida de colegio en Bello</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1397,10 +1397,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNZGptN2ozLWktYnNOTWpuMjdDR21vSzJ3SEhhajFHQVZXRmhDalZxem9uS3lFYjRtSnRTZWx5eEcyMGhOMG55Z09sRnFjZlVCXzI3d2k5TGhPVDUwbmNPNFBWWGxyckp2VUpqVlpJU0hlNTJUS3E2QTBPX0pMMUtDSFdZR3hqbFpOQlFLV3dXdHd5ZTRFRDJ1MXlxc0p1cEk4M253MldaOXdCNUp5LURMcUo1MkpqbGQ3TXVsZFo0NVRzMTZweE5MSzliY3QySERvWGxCS183ONIB6wFBVV95cUxQNmZwTXFhTVNaR21LWWdoX0lkSUNKQjduRnJZLU1kTEJ4bjNFZEdUSEhqMHlMUnk5Wm5naVNjVU43VGVrNWVkMXNRZ0V0d3h4bXQwc3o1U3dOREdzN1hRQmFxRmRIRlR5ZnVQWDFKcnAwX3pjem1mek5zNkx0dWJRWDVrem5xOHE4angzMGFYMXNkVnFvWHEwQW9HSXU4b1I2djhXaGNpSEl4OEtac1kwN2dtQmZ5NEJhNU8xazFZajNZWXpGV1VwclVpNHRveFItaTU1VXZoSkZibHJFV1lvWDkzNG1Cd09kVUVF?oc=5</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/medellin/estudiante-de-14-anos-en-bello-muere-tras-rina-con-arma-blanca/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>La víctima cursaba sétimo grado en el colegio CUVIC, murió tras riña con arma blanca a la salida de la jornada escolar.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1410,37 +1414,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Más de 85.000 niños están en riesgo de abandonar los colegios en Bogotá: alertan sobre vulneración de derechos - Infobae</t>
+          <t>La juventud colombiana en 2026: entre la esperanza y el cansancio - El Espectador</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOUjhkOUc3eTE2NTVsUkQ1b0VIRnFmbFRWd19mWDV0OHlyZ3Q2YUdsbHJWQVVXdkRJc2hOWlFwSmQ3UzNNb0lwNEVlU0dOM05QZ1hPZzVJT21xRWRRclgwNjlFUENHRjUyNU9oUXh0aWI4STAxblo4cTZsVlpNR2x1Wkk2aW5neTJDY0dzODVRQy1BNTJUd09Vdl85dDhoenVBLVFXekM3ZjRHYlNsMXl2XzFxWDFJTnlEUFlXb3hMV3d2YmItZVNIT0xJMUlGcnBJeGJhNVRaMW8wV1lnem1wbEtpbEY1ZUxm0gGDAkFVX3lxTE5DY0RudmZkU1BKdnFMMW1mekRBUmtpZlRaRGRfeTZsMGVEUHJZNks2d1B2MXp6amtUYk1xUWN2LXBfVGxHOEFocHZpWnViVlh3dnlBZkZGdDJQSlRSX1pwY1hqWXpvcVhjZEpyRk1wTmdwTWt2cWJ0VVFNbGF3QjJGczhORFplQl9lRmdKRE1IZUZ4U29UaDhIR1BsLTMxZmtkWE5TbmpWeHJrcE45YTk4eWtfTW43dlFsUUlpaUNHN0VtNzRlYzJtT3o5SkYyVGhVcUNFTFVab21sS3oybXZselp4WGFtdTlUVHU3TG8tR1Z1UVd5b1l6eVhpZkpBbF9RdmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNZGptN2ozLWktYnNOTWpuMjdDR21vSzJ3SEhhajFHQVZXRmhDalZxem9uS3lFYjRtSnRTZWx5eEcyMGhOMG55Z09sRnFjZlVCXzI3d2k5TGhPVDUwbmNPNFBWWGxyckp2VUpqVlpJU0hlNTJUS3E2QTBPX0pMMUtDSFdZR3hqbFpOQlFLV3dXdHd5ZTRFRDJ1MXlxc0p1cEk4M253MldaOXdCNUp5LURMcUo1MkpqbGQ3TXVsZFo0NVRzMTZweE5MSzliY3QySERvWGxCS183ONIB6wFBVV95cUxQNmZwTXFhTVNaR21LWWdoX0lkSUNKQjduRnJZLU1kTEJ4bjNFZEdUSEhqMHlMUnk5Wm5naVNjVU43VGVrNWVkMXNRZ0V0d3h4bXQwc3o1U3dOREdzN1hRQmFxRmRIRlR5ZnVQWDFKcnAwX3pjem1mek5zNkx0dWJRWDVrem5xOHE4angzMGFYMXNkVnFvWHEwQW9HSXU4b1I2djhXaGNpSEl4OEtac1kwN2dtQmZ5NEJhNU8xazFZajNZWXpGV1VwclVpNHRveFItaTU1VXZoSkZibHJFV1lvWDkzNG1Cd09kVUVF?oc=5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1453,44 +1457,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estudiante de 14 años murió tras riña con arma blanca a la salida de colegio en Bello</t>
+          <t>Más de 85.000 niños están en riesgo de abandonar los colegios en Bogotá: alertan sobre vulneración de derechos - Infobae</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/medellin/estudiante-de-14-anos-en-bello-muere-tras-rina-con-arma-blanca/</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>La víctima cursaba sétimo grado en el colegio CUVIC, murió tras riña con arma blanca a la salida de la jornada escolar.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOUjhkOUc3eTE2NTVsUkQ1b0VIRnFmbFRWd19mWDV0OHlyZ3Q2YUdsbHJWQVVXdkRJc2hOWlFwSmQ3UzNNb0lwNEVlU0dOM05QZ1hPZzVJT21xRWRRclgwNjlFUENHRjUyNU9oUXh0aWI4STAxblo4cTZsVlpNR2x1Wkk2aW5neTJDY0dzODVRQy1BNTJUd09Vdl85dDhoenVBLVFXekM3ZjRHYlNsMXl2XzFxWDFJTnlEUFlXb3hMV3d2YmItZVNIT0xJMUlGcnBJeGJhNVRaMW8wV1lnem1wbEtpbEY1ZUxm0gGDAkFVX3lxTE5DY0RudmZkU1BKdnFMMW1mekRBUmtpZlRaRGRfeTZsMGVEUHJZNks2d1B2MXp6amtUYk1xUWN2LXBfVGxHOEFocHZpWnViVlh3dnlBZkZGdDJQSlRSX1pwY1hqWXpvcVhjZEpyRk1wTmdwTWt2cWJ0VVFNbGF3QjJGczhORFplQl9lRmdKRE1IZUZ4U29UaDhIR1BsLTMxZmtkWE5TbmpWeHJrcE45YTk4eWtfTW43dlFsUUlpaUNHN0VtNzRlYzJtT3o5SkYyVGhVcUNFTFVab21sS3oybXZselp4WGFtdTlUVHU3TG8tR1Z1UVd5b1l6eVhpZkpBbF9RdmM?oc=5</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>“Boom” de deudores jóvenes: más tarjetas, más riesgo; así es la nueva cara del crédito en Colombia - ELTIEMPO.COM</t>
+          <t>Subsidios y endeudamiento juvenil: puntos críticos de la reforma pensional en Colombia - Caracol Radio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQSldNa3RSdGU3cW1YdzJGc2JTYks2Yzc0Sl9lSTZvZF9WblJOa0ZMVFVoSkpCejAtM2NmZHhEbjFHWEI4bUh3cHJOWFktV0hkeWxqZ3BvNDhMWERyQ1BRdUpPVmJjdjBvZG1TWTRjMm9QWmsyMlFvOG56Sm1TaUdWYnhYZVRaX3Y1T1V3ZkFGdnIydncxUjV2dzhsSWVyaHlWcmNERlJpeUVxZXVDdmczZFZDRnYyWmlaUXIyRXM3anB5UTVzdFprWG9vTTNkcUNDMmNLUk5EbC1FQzhVTmVOTVd4YjBrXy0za015dzNZU2tld9IB9wFBVV95cUxNXy1zRWx4U1U2cFNiWjZ1d1pJWFpxS1hiMzdHbVVqV1ZaV01yT0k3V2FBVEhDSHZkTExnOFZmM1ZsLURvV0gtbE1qRllwYVcyaEZMLTItNGY5dU82QUMzdVNYaFlYbUhhMDloRll3dVFjY3B6eUk3VUFRaWFkaHVRXzQ0RGVZdWgzWUY3R1RPMlNvY3ZBbWJEYnY3NUNoSHZGTTI0bXdwWE5HYkFBejMxc1FOb2l0ajdsQkdidXUxcHhOUzlraXFDd1NteXhHeTBQaUpodE5WV1lkcXJyT0FVUi1rcGk2eUdPaWZmWmZGVlFBZ3BDaktn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQYk9nR0dVZ3JPRXBES2dxRmV2WXZqaFRqWkxOcFlxeWE4Snllb3h1YlpOTTdjRElEc3gtSFFkbWtDeUlCYkM5THo3cDFrcWRXMm5MRzBiWVFtZlFJNVprMC03VDRJcGo4Q1FDanJFa1BGWG5ZWnZQSjFJSk9tNllBc2xXVVpxVW82Z1RKMFZPQVRnT0Z4Z25lVllVTzlwb1BRQXpvYmlfeC1oRlNBbFRhYUl6MG9CRTRwOGNwc3VyVkNYTHpFdXpyU0x6VjBaUk1r0gHQAUFVX3lxTFBiT2dHR1Vnck9FcERLZ3FGZXZZdmpoVGpaTE5wWXF5YThKeWVveHViWk5NN2NESURzeC1IUWRta0N5SUJiQzlMejdwMWtxZFcybkxHMGJZUW1mUUk1WmswLTdUNElwajhDUUNqckVrUEZYblladlBKMUlKT202WUFzbFdVWnFVbzZnVEowVk9BVGdPRnhnbmVWWVVPOXBvUFFBem9iaV94LWhGU0FsVGFhSXowb0JFNHA4Y3BzdXJWQ1hMekV1enJTTHpWMFpSTWs?oc=5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -2020,44 +2020,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>Subsidios y endeudamiento juvenil: puntos críticos de la reforma pensional en Colombia - Caracol Radio</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZWw5MVkzUXpQT18yNm1TS1l3bHFVYTVTcW9zN01YUFFvOWN0ZlNQbC0yTmcyazJESWxxeW9tZG52RF81N2JlY2RpXzNDbndkVXJhY3lkZ0ZWdUhzYzJOTHVwQ0hJaGlNUHozenNrODl2NEVXejNrQm81Uzd2Y0FXXzBmZ3luMDhuLVR6SElPeTdUVU5Tdnlmci1uQkNCeVVMWjJoSlN4RE1QUXF2cGtQY3VUbTBzX1kzV214ZNIB0AFBVV95cUxQYk9nR0dVZ3JPRXBES2dxRmV2WXZqaFRqWkxOcFlxeWE4Snllb3h1YlpOTTdjRElEc3gtSFFkbWtDeUlCYkM5THo3cDFrcWRXMm5MRzBiWVFtZlFJNVprMC03VDRJcGo4Q1FDanJFa1BGWG5ZWnZQSjFJSk9tNllBc2xXVVpxVW82Z1RKMFZPQVRnT0Z4Z25lVllVTzlwb1BRQXpvYmlfeC1oRlNBbFRhYUl6MG9CRTRwOGNwc3VyVkNYTHpFdXpyU0x6VjBaUk1r?oc=5</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2067,17 +2063,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2087,7 +2083,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2097,12 +2093,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.diarioadn.co/seccion/cultura</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
         </is>
       </c>
     </row>
@@ -2114,27 +2110,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Subsidios y endeudamiento juvenil: puntos críticos de la reforma pensional en Colombia - Caracol Radio</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2144,10 +2140,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQYk9nR0dVZ3JPRXBES2dxRmV2WXZqaFRqWkxOcFlxeWE4Snllb3h1YlpOTTdjRElEc3gtSFFkbWtDeUlCYkM5THo3cDFrcWRXMm5MRzBiWVFtZlFJNVprMC03VDRJcGo4Q1FDanJFa1BGWG5ZWnZQSjFJSk9tNllBc2xXVVpxVW82Z1RKMFZPQVRnT0Z4Z25lVllVTzlwb1BRQXpvYmlfeC1oRlNBbFRhYUl6MG9CRTRwOGNwc3VyVkNYTHpFdXpyU0x6VjBaUk1r0gHQAUFVX3lxTFBiT2dHR1Vnck9FcERLZ3FGZXZZdmpoVGpaTE5wWXF5YThKeWVveHViWk5NN2NESURzeC1IUWRta0N5SUJiQzlMejdwMWtxZFcybkxHMGJZUW1mUUk1WmswLTdUNElwajhDUUNqckVrUEZYblladlBKMUlKT202WUFzbFdVWnFVbzZnVEowVk9BVGdPRnhnbmVWWVVPOXBvUFFBem9iaV94LWhGU0FsVGFhSXowb0JFNHA4Y3BzdXJWQ1hMekV1enJTTHpWMFpSTWs?oc=5</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2157,42 +2157,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/cultura</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Subsidios y endeudamiento juvenil: puntos críticos de la reforma pensional en Colombia - Caracol Radio</t>
+          <t>“Boom” de deudores jóvenes: más tarjetas, más riesgo; así es la nueva cara del crédito en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZWw5MVkzUXpQT18yNm1TS1l3bHFVYTVTcW9zN01YUFFvOWN0ZlNQbC0yTmcyazJESWxxeW9tZG52RF81N2JlY2RpXzNDbndkVXJhY3lkZ0ZWdUhzYzJOTHVwQ0hJaGlNUHozenNrODl2NEVXejNrQm81Uzd2Y0FXXzBmZ3luMDhuLVR6SElPeTdUVU5Tdnlmci1uQkNCeVVMWjJoSlN4RE1QUXF2cGtQY3VUbTBzX1kzV214ZNIB0AFBVV95cUxQYk9nR0dVZ3JPRXBES2dxRmV2WXZqaFRqWkxOcFlxeWE4Snllb3h1YlpOTTdjRElEc3gtSFFkbWtDeUlCYkM5THo3cDFrcWRXMm5MRzBiWVFtZlFJNVprMC03VDRJcGo4Q1FDanJFa1BGWG5ZWnZQSjFJSk9tNllBc2xXVVpxVW82Z1RKMFZPQVRnT0Z4Z25lVllVTzlwb1BRQXpvYmlfeC1oRlNBbFRhYUl6MG9CRTRwOGNwc3VyVkNYTHpFdXpyU0x6VjBaUk1r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQSldNa3RSdGU3cW1YdzJGc2JTYks2Yzc0Sl9lSTZvZF9WblJOa0ZMVFVoSkpCejAtM2NmZHhEbjFHWEI4bUh3cHJOWFktV0hkeWxqZ3BvNDhMWERyQ1BRdUpPVmJjdjBvZG1TWTRjMm9QWmsyMlFvOG56Sm1TaUdWYnhYZVRaX3Y1T1V3ZkFGdnIydncxUjV2dzhsSWVyaHlWcmNERlJpeUVxZXVDdmczZFZDRnYyWmlaUXIyRXM3anB5UTVzdFprWG9vTTNkcUNDMmNLUk5EbC1FQzhVTmVOTVd4YjBrXy0za015dzNZU2tld9IB9wFBVV95cUxNXy1zRWx4U1U2cFNiWjZ1d1pJWFpxS1hiMzdHbVVqV1ZaV01yT0k3V2FBVEhDSHZkTExnOFZmM1ZsLURvV0gtbE1qRllwYVcyaEZMLTItNGY5dU82QUMzdVNYaFlYbUhhMDloRll3dVFjY3B6eUk3VUFRaWFkaHVRXzQ0RGVZdWgzWUY3R1RPMlNvY3ZBbWJEYnY3NUNoSHZGTTI0bXdwWE5HYkFBejMxc1FOb2l0ajdsQkdidXUxcHhOUzlraXFDd1NteXhHeTBQaUpodE5WV1lkcXJyT0FVUi1rcGk2eUdPaWZmWmZGVlFBZ3BDaktn?oc=5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jóvenes habitantes de calle serán guardianes de Bogotá: se capacitarán en temas de reciclaje - Bogota.gov.co</t>
+          <t>En el oriente de Cali tenían a dos adolescentes que serían reclutados por la estructura criminal 'Jacobo Arenas': los iban a llevar al Cauca - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZTlVbXhUR0VMSmF3NDJXWVlwWmwyYzBISlQ0MVRNSUdOSWQwcThFZWt3eTBJUmpRMVl1YkVDR3NSa0FEWEpqdVJfWnlNcHA4SWhpai05OHo0czdBVF8wTnlLVGRfVEpzeEc4NDhXcGlEaThvcDlHdXJIZ01INDlaN1lad2tubHVWM0Z0ZFlEOGV0dmhESjNmZDJPMFlJY01ETHBNUmhlOWtJZkNaUkRkQnowdHd3Wlp2MlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxPUDNwLXRyY3FHY2JlX0luT0d3UzBjSXpGZFBsRFptUnBFUTZRbVJLWUhWQmpVVzhlc1pVMEMtSjhCR2NvRFNocGtCZkZ3MDFxbEFJci10bmZtdGdFS0R5WGtnMU1lOTJxSXBpSVQtMlRKSGtWaWpmWE0tbzdqNHF2RVpYQ0UwUmYtVlMxMFJmZGpReHZhWm1uYUFKQmtIbjRsS2FUdzFDcFVidlQ1cjBuR0RkUTB1YUVhN0hQNTdELVdQYy1lcDZ5a09YUllmLUVFck1DemFsX2hSOVVjZEZhZm5XY2FWYjFXblNmenZxb0JrUVVvT3pHRW5PUlhKZEVuUlZSSklUMGpmZ0hxX2VZaURuamxFeW_SAZcCQVVfeXFMT1AzcC10cmNxR2NiZV9Jbk9Hd1MwY0l6RmRQbERabVJwRVE2UW1SS1lIVkJqVVc4ZXNaVTBDLUo4Qkdjb0RTaHBrQmZGdzAxcWxBSXItdG5mbXRnRUtEeVhrZzFNZTkycUlwaUlULTJUSkhrVmlqZlhNLW83ajRxdkVaWENFMFJmLVZTMTBSZmRqUXh2YVptbmFBSkJrSG40bEthVHcxQ3BVYnZUNXIwbkdEZFEwdWFFYTdIUDU3RC1XUGMtZXA2eWtPWFJZZi1FRXJNQ3phbF9oUjlVY2RGYWZuV2NhVmIxV25TZnp2cW9Ca1FVb096R0VuT1JYSmRFblJWUkpJVDBqZmdIcV9lWWlEbmpsRXlv?oc=5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>En el oriente de Cali tenían a dos adolescentes que serían reclutadas por la estructura criminal 'Jacobo Arenas': los iban a llevar al Cauca - ELTIEMPO.COM</t>
+          <t>Alcaldía conecta a estudiantes con universidades y oportunidades de financiación - Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPT1ZiOXh5MXdsMHFndzNHWDVEem54MUpaQXIwLWg2VlRKQXk5OWFaR0NHRWJPMzhKQ1JwOS1BUzlkYUNVZEpBaGR2SElSNG9zUXFFV3YxQ0pseWlIdjM3cG5JSExJQUtIOHVwWEhuQ0wwOERncldqTTBvak1MOThJNmFCbGVwWHFPZlljVFEtb000bWhyRWNHdlFySGtKY3pXd2dDc0dUdDdxb0dzOXRGVXVlcm5iVzJMTTJzaThCdDVSNmpSWTlrVGs3d2dxYWxtRlpmRmtIaElDd3IxdERjQjVjT0tfRGV4d1NkVTV2T00yN2QzWkYxUHBidDhlVEJGSFNoY0lQRVdCc2U2c0tlSUZB0gGXAkFVX3lxTE9QM3AtdHJjcUdjYmVfSW5PR3dTMGNJekZkUGxEWm1ScEVRNlFtUktZSFZCalVXOGVzWlUwQy1KOEJHY29EU2hwa0JmRncwMXFsQUlyLXRuZm10Z0VLRHlYa2cxTWU5MnFJcGlJVC0yVEpIa1ZpamZYTS1vN2o0cXZFWlhDRTBSZi1WUzEwUmZkalF4dmFabW5hQUpCa0huNGxLYVR3MUNwVWJ2VDVyMG5HRGRRMHVhRWE3SFA1N0QtV1BjLWVwNnlrT1hSWWYtRUVyTUN6YWxfaFI5VWNkRmFmbldjYVZiMVduU2Z6dnFvQmtRVW9PekdFbk9SWEpkRW5SVlJKSVQwamZnSHFfZVlpRG5qbEV5bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSGNJLWNiT0JsQlpPUmVWSjJDZE82M2pOVGtLNkozcXFjdU5pa1pMaENkbFQ3c3dmSGc2X1dtdy1KM0txRUlaMjNvZEY3T19lNmZmWk1wZllDdWhqelEzd3ludXhRRnlVZG9OU09xLTlyLUUzTWE2LTFGcURsWmVFeWNxc3lLY05hWFZsR1FwTTFGZl9ZeURESE1HTkoxbWhhMVp2TWg3bklENzFsakRkdUlIQXAwT1pUZlVDMTBqMlBYS1JxQ3BzeGZ2VmF6ZU12c24xVw?oc=5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jóvenes habitantes de calle serán guardianes de Bogotá: se capacitarán en temas de reciclaje - Suba Alternativa</t>
+          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Suba Alternativa</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2348,22 +2348,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQS1VXYmlYVUpOTVJ4NGVoY0M2OXc2OVl2dkhRbmZBYW5DN0tIVXNpV3kycERZbmktTTJwMWN3ZTR0NkZtUWxTVXNMaVNyZjQ1cDJiN1pLRFlRMV9kdl9zdFhIUEFqUElSSTBYbEFNbHNKOFgtRjU4Z0VkZ3RROTcxbmFzRFZvYUpZTDBaNTBSUUh5VUFVQzFBSU8xVXphcU8ycXZnekpmaU1yTzh0NUtZN19jVXhNR3haQ3Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>¿Polémica tendencia de los 'therians' llega a Colombia? Anuncian encuentro de jóvenes que se 'identifican' como animales en tradicional parque de Cali - ELTIEMPO.com</t>
+          <t>Plan en Bogotá busca convertir a jóvenes habitantes de calle en promotores ambientales - Periodismo Público</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ELTIEMPO.com</t>
+          <t>Periodismo Público</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOOWxBdEpsazBoazhCNG0tOEFiQ1JtQVNmQVZzZGNpb2pELW9wZGtWbGdOQnpCYmUtTXoxTlRLN3czRXhKaW52Ry1vdjlfekU1czV4LTg3ejVoQ2lONFh6QmhKN2VtQWtWVnVNUXg4bHNmNWNXQ0NMaHFqaF9XbWFvUFo1ZjQyT051TG5xaUV5UWg2YThMbnRTVVpNNVlaU3F0ZzNVS3RJcjJkMWNvYmtUcnpUNWhqejhtNDM4NHZYZ2JKbE9kaUVQOEdZZHNXeTcwQVY2QlZ2ZUVaaGluRXV5RndaaGluZmt0LXVOQjFFOUh5YkVuYU1vT2l0alNwbkI0VF9QY1pxWWgwdTZPZFR1eGhNSkNZQ3JrNEh30gGgAkFVX3lxTE9EQmdsN2FOb2NaWG9FSkhVaG1aM1hGYTBJUUZjTjBPWE5wOThPR1NoWHpKcTVZeU80WDJkT19Qc2RGMS1pRmhKNjQxTVc3NTdLZmtKX19yNjlCcXVUckY0ODk0OW9YM1BDQjV0YUk5UWphd3JJSjVJd2FmYkdFdzRVbHlpM0k5X05zSFNOcWtMMkRtd1cwU1ZUZ010Z2dFUHZYQ2IxVDQ4MHhWT2pZeWc4TjFzQ1d1em1UY0pIODA2MFJ5NGNzTVRiX0ljNWhqbHZTNTNnSUlxek1MSEJ5d3dSdk5nbHAxSGQ4QmNXWjhrc1ljb0pkNGI0WjZDNnNKZFByLXZ2a2k4VkI2cEc5NlM0TmJzWGFLbkdDOHpZOS0tMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNYjhpNDNHdXpiRVI4Uk56Tlk0dlZQbVZUa0RvN1VMTW9ubU1vTDI3Q3R1WW1nUDYyUzRkM0NubGN0dXBvY0xWRVdwaW9qQzQyc3NSLU9FRV91OGh1bnVvanhrcmFpdVl6amdvNnpQamNQMFktX0hPdUl2SkNnbFI3WFNSakhyQVpSOGt5elZGcGc4blNici10bXpmTHM0TlIxNUdBT2x3YkMyb3lvT044aXRNWDg1Z0E?oc=5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>En el oriente de Cali tenían a dos adolescentes que serían reclutados por la estructura criminal 'Jacobo Arenas': los iban a llevar al Cauca - ELTIEMPO.COM</t>
+          <t>¿Polémica tendencia de los 'therians' llega a Colombia? Anuncian encuentro de jóvenes que se 'identifican' como animales en tradicional parque de Cali - ELTIEMPO.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>ELTIEMPO.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxPUDNwLXRyY3FHY2JlX0luT0d3UzBjSXpGZFBsRFptUnBFUTZRbVJLWUhWQmpVVzhlc1pVMEMtSjhCR2NvRFNocGtCZkZ3MDFxbEFJci10bmZtdGdFS0R5WGtnMU1lOTJxSXBpSVQtMlRKSGtWaWpmWE0tbzdqNHF2RVpYQ0UwUmYtVlMxMFJmZGpReHZhWm1uYUFKQmtIbjRsS2FUdzFDcFVidlQ1cjBuR0RkUTB1YUVhN0hQNTdELVdQYy1lcDZ5a09YUllmLUVFck1DemFsX2hSOVVjZEZhZm5XY2FWYjFXblNmenZxb0JrUVVvT3pHRW5PUlhKZEVuUlZSSklUMGpmZ0hxX2VZaURuamxFeW_SAZcCQVVfeXFMT1AzcC10cmNxR2NiZV9Jbk9Hd1MwY0l6RmRQbERabVJwRVE2UW1SS1lIVkJqVVc4ZXNaVTBDLUo4Qkdjb0RTaHBrQmZGdzAxcWxBSXItdG5mbXRnRUtEeVhrZzFNZTkycUlwaUlULTJUSkhrVmlqZlhNLW83ajRxdkVaWENFMFJmLVZTMTBSZmRqUXh2YVptbmFBSkJrSG40bEthVHcxQ3BVYnZUNXIwbkdEZFEwdWFFYTdIUDU3RC1XUGMtZXA2eWtPWFJZZi1FRXJNQ3phbF9oUjlVY2RGYWZuV2NhVmIxV25TZnp2cW9Ca1FVb096R0VuT1JYSmRFblJWUkpJVDBqZmdIcV9lWWlEbmpsRXlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxOOWxBdEpsazBoazhCNG0tOEFiQ1JtQVNmQVZzZGNpb2pELW9wZGtWbGdOQnpCYmUtTXoxTlRLN3czRXhKaW52Ry1vdjlfekU1czV4LTg3ejVoQ2lONFh6QmhKN2VtQWtWVnVNUXg4bHNmNWNXQ0NMaHFqaF9XbWFvUFo1ZjQyT051TG5xaUV5UWg2YThMbnRTVVpNNVlaU3F0ZzNVS3RJcjJkMWNvYmtUcnpUNWhqejhtNDM4NHZYZ2JKbE9kaUVQOEdZZHNXeTcwQVY2QlZ2ZUVaaGluRXV5RndaaGluZmt0LXVOQjFFOUh5YkVuYU1vT2l0alNwbkI0VF9QY1pxWWgwdTZPZFR1eGhNSkNZQ3JrNEh30gGgAkFVX3lxTE9EQmdsN2FOb2NaWG9FSkhVaG1aM1hGYTBJUUZjTjBPWE5wOThPR1NoWHpKcTVZeU80WDJkT19Qc2RGMS1pRmhKNjQxTVc3NTdLZmtKX19yNjlCcXVUckY0ODk0OW9YM1BDQjV0YUk5UWphd3JJSjVJd2FmYkdFdzRVbHlpM0k5X05zSFNOcWtMMkRtd1cwU1ZUZ010Z2dFUHZYQ2IxVDQ4MHhWT2pZeWc4TjFzQ1d1em1UY0pIODA2MFJ5NGNzTVRiX0ljNWhqbHZTNTNnSUlxek1MSEJ5d3dSdk5nbHAxSGQ4QmNXWjhrc1ljb0pkNGI0WjZDNnNKZFByLXZ2a2k4VkI2cEc5NlM0TmJzWGFLbkdDOHpZOS0tMQ?oc=5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
+          <t>Jóvenes habitantes de calle serán guardianes de Bogotá: se capacitarán en temas de reciclaje - Suba Alternativa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Suba Alternativa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQS1VXYmlYVUpOTVJ4NGVoY0M2OXc2OVl2dkhRbmZBYW5DN0tIVXNpV3kycERZbmktTTJwMWN3ZTR0NkZtUWxTVXNMaVNyZjQ1cDJiN1pLRFlRMV9kdl9zdFhIUEFqUElSSTBYbEFNbHNKOFgtRjU4Z0VkZ3RROTcxbmFzRFZvYUpZTDBaNTBSUUh5VUFVQzFBSU8xVXphcU8ycXZnekpmaU1yTzh0NUtZN19jVXhNR3haQ3Mw?oc=5</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Plan en Bogotá busca convertir a jóvenes habitantes de calle en promotores ambientales - Periodismo Público</t>
+          <t>En el oriente de Cali tenían a dos adolescentes que serían reclutadas por la estructura criminal 'Jacobo Arenas': los iban a llevar al Cauca - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Periodismo Público</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2520,22 +2520,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNYjhpNDNHdXpiRVI4Uk56Tlk0dlZQbVZUa0RvN1VMTW9ubU1vTDI3Q3R1WW1nUDYyUzRkM0NubGN0dXBvY0xWRVdwaW9qQzQyc3NSLU9FRV91OGh1bnVvanhrcmFpdVl6amdvNnpQamNQMFktX0hPdUl2SkNnbFI3WFNSakhyQVpSOGt5elZGcGc4blNici10bXpmTHM0TlIxNUdBT2x3YkMyb3lvT044aXRNWDg1Z0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPT1ZiOXh5MXdsMHFndzNHWDVEem54MUpaQXIwLWg2VlRKQXk5OWFaR0NHRWJPMzhKQ1JwOS1BUzlkYUNVZEpBaGR2SElSNG9zUXFFV3YxQ0pseWlIdjM3cG5JSExJQUtIOHVwWEhuQ0wwOERncldqTTBvak1MOThJNmFCbGVwWHFPZlljVFEtb000bWhyRWNHdlFySGtKY3pXd2dDc0dUdDdxb0dzOXRGVXVlcm5iVzJMTTJzaThCdDVSNmpSWTlrVGs3d2dxYWxtRlpmRmtIaElDd3IxdERjQjVjT0tfRGV4d1NkVTV2T00yN2QzWkYxUHBidDhlVEJGSFNoY0lQRVdCc2U2c0tlSUZB0gGXAkFVX3lxTE9QM3AtdHJjcUdjYmVfSW5PR3dTMGNJekZkUGxEWm1ScEVRNlFtUktZSFZCalVXOGVzWlUwQy1KOEJHY29EU2hwa0JmRncwMXFsQUlyLXRuZm10Z0VLRHlYa2cxTWU5MnFJcGlJVC0yVEpIa1ZpamZYTS1vN2o0cXZFWlhDRTBSZi1WUzEwUmZkalF4dmFabW5hQUpCa0huNGxLYVR3MUNwVWJ2VDVyMG5HRGRRMHVhRWE3SFA1N0QtV1BjLWVwNnlrT1hSWWYtRUVyTUN6YWxfaFI5VWNkRmFmbldjYVZiMVduU2Z6dnFvQmtRVW9PekdFbk9SWEpkRW5SVlJKSVQwamZnSHFfZVlpRG5qbEV5bw?oc=5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alcaldía conecta a estudiantes con universidades y oportunidades de financiación - Alcaldía de Armenia</t>
+          <t>Jóvenes habitantes de calle serán guardianes de Bogotá: se capacitarán en temas de reciclaje - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alcaldía de Armenia</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2563,22 +2563,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPSGNJLWNiT0JsQlpPUmVWSjJDZE82M2pOVGtLNkozcXFjdU5pa1pMaENkbFQ3c3dmSGc2X1dtdy1KM0txRUlaMjNvZEY3T19lNmZmWk1wZllDdWhqelEzd3ludXhRRnlVZG9OU09xLTlyLUUzTWE2LTFGcURsWmVFeWNxc3lLY05hWFZsR1FwTTFGZl9ZeURESE1HTkoxbWhhMVp2TWg3bklENzFsakRkdUlIQXAwT1pUZlVDMTBqMlBYS1JxQ3BzeGZ2VmF6ZU12c24xVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZTlVbXhUR0VMSmF3NDJXWVlwWmwyYzBISlQ0MVRNSUdOSWQwcThFZWt3eTBJUmpRMVl1YkVDR3NSa0FEWEpqdVJfWnlNcHA4SWhpai05OHo0czdBVF8wTnlLVGRfVEpzeEc4NDhXcGlEaThvcDlHdXJIZ01INDlaN1lad2tubHVWM0Z0ZFlEOGV0dmhESjNmZDJPMFlJY01ETHBNUmhlOWtJZkNaUkRkQnowdHd3Wlp2MlE?oc=5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Elecciones 2026: 70% de los jóvenes en Colombia todavía no saben por quién votar a la Presidencia, según encuesta | El Colombiano - El Colombiano</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZlNPMmVNZ0lHTEh6bFpBTjJqUzZXdU11czVXbDBYeTNhS2k5ODRJejhtU2NQRDZqd3p4eFMxOEVLSWl3UUU1RmNicy1ZVnItc2FiWHBnTlJVd3c2SUlUSzAyQVBQYTlZc2VaUUlIOXBtSFp4UDY1TWlfcHdNQjVSVmUzTldUUGxqbzVDY0tsb29mOEo2S3FlNXVWWXpHd2FtM3dYNzN1QjhwUUd4YnN3adIBtgFBVV95cUxPb2Z2OW1VRWVkVU90ZUpaanJ4NklTejBBaUNSQ2MzTERhb1JZZEJHY1lYeUhydmVkelB5cGVDRTliNHVHV1JEc0dlQURNbWJmVElfdUhwMzNhREh5WnQwMkgzVFZqTElNNkUxMzdYYVlhbDZEemhpNmFScHUzM3JVc3ZQOXAxQU1HRXJpU3FxQTNhSFZnb21qZHl4ejJ5a2VNbFNPLVJ6Wk1qeEt6amhzc1Q2aTNUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOGlJcXNqT09nb1VFRXJYa3RTckd5Vklkb3RwSXJvNlV0cml2aDQ5ckhveDdJYVhRZzJfVHBSYmlGTTRhV2lLODQ4Zk52SmFBVDhCXzFuVTh5U2pfM2tOVWRLZGRQN0kwRUcyUGI2UXhhOWVTUGoxcjRTVmFFVHZsX3prZ2F5NThtaE5ZX1lYcGNMMkpNdVBxUjNmMHJtVXlNTndsZ09LdjRRaE1JeW9EWS0xMXR5NGJZ?oc=5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace - Bogota.gov.co</t>
+          <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2783,17 +2783,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNOGlJcXNqT09nb1VFRXJYa3RTckd5Vklkb3RwSXJvNlV0cml2aDQ5ckhveDdJYVhRZzJfVHBSYmlGTTRhV2lLODQ4Zk52SmFBVDhCXzFuVTh5U2pfM2tOVWRLZGRQN0kwRUcyUGI2UXhhOWVTUGoxcjRTVmFFVHZsX3prZ2F5NThtaE5ZX1lYcGNMMkpNdVBxUjNmMHJtVXlNTndsZ09LdjRRaE1JeW9EWS0xMXR5NGJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQSDhDeEZJVVh5SGI1Zk1iekZWQnhDbVctZnVUYzhqQ2E1aWJRS1VCeHVkNGw0ZWpPQm1Eci1LcDdFWGZXU181dHk1R29RRC1QeXZuWFNSYXhLUjhubTBBRnQ1T01zV2VpZEw2VHBzYkNFbWVrdFlFNWtKX0p4a0N2dlV2aXBBX29hWlpyVk9jR0lOVzJ1WmIwRW9lTkQ4THBxSkhiNTlZa9IBrAFBVV95cUxNWjh0d2x2QVNiM0Y2WXNZeXYyZm1mUEkxOG9LMjBjcWVhbjVwMjlvdUtLOVNJVk5ZNTR3dkd4RW9GVGMwZ19GUEhPckRrdGVFZVVSN2ZDaWFGbDZUX2d2dDJMQm4zNkZmYkYzbjVEbWJRcTJLaVktR19CN2pYNzkzaTRPdW9OeW5IVzFGWU9fbnpTeWM5ODZ2MHdNa0dXVFM2QXFzQS0wRnRrNXVa?oc=5</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Indignante: uso de IA en Colombia disparó creación de material sexual ilegal con niños | El Colombiano - El Colombiano</t>
+          <t>Elecciones 2026: 70% de los jóvenes en Colombia todavía no saben por quién votar a la Presidencia, según encuesta | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQSDhDeEZJVVh5SGI1Zk1iekZWQnhDbVctZnVUYzhqQ2E1aWJRS1VCeHVkNGw0ZWpPQm1Eci1LcDdFWGZXU181dHk1R29RRC1QeXZuWFNSYXhLUjhubTBBRnQ1T01zV2VpZEw2VHBzYkNFbWVrdFlFNWtKX0p4a0N2dlV2aXBBX29hWlpyVk9jR0lOVzJ1WmIwRW9lTkQ4THBxSkhiNTlZa9IBrAFBVV95cUxNWjh0d2x2QVNiM0Y2WXNZeXYyZm1mUEkxOG9LMjBjcWVhbjVwMjlvdUtLOVNJVk5ZNTR3dkd4RW9GVGMwZ19GUEhPckRrdGVFZVVSN2ZDaWFGbDZUX2d2dDJMQm4zNkZmYkYzbjVEbWJRcTJLaVktR19CN2pYNzkzaTRPdW9OeW5IVzFGWU9fbnpTeWM5ODZ2MHdNa0dXVFM2QXFzQS0wRnRrNXVa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZlNPMmVNZ0lHTEh6bFpBTjJqUzZXdU11czVXbDBYeTNhS2k5ODRJejhtU2NQRDZqd3p4eFMxOEVLSWl3UUU1RmNicy1ZVnItc2FiWHBnTlJVd3c2SUlUSzAyQVBQYTlZc2VaUUlIOXBtSFp4UDY1TWlfcHdNQjVSVmUzTldUUGxqbzVDY0tsb29mOEo2S3FlNXVWWXpHd2FtM3dYNzN1QjhwUUd4YnN3adIBtgFBVV95cUxPb2Z2OW1VRWVkVU90ZUpaanJ4NklTejBBaUNSQ2MzTERhb1JZZEJHY1lYeUhydmVkelB5cGVDRTliNHVHV1JEc0dlQURNbWJmVElfdUhwMzNhREh5WnQwMkgzVFZqTElNNkUxMzdYYVlhbDZEemhpNmFScHUzM3JVc3ZQOXAxQU1HRXJpU3FxQTNhSFZnb21qZHl4ejJ5a2VNbFNPLVJ6Wk1qeEt6amhzc1Q2aTNUdw?oc=5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Carreras académicas más elegidas por los jóvenes en Colombia este 2026: tecnología y salud son algunas - ELTIEMPO.COM</t>
+          <t>Colegios en Colombia implementarán cátedra obligatoria de protección animal y biodiversidad - Senado.gov.co</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Senado.gov.co</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNbG9GRW1GYVhUNWlIWDJ0eHdlNHdvenBSeW80MFF6aThCWi0xcUZmN2VlTnoyY3dVdjZaRDJocENhQnRrMGdfa3Y4Z2diS0F2RU9lTXdyUkM4a1pESnB4Qzc5bFJXeEZfYTZfWFRHV0lFVTU2M3daMFpWUk53OU5wR1luNXFoejNYc0xBb2kwZHhqck9obW1DaGtUR1Z5bWdKa2ZGQmFWaGRBNTRITXBpNF84NVBDTGtiZkc3WlJ6bkxSc1RRZklrUUhaaXdGNXFHOU82eDR3M2prcUstMHZQZ0xKSdIB6AFBVV95cUxOb3lzVlp1cU5CN3lTU0F4bm1aVk1SeENCd2JIQzI5aXhaZGJfWUlhWXBpSnQ2NjhGZFlOY2NrbzYwdWdZOVZfVF9vUE5zYVhSaGtPbjd1WVVRNUZBYjlVZkVTZW13ZWZrbld6SjNDN1FtU2M1M2F5REtidFFuTzByV2g0TDBUOFp0Wms1Sm5IV2plTHp4UkpDMjJSMWdaRExXVE5uSmx0VzZXR2VlVDkxTWY0SE1TRVU1QVZLMGV3eUp0andRVm8zOW4zTFdvdWlxd2dldVAtOTVDU0xCVy1TQmQ2SUJtd1Fr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPdkRscDEzLTMzYnhsa2M2N2JfZ3M4ampEZzM5ZVFDRm9aSHBySC1idWljUS1BbW8yVjlUcmF4YW9NNVA2M0dzblQ3aGo3emV5RTFnc1ZkclFHWF9XVDBubmU2Q0lpQmJCTzFiUTNOMnNIdm90NmJua0RwNlNuZXJ1bDIweU95akZQWmFNcmFfT2sxNG1Qb3BDU3hyQmJsT3hqQVlHZnBGb2RNUnJBS201YzV6SFVRR21IX0U3eHNSZEo3MFNuZmVPakgwZGEzVlFYTGJZcEg0dGtSdFpvMnU3TExoMzIxZw?oc=5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
+          <t>Carreras académicas más elegidas por los jóvenes en Colombia este 2026: tecnología y salud son algunas - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bogota.alerta.com.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2907,22 +2907,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOblktRDZRdDlQREx0SWFrYjhnWkoxMmY3MHJJcEJCQU9lbDcwUi1wTFAtVTVySlhnbG9LNGtpd2NHZ05VQ1p0cFpqNkdiU05ENWlISEZUQV9aNExDb3NUUHU1MkduSHJ5LUlsUlhYR0FOMkRvVXloSW1PS1RZZzV3T3VUU1EyQWdGMWhmQTF4a1ZXV0ZlRFRvdDVQcVgyN1ZyakZoeEZuZXpGbG53ZzVfdG5oQ01lajJo0gG8AUFVX3lxTE45S1pNZFFOTUdlajl3elgyYkNGZ01TVGxaRjVPMENmQ2Qwek1GQUhGcVNSSURsN01uM1FYSTR4R2J5U29LSVRWbElNc3hOaUo4V09MdG82SnhHWUFMd1hqTU5DWTFtWmJOZEZqUFRjUmtaZUs4YXQyWjdMZjVyS0J6Q1FNbHBfNENodDRGQ3VZNGVwY2RTS1YzekN4UkwtakV4TlFPYzU5WFA3aGJmd01YOHpfQUNiZ21xSTJp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNbG9GRW1GYVhUNWlIWDJ0eHdlNHdvenBSeW80MFF6aThCWi0xcUZmN2VlTnoyY3dVdjZaRDJocENhQnRrMGdfa3Y4Z2diS0F2RU9lTXdyUkM4a1pESnB4Qzc5bFJXeEZfYTZfWFRHV0lFVTU2M3daMFpWUk53OU5wR1luNXFoejNYc0xBb2kwZHhqck9obW1DaGtUR1Z5bWdKa2ZGQmFWaGRBNTRITXBpNF84NVBDTGtiZkc3WlJ6bkxSc1RRZklrUUhaaXdGNXFHOU82eDR3M2prcUstMHZQZ0xKSdIB6AFBVV95cUxOb3lzVlp1cU5CN3lTU0F4bm1aVk1SeENCd2JIQzI5aXhaZGJfWUlhWXBpSnQ2NjhGZFlOY2NrbzYwdWdZOVZfVF9vUE5zYVhSaGtPbjd1WVVRNUZBYjlVZkVTZW13ZWZrbld6SjNDN1FtU2M1M2F5REtidFFuTzByV2g0TDBUOFp0Wms1Sm5IV2plTHp4UkpDMjJSMWdaRExXVE5uSmx0VzZXR2VlVDkxTWY0SE1TRVU1QVZLMGV3eUp0andRVm8zOW4zTFdvdWlxd2dldVAtOTVDU0xCVy1TQmQ2SUJtd1Fr?oc=5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2935,12 +2935,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Colegios en Colombia implementarán cátedra obligatoria de protección animal y biodiversidad - Senado.gov.co</t>
+          <t>IDIPRON se la jugó por los jóvenes: respaldo superó 18 mil historias - bogota.alerta.com.co</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Senado.gov.co</t>
+          <t>bogota.alerta.com.co</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2950,22 +2950,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPdkRscDEzLTMzYnhsa2M2N2JfZ3M4ampEZzM5ZVFDRm9aSHBySC1idWljUS1BbW8yVjlUcmF4YW9NNVA2M0dzblQ3aGo3emV5RTFnc1ZkclFHWF9XVDBubmU2Q0lpQmJCTzFiUTNOMnNIdm90NmJua0RwNlNuZXJ1bDIweU95akZQWmFNcmFfT2sxNG1Qb3BDU3hyQmJsT3hqQVlHZnBGb2RNUnJBS201YzV6SFVRR21IX0U3eHNSZEo3MFNuZmVPakgwZGEzVlFYTGJZcEg0dGtSdFpvMnU3TExoMzIxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOblktRDZRdDlQREx0SWFrYjhnWkoxMmY3MHJJcEJCQU9lbDcwUi1wTFAtVTVySlhnbG9LNGtpd2NHZ05VQ1p0cFpqNkdiU05ENWlISEZUQV9aNExDb3NUUHU1MkduSHJ5LUlsUlhYR0FOMkRvVXloSW1PS1RZZzV3T3VUU1EyQWdGMWhmQTF4a1ZXV0ZlRFRvdDVQcVgyN1ZyakZoeEZuZXpGbG53ZzVfdG5oQ01lajJo0gG8AUFVX3lxTE45S1pNZFFOTUdlajl3elgyYkNGZ01TVGxaRjVPMENmQ2Qwek1GQUhGcVNSSURsN01uM1FYSTR4R2J5U29LSVRWbElNc3hOaUo4V09MdG82SnhHWUFMd1hqTU5DWTFtWmJOZEZqUFRjUmtaZUs4YXQyWjdMZjVyS0J6Q1FNbHBfNENodDRGQ3VZNGVwY2RTS1YzekN4UkwtakV4TlFPYzU5WFA3aGJmd01YOHpfQUNiZ21xSTJp?oc=5</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Colombia: El reclutamiento de niños por grupos armados se cuadruplicó en cinco años | Noticias ONU - UN News</t>
+          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UN News</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3208,22 +3208,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9wSzZjZVpFS1l3NGk2RTY1NlEweXZQcGhjaG9VRm11d0Y4U2xkLVBCYzhoY1o5dmJmQ1g2UE5wR2cxckxPZEowdnpnZkdDT2tyTWRfcmlXYw?oc=5</t>
+          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
+          <t>Enfoque Internacional - Niños soldado en Colombia: 'Tiktok es una red muy usual para el reclutamiento' - RFI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3266,14 +3266,10 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPSXVVRUV0NTJIWUpLRjctUXJwTkZ5bnR2clhrc0JQSzVseXZnY0VZSWZoVFRTblJGNFQ4TWxWZ2kxaUxIckxxVTdORGE5ZGdXU0ZsOUVvSWYxWEtobWhNbjB2THg5NGxidFNMcnNFWmNtR251WVZSTHc4ajB5NkZkdFQ4YUpTa0MwVDlHUzV5QWhCUjh3b0xTdnNweFpEb21LT2VUMWJOQWJHT1lQWThRV2Z5a0U2RWtTOHN3R2VMWFNjemMwdUhUdE9RU29NZ2xZSnBzbTluY0pRa1E?oc=5</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3283,12 +3279,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>En el Día de las Manos Rojas, la Defensoría del Pueblo alza la voz contra el reclutamiento de niñas, niños y adolescentes - Defensoría del Pueblo de Colombia</t>
+          <t>Novela Cetré: Athletico Paranaense vuelve a contactar a Estudiantes - AS Colombia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Defensoría del Pueblo de Colombia</t>
+          <t>AS Colombia</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3298,7 +3294,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3313,7 +3309,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOeEM0U1NNTGdPenhCTGZmZ0l6ZkxXdWppZHJXM1FfaGFqUHFRc2JvUDJqUDBwUVdFenh5QWhlbi1JSV85UmNRVE1mcjdxNkNQWVNnSFZBem9MLTdnX2paeFFZZ1N3TjZPZlZjSUdrOEZWRTM1bXF6SVJFdHNCaW0xQzM1ZE1pdFFENXB2OENSRFNTZkd5OXdsYzZpcDg2X3FWaFRDa0NLT2w2Z1ptUXVXalBQSzN5UXFOMktuVWJtS050YzRReGx4YmFuZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxON2ZpdV8xQlA4UUYyRFNZcGlJdmRCOEpHa3JzRG5TUFRueUcycjNyVFZIV0E0ZEZZelRzbEtDbkpFdXloQ1ZjMDkyT2c3MWdndTNMU0FMZmVBeHhNT09hUzYxQkcyLTY2a0ZROThzTXBSeE5lQVF1TWNWMFcxWDNhaXBDU1U3UGt5dXhvay1HdExSbExpeVdhS2czWFNjaU9ZNy1fdm1heVllZnE4WVQ2dlpoZjBDbGZqM1V0M3p4Z3N1ZVlpb0FTV2V4MUtQd9IB4gFBVV95cUxQVlNjaVJTcUpQdk5pcUs5X2tmT3BfTGQ4UGwwSWgxa3hRcF9WYVhsRDFfM3A2M3pXaXZ3NFo2bi1fMUw5UllSYWFSb2x0ZUs1eENCMnZqc1QwMi1JdEFEYU91OEsxVU8xNGZOTi0zbDhCRmhyR3AtVVJraHc4akpIYWY4U2lYMURhRWFPazBrUVowZXhiMktxWG55YUVndU1fMVFTLXVZaFlHdm9SS2hqZkEyN0MtdUhna2VqaHI3VnU4YUtZbFRjTnU2bnhJZUhzY0ljYU8wdDNpckdFeEc2dUhR?oc=5</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3326,7 +3322,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
+          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3356,10 +3352,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Estas son las reconocidas universidades acreditadas en Colombia de las que se están saliendo los estudiantes: subió la deserción, según el Ministerio de Educación - Infobae</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3384,12 +3384,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNdURDZWdBYVZGbjVuWGh6ZmFMdUY2bjcyc1hLWWxKSnl2dVVSMjRvNGFkZmN5aGgyVlFSUzhUb29lOTg5MWFFY3F0RFM5Y3NtTHZyY0hrcnExYjJjWE9NRkJhbTVwTnZYRElXckIwSDEtM20zeHpkX1pBdGJ0bXhjenY0bUVWSkNNREFKM3FlMDVnT2pqdXdBY0lSSDI3MUJIOFl6Umk3SWdCeU1fYk9TZkVEODJ4dHZoOEdNQVFueHBlVUxNLUNpdUY4YWVWLUpMRER4bkNQek5fWC1Mamk4Ymp1NF9mN3JDWmFIV25hNUpydndyeXNoTUt0QXRxcTBZMHVybk0yNEhfeWdhc3pYadIBqwJBVV95cUxPVTVQb2JnXzBJTkFYNUNOZ1YxeTBJU1Z3bTkxb3Nkak5HdVZ5N0Qwb284LXBwRDZNakVfM0RsR0JOWllycENEYVlLQTV2cW52Ymdpa0NGOHB4d1pVNjFXU0VESEQ3OUR2Mmhrck1uU2NKT2oweEYxT3R3MmNzVzFobVZPUnFGT3paeVA5NzV1cmFQeHYwT2htdmQzc0x0Y1hCUWJGOUdoVHV5elNKa3VWZ0xIaHY2OGJXY3VOR1NuTkFXYzh2QnhWSmxnMFVFRUdxaThzZFBxTHlxNHRyTUpMSHNGRUFCeS1XUXlkMVlUd0hhY3RfWkJXZmN0UzdEYWdyOWR2WGFialRYdTAwUEp2OUkyRFZQcjNWcTgzNndlNEl3RHljMElWTkxvOA?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
+          <t>En Colombia, cada 48 horas reclutan a un niño, niña o adolescente - Caracol Radio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unicef</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOaE5BNl9aTGdKUjlkdW1BaGZOUnNCSTFLYXBRcGdGamVqR2xlazBGZmhjYjBxYUxYa1BfZ2t3NDZpOS14eWRmbFFIWkFfLUMzSVdFQV9oRGNXeUlycl9CMkJjc0R3MVBIcnVtVk5BcERONnJnVFBpckFCQWNKaGlhbFVCUjhyQTlSb24tSElRYWJyQ1FELVdTMlhRQ3BmeDJXMlNKMnRhdm91RjVxMTFOOVpuMkF6SFdQSUs1TFU5LVgxN1JMSWQ3X1piT0lXN3FI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPZ3FnbG5UcDl2dElHc2tndjRGZHFfTEtwSzZXTm00TEtwbkprdnJLQ2dmZ2RiTjdLbURnelZWYUZRQ0Z6QXVCMWxla3VTVTM3NDVnTTZ1amJ1dGRvVGdzbW5Fc3E3ZkFlOUhpRlVnbnRSZWowdVNDM1FrSkhQbEc5eVlLQkw3RTlVem9sX1haX2ZfUVM3TndFNXpoUDF5S2_SAbMBQVVfeXFMTTVGUDR6b3R0QVlKZTlDRGh6Um9kbE1qNjA1OUctWTRVRWgyQ1R5QkdEYmUtS3JVbWtGcjRzTXBxSXFGNTdiQkdyMU16VER0OHJKUEViVWRMUExfQ05neHJRbERGcDdQU3VmYnVXbnBiWVJXSFZCdlZqVng3NXg3RWdGWFFiUXZwZGo0dW95bGhxdmpqLUs1X3BJcWVIV0YycHl1dDZLUU5mdDIybWxvZVJKZzQ?oc=5</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3455,27 +3455,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cada dos días es reclutado un menor de edad en Colombia: en 2025, 40 % fueron niñas, dice la Defensoría - ELTIEMPO.COM</t>
+          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQcDdFdmtDc2pySXhNZEtwcTVsTk9ZS1JDSEtHSGl0YXk3dEhNQ1V6dlBmYXZBUTBfNnBqaVR5TUFfNVdSemdFdE1hVDhHVV9TSUhaVnR3d0IzanJIbGhjb1B4aS04djYwWnp6YS1NekYtb1YyWWlkekhEZjV5TmhfbWhHNmswWlpqT1JTTl95NWV5eWd3ajhYTEpiaXJIRldnX0pqT3hRVnRMSEJGQW9OTlpFRWkxRGxESV83QkdCVGx3LUJySVR4TEs1TGFNM0pxVEY2OEdUQ2VSbjh1ckVud1BldVhHdXI0c1h1R0ZvX09YVm53d1HSAfsBQVVfeXFMTTRod3NmNUxMSDhrc29tdzR2RFMyVFpfWmh3b01yNVVRR1ZPQnl6Q0ZZQ3VMc2x6UXhpaHAwVzhQWjdPZ294YnRNMXNVQUdrVnp4VFFIZVowRHdEVm4wR0J4NGpzVjlDWkpBMmU4R0p5UUNTREZOWGlGNDBXS3N4RkJvNDlfQTYzd2FDUEVsUE5WdGF6NU4zVzM1MnVlVDQ4SVIxZDRaTmNZd1RpMWxvelpPUm0xZlBkZDhfanp5WVotbjZxTjJydE45NGRCeTk2c1RzcnZGVUhzakxWRjBNZVMwN2tFUlFQMXVTUWF4SHRFdWs1SUE1dmZWMVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3498,12 +3498,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Colombia está perdiendo a sus niños en la guerra - EL PAÍS</t>
+          <t>Infancias en la guerra: el reclutamiento vuelve a aumentar en Colombia y así es el negocio que hay detrás - CAMBIO Colombia</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EL PAÍS</t>
+          <t>CAMBIO Colombia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPc0p4UDhDd3FDTi1IQUUwUzRzd3dTTHE4cEZuSUp5cTY5dDRUMFRiSHlEUk5naU1ZZUctWEFGODlhLWowNmNuSkE0eUcxZlI1dzJJaU93N1pUaXFid3RjdkNHeHhJbmpQel9CM3hQaUdXUFBVZ2hlQjR0WnZ6emI3TERNZmF3RC1laFpwWjZzSlp4X1QyUmdvTHVZQmYxempldUHSAbYBQVVfeXFMTVBPN1dRZWxmb3pMMFM2TmdwMmlhTVVqTHVmWDdOdDlqWGUtQmRzODdFYmdVSHlYT295Z0tCSmJhOGlFUFJXVG9pd24yMDRUTUJRR25XZkxYeWc3TUpqNF90d28wdDEwTlRGOHNOaTVqbTNtbmxUUkxtSkdTOGtCajljY29LOTJ3TGMtNU5jZXZ1RnBnRTl4UHRLZ1A5MGFiVUFnQ3h2SzFEV2V1S3dKcW5URmQ0anc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPWTRzcnA4QnE0QS1RSF92WnBRbVRLM3c5cVFRcVlOQ2VhXzRSa1NLalZpNHRNME0zc2Nid3BzeU1Kb0xIdTFMYlZqQ2llVUotWS12bHY3bEtoZEY1M29GM0JWM1BHYXBVZmY0UEN4czNtRHBIQ09uZmYzYmlLQ2IzcV85QXJNbXpvajZ3YWtnX0FHU3pyTjV5d3RTNUJiSW9wODJJTy1jUHV6M241cFRtM3JIdnVIZjZaRjdtNlUzWmF6ZUM2MFVLaGIzMWc0WjNKZldCcmthdm1OWi1Rb1ZCR1NyQTV2M3gxeUFoTHAweWJIMElBQjdIbEthRlZaR2VUTmJ4Zjl4OW0?oc=5</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3541,22 +3541,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Infancias en la guerra: el reclutamiento vuelve a aumentar en Colombia y así es el negocio que hay detrás - CAMBIO Colombia</t>
+          <t>Colombia está perdiendo a sus niños en la guerra - EL PAÍS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAMBIO Colombia</t>
+          <t>EL PAÍS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPWTRzcnA4QnE0QS1RSF92WnBRbVRLM3c5cVFRcVlOQ2VhXzRSa1NLalZpNHRNME0zc2Nid3BzeU1Kb0xIdTFMYlZqQ2llVUotWS12bHY3bEtoZEY1M29GM0JWM1BHYXBVZmY0UEN4czNtRHBIQ09uZmYzYmlLQ2IzcV85QXJNbXpvajZ3YWtnX0FHU3pyTjV5d3RTNUJiSW9wODJJTy1jUHV6M241cFRtM3JIdnVIZjZaRjdtNlUzWmF6ZUM2MFVLaGIzMWc0WjNKZldCcmthdm1OWi1Rb1ZCR1NyQTV2M3gxeUFoTHAweWJIMElBQjdIbEthRlZaR2VUTmJ4Zjl4OW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPc0p4UDhDd3FDTi1IQUUwUzRzd3dTTHE4cEZuSUp5cTY5dDRUMFRiSHlEUk5naU1ZZUctWEFGODlhLWowNmNuSkE0eUcxZlI1dzJJaU93N1pUaXFid3RjdkNHeHhJbmpQel9CM3hQaUdXUFBVZ2hlQjR0WnZ6emI3TERNZmF3RC1laFpwWjZzSlp4X1QyUmdvTHVZQmYxempldUHSAbYBQVVfeXFMTVBPN1dRZWxmb3pMMFM2TmdwMmlhTVVqTHVmWDdOdDlqWGUtQmRzODdFYmdVSHlYT295Z0tCSmJhOGlFUFJXVG9pd24yMDRUTUJRR25XZkxYeWc3TUpqNF90d28wdDEwTlRGOHNOaTVqbTNtbmxUUkxtSkdTOGtCajljY29LOTJ3TGMtNU5jZXZ1RnBnRTl4UHRLZ1A5MGFiVUFnQ3h2SzFEV2V1S3dKcW5URmQ0anc?oc=5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Defensoría del Pueblo exige cese inmediato del reclutamiento forzado de niñas, niños y adolescentes en Colombia - Defensoría del Pueblo de Colombia</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Defensoría del Pueblo de Colombia</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOOXBhbnlhY2EtSG5ZSHlTVlJ0U01WUDBnSlJlWFBGajVCZld5TUpmVW9MLWRxZE1IeVI0eGlBVGhnbWVaQV9MWUQtclg1Y2F6eGZqamxsSzFQMWRJV3MtSExwT2lyd24xY1k5RnBHUTJ0eFdmd1VrMXU5ank5dDZkLVJ3MjM3Q01lREZFc081Q3JqTHBITk9MMmJiYjFtS2MzRTg5S05ZOFk0M29hNHRsbV85NHgwMWl3WE1SRVdPeEgwVWp4b21wdElhUUNFZy05eUJLbFBfQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3674,27 +3674,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Colombia: El reclutamiento de niños por grupos armados se cuadruplicó en cinco años | Noticias ONU - UN News</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>UN News</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3704,14 +3704,10 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9wSzZjZVpFS1l3NGk2RTY1NlEweXZQcGhjaG9VRm11d0Y4U2xkLVBCYzhoY1o5dmJmQ1g2UE5wR2cxckxPZEowdnpnZkdDT2tyTWRfcmlXYw?oc=5</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3721,12 +3717,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Enfoque Internacional - Niños soldado en Colombia: 'Tiktok es una red muy usual para el reclutamiento' - RFI</t>
+          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3736,12 +3732,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3751,10 +3747,14 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPSXVVRUV0NTJIWUpLRjctUXJwTkZ5bnR2clhrc0JQSzVseXZnY0VZSWZoVFRTblJGNFQ4TWxWZ2kxaUxIckxxVTdORGE5ZGdXU0ZsOUVvSWYxWEtobWhNbjB2THg5NGxidFNMcnNFWmNtR251WVZSTHc4ajB5NkZkdFQ4YUpTa0MwVDlHUzV5QWhCUjh3b0xTdnNweFpEb21LT2VUMWJOQWJHT1lQWThRV2Z5a0U2RWtTOHN3R2VMWFNjemMwdUhUdE9RU29NZ2xZSnBzbTluY0pRa1E?oc=5</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Novela Cetré: Athletico Paranaense vuelve a contactar a Estudiantes - AS Colombia</t>
+          <t>En el Día de las Manos Rojas, la Defensoría del Pueblo alza la voz contra el reclutamiento de niñas, niños y adolescentes - Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AS Colombia</t>
+          <t>Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxON2ZpdV8xQlA4UUYyRFNZcGlJdmRCOEpHa3JzRG5TUFRueUcycjNyVFZIV0E0ZEZZelRzbEtDbkpFdXloQ1ZjMDkyT2c3MWdndTNMU0FMZmVBeHhNT09hUzYxQkcyLTY2a0ZROThzTXBSeE5lQVF1TWNWMFcxWDNhaXBDU1U3UGt5dXhvay1HdExSbExpeVdhS2czWFNjaU9ZNy1fdm1heVllZnE4WVQ2dlpoZjBDbGZqM1V0M3p4Z3N1ZVlpb0FTV2V4MUtQd9IB4gFBVV95cUxQVlNjaVJTcUpQdk5pcUs5X2tmT3BfTGQ4UGwwSWgxa3hRcF9WYVhsRDFfM3A2M3pXaXZ3NFo2bi1fMUw5UllSYWFSb2x0ZUs1eENCMnZqc1QwMi1JdEFEYU91OEsxVU8xNGZOTi0zbDhCRmhyR3AtVVJraHc4akpIYWY4U2lYMURhRWFPazBrUVowZXhiMktxWG55YUVndU1fMVFTLXVZaFlHdm9SS2hqZkEyN0MtdUhna2VqaHI3VnU4YUtZbFRjTnU2bnhJZUhzY0ljYU8wdDNpckdFeEc2dUhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOeEM0U1NNTGdPenhCTGZmZ0l6ZkxXdWppZHJXM1FfaGFqUHFRc2JvUDJqUDBwUVdFenh5QWhlbi1JSV85UmNRVE1mcjdxNkNQWVNnSFZBem9MLTdnX2paeFFZZ1N3TjZPZlZjSUdrOEZWRTM1bXF6SVJFdHNCaW0xQzM1ZE1pdFFENXB2OENSRFNTZkd5OXdsYzZpcDg2X3FWaFRDa0NLT2w2Z1ptUXVXalBQSzN5UXFOMktuVWJtS050YzRReGx4YmFuZw?oc=5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
+          <t>Defensoría del Pueblo exige cese inmediato del reclutamiento forzado de niñas, niños y adolescentes en Colombia - Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Defensoría del Pueblo de Colombia</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3822,22 +3822,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOOXBhbnlhY2EtSG5ZSHlTVlJ0U01WUDBnSlJlWFBGajVCZld5TUpmVW9MLWRxZE1IeVI0eGlBVGhnbWVaQV9MWUQtclg1Y2F6eGZqamxsSzFQMWRJV3MtSExwT2lyd24xY1k5RnBHUTJ0eFdmd1VrMXU5ank5dDZkLVJ3MjM3Q01lREZFc081Q3JqTHBITk9MMmJiYjFtS2MzRTg5S05ZOFk0M29hNHRsbV85NHgwMWl3WE1SRVdPeEgwVWp4b21wdElhUUNFZy05eUJLbFBfQQ?oc=5</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
+          <t>Estas son las reconocidas universidades acreditadas en Colombia de las que se están saliendo los estudiantes: subió la deserción, según el Ministerio de Educación - Infobae</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNdURDZWdBYVZGbjVuWGh6ZmFMdUY2bjcyc1hLWWxKSnl2dVVSMjRvNGFkZmN5aGgyVlFSUzhUb29lOTg5MWFFY3F0RFM5Y3NtTHZyY0hrcnExYjJjWE9NRkJhbTVwTnZYRElXckIwSDEtM20zeHpkX1pBdGJ0bXhjenY0bUVWSkNNREFKM3FlMDVnT2pqdXdBY0lSSDI3MUJIOFl6Umk3SWdCeU1fYk9TZkVEODJ4dHZoOEdNQVFueHBlVUxNLUNpdUY4YWVWLUpMRER4bkNQek5fWC1Mamk4Ymp1NF9mN3JDWmFIV25hNUpydndyeXNoTUt0QXRxcTBZMHVybk0yNEhfeWdhc3pYadIBqwJBVV95cUxPVTVQb2JnXzBJTkFYNUNOZ1YxeTBJU1Z3bTkxb3Nkak5HdVZ5N0Qwb284LXBwRDZNakVfM0RsR0JOWllycENEYVlLQTV2cW52Ymdpa0NGOHB4d1pVNjFXU0VESEQ3OUR2Mmhrck1uU2NKT2oweEYxT3R3MmNzVzFobVZPUnFGT3paeVA5NzV1cmFQeHYwT2htdmQzc0x0Y1hCUWJGOUdoVHV5elNKa3VWZ0xIaHY2OGJXY3VOR1NuTkFXYzh2QnhWSmxnMFVFRUdxaThzZFBxTHlxNHRyTUpMSHNGRUFCeS1XUXlkMVlUd0hhY3RfWkJXZmN0UzdEYWdyOWR2WGFialRYdTAwUEp2OUkyRFZQcjNWcTgzNndlNEl3RHljMElWTkxvOA?oc=5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>En Colombia, cada 48 horas reclutan a un niño, niña o adolescente - Caracol Radio</t>
+          <t>Cada dos días es reclutado un menor de edad en Colombia: en 2025, 40 % fueron niñas, dice la Defensoría - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPZ3FnbG5UcDl2dElHc2tndjRGZHFfTEtwSzZXTm00TEtwbkprdnJLQ2dmZ2RiTjdLbURnelZWYUZRQ0Z6QXVCMWxla3VTVTM3NDVnTTZ1amJ1dGRvVGdzbW5Fc3E3ZkFlOUhpRlVnbnRSZWowdVNDM1FrSkhQbEc5eVlLQkw3RTlVem9sX1haX2ZfUVM3TndFNXpoUDF5S2_SAbMBQVVfeXFMTTVGUDR6b3R0QVlKZTlDRGh6Um9kbE1qNjA1OUctWTRVRWgyQ1R5QkdEYmUtS3JVbWtGcjRzTXBxSXFGNTdiQkdyMU16VER0OHJKUEViVWRMUExfQ05neHJRbERGcDdQU3VmYnVXbnBiWVJXSFZCdlZqVng3NXg3RWdGWFFiUXZwZGo0dW95bGhxdmpqLUs1X3BJcWVIV0YycHl1dDZLUU5mdDIybWxvZVJKZzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQcDdFdmtDc2pySXhNZEtwcTVsTk9ZS1JDSEtHSGl0YXk3dEhNQ1V6dlBmYXZBUTBfNnBqaVR5TUFfNVdSemdFdE1hVDhHVV9TSUhaVnR3d0IzanJIbGhjb1B4aS04djYwWnp6YS1NekYtb1YyWWlkekhEZjV5TmhfbWhHNmswWlpqT1JTTl95NWV5eWd3ajhYTEpiaXJIRldnX0pqT3hRVnRMSEJGQW9OTlpFRWkxRGxESV83QkdCVGx3LUJySVR4TEs1TGFNM0pxVEY2OEdUQ2VSbjh1ckVud1BldVhHdXI0c1h1R0ZvX09YVm53d1HSAfsBQVVfeXFMTTRod3NmNUxMSDhrc29tdzR2RFMyVFpfWmh3b01yNVVRR1ZPQnl6Q0ZZQ3VMc2x6UXhpaHAwVzhQWjdPZ294YnRNMXNVQUdrVnp4VFFIZVowRHdEVm4wR0J4NGpzVjlDWkpBMmU4R0p5UUNTREZOWGlGNDBXS3N4RkJvNDlfQTYzd2FDUEVsUE5WdGF6NU4zVzM1MnVlVDQ4SVIxZDRaTmNZd1RpMWxvelpPUm0xZlBkZDhfanp5WVotbjZxTjJydE45NGRCeTk2c1RzcnZGVUhzakxWRjBNZVMwN2tFUlFQMXVTUWF4SHRFdWs1SUE1dmZWMVk?oc=5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
+          <t>El reclutamiento y el uso de niños y niñas por grupos armados en Colombia se cuadruplica en un periodo de cinco años - Unicef</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Unicef</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOaE5BNl9aTGdKUjlkdW1BaGZOUnNCSTFLYXBRcGdGamVqR2xlazBGZmhjYjBxYUxYa1BfZ2t3NDZpOS14eWRmbFFIWkFfLUMzSVdFQV9oRGNXeUlycl9CMkJjc0R3MVBIcnVtVk5BcERONnJnVFBpckFCQWNKaGlhbFVCUjhyQTlSb24tSElRYWJyQ1FELVdTMlhRQ3BmeDJXMlNKMnRhdm91RjVxMTFOOVpuMkF6SFdQSUs1TFU5LVgxN1JMSWQ3X1piT0lXN3FI?oc=5</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Viajes con menores de edad en Colombia cambian este 2026: esto dice la nueva ley - La FM</t>
+          <t>Jóvenes colombianos dan sus primeros pasos para convertirse en pilotos militares - Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>La FM</t>
+          <t>Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNy16bzc2dktiRGkyeXN3blBBRzZ3WjNxek9QX3hqV0o0dlZfNUtvd3ZMR1pvcEJXSndIU0lyMDZCb0hQa3R6WXVBTnZmOVNTU0xqN2Z5OF9UWUVuRDRzOUNrajNwbXkzUGJnRU44LTJYdEdQSEJJcDZOLUJqSG5DaG5MdVhyejh30gGIAUFVX3lxTE9CMGNNcjFpQzFVSzNhN3pzSF81anVxX2dfX0tFODRCVGFEN1ViUkV6OU9ldU1sbm0xd2xkLVdKZUtkX1ZZNDF6Ti1sNWNfTVlVeHdxQ2dET0hIMm1YQ1d5eG4xMVdEdmUyVll5SlRUYkVZZlU3X012aFRSRVEtdFg5UVdDMUI5elg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPV2ZoS2txM1NrTDg2Zl9yRGJhaGk5QjJjZnlRZmJWRjNQTi1ETWo1bURhb3hyaWV1YzBDSzRoTVJWb0NOcGdVeTZ2M3ZkMC1OZThFMEM5RXMwaXdZOXdXVkpZS1FfU1Q5dXdxSGZKZ3hrbjJ1NFNwZWQ4NWJINldQQTM1Vll0cU05Z3dhSC15dDVFXzZVOXc1dDBpUFhySkJVYjdTUTZBWUdBWmNDdlB3a1VxU2pqdw?oc=5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Más de 800 colegios privados han cerrado en Colombia desde 2020 y el panorama parece empeorar - bloomberglinea.com</t>
+          <t>Viajes con menores de edad en Colombia cambian este 2026: esto dice la nueva ley - La FM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>bloomberglinea.com</t>
+          <t>La FM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQMUlhLWE5ZzVjSzRUNEF0Z0kyTFNsb0d4dnh0aEpXUXNVbmxHYTRhZFJPX0llWXRZdFpkbnNGeEFmZWdzY3dEUWJLbDdDb0wxcGNyMFJKQ3ZJR0xwN28tMGhrVDhRV1dGUlpSa0g3LUlEQlcyajd6MEtqV2oxakJkYVFSdmxEUmI1NlJVcXhFQ01RRXRYdGU5RHpRbnp0STVsWERmZkhpVnVPc3NUU0hYZzZBS2ZUUkRyQldrRXlMVDVSQ05Jc3hLQ0pEWWVrTkNRR09FRDVPTFhMQnA1TTRCRWpB0gH2AUFVX3lxTE5NZGlCQjUyZDktS2RmeEdqbzkydjZfckZjNlJBa00xa3E2bTREbXB6eE1zVnZFdGtFOEdLdC1ZTFlSSDl3cDBlZTM1VDNSQ2o2UThxeFhVU3J1UTF5Yzk5OWQzSkFsQUl4NmN6LVRVbm96VWRVd0IxTXhIdGIyVDhXczZSUTJ6YnBXYnB1LW1NMlBybnQteGFOeC1uX2JOUkRGU0JCY1VRVGltcTFiZWxCa052a3hFRnU3WVptR1V3d2oyMWRVMmpHT1d3Wjh1eThwanIzc0NWVjFqNlF1TUdlN2psdkdhSnIyZWxtUC0xR2pVdGRtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQNy16bzc2dktiRGkyeXN3blBBRzZ3WjNxek9QX3hqV0o0dlZfNUtvd3ZMR1pvcEJXSndIU0lyMDZCb0hQa3R6WXVBTnZmOVNTU0xqN2Z5OF9UWUVuRDRzOUNrajNwbXkzUGJnRU44LTJYdEdQSEJJcDZOLUJqSG5DaG5MdVhyejh30gGIAUFVX3lxTE9CMGNNcjFpQzFVSzNhN3pzSF81anVxX2dfX0tFODRCVGFEN1ViUkV6OU9ldU1sbm0xd2xkLVdKZUtkX1ZZNDF6Ti1sNWNfTVlVeHdxQ2dET0hIMm1YQ1d5eG4xMVdEdmUyVll5SlRUYkVZZlU3X012aFRSRVEtdFg5UVdDMUI5elg?oc=5</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4581,12 +4581,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jóvenes colombianos dan sus primeros pasos para convertirse en pilotos militares - Fuerza Aeroespacial Colombiana</t>
+          <t>Más de 800 colegios privados han cerrado en Colombia desde 2020 y el panorama parece empeorar - bloomberglinea.com</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fuerza Aeroespacial Colombiana</t>
+          <t>bloomberglinea.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPV2ZoS2txM1NrTDg2Zl9yRGJhaGk5QjJjZnlRZmJWRjNQTi1ETWo1bURhb3hyaWV1YzBDSzRoTVJWb0NOcGdVeTZ2M3ZkMC1OZThFMEM5RXMwaXdZOXdXVkpZS1FfU1Q5dXdxSGZKZ3hrbjJ1NFNwZWQ4NWJINldQQTM1Vll0cU05Z3dhSC15dDVFXzZVOXc1dDBpUFhySkJVYjdTUTZBWUdBWmNDdlB3a1VxU2pqdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQMUlhLWE5ZzVjSzRUNEF0Z0kyTFNsb0d4dnh0aEpXUXNVbmxHYTRhZFJPX0llWXRZdFpkbnNGeEFmZWdzY3dEUWJLbDdDb0wxcGNyMFJKQ3ZJR0xwN28tMGhrVDhRV1dGUlpSa0g3LUlEQlcyajd6MEtqV2oxakJkYVFSdmxEUmI1NlJVcXhFQ01RRXRYdGU5RHpRbnp0STVsWERmZkhpVnVPc3NUU0hYZzZBS2ZUUkRyQldrRXlMVDVSQ05Jc3hLQ0pEWWVrTkNRR09FRDVPTFhMQnA1TTRCRWpB0gH2AUFVX3lxTE5NZGlCQjUyZDktS2RmeEdqbzkydjZfckZjNlJBa00xa3E2bTREbXB6eE1zVnZFdGtFOEdLdC1ZTFlSSDl3cDBlZTM1VDNSQ2o2UThxeFhVU3J1UTF5Yzk5OWQzSkFsQUl4NmN6LVRVbm96VWRVd0IxTXhIdGIyVDhXczZSUTJ6YnBXYnB1LW1NMlBybnQteGFOeC1uX2JOUkRGU0JCY1VRVGltcTFiZWxCa052a3hFRnU3WVptR1V3d2oyMWRVMmpHT1d3Wjh1eThwanIzc0NWVjFqNlF1TUdlN2psdkdhSnIyZWxtUC0xR2pVdGRtUQ?oc=5</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Menores de edad en Colombia pueden viajar sin permiso de ambos padres en 2026: en estos casos aplica - Eluniversal.com.co</t>
+          <t>El discurso oficial planteó retos para la juventud y riesgos en la frontera mientras la reorganización de redes criminales se traslada al sur del continente - facebook.com</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eluniversal.com.co</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNUkViVng5bVFEQmo3RnFIQXA5dWV6b0czWnJnaC0zRkc2QWx4dUJsZGZ1cXp3R2RfazFVeGdQZUU3Y1dvWUhlQ2o3NlVIaWlMamJNLXNUdlBzeFIyaFJSSVBoZEotTjRiNjRyUFV4Q1FEWFgxWGIyVGtRbUdrQl9mc0dzNXZlejhIelR3WkwwSDFGTzBydll5M1RHZm9YcmFId2NrMVF5eUczbW82bVU4X3p4dTliaTNRcWYwTlI0UG90b2hDUHYyTkhlbGRoelMzVGh3OGhLQnlPanNiOEgxTWlrYklBZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdlNPUVI5dDdwZ3B3eHdpemJIa1VFMnh0STBza3hUb3lzVGxYQS1JRHpya21SSHF3RXdBcjROYUptREtXVlJWdjR6dWNhWDd2akZmVVhpdGJjNHlITnZDeVRlRzFHR2xpcV9adWVXS3huM1R5ZUpOVnlYX1FKd3U4WXc4eXFaVlpQT2kwZHlKOTI0U0QtdlQ1STNBM1RhTkhOMVE3SlJRNHJ3VzB5YXdoNVFyT2RIWGhWY0dnaVcwWFNVVHZ2ekVSVTd0S3Rxc1VVRUNkdmgxUm41X3ZsLW9JVG9QRnR0QQ?oc=5</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
+          <t>“Ahora que estamos un poco más viejos, queremos ser un ejemplo para la juventud”: Camilo Villegas, golfista colombiano - UNIMINUTO Radio</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>UNIMINUTO Radio</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5155,22 +5155,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPOFJRNk52Mkx1Q2hFTm5oQV9UUFlLYkVlMjZEanRsN0hnQU9xRTJTR08tQTl2MVYzQTFMWkRuYXJFcG4zbk5iYWE0clBva0dWVXFlMmt5NTQxTUhtamwzazlacC1HdXZjRkRFVW03U3ZNVVdGTEZHY0JHalFaVXJwLXpZRVpIYm1FcWhkUWVyY29Ud1Rzb1NDUG1UczFJdXNJNnh5MkpPbU5WTDFnV3hmcjBTbXpTcndtNnotMmNqNzdEYXJLSEM1cTA3U0F1ZzctQy1tMUhjc28wcU9kT04wc053?oc=5</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>El discurso oficial planteó retos para la juventud y riesgos en la frontera mientras la reorganización de redes criminales se traslada al sur del continente - facebook.com</t>
+          <t>Preocupante cifra para los colegios privados en Colombia: Hay instituciones con solo la mitad de la ocupación de estudiantes - Yahoo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdlNPUVI5dDdwZ3B3eHdpemJIa1VFMnh0STBza3hUb3lzVGxYQS1JRHpya21SSHF3RXdBcjROYUptREtXVlJWdjR6dWNhWDd2akZmVVhpdGJjNHlITnZDeVRlRzFHR2xpcV9adWVXS3huM1R5ZUpOVnlYX1FKd3U4WXc4eXFaVlpQT2kwZHlKOTI0U0QtdlQ1STNBM1RhTkhOMVE3SlJRNHJ3VzB5YXdoNVFyT2RIWGhWY0dnaVcwWFNVVHZ2ekVSVTd0S3Rxc1VVRUNkdmgxUm41X3ZsLW9JVG9QRnR0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQa2pKZUJvTU5hVXBIajh1WjYxNjZfRGltMENTcG1YeDhoNi1BbElmZjhJYXZPal9Cc1NHc1JxM3NtWTZmb2ItX052MnpyaDZzMWJPeFRhMVBJQWtGemV2MWp1UUIyZExmeFk4eVpuT0pZMHdtRTRycnhMX2xtckdIWHNQQXc0T2laRzVBdXAxckJIRE5YUkhV?oc=5</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>“Ahora que estamos un poco más viejos, queremos ser un ejemplo para la juventud”: Camilo Villegas, golfista colombiano - UNIMINUTO Radio</t>
+          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UNIMINUTO Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5241,22 +5241,22 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPOFJRNk52Mkx1Q2hFTm5oQV9UUFlLYkVlMjZEanRsN0hnQU9xRTJTR08tQTl2MVYzQTFMWkRuYXJFcG4zbk5iYWE0clBva0dWVXFlMmt5NTQxTUhtamwzazlacC1HdXZjRkRFVW03U3ZNVVdGTEZHY0JHalFaVXJwLXpZRVpIYm1FcWhkUWVyY29Ud1Rzb1NDUG1UczFJdXNJNnh5MkpPbU5WTDFnV3hmcjBTbXpTcndtNnotMmNqNzdEYXJLSEM1cTA3U0F1ZzctQy1tMUhjc28wcU9kT04wc053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Preocupante cifra para los colegios privados en Colombia: Hay instituciones con solo la mitad de la ocupación de estudiantes - Yahoo</t>
+          <t>Menores de edad en Colombia pueden viajar sin permiso de ambos padres en 2026: en estos casos aplica - Eluniversal.com.co</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>Eluniversal.com.co</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQa2pKZUJvTU5hVXBIajh1WjYxNjZfRGltMENTcG1YeDhoNi1BbElmZjhJYXZPal9Cc1NHc1JxM3NtWTZmb2ItX052MnpyaDZzMWJPeFRhMVBJQWtGemV2MWp1UUIyZExmeFk4eVpuT0pZMHdtRTRycnhMX2xtckdIWHNQQXc0T2laRzVBdXAxckJIRE5YUkhV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNUkViVng5bVFEQmo3RnFIQXA5dWV6b0czWnJnaC0zRkc2QWx4dUJsZGZ1cXp3R2RfazFVeGdQZUU3Y1dvWUhlQ2o3NlVIaWlMamJNLXNUdlBzeFIyaFJSSVBoZEotTjRiNjRyUFV4Q1FEWFgxWGIyVGtRbUdrQl9mc0dzNXZlejhIelR3WkwwSDFGTzBydll5M1RHZm9YcmFId2NrMVF5eUczbW82bVU4X3p4dTliaTNRcWYwTlI0UG90b2hDUHYyTkhlbGRoelMzVGh3OGhLQnlPanNiOEgxTWlrYklBZw?oc=5</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UNAD se consolida como la universidad con más estudiantes matriculados en Colombia - Noticias UNAD</t>
+          <t>Indepaz advierte que cada 48 horas reclutan a un menor de edad en Colombia - Asuntos Legales</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Noticias UNAD</t>
+          <t>Asuntos Legales</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPRXI2ZFJ2VWhVRVI2MVBYUG1mbEZ5YjQzR1JuTVZwQ0QyMS1UbXl0aFdxX3hvNGVzTm1rMjNPTDAwUXFCVmtZZk43WkdyZUd3cXZkMjdxdE1acTczWmRmZVNyT05vcjFUUW5oZmRGVFFpeFozZjc4T2Jnb0JzNDVOVHVyS0liak56NzVZUEQ3anF1TlFOVVdkYWhJNTU1RmhtckJGWGlTN2xzem5NZTA2WFZ2bmE3c25ScndCeTZ1OWpxYVlLd0NaQUg2a3lvdjlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzZRdHpsR0ppR0ZOcHpRQkM3X0xRYUpQQXZTYmNSMkVPVTY0eHEzeUNXVXYyNFE2SVpaNDNOSG1aajZrUWdFZW9KQU5xS1ZsWjAzaGt0Q2tuUHRzanNCMmQ5OW5CaVhuSmo1bFZsTGR4OEtrTHJGNFR1RlVJZm8yQzNvYThsdDFhQnNKcHZnTi1GN2pYbEFibzdkcV9VT0lsUUdldi10ZUVTRWd4bVdoOE1OcUxyMnFpRlB6OU9kNUxLVHFvcGc?oc=5</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Alerta nacional: Niñas y adolescentes fueron las principales víctimas de delitos sexuales en 2025 - Publimetro Colombia</t>
+          <t>Llega el fin de polémica norma en los colegios: no podrán impedir el ingreso de estudiantes aunque incumpla... - redmas.com.co</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Publimetro Colombia</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNDJzNU02WjZVRFlSSDlrcGRZQVh5eXowNnR3S0tJVUtwbE9Qb3h6dnN4UkhyTG92WWtrMVlIaXB4RXpFcHVFU2RybTRVM1JyaVJPU05WbDJEeHpiZ3JCTGw2WkRoY0JmM2kzTndoWkUwcVVmeDBKckhUSDlfMkhRMk1qeHJDd3JadWdTdndkZ1diRFJVdGdLcG9QbENyVmpZY3FxeG5qdEF0dWdqenZRQ25qNUdlMnpuem9MRTRsYXpZMzJFMVg3MWN3ZTl2OHk0eUdURzBqN25tS28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQa0Q4WmNWV1NnY0hxOGhTRDB4Q0tyNW9VLTNFaTBIU2ZIN1ZRQ1R3LURaR0YwSHplWW5ZcGxDUnNvbXJyNFdWQmNtc0FPUnMzdnhxMkExbTVTdzlOTmQ0RGp0UG11RWRrZldGcnNlM0xPclh2MkozOW4yallGNm5JU0xBVHBhYUlPU0cxamI4NHVNcEMzbnhHZGp0aFpvQ0QyOGJUbzRqd3k4a3ppNXpJSDUxNl9JODgwOXVTNFdFWWhfendmeVQwS192X0ktMnFKVHNJMlR3X3dXUXRDZExHcUFqQndNd2R5RWFtWVZSRGRlTGM1Y2NiUEhkaTjSAYICQVVfeXFMTnFIaUUyVDJYOU9aOHJ1MnZ4ZlFMN3JDdkxTR1NoaTI1Uko0MzVJbFI5aWdpaUhfdDlYeVFrRE1tV2JkX21SaFJCVEtMc3IxMG1EUWZwakZZSlRPZ2JiLUtJLXpwSHAxb2EtUy1nejFRcWRxdFBNX29KV0ExMzNHTUZZQXpGQXFwRHVfSG5sX0FpclBoSHhwa1RidndpMFoxT2JiV0hLb3plSmFUZ05UdmxVb1Q5QkFDUmV3VUR3eWlQTFI3OFdNSjh5NFEzNnJzQzBpdnZ4TVhUSU91T3BROEFLTThBZkVKbU1KUU0xUURDaG5ObWR1UC1GSlZ4N0JLdzhB?oc=5</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Indepaz advierte que cada 48 horas reclutan a un menor de edad en Colombia - Asuntos Legales</t>
+          <t>Alerta nacional: Niñas y adolescentes fueron las principales víctimas de delitos sexuales en 2025 - Publimetro Colombia</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Asuntos Legales</t>
+          <t>Publimetro Colombia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNMzZRdHpsR0ppR0ZOcHpRQkM3X0xRYUpQQXZTYmNSMkVPVTY0eHEzeUNXVXYyNFE2SVpaNDNOSG1aajZrUWdFZW9KQU5xS1ZsWjAzaGt0Q2tuUHRzanNCMmQ5OW5CaVhuSmo1bFZsTGR4OEtrTHJGNFR1RlVJZm8yQzNvYThsdDFhQnNKcHZnTi1GN2pYbEFibzdkcV9VT0lsUUdldi10ZUVTRWd4bVdoOE1OcUxyMnFpRlB6OU9kNUxLVHFvcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNDJzNU02WjZVRFlSSDlrcGRZQVh5eXowNnR3S0tJVUtwbE9Qb3h6dnN4UkhyTG92WWtrMVlIaXB4RXpFcHVFU2RybTRVM1JyaVJPU05WbDJEeHpiZ3JCTGw2WkRoY0JmM2kzTndoWkUwcVVmeDBKckhUSDlfMkhRMk1qeHJDd3JadWdTdndkZ1diRFJVdGdLcG9QbENyVmpZY3FxeG5qdEF0dWdqenZRQ25qNUdlMnpuem9MRTRsYXpZMzJFMVg3MWN3ZTl2OHk0eUdURzBqN25tS28?oc=5</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Llega el fin de polémica norma en los colegios: no podrán impedir el ingreso de estudiantes aunque incumpla... - redmas.com.co</t>
+          <t>UNAD se consolida como la universidad con más estudiantes matriculados en Colombia - Noticias UNAD</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Noticias UNAD</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQa0Q4WmNWV1NnY0hxOGhTRDB4Q0tyNW9VLTNFaTBIU2ZIN1ZRQ1R3LURaR0YwSHplWW5ZcGxDUnNvbXJyNFdWQmNtc0FPUnMzdnhxMkExbTVTdzlOTmQ0RGp0UG11RWRrZldGcnNlM0xPclh2MkozOW4yallGNm5JU0xBVHBhYUlPU0cxamI4NHVNcEMzbnhHZGp0aFpvQ0QyOGJUbzRqd3k4a3ppNXpJSDUxNl9JODgwOXVTNFdFWWhfendmeVQwS192X0ktMnFKVHNJMlR3X3dXUXRDZExHcUFqQndNd2R5RWFtWVZSRGRlTGM1Y2NiUEhkaTjSAYICQVVfeXFMTnFIaUUyVDJYOU9aOHJ1MnZ4ZlFMN3JDdkxTR1NoaTI1Uko0MzVJbFI5aWdpaUhfdDlYeVFrRE1tV2JkX21SaFJCVEtMc3IxMG1EUWZwakZZSlRPZ2JiLUtJLXpwSHAxb2EtUy1nejFRcWRxdFBNX29KV0ExMzNHTUZZQXpGQXFwRHVfSG5sX0FpclBoSHhwa1RidndpMFoxT2JiV0hLb3plSmFUZ05UdmxVb1Q5QkFDUmV3VUR3eWlQTFI3OFdNSjh5NFEzNnJzQzBpdnZ4TVhUSU91T3BROEFLTThBZkVKbU1KUU0xUURDaG5ObWR1UC1GSlZ4N0JLdzhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPRXI2ZFJ2VWhVRVI2MVBYUG1mbEZ5YjQzR1JuTVZwQ0QyMS1UbXl0aFdxX3hvNGVzTm1rMjNPTDAwUXFCVmtZZk43WkdyZUd3cXZkMjdxdE1acTczWmRmZVNyT05vcjFUUW5oZmRGVFFpeFozZjc4T2Jnb0JzNDVOVHVyS0liak56NzVZUEQ3anF1TlFOVVdkYWhJNTU1RmhtckJGWGlTN2xzem5NZTA2WFZ2bmE3c25ScndCeTZ1OWpxYVlLd0NaQUg2a3lvdjlR?oc=5</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IEEE. Del campo de batalla a la construcción de la paz: el papel de las autoridades en la desmovilización y reinserción de las niñas soldados en la Colombia del futuro - Ministerio de Defensa</t>
+          <t>En Japón estudiantes colombianos podrán estudiar lengua y cultura de ese país con becas de intercambio del ICETEX y el gobierno del Japón. - icetex.gov.co</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ministerio de Defensa</t>
+          <t>icetex.gov.co</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQQ3hUMDdhc1ZEcHp1a0dtb3dTbE13d1duR3pUX0dWLTJqbzZfYmlIYl9Id2M3Yy1CdmNtUk1qam1xRnc2NTNJRDk3UXF2TzJGYVNWY3YwXzRYSVlDZ05uQ1c4blY4V2d6XzNzc2JRckdJVE0zSWNnNXJPY3NhODN4b1hYcFhiQUl4UGJ1VkNDWGIwZms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOR3VLZkYwT0EzdC1YZkZFSktLdlFzRGZfVDQwWlE2Vlc2SkY3WmJaZkxvLXU3dVhZd0l5VHl5ZVRwMkw5NGdpTDdYODYyc096ZnhTNkd1V3NGNkdaZjZxM3hicHg2V3kyU0dvLVV0bkpRTWtQZTQ5eGtOY3BXNWxpSnhCZWJtWmtZelFKSlJfUmJfYmxHdlRKY2F0aUxrNXhRQ3MwREtFeHdzcFd3eWgwV1RMclVNckxTSm5qSjVwMVZzS0tEYzlleTFlalhlRzlOLUFmSjRpbTZWLXJsMlNzQg?oc=5</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Reconocidos colegios de Colombia no abrieron sus puertas en 2026 tras años de historia: se despiden de estu... - redmas.com.co</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6669,17 +6669,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPUzRTZldvRkIxRnROTWFON1RxYjhpb0V3a0psY0lFYUVMYlVCb1dPSVUyRzlMOENOTENqeWF4MUtiT181bDJ1TnZuQ0dSYU1yZEljZVR1Qm5pYldRNjhVV0lndy1qSWpNZkFTWVBRY1I3ZHZCQjRCdW9NOUdmamhNNU5FcXJDVzlXZXJ3VEpCaVM5cU14Yzc1c0RpTVc2c3Q4SnhVbWx3TzMyUlN5SWdWbUJGblRlZzRaRExGdGtjMzI1M29KQ0hlSUF5cWZfY3dqdDd1Mk16WldZUHdScGo1WTl2NWctc3V0RlFwZzZqQTY5QllHSVV4M21iVHY5VTNfZlJJQWFVY9IBjAJBVV95cUxQa25SdDJjem94UFMzQWQ4VTZmVUVveTNZbEgyLWJVdmRCdEVXRHpWSjdHZ1JuUU9lek56eTZsVFhWeVQ5VHZudWI0ZXVqTENNdHhuWWlfdFYwNWE5YjcxWXR6b1k2aWNzLXBsaFpfOXZxcTJUNnRZVU43dWE1clBlVGd2S3gteXp0TUllWGhJRmJrSHBTM2ZfT2pQRGdSV2o5dlVibVdFSkViZ09NOVNweVJMRXFGS0pmb1QxdHBZNmtBX3lKdnk5dlZrdWc2VzBlX3MyLUpvcjVXeURabWZDX1ozT3J4Y2pmdGdKZFNJeHR4bTRPSi1XU3FxRFFzbl9jQTl6UUF0bWI1NThu?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -6692,12 +6692,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Estos son los programas de educación superior que la candidata Paloma Valencia propone revivir para los jóvenes en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQbFBTcllrWjJwdEJlbnJRN3Fpa2I5U2V6NTJiRWpfRlNqY0J0ODNPS2cyZEllM1c3V2pvUWtKWXM2endVdFR5WHhzQU5fdHZ5OTBfN3lXaFBqRzdHb0lhb3RON3ZJNTUyTXFDN3IzVE54d0hkMHNuUUNkbGhLanMxWUNkZG1YYzJ5dUNRMXhRbVZELUZLOG1ZMTl2eVUtcUxDMWdkYndPUWpVb25RUFFpb1NzWHk3cVh3d0JPSWhpYzBhVWFfaWp5YkxOUS1sWUNvXzBNWXhRS2VlcGt4YVRIX2VjYzk4RzBmeHBXVzBLOHFuQTJrOGRjc2Z4QXB6TS1oMEM4N0t3SXk5YzlOaEtPdS1iVVY4RGNILXpHVXlyNjV2TWfSAagCQVVfeXFMTmRvRUNOVGpWeUQxZUtaN1UtTjlOMjBLTmZpbHN5cmZVRzRpeFE1QlcyTFdjN0xtQVNuLVJzREdTc2ZYRWpVMFl5dXg2SG1HenR0NE9WNklvZkEwYk1VaTRPNTJHbC0xRG1lcDZfRG1XLW1sZHJLcVIzd1pSektGUUNTbFZFWlN6VWMxTF9rbGV0bC0tdUNmaWJpUjRSX1VUM0podFloLWt0dlI5WllVeDRyWV9PUGswZE5oV2dzbXRkY1FjeERRRkJzTkpVcVV1LVBhazVoQWtCbGJVSy1nUFZyQ0dacER5RG1aOWJmWFFHalpBUkxiV3RBZ045X05tWHd4Y2hoWGJDLS1EcDhYOHBnNGVlWEpiUGNwQmhoeUJ5M0NoTU9zSGg?oc=5</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Estos son los programas de educación superior que la candidata Paloma Valencia propone revivir para los jóvenes en Colombia - ELTIEMPO.COM</t>
+          <t>Inició el calendario escolar 2026 para los estudiantes de Cali establecido en la Resolución No. 4143.0.21.0. 06508 del 31 de octubre de 2025 - cali.gov.co</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>cali.gov.co</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxQbFBTcllrWjJwdEJlbnJRN3Fpa2I5U2V6NTJiRWpfRlNqY0J0ODNPS2cyZEllM1c3V2pvUWtKWXM2endVdFR5WHhzQU5fdHZ5OTBfN3lXaFBqRzdHb0lhb3RON3ZJNTUyTXFDN3IzVE54d0hkMHNuUUNkbGhLanMxWUNkZG1YYzJ5dUNRMXhRbVZELUZLOG1ZMTl2eVUtcUxDMWdkYndPUWpVb25RUFFpb1NzWHk3cVh3d0JPSWhpYzBhVWFfaWp5YkxOUS1sWUNvXzBNWXhRS2VlcGt4YVRIX2VjYzk4RzBmeHBXVzBLOHFuQTJrOGRjc2Z4QXB6TS1oMEM4N0t3SXk5YzlOaEtPdS1iVVY4RGNILXpHVXlyNjV2TWfSAagCQVVfeXFMTmRvRUNOVGpWeUQxZUtaN1UtTjlOMjBLTmZpbHN5cmZVRzRpeFE1QlcyTFdjN0xtQVNuLVJzREdTc2ZYRWpVMFl5dXg2SG1HenR0NE9WNklvZkEwYk1VaTRPNTJHbC0xRG1lcDZfRG1XLW1sZHJLcVIzd1pSektGUUNTbFZFWlN6VWMxTF9rbGV0bC0tdUNmaWJpUjRSX1VUM0podFloLWt0dlI5WllVeDRyWV9PUGswZE5oV2dzbXRkY1FjeERRRkJzTkpVcVV1LVBhazVoQWtCbGJVSy1nUFZyQ0dacER5RG1aOWJmWFFHalpBUkxiV3RBZ045X05tWHd4Y2hoWGJDLS1EcDhYOHBnNGVlWEpiUGNwQmhoeUJ5M0NoTU9zSGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNWlRsbG45VUtFQ04wZTVnTUpVVENFbU9kZkxiNTd4c3RPTUR3bmRJSF9ZR3k1U3NjN1BKN3RBbF9Nc0dqUzBmZDZweE1mOUZxb2s2REgyR19VZ1NiZi1VLUFUTTFyUUE1RDN6bDdKN1ZtNkQ4bjV6R3lJZTJtT2JRdzJWUGo2TTFDLVpEWkpGZWVYaWZBbTdQaFljSHVYOHhCY1JCdEVQOC1xSGlZWDN0QUJCY1BRVjFienNpNzEyOWpzc1ZfNG5fanItY3B1SkktMFZaRUxZcDQ0T0J3d3hUVFZ6c2hhbTR6YUdJZVhxanlBb2twY1JfSHhLNWxvSlNLN2dBLWlRd3Rvbm1FYmFQeEZlTEYwdG4zQzVJ?oc=5</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Inició el calendario escolar 2026 para los estudiantes de Cali establecido en la Resolución No. 4143.0.21.0. 06508 del 31 de octubre de 2025 - cali.gov.co</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>cali.gov.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNWlRsbG45VUtFQ04wZTVnTUpVVENFbU9kZkxiNTd4c3RPTUR3bmRJSF9ZR3k1U3NjN1BKN3RBbF9Nc0dqUzBmZDZweE1mOUZxb2s2REgyR19VZ1NiZi1VLUFUTTFyUUE1RDN6bDdKN1ZtNkQ4bjV6R3lJZTJtT2JRdzJWUGo2TTFDLVpEWkpGZWVYaWZBbTdQaFljSHVYOHhCY1JCdEVQOC1xSGlZWDN0QUJCY1BRVjFienNpNzEyOWpzc1ZfNG5fanItY3B1SkktMFZaRUxZcDQ0T0J3d3hUVFZ6c2hhbTR6YUdJZVhxanlBb2twY1JfSHhLNWxvSlNLN2dBLWlRd3Rvbm1FYmFQeEZlTEYwdG4zQzVJ?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>IEEE. Del campo de batalla a la construcción de la paz: el papel de las autoridades en la desmovilización y reinserción de las niñas soldados en la Colombia del futuro - Ministerio de Defensa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ministerio de Defensa</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6836,22 +6836,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQQ3hUMDdhc1ZEcHp1a0dtb3dTbE13d1duR3pUX0dWLTJqbzZfYmlIYl9Id2M3Yy1CdmNtUk1qam1xRnc2NTNJRDk3UXF2TzJGYVNWY3YwXzRYSVlDZ05uQ1c4blY4V2d6XzNzc2JRckdJVE0zSWNnNXJPY3NhODN4b1hYcFhiQUl4UGJ1VkNDWGIwZms?oc=5</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6864,12 +6864,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>En Japón estudiantes colombianos podrán estudiar lengua y cultura de ese país con becas de intercambio del ICETEX y el gobierno del Japón. - icetex.gov.co</t>
+          <t>Reconocidos colegios de Colombia no abrieron sus puertas en 2026 tras años de historia: se despiden de estu... - redmas.com.co</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>icetex.gov.co</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOR3VLZkYwT0EzdC1YZkZFSktLdlFzRGZfVDQwWlE2Vlc2SkY3WmJaZkxvLXU3dVhZd0l5VHl5ZVRwMkw5NGdpTDdYODYyc096ZnhTNkd1V3NGNkdaZjZxM3hicHg2V3kyU0dvLVV0bkpRTWtQZTQ5eGtOY3BXNWxpSnhCZWJtWmtZelFKSlJfUmJfYmxHdlRKY2F0aUxrNXhRQ3MwREtFeHdzcFd3eWgwV1RMclVNckxTSm5qSjVwMVZzS0tEYzlleTFlalhlRzlOLUFmSjRpbTZWLXJsMlNzQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPUzRTZldvRkIxRnROTWFON1RxYjhpb0V3a0psY0lFYUVMYlVCb1dPSVUyRzlMOENOTENqeWF4MUtiT181bDJ1TnZuQ0dSYU1yZEljZVR1Qm5pYldRNjhVV0lndy1qSWpNZkFTWVBRY1I3ZHZCQjRCdW9NOUdmamhNNU5FcXJDVzlXZXJ3VEpCaVM5cU14Yzc1c0RpTVc2c3Q4SnhVbWx3TzMyUlN5SWdWbUJGblRlZzRaRExGdGtjMzI1M29KQ0hlSUF5cWZfY3dqdDd1Mk16WldZUHdScGo1WTl2NWctc3V0RlFwZzZqQTY5QllHSVV4M21iVHY5VTNfZlJJQWFVY9IBjAJBVV95cUxQa25SdDJjem94UFMzQWQ4VTZmVUVveTNZbEgyLWJVdmRCdEVXRHpWSjdHZ1JuUU9lek56eTZsVFhWeVQ5VHZudWI0ZXVqTENNdHhuWWlfdFYwNWE5YjcxWXR6b1k2aWNzLXBsaFpfOXZxcTJUNnRZVU43dWE1clBlVGd2S3gteXp0TUllWGhJRmJrSHBTM2ZfT2pQRGdSV2o5dlVibVdFSkViZ09NOVNweVJMRXFGS0pmb1QxdHBZNmtBX3lKdnk5dlZrdWc2VzBlX3MyLUpvcjVXeURabWZDX1ozT3J4Y2pmdGdKZFNJeHR4bTRPSi1XU3FxRFFzbl9jQTl6UUF0bWI1NThu?oc=5</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Se acaban los castigos para estudiantes en colegios: Corte Constitucional pone contra las cuerdas a los rec... - redmas.com.co</t>
+          <t>Más de 220 menores de edad fueron rescatados tras estar abandonados en Bogotá en 2025 - Caracol Radio</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7481,22 +7481,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPeUdyQjFZLUJGUHR0WTBwSldBTGJtRHFmU2NJNkJWT0tBMzlNTFJ6RWpTekQxRVUyX2phUHE4dzFwbTBQZ3Q3SHE1QllpQUN0Q1BJdGpVQjVGWmNrX25wVGZhLUhfei1weWVPbnloMEczS0Y0YXNUN1otS1MxQVQxaE5SMldWdkVvV2xvTEx5VlY3V25WNmYyVnFsM1ZZcFUwb2dYa0FBbkcwUjZGempNelNEUFdsNk9BbFNHOVVfRUR2UEs5RFd1OFJYSVpzM2NSb0NRZUYzRHJRSzJfelFreE5IaHU1T3pZdktHeWtQUHRNMGd3c1FiaDhfTXJwTF9PME42elZja9IBjAJBVV95cUxOTlRtWDJiVkhqc0tmcHpDUkFGSVA1bHFTdlJIbkZBUElBNnRvWjV0bEhXaVhhakpJUEtUZ0xGeGNVV09HWTNPUzl5S0Y4bzZiQmJNc0o4VkdnYmJRSHRGQlJadmxyNFNuNk9GZUpURHlnWlEzbTh3VzFHZ1pBMWZ5WHNEZm9ubkYzUU1KTGdOdGNLbHpJTDlRNENZNTRISG9sT29kQ0RjRTFRNDNUSUtsY3p0dFRhLThoX3lxU2Y2RXFoMmVtSXB3eVRuT3p6ZG5NVk1zRmlENFVZa1gyRmJQNHhpMGFXRFNtOVZ3YUh3QmFZaXVWY2Etd2I3SFBWZk45aE12dkE3WEJwdEg1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOalk3YjJZcTBJakNTakdzSVVMcWZOWmFVM09BaWpMWFVUYnMzVER4QzRNTmNJUURGUWZ6Mmw2YjhMcDhPenR4VzRaQXlpUTRUc3pUcnhjUkxCZVZ4b0REQ3lBZnU5d0pYWV9CNWd0Q29ZLXNpWWxMeTl0WG4tNmNTT2xNYW53OUIwNXhQUnlIQXNSWWxEcUt4Yk15UWZwa3IzZnBBbW5vZ1VBYlp6dmZWR1FaZWE2azFHSVk3dQ?oc=5</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -7509,12 +7509,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>¿Qué está pasando con los colegios privados en Colombia? - El Nuevo Siglo</t>
+          <t>Aunque las cifras bajaron frente a 2024, cientos de niños y adolescentes, muchos de ellos indígenas, fueron reclutados por grupos armados en zonas de alta vulnerabilidad - facebook.com</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>El Nuevo Siglo</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZzZTLXZVaUFVM043V2MtUHZGUFRWVktvSjF2d0c5cUNrbzg1MThzdW1mUVhIeTV5ZW8xak9obGxzMjJTRXVYVG93R2V3OGVqWjBNQnRoNWxVMXBEMWR2eHIxb1pyOFllWEZxem8wSTQ2aktzVTNndUNMU2szeHJKWTNDWlFWbDVtNEwyckF4ajF6WlhjTC02bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPWWtnRGpyNFl6cVhWWGhFRjhDYVFfZnR6Q0JrclZhRXF1NUxCMEZjbWRneExlUGNoN2RoTk1uUjdiRVBJVmoydVdmRzdJX3BDRExySmxxZ2dITkhUT0tZRzRDQ3NvcWI3LW5za0NyaGVoNzN0NjY3Xzdna2daS2RuRmtYS1dwUmUxclBpdURNRmR0Y3JOeU1DWXFFUEpXLVlqSGtzWUs5Mm9ib29RLUxHaDVQMEc0WkJyWkF2UV9abFB6NkZmSkh6NEE4VVhyR21tdV96bDNIRnhCWk1WVFluVFMzeHQ?oc=5</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -7552,12 +7552,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>⚽ Santa Fe propone torneo sub-23 para dar oportunidades a jóvenes y futbolistas sin club. #Fútbol #Juventud #Colombia - Facebook</t>
+          <t>Colombia presentó avances en la protección de la niñez y la adolescencia ante el Comité de los Derechos del Niño - Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxObFJ5amljVE9jSVpXcTh3b1pqaXNPWWp3QkFjZkFPT25VRk9KbDczbno3VFFlZnZkc2RURl9PdXVxOXNCV2lYdGZHYmVmYmoyLTl6TWJsNjYzLVJwOEoyWmM0TU1zYTJld24wdUJTcHE5RzhXdlk5VTE4WVpWQWpYS3R5REo4aURzZ0tkMTA2WGd1Y1dQdWFrTy1zZHZueWhlb1gwYXc0dWhjZ05Oc0tlQVpCR2pta2E4MU1vTTVFUW0yRDZDcWN5Z3g2RUYtUjdfWFdDc3Z1czBRMkYzVFcwV1pUUEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQajg4Z0F1TkdHLTRxTG9Sd2tUTXBxWDNyaWo4a1RuTXFZUHNVaDM2XzRvNDZWZS1ZRXVNaGRFc0hiaVVsaUU3NHdtNTVUbXRVbVZReGJPaEVzVzdZSHNweWdrVmhpQVV1REVfcmpSeDlFeGhZNjFEb2huNTlpZkVTMlhpbVRPZEh1OXdhLWxmdnBRNURlV2dYemhVenJheTZLZkZhMU93NXVVX0pobC1VNFhoN2FrNG1XZUl5MG9iNFQ?oc=5</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -7595,12 +7595,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>¿Qué está pasando con los colegios privados en Colombia? - Ministerio de Educación Nacional</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPR1N5MGEzQ0xqcVF5cVd3TUJXVGJ0Um9kSElKTXVWbDc4Q1FEdTBrbjI0TmJ5OFFNZFRseXQwYmhEYTNvM2dNWUlfaU1WMnFEb0luTEdadTJ4VmFuZ1h1eHM0T0ZPQ1BGRlhlQlpEZGJtRklRbXhtVE8xMVVFUGZESjRIYXBVVF9DTUJOcVRMZExSSkZVbmdTQzVOZG01aUIzT1VjamFsUFJrZVZ4aHFJNlZEUWNqVHBiZUpQSjZ4NHo?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -7638,12 +7638,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>¿Qué está pasando con los colegios privados en Colombia? - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPR1N5MGEzQ0xqcVF5cVd3TUJXVGJ0Um9kSElKTXVWbDc4Q1FEdTBrbjI0TmJ5OFFNZFRseXQwYmhEYTNvM2dNWUlfaU1WMnFEb0luTEdadTJ4VmFuZ1h1eHM0T0ZPQ1BGRlhlQlpEZGJtRklRbXhtVE8xMVVFUGZESjRIYXBVVF9DTUJOcVRMZExSSkZVbmdTQzVOZG01aUIzT1VjamFsUFJrZVZ4aHFJNlZEUWNqVHBiZUpQSjZ4NHo?oc=5</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Colombia presentó avances en la protección de la niñez y la adolescencia ante el Comité de los Derechos del Niño - Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>⚽ Santa Fe propone torneo sub-23 para dar oportunidades a jóvenes y futbolistas sin club. #Fútbol #Juventud #Colombia - Facebook</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQajg4Z0F1TkdHLTRxTG9Sd2tUTXBxWDNyaWo4a1RuTXFZUHNVaDM2XzRvNDZWZS1ZRXVNaGRFc0hiaVVsaUU3NHdtNTVUbXRVbVZReGJPaEVzVzdZSHNweWdrVmhpQVV1REVfcmpSeDlFeGhZNjFEb2huNTlpZkVTMlhpbVRPZEh1OXdhLWxmdnBRNURlV2dYemhVenJheTZLZkZhMU93NXVVX0pobC1VNFhoN2FrNG1XZUl5MG9iNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxObFJ5amljVE9jSVpXcTh3b1pqaXNPWWp3QkFjZkFPT25VRk9KbDczbno3VFFlZnZkc2RURl9PdXVxOXNCV2lYdGZHYmVmYmoyLTl6TWJsNjYzLVJwOEoyWmM0TU1zYTJld24wdUJTcHE5RzhXdlk5VTE4WVpWQWpYS3R5REo4aURzZ0tkMTA2WGd1Y1dQdWFrTy1zZHZueWhlb1gwYXc0dWhjZ05Oc0tlQVpCR2pta2E4MU1vTTVFUW0yRDZDcWN5Z3g2RUYtUjdfWFdDc3Z1czBRMkYzVFcwV1pUUEU?oc=5</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Aunque las cifras bajaron frente a 2024, cientos de niños y adolescentes, muchos de ellos indígenas, fueron reclutados por grupos armados en zonas de alta vulnerabilidad - facebook.com</t>
+          <t>¿Qué está pasando con los colegios privados en Colombia? - El Nuevo Siglo</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>El Nuevo Siglo</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPWWtnRGpyNFl6cVhWWGhFRjhDYVFfZnR6Q0JrclZhRXF1NUxCMEZjbWRneExlUGNoN2RoTk1uUjdiRVBJVmoydVdmRzdJX3BDRExySmxxZ2dITkhUT0tZRzRDQ3NvcWI3LW5za0NyaGVoNzN0NjY3Xzdna2daS2RuRmtYS1dwUmUxclBpdURNRmR0Y3JOeU1DWXFFUEpXLVlqSGtzWUs5Mm9ib29RLUxHaDVQMEc0WkJyWkF2UV9abFB6NkZmSkh6NEE4VVhyR21tdV96bDNIRnhCWk1WVFluVFMzeHQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQZzZTLXZVaUFVM043V2MtUHZGUFRWVktvSjF2d0c5cUNrbzg1MThzdW1mUVhIeTV5ZW8xak9obGxzMjJTRXVYVG93R2V3OGVqWjBNQnRoNWxVMXBEMWR2eHIxb1pyOFllWEZxem8wSTQ2aktzVTNndUNMU2szeHJKWTNDWlFWbDVtNEwyckF4ajF6WlhjTC02bA?oc=5</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Más de 220 menores de edad fueron rescatados tras estar abandonados en Bogotá en 2025 - Caracol Radio</t>
+          <t>Se acaban los castigos para estudiantes en colegios: Corte Constitucional pone contra las cuerdas a los rec... - redmas.com.co</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7782,22 +7782,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOalk3YjJZcTBJakNTakdzSVVMcWZOWmFVM09BaWpMWFVUYnMzVER4QzRNTmNJUURGUWZ6Mmw2YjhMcDhPenR4VzRaQXlpUTRUc3pUcnhjUkxCZVZ4b0REQ3lBZnU5d0pYWV9CNWd0Q29ZLXNpWWxMeTl0WG4tNmNTT2xNYW53OUIwNXhQUnlIQXNSWWxEcUt4Yk15UWZwa3IzZnBBbW5vZ1VBYlp6dmZWR1FaZWE2azFHSVk3dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPeUdyQjFZLUJGUHR0WTBwSldBTGJtRHFmU2NJNkJWT0tBMzlNTFJ6RWpTekQxRVUyX2phUHE4dzFwbTBQZ3Q3SHE1QllpQUN0Q1BJdGpVQjVGWmNrX25wVGZhLUhfei1weWVPbnloMEczS0Y0YXNUN1otS1MxQVQxaE5SMldWdkVvV2xvTEx5VlY3V25WNmYyVnFsM1ZZcFUwb2dYa0FBbkcwUjZGempNelNEUFdsNk9BbFNHOVVfRUR2UEs5RFd1OFJYSVpzM2NSb0NRZUYzRHJRSzJfelFreE5IaHU1T3pZdktHeWtQUHRNMGd3c1FiaDhfTXJwTF9PME42elZja9IBjAJBVV95cUxOTlRtWDJiVkhqc0tmcHpDUkFGSVA1bHFTdlJIbkZBUElBNnRvWjV0bEhXaVhhakpJUEtUZ0xGeGNVV09HWTNPUzl5S0Y4bzZiQmJNc0o4VkdnYmJRSHRGQlJadmxyNFNuNk9GZUpURHlnWlEzbTh3VzFHZ1pBMWZ5WHNEZm9ubkYzUU1KTGdOdGNLbHpJTDlRNENZNTRISG9sT29kQ0RjRTFRNDNUSUtsY3p0dFRhLThoX3lxU2Y2RXFoMmVtSXB3eVRuT3p6ZG5NVk1zRmlENFVZa1gyRmJQNHhpMGFXRFNtOVZ3YUh3QmFZaXVWY2Etd2I3SFBWZk45aE12dkE3WEJwdEg1?oc=5</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>La deserción escolar le cuesta a Colombia $2,8 billones al año: casi el 40% de los estudiantes abandona las aulas - Publimetro Colombia</t>
+          <t>¿Dónde estudian los genios de Colombia? Estos son los únicos colegios del país con calificación AAA+ - Portafolio.co</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Publimetro Colombia</t>
+          <t>Portafolio.co</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNOWpHQlNpRUdaU1ZWSzBzd3EzM2I3cmZXdzd4aUNrMjlnbWJPZkNNbVVGYXRrX2VPUjJxcEt5ZUJha3lyOS1VODQtTmV5d3NFdU80ME01eFg5X2dWZ25GT0Vhdl9TbVJBZ1RkaEJBZHh3aXNpNEMweEJEM3NuUmxRLWMzQWdUOEFkUUlKbm1PR1FyWVNMSGppa3VOZ2JUQy1wTl9sdkRpT0xhdWNaclNBdmxycEZnTUU0dHJvVVdsbWRaeDc2V1ZHb3dNMmNucmpuTzRkdDRzaERIY093NW81MnpDM0diSHRTbkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPczRONEpvSjI3TmpVWEdqVnNtUG1LeFBjSjc2X0ZfR2RQaVcxN1J6ZDBheFcwVHNPZGcyelI3RUFsWEp1YXBQcDFacFJjSkVXVWRCZ3ZhMzdZRmtvOVBHckJjWDlhdlV4NUF3anRJR21qN0RqV1dhRFlLQ2lIVm40NnRSNlBXMDNWZlB0dkhMWW1zOXRkOUJyRmVBaENseXYyREtzUlRxUkJsTUJ1eUJPQWs0aW5hdU96LXU2ejVkMlJNZERnZXRTUk9ydXB0UURFX3dvVkJ5Qm9SUDFFUXBuTzBn0gHnAUFVX3lxTE5wZFNHdzdvOWxRLWQtOWtrcUFzZi0ydEFMXzF0YUZOa3AwQjlNUjFablhQRTdwR2J5Qzh5WDZ3UEZ4QTZSc2MwbHB6TnM0WTduMjduVnM2RnRTY0JQR1ZtWTB0QThMaXNVQlZQV2xENVBZTXV6ZHQxVGNTNDF1ZGpxbU9BeEFxMGZrUVNIdVNJeUpjcmVXcm5pemM2SHRUR0duN0hKWjVlNzR4bDFsWVRKTjhmbTJoQlM1a2RheHVSc0N5MkNucmFhdnkzYUFHby1Qb3R0TE56dHBMNUoyVnhTa01IU3liWQ?oc=5</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -7853,12 +7853,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Medicina Legal confirma la muerte de cuatro menores de edad por los enfrentamientos entre disidencias en Guaviare - EL PAÍS</t>
+          <t>Imposición de boinas: jóvenes construyen un futuro sólido al servicio de Colombia - Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>EL PAÍS</t>
+          <t>Fuerza Aeroespacial Colombiana</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNQ0VEeWtCQWV2VXlEekdmTTBNNWdRVTNNVEd0Vmt6QkM4UGItcWQwOFZhZFNHNGJIOWhpWGhVeFFxTFRFV3lHeTdIOFF5aDltV0hWUURZM1dsQmFfVmFvTU1JdGJ5U09wVktadWhJWUNMdnllQVJXOU4zZS1SdDVqdk5OOGJqc0hDNFVUa3ZkZ2dQNXZkMDdlbVh3RXlHSnh5N1J4a2VLYU1SR3N5czFVQ3BfZW5wQmZtY0Y4RmctWU5BbjhGU2hvSVRLdjdLWV9pcUZSZXRqYXR1am1tNll5VXR4bmtCZlR1blhXUFl1V1VqU3pGUG9jbtIBjAJBVV95cUxQWXZ3bFpiSDN6eWVxM2ZTckYwcUpSRExJc2ZYVUtONWhLYnJBX0JMZ2lUTFJkRzFKZmZUQ0R5OFVBM3pkZzlWdldJc0tPZ2E0R3JGd0JkUElqOTJDSmdmbWlzRjJrWXZIQ0pnMHgwb1lVekpVWTRiMHZIdHpnUXhyTURpeDV5X0NHbFFXTnFYN3hQbDYwVG0yQUFGTFM2a2tIRFMyQU93WG95LTExWUlJbkRsQ1RYcC04UXYzYmtXNFNxbDctWmN6RFVZWWtNbEFFQVF1N2lDd1NGVFBzR3BJUkpWR2FvLXZoQnR6V1Mzc1NMNHNtRkFmalRrd1FMT3lWY2VhT3RzRkkxXzdC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSlFESU01MVJsb3l4c2RqRHh3UHVHcHZjcEhSUldGYmZLZmNnOC14NUh2a1dFZUlkZ000STZVcEt5a3RVellXTWQ1SFF1YjZlLTVvRTdBbVhvX2FMc0I5dEhMamZJajJvOW1hWFFPd3ZvdGZlNE90M0Z1VGpKN2NZZVVwS083dWJJb3VaUGZtQWw4eFNYOWhFSWh3VExoRi1ZSGJMOGNUYUxhV3JQbE1KalphcWw?oc=5</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -7896,12 +7896,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
+          <t>Consejos Locales de Juventud en Bogotá: 21 jóvenes se posesionaron en Tunjuelito - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7911,22 +7911,22 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNUnRxaERnUnRKcEkxaWZ2cHlsZFRuQkRtMXpDcWZxdU1NNk05VERuZV9CQVhPbXI3Y1d1RGFPMGF0ZGsyamNvZEhFTkQzQWdUSzVNVjg1U0JNQ29WTVRxTldKNWEwX2sybGE5TXhfcU5BUEJ4YVU3MmhFdnpGb0JzV0c2ck1mcGZnc2RVLTd0MEtzZktlQXVzRTN4bVZEa1JOTnlMa0VYWGtkYVJIdURz?oc=5</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -8068,12 +8068,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Consejos Locales de Juventud en Bogotá: 21 jóvenes se posesionaron en Tunjuelito - Bogota.gov.co</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8083,22 +8083,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNUnRxaERnUnRKcEkxaWZ2cHlsZFRuQkRtMXpDcWZxdU1NNk05VERuZV9CQVhPbXI3Y1d1RGFPMGF0ZGsyamNvZEhFTkQzQWdUSzVNVjg1U0JNQ29WTVRxTldKNWEwX2sybGE5TXhfcU5BUEJ4YVU3MmhFdnpGb0JzV0c2ck1mcGZnc2RVLTd0MEtzZktlQXVzRTN4bVZEa1JOTnlMa0VYWGtkYVJIdURz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -8111,12 +8111,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Imposición de boinas: jóvenes construyen un futuro sólido al servicio de Colombia - Fuerza Aeroespacial Colombiana</t>
+          <t>Medicina Legal confirma la muerte de cuatro menores de edad por los enfrentamientos entre disidencias en Guaviare - EL PAÍS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Fuerza Aeroespacial Colombiana</t>
+          <t>EL PAÍS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSlFESU01MVJsb3l4c2RqRHh3UHVHcHZjcEhSUldGYmZLZmNnOC14NUh2a1dFZUlkZ000STZVcEt5a3RVellXTWQ1SFF1YjZlLTVvRTdBbVhvX2FMc0I5dEhMamZJajJvOW1hWFFPd3ZvdGZlNE90M0Z1VGpKN2NZZVVwS083dWJJb3VaUGZtQWw4eFNYOWhFSWh3VExoRi1ZSGJMOGNUYUxhV3JQbE1KalphcWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNQ0VEeWtCQWV2VXlEekdmTTBNNWdRVTNNVEd0Vmt6QkM4UGItcWQwOFZhZFNHNGJIOWhpWGhVeFFxTFRFV3lHeTdIOFF5aDltV0hWUURZM1dsQmFfVmFvTU1JdGJ5U09wVktadWhJWUNMdnllQVJXOU4zZS1SdDVqdk5OOGJqc0hDNFVUa3ZkZ2dQNXZkMDdlbVh3RXlHSnh5N1J4a2VLYU1SR3N5czFVQ3BfZW5wQmZtY0Y4RmctWU5BbjhGU2hvSVRLdjdLWV9pcUZSZXRqYXR1am1tNll5VXR4bmtCZlR1blhXUFl1V1VqU3pGUG9jbtIBjAJBVV95cUxQWXZ3bFpiSDN6eWVxM2ZTckYwcUpSRExJc2ZYVUtONWhLYnJBX0JMZ2lUTFJkRzFKZmZUQ0R5OFVBM3pkZzlWdldJc0tPZ2E0R3JGd0JkUElqOTJDSmdmbWlzRjJrWXZIQ0pnMHgwb1lVekpVWTRiMHZIdHpnUXhyTURpeDV5X0NHbFFXTnFYN3hQbDYwVG0yQUFGTFM2a2tIRFMyQU93WG95LTExWUlJbkRsQ1RYcC04UXYzYmtXNFNxbDctWmN6RFVZWWtNbEFFQVF1N2lDd1NGVFBzR3BJUkpWR2FvLXZoQnR6V1Mzc1NMNHNtRkFmalRrd1FMT3lWY2VhT3RzRkkxXzdC?oc=5</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>¿Dónde estudian los genios de Colombia? Estos son los únicos colegios del país con calificación AAA+ - Portafolio.co</t>
+          <t>La deserción escolar le cuesta a Colombia $2,8 billones al año: casi el 40% de los estudiantes abandona las aulas - Publimetro Colombia</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portafolio.co</t>
+          <t>Publimetro Colombia</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPczRONEpvSjI3TmpVWEdqVnNtUG1LeFBjSjc2X0ZfR2RQaVcxN1J6ZDBheFcwVHNPZGcyelI3RUFsWEp1YXBQcDFacFJjSkVXVWRCZ3ZhMzdZRmtvOVBHckJjWDlhdlV4NUF3anRJR21qN0RqV1dhRFlLQ2lIVm40NnRSNlBXMDNWZlB0dkhMWW1zOXRkOUJyRmVBaENseXYyREtzUlRxUkJsTUJ1eUJPQWs0aW5hdU96LXU2ejVkMlJNZERnZXRTUk9ydXB0UURFX3dvVkJ5Qm9SUDFFUXBuTzBn0gHnAUFVX3lxTE5wZFNHdzdvOWxRLWQtOWtrcUFzZi0ydEFMXzF0YUZOa3AwQjlNUjFablhQRTdwR2J5Qzh5WDZ3UEZ4QTZSc2MwbHB6TnM0WTduMjduVnM2RnRTY0JQR1ZtWTB0QThMaXNVQlZQV2xENVBZTXV6ZHQxVGNTNDF1ZGpxbU9BeEFxMGZrUVNIdVNJeUpjcmVXcm5pemM2SHRUR0duN0hKWjVlNzR4bDFsWVRKTjhmbTJoQlM1a2RheHVSc0N5MkNucmFhdnkzYUFHby1Qb3R0TE56dHBMNUoyVnhTa01IU3liWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxNOWpHQlNpRUdaU1ZWSzBzd3EzM2I3cmZXdzd4aUNrMjlnbWJPZkNNbVVGYXRrX2VPUjJxcEt5ZUJha3lyOS1VODQtTmV5d3NFdU80ME01eFg5X2dWZ25GT0Vhdl9TbVJBZ1RkaEJBZHh3aXNpNEMweEJEM3NuUmxRLWMzQWdUOEFkUUlKbm1PR1FyWVNMSGppa3VOZ2JUQy1wTl9sdkRpT0xhdWNaclNBdmxycEZnTUU0dHJvVVdsbWRaeDc2V1ZHb3dNMmNucmpuTzRkdDRzaERIY093NW81MnpDM0diSHRTbkE?oc=5</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -8369,27 +8369,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Menos estudiantes, cierre de colegios y menor fuerza laboral: el efecto dominó que causaría la caída de los nacimientos en Colombia - ELTIEMPO.COM</t>
+          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOMWJRUzdtRlZyMGg3cnFZYVBRZzZQVGExREJVZGxOZk03d3IxbVZfREhIQmRIMTcwM0RhV0VITzl5MkdIbVNEd0ppLS1TUGpLVmF2dzJ6bTdyeU15Vms5SzlGU3MtZ0l2aUlWSzdTYk13OGxOVjQ3akNucUdmLV9yeXZjcjdYLVJyWnl5a25scDBxWnVRSlg5VFZ3TkVlS0pzU3ZXM2RZZTdrbjZ4Q2dub1FraTNwVzd5M0FObGo3dUEzYmlwdFd3T256anIweVZFUkt2VWFOeUN6SkFBQ1QxQ19GQkF4NE0yMHpvWUZTRVdjZ21BYnZlVkFBWnlwRElSeTB6M0xvVGXSAY4CQVVfeXFMTzJyUHA2bWVUTnc2WDBiUkJzWVdRWUNobktMNEQ1SVBnb0kxSFh1SlMzejA4VEhfRTEtRDBfb0N4dkVLbkZkMVVEakZOaENacG1vdDNVck15LVNCdU5IMUJ2b2pnV2RGd1JKMVBmemk0bGpHTTVMQlJ0LTE0Rmw5TjVDVVkyV3o3X0pveThGc283dzlDMnlWZXAzUkJhMUllRnF5bVpSSS16N0hPMGFhQjh3cVRVWFRLT1JxQ3JkaU8wX2ZwaUthalFqNkRITU5YdnU3LWZlaTBhSTJrd1FMNndPY3llbG1nSXJFWTJUVUpZTW5idVpNVVVwTU9qV1lqM3d5UDFrZjcwaTVmbE5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
+          <t>Menos estudiantes, cierre de colegios y menor fuerza laboral: el efecto dominó que causaría la caída de los nacimientos en Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxOMWJRUzdtRlZyMGg3cnFZYVBRZzZQVGExREJVZGxOZk03d3IxbVZfREhIQmRIMTcwM0RhV0VITzl5MkdIbVNEd0ppLS1TUGpLVmF2dzJ6bTdyeU15Vms5SzlGU3MtZ0l2aUlWSzdTYk13OGxOVjQ3akNucUdmLV9yeXZjcjdYLVJyWnl5a25scDBxWnVRSlg5VFZ3TkVlS0pzU3ZXM2RZZTdrbjZ4Q2dub1FraTNwVzd5M0FObGo3dUEzYmlwdFd3T256anIweVZFUkt2VWFOeUN6SkFBQ1QxQ19GQkF4NE0yMHpvWUZTRVdjZ21BYnZlVkFBWnlwRElSeTB6M0xvVGXSAY4CQVVfeXFMTzJyUHA2bWVUTnc2WDBiUkJzWVdRWUNobktMNEQ1SVBnb0kxSFh1SlMzejA4VEhfRTEtRDBfb0N4dkVLbkZkMVVEakZOaENacG1vdDNVck15LVNCdU5IMUJ2b2pnV2RGd1JKMVBmemk0bGpHTTVMQlJ0LTE0Rmw5TjVDVVkyV3o3X0pveThGc283dzlDMnlWZXAzUkJhMUllRnF5bVpSSS16N0hPMGFhQjh3cVRVWFRLT1JxQ3JkaU8wX2ZwaUthalFqNkRITU5YdnU3LWZlaTBhSTJrd1FMNndPY3llbG1nSXJFWTJUVUpZTW5idVpNVVVwTU9qV1lqM3d5UDFrZjcwaTVmbE5B?oc=5</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
+          <t>Día Internacional de la Educación 2026 celebra el poder de la juventud - UNESCO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRWU1YmM4clFjLXhocUloOFB3QWpFRVVrTWg1ajdkLWluRGEydUJ1VXo1cmU0djVzU01DU04yTmJGTm1BZ2VQaVdWTl9ITVFtVE91U1NEVnM3STdERkkxd3VBS3AtZXliVmdnNFFTNEp3WlJXcTdaTG5LX3NhMFdLU3NLNHZJTHRCVW5hLVlDLTRqakJZTS1POEcyOXpnWC12VVJPSS1ZZk9WSXowS0JqeGczUGNQTkFZYWRiQ3RKSk9RanJVR2FHRQ?oc=5</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -8541,12 +8541,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Día Internacional de la Educación 2026 celebra el poder de la juventud - UNESCO</t>
+          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRWU1YmM4clFjLXhocUloOFB3QWpFRVVrTWg1ajdkLWluRGEydUJ1VXo1cmU0djVzU01DU04yTmJGTm1BZ2VQaVdWTl9ITVFtVE91U1NEVnM3STdERkkxd3VBS3AtZXliVmdnNFFTNEp3WlJXcTdaTG5LX3NhMFdLU3NLNHZJTHRCVW5hLVlDLTRqakJZTS1POEcyOXpnWC12VVJPSS1ZZk9WSXowS0JqeGczUGNQTkFZYWRiQ3RKSk9RanJVR2FHRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU0gGGAkFVX3lxTE9kVTNSLWtRcmp3VzFBcXViWi1BSWVxdF9YaERoMFpoZkM5bFNjV1pBcVRqS1FRLXdlMTUtcjRYcVpveUhRNWFwQ0VDblBnZW1TME9STnhpWW9DanJvVXlqTVloLUU2ZTAtMENhU2lDV1hMLTYyNXJfU1htMHlmSzBkUnlGamd5cXlfOXlJV2ZmWUMzVUlKamlQa2VmZnVDVkcyR2pVZkx3VEk3aTFqYk51dk5paVhheURPQ0NQcVI0NkFYMXFwbml0bU85WmpINnNMUWpfZnVnbE1BNnRxQnozUUNnNGwtWXN3R1FBczNBZzVVeEQxSEZPeE5rMEd0Y3NVbVRiSHc?oc=5</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
+          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -8614,10 +8614,14 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU0gGGAkFVX3lxTE9kVTNSLWtRcmp3VzFBcXViWi1BSWVxdF9YaERoMFpoZkM5bFNjV1pBcVRqS1FRLXdlMTUtcjRYcVpveUhRNWFwQ0VDblBnZW1TME9STnhpWW9DanJvVXlqTVloLUU2ZTAtMENhU2lDV1hMLTYyNXJfU1htMHlmSzBkUnlGamd5cXlfOXlJV2ZmWUMzVUlKamlQa2VmZnVDVkcyR2pVZkx3VEk3aTFqYk51dk5paVhheURPQ0NQcVI0NkFYMXFwbml0bU85WmpINnNMUWpfZnVnbE1BNnRxQnozUUNnNGwtWXN3R1FBczNBZzVVeEQxSEZPeE5rMEd0Y3NVbVRiSHc?oc=5</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/vida</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8627,12 +8631,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Por qué tantas personas de 30 siguen actuando como adolescentes al elegir pareja, según expertos en comportamiento</t>
+          <t>En los últimos cinco años nivel nacional han cerrado las puertas más de 800 colegios - LaRepublica.co</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>LaRepublica.co</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8642,7 +8646,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8657,14 +8661,10 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/vida</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Afirman que la madurez emocional no llega sola con los años sino que se construye.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVkVKVlhVU1d2Tk9ITl84dEtTVHBMTF92RDJLa0JNTFJhRVljR2syeFBUQVJnV0EteVN5eG1zVVBuMldzOUVNSzZ4M0s3cWY2NXhTa05zNklVcVRIU0FOSGJSajVRM2Y0QzRLQk1yUHprM3NPRXA3dm9qQXVCNHRVa204OE82V3NBU0FLcF9HeU0yR0tQN0tWNmkxcjZBaHVsc05iZjg4Qy1tU1VSNmxPNHhrdXZJaV81YlBvc1JNalLSAcABQVVfeXFMTmtFbWJiYWI5d19VS21uUEx6Q09oeUs3bjFVdDBtbFdoZmNsZDBJUlZhdHhEUlFOMmVFSmdSbXZRX3c3YXFzVWtRcldzR00zU19PNWx5X053QUM3N2N6UVRwcVNtek1qeV95a0tsQ2Y1TGpnQWRDYXBGTDZLVlppd1BYeGh6LUlZVmtQQkw4dmhERlRza3UxZGg1VXdKRkEwT0R4eXZlN2tDdEdLUWxGQjE3ekh1eWR6Skg2eGNIM3lU?oc=5</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>En los últimos cinco años nivel nacional han cerrado las puertas más de 800 colegios - LaRepublica.co</t>
+          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>LaRepublica.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVkVKVlhVU1d2Tk9ITl84dEtTVHBMTF92RDJLa0JNTFJhRVljR2syeFBUQVJnV0EteVN5eG1zVVBuMldzOUVNSzZ4M0s3cWY2NXhTa05zNklVcVRIU0FOSGJSajVRM2Y0QzRLQk1yUHprM3NPRXA3dm9qQXVCNHRVa204OE82V3NBU0FLcF9HeU0yR0tQN0tWNmkxcjZBaHVsc05iZjg4Qy1tU1VSNmxPNHhrdXZJaV81YlBvc1JNalLSAcABQVVfeXFMTmtFbWJiYWI5d19VS21uUEx6Q09oeUs3bjFVdDBtbFdoZmNsZDBJUlZhdHhEUlFOMmVFSmdSbXZRX3c3YXFzVWtRcldzR00zU19PNWx5X053QUM3N2N6UVRwcVNtek1qeV95a0tsQ2Y1TGpnQWRDYXBGTDZLVlppd1BYeGh6LUlZVmtQQkw4dmhERlRza3UxZGg1VXdKRkEwT0R4eXZlN2tDdEdLUWxGQjE3ekh1eWR6Skg2eGNIM3lU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU?oc=5</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Esta es la nueva materia que llegará a todos los colegios públicos de Colombia: habrá más oportunidades de estudio en Europa - ELTIEMPO.COM</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -8747,10 +8747,14 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNSWNOd3ZJeEt2LXF1amNOVlZpNTVBOWtTcEtNX21aQ1RDWkRtblF1ekRGclhxSS1jVTZxVzRTai04WkJFbzc1MTVNeEZGV29FSG9xSEd2enpXS1ZuNFIzdkVYTmpQQUVkelhOYktRVWQ4RGl5TGRfVkNNMk80TXo2WnphZnBHYXo1Qk45aVpUaTBUTlllcnJBVDF5aC0yMC1WeDl5b1lLcDZGZUpWRWQwS3NJUDB1a1lYYUlTVkJ3RVJlMFdHYkhvQ0tvUzdacjNuRHUxRWo4QXBJMzgyTHA0Ti1tVjV3TFlPcno4NFlINEt1cFI4TWZneEs2ZUo2VlhU?oc=5</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8760,12 +8764,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Cambió el calendario en colegios en Colombia: esas son las nuevas fechas de vacaciones - La FM</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>La FM</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8780,7 +8784,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -8790,14 +8794,10 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPV3JMcmxKczJ0SUVEa0xWa016eEQ1NXhSTFpiYXRZOFpxMjlMMXpjOWx4dzZzVXJiRC00UmhGWVFrQjN2ZmFOU0lmWmUzSUtWOEJSX2VxVXRldW1HcXdBN2ZydVRpb09FNDEwbTJtYnRYQjM3eG55cTZaRW9GOURaRDJZUk5QTDVZS2hxeUVhemtkS2U3VnQtT09nc1dnRkhTU3NzMlpRS3ZYZkROWExud0szRG7SAbQBQVVfeXFMTXJvM0I0SEZhNldLZ3RRWmdhWnFwS0JicnhBOGZPTDZJdlJyR3ZLQ3BYTkNWZWhybzdxVEstR3duOXZFWHdVVWI1ZlAtYVl2T2hZejhfZXAwS2hPekMxbGp6X2UxUk05eWdUajNPWU80cENHRkFySDVkTmRBbExyLUFqMjZtYUEyQmVtTV9sU3RjU2RHeXFPQ3ZyTkJOalZDblRid05OTFRSNWc4dkc2Qm1HMkNy?oc=5</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Cambió el calendario en colegios en Colombia: esas son las nuevas fechas de vacaciones - La FM</t>
+          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>La FM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPV3JMcmxKczJ0SUVEa0xWa016eEQ1NXhSTFpiYXRZOFpxMjlMMXpjOWx4dzZzVXJiRC00UmhGWVFrQjN2ZmFOU0lmWmUzSUtWOEJSX2VxVXRldW1HcXdBN2ZydVRpb09FNDEwbTJtYnRYQjM3eG55cTZaRW9GOURaRDJZUk5QTDVZS2hxeUVhemtkS2U3VnQtT09nc1dnRkhTU3NzMlpRS3ZYZkROWExud0szRG7SAbQBQVVfeXFMTXJvM0I0SEZhNldLZ3RRWmdhWnFwS0JicnhBOGZPTDZJdlJyR3ZLQ3BYTkNWZWhybzdxVEstR3duOXZFWHdVVWI1ZlAtYVl2T2hZejhfZXAwS2hPekMxbGp6X2UxUk05eWdUajNPWU80cENHRkFySDVkTmRBbExyLUFqMjZtYUEyQmVtTV9sU3RjU2RHeXFPQ3ZyTkJOalZDblRid05OTFRSNWc4dkc2Qm1HMkNy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Jóvenes creen en democracia, pero ven barreras para incidir y participar: las claves de nueva encuesta de percepción de Cifras y Conceptos - ELTIEMPO.COM</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8865,22 +8865,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNVllVbkwzWi1PdVRWcmQ4VjJEd0lwREZXdnBNSHBFcDFEWnctSEtqZVVEVk9WNHZxQzZYSGxwOU1aSkhQX3dtLTRxZGxabzNfZlJtRWhrVTlGYnpoYkdqRFM4SE1CTmw1QTh0eEhfSXEyaF9wMVlUUU04aFR1VG1heGQ3cjdWZ2EtYm9GVTZyZzQxNUwwUTV1c3ZRNTJycmwzSjFIZHc4T25mM3JLUmUxd09FeHNIT0o5UWowMVJIX0NOZk81SmJxMGJqMWlpamE5UFlVS0ZwZExUNGRUVU9CbVJfRFgzUVdaRDRqMExnRjRjSmJLSmJoQUNzaFpKMDFtYXg5eEZ0WkYzM0RoUnk2NGdsTWZ1Z9IBmwJBVV95cUxPMEtpSWotNUdlNkNuSjl5U2x4YkhzTWNxeUlBZzk1UWNOaWZxQjhMenJvVVh0SHpBNjVNdWM4c2hWWVpWeVA1X2c2V2FLSHY5RFNGN05hMkFVOXBsdnlyUFFmTTJyeHRqY08tV2lQVDdQZUctOTlwV1d3N2JJRVlyU2thcmVzbmpsNXZsdzhFQjFkLWNIQmVUblNXNDVTZXV3eHN0M0ZOUmFYazBKWF9IdmVMVW9UTThDckZlbkVERy1RNGV5SmFySWFmMFVWSy1aNjd6Z2Q5RWsyTk1jU1lSdWhQWlc3R1NhZDdLY1RqTDBDeXRaX0kyN3RBeTloc0o2OFhRdXJTLWtibDRJS29ITzd4WEFJQXNVbVhR?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -8893,12 +8893,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Abierta convocatoria para estudiantes quienes recibirán $2 millones mensuales por ir a la universidad</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>icetex.gov.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8921,7 +8921,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+        </is>
+      </c>
       <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
@@ -8932,12 +8936,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
+          <t>Crisis en la educación privada de Bogotá: en lo que va del 2026 han cerrado 35 colegios - Portafolio.co</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Portafolio.co</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8947,22 +8951,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ29TeFBiMWZnaUctc2xlYmJhZ1hkcVZIc3A0WDFDTkpMR2R0ZlJzTlVBT0hKNjZweDJTZ2Z1WEFEcUZKYnpwS1hPZlNyTUpMU0hLOUpIc2NRVktESEotTFV4cjJwbzZnQWY3YlNVdXpRb0pET2VTck56Z1p5OEpUS2ljZWh4UVBCeDBSRXV3S2xERUxaekZMeDNXTDNUVXc5WmpfRktuXzd6UGNGeF9ZUU9NM1NuLUnSAbwBQVVfeXFMT2U4aTE3VGM2SFl3VXE3VlVrOHpYaGhNRFVzM2RwS0xBYkdDVE1nQ0RnbUdUc2FwRGRzdUtGdzA2MlNLZ1dZekhKMFZ2LVd2bm1GQnhWMzZtUkxkV2FBUFpjclhFaHZMSUp4QWhpVEstUHdqcGk5LXFvd0Z5dEJOS3FhXzg2aTcxX3dEY2Zvb2RpUXFlMmdtOTlmS3Jlbk9rX3FHWGkzYzNMWHIxNjlEUmpnUnpoN0t3cGxfMGU?oc=5</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -8975,12 +8979,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>80 adolescentes vinculadas a Bienestar Familiar reciben formación en salud menstrual - Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Colegios serán más estrictos en 2026: Eliminan la ley que amparaba a los estudiantes en esta situación - redmas.com.co</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8990,12 +8994,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -9005,7 +9009,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZllZb2c2OS12UW5RLU9YQWJyclk5dEtzdHhwNDFybVVnOTJ3LW5sTC0wM1NoTm9mNEN4eDIwYWFUTGFsTnYxQld0MHVtdGFYV0JWTVBaM3JiU3hhQkRMV0RxbWZwbENoNE1MaVUyZGYwd3RmOUJFVU41eUlMVG15a3BNWEZ5akdJWWVvcGtxTW9LdEtGUXE0ckVrSG5NYjBLaVRxTXgxaGp3dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNSGx6SGg2V3AxTDZ1SkRMemhiTXV6eVE2T1NudWQxRm8yU09lQmpucEMzdzhsVm80enc2SGZYN2ZWa2o4WmdaZWJ5WThNS2JwOFBSVnJ1TkdjRE10M2tkQk1zc3hJUE91d0ZNQXVCcVVFaUk2TEhsNGNFMDJwanVsM1R2Tm9KdG9kNVpVNWI3d244U1JWenRlcXBEVlRrWmtUclVZdWQ5SzRVMFNLbnJxT3libE5UQk1xSlBLYW9pS2cxb3hyVXdVVzExbFlKcWJsTkRzTGhGQjI4M3MzeU5wYzB2MkZZQdIB6wFBVV95cUxOaXVlcUFwUUNqbS1CTURNUGZrUktkZ1phUkxOYUswaF9GbkZZc3p4SGpaZ0FWOExhaWhadHowMHd6SUM5RUNNVGZZanJrMVd1VUoybG84elg0Z3cwcGdiYmJUVjZrZDd2TXcxMEF3YUNCbzNxd0l6QXpSUUZDV3NDczAwOU10RXcyVGVrVk9yczh1Q1FoVG0tRXY1cjFBNmg3VFlrRDZCWElFSTBJbGhjampvMnZCTDNidGljWC1BU2VFR0dqUVBkVkVMLVBINUZkMVQ1UXVnaFBpQzNiMTdtcjQ1Y1NUdmxweGZv?oc=5</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -9018,12 +9022,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Colombia lista para los Juegos de Invierno de la Juventud 2026 - EL INFORMADOR - Santa Marta, Colombia</t>
+          <t>Actividades en Bogotá para niños y adolescentes gratis en enero - Colombia.com</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>EL INFORMADOR - Santa Marta, Colombia</t>
+          <t>Colombia.com</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9038,17 +9042,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNT0x5eFk2VFI4TjZyS0I4Wk55RzNuZFl6R3lWTlNOWlVEVFNSUFp3d3hTeU1mUU9JN1hWdHgyYkloUE1xVGctblpGZVZsOHI4cVZLdlZmRnQtZklkOWsyaUlsM0lLRkRxZ2F6dTIzdmRyQ0UwQW82X0djWkpiRDBrUVFVYUt4ZkF4dS1VOWRkbjIwbXBIRERpcVBBcm9OLXlKVUswSHItY0hEYzF3dGw4ZVBFdjZHcmQ4YUJnYWo3OTU3OU12dEtOYVlOZVBCY1Z5Y1VSSzM5WmVpUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdVdPZUt4NUl4bDJxN1NGSkJoMlJmSGdickotNUVPdHlPN1czS3dXUEFnbEtUY2szR0drY3ZWZkxFcEVaOXFtUF9VNDlRcVNST0RycnlkSHp3YWJ0SGd6V0ZPVWs2TWt1UHBYQWI4ajNkQnYxNEhsOWo0YjB1a3NIQ3k5SXRCNDZHZkZ6Rm1hdDkxZFc2UlU5amp0bElHOEhjSl9pVFhqOS1hSlNOWHp5VEtn?oc=5</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -9061,12 +9065,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Armenia posesionó a los nuevos Consejeros Municipales de Juventud para el periodo 2026–2029 - Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alcaldía de Armenia</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9076,22 +9080,22 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMVA5RW15YWg0b1ZqdVltdnJETFVFcW82bjJ3TmJQUXRMM01uMFpJTUliTUVkczFXVm9kdGlZdnBlR3NTR1FWRGlOck5VOFZTTC1UaEFhQmozd0EzZllJamY2RHBKeXBsTGFTMWl6QUVzRHBqWDdXaTRkamxhQzRaUG9DSFpnQllQUUtaMFpIR0tJYTNmQmJTVnN2cDNiNGtmZUlHdVg0bi1lNTZrY2JfbmpOM24wTlNKTkxGNFhZU20waDAzLTdGNDRsSm1oSVI1N3QyTHlpazNlY2tYRzQwTGFYNA?oc=5</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -9104,12 +9108,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Actividades en Bogotá para niños y adolescentes gratis en enero - Colombia.com</t>
+          <t>Colombia lista para los Juegos de Invierno de la Juventud 2026 - EL INFORMADOR - Santa Marta, Colombia</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Colombia.com</t>
+          <t>EL INFORMADOR - Santa Marta, Colombia</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9124,17 +9128,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Santa Marta</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdVdPZUt4NUl4bDJxN1NGSkJoMlJmSGdickotNUVPdHlPN1czS3dXUEFnbEtUY2szR0drY3ZWZkxFcEVaOXFtUF9VNDlRcVNST0RycnlkSHp3YWJ0SGd6V0ZPVWs2TWt1UHBYQWI4ajNkQnYxNEhsOWo0YjB1a3NIQ3k5SXRCNDZHZkZ6Rm1hdDkxZFc2UlU5amp0bElHOEhjSl9pVFhqOS1hSlNOWHp5VEtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNT0x5eFk2VFI4TjZyS0I4Wk55RzNuZFl6R3lWTlNOWlVEVFNSUFp3d3hTeU1mUU9JN1hWdHgyYkloUE1xVGctblpGZVZsOHI4cVZLdlZmRnQtZklkOWsyaUlsM0lLRkRxZ2F6dTIzdmRyQ0UwQW82X0djWkpiRDBrUVFVYUt4ZkF4dS1VOWRkbjIwbXBIRERpcVBBcm9OLXlKVUswSHItY0hEYzF3dGw4ZVBFdjZHcmQ4YUJnYWo3OTU3OU12dEtOYVlOZVBCY1Z5Y1VSSzM5WmVpUQ?oc=5</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -9147,12 +9151,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Colegios serán más estrictos en 2026: Eliminan la ley que amparaba a los estudiantes en esta situación - redmas.com.co</t>
+          <t>Menor de edad colombiana tardó seis años para reencontrarse con su mamá en España, pero murió en grave accidente de tránsito</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9162,12 +9166,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -9177,7 +9181,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNSGx6SGg2V3AxTDZ1SkRMemhiTXV6eVE2T1NudWQxRm8yU09lQmpucEMzdzhsVm80enc2SGZYN2ZWa2o4WmdaZWJ5WThNS2JwOFBSVnJ1TkdjRE10M2tkQk1zc3hJUE91d0ZNQXVCcVVFaUk2TEhsNGNFMDJwanVsM1R2Tm9KdG9kNVpVNWI3d244U1JWenRlcXBEVlRrWmtUclVZdWQ5SzRVMFNLbnJxT3libE5UQk1xSlBLYW9pS2cxb3hyVXdVVzExbFlKcWJsTkRzTGhGQjI4M3MzeU5wYzB2MkZZQdIB6wFBVV95cUxOaXVlcUFwUUNqbS1CTURNUGZrUktkZ1phUkxOYUswaF9GbkZZc3p4SGpaZ0FWOExhaWhadHowMHd6SUM5RUNNVGZZanJrMVd1VUoybG84elg0Z3cwcGdiYmJUVjZrZDd2TXcxMEF3YUNCbzNxd0l6QXpSUUZDV3NDczAwOU10RXcyVGVrVk9yczh1Q1FoVG0tRXY1cjFBNmg3VFlrRDZCWElFSTBJbGhjampvMnZCTDNidGljWC1BU2VFR0dqUVBkVkVMLVBINUZkMVQ1UXVnaFBpQzNiMTdtcjQ1Y1NUdmxweGZv?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/15/menor-de-edad-colombiana-tardo-seis-anos-para-reencontrarse-con-su-mama-en-espana-pero-murio-en-grave-accidente-de-transito/</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -9190,12 +9194,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Armenia posesionó a los nuevos Consejeros Municipales de Juventud para el periodo 2026–2029 - Alcaldía de Armenia</t>
+          <t>Abierta convocatoria para estudiantes quienes recibirán $2 millones mensuales por ir a la universidad</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Alcaldía de Armenia</t>
+          <t>icetex.gov.co</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9205,12 +9209,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -9218,11 +9222,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPMVA5RW15YWg0b1ZqdVltdnJETFVFcW82bjJ3TmJQUXRMM01uMFpJTUliTUVkczFXVm9kdGlZdnBlR3NTR1FWRGlOck5VOFZTTC1UaEFhQmozd0EzZllJamY2RHBKeXBsTGFTMWl6QUVzRHBqWDdXaTRkamxhQzRaUG9DSFpnQllQUUtaMFpIR0tJYTNmQmJTVnN2cDNiNGtmZUlHdVg0bi1lNTZrY2JfbmpOM24wTlNKTkxGNFhZU20waDAzLTdGNDRsSm1oSVI1N3QyTHlpazNlY2tYRzQwTGFYNA?oc=5</t>
-        </is>
-      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Crisis en la educación privada de Bogotá: en lo que va del 2026 han cerrado 35 colegios - Portafolio.co</t>
+          <t>Jóvenes creen en democracia, pero ven barreras para incidir y participar: las claves de nueva encuesta de percepción de Cifras y Conceptos - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portafolio.co</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9248,22 +9248,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ29TeFBiMWZnaUctc2xlYmJhZ1hkcVZIc3A0WDFDTkpMR2R0ZlJzTlVBT0hKNjZweDJTZ2Z1WEFEcUZKYnpwS1hPZlNyTUpMU0hLOUpIc2NRVktESEotTFV4cjJwbzZnQWY3YlNVdXpRb0pET2VTck56Z1p5OEpUS2ljZWh4UVBCeDBSRXV3S2xERUxaekZMeDNXTDNUVXc5WmpfRktuXzd6UGNGeF9ZUU9NM1NuLUnSAbwBQVVfeXFMT2U4aTE3VGM2SFl3VXE3VlVrOHpYaGhNRFVzM2RwS0xBYkdDVE1nQ0RnbUdUc2FwRGRzdUtGdzA2MlNLZ1dZekhKMFZ2LVd2bm1GQnhWMzZtUkxkV2FBUFpjclhFaHZMSUp4QWhpVEstUHdqcGk5LXFvd0Z5dEJOS3FhXzg2aTcxX3dEY2Zvb2RpUXFlMmdtOTlmS3Jlbk9rX3FHWGkzYzNMWHIxNjlEUmpnUnpoN0t3cGxfMGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxNVllVbkwzWi1PdVRWcmQ4VjJEd0lwREZXdnBNSHBFcDFEWnctSEtqZVVEVk9WNHZxQzZYSGxwOU1aSkhQX3dtLTRxZGxabzNfZlJtRWhrVTlGYnpoYkdqRFM4SE1CTmw1QTh0eEhfSXEyaF9wMVlUUU04aFR1VG1heGQ3cjdWZ2EtYm9GVTZyZzQxNUwwUTV1c3ZRNTJycmwzSjFIZHc4T25mM3JLUmUxd09FeHNIT0o5UWowMVJIX0NOZk81SmJxMGJqMWlpamE5UFlVS0ZwZExUNGRUVU9CbVJfRFgzUVdaRDRqMExnRjRjSmJLSmJoQUNzaFpKMDFtYXg5eEZ0WkYzM0RoUnk2NGdsTWZ1Z9IBmwJBVV95cUxPMEtpSWotNUdlNkNuSjl5U2x4YkhzTWNxeUlBZzk1UWNOaWZxQjhMenJvVVh0SHpBNjVNdWM4c2hWWVpWeVA1X2c2V2FLSHY5RFNGN05hMkFVOXBsdnlyUFFmTTJyeHRqY08tV2lQVDdQZUctOTlwV1d3N2JJRVlyU2thcmVzbmpsNXZsdzhFQjFkLWNIQmVUblNXNDVTZXV3eHN0M0ZOUmFYazBKWF9IdmVMVW9UTThDckZlbkVERy1RNGV5SmFySWFmMFVWSy1aNjd6Z2Q5RWsyTk1jU1lSdWhQWlc3R1NhZDdLY1RqTDBDeXRaX0kyN3RBeTloc0o2OFhRdXJTLWtibDRJS29ITzd4WEFJQXNVbVhR?oc=5</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>80 adolescentes vinculadas a Bienestar Familiar reciben formación en salud menstrual - Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPZllZb2c2OS12UW5RLU9YQWJyclk5dEtzdHhwNDFybVVnOTJ3LW5sTC0wM1NoTm9mNEN4eDIwYWFUTGFsTnYxQld0MHVtdGFYV0JWTVBaM3JiU3hhQkRMV0RxbWZwbENoNE1MaVUyZGYwd3RmOUJFVU41eUlMVG15a3BNWEZ5akdJWWVvcGtxTW9LdEtGUXE0ckVrSG5NYjBLaVRxTXgxaGp3dw?oc=5</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -9319,12 +9319,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>La crisis de los colegios privados no se detiene: 35 instituciones cerraron en Bogotá para la vigencia 2026, ya van más de 400 en seis años - ELTIEMPO.COM</t>
+          <t>IDIPRON abre inscripciones a talleres gratuitos para niños y jóvenes en Bogotá - City Tv</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>City Tv</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSTN2aW1qSHhkQlJ2aHJNcHltQWxFaVlMZGk3MUNYdWk5YVRxdDc1WkNoQVQ0QjFUMHdERjNhd3kyOUNFbnJSVmdJd3psenZSS21Rb01DY1RLX2lTdkFqaHAzZ0RUekVFZU1zek1jRUotOWJ6T2dyQlN6QjFrRHY1Z0F2enRCUUtHS05TV3lMc1djQlJCeXlxdEhjWWloUGZhZjRMeDlseHVSUjAtS2NZWHdzY2czdm1USS13b213QXJtNHJPbnVldnhoNGNrNUk0bnZTTld4cy1KRUFoYVBnYVVxeWZoS2doUFRyMEtPRmlNZUhPLU43VmlFVUczelVoLXpYa0xYYkRSM3BWdnFPWk1sb9IBmAJBVV95cUxOWnZBMkpVRVNrOXFCcVAzczdmZEw4d1JrX1FvYkFXMXh6Y042dTdpQlhCVVQwLUNwZHF3YWVuU3ZidFl1eFM2Uk1HT2s3djZnWFYzMWl6NHlaYkpnRW9HSE9JWjBVWVpiY1FHbjVzLXBlbkNON09MYWVCenNVdXNPZXBlNE9BX2ZiZ1paendNOUVQeEp4SWZ6Umx3cXVCUGdyRFpmTWZ2M0Z2YlFIakNzc0lQelBoNVFWRmMzdnFJTmlGZVptMFFhSVNoZHkxM1lpQUIzUDZ0YTdJdVlOQlBrTWJhUExyblBRdklJMU5JV1g0ZmdCZ1pVWUx0YzJaUmdRX2tSYWNjWXZudnRJUGZ3cU9BX2VNVGxl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPcjJHT1RUMjN1bnRiNExKMlc0T2xKY3dGWTBCaWt2QW9YaEZnV19yMl9uai0xd3oxWFFkclZCb0RUSVZiRzNoQW9PYThKR2tBV0VwSzJyOU1Ya0Z3RE1LZ1N3MXhYY1JqWkRoU25IQ0RxQXJ3cE9ZMDdrcV9JTlY3X1hyZkNkN2lRMGhENGRFcmlrNHJqTnFoanhyZmJEeEFvWGV6bkJrM3dISGpHaG9DOW9JUWNCcFJIaGppa3cwTHB2MklnVk9HNWZwUk5Gek5pY1BwVldLb2VCUkhrc0dv0gHnAUFVX3lxTFBVcWZtM3c5N3VLVFZ0VFJhb0xSLTZLVjVWdE1qWW1Jd1B1bGtEUkphZnlTNjVCaVJUdHNlYngtRVhtempvSjM3V0puMTMzZGVGejhuZm9nVkxRR3QtQ25mRFVjQUNvbGFBbkZqdG9pQzFVSzhDUmtWODZMQWYzWjVZRjJzdjlxN2FLX3daclVDNnNsall0eGRrTzNIb00weHNHMDNwM0pBQk4wM0lTQm5yX3BQRUlfNm5YYVNxcTdOeTRCc09kMUpGSWFxR01yWDczLXFGaWw2d3FNbk92RjBWQ2tvdVBwbw?oc=5</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -9362,12 +9362,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Caldas: en este Pueblo Patrimonio de Colombia se posesionó el Consejo Municipal de Juventudes - La Patria</t>
+          <t>Los jóvenes creen en la democracia, pero ven retos en su funcionamiento en Colombia: estudio de Cifras y Conceptos - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>La Patria</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPMUptZlhIdEJLSnhzNmJURVRSemxxbGMwUHp1UDZYcTJtUWNIZ2U3UmNWZ2FJUEE3UkpYa3lWX0t5N1drTWFHck94bzJxSThDV1E3TTBFUi1qbFV6YzNjYUhTUUZkWmFDYW9lVldYV3Y1UUpxSmdkczhRbGxvdm5faDZESTl6Nm4xd2RBQXF0RTREZzc1NzlqMjY3enljNlVMMzJ4RFdLNHdqdC0tcWVrMmQwcV9rOE52ZWpNQ2dzMUh6dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPNjZKLUxUTlYxcm5RdlpaWk5mYjg4cmo4OGhFNkx1TWViYjZpV2VpN1JDdWgtckFxN05TVF9MbU9IVGQwNjI4WFlDajhjMjFEZl83SExwLVNoazBrcHVQMHhiVm51NGRnSkZBUGR1ejZibmJvRHhwbUMwVVQzUlFVZjRqWUh2ZzRVeDl1VFBfMFRYTlgxbmZzTjY5ODRPS0xPR25WSFF0aVpEQ0RVMnpaMVRGcjlyQVdYbkVQMjdNVm44QXR3TmQ0aC1WdkluVGF0WHNaY2RUXzRFbV9pTER4RjZoUFQxVUd3c1lZblM2cUZid3Bhc2FMOHhJc0RZVGZJbEF3YmowSUgySEHSAZACQVVfeXFMUGF5NGVXT2o3YWt3YmZwUG9GTXRpTFhYanhCR28wcWQ4LUJrd2kyRW43NTlZcklraXhCRlFFSXBxY0I0VFJoWllWZVBmNGczQW43UEZjSWl2d1hLWk15TlFNX1k3TUZGUkxMcy1PQWkyWFJWNTVvdHU1MHdhWWY3UkUwd0VRUklHTVkzQnFzaGtSZmdLWk9TblZhMmpWdU5Rc0thNXdzeHJKaGFqbEgzNUpYVzU0MEUtYkZjTEVtNElsYXV1MFY1djl2bDFMcGZ1VTBqaGYyV1UtMnZ1T2RVbGJFeHk0VDQyTGxmbnJLOU5ZVjhkZ2hBMlFxRFdkdkFLaXhBbUNqVEFVa21iNy1uang?oc=5</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Así inicia el calendario escolar 2026 - Ministerio de Educación Nacional</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVDhlQmp2WFB1ZVZYS1Y1TzZEWkxhcWlpLUFEMXd2eXdELVRzSkVZSW5BR19rMlJTenpPS2d1Z2l1V2Z5VWxlRmpJaW1wZjJOem9fVjNMSlVKTFhZQTc0R05PYkxzbjRoVFFSVWt4aE16Y0JDM3prbVFLUUNscFpiZzdIRWw4TGRlWE1qbUwwQnJ5TmxsaTRZbXlzcGNnblhEOTJXZzVudTNHdw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
+          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9463,22 +9463,22 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Estudio advierte sobre el uso de pantallas en menores de edad; ¿deben niños y adolescentes estar expuestos a ellas? - elpais.com.co</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>elpais.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNODE5UmhRcnUwTnJXb3B0aVNXMXRod0lXQmtTcWZoODdYVHJtTzVObER5UEpiSnBCbTJIaDJUN3lONnZEbkdNaXdvMmxvX3hNTVp5dGtrUld5NUVrZVBsampEenEyakpxQWJOYldrdUhPeWM5UVFUVk1IbDl3VEw5cEF1MnNRSnNrUnVkRnpTcDhiOUdUSzUwNGRjVHdKamsxeklBVzl0dzZSZ05FRFpuXzBySWVYY1o5YjBjbXg1MlRSUVlGaWtaeTQwM2ZrQzhIMHFlY2VFM0xVY0NiWFZ4Q2ZYczlVd1JGTHNadmZn0gHzAUFVX3lxTE1rQ2pPNXZMVm5rc0FVdExOa0xJVl96TEJIRmZTXzhfQ3hoY21NaTRHalNUM1JsMHMyZ1Q1bVNSNlpzdmkwS1BhWE54ZXlnVG9rdzlBczZaMlFfeUxBc0ZZQmQ5NUo0WThLVW9XNlZkeGxiOF80Rkh6S3hvV21yczVReWtOVlltNlV4dXl0QjhueDJKZ1lBaGpvTUJwQlc5NkV0OWp2UDc3VGgtYWpEcTdRb05WQkRsRWZ1WlhTcjBIeUJPM2ZHZDhSQndRM194T2dXeVRTSDBxRXBqLXhGd2g5UkVoQnlMeElsVUhuUm5jbS1VYw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -9534,12 +9534,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Confirman cambio académico en los colegios para 2026: Estudiantes estrenarán nueva asignatura por ley en Co... - redmas.com.co</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOOUFOa2tMOGxIRnZxRkV4d1NjaXRZdzZBc25VdGhZM002c2JLQVhORmZQRjVXeUNPbVNSaVFlRzBvb3FTc0RWajcwRkM0OGNyZi1ocHNuR2Q3dkRZbUIzSEdtSzBYcUNsNEF3Nzc0S1hOT2ZHMnZOTnZJdXgyQmIyWnhlNmdOZkU2alBTTnNhaWNnZGE4d2ltUDBOZGtZUFRRN0RGbXljUGRMLUZzbl9FdTBDXzk2di13Zk52MDR0T3I5QXlaNlo2bWNqalVtLWp4Ri1uNWZSNG5yVnJaalZiRDN0cFprNVpwOVdkRDVn0gHzAUFVX3lxTFBPb1BUb3RCTHdMbjhXcTdmUF9GSDVkUFJqd1JxZXhkR0w1cXRUUTl2NXVSN3dQOFRTWk80eEhudmN1bHJmT29HeFRMSWU0dlJnbkU1QkJpbkM5M2hmYW14c19JNTZ4dWV5eEFWcFBISXNYenlWN2ZFMVZLV19EUmVFNHBwQU9aeU5ORS1Oc0ItNElXV29MV3hjRzdVMHY5SmJSM2hPRmg0LTNheXBWRmJmcEdsa1ZMZEg4LXZtQmZBeml2QnRQS002RzQ4NmgtTjRRbHJ4QWpVcEhTMVdGdTNFTkVoSnhVVkpXWUhxaDR3VGQxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -9577,12 +9577,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IDIPRON abre inscripciones a talleres gratuitos para niños y jóvenes en Bogotá - City Tv</t>
+          <t>Confirman cambio académico en los colegios para 2026: Estudiantes estrenarán nueva asignatura por ley en Co... - redmas.com.co</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>City Tv</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9592,22 +9592,22 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPcjJHT1RUMjN1bnRiNExKMlc0T2xKY3dGWTBCaWt2QW9YaEZnV19yMl9uai0xd3oxWFFkclZCb0RUSVZiRzNoQW9PYThKR2tBV0VwSzJyOU1Ya0Z3RE1LZ1N3MXhYY1JqWkRoU25IQ0RxQXJ3cE9ZMDdrcV9JTlY3X1hyZkNkN2lRMGhENGRFcmlrNHJqTnFoanhyZmJEeEFvWGV6bkJrM3dISGpHaG9DOW9JUWNCcFJIaGppa3cwTHB2MklnVk9HNWZwUk5Gek5pY1BwVldLb2VCUkhrc0dv0gHnAUFVX3lxTFBVcWZtM3c5N3VLVFZ0VFJhb0xSLTZLVjVWdE1qWW1Jd1B1bGtEUkphZnlTNjVCaVJUdHNlYngtRVhtempvSjM3V0puMTMzZGVGejhuZm9nVkxRR3QtQ25mRFVjQUNvbGFBbkZqdG9pQzFVSzhDUmtWODZMQWYzWjVZRjJzdjlxN2FLX3daclVDNnNsall0eGRrTzNIb00weHNHMDNwM0pBQk4wM0lTQm5yX3BQRUlfNm5YYVNxcTdOeTRCc09kMUpGSWFxR01yWDczLXFGaWw2d3FNbk92RjBWQ2tvdVBwbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOOUFOa2tMOGxIRnZxRkV4d1NjaXRZdzZBc25VdGhZM002c2JLQVhORmZQRjVXeUNPbVNSaVFlRzBvb3FTc0RWajcwRkM0OGNyZi1ocHNuR2Q3dkRZbUIzSEdtSzBYcUNsNEF3Nzc0S1hOT2ZHMnZOTnZJdXgyQmIyWnhlNmdOZkU2alBTTnNhaWNnZGE4d2ltUDBOZGtZUFRRN0RGbXljUGRMLUZzbl9FdTBDXzk2di13Zk52MDR0T3I5QXlaNlo2bWNqalVtLWp4Ri1uNWZSNG5yVnJaalZiRDN0cFprNVpwOVdkRDVn0gHzAUFVX3lxTFBPb1BUb3RCTHdMbjhXcTdmUF9GSDVkUFJqd1JxZXhkR0w1cXRUUTl2NXVSN3dQOFRTWk80eEhudmN1bHJmT29HeFRMSWU0dlJnbkU1QkJpbkM5M2hmYW14c19JNTZ4dWV5eEFWcFBISXNYenlWN2ZFMVZLV19EUmVFNHBwQU9aeU5ORS1Oc0ItNElXV29MV3hjRzdVMHY5SmJSM2hPRmg0LTNheXBWRmJmcEdsa1ZMZEg4LXZtQmZBeml2QnRQS002RzQ4NmgtTjRRbHJ4QWpVcEhTMVdGdTNFTkVoSnhVVkpXWUhxaDR3VGQxQQ?oc=5</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -9620,12 +9620,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
+          <t>Estudio advierte sobre el uso de pantallas en menores de edad; ¿deben niños y adolescentes estar expuestos a ellas? - elpais.com.co</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>elpais.com.co</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNODE5UmhRcnUwTnJXb3B0aVNXMXRod0lXQmtTcWZoODdYVHJtTzVObER5UEpiSnBCbTJIaDJUN3lONnZEbkdNaXdvMmxvX3hNTVp5dGtrUld5NUVrZVBsampEenEyakpxQWJOYldrdUhPeWM5UVFUVk1IbDl3VEw5cEF1MnNRSnNrUnVkRnpTcDhiOUdUSzUwNGRjVHdKamsxeklBVzl0dzZSZ05FRFpuXzBySWVYY1o5YjBjbXg1MlRSUVlGaWtaeTQwM2ZrQzhIMHFlY2VFM0xVY0NiWFZ4Q2ZYczlVd1JGTHNadmZn0gHzAUFVX3lxTE1rQ2pPNXZMVm5rc0FVdExOa0xJVl96TEJIRmZTXzhfQ3hoY21NaTRHalNUM1JsMHMyZ1Q1bVNSNlpzdmkwS1BhWE54ZXlnVG9rdzlBczZaMlFfeUxBc0ZZQmQ5NUo0WThLVW9XNlZkeGxiOF80Rkh6S3hvV21yczVReWtOVlltNlV4dXl0QjhueDJKZ1lBaGpvTUJwQlc5NkV0OWp2UDc3VGgtYWpEcTdRb05WQkRsRWZ1WlhTcjBIeUJPM2ZHZDhSQndRM194T2dXeVRTSDBxRXBqLXhGd2g5UkVoQnlMeElsVUhuUm5jbS1VYw?oc=5</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -9706,12 +9706,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
+          <t>Así inicia el calendario escolar 2026 - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVDhlQmp2WFB1ZVZYS1Y1TzZEWkxhcWlpLUFEMXd2eXdELVRzSkVZSW5BR19rMlJTenpPS2d1Z2l1V2Z5VWxlRmpJaW1wZjJOem9fVjNMSlVKTFhZQTc0R05PYkxzbjRoVFFSVWt4aE16Y0JDM3prbVFLUUNscFpiZzdIRWw4TGRlWE1qbUwwQnJ5TmxsaTRZbXlzcGNnblhEOTJXZzVudTNHdw?oc=5</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>Caldas: en este Pueblo Patrimonio de Colombia se posesionó el Consejo Municipal de Juventudes - La Patria</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>La Patria</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPMUptZlhIdEJLSnhzNmJURVRSemxxbGMwUHp1UDZYcTJtUWNIZ2U3UmNWZ2FJUEE3UkpYa3lWX0t5N1drTWFHck94bzJxSThDV1E3TTBFUi1qbFV6YzNjYUhTUUZkWmFDYW9lVldYV3Y1UUpxSmdkczhRbGxvdm5faDZESTl6Nm4xd2RBQXF0RTREZzc1NzlqMjY3enljNlVMMzJ4RFdLNHdqdC0tcWVrMmQwcV9rOE52ZWpNQ2dzMUh6dw?oc=5</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Los jóvenes creen en la democracia, pero ven retos en su funcionamiento en Colombia: estudio de Cifras y Conceptos - ELTIEMPO.COM</t>
+          <t>La crisis de los colegios privados no se detiene: 35 instituciones cerraron en Bogotá para la vigencia 2026, ya van más de 400 en seis años - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9807,22 +9807,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPNjZKLUxUTlYxcm5RdlpaWk5mYjg4cmo4OGhFNkx1TWViYjZpV2VpN1JDdWgtckFxN05TVF9MbU9IVGQwNjI4WFlDajhjMjFEZl83SExwLVNoazBrcHVQMHhiVm51NGRnSkZBUGR1ejZibmJvRHhwbUMwVVQzUlFVZjRqWUh2ZzRVeDl1VFBfMFRYTlgxbmZzTjY5ODRPS0xPR25WSFF0aVpEQ0RVMnpaMVRGcjlyQVdYbkVQMjdNVm44QXR3TmQ0aC1WdkluVGF0WHNaY2RUXzRFbV9pTER4RjZoUFQxVUd3c1lZblM2cUZid3Bhc2FMOHhJc0RZVGZJbEF3YmowSUgySEHSAZACQVVfeXFMUGF5NGVXT2o3YWt3YmZwUG9GTXRpTFhYanhCR28wcWQ4LUJrd2kyRW43NTlZcklraXhCRlFFSXBxY0I0VFJoWllWZVBmNGczQW43UEZjSWl2d1hLWk15TlFNX1k3TUZGUkxMcy1PQWkyWFJWNTVvdHU1MHdhWWY3UkUwd0VRUklHTVkzQnFzaGtSZmdLWk9TblZhMmpWdU5Rc0thNXdzeHJKaGFqbEgzNUpYVzU0MEUtYkZjTEVtNElsYXV1MFY1djl2bDFMcGZ1VTBqaGYyV1UtMnZ1T2RVbGJFeHk0VDQyTGxmbnJLOU5ZVjhkZ2hBMlFxRFdkdkFLaXhBbUNqVEFVa21iNy1uang?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNSTN2aW1qSHhkQlJ2aHJNcHltQWxFaVlMZGk3MUNYdWk5YVRxdDc1WkNoQVQ0QjFUMHdERjNhd3kyOUNFbnJSVmdJd3psenZSS21Rb01DY1RLX2lTdkFqaHAzZ0RUekVFZU1zek1jRUotOWJ6T2dyQlN6QjFrRHY1Z0F2enRCUUtHS05TV3lMc1djQlJCeXlxdEhjWWloUGZhZjRMeDlseHVSUjAtS2NZWHdzY2czdm1USS13b213QXJtNHJPbnVldnhoNGNrNUk0bnZTTld4cy1KRUFoYVBnYVVxeWZoS2doUFRyMEtPRmlNZUhPLU43VmlFVUczelVoLXpYa0xYYkRSM3BWdnFPWk1sb9IBmAJBVV95cUxOWnZBMkpVRVNrOXFCcVAzczdmZEw4d1JrX1FvYkFXMXh6Y042dTdpQlhCVVQwLUNwZHF3YWVuU3ZidFl1eFM2Uk1HT2s3djZnWFYzMWl6NHlaYkpnRW9HSE9JWjBVWVpiY1FHbjVzLXBlbkNON09MYWVCenNVdXNPZXBlNE9BX2ZiZ1paendNOUVQeEp4SWZ6Umx3cXVCUGdyRFpmTWZ2M0Z2YlFIakNzc0lQelBoNVFWRmMzdnFJTmlGZVptMFFhSVNoZHkxM1lpQUIzUDZ0YTdJdVlOQlBrTWJhUExyblBRdklJMU5JV1g0ZmdCZ1pVWUx0YzJaUmdRX2tSYWNjWXZudnRJUGZ3cU9BX2VNVGxl?oc=5</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -9835,12 +9835,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -9850,25 +9850,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9878,12 +9882,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>La lista de útiles escolares que está prohibido pedir en los colegios de Colombia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -9898,7 +9902,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -9908,7 +9912,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQzdnLVlLd2xJOHFWaGxaMzE5UVFSUWNRSGotUU1QRTNnaGxjQV9CN3RxVzBvZGU5aUxrdGpiQ2hVTkpqMEVGS0xad0JwVWhVNDdiZWt1eF9OZVNqRE9RRHRFTGVmbmFPWDhNWVlHR0xjV2xsR2ZCd0JrcVNmaGdneWxibjJjdkhsMnNwWThGVlhiX0Jfanc1YVpZOUZqUUttZm9kbDlaNHEweHJpU3B1Y18xRzdieWd1enN3eHVEZ0lUbm5sLW1j0gHMAUFVX3lxTFB6djRKRmdOdXpUVDFzSWY1MUNpTlAya3VreEZfM196VENfYWhVZ1g3RUJveVlOY0ItV1RlellpRTJPaXJWdVdYdTFwRUtST2lCdlBTbVM2REFvYVpZODEyWm8zTGpkSXNESl9xdTI3OEdmbndpZjIyNmFudWFYTFozOWozTEdvWERVQmJTMUc5T2RDWU1lSDhSSk1iLXRiMTFoLVoxRDFwckRmXzRKcGF0SDNHd1I3MVpyOFNHc0ZVcjBmVFV1bnVXdXVJNQ?oc=5</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -9921,12 +9925,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PTIES: La apuesta del Gobierno Nacional para llevar educación superior digna a más de 27.000 jóvenes en las regiones más remotas de Colombia - Ministerio de Educación Nacional</t>
+          <t>La lista de útiles escolares que está prohibido pedir en los colegios de Colombia - ELTIEMPO.com</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>ELTIEMPO.com</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -9951,7 +9955,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQV190TVQ0UHhYOWIxUGNuYTdTaWNLbW5xWUtBVFMtUEl4cmUtNmlTYzQ1QnNVUElkUXZfSFJ2MlgybzVjcFNTbXdDX2FWbDV1cWZ5WnpLR1Q4MXZGNGttTDhLWTJtNXlkenc3X01sdUlXbEh5X2dwRzJ6Vk1rWWRlZXNEVVpPMHJTS05QM0NsdkZGVm9jUjd5VG1aekdjdG1abE9OVXFQZTdDakxvN2pka0tkNWFuQUpVS3pMZGZxMDFqcUJRdWVyaGF2Uk9DWERYREozQ19fS01tNzNhUzZBOXIyOVBfazFjak1wbjN1U2FjOTk2YmhrSzM2eW54Qi1lUFRtQkpCTHRJSDJvcUxLTUhSSjdUeFkwNlE2SmFZS1dfU3JaM1NtRi1GR0xfRU5RZFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQzdnLVlLd2xJOHFWaGxaMzE5UVFSUWNRSGotUU1QRTNnaGxjQV9CN3RxVzBvZGU5aUxrdGpiQ2hVTkpqMEVGS0xad0JwVWhVNDdiZWt1eF9OZVNqRE9RRHRFTGVmbmFPWDhNWVlHR0xjV2xsR2ZCd0JrcVNmaGdneWxibjJjdkhsMnNwWThGVlhiX0Jfanc1YVpZOUZqUUttZm9kbDlaNHEweHJpU3B1Y18xRzdieWd1enN3eHVEZ0lUbm5sLW1j?oc=5</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -9964,12 +9968,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Medellín tiene nuevo Consejo Distrital de Juventud: este martes se posesionaron sus 23 integrantes | El Colombiano - El Colombiano</t>
+          <t>PTIES: La apuesta del Gobierno Nacional para llevar educación superior digna a más de 27.000 jóvenes en las regiones más remotas de Colombia - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>El Colombiano</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9979,12 +9983,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9994,7 +9998,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUjhnNlN4LXZ6YjM1V2xra3dtSUhLTERUemk5YlI5QlNKR0R4NmZLWTRwZTFRNnB3ZzNNejZoWktZdnVHQnZBWjZuY1otQTNBeFg3cWRnLTBpeW5KU2FOcFZLODdsUVYwSTR3Nl85eklDVXowVWloSVRZeEpOTnkySl9jeThrdUNCQW1mXy0ycnNNRktaSHZ6cWlwVjRpSE5ESDdKb0hvQ25tdmlJdzNR0gG0AUFVX3lxTE5LZ1VUZm1rYUdOUUNXSnpHOFN6MjlxWHYzNjhkZnlYWXpUNFdhczNZRzlkTTltbmJNOS12b3RoV2lNVjhkZUtRbmtaVloxSWVlRUhCNnJ6N09iaElvbkNLQTdVYUp0cWMwZS1YMXdKX0toX1FxdFk4NlJKbkwwT1A3MXU3VDc3LUJnWDZhd0l6dDk0ME9Hb2xwQzhxZm5DM2ttU3F6ei1KYzEwZ3JRR0JRX1JFUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQV190TVQ0UHhYOWIxUGNuYTdTaWNLbW5xWUtBVFMtUEl4cmUtNmlTYzQ1QnNVUElkUXZfSFJ2MlgybzVjcFNTbXdDX2FWbDV1cWZ5WnpLR1Q4MXZGNGttTDhLWTJtNXlkenc3X01sdUlXbEh5X2dwRzJ6Vk1rWWRlZXNEVVpPMHJTS05QM0NsdkZGVm9jUjd5VG1aekdjdG1abE9OVXFQZTdDakxvN2pka0tkNWFuQUpVS3pMZGZxMDFqcUJRdWVyaGF2Uk9DWERYREozQ19fS01tNzNhUzZBOXIyOVBfazFjak1wbjN1U2FjOTk2YmhrSzM2eW54Qi1lUFRtQkpCTHRJSDJvcUxLTUhSSjdUeFkwNlE2SmFZS1dfU3JaM1NtRi1GR0xfRU5RZFE?oc=5</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -10007,12 +10011,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>La lista de útiles escolares que está prohibido pedir en los colegios de Colombia - ELTIEMPO.com</t>
+          <t>Medellín tiene nuevo Consejo Distrital de Juventud: este martes se posesionaron sus 23 integrantes | El Colombiano - El Colombiano</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ELTIEMPO.com</t>
+          <t>El Colombiano</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10022,12 +10026,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -10037,7 +10041,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQzdnLVlLd2xJOHFWaGxaMzE5UVFSUWNRSGotUU1QRTNnaGxjQV9CN3RxVzBvZGU5aUxrdGpiQ2hVTkpqMEVGS0xad0JwVWhVNDdiZWt1eF9OZVNqRE9RRHRFTGVmbmFPWDhNWVlHR0xjV2xsR2ZCd0JrcVNmaGdneWxibjJjdkhsMnNwWThGVlhiX0Jfanc1YVpZOUZqUUttZm9kbDlaNHEweHJpU3B1Y18xRzdieWd1enN3eHVEZ0lUbm5sLW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUjhnNlN4LXZ6YjM1V2xra3dtSUhLTERUemk5YlI5QlNKR0R4NmZLWTRwZTFRNnB3ZzNNejZoWktZdnVHQnZBWjZuY1otQTNBeFg3cWRnLTBpeW5KU2FOcFZLODdsUVYwSTR3Nl85eklDVXowVWloSVRZeEpOTnkySl9jeThrdUNCQW1mXy0ycnNNRktaSHZ6cWlwVjRpSE5ESDdKb0hvQ25tdmlJdzNR0gG0AUFVX3lxTE5LZ1VUZm1rYUdOUUNXSnpHOFN6MjlxWHYzNjhkZnlYWXpUNFdhczNZRzlkTTltbmJNOS12b3RoV2lNVjhkZUtRbmtaVloxSWVlRUhCNnJ6N09iaElvbkNLQTdVYUp0cWMwZS1YMXdKX0toX1FxdFk4NlJKbkwwT1A3MXU3VDc3LUJnWDZhd0l6dDk0ME9Hb2xwQzhxZm5DM2ttU3F6ei1KYzEwZ3JRR0JRX1JFUA?oc=5</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -10050,12 +10054,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>La lista de útiles escolares que está prohibido pedir en los colegios de Colombia - ELTIEMPO.COM</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10065,22 +10069,22 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOQzdnLVlLd2xJOHFWaGxaMzE5UVFSUWNRSGotUU1QRTNnaGxjQV9CN3RxVzBvZGU5aUxrdGpiQ2hVTkpqMEVGS0xad0JwVWhVNDdiZWt1eF9OZVNqRE9RRHRFTGVmbmFPWDhNWVlHR0xjV2xsR2ZCd0JrcVNmaGdneWxibjJjdkhsMnNwWThGVlhiX0Jfanc1YVpZOUZqUUttZm9kbDlaNHEweHJpU3B1Y18xRzdieWd1enN3eHVEZ0lUbm5sLW1j0gHMAUFVX3lxTFB6djRKRmdOdXpUVDFzSWY1MUNpTlAya3VreEZfM196VENfYWhVZ1g3RUJveVlOY0ItV1RlellpRTJPaXJWdVdYdTFwRUtST2lCdlBTbVM2REFvYVpZODEyWm8zTGpkSXNESl9xdTI3OEdmbndpZjIyNmFudWFYTFozOWozTEdvWERVQmJTMUc5T2RDWU1lSDhSSk1iLXRiMTFoLVoxRDFwckRmXzRKcGF0SDNHd1I3MVpyOFNHc0ZVcjBmVFV1bnVXdXVJNQ?oc=5</t>
+          <t>https://www.alertabogota.com/noticias/local</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -10093,12 +10097,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10108,7 +10112,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -10123,14 +10127,10 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>¿Cuándo empiezan las clases en los colegios de Bogotá para 2026?: Distrito confirmó la fecha - Caracol Radio</t>
+          <t>Petro refuerza su apoyo a los estudiantes de las universidades públicas con miras a las elecciones - EL PAÍS</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>EL PAÍS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -10633,17 +10633,17 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQMTE0ZkUxTS15Z254MWd4VWMxZzk3azFJQ0pUVTJjY0xTZVRpMHdVSUpOQ21pV1ZtTmRpaXpMczdoWkdyY0FrWGQ1QTIxd092Y0ZRYWFHTlc5U2w3bXFpRUtxR0p1MFJnU29IUEwxWVdZNVZXRDFGaC1xc1NwV21YcWJJdVdzNG9hc3FRcjVObGR5WXYwVGVXYW1qY3ZrVXBoc0RqVXlVVG1TamExREFyeG1XV2dKbnNyZUQ0M2RMZnVKZ9IB1gFBVV95cUxOU2JQQ2FtVEtoN2xUZk1yWUZlMmtmME9pQzdTSjhYSjBQNjVjenRfSnBrc2JTbHFsZUkwTUR6ZjRFa21vUkozeTlKM2dYR3hCc3JXZm15ZGx1ckhBOUdnY3JDVm1uTkxCanZqRGhhQ2s3SHZtem9OblE4bjVxRUg0SE1SWl8xcHJodF9PUHYwOGNYT1dBTlBubjRJX3ZkSDJTTDlyOGl1a09zdEViUnNvbVRMNG1NRllyVEtOMko1alVIQXc0ejQ2SlpISHBUYjNwdVNRMVl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNTGNKT1ZIVC1RXzM0MUt3T2prd20zVjVOaG45cEg2eHJiRTVYQnhPRTQwX1VlVEF1VmV6WVNuTWIwMXFzbEw2cC1tRzl2ME11YXh2QUdoSE41dlNzQlZDMXhWM3ByZE40R3lhMVVoLXJRQ0dENHJZcVBZeEtJbDExZFo0NkRoSTFZSm5XVkJrVmZkZ2RRU2VST1FvWVlwMm1QM21tSjNXNjJsdGxjTmZqSkk5d3dDMjhETzZFM2x1V3pGNnNUeWFGVVNBZWwwU2EtdVdnN0gyMlIzX0I3LVF3V2h4TE7SAfgBQVVfeXFMT0NMSnh2NDNyM2N6NkNvc2FRLVdYS2xHRnh6cGlSLUpWOTQyeUs5NkphOHhDMTFrT09uSDlETHoxbXFvYk45el84eGMzal9JbTExU0RjdXczcDRkcHNoR1YtZ1VyUUlnU0ljU3JwWFhIZXloeGI3bWhpOThQRjdJUTJ3QS16UXlLN3hrZHFRMFotTXhTQzhtNk1rQTZkQ0haR016U0JPVWM3RUFwb0JFSW1naEFtWUU4S0NSSXZWUjJjMjNWb1QzSWNpSkdSM1JYUGRjcXNRSjBZRzZWR3E2ekNEemxIalhqVWlZQ25acWEwdGU2OTlHRXM?oc=5</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -10656,12 +10656,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>¿Cuándo inician las clases en los colegios distritales de Bogotá este 2026? Fechas y más - Bogota.gov.co</t>
+          <t>Confirman cambio en las vacaciones de los colegios en 2026: Bogotá reajusta el descanso de los estudiantes - redmas.com.co</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZTVQT2p4UFNyUjFyYnV1M2xEMXgyQVpqZE9OazBzUjJ2bmw3T09zMGpGY0JxcXRaSGNCVkFGbEtsaEVrekk1dDF2VHFLT3UtYTF3WmFHd2hBTVVZYkZDSG10ZlNRQVBrd0ljSjRWSmI5VGkyMG1qMVpOZV9IY1FtNWpod0VKVklxR3loT0dOOFFXQU5iUlgxb04xUFlfNk9Xb1hjNkFlNmltQlRVdEc5LQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQb0NOTFo5Z0Z1V0ZCaHIxY0NiRHFwZWJHWVJaNGpWR0J0MUhFVTlIMlowdUVJWnNkTWdCSXQydm9kVTBvT2JLT1AzeVd2VTdxY1dVZzNFOXlTbXlBR1dzR3lfRG5fZzdRZUExbkU5bVlpU2pYRW9RWmNGWGZDMTA0S1p3UXNfdEsyQi1YS09oVGtnMVhxU0lueXdldW93aUwyaW5QNVJiT002dHZ0NzZkMmtQSWdBMUZRak1vSUdrakJtVHNTanI1RFVEeGJBdkxXcDdORDRzT3R5bHJaS1lrWlczaTBhczUyOFBVZ1VlOVVqUnFJdDl1ZmZ0djhFcHRLMUHSAYcCQVVfeXFMTXlGMTBtM3g4cnFEalRJNjA3SkxVOUhKRmlwWjhJTnFQOGtKRFdJNzhaSGcwS0czOEF4RmlBbHZYcF9wU2lsNVR1T2EtNUtsTVBmZlpYcTJLY2gxc3Y2Yk1XMXRFV1NLVU9nZDA2Rm1mWEVTUVZfSktaVy01WTc3Q2VXU09EbG1hZ3lhSUltVjUtXzAzZVpuZWpjMFNqX3lOUzNoVnltaVoxMnY4MGNfV0wzblE5Tk1GSXhfeFc3QzhLMVkzX2FsRUQtQnZYNEYtcVp0VTh6Yl93TEJNQ0RMMVlIUWp1Q3hrZ1hxaFJ6QlZQeVU1YmhwZHFiUE9BSVR4S1ZTbWNWSzA?oc=5</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Petro refuerza su apoyo a los estudiantes de las universidades públicas con miras a las elecciones - EL PAÍS</t>
+          <t>¿Cuándo inician las clases en los colegios distritales de Bogotá este 2026? Fechas y más - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>EL PAÍS</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -10719,17 +10719,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNTGNKT1ZIVC1RXzM0MUt3T2prd20zVjVOaG45cEg2eHJiRTVYQnhPRTQwX1VlVEF1VmV6WVNuTWIwMXFzbEw2cC1tRzl2ME11YXh2QUdoSE41dlNzQlZDMXhWM3ByZE40R3lhMVVoLXJRQ0dENHJZcVBZeEtJbDExZFo0NkRoSTFZSm5XVkJrVmZkZ2RRU2VST1FvWVlwMm1QM21tSjNXNjJsdGxjTmZqSkk5d3dDMjhETzZFM2x1V3pGNnNUeWFGVVNBZWwwU2EtdVdnN0gyMlIzX0I3LVF3V2h4TE7SAfgBQVVfeXFMT0NMSnh2NDNyM2N6NkNvc2FRLVdYS2xHRnh6cGlSLUpWOTQyeUs5NkphOHhDMTFrT09uSDlETHoxbXFvYk45el84eGMzal9JbTExU0RjdXczcDRkcHNoR1YtZ1VyUUlnU0ljU3JwWFhIZXloeGI3bWhpOThQRjdJUTJ3QS16UXlLN3hrZHFRMFotTXhTQzhtNk1rQTZkQ0haR016U0JPVWM3RUFwb0JFSW1naEFtWUU4S0NSSXZWUjJjMjNWb1QzSWNpSkdSM1JYUGRjcXNRSjBZRzZWR3E2ekNEemxIalhqVWlZQ25acWEwdGU2OTlHRXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOZTVQT2p4UFNyUjFyYnV1M2xEMXgyQVpqZE9OazBzUjJ2bmw3T09zMGpGY0JxcXRaSGNCVkFGbEtsaEVrekk1dDF2VHFLT3UtYTF3WmFHd2hBTVVZYkZDSG10ZlNRQVBrd0ljSjRWSmI5VGkyMG1qMVpOZV9IY1FtNWpod0VKVklxR3loT0dOOFFXQU5iUlgxb04xUFlfNk9Xb1hjNkFlNmltQlRVdEc5LQ?oc=5</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Confirman cambio en las vacaciones de los colegios en 2026: Bogotá reajusta el descanso de los estudiantes - redmas.com.co</t>
+          <t>¿Cuándo empiezan las clases en los colegios de Bogotá para 2026?: Distrito confirmó la fecha - Caracol Radio</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQb0NOTFo5Z0Z1V0ZCaHIxY0NiRHFwZWJHWVJaNGpWR0J0MUhFVTlIMlowdUVJWnNkTWdCSXQydm9kVTBvT2JLT1AzeVd2VTdxY1dVZzNFOXlTbXlBR1dzR3lfRG5fZzdRZUExbkU5bVlpU2pYRW9RWmNGWGZDMTA0S1p3UXNfdEsyQi1YS09oVGtnMVhxU0lueXdldW93aUwyaW5QNVJiT002dHZ0NzZkMmtQSWdBMUZRak1vSUdrakJtVHNTanI1RFVEeGJBdkxXcDdORDRzT3R5bHJaS1lrWlczaTBhczUyOFBVZ1VlOVVqUnFJdDl1ZmZ0djhFcHRLMUHSAYcCQVVfeXFMTXlGMTBtM3g4cnFEalRJNjA3SkxVOUhKRmlwWjhJTnFQOGtKRFdJNzhaSGcwS0czOEF4RmlBbHZYcF9wU2lsNVR1T2EtNUtsTVBmZlpYcTJLY2gxc3Y2Yk1XMXRFV1NLVU9nZDA2Rm1mWEVTUVZfSktaVy01WTc3Q2VXU09EbG1hZ3lhSUltVjUtXzAzZVpuZWpjMFNqX3lOUzNoVnltaVoxMnY4MGNfV0wzblE5Tk1GSXhfeFc3QzhLMVkzX2FsRUQtQnZYNEYtcVp0VTh6Yl93TEJNQ0RMMVlIUWp1Q3hrZ1hxaFJ6QlZQeVU1YmhwZHFiUE9BSVR4S1ZTbWNWSzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQMTE0ZkUxTS15Z254MWd4VWMxZzk3azFJQ0pUVTJjY0xTZVRpMHdVSUpOQ21pV1ZtTmRpaXpMczdoWkdyY0FrWGQ1QTIxd092Y0ZRYWFHTlc5U2w3bXFpRUtxR0p1MFJnU29IUEwxWVdZNVZXRDFGaC1xc1NwV21YcWJJdVdzNG9hc3FRcjVObGR5WXYwVGVXYW1qY3ZrVXBoc0RqVXlVVG1TamExREFyeG1XV2dKbnNyZUQ0M2RMZnVKZ9IB1gFBVV95cUxOU2JQQ2FtVEtoN2xUZk1yWUZlMmtmME9pQzdTSjhYSjBQNjVjenRfSnBrc2JTbHFsZUkwTUR6ZjRFa21vUkozeTlKM2dYR3hCc3JXZm15ZGx1ckhBOUdnY3JDVm1uTkxCanZqRGhhQ2s3SHZtem9OblE4bjVxRUg0SE1SWl8xcHJodF9PUHYwOGNYT1dBTlBubjRJX3ZkSDJTTDlyOGl1a09zdEViUnNvbVRMNG1NRllyVEtOMko1alVIQXc0ejQ2SlpISHBUYjNwdVNRMVl3?oc=5</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n0gHeAUFVX3lxTE5ELS1vYi1fLWZ3THVvOFJJNmZ0QjlxWXRDZ2FQSVh1bXZkM2V2d2d6dEg0WkRvd2xZM1NYdFh5RzZDbjh0Y0VSVlJFTGNFYW5ydmdYcmtxMnFIZ24ydEhYZUJBZDI1Qmpxc0pldFZreWpFblQyZEo3UFUzcFFfRk10VEN1WHAwcWg3MWNVLU1zSC1vY2pQREVWLUVMbzQ5cUdITEhOeGVSSFgxRGpFNFJ3UGhndmVVMWVIdU11RlZ3RUppWFR4dTJ3UXhLVE4ydThUaFhsMXFFRURsUHRVZw?oc=5</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -11000,12 +11000,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Estudiantes ganan la batalla: les pagarán $2 millones mensuales en sus prácticas desde 2026 si cumplen esta... - redmas.com.co</t>
+          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>redmas.com.co</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNN2FROTMzTUQ2cEpiMGhTeDdSbFNqajFoeV9hdy1KOWt1QTdia3A1QzNvbmJuYjJiUFJpSDNaWWRoVGEyMzZKcG1NZHZBOGxFa21WaE5mYUVPOWV5Qko0bkktU3Ezb1JwbjRLUUlwT0pjSkxxUVpZRktYTl9FdDFvZnp1TGhoNTExM1p5NEFDQWR5UEdQYVFoNFZ3YnRyZDUyRWg2VkR4RHNRM0VkS0FNWk1JZG5ydzI3SkZEbmdTczJNNmZHRFZjTERJVHA4aS1FOHFWb0NQVmZnZmgtUjJfTFhxRUx3TWVBUjJQMU5wb0w2ZjVTdHREUdIB_gFBVV95cUxOOVRnWEQwY2RpZkVWLUxFeGpwdElDRzAwNktMOWxYdThYR2l3Vm4yQVNfUVRfeDl3cDJqejNJNTVTYXh5UW9WdVlDbmd5aDFKYXEwVkZfc2JRVDRoZ004Qm5mSG55dHdSb3RKbjR6VWZPQmgzdGo1TmpUM3RucG9rUlVaZjN2dXZrZDZuenNFQWFNX3FJRmhpOWFzanUtY19xT3J3N1JVNkxpalB1NFR5cmFsZG5lTmQ1U0M3Vld4NEtxTHEzcVRmNnUzZGxkei1wZWxZazdVSGpZS3E4TUlsR3lHYThaWnlwVFJmTnpIVTZvY2xLZ1RoMDQyRmVlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -11043,12 +11043,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Cuándo es la semana de receso escolar en Colombia 2026: Fechas oficiales Ministerio de Educación - Caracol Radio</t>
+          <t>Cierran sus puertas: estos son los prestigiosos colegios de Colombia que ya no funcionarán en 2026 - Semana.com</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Semana.com</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n0gHeAUFVX3lxTE5ELS1vYi1fLWZ3THVvOFJJNmZ0QjlxWXRDZ2FQSVh1bXZkM2V2d2d6dEg0WkRvd2xZM1NYdFh5RzZDbjh0Y0VSVlJFTGNFYW5ydmdYcmtxMnFIZ24ydEhYZUJBZDI1Qmpxc0pldFZreWpFblQyZEo3UFUzcFFfRk10VEN1WHAwcWg3MWNVLU1zSC1vY2pQREVWLUVMbzQ5cUdITEhOeGVSSFgxRGpFNFJ3UGhndmVVMWVIdU11RlZ3RUppWFR4dTJ3UXhLVE4ydThUaFhsMXFFRURsUHRVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTVZGRXZlSDMzdUlmSHU1Z21OY2ZCM1pVVUR1OGoyTFpuXzVnZmIzaXg4bml1NlFrcGEyN0lTb1o1V0FYeTlaeWNtM0c5TW9IUVZBaDBLR053MVpiN1hXa3lDWWNub2ZDVzlhWUZkUDNkZWd2b09oMnhKWWRTVzlhdHBtOE1IaUVWNjNyellzUVdoM3h4X1lweVdrMmRLQUhFa1NtMi03NFRvcm9wemtuMTlHNURGLTBTanZpNkxzam9zT3FfbzVzVldXYVJrRXdQZFl0cVFRU3NDMEF3X2I2ctIB5gFBVV95cUxNdFowTkZuMEcyRGV5QXRtbFRCX1VpM19uWGs4dGFZUGpCUzNpNGxmTEFfVHdLREw0X3R4b2NyZHNuejNmMl9mUlR2QlFscFRyME9NUmpPZy1zQ2JZdmcyV0hnREl6UTBEdlVSUlBDNlVoeDNzSndNNms2ZUZrc0FUbzdKenBIampNNTJub3FzLWRSQlB1bkhIaE5sMnFYcGd2SlpHdngtOVJ4dEZid0VEMHV4MklTT0NBRVZONGtsaXBja0VZT3pCbXhYcXVpUG9XcjVpRDRKQWpCajA1c3Q1bUx2bGpWUQ?oc=5</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -11086,12 +11086,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Cierran sus puertas: estos son los prestigiosos colegios de Colombia que ya no funcionarán en 2026 - Semana.com</t>
+          <t>Estudiantes ganan la batalla: les pagarán $2 millones mensuales en sus prácticas desde 2026 si cumplen esta... - redmas.com.co</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Semana.com</t>
+          <t>redmas.com.co</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11101,12 +11101,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTVZGRXZlSDMzdUlmSHU1Z21OY2ZCM1pVVUR1OGoyTFpuXzVnZmIzaXg4bml1NlFrcGEyN0lTb1o1V0FYeTlaeWNtM0c5TW9IUVZBaDBLR053MVpiN1hXa3lDWWNub2ZDVzlhWUZkUDNkZWd2b09oMnhKWWRTVzlhdHBtOE1IaUVWNjNyellzUVdoM3h4X1lweVdrMmRLQUhFa1NtMi03NFRvcm9wemtuMTlHNURGLTBTanZpNkxzam9zT3FfbzVzVldXYVJrRXdQZFl0cVFRU3NDMEF3X2I2ctIB5gFBVV95cUxNdFowTkZuMEcyRGV5QXRtbFRCX1VpM19uWGs4dGFZUGpCUzNpNGxmTEFfVHdLREw0X3R4b2NyZHNuejNmMl9mUlR2QlFscFRyME9NUmpPZy1zQ2JZdmcyV0hnREl6UTBEdlVSUlBDNlVoeDNzSndNNms2ZUZrc0FUbzdKenBIampNNTJub3FzLWRSQlB1bkhIaE5sMnFYcGd2SlpHdngtOVJ4dEZid0VEMHV4MklTT0NBRVZONGtsaXBja0VZT3pCbXhYcXVpUG9XcjVpRDRKQWpCajA1c3Q1bUx2bGpWUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNN2FROTMzTUQ2cEpiMGhTeDdSbFNqajFoeV9hdy1KOWt1QTdia3A1QzNvbmJuYjJiUFJpSDNaWWRoVGEyMzZKcG1NZHZBOGxFa21WaE5mYUVPOWV5Qko0bkktU3Ezb1JwbjRLUUlwT0pjSkxxUVpZRktYTl9FdDFvZnp1TGhoNTExM1p5NEFDQWR5UEdQYVFoNFZ3YnRyZDUyRWg2VkR4RHNRM0VkS0FNWk1JZG5ydzI3SkZEbmdTczJNNmZHRFZjTERJVHA4aS1FOHFWb0NQVmZnZmgtUjJfTFhxRUx3TWVBUjJQMU5wb0w2ZjVTdHREUdIB_gFBVV95cUxOOVRnWEQwY2RpZkVWLUxFeGpwdElDRzAwNktMOWxYdThYR2l3Vm4yQVNfUVRfeDl3cDJqejNJNTVTYXh5UW9WdVlDbmd5aDFKYXEwVkZfc2JRVDRoZ004Qm5mSG55dHdSb3RKbjR6VWZPQmgzdGo1TmpUM3RucG9rUlVaZjN2dXZrZDZuenNFQWFNX3FJRmhpOWFzanUtY19xT3J3N1JVNkxpalB1NFR5cmFsZG5lTmQ1U0M3Vld4NEtxTHEzcVRmNnUzZGxkei1wZWxZazdVSGpZS3E4TUlsR3lHYThaWnlwVFJmTnpIVTZvY2xLZ1RoMDQyRmVlQQ?oc=5</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -11129,12 +11129,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
+          <t>Cuándo es la semana de receso escolar en Colombia 2026: Fechas oficiales Ministerio de Educación - Caracol Radio</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOY0ZfaTZjbHVyQlNmaUVoMWF5NHp6LThmSFMxVElnN2J6Tmt2alNHMTRiY21tNUl2MXRFU2F2NVVSVUI2cVE5cE10eXFnRmhvVVBvT0tMS3VMUm9hMWlUcUQ0S3Y5OUJDTWtydy16dXV6emRfNGRsUFJpM0tKQkNnUmhTLUhXMnRqMUUzcWVUd2pzdWVNZFNxaXljeXVKYmpIVTRIY2dXb1lfcU91aWVHWUI4WV9XNHE3YUtlbDVoME1ucERMVGo4OS1n?oc=5</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -11903,12 +11903,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
+          <t>Bogotá presenta el primer estudio sobre dinámicas de niños y jóvenes en condición de calle - Caracol Radio</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -11918,22 +11918,22 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcDl2Z1NjUWM5d3VaOUZWRjNWZld1QngyQWlmbGFnelB5ZU4tNGJISm5KXy1aN01uWERNaVQzUGJmSWJFeVNxSjVTLVhRYU92dEVia1F2TVhvQUxmdVdvd3BRLUZLLWdYNkg3eUNKd1NhTGlwZGpVazdZOW9OU2RBLXhYYk5qcUpmSm55QkxRem55MUxQYmZjVUJSSThyU01XbGQyTTlyQnU5cFJTNnVmNXpvMGY4ZGVjZGFzXzVhVXAzZ2PSAdcBQVVfeXFMTUJvMXgzWXo2cnlEaEtYNnFCN0xHb2ZrZlp0YS1fV0gzbl9PanE4RDFNLTNMN1FZcU9kak55S2M2OEd2d3ZmU2RPYjRZWDlmR3NmUWxDNEQ2am9jTlB2SzI3SG9KQ3c2NHU0OWxJYkRYdWRMUTh3ZEs4ZjgwTGdnanA2S1RxYmlxRFVmNnRKTGMxVWwzSzczRTd1ZFFEYVJWd3ljbmVKU1l0VjZnZ2QwbnN0SmozVEV0cTJzbC1yQ3g0SUthMEk1aDhzeF9MWENqRFgzbTNPYWM?oc=5</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Bogotá también abraza en Navidad a jóvenes vulnerables y en riesgo de calle - La FM</t>
+          <t>30 quemados con pólvora en el Valle del Cauca y no ha terminado diciembre: 12 de ellos son niños y adolescentes; piden a la población mayor conciencia - ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La FM</t>
+          <t>ELTIEMPO.COM</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -11966,17 +11966,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNOG5Za2d6dXAtQzZJMDZoYlhieUtZb3I0OXh4QlFIeWNoRkIwMGxlUmFCUkpjZ0FyeThvYVprUEFpQXpQc3hfOVJfcmZOdk81QlhCTGFSeVlieUstcDR2NkozUGlEUnJ1WHRrUVh2WFRZQklfR3ZxM19UWmlka3B1OG5xY2tKMkJONGJuVkhyeHh1RTdhbUJ1cktib9IBmwFBVV95cUxQVmRGQnY2UkxUaTI2OTNUNzdOSTNoX1FmUE82azZ5c21GdjZHcUU5dEh1SVFDVTJ4M24tM3pfbUVEVUxTUEhRblFYTS1oenhXMU9SYm1GS2dHN25yQi1CeVlPcnoxdU9ocF80QzN1clQzcEJKS0JHc3d5dllCdVlmWE5CQ2c2Qk9na1hianI1ekNaSXQtSjB3X2padw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOZGZFRWYzbUs0eWpFUVdsRnUtMXNTVmpIR0hlcU9FbXcyQkxIek92Qk02TVlMNGgyeUxBRkkycHpVeHBwREZvZlhJRXUteWl5aFc3X1dSMjlpbmJwLUtsN0FQR2FkbzVVaVRQNHBpdjNfUWhQaUIycXZmUUN5N1kxbnNQY1BqbWZmOWU2YjAzUnRQNkF3eUJVUEg3TlRTd1F5WWZHVkZaVnhpNW1hSl9SbEpBR1RweEVtSFM0QWotcEJ3aHotT1pGTTBXbDhrOEdHLXRLd2hQcEV4aXQtQ2lULVNKQ0xNaXF0ZkktOEZUaVpyczRoZ3ZuZEtKc3F2bW15eWpCall6WVRGUTBpRHNxWHpOZEtJSTc1bk5pOV9HRFHSAaYCQVVfeXFMTnFJd1RaMUdoeDcydmdqWXRFSmFzRUd0b2FaUHFMVld4VDlyQkVRemtUVFZTVEVoWHdyRHpILXpFU0VVeklITTVMVGx1dElFYmY1WXFEX0NrN29zMDcxcTJfMFExMHVxV0ZfUE93cGQ3QW5jemNaT2VlS2MwME1DVTNnR0NwbWdPaDZQRDQxelBMUXZhREc1aG1DQ09BMkRFR3MwanZiWThJVlExUkhmMmlDVnhTTnI5N3RpUDlFanBsblJ3NktFVVR4QXV1WWo4NUNFaHUxNkU1VXgyMmIwTmd4SXpGSFQzejluLXRPYTdPV2JkN2NMWkNLUjZNOWdyU0JJTzN2WmZUeHM2WUN4aWR2TU1LT2tvbjVHRkNpM05Eb1hEaldB?oc=5</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -11989,12 +11989,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Colombia fortalece la respuesta institucional frente a la niñez y adolescencia migrante - Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Más de 64.000 estudiantes se matricularon en programas en línea - Noticias UNAD</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+          <t>Noticias UNAD</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcl8yMC0tR0ZJZXk3NW9tdGs1TTFMTXQ4Z3pkamhhZDFmbURaTWRWc3dvMXhLTUF1WlJaQ25kZmF5eU4wQUNuMy1OQ1FKM3NFOFZrblZKMzlxNWowSjd2a2EySTZsVzNEWTNHZmtqd3ZBU2ozMFFEZ29LdF8wb0Nvb2UzZzQyNzFWdlBwVTZ4RF80cmxwd2NoZVdXNDhlOGxVMENaSnA1T0gzRFJrOE1nRFJaekZ6allTdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNOHZRdHo4NTlxNUgtRl95X2V2MGJBSDQ2RXlncFQyb1FET1o2UV83MmtZc2ZMRG41aXNCeWxiNUVhWnJ2ajY4WDRzb25OWm5ZcU0xWlJKN2Q2VnZlTUprVzh5QWJNb2xaUnByMmFLN1V3bkpQLU9ZbGVsQUtvUWFSbERMek81aEhPMFZzdXZ3dElzLWQxcW9kRi1xTWRnN0pKSzBKNEw2aUVMaElQZHBHcVh3?oc=5</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -12032,12 +12032,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Bogotá presenta el primer estudio sobre dinámicas de niños y jóvenes en condición de calle - Caracol Radio</t>
+          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12047,22 +12047,22 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPcDl2Z1NjUWM5d3VaOUZWRjNWZld1QngyQWlmbGFnelB5ZU4tNGJISm5KXy1aN01uWERNaVQzUGJmSWJFeVNxSjVTLVhRYU92dEVia1F2TVhvQUxmdVdvd3BRLUZLLWdYNkg3eUNKd1NhTGlwZGpVazdZOW9OU2RBLXhYYk5qcUpmSm55QkxRem55MUxQYmZjVUJSSThyU01XbGQyTTlyQnU5cFJTNnVmNXpvMGY4ZGVjZGFzXzVhVXAzZ2PSAdcBQVVfeXFMTUJvMXgzWXo2cnlEaEtYNnFCN0xHb2ZrZlp0YS1fV0gzbl9PanE4RDFNLTNMN1FZcU9kak55S2M2OEd2d3ZmU2RPYjRZWDlmR3NmUWxDNEQ2am9jTlB2SzI3SG9KQ3c2NHU0OWxJYkRYdWRMUTh3ZEs4ZjgwTGdnanA2S1RxYmlxRFVmNnRKTGMxVWwzSzczRTd1ZFFEYVJWd3ljbmVKU1l0VjZnZ2QwbnN0SmozVEV0cTJzbC1yQ3g0SUthMEk1aDhzeF9MWENqRFgzbTNPYWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -12075,12 +12075,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Más de 64.000 estudiantes se matricularon en programas en línea - Noticias UNAD</t>
+          <t>Colombia fortalece la respuesta institucional frente a la niñez y adolescencia migrante - Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Noticias UNAD</t>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNOHZRdHo4NTlxNUgtRl95X2V2MGJBSDQ2RXlncFQyb1FET1o2UV83MmtZc2ZMRG41aXNCeWxiNUVhWnJ2ajY4WDRzb25OWm5ZcU0xWlJKN2Q2VnZlTUprVzh5QWJNb2xaUnByMmFLN1V3bkpQLU9ZbGVsQUtvUWFSbERMek81aEhPMFZzdXZ3dElzLWQxcW9kRi1xTWRnN0pKSzBKNEw2aUVMaElQZHBHcVh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNcl8yMC0tR0ZJZXk3NW9tdGs1TTFMTXQ4Z3pkamhhZDFmbURaTWRWc3dvMXhLTUF1WlJaQ25kZmF5eU4wQUNuMy1OQ1FKM3NFOFZrblZKMzlxNWowSjd2a2EySTZsVzNEWTNHZmtqd3ZBU2ozMFFEZ29LdF8wb0Nvb2UzZzQyNzFWdlBwVTZ4RF80cmxwd2NoZVdXNDhlOGxVMENaSnA1T0gzRFJrOE1nRFJaekZ6allTdnc?oc=5</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -12118,12 +12118,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>30 quemados con pólvora en el Valle del Cauca y no ha terminado diciembre: 12 de ellos son niños y adolescentes; piden a la población mayor conciencia - ELTIEMPO.COM</t>
+          <t>Bogotá también abraza en Navidad a jóvenes vulnerables y en riesgo de calle - La FM</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ELTIEMPO.COM</t>
+          <t>La FM</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12138,17 +12138,17 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOZGZFRWYzbUs0eWpFUVdsRnUtMXNTVmpIR0hlcU9FbXcyQkxIek92Qk02TVlMNGgyeUxBRkkycHpVeHBwREZvZlhJRXUteWl5aFc3X1dSMjlpbmJwLUtsN0FQR2FkbzVVaVRQNHBpdjNfUWhQaUIycXZmUUN5N1kxbnNQY1BqbWZmOWU2YjAzUnRQNkF3eUJVUEg3TlRTd1F5WWZHVkZaVnhpNW1hSl9SbEpBR1RweEVtSFM0QWotcEJ3aHotT1pGTTBXbDhrOEdHLXRLd2hQcEV4aXQtQ2lULVNKQ0xNaXF0ZkktOEZUaVpyczRoZ3ZuZEtKc3F2bW15eWpCall6WVRGUTBpRHNxWHpOZEtJSTc1bk5pOV9HRFHSAaYCQVVfeXFMTnFJd1RaMUdoeDcydmdqWXRFSmFzRUd0b2FaUHFMVld4VDlyQkVRemtUVFZTVEVoWHdyRHpILXpFU0VVeklITTVMVGx1dElFYmY1WXFEX0NrN29zMDcxcTJfMFExMHVxV0ZfUE93cGQ3QW5jemNaT2VlS2MwME1DVTNnR0NwbWdPaDZQRDQxelBMUXZhREc1aG1DQ09BMkRFR3MwanZiWThJVlExUkhmMmlDVnhTTnI5N3RpUDlFanBsblJ3NktFVVR4QXV1WWo4NUNFaHUxNkU1VXgyMmIwTmd4SXpGSFQzejluLXRPYTdPV2JkN2NMWkNLUjZNOWdyU0JJTzN2WmZUeHM2WUN4aWR2TU1LT2tvbjVHRkNpM05Eb1hEaldB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNOG5Za2d6dXAtQzZJMDZoYlhieUtZb3I0OXh4QlFIeWNoRkIwMGxlUmFCUkpjZ0FyeThvYVprUEFpQXpQc3hfOVJfcmZOdk81QlhCTGFSeVlieUstcDR2NkozUGlEUnJ1WHRrUVh2WFRZQklfR3ZxM19UWmlka3B1OG5xY2tKMkJONGJuVkhyeHh1RTdhbUJ1cktib9IBmwFBVV95cUxQVmRGQnY2UkxUaTI2OTNUNzdOSTNoX1FmUE82azZ5c21GdjZHcUU5dEh1SVFDVTJ4M24tM3pfbUVEVUxTUEhRblFYTS1oenhXMU9SYm1GS2dHN25yQi1CeVlPcnoxdU9ocF80QzN1clQzcEJKS0JHc3d5dllCdVlmWE5CQ2c2Qk9na1hianI1ekNaSXQtSjB3X2padw?oc=5</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Colombia conmemora una década de la Resolución 2250 con un diálogo nacional sobre juventudes, paz y seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>IDIPRON alerta sobre niños y jóvenes en riesgo de habitar calle en Bogotá - City Tv</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>City Tv</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12176,22 +12176,22 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTjN2Wkl1aXB1Wi1DX25OQnZ6amUwVGhLenJTU0VQZkpwZW5zVUxwbEFZZFI4bG4yMS1Qa2J6MWtaYjRLODBfSVNaNktKbWljNVRMSU1uckx2ZXhyVWZ1QlJmeWVvcjVLQWE5cC1lclVkcDNFMlBnMWk1dFF3VVdEaW91ZEFGdG1JU2tRcHk3VGtnOER4MDRjRWQwUzlRUXBRTC10WGg3VkRfcHlVSkFvTUxyekwwMVRVdjRlQ3kzd2tZd2EwZGVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdEpCWHhRQ0JwdHNjV1BoWnNrWk4xWnFFbUQ0QzY2dU1XZk5TWHNyVk9NTlJlaVZ2MTlFVDk3MzNVWHFxWUFZQ3A0UVZHYzhPWUROMi0xWE5OOHpLZEhIVThRalhrOEN1MEE3U2RVRV94bDJpbjRiaUdBbWtfWnlaZ3RydVFtQTdQM3RVSE1qVWRoX0tXanBqQlNqX3RrWVVDMmpzc05JdmlJblFhSTZrazNKb0ltVEh6bGhudjlWQ1VZcjlRZllSWHBGaW01Nmd2dEdTelNRN3g?oc=5</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -12204,12 +12204,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Colombia y Alemania se unen para que más estudiantes aprendan alemán en los colegios públicos - Ministerio de Educación Nacional</t>
+          <t>El mapa de riesgo de la niñez: estudio del Idipron revela la grave situación de los menores en contexto de calle en Bogotá - Semana.com</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ministerio de Educación Nacional</t>
+          <t>Semana.com</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12219,22 +12219,22 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOdDBneDZDSVFGTEdLQVVyWWJrazBhb2R3ZzZWb051Rkd0MjhKWU5MWFdCVVhNV1JVMlczeDl5elhqLTl5Y19aczFZNmNrV2xKMFdjV0NTWE1RMHplTU9PbzJDWXd4TkNjX0ZrQ2o2ZXRSYVRJT3RKZU1xUG5odGFjYm1BeXJfSkF5WDB1SEZLRWJjSzdKemRXbWFVWGZsaHVONXFkM0RPSWZ0VmRRN2NwenoxRUNrOFhPbmExeUVrUXRXczVfem1iaXdjSTBIR0FoUFpRYUswN3ZFYUlGNFpJZXp1UjJ3bUt0UEVuNnEtSm5sVzFt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNVmlPaF9SMDVfSXIxa05XNjBTd0NscTdOYTh4SEtlRU9QZGItVjN3S0Uza3BCbklvdzd3YlYxeHdGWVVIWXpxc1AzLVF4TzVzUlV1WlVjNjhvQnAwUkRJaURBZ2FqeDhpb0Z5d2d6bVN1Y3hNVE5IakpNUk83X1FLVUJTdG5MbkZHaWJCLXlfQ3pWMkVrUi1zdUk0Tkp6SDZTVDVvUUVLY1FoOEhnU1JieXplX1B1eDJ1VTZRMjZoNlZGUXVtU0VRZTV5eFE4S25yUXEtVTUwb3pTVlo3V045bjNvdENRaWlJWllpMTFjTnVCMVBSdlE0Z1gtU3pBRk1scWhCaU1PRdIBjAJBVV95cUxPc1E4TmdZZzgyZU5xVUZoeHI3eE03YUc3b2RKNzk1M0w2YXE1UVl1a0ttcWZ2WEh1bzdGU3czNmNNbXc5bnZHX2NhWWY4b1NQVTNfV2ktX2Y5TE5uVHp5VnBneWlMQXhQR0ZoUWs1Z2xBU25FNW5xZFlMQ1FGQWk2QVVud2w4NkU5N2ZNOTVfUGptaVkzR0hYUEhjVHUzN2ZuY0Nkdmo2NDc5Y05zVjcxU1liTU1aRjIzeXB6ZkJabHZTNko5ZXpxY1RoNWdjWGJER05HSmdyclJKYVJUOXAtSlRoU21qbU5lQkxVZEJYTUtJS252Q000bVJzVEFuWGtGMEhKWm9Pd2JCVjk3?oc=5</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -12247,12 +12247,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Barranquilla será sede de la Asamblea Nacional de Juventudes 2025 desde este viernes - ELHERALDO.CO</t>
+          <t>Bogotá presenta por primera vez un estudio Georreferenciado de los Contextos de Calle de la Niñez y la Adolescencia - Bogota.gov.co</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ELHERALDO.CO</t>
+          <t>Bogota.gov.co</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12267,17 +12267,17 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPZnFRNm1qalphMGhIaGdYT0hVWUFDUlZmbENKeGd2ZkkyaHNkRzlXU1ZleWtsamdoNzdZRFkxWXpwTU04RFQ0VWZScUlxWkFMcklPVTJEVEZ2UDhMNVdUdTVOQl8tdF9NTlZVYzA4YmFWbkpCNV9Xdkpod2FvcW44cEcxTUJPWlBCT3lqQ3VKZUpUZ3pkVG90a1U5bmpaYmoxc1lsRlVQNUt5ZFlNNnhiUnMwR2xITm94Ym5LXzJLVWJHazRtN1FPd2xLWdIB5gFBVV95cUxORGdBSHFILTcyZm5VVTVEOFFsQzB5bTV4aUdWT280QXUwREctNC05OG1qbE5oazJQZ3N1NENlM0J0Y1hwSFYyN1UyaU15dTk5Ty0wVTdJNmQ0dDYtTlhnYk9pMTRRRlRpYmw1d3Y5Z2lmWm9tR1pUMTAtZWNhQ244SVBPMm1DLXVmQTZvQ1U1ejkyRHlqU2hOLWxfeGFfaXZJbUQ2N2tEbmplSXhkYmxqUUdDQWYwdGNYVVFBN1JyZm5MMTJRTFlmNHhxajg4UGxnUTNySDNrWUJmaXNqUGJhdkFIRFY0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPajQ0NUdTQzVVQ21yQTBXYjhlc1o3NDA3aXRMaEhIWHVPN1ZOQVN5UHZ4OU1Ma1RGdlVlU3VkczhiVHkxbEJPdUxKeHY5RUgzQ0NNTlZMNkJjSl9oeVBQREZ3ek02QXd6UlhDeE9NMDlJdEJMb3ljclhaeEZVTEhDOEg0Y3hSdU9hUWlFaXlmbXJKWGFXQXNxS0k1Z0tlanBHZjlNY2h4T0JHYU5ObXh3TUdOU0ZkMkplNTZn?oc=5</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Bogotá presenta por primera vez un estudio Georreferenciado de los Contextos de Calle de la Niñez y la Adolescencia - Bogota.gov.co</t>
+          <t>Barranquilla será sede de la Asamblea Nacional de Juventudes 2025 desde este viernes - ELHERALDO.CO</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bogota.gov.co</t>
+          <t>ELHERALDO.CO</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -12353,17 +12353,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPajQ0NUdTQzVVQ21yQTBXYjhlc1o3NDA3aXRMaEhIWHVPN1ZOQVN5UHZ4OU1Ma1RGdlVlU3VkczhiVHkxbEJPdUxKeHY5RUgzQ0NNTlZMNkJjSl9oeVBQREZ3ek02QXd6UlhDeE9NMDlJdEJMb3ljclhaeEZVTEhDOEg0Y3hSdU9hUWlFaXlmbXJKWGFXQXNxS0k1Z0tlanBHZjlNY2h4T0JHYU5ObXh3TUdOU0ZkMkplNTZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPZnFRNm1qalphMGhIaGdYT0hVWUFDUlZmbENKeGd2ZkkyaHNkRzlXU1ZleWtsamdoNzdZRFkxWXpwTU04RFQ0VWZScUlxWkFMcklPVTJEVEZ2UDhMNVdUdTVOQl8tdF9NTlZVYzA4YmFWbkpCNV9Xdkpod2FvcW44cEcxTUJPWlBCT3lqQ3VKZUpUZ3pkVG90a1U5bmpaYmoxc1lsRlVQNUt5ZFlNNnhiUnMwR2xITm94Ym5LXzJLVWJHazRtN1FPd2xLWdIB5gFBVV95cUxORGdBSHFILTcyZm5VVTVEOFFsQzB5bTV4aUdWT280QXUwREctNC05OG1qbE5oazJQZ3N1NENlM0J0Y1hwSFYyN1UyaU15dTk5Ty0wVTdJNmQ0dDYtTlhnYk9pMTRRRlRpYmw1d3Y5Z2lmWm9tR1pUMTAtZWNhQ244SVBPMm1DLXVmQTZvQ1U1ejkyRHlqU2hOLWxfeGFfaXZJbUQ2N2tEbmplSXhkYmxqUUdDQWYwdGNYVVFBN1JyZm5MMTJRTFlmNHhxajg4UGxnUTNySDNrWUJmaXNqUGJhdkFIRFY0QQ?oc=5</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -12376,12 +12376,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>El mapa de riesgo de la niñez: estudio del Idipron revela la grave situación de los menores en contexto de calle en Bogotá - Semana.com</t>
+          <t>Colombia conmemora una década de la Resolución 2250 con un diálogo nacional sobre juventudes, paz y seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Semana.com</t>
+          <t>Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -12391,22 +12391,22 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNVmlPaF9SMDVfSXIxa05XNjBTd0NscTdOYTh4SEtlRU9QZGItVjN3S0Uza3BCbklvdzd3YlYxeHdGWVVIWXpxc1AzLVF4TzVzUlV1WlVjNjhvQnAwUkRJaURBZ2FqeDhpb0Z5d2d6bVN1Y3hNVE5IakpNUk83X1FLVUJTdG5MbkZHaWJCLXlfQ3pWMkVrUi1zdUk0Tkp6SDZTVDVvUUVLY1FoOEhnU1JieXplX1B1eDJ1VTZRMjZoNlZGUXVtU0VRZTV5eFE4S25yUXEtVTUwb3pTVlo3V045bjNvdENRaWlJWllpMTFjTnVCMVBSdlE0Z1gtU3pBRk1scWhCaU1PRdIBjAJBVV95cUxPc1E4TmdZZzgyZU5xVUZoeHI3eE03YUc3b2RKNzk1M0w2YXE1UVl1a0ttcWZ2WEh1bzdGU3czNmNNbXc5bnZHX2NhWWY4b1NQVTNfV2ktX2Y5TE5uVHp5VnBneWlMQXhQR0ZoUWs1Z2xBU25FNW5xZFlMQ1FGQWk2QVVud2w4NkU5N2ZNOTVfUGptaVkzR0hYUEhjVHUzN2ZuY0Nkdmo2NDc5Y05zVjcxU1liTU1aRjIzeXB6ZkJabHZTNko5ZXpxY1RoNWdjWGJER05HSmdyclJKYVJUOXAtSlRoU21qbU5lQkxVZEJYTUtJS252Q000bVJzVEFuWGtGMEhKWm9Pd2JCVjk3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTjN2Wkl1aXB1Wi1DX25OQnZ6amUwVGhLenJTU0VQZkpwZW5zVUxwbEFZZFI4bG4yMS1Qa2J6MWtaYjRLODBfSVNaNktKbWljNVRMSU1uckx2ZXhyVWZ1QlJmeWVvcjVLQWE5cC1lclVkcDNFMlBnMWk1dFF3VVdEaW91ZEFGdG1JU2tRcHk3VGtnOER4MDRjRWQwUzlRUXBRTC10WGg3VkRfcHlVSkFvTUxyekwwMVRVdjRlQ3kzd2tZd2EwZGVZ?oc=5</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -12419,12 +12419,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>IDIPRON alerta sobre niños y jóvenes en riesgo de habitar calle en Bogotá - City Tv</t>
+          <t>Colombia y Alemania se unen para que más estudiantes aprendan alemán en los colegios públicos - Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>City Tv</t>
+          <t>Ministerio de Educación Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -12434,22 +12434,22 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdEpCWHhRQ0JwdHNjV1BoWnNrWk4xWnFFbUQ0QzY2dU1XZk5TWHNyVk9NTlJlaVZ2MTlFVDk3MzNVWHFxWUFZQ3A0UVZHYzhPWUROMi0xWE5OOHpLZEhIVThRalhrOEN1MEE3U2RVRV94bDJpbjRiaUdBbWtfWnlaZ3RydVFtQTdQM3RVSE1qVWRoX0tXanBqQlNqX3RrWVVDMmpzc05JdmlJblFhSTZrazNKb0ltVEh6bGhudjlWQ1VZcjlRZllSWHBGaW01Nmd2dEdTelNRN3g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOdDBneDZDSVFGTEdLQVVyWWJrazBhb2R3ZzZWb051Rkd0MjhKWU5MWFdCVVhNV1JVMlczeDl5elhqLTl5Y19aczFZNmNrV2xKMFdjV0NTWE1RMHplTU9PbzJDWXd4TkNjX0ZrQ2o2ZXRSYVRJT3RKZU1xUG5odGFjYm1BeXJfSkF5WDB1SEZLRWJjSzdKemRXbWFVWGZsaHVONXFkM0RPSWZ0VmRRN2NwenoxRUNrOFhPbmExeUVrUXRXczVfem1iaXdjSTBIR0FoUFpRYUswN3ZFYUlGNFpJZXp1UjJ3bUt0UEVuNnEtSm5sVzFt?oc=5</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -12591,12 +12591,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Los estudiantes a los que los colegios en Colombia no podrán negar el cupo a pesar de esta situación - AS Colombia</t>
+          <t>Colombia recoge aportes clave de jóvenes migrantes para el Primer Plan de Acción Nacional de Juventud, Paz y Seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>AS Colombia</t>
+          <t>Ministerio de Relaciones Exteriores de Colombia</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPNzltbTBsa2trTDhUaW13ZEx3VVVCNWJYWUdMMzRiN3RJZnlaSlpSczNiTGVDT3JhcTd3YWZtV1lfdW5RT1JxY21FU0JqZlJyUVAwd2c2RWViQ09tb1BQbjkzVHItRUpnaWtWZjc3cEQ0QjdaWTJXaUI0UGY4c2c0Vmpzay1EVVgzX2RUMndFcXZkU25ZMFEzM1ZHbjc1UEdQQU9TNzc5TGVLRkFCdG0ybEpZdHc2VktRaVF4YTVCcTFLZk5ITnpWLVItMU5CbzZqV1lMMGxoNEN1VlRzdjc00gHzAUFVX3lxTE5Talh5Y09PR1RuSzhlOTZUbHNVRENDMlpXbE5rTGdZQ3ozUVFjM0p5V2VmcE1FQzVKdkZwc2p3SEl3SVhBT2NuajQzOWlkazF5UHZDQzg3VGFySHNtRDh6Wkx4bEhGdFdjZGFGVkxhZ2xZNjRLM3FZdGYxZVdSVDZNUURCckQ4NExUYXRpdHJHRHo4Sk9qUjh5djMwdm8xYjFpcVNmd083NXR6bUQwWE04V2FWek83U0xGdHY4LXBkbFlSZEhaTWktNmtkaHYxVDlFbXhrYXFDRXdid3hRSk1uVktwQ1NETFZrRW5xMFI4Y1oxWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQb2FIenFRUjRjWTdVdHhwUWVLcDU3SHVBLTF4WGdDbDdvdEhuaFhXWkF3TndUeGxTMVVaZWt3dHZsUFF1ZWxFR0hJNWNPMkhpRWhZaVNvUFVIVW5zRUlhS2toYUUyM2wzTnVLRGxBdnNJSG9ISlBteXdMS3AtVEM5blJqbXFlYVo2M0ZKY2w2SXBKOEd2QnIyUHgzX0ZFcEtBUWh5X3V5SkNoWkZyUE9pRkM5TENhdzFhaW1QTlhvUXNmQ2FRVTBzLQ?oc=5</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -12634,12 +12634,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Colombia recoge aportes clave de jóvenes migrantes para el Primer Plan de Acción Nacional de Juventud, Paz y Seguridad - Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>Colombia reporta 185 casos de niños quemados por pólvora, un crecimiento del 9% frente al 2024 - Caracol Radio</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ministerio de Relaciones Exteriores de Colombia</t>
+          <t>Caracol Radio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQb2FIenFRUjRjWTdVdHhwUWVLcDU3SHVBLTF4WGdDbDdvdEhuaFhXWkF3TndUeGxTMVVaZWt3dHZsUFF1ZWxFR0hJNWNPMkhpRWhZaVNvUFVIVW5zRUlhS2toYUUyM2wzTnVLRGxBdnNJSG9ISlBteXdMS3AtVEM5blJqbXFlYVo2M0ZKY2w2SXBKOEd2QnIyUHgzX0ZFcEtBUWh5X3V5SkNoWkZyUE9pRkM5TENhdzFhaW1QTlhvUXNmQ2FRVTBzLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOVWdJWWtTdmZkcUY3QUM1ZmJJZTdkRnZvVlgtbkpsZS1aa2Y3SkZLMG5XWjlURkhBZzRFRTM0VTZab2FzWFBKM0pNYktVVl9KckdZaVdXTGRpMDRVZ0FPMmU1bmhsQk9NT3VWZjdkSnk1Qnc5bTZGN29vMWhzRkREOURQMzJhNVhXajdPaXlGVnhLNU9WeXBveVBidFVpblZweW9iamtzR2Y1UG5VX3BHX3VaQmpJcHdodmRNa0xkWmd4ZlgtUUHSAdoBQVVfeXFMTmUzalpBM2J2NHFmV185akVudW9XQVVqWDVNMi02cDBDdFBnXzFWMnNSb1J5SF9sMElVcl84WnQwTVdtMURQRm00TTZoc1BCZnJ5NGlqcWdjQUFtRGNiTlZia0tPVy1rZGR6dy1RVDI3Y21XMEZPV19KQXhFYVIwY0lDdHlrMU9sVldSQ2F6X0x2RnFXbVNRXzNsRUwzM1JwMVBsR0stdmRUU1M4bGJJVEllZm1heGNlMVdTQ1lRZUt1V3EtS09LUnV2QzFjSDltRHY0VGZROU40N2c?oc=5</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -12677,12 +12677,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Colombia reporta 185 casos de niños quemados por pólvora, un crecimiento del 9% frente al 2024 - Caracol Radio</t>
+          <t>Los estudiantes a los que los colegios en Colombia no podrán negar el cupo a pesar de esta situación - AS Colombia</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Caracol Radio</t>
+          <t>AS Colombia</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOVWdJWWtTdmZkcUY3QUM1ZmJJZTdkRnZvVlgtbkpsZS1aa2Y3SkZLMG5XWjlURkhBZzRFRTM0VTZab2FzWFBKM0pNYktVVl9KckdZaVdXTGRpMDRVZ0FPMmU1bmhsQk9NT3VWZjdkSnk1Qnc5bTZGN29vMWhzRkREOURQMzJhNVhXajdPaXlGVnhLNU9WeXBveVBidFVpblZweW9iamtzR2Y1UG5VX3BHX3VaQmpJcHdodmRNa0xkWmd4ZlgtUUHSAdoBQVVfeXFMTmUzalpBM2J2NHFmV185akVudW9XQVVqWDVNMi02cDBDdFBnXzFWMnNSb1J5SF9sMElVcl84WnQwTVdtMURQRm00TTZoc1BCZnJ5NGlqcWdjQUFtRGNiTlZia0tPVy1rZGR6dy1RVDI3Y21XMEZPV19KQXhFYVIwY0lDdHlrMU9sVldSQ2F6X0x2RnFXbVNRXzNsRUwzM1JwMVBsR0stdmRUU1M4bGJJVEllZm1heGNlMVdTQ1lRZUt1V3EtS09LUnV2QzFjSDltRHY0VGZROU40N2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPNzltbTBsa2trTDhUaW13ZEx3VVVCNWJYWUdMMzRiN3RJZnlaSlpSczNiTGVDT3JhcTd3YWZtV1lfdW5RT1JxY21FU0JqZlJyUVAwd2c2RWViQ09tb1BQbjkzVHItRUpnaWtWZjc3cEQ0QjdaWTJXaUI0UGY4c2c0Vmpzay1EVVgzX2RUMndFcXZkU25ZMFEzM1ZHbjc1UEdQQU9TNzc5TGVLRkFCdG0ybEpZdHc2VktRaVF4YTVCcTFLZk5ITnpWLVItMU5CbzZqV1lMMGxoNEN1VlRzdjc00gHzAUFVX3lxTE5Talh5Y09PR1RuSzhlOTZUbHNVRENDMlpXbE5rTGdZQ3ozUVFjM0p5V2VmcE1FQzVKdkZwc2p3SEl3SVhBT2NuajQzOWlkazF5UHZDQzg3VGFySHNtRDh6Wkx4bEhGdFdjZGFGVkxhZ2xZNjRLM3FZdGYxZVdSVDZNUURCckQ4NExUYXRpdHJHRHo4Sk9qUjh5djMwdm8xYjFpcVNmd083NXR6bUQwWE04V2FWek83U0xGdHY4LXBkbFlSZEhaTWktNmtkaHYxVDlFbXhrYXFDRXdid3hRSk1uVktwQ1NETFZrRW5xMFI4Y1oxWQ?oc=5</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
+          <t>Estudiantes de colegios públicos en Bogotá que tendrían que reponer clase el sábado</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -588,22 +588,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
+          <t>https://www.pulzo.com/nacion/bogota/estudiantes-colegios-publicos-bogota-que-tendrian-que-reponer-clase-PP5091931A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -611,17 +611,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Por paro de docentes en Bogotá: Secretaría de Educación advirtió que los profesores tendrían que trabajar en sábado</t>
+          <t>La travesía del gigante telescopio que Rodolfo Llinás le regaló al histórico Observatorio de la Universidad Nacional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -636,44 +636,44 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/paro-de-docentes-en-bogota-secretaria-de-educacion-confirmo-reposicion-de-clases-si-el-profesor-se-ausenta/</t>
+          <t>https://www.las2orillas.co/la-travesia-del-gigante-telescopio-que-rodolfo-llinas-le-regalo-al-historico-observatorio-de-la-universidad-nacional/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Una estrategia coordinada busca que los centros escolares registren y reporten detalladamente las asistencias, horarios y participación de docentes y estudiantes, a fin de garantizar el desarrollo normal de contenidos curriculares</t>
+          <t>En medio del paro de la Nacional, el cientifico donó su telescopio personal, el más grande instalado en Colombia, ahora al servicio de estudiantes e investigadoresEl artículoLa travesía del gigante telescopio que Rodolfo Llinás le regaló al...</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
+          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -683,24 +683,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -710,42 +706,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
+          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
+          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
         </is>
       </c>
     </row>
@@ -757,42 +753,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prosperidad Social inicia entrega de transferencia monetaria de Jóvenes en Paz</t>
+          <t>La crisis de natalidad acaba el negocio de los colegios privados, pero abre una oportunidad para mejorar la educación</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-entrega-de-transferencia-monetaria-de-jovenes-en-paz/</t>
+          <t>https://www.las2orillas.co/la-crisis-de-natalidad-acaba-el-negocio-de-los-colegios-privados-pero-abre-una-oportunidad-para-mejorar-la-educacion/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Esta transferencia corresponde al ciclo 1 de 2026. Más de 12.000 jóvenes en el país recibirán los recursos. Bogotá D. C., 24 de febrero de 2026. Prosperidad Social realizará este 27 de febrero la transferencia monetaria condicionada para los...</t>
+          <t>Colombia tiene 33 alumnos por docente, el triple que los países líderes. La crisis de natalidad permite reducir esta brecha y apostar por la equidad socialEl artículoLa crisis de natalidad acaba el negocio de los colegios privados, pero abre una...</t>
         </is>
       </c>
     </row>
@@ -804,7 +800,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs. Juventud: hora y dónde ver el partido decisivo del Poderoso en la Copa Libertadores</t>
+          <t>Por paro de docentes en Bogotá: Secretaría de Educación advirtió que los profesores tendrían que trabajar en sábado</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -819,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/deportes/2026/03/11/independiente-medellin-vs-juventud-hora-y-donde-ver-el-partido-decisivo-del-poderoso-en-la-copa-libertadores/</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/paro-de-docentes-en-bogota-secretaria-de-educacion-confirmo-reposicion-de-clases-si-el-profesor-se-ausenta/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>El rojo paisa quiere estar entre los 32 mejores equipos de América para la edición del 2026</t>
+          <t>Una estrategia coordinada busca que los centros escolares registren y reporten detalladamente las asistencias, horarios y participación de docentes y estudiantes, a fin de garantizar el desarrollo normal de contenidos curriculares</t>
         </is>
       </c>
     </row>
@@ -851,42 +847,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
+          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
+          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
         </is>
       </c>
     </row>
@@ -898,17 +894,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
+          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -918,22 +914,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
         </is>
       </c>
     </row>
@@ -945,42 +941,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>La crisis de natalidad acaba el negocio de los colegios privados, pero abre una oportunidad para mejorar la educación</t>
+          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-crisis-de-natalidad-acaba-el-negocio-de-los-colegios-privados-pero-abre-una-oportunidad-para-mejorar-la-educacion/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Colombia tiene 33 alumnos por docente, el triple que los países líderes. La crisis de natalidad permite reducir esta brecha y apostar por la equidad socialEl artículoLa crisis de natalidad acaba el negocio de los colegios privados, pero abre una...</t>
+          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
         </is>
       </c>
     </row>
@@ -992,17 +988,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
+          <t>Independiente Medellín vs. Juventud: hora y dónde ver el partido decisivo del Poderoso en la Copa Libertadores</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1012,39 +1008,39 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
+          <t>https://www.infobae.com/colombia/deportes/2026/03/11/independiente-medellin-vs-juventud-hora-y-donde-ver-el-partido-decisivo-del-poderoso-en-la-copa-libertadores/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
+          <t>El rojo paisa quiere estar entre los 32 mejores equipos de América para la edición del 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
+          <t>Prosperidad Social inicia entrega de transferencia monetaria de Jóvenes en Paz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1054,7 +1050,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1069,71 +1065,71 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-entrega-de-transferencia-monetaria-de-jovenes-en-paz/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
+          <t>Esta transferencia corresponde al ciclo 1 de 2026. Más de 12.000 jóvenes en el país recibirán los recursos. Bogotá D. C., 24 de febrero de 2026. Prosperidad Social realizará este 27 de febrero la transferencia monetaria condicionada para los...</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
+          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
+          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
+          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
+          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1163,24 +1159,24 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
+          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
+          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1195,7 +1191,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1210,34 +1206,34 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
+          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1257,59 +1253,59 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
         </is>
       </c>
     </row>
@@ -1321,64 +1317,64 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/cultura</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1388,7 +1384,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1398,67 +1394,71 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
+          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+          <t>https://www.diarioadn.co/seccion/cultura</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
+          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1488,57 +1488,57 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1578,10 +1578,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1591,12 +1595,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
+          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1611,24 +1615,20 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
+          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1701,20 +1701,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1754,71 +1758,63 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1833,45 +1829,49 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1891,20 +1891,24 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1919,7 +1923,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1934,7 +1938,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -1942,12 +1946,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1962,22 +1966,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -1985,12 +1989,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2010,17 +2014,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2028,22 +2032,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
+          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2053,39 +2057,35 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2123,17 +2123,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
+          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2143,20 +2143,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2166,12 +2170,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2181,12 +2185,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2196,29 +2200,25 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2243,20 +2243,24 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2271,22 +2275,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2294,12 +2298,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2329,7 +2333,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2337,12 +2341,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2357,7 +2361,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2372,7 +2376,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2380,17 +2384,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2400,7 +2404,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2415,7 +2419,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2423,12 +2427,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2443,22 +2447,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2466,32 +2470,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Estados Unidos reclama a Colombia ante ONU el incremento de reclutamiento de menores de edad - El Espectador</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2501,7 +2505,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPVFRDQXk2WVcwQVhLTmljT1B4akFGM3ozQlBvc3QyOHJua1BfT1hxRnFJY212eFowWTVTdVBmTHN6d2REcXc5VGVuUmw1LWsxNWxOeW82UzBPaVQ3azZfQVNSb0pUTHFqTHdGVWJXS2Z5YmVSbXZJSXd4dzdTamNXdUtqMTRwVDV4MF9acHJFX1pTZ19NVVNvLWdNb1Y1d0FzZlN2dWVMamlvVlNCN01ZS2MxZDh1M250d2tsNEVpc2NYRUJXcE9KYk0yd1FHU3BiNUtFOENRdWZ4ZHdsR0l2cFRFMEpKTGYtaUk4dmhuRjhyaVU3RDYxbUpCUzjSAZACQVVfeXFMTmxJSVphakhMc1dSdUhqdDJFZW00OTIwT0NRNndiZGNtLWROVW1NZFFHWHhTMzVYb3N6aHRBV1NObF94cEVSeHZMOWpPTW1oVXdGeDloRU9uSWpIUXNldU1qY2lUM3dNWnhwMUNESWVTUy1SNGYzZkM0Nk1ORE9zQkNkdzc1MnJpUldVTnhKeUsycE1rcGdwMi1SN3F4bkZUdHZGNUJWT1RLeS1ZMFJUVkdmOXpHcnpId0N2QW9oOEVsbkYyVU9xbUtnTEVBdW1kNnlOY2wwVGVUY1dCc3N5WkQ5ZTBRUTFKSndYUU4zYVU2aUc1cUlsLUt4d3B6OTZ4Xzl0cC0tMFAwQ0hwM2JWUC0?oc=5</t>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2509,12 +2513,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad - Infobae</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2544,7 +2548,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQSmlvdlUzeHJlOVhEOTBjQVN5TlhCWkNmaUNEQnczelA1YWVHXzJ1ZHZkM2JKcWdCNzdKYkViRnQyaFpldFB5MGQ4SU54WDVoVGNlbWdRQzJhM0hvRGFaaF9MR3lxUWhSbGJUTFNKcHVmQjJ4MjlibnNuaGNVcXVaVE1aa0stdmFzYmxvTnlmc1hwMFdQUDJGVkVuS2Y4NTgydk9zQlZsU2l0OXA2NjUzZnk3SnpDOUx6RjItNE9EYWlscDBlR19XV1pIdEgxVF9XT2RWMHItMmdEeHlqdmdfYzh1X0dIT2lLNjlvR2RsRWhDZ25iMWVGbTNzaUtQZy1STHfSAZwCQVVfeXFMTXRiNGt6QnJSZDJ3NXItNWZ1enZWUkZmMEhPSm5pNWpLT2hSLXdLWnBzOTFLcVdzM3Q2SWZ1UWpzdU13NjVDNUR6S2o5N1BhOWdlYWEyVDh2bGVqTE1LR19KUnFaUFJEVWZhTlZ4Z3RwV3J2U1I3VmtReVVaTGxMTldfeEZmclhOby1iaFpVU2ZjOUJqRERwNFlMNVdzbDVFX3BQWmg1YjNhY0hrQWJ4UW53Z0lRTWlLWFEyWm5Jck5qX3ROSXVqZUxtTHM3WDk2TDJzUDJUN21VTjkxamZMRUd2Unl3emJEaGJxejJPdFViSkNWbTRudzNRUmE4bFg4a1JaLURLa0lQakk0U0kyRFFwV0ZlRHBtZ3VNc1Q?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2595,12 +2599,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2615,7 +2619,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2630,7 +2634,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQSmlvdlUzeHJlOVhEOTBjQVN5TlhCWkNmaUNEQnczelA1YWVHXzJ1ZHZkM2JKcWdCNzdKYkViRnQyaFpldFB5MGQ4SU54WDVoVGNlbWdRQzJhM0hvRGFaaF9MR3lxUWhSbGJUTFNKcHVmQjJ4MjlibnNuaGNVcXVaVE1aa0stdmFzYmxvTnlmc1hwMFdQUDJGVkVuS2Y4NTgydk9zQlZsU2l0OXA2NjUzZnk3SnpDOUx6RjItNE9EYWlscDBlR19XV1pIdEgxVF9XT2RWMHItMmdEeHlqdmdfYzh1X0dIT2lLNjlvR2RsRWhDZ25iMWVGbTNzaUtQZy1STHfSAZwCQVVfeXFMTXRiNGt6QnJSZDJ3NXItNWZ1enZWUkZmMEhPSm5pNWpLT2hSLXdLWnBzOTFLcVdzM3Q2SWZ1UWpzdU13NjVDNUR6S2o5N1BhOWdlYWEyVDh2bGVqTE1LR19KUnFaUFJEVWZhTlZ4Z3RwV3J2U1I3VmtReVVaTGxMTldfeEZmclhOby1iaFpVU2ZjOUJqRERwNFlMNVdzbDVFX3BQWmg1YjNhY0hrQWJ4UW53Z0lRTWlLWFEyWm5Jck5qX3ROSXVqZUxtTHM3WDk2TDJzUDJUN21VTjkxamZMRUd2Unl3emJEaGJxejJPdFViSkNWbTRudzNRUmE4bFg4a1JaLURLa0lQakk0U0kyRFFwV0ZlRHBtZ3VNc1Q?oc=5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2638,32 +2642,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>Estados Unidos reclama a Colombia ante ONU el incremento de reclutamiento de menores de edad - El Espectador</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2673,7 +2677,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPVFRDQXk2WVcwQVhLTmljT1B4akFGM3ozQlBvc3QyOHJua1BfT1hxRnFJY212eFowWTVTdVBmTHN6d2REcXc5VGVuUmw1LWsxNWxOeW82UzBPaVQ3azZfQVNSb0pUTHFqTHdGVWJXS2Z5YmVSbXZJSXd4dzdTamNXdUtqMTRwVDV4MF9acHJFX1pTZ19NVVNvLWdNb1Y1d0FzZlN2dWVMamlvVlNCN01ZS2MxZDh1M250d2tsNEVpc2NYRUJXcE9KYk0yd1FHU3BiNUtFOENRdWZ4ZHdsR0l2cFRFMEpKTGYtaUk4dmhuRjhyaVU3RDYxbUpCUzjSAZACQVVfeXFMTmxJSVphakhMc1dSdUhqdDJFZW00OTIwT0NRNndiZGNtLWROVW1NZFFHWHhTMzVYb3N6aHRBV1NObF94cEVSeHZMOWpPTW1oVXdGeDloRU9uSWpIUXNldU1qY2lUM3dNWnhwMUNESWVTUy1SNGYzZkM0Nk1ORE9zQkNkdzc1MnJpUldVTnhKeUsycE1rcGdwMi1SN3F4bkZUdHZGNUJWT1RLeS1ZMFJUVkdmOXpHcnpId0N2QW9oOEVsbkYyVU9xbUtnTEVBdW1kNnlOY2wwVGVUY1dCc3N5WkQ5ZTBRUTFKSndYUU4zYVU2aUc1cUlsLUt4d3B6OTZ4Xzl0cC0tMFAwQ0hwM2JWUC0?oc=5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2681,12 +2685,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2706,7 +2710,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2716,7 +2720,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2729,7 +2733,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2749,7 +2753,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2759,7 +2763,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2767,12 +2771,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2787,7 +2791,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2802,7 +2806,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2810,12 +2814,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2835,17 +2839,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2853,27 +2857,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2888,7 +2892,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2896,17 +2900,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2921,71 +2925,63 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
+          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2995,42 +2991,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
         </is>
       </c>
     </row>
@@ -3042,40 +3038,44 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
+          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -3123,12 +3123,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3166,27 +3166,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3201,20 +3201,24 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3229,12 +3233,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3244,7 +3248,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3252,12 +3256,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3272,22 +3276,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3300,7 +3304,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
+          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3320,7 +3324,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3330,7 +3334,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3343,7 +3347,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3358,22 +3362,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3401,22 +3405,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3424,17 +3428,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3449,17 +3453,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3467,17 +3471,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3487,12 +3491,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3502,14 +3506,10 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3534,22 +3534,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.alertabogota.com/noticias/local</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3557,17 +3557,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3592,30 +3592,34 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>¿Cuándo entran a clases los colegios públicos y distritales en enero de 2026? - El Espectador</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3635,7 +3639,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVGV3a0tQeW5uLVpJdlBBT3Rrc0NrUm9Va3pHY3NYMko1d1N4bjUzdjVYZ3ZjZWZpQ0xYak0yQVNLdFRsVXJxbnJMSVJVT3ZyaEZ4ZEZIU01RWVoyUHd6Q0hiNFdCMElNeXExYXVrQVJaQU8tN0RUMC0xZERQdFZ2aWo0UXQtZTZ5VmN6NE9YSjlhYUVGd01ycDBCaC1RMEhUcmk5TTdEekozS3g5Ry02SEVTOWprUdIBygFBVV95cUxQMlJDNFNLREl3U2ZaeXVGYy1GS2NmWlVydW1DX24wRE9NOVhBbzhqNWNzMmhTNEdTa0JFa281R1FVRUFfdjlUXzd2Nl8xTGxMb3JIaUVxOG1DTTBwRlluV1B3QVF6QTI1cEd1TTlVQlJiVWJkLWFFRFo1RlVsQjRMS2ZmTDhpUTY3bGdfRzlXWmliT2NybEFPcnRfaWJpX3UtazA0ekRpOFpOeU93TGNsOTV6Ynp3VkhKRnVPcmswemZHYnZNQUxrWHNn?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3643,32 +3647,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Niños colombianos pasan 8.9 horas diarias frente a pantallas: qué efectos hay en su salud - El Espectador</t>
+          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3678,7 +3682,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZkRQZ0I3REZBYkZoNlVha2RNQ3F6dmlSYU5hTTBBOGkzMlBSM2xXV0RsMFRKcy1XRG1xWWNmQk5mUWE3ci1BMGZpNGZHeHFjcDBmdGQxb1cwNG95V0R0RVNodGlYcXFFcHRLdWU3bWgtSC1vV2YwTE5wVVpBejlZd2ZmRENoVTl4cDNnNWQwUDBxRFlIak83MjRYelRLRVdodS1wNnRLeC1wS1ViT2Y2SDhOSmdYZ0taY3BDNmxYMUpuUdIB1gFBVV95cUxOTUtIYTlOYUdmTHVzRmZWQVNGRkVsdDk3cEg4bDlRaXhVRUZyd2tBOHFXUWplMUtQYUpRX29LbDZNOHhDcXc4OHQ0OTVNS1I3cElDR1RRNFliRXA0UjV0Y1kzbmdzRzFVSnNYUlZUeEN4OEt1SnZDbXRzQ1hycHoxRTE1RlZzNk5BR1o2LTBTTWZka01pR2oycmV1MWlZY2ZoSjVvRlBvMWVLODJMbnFaZ251aU0zWGZqWHkwX1lMTEZCaC04ZEQwZTNTaU1ycktSUDhuRVRR?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3686,32 +3690,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
+          <t>¿Cuándo entran a clases los colegios públicos y distritales en enero de 2026? - El Espectador</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3721,7 +3725,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVGV3a0tQeW5uLVpJdlBBT3Rrc0NrUm9Va3pHY3NYMko1d1N4bjUzdjVYZ3ZjZWZpQ0xYak0yQVNLdFRsVXJxbnJMSVJVT3ZyaEZ4ZEZIU01RWVoyUHd6Q0hiNFdCMElNeXExYXVrQVJaQU8tN0RUMC0xZERQdFZ2aWo0UXQtZTZ5VmN6NE9YSjlhYUVGd01ycDBCaC1RMEhUcmk5TTdEekozS3g5Ry02SEVTOWprUdIBygFBVV95cUxQMlJDNFNLREl3U2ZaeXVGYy1GS2NmWlVydW1DX24wRE9NOVhBbzhqNWNzMmhTNEdTa0JFa281R1FVRUFfdjlUXzd2Nl8xTGxMb3JIaUVxOG1DTTBwRlluV1B3QVF6QTI1cEd1TTlVQlJiVWJkLWFFRFo1RlVsQjRMS2ZmTDhpUTY3bGdfRzlXWmliT2NybEFPcnRfaWJpX3UtazA0ekRpOFpOeU93TGNsOTV6Ynp3VkhKRnVPcmswemZHYnZNQUxrWHNn?oc=5</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3729,32 +3733,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Estudiantes de Medicina anunciaron protesta y Gustavo Petro les respondió: habría plantón en 17 ciudades - Infobae</t>
+          <t>Niños colombianos pasan 8.9 horas diarias frente a pantallas: qué efectos hay en su salud - El Espectador</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3764,7 +3768,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOckVuZWpkQV9QTnd6UzZmSXdvNl9xX3plZHNIRkV1X2liZTJmYjRHY05uVDc5M09nekFlMDVwVS01WWtsZmstN1VtZkc3M0E5d0xGd1lRMzh5c0Qtc09iei1pVmdSekozWUVLenM5YVRtTms0R3BJdEZocU9YVE5wUEo0UVdLRnQ3cENPWm1ETmhsbjFULThLTVRKanQwSTVvM2hCQW5VODlJejZkRkpYUHpzREpEeDY1M29UaV82cUZQVFp6OEpmRVlxRTBzQzFUcWlPbTVWOVQwSG9LVF9KcGhiejZzTWt2S05KYzdyeDgzbThZMmhkdUNQZTBBdGNHN2RletIBnwJBVV95cUxPOTVVOXMyRFBNN21yQnZ5RHkzMTZOMVYybU0xXzNzczIycm95cHdBcEFKc0d0VVlLT25PYWJkVDhnbUVMdlQwTHktNlJqNG9EeXFDQ1RSaG51Tnc4ZXlsWXpVYzZSZWl1MXVRQVdabXI5ZTRUYXdQblUzWmN5NEE3VW1PRF8yNWdHcjVsdXZ3STF2cUJlenZHbTluZkpKYzRvSlhDZVlNVWdnVjBqZEFuSHpuQnNwdUVMMjBkMm5JNUZVZkFfOHFUMHFpeEdLWGFzZ0Q0V0pZdzdrMXdpUkRsRVZQRVppU3hnTXZlU05GRWZlZ3hKUnBKdFlWdy02cXJRdE1YWUFsSDRZTXctSDRhSkRMMV95QlRPUkJIVV92Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZkRQZ0I3REZBYkZoNlVha2RNQ3F6dmlSYU5hTTBBOGkzMlBSM2xXV0RsMFRKcy1XRG1xWWNmQk5mUWE3ci1BMGZpNGZHeHFjcDBmdGQxb1cwNG95V0R0RVNodGlYcXFFcHRLdWU3bWgtSC1vV2YwTE5wVVpBejlZd2ZmRENoVTl4cDNnNWQwUDBxRFlIak83MjRYelRLRVdodS1wNnRLeC1wS1ViT2Y2SDhOSmdYZ0taY3BDNmxYMUpuUdIB1gFBVV95cUxOTUtIYTlOYUdmTHVzRmZWQVNGRkVsdDk3cEg4bDlRaXhVRUZyd2tBOHFXUWplMUtQYUpRX29LbDZNOHhDcXc4OHQ0OTVNS1I3cElDR1RRNFliRXA0UjV0Y1kzbmdzRzFVSnNYUlZUeEN4OEt1SnZDbXRzQ1hycHoxRTE1RlZzNk5BR1o2LTBTTWZka01pR2oycmV1MWlZY2ZoSjVvRlBvMWVLODJMbnFaZ251aU0zWGZqWHkwX1lMTEZCaC04ZEQwZTNTaU1ycktSUDhuRVRR?oc=5</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3772,12 +3776,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Accidente de estudiantes del Liceo Antioqueño: bus iba con el 97% de su capacidad, sin cinturones y con fallas graves de seguridad - Infobae</t>
+          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3797,7 +3801,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3807,7 +3811,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZGtNeVVBeHQta1Zhc2Z5YVpZR09qcnJZdnZCOGJ1TGdwbEktWVQ1UElPWmI2bEFEZUlOUGI5Z1J5U053TlBHcHkxclNnYlA2VU8zaWMwN3ZXdW9kdW1wTEJ5akcwcC1kZXk1eFZnQTlNT3JsUnRlRGNwTFpuNFZ4SnowUW5qQnhacGxHSTlCUXdRWDBXRjdHQUd1RGtkUjFJOXZhNmZkWXdfd0I3WGdYcWllRThlRkR4LXdQa1JNbDBlN2pyOUtJSU1zbGhob1cxUWhjeE03aXVJYWpLaTh4QmpyZGpXOVQ4dHJURUd2MWdtb01wd3hISTladGdKbDV1NmfSAZwCQVVfeXFMTmlvd2VmT04wQVNQWEh2LVQ3WXF6M0hZZU4wa3RKa3dUMEU3c3NPQmhONUoxbGNQNnJPR1dsUWp3d3pVT19vM1JoUnZNTWZIR1hWcjZXYXBNcVQ5OVN4dGR2S2dfbXZWclFFeU9GNUM2eEY3OWR5OWo5OUZTeXVSMWhKTHV0VGx6RFc4eVktSGFXdGJwa0FNWTd4b3hyakQxRWNJMXlOUjhiaEhtbXZhWkhDUmZ3ZVVTNGNfTEdUZjl3Z3VPT0VwVjZ5OHBOT0tEVmlZbTFKVUtXcU5JaWN0MnVpNWFLdmVtZTlaQV9Cd0Y3RUc3eXI1R3hrNnRXVnZELVliZTRrVUNaYXNsdFJ1Q2ZkRFpRSnhYcjl3NGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3815,27 +3819,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>¿El alemán será materia obligatoria en colegios públicos? Esto dice el Mineducación - El Espectador</t>
+          <t>Estudiantes de Medicina anunciaron protesta y Gustavo Petro les respondió: habría plantón en 17 ciudades - Infobae</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3850,7 +3854,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFh6ZDVETFROR255WTE1dm1uNXhtaXg4aGNjOUtZblZDbU9RbnFhLU81Z29yVDZzeG1HcFpjeS12UFJNX1lSaXRRVWIyWUFyWkMyaDJobmNReFhjRzREcTFBTGFsX3RwNDRnUHhydUtWdEcyR0VFeVRXUlg5c0hJZlhydURCVG0zcmd0SkNVbk5qak8tbkJGWnducXNZV1hOUFEtSHRWbmVvOFRXSFM4aG5zbU9SOWJ2Y1RTRGNB0gHSAUFVX3lxTE5jTVU1LW82UDhqRVdjVnNNQ29LZXpEdTM1a2NiRlNUaVBBUnVCZ25hamlJM3RiZW9DNzBMYWNBanJaemVuaEdzUUMyOFljN0t3SU1ac0ZRNnBLWm1LNjAycG8yUFRTZllRWVIwTWV0dTN2TTM3WEt5ZWNNWFlia2VvMFdnNEZtMTlDSWhwX1ZLc3hCTDlvT20zd3ZJUEE2UVJVc1Z3bGpnOENxSWNYcExDX0hiaGxTMnE2dXBSaEJnRE9Od2VQdk1vQmVCUy1PdjlSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOckVuZWpkQV9QTnd6UzZmSXdvNl9xX3plZHNIRkV1X2liZTJmYjRHY05uVDc5M09nekFlMDVwVS01WWtsZmstN1VtZkc3M0E5d0xGd1lRMzh5c0Qtc09iei1pVmdSekozWUVLenM5YVRtTms0R3BJdEZocU9YVE5wUEo0UVdLRnQ3cENPWm1ETmhsbjFULThLTVRKanQwSTVvM2hCQW5VODlJejZkRkpYUHpzREpEeDY1M29UaV82cUZQVFp6OEpmRVlxRTBzQzFUcWlPbTVWOVQwSG9LVF9KcGhiejZzTWt2S05KYzdyeDgzbThZMmhkdUNQZTBBdGNHN2RletIBnwJBVV95cUxPOTVVOXMyRFBNN21yQnZ5RHkzMTZOMVYybU0xXzNzczIycm95cHdBcEFKc0d0VVlLT25PYWJkVDhnbUVMdlQwTHktNlJqNG9EeXFDQ1RSaG51Tnc4ZXlsWXpVYzZSZWl1MXVRQVdabXI5ZTRUYXdQblUzWmN5NEE3VW1PRF8yNWdHcjVsdXZ3STF2cUJlenZHbTluZkpKYzRvSlhDZVlNVWdnVjBqZEFuSHpuQnNwdUVMMjBkMm5JNUZVZkFfOHFUMHFpeEdLWGFzZ0Q0V0pZdzdrMXdpUkRsRVZQRVppU3hnTXZlU05GRWZlZ3hKUnBKdFlWdy02cXJRdE1YWUFsSDRZTXctSDRhSkRMMV95QlRPUkJIVV92Yw?oc=5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3858,17 +3862,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
+          <t>Accidente de estudiantes del Liceo Antioqueño: bus iba con el 97% de su capacidad, sin cinturones y con fallas graves de seguridad - Infobae</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3878,7 +3882,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3893,7 +3897,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZGtNeVVBeHQta1Zhc2Z5YVpZR09qcnJZdnZCOGJ1TGdwbEktWVQ1UElPWmI2bEFEZUlOUGI5Z1J5U053TlBHcHkxclNnYlA2VU8zaWMwN3ZXdW9kdW1wTEJ5akcwcC1kZXk1eFZnQTlNT3JsUnRlRGNwTFpuNFZ4SnowUW5qQnhacGxHSTlCUXdRWDBXRjdHQUd1RGtkUjFJOXZhNmZkWXdfd0I3WGdYcWllRThlRkR4LXdQa1JNbDBlN2pyOUtJSU1zbGhob1cxUWhjeE03aXVJYWpLaTh4QmpyZGpXOVQ4dHJURUd2MWdtb01wd3hISTladGdKbDV1NmfSAZwCQVVfeXFMTmlvd2VmT04wQVNQWEh2LVQ3WXF6M0hZZU4wa3RKa3dUMEU3c3NPQmhONUoxbGNQNnJPR1dsUWp3d3pVT19vM1JoUnZNTWZIR1hWcjZXYXBNcVQ5OVN4dGR2S2dfbXZWclFFeU9GNUM2eEY3OWR5OWo5OUZTeXVSMWhKTHV0VGx6RFc4eVktSGFXdGJwa0FNWTd4b3hyakQxRWNJMXlOUjhiaEhtbXZhWkhDUmZ3ZVVTNGNfTEdUZjl3Z3VPT0VwVjZ5OHBOT0tEVmlZbTFKVUtXcU5JaWN0MnVpNWFLdmVtZTlaQV9Cd0Y3RUc3eXI1R3hrNnRXVnZELVliZTRrVUNaYXNsdFJ1Q2ZkRFpRSnhYcjl3NGE?oc=5</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3901,27 +3905,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
+          <t>¿El alemán será materia obligatoria en colegios públicos? Esto dice el Mineducación - El Espectador</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3936,7 +3940,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFh6ZDVETFROR255WTE1dm1uNXhtaXg4aGNjOUtZblZDbU9RbnFhLU81Z29yVDZzeG1HcFpjeS12UFJNX1lSaXRRVWIyWUFyWkMyaDJobmNReFhjRzREcTFBTGFsX3RwNDRnUHhydUtWdEcyR0VFeVRXUlg5c0hJZlhydURCVG0zcmd0SkNVbk5qak8tbkJGWnducXNZV1hOUFEtSHRWbmVvOFRXSFM4aG5zbU9SOWJ2Y1RTRGNB0gHSAUFVX3lxTE5jTVU1LW82UDhqRVdjVnNNQ29LZXpEdTM1a2NiRlNUaVBBUnVCZ25hamlJM3RiZW9DNzBMYWNBanJaemVuaEdzUUMyOFljN0t3SU1ac0ZRNnBLWm1LNjAycG8yUFRTZllRWVIwTWV0dTN2TTM3WEt5ZWNNWFlia2VvMFdnNEZtMTlDSWhwX1ZLc3hCTDlvT20zd3ZJUEE2UVJVc1Z3bGpnOENxSWNYcExDX0hiaGxTMnE2dXBSaEJnRE9Od2VQdk1vQmVCUy1PdjlSZw?oc=5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3944,17 +3948,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
+          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3964,22 +3968,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3987,12 +3991,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
+          <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4012,7 +4016,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4030,27 +4034,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>La localidad de Usaquén tiene una Casa de Juventud para beneficiar a más de 100.000 jóvenes</t>
+          <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4065,71 +4069,63 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#74871d874f</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>●Bogotá abre un nuevo espacio para las y los jóvenes de la localidad, ubicado en la calle 155 #7-45, con acto protocolario y participación de autoridades y representantes juveniles. ●Esta casa amplía la cobertura territorial del servicio Casas de...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
+          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
+          <t>La localidad de Usaquén tiene una Casa de Juventud para beneficiar a más de 100.000 jóvenes</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4144,7 +4140,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4159,24 +4155,24 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#74871d874f</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
+          <t>●Bogotá abre un nuevo espacio para las y los jóvenes de la localidad, ubicado en la calle 155 #7-45, con acto protocolario y participación de autoridades y representantes juveniles. ●Esta casa amplía la cobertura territorial del servicio Casas de...</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
+          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4191,7 +4187,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4206,24 +4202,24 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
+          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
+          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4238,7 +4234,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4253,24 +4249,24 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
+          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
+          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4300,24 +4296,24 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Últimos días para inscribirse y obtener una beca en formación técnico laboral de la Agencia Atenea</t>
+          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4347,24 +4343,24 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#d7dc735e17</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>•Son 1.500 cupos y se cubre el 100 % de la matrícula, apoyo económico por semestre y acompañamiento en la ruta educativa y laboral. • La convocatoria se cierra el domingo 21 de septiembre a las 11 y 59 de la noche</t>
+          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
+          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4394,24 +4390,24 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+          <t>Últimos días para inscribirse y obtener una beca en formación técnico laboral de la Agencia Atenea</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4426,7 +4422,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4441,24 +4437,24 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#d7dc735e17</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
+          <t>•Son 1.500 cupos y se cubre el 100 % de la matrícula, apoyo económico por semestre y acompañamiento en la ruta educativa y laboral. • La convocatoria se cierra el domingo 21 de septiembre a las 11 y 59 de la noche</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
+          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4488,57 +4484,151 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
+          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SDIS - Juventud</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SDIS - Juventud</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>El Frailejón abre sus puertas: Usme estrena nueva Casa de la Juventud</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>SDIS - Juventud</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>institucional</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Otra</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Bogotá</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c7eca5d4bd</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>• Aunque ya existía una Casa de la Juventud en Usme, la sede se traslada y reinaugura para ofrecer mejores condiciones, ampliar servicios y fortalecer la atención a los jóvenes. • La reapertura se desarrolló con el acompañamiento de la Plataforma...</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,22 +478,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gobierno geolocaliza casi 1.000 colegios en La Guajira que eran “invisibles”: no figuraban en el mapa</t>
+          <t>Abren 200 becas para jóvenes del Pacífico que lideren proyectos en sus territorios</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,29 +513,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/12/gobierno-geolocaliza-casi-1000-colegios-en-la-guajira-que-eran-invisibles-no-figuraban-en-el-mapa/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abren-200-becas-para-jovenes-del-pacifico-que-lideren-proyectos-en-sus-territorios/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Los pocos planteles educativos con geolocalización en plataformas de ubicación están en las cabeceras municipales del departamento</t>
+          <t>El programa DALE lidera Pacífico ofrecerá formación, mentorías y acompañamiento a jóvenes que impulsen iniciativas comunitarias en litoral.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Solo 1 de cada 4 estudiantes colombianos logra el nivel avanzado en educación media: ¿por qué importa?</t>
+          <t>Figura de Independiente Medellín dedicó su gol en la clasificación del equipo en la Copa Libertadores a una persona que “está en tratamiento”</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -545,12 +545,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -560,10 +560,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/desigualdad-en-la-educacion-media-en-colombia-solo-el-13-de-estudiantes-logra-competencias-clave-PP5091242A</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/deportes/2026/03/13/figura-de-independiente-medellin-dedico-su-gol-en-la-clasificacion-del-equipo-en-la-copa-libertadores-a-una-persona-que-esta-en-tratamiento/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>El equipo dirigido por Alejandro Restrepo venció 2-1 a Juventud de Uruguay ante 12.000 hinchas y clasificó a la fase de grupos, donde acompañará a Deportes Tolima, Junior y Santa Fe en el torneo continental</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Estudiantes de colegios públicos en Bogotá que tendrían que reponer clase el sábado</t>
+          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -588,22 +592,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/estudiantes-colegios-publicos-bogota-que-tendrian-que-reponer-clase-PP5091931A</t>
+          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -616,12 +620,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La travesía del gigante telescopio que Rodolfo Llinás le regaló al histórico Observatorio de la Universidad Nacional</t>
+          <t>Solo 1 de cada 4 estudiantes colombianos logra el nivel avanzado en educación media: ¿por qué importa?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,14 +650,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-travesia-del-gigante-telescopio-que-rodolfo-llinas-le-regalo-al-historico-observatorio-de-la-universidad-nacional/</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>En medio del paro de la Nacional, el cientifico donó su telescopio personal, el más grande instalado en Colombia, ahora al servicio de estudiantes e investigadoresEl artículoLa travesía del gigante telescopio que Rodolfo Llinás le regaló al...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/desigualdad-en-la-educacion-media-en-colombia-solo-el-13-de-estudiantes-logra-competencias-clave-PP5091242A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
+          <t>Gobierno geolocaliza casi 1.000 colegios en La Guajira que eran “invisibles”: no figuraban en el mapa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -693,72 +693,76 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/03/12/gobierno-geolocaliza-casi-1000-colegios-en-la-guajira-que-eran-invisibles-no-figuraban-en-el-mapa/</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Los pocos planteles educativos con geolocalización en plataformas de ubicación están en las cabeceras municipales del departamento</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
+          <t>La travesía del gigante telescopio que Rodolfo Llinás le regaló al histórico Observatorio de la Universidad Nacional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
+          <t>https://www.las2orillas.co/la-travesia-del-gigante-telescopio-que-rodolfo-llinas-le-regalo-al-historico-observatorio-de-la-universidad-nacional/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
+          <t>En medio del paro de la Nacional, el cientifico donó su telescopio personal, el más grande instalado en Colombia, ahora al servicio de estudiantes e investigadoresEl artículoLa travesía del gigante telescopio que Rodolfo Llinás le regaló al...</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>La crisis de natalidad acaba el negocio de los colegios privados, pero abre una oportunidad para mejorar la educación</t>
+          <t>Estudiantes de colegios públicos en Bogotá que tendrían que reponer clase el sábado</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -773,24 +777,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-crisis-de-natalidad-acaba-el-negocio-de-los-colegios-privados-pero-abre-una-oportunidad-para-mejorar-la-educacion/</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Colombia tiene 33 alumnos por docente, el triple que los países líderes. La crisis de natalidad permite reducir esta brecha y apostar por la equidad socialEl artículoLa crisis de natalidad acaba el negocio de los colegios privados, pero abre una...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/estudiantes-colegios-publicos-bogota-que-tendrian-que-reponer-clase-PP5091931A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Por paro de docentes en Bogotá: Secretaría de Educación advirtió que los profesores tendrían que trabajar en sábado</t>
+          <t>Independiente Medellín vs. Juventud: hora y dónde ver el partido decisivo del Poderoso en la Copa Libertadores</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/paro-de-docentes-en-bogota-secretaria-de-educacion-confirmo-reposicion-de-clases-si-el-profesor-se-ausenta/</t>
+          <t>https://www.infobae.com/colombia/deportes/2026/03/11/independiente-medellin-vs-juventud-hora-y-donde-ver-el-partido-decisivo-del-poderoso-en-la-copa-libertadores/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Una estrategia coordinada busca que los centros escolares registren y reporten detalladamente las asistencias, horarios y participación de docentes y estudiantes, a fin de garantizar el desarrollo normal de contenidos curriculares</t>
+          <t>El rojo paisa quiere estar entre los 32 mejores equipos de América para la edición del 2026</t>
         </is>
       </c>
     </row>
@@ -847,42 +847,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
+          <t>La crisis de natalidad acaba el negocio de los colegios privados, pero abre una oportunidad para mejorar la educación</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
+          <t>https://www.las2orillas.co/la-crisis-de-natalidad-acaba-el-negocio-de-los-colegios-privados-pero-abre-una-oportunidad-para-mejorar-la-educacion/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
+          <t>Colombia tiene 33 alumnos por docente, el triple que los países líderes. La crisis de natalidad permite reducir esta brecha y apostar por la equidad socialEl artículoLa crisis de natalidad acaba el negocio de los colegios privados, pero abre una...</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
+          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
+          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
+          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
+          <t>Prosperidad Social inicia entrega de transferencia monetaria de Jóvenes en Paz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-entrega-de-transferencia-monetaria-de-jovenes-en-paz/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+          <t>Esta transferencia corresponde al ciclo 1 de 2026. Más de 12.000 jóvenes en el país recibirán los recursos. Bogotá D. C., 24 de febrero de 2026. Prosperidad Social realizará este 27 de febrero la transferencia monetaria condicionada para los...</t>
         </is>
       </c>
     </row>
@@ -988,42 +988,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs. Juventud: hora y dónde ver el partido decisivo del Poderoso en la Copa Libertadores</t>
+          <t>Colombia Mayor y Renta Joven: Prosperidad Social realizará la Maratón por las Generaciones</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/deportes/2026/03/11/independiente-medellin-vs-juventud-hora-y-donde-ver-el-partido-decisivo-del-poderoso-en-la-copa-libertadores/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/colombia-mayor-y-renta-joven-prosperidad-social-realizara-la-maraton-por-las-generaciones/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>El rojo paisa quiere estar entre los 32 mejores equipos de América para la edición del 2026</t>
+          <t>Se trata de una jornada continua de atención telefónica, en la que se resolverán inquietudes que tengan beneficiarias y beneficiarios de estos dos programas de la entidad. El canal telefónico tendrá atención continua por más de 36 horas, mientras...</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prosperidad Social inicia entrega de transferencia monetaria de Jóvenes en Paz</t>
+          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-entrega-de-transferencia-monetaria-de-jovenes-en-paz/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Esta transferencia corresponde al ciclo 1 de 2026. Más de 12.000 jóvenes en el país recibirán los recursos. Bogotá D. C., 24 de febrero de 2026. Prosperidad Social realizará este 27 de febrero la transferencia monetaria condicionada para los...</t>
+          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
+          <t>Por paro de docentes en Bogotá: Secretaría de Educación advirtió que los profesores tendrían que trabajar en sábado</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1097,91 +1097,91 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/paro-de-docentes-en-bogota-secretaria-de-educacion-confirmo-reposicion-de-clases-si-el-profesor-se-ausenta/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
+          <t>Una estrategia coordinada busca que los centros escolares registren y reporten detalladamente las asistencias, horarios y participación de docentes y estudiantes, a fin de garantizar el desarrollo normal de contenidos curriculares</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
+          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
+          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
+          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1206,24 +1206,24 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
+          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
+          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1253,24 +1253,24 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
+          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
+          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1300,34 +1300,34 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
+          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1347,59 +1347,59 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
         </is>
       </c>
     </row>
@@ -1411,64 +1411,64 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/cultura</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1488,87 +1488,91 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
+          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+          <t>https://www.diarioadn.co/seccion/cultura</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1578,39 +1582,35 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1625,10 +1625,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1638,7 +1642,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1681,7 +1685,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
+          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1696,12 +1700,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1711,12 +1715,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
+          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
+          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
         </is>
       </c>
     </row>
@@ -1728,27 +1732,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
+          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1758,10 +1762,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1771,22 +1779,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
+          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1801,7 +1809,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1814,7 +1822,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1844,39 +1852,35 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
+          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1891,77 +1895,77 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1981,20 +1985,24 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2009,7 +2017,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2024,7 +2032,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2032,12 +2040,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2052,22 +2060,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -2075,12 +2083,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2100,17 +2108,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2118,22 +2126,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
+          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2143,39 +2151,35 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2190,7 +2194,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2200,7 +2204,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2213,42 +2217,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2264,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
+          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2290,7 +2294,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2298,12 +2302,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
+          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2318,12 +2322,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2333,7 +2337,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2341,17 +2345,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2361,35 +2365,39 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2419,7 +2427,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2427,12 +2435,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2447,7 +2455,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2462,7 +2470,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
+          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2470,17 +2478,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2490,7 +2498,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2505,7 +2513,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2513,12 +2521,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2533,22 +2541,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
+          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2556,17 +2564,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Estados Unidos hizo llamado de atención a Colombia ante la ONU por aumento de reclutamiento de menores de edad:“Dudas sobre impunidad al terrorismo” - Infobae</t>
+          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Blu Radio</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2576,12 +2584,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2591,7 +2599,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNNFJLRzNtTGZtU1ZCaVUxbGR1QUhBMzV5eFVUT2w4TWZVZnNfYmNMX1IydEVyYnhGT3ZJcDZMaG85R0RUUU9LaEsxT0hyYTFEcy1lNmVTMTA4TWlTbzJ2NmJNbTdxTXZQeUVsczJGMTdSZVlYVHlwblhqeG53UzZ5QkhsMVFyTWRORUQtOUNJMXFBSzJiNkZGQjJSZ1lvcWdfUHFTN1duQjJvcWVyMEZIZE01OGMyakhIQk5WbkROZlpIaDg5UHJRLWdEWVVSRlN4N21hNlhvemlncnlCZlNsM1BvYlJrX2hnUEpmREFCT1pzWS14YmtLMzNHWk1ndnN1NVE5YUdaajNmelBLZEViNEFHNHdjbFhqZEHSAbQCQVVfeXFMTXBsTHJ3d1N1RXh4WFdBdjAtMVFYcEJTV2xwd0xHZERGQVlHNXNvcW5hYmdpN09Wd1ljMjR4RjNSRWMxMl8xMmN5TzN2XzQzUDhCdlJ2WjdNSklzMG1yRzI5YnRnRDFhYWo3Wi1wOEdNbHE4UElzU2FGN3Z2b29XX0Z0bXBDczQzbE1oRE9zVjk1VG9OMzZSNlhsbjlFZUp4em84bGxJSTJyRG8yOWlvUkxPZkhVT0picHVCXzRRX2dhY1VTTWlJcUFYRnVBQzV0ck10YkktYXVpSE5uNm40U1lneGt5c0p5VUNzYnl0NEpqWmVLUE5UcWxOT1BJbnFDZmJRSG9XaTYyMXhqT3dhekhSUDBLSnh6dGxBNFNNYzktYTdZMmxmZm13bXhDd2x3Y0tvWkM?oc=5</t>
+          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2599,12 +2607,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad - Infobae</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2634,7 +2642,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQSmlvdlUzeHJlOVhEOTBjQVN5TlhCWkNmaUNEQnczelA1YWVHXzJ1ZHZkM2JKcWdCNzdKYkViRnQyaFpldFB5MGQ4SU54WDVoVGNlbWdRQzJhM0hvRGFaaF9MR3lxUWhSbGJUTFNKcHVmQjJ4MjlibnNuaGNVcXVaVE1aa0stdmFzYmxvTnlmc1hwMFdQUDJGVkVuS2Y4NTgydk9zQlZsU2l0OXA2NjUzZnk3SnpDOUx6RjItNE9EYWlscDBlR19XV1pIdEgxVF9XT2RWMHItMmdEeHlqdmdfYzh1X0dIT2lLNjlvR2RsRWhDZ25iMWVGbTNzaUtQZy1STHfSAZwCQVVfeXFMTXRiNGt6QnJSZDJ3NXItNWZ1enZWUkZmMEhPSm5pNWpLT2hSLXdLWnBzOTFLcVdzM3Q2SWZ1UWpzdU13NjVDNUR6S2o5N1BhOWdlYWEyVDh2bGVqTE1LR19KUnFaUFJEVWZhTlZ4Z3RwV3J2U1I3VmtReVVaTGxMTldfeEZmclhOby1iaFpVU2ZjOUJqRERwNFlMNVdzbDVFX3BQWmg1YjNhY0hrQWJ4UW53Z0lRTWlLWFEyWm5Jck5qX3ROSXVqZUxtTHM3WDk2TDJzUDJUN21VTjkxamZMRUd2Unl3emJEaGJxejJPdFViSkNWbTRudzNRUmE4bFg4a1JaLURLa0lQakk0U0kyRFFwV0ZlRHBtZ3VNc1Q?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/24/estados-unidos-condeno-a-cadena-perpetua-a-manuel-poceiro-turista-que-llego-a-colombia-a-explotar-sexualmente-a-menores-de-edad/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2647,22 +2655,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Estados Unidos reclama a Colombia ante ONU el incremento de reclutamiento de menores de edad - El Espectador</t>
+          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2677,7 +2685,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPVFRDQXk2WVcwQVhLTmljT1B4akFGM3ozQlBvc3QyOHJua1BfT1hxRnFJY212eFowWTVTdVBmTHN6d2REcXc5VGVuUmw1LWsxNWxOeW82UzBPaVQ3azZfQVNSb0pUTHFqTHdGVWJXS2Z5YmVSbXZJSXd4dzdTamNXdUtqMTRwVDV4MF9acHJFX1pTZ19NVVNvLWdNb1Y1d0FzZlN2dWVMamlvVlNCN01ZS2MxZDh1M250d2tsNEVpc2NYRUJXcE9KYk0yd1FHU3BiNUtFOENRdWZ4ZHdsR0l2cFRFMEpKTGYtaUk4dmhuRjhyaVU3RDYxbUpCUzjSAZACQVVfeXFMTmxJSVphakhMc1dSdUhqdDJFZW00OTIwT0NRNndiZGNtLWROVW1NZFFHWHhTMzVYb3N6aHRBV1NObF94cEVSeHZMOWpPTW1oVXdGeDloRU9uSWpIUXNldU1qY2lUM3dNWnhwMUNESWVTUy1SNGYzZkM0Nk1ORE9zQkNkdzc1MnJpUldVTnhKeUsycE1rcGdwMi1SN3F4bkZUdHZGNUJWT1RLeS1ZMFJUVkdmOXpHcnpId0N2QW9oOEVsbkYyVU9xbUtnTEVBdW1kNnlOY2wwVGVUY1dCc3N5WkQ5ZTBRUTFKSndYUU4zYVU2aUc1cUlsLUt4d3B6OTZ4Xzl0cC0tMFAwQ0hwM2JWUC0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQSmlvdlUzeHJlOVhEOTBjQVN5TlhCWkNmaUNEQnczelA1YWVHXzJ1ZHZkM2JKcWdCNzdKYkViRnQyaFpldFB5MGQ4SU54WDVoVGNlbWdRQzJhM0hvRGFaaF9MR3lxUWhSbGJUTFNKcHVmQjJ4MjlibnNuaGNVcXVaVE1aa0stdmFzYmxvTnlmc1hwMFdQUDJGVkVuS2Y4NTgydk9zQlZsU2l0OXA2NjUzZnk3SnpDOUx6RjItNE9EYWlscDBlR19XV1pIdEgxVF9XT2RWMHItMmdEeHlqdmdfYzh1X0dIT2lLNjlvR2RsRWhDZ25iMWVGbTNzaUtQZy1STHfSAZwCQVVfeXFMTXRiNGt6QnJSZDJ3NXItNWZ1enZWUkZmMEhPSm5pNWpLT2hSLXdLWnBzOTFLcVdzM3Q2SWZ1UWpzdU13NjVDNUR6S2o5N1BhOWdlYWEyVDh2bGVqTE1LR19KUnFaUFJEVWZhTlZ4Z3RwV3J2U1I3VmtReVVaTGxMTldfeEZmclhOby1iaFpVU2ZjOUJqRERwNFlMNVdzbDVFX3BQWmg1YjNhY0hrQWJ4UW53Z0lRTWlLWFEyWm5Jck5qX3ROSXVqZUxtTHM3WDk2TDJzUDJUN21VTjkxamZMRUd2Unl3emJEaGJxejJPdFViSkNWbTRudzNRUmE4bFg4a1JaLURLa0lQakk0U0kyRFFwV0ZlRHBtZ3VNc1Q?oc=5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2685,27 +2693,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
+          <t>Estados Unidos reclama a Colombia ante ONU el incremento de reclutamiento de menores de edad - El Espectador</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2720,7 +2728,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPVFRDQXk2WVcwQVhLTmljT1B4akFGM3ozQlBvc3QyOHJua1BfT1hxRnFJY212eFowWTVTdVBmTHN6d2REcXc5VGVuUmw1LWsxNWxOeW82UzBPaVQ3azZfQVNSb0pUTHFqTHdGVWJXS2Z5YmVSbXZJSXd4dzdTamNXdUtqMTRwVDV4MF9acHJFX1pTZ19NVVNvLWdNb1Y1d0FzZlN2dWVMamlvVlNCN01ZS2MxZDh1M250d2tsNEVpc2NYRUJXcE9KYk0yd1FHU3BiNUtFOENRdWZ4ZHdsR0l2cFRFMEpKTGYtaUk4dmhuRjhyaVU3RDYxbUpCUzjSAZACQVVfeXFMTmxJSVphakhMc1dSdUhqdDJFZW00OTIwT0NRNndiZGNtLWROVW1NZFFHWHhTMzVYb3N6aHRBV1NObF94cEVSeHZMOWpPTW1oVXdGeDloRU9uSWpIUXNldU1qY2lUM3dNWnhwMUNESWVTUy1SNGYzZkM0Nk1ORE9zQkNkdzc1MnJpUldVTnhKeUsycE1rcGdwMi1SN3F4bkZUdHZGNUJWT1RLeS1ZMFJUVkdmOXpHcnpId0N2QW9oOEVsbkYyVU9xbUtnTEVBdW1kNnlOY2wwVGVUY1dCc3N5WkQ5ZTBRUTFKSndYUU4zYVU2aUc1cUlsLUt4d3B6OTZ4Xzl0cC0tMFAwQ0hwM2JWUC0?oc=5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2728,12 +2736,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
+          <t>Estados Unidos hizo llamado de atención a Colombia ante la ONU por aumento de reclutamiento de menores de edad:“Dudas sobre impunidad al terrorismo” - Infobae</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2748,12 +2756,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2763,7 +2771,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNNFJLRzNtTGZtU1ZCaVUxbGR1QUhBMzV5eFVUT2w4TWZVZnNfYmNMX1IydEVyYnhGT3ZJcDZMaG85R0RUUU9LaEsxT0hyYTFEcy1lNmVTMTA4TWlTbzJ2NmJNbTdxTXZQeUVsczJGMTdSZVlYVHlwblhqeG53UzZ5QkhsMVFyTWRORUQtOUNJMXFBSzJiNkZGQjJSZ1lvcWdfUHFTN1duQjJvcWVyMEZIZE01OGMyakhIQk5WbkROZlpIaDg5UHJRLWdEWVVSRlN4N21hNlhvemlncnlCZlNsM1BvYlJrX2hnUEpmREFCT1pzWS14YmtLMzNHWk1ndnN1NVE5YUdaajNmelBLZEViNEFHNHdjbFhqZEHSAbQCQVVfeXFMTXBsTHJ3d1N1RXh4WFdBdjAtMVFYcEJTV2xwd0xHZERGQVlHNXNvcW5hYmdpN09Wd1ljMjR4RjNSRWMxMl8xMmN5TzN2XzQzUDhCdlJ2WjdNSklzMG1yRzI5YnRnRDFhYWo3Wi1wOEdNbHE4UElzU2FGN3Z2b29XX0Z0bXBDczQzbE1oRE9zVjk1VG9OMzZSNlhsbjlFZUp4em84bGxJSTJyRG8yOWlvUkxPZkhVT0picHVCXzRRX2dhY1VTTWlJcUFYRnVBQzV0ck10YkktYXVpSE5uNm40U1lneGt5c0p5VUNzYnl0NEpqWmVLUE5UcWxOT1BJbnFDZmJRSG9XaTYyMXhqT3dhekhSUDBLSnh6dGxBNFNNYzktYTdZMmxmZm13bXhDd2x3Y0tvWkM?oc=5</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -2771,12 +2779,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2796,7 +2804,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2806,7 +2814,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/el-club-mas-exclusivo-de-la-educacion-colombiana-solo-cinco-colegios-en-la-categoria-mas-alta-de-importante-ranking/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2819,7 +2827,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
+          <t>Docente indígena en Risaralda enfrenta cargos por presunto abuso sexual a estudiantes de una institución educativa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2839,7 +2847,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2849,7 +2857,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/21/docente-indigena-en-risaralda-enfrenta-cargos-por-presunto-abuso-sexual-a-estudiantes-de-una-institucion-educativa/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -2857,12 +2865,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
+          <t>En el regreso a clases, el sueño insuficiente en adolescentes duplica el riesgo de problemas de atención y conducta - Infobae</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2877,7 +2885,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2892,7 +2900,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTjNaNDNPUHFZYzdoUlNIaUJZbGlqb2JPZndHd3Rad0F4VGwtRHFFQXdzaEIzRWN3bndOTjhsa0JReEtYS1B3TWN5ZVhaRG1RZGtxTkVDVVI2TWV0aTFxTC1KZUJfT2NDZEpIc0tLckJjMmhEOHZvZjVHaEhGRDB2c2NxSmw5SUJpVi0tUlVaZDI1cDgyY1p5QzVRMTlMQ0NOMlkxNGlad243SzF0TFJXZ3RNRGtRY0xtSW5VSnNZaHZCYUJWWG83RzBEZEY4dUFZYUxtLTlqVGx0bWVjbk9vMzFBS0o2LUlyTXNLb3M3ZzbSAYsCQVVfeXFMTTZoYWJjUTZubmFSQjVXNzlCZkdxTkhLby1HTG1iUmdWVVNSMGZpM3EwNkd3U3NSaVhDZWJJeHpQcC1KbUlUWjhFMERwZVBmRXM5NnJVNFQ2RmFDZmNSaXlkOG5tYWhlZlFydUw5X0xVZGkxWmVIM0tuVmd4eHBOMF9SSExuc2tzQ2stNU9kdjlCemxvZTV4MUlVbElWT3dmYmVSYXE0c0VUQTRUTGtYVDZ1SmRKU0R6Z3ZlTEExQmVMa0RDRHl2ZVlvUmVTQWl3aVJJM3hrQU5rMlpLVUYzOUNjOVBDZmVzdWtoeFdqT3JLaUdGY2JOaUw0MnJyQXVNMTQ4Wl9JNHBaYjdv?oc=5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -2900,12 +2908,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
+          <t>El club más exclusivo de la educación colombiana: solo cinco colegios en la categoría más alta de importante ranking - Infobae</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2925,17 +2933,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxQdlZHUENSeWozNzYtd3djZFRrTmxGeE9sXzlpNDFXYXVyYUlLWWQza0V0MlZBTVRxWmI2Zm9GNk1zMVBlWFI0NDY2Yy1kYjdmOUh4VGg1VnpxZERDWFFMM2tGZ1VVMVBDMFFUWE10SFkxLUJ6am1zYm4zYTVSUEc0Zmx1eXdHUEw2STFiNVRINUs4alBQV28xZGpTYV9RX3NaMFhsN3BMVWU3N2JtZ3UyNjdrYl9DMmJVTC01blVkblh6Q09PRzJuTVZyMFdSYnhOM1M0cFZvNXRlSGhOSzdfMDJzTHNqNndIVEIzOHEybWVDd9IBjAJBVV95cUxPQkpOR214eE1HM3l2WTFaQ01jNmRIa25id0psWW5TVmFibHFrNGxnYkxSTDNzajlYcWg4UjBMelQ5WXVaX3RjaEI5cnRqNDlVdGpyenJvTVFPMEZLeExwMUNFUWlWM2d3NTRlOWJHb0tuck5wVnlkNGZ3MkJsUXhCQTZFX3N4MV82V1B2V0pMWmdWZE43UmlHLXQxOEV1bndwdy01YWVhRmJVd2xVcC1XaDJDVWxvNFVNcEJMSHMtMHRiUENjUTBIRURsZXU2ejZuLVR2UDI2ZzJaTFk3QW1ZWGNQYVlWZ0MwNlVXaUF0SEo4Uy1pdzFKSkFFWjN3WkpLTXBKdEo3MUVZZnk2?oc=5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2943,27 +2951,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
+          <t>Así fue la reacción de jóvenes españoles al descubrir los múltiples significados de la palabra ‘cachucha’</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2978,7 +2986,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/19/asi-fue-la-reaccion-de-jovenes-espanoles-al-descubrir-los-multiples-significados-de-la-palabra-cachucha/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -2986,17 +2994,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
+          <t>Este es el calendario de vacaciones y recesos en colegios públicos de Bogotá en 2026, prográmese</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3011,71 +3019,63 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/regiones</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/01/17/este-es-el-calendario-de-vacaciones-y-recesos-en-colegios-publicos-de-bogota-en-2026-programese/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
+          <t>Mejoró la ocupación laboral de la juventud: ¿cuáles son los puntos ciegos? - El Espectador</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOaUM2MXFDODhjdXVZLS1BUG9oUm52dEExRVFkb3hiZ2RCR3oyM1AwUEV2SEhIZTVjRlhWdnJ2dUdkRjE3bVhtc2hUcFpSODVCWkgyZG83T3ZPQ2ctY0l6ZXV3UVBxYmxxRzhEcDdQYlVkT3Rvdk83eWRGZkpNVEpfSEs2Y3A0V3BGcnhiQ3hwVENoZjZQS0J5SGp2VDhFVS1rM3JKcnhxdnpIR3BjWDdObkpkSE0tdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
+          <t>Yumbo se pone la camiseta del futuro: lanza Aulas STEAM con inversión histórica de $ 9.500 millones</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3115,10 +3115,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/regiones</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Iniciativa busca impactar a más de 10.400 estudiantes</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3128,7 +3132,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
+          <t>Corte Constitucional fijó nuevos criterios para el manejo de conflictos escolares entre menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3143,12 +3147,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3158,7 +3162,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOOVhMdnBkeXFCaTNlNTNGX2ZaTGxqVnB0b2FIZ0owQTl3LXFiUldIQ2FhOFJZeGdEa3FJTjRoMkxuTHFYNFFBTTVMakFUY0tob051TWxCOVluajg1d24tdWRxM256TTFndk9FSUQ5b2FpNGY3U3ZxQ00za1JhYThoamVHUnBRVUdySkNHNzFhU1JFQ0JsLVJ1N0ZZLU1EdE5tcUViVXluc2hTWm0zblFKcWxXdW9mVDZic1FTWXpyS1NLTWNaZmlEMXZ1T0xoYVR4U2xwZjVycEtkOE1EQlBYLUtn0gH8AUFVX3lxTFB1aVQ2NGIzQ0hhVm54dGlrb0Q4WWtXUVFrdVA0N2dyVEMzWXN3T1p1QmlVZm4wQzdXZmJnZU5TcjlLSFFGTEZwODlYU0FmTU5ra0wtOEhuUWJVMWh5eXlqVEg2WGhHM2tMOVZwMkxTM25vZUFtRHA0S3JjQ1l3RElwVE8wWjRZSWhCcE5Ib1gwWXVpZ09TM2dvOVc5bzBFbFRWdmtYNUZSTzR3T1VrU1I1V25nLWlDSWsxRVJWUmczUFo2Z2lQNTBhOTR4MzhKZDc4YjJxSXJoaU5OU016NGdDX3JtTXp4dVNBTXozV09XSUhRaTJ0ckJvMS00Vw?oc=5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -3171,112 +3175,112 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
+          <t>Radiografía de los ‘ninis’ en Colombia: 2,26 millones de jóvenes están desconectados del estudio y el empleo - Infobae</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQQzU0U2tHY3lvTUVKRmR2SExOeUdySS0ycnZSVWd3MlhIQmJmYVZxNm9NNVZ2YU8wZ1MtcUJiOXRPLWZhWUNLcUtVdG1uUVVUd0VfYU5sQWVNSjlDVWdDUTc2ZG8yajJIUlk0bVJxTTR3clhjd0wwRl9wSTRSUlk0UnZtY2FZTWZ2QUhQbjJ1TkdibEw4YmU4YXNTMEJUeV85V0dfSzdUQ0hSSk5DbFdZUk5VV2dnaGdabHhVQ1p2bjlCTlVKNHJNV3NoNmQtcG9CUkZaMWVDVXZmWDFXSTIxVi00UdIB_gFBVV95cUxQQXJkUXE5UnM4ZVhIZHo3UFJuSU0xVllueWt3Unk2aC03YllYdDBfc0FvalRGMDNsWjBRNmZfNUV1bTlsbWM3dFlLOGNCajVqcXQ5Z2hVRzdROXlpTUdrWEtLdVNyaDFqRGlnckQ3OUhfTjVNVk53YklESGhMMlRCcUVkNFRYMS04RUUwR2hvdERISVdENVlydzZhOGpfaU1yX0xkSkg0S3laV3E2MVV1UHRDN05aRU1iMlBiS2lRcXNWYTdMTlhVTzI2VkJkeFZTXzhqbS1adkpFa1RiX2dBaDJDaWhVYXVsM1psSV9jWjZGdy1QUXJ1d0xCdUxMdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
+          <t>Casas de Juventud lanzan nuevos Semilleros Distritales para potenciar el talento juvenil en Bogotá</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#f8686f5026</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>•Bogotá abre la convocatoria a semilleros gratuitos en artes, deporte y cultura urbana, dirigidos a jóvenes entre 14 y 28 años de todas las localidades, como una estrategia distrital para fortalecer la expresión, la participación y el desarrollo de...</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
+          <t>Distrito Joven acompañó a más de 50 mil jóvenes en la construcción de sus proyectos de vida durante 2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3291,20 +3295,24 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#729a4b8e04</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>• Durante 2025, la Subdirección para la Juventud acompañó a más de 50 mil jóvenes en Bogotá, fortaleciendo sus proyectos de vida a través de una atención integral. • Los servicios y estrategias implementados promovieron la inclusión social,...</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
+          <t>La caída del “capo dei capi” de la Cosa Nostra: de una infancia dura al líder más temido de la mafia siciliana</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3324,7 +3332,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3334,7 +3342,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+          <t>https://www.infobae.com/historias/2026/01/15/la-caida-del-capo-dei-capi-de-la-cosa-nostra-de-una-infancia-dura-al-lider-mas-temido-de-la-mafia-siciliana/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3342,12 +3350,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3362,22 +3370,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/el-desplome-de-los-colegios-privados-en-bogota-no-se-detiene-35-cierran-sus-puertas-para-2026/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3390,7 +3398,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
+          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3410,17 +3418,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3433,7 +3441,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
+          <t>El desplome de los colegios privados en Bogotá no se detiene: 35 cierran sus puertas para 2026 - Infobae</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3448,22 +3456,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPa1M0STVRWFpyLVgzeEMwUW9fTDdXVWs5RzdvbWt0WE9ZcHFZZVQ3dnhQMjh2TnJqaUV0eFFESUk2YzV3MkxVMTNNLTI4VUxrdnhUcy1Zck5WMHZVQVVYY0hEZFdwTUF1RUNJcmRQMWYwR1JfaWNvR0JQYlNDZ01BUi1lQzBJWTcweFBFMm13aVA0ajdqbTFncDJ2VTd1VjFkUUViNU1HWjgzb2ZvWWJqZjg0bWdFMjVTN1BlOEJBUUdGSnFjNUFfNDdRakZFcjA2ZDUyQ9IB7wFBVV95cUxOT05HTjcwSXlhWFBKN3dPUXd1enFRVE5UenJpZENPOTB1U1RuZTRKODN0aVc1MVpuaS1wY1pTZ1laemFkeE5zWHAzWF9aZXlYOFE0cUk2M0dRY3g1amRMUXBRNEd1VzNVdVljWHlMeVAxRWliWExhQWZFQkFvdVhXaVk2dnd2eFowVXVoN2hoc1FhNHNtdVBaQng2Y0pjTTJzR08xRktlenRmQnBnWExqSExKU3FBeEljT2c0MGxXLVo1VWFFQWlpNFUtbmx3Z2RZLWtqV0JwNlhLMWZWNFRUb3MyTXp1VHdMdllnTFI4SQ?oc=5</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3476,7 +3484,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Menor de edad colombiano fue baleado frente a su escuela en Chicago, la familia exige justicia</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a enviar mensaje de terror a otros niños</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3491,12 +3499,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3506,7 +3514,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/14/menor-de-edad-colombiano-fue-baleado-frente-a-su-escuela-en-chicago-la-familia-exige-justicia/</t>
+          <t>https://www.infobae.com/colombia/2026/01/14/menor-que-fue-secuestrada-en-el-catatumbo-denuncio-que-las-disidencias-la-obligaron-a-enviar-mensaje-de-terror-a-otros-ninos/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3514,17 +3522,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
+          <t>Menor que fue secuestrada en el Catatumbo denunció que las disidencias la obligaron a grabar mensaje de terror a otros niños - Infobae</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alerta Bogotá</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3539,17 +3547,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.alertabogota.com/noticias/local</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObmZIdEpqTkVXcjc4UjRzR0hob1dZYk1GUUljTXNIc2psanNtWU9YZjJRaU41NWNsR3FaUUpmR0JhQTVxdEpvUXBCbjZFcWFtWXBwTFYyak9tc3Nldng1d041LVlkWGZLRm5ULW5OU2x5b1NIbHJTUTBJY3ZDbHB4ZThnUS1JV09DUm0xVEVSMV9TZ1BpdktCRzFTNnA2LUwxQnpBLTZxWHJoOXhXZTV4ZkNrRlFFSHNjNjBqOUF4bW8yNUY2el9DUDdlbU1iNXRHTGZ3eEV3d1JBNGRuUFhzM0hXd1RmdDhoYS1tM2otLVZmLUFROE9iSHYwZlRfQdIBmAJBVV95cUxQeGhobjhnanVFNTItaDNFczFzbWZBeExqSEo0bXo0LVZGYVFHcEtTTW1Seks2T21Ya19QcVVIdzJsbjgxVUJVWHE4MXZyMmVTYXBkeGdvXzAzSGljU0YtcERJdDcweFgwcVdvOFRWX0d4cEFKcG10dGc5UkVOeVZRN1BOcEREWUJwa2Q4Y1VXU0ZJR242QWtIdlFHWkQ3LXR0cnlDVE1WYU90SV9HUmdqdVI0T0FIbkwzbXI1TXZpbTNvWnNwWl9iOWF1dXZ1eGh0Zk4xSmpTUmhMdEZVTy1CeVBtS3VaZHJwY3BrS3FuZmszQTZxOWh1TkdzclZOVFU4cElBY3JRMUtDYm81djJ6XzR0YTVRRW5J?oc=5</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3557,17 +3565,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
+          <t>Estudio reveló las principales problemáticas que preocupan a los jóvenes en Colombia, previo a las elecciones de Congreso y Presidencia - Infobae</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3577,12 +3585,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3592,14 +3600,10 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/actualidad</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNYXdTSFVia3cwbnV6Y050TzB5M2JQckhpbDVVajdoRnZnZG1yTThKbVF0bFhsUWN0ZnFuM1h5M0VYWmxiUGZjaHN3WV85OFpwWlFaWkFkanlsSmcwNFhJQk5PTjJBZ3RXcTgzNHFCQU5qTGlUZlB3WTkxZmx3SVIwV05jblIwUFNNUUdBTkU2M2FZSHNlTUgyb2ZhZWsyMktyc0UtR2k2Z001NkUxZ01xSkxoei1uMUZqaGJfV0k2MWktaDVNRGtGOS1nNXlGTEdSZ1VSdEJGRDRkbkNPM3R1aURVbl9ZR3FYcC1aMkI4T0k4bDJaT0Jmb1dLNktqQVVOeHVpUGpkUGd3TmvSAaYCQVVfeXFMTl9Uc2p1OEVpYzZaLUFYOERNUjVQVjVSaHJtTEhhT1BibW1BMkVwQ0VVUFc3d2RsaWNtNHdTZm0tbDRlMHBPLWVES0Vyd3hKZHRQUmExYmVmaXNrZE5rTGhEWmd0YXQ5cjdPOGIyeVdEYUV5NHplUnFMX2pYWkRXdEFxbVB1UGhEOENhTWM3S2NCVnJQbDg4clVoSUhIWENVSUh1VE54MjZKUjF3OWdpUDZjdld4WU1BLTA2dWR2ZEwxQUpnLUNXS3JZZ2hWUkFQN2taQktacVNhM3NMOS1ZR1g2dkhmYmVmU0Q4Q0o2dWNCZUNMQnJsaDFjQlRXQUp5NUpEYllxWlhVQVVfbVlBdmVBa2RJRjVqNUNfTGxHMnFRaGhYMnN3?oc=5</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3609,12 +3613,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
+          <t>Estudiantes respiran con el aumento del pasaje de TransMilenio: no tendrán que gastarse lo del almuerzo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Alerta Bogotá</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3624,22 +3628,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
+          <t>https://www.alertabogota.com/noticias/local</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3647,17 +3651,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
+          <t>Tres estudiantes resultan heridos tras caer desde un bus de dos niveles; autoridades investigan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3667,12 +3671,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3682,30 +3686,34 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/actualidad</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Los menores, de 13 y 14 años, tuvieron que ser hospitalizados.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>¿Cuándo entran a clases los colegios públicos y distritales en enero de 2026? - El Espectador</t>
+          <t>Treinta niños quedaron sin aulas en zona rural de Nechí, Antioquia: incendio incineró la única escuela de un caserío</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3725,7 +3733,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVGV3a0tQeW5uLVpJdlBBT3Rrc0NrUm9Va3pHY3NYMko1d1N4bjUzdjVYZ3ZjZWZpQ0xYak0yQVNLdFRsVXJxbnJMSVJVT3ZyaEZ4ZEZIU01RWVoyUHd6Q0hiNFdCMElNeXExYXVrQVJaQU8tN0RUMC0xZERQdFZ2aWo0UXQtZTZ5VmN6NE9YSjlhYUVGd01ycDBCaC1RMEhUcmk5TTdEekozS3g5Ry02SEVTOWprUdIBygFBVV95cUxQMlJDNFNLREl3U2ZaeXVGYy1GS2NmWlVydW1DX24wRE9NOVhBbzhqNWNzMmhTNEdTa0JFa281R1FVRUFfdjlUXzd2Nl8xTGxMb3JIaUVxOG1DTTBwRlluV1B3QVF6QTI1cEd1TTlVQlJiVWJkLWFFRFo1RlVsQjRMS2ZmTDhpUTY3bGdfRzlXWmliT2NybEFPcnRfaWJpX3UtazA0ekRpOFpOeU93TGNsOTV6Ynp3VkhKRnVPcmswemZHYnZNQUxrWHNn?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/13/treinta-ninos-quedaron-sin-aulas-en-zona-rural-de-nechi-antioquia-incendio-incinero-la-unica-escuela-de-un-caserio/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3733,32 +3741,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Niños colombianos pasan 8.9 horas diarias frente a pantallas: qué efectos hay en su salud - El Espectador</t>
+          <t>El particular castigo de Policía en Barranquilla a un grupo de jóvenes quedó en video: “El cuerpo sufre”</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3768,7 +3776,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZkRQZ0I3REZBYkZoNlVha2RNQ3F6dmlSYU5hTTBBOGkzMlBSM2xXV0RsMFRKcy1XRG1xWWNmQk5mUWE3ci1BMGZpNGZHeHFjcDBmdGQxb1cwNG95V0R0RVNodGlYcXFFcHRLdWU3bWgtSC1vV2YwTE5wVVpBejlZd2ZmRENoVTl4cDNnNWQwUDBxRFlIak83MjRYelRLRVdodS1wNnRLeC1wS1ViT2Y2SDhOSmdYZ0taY3BDNmxYMUpuUdIB1gFBVV95cUxOTUtIYTlOYUdmTHVzRmZWQVNGRkVsdDk3cEg4bDlRaXhVRUZyd2tBOHFXUWplMUtQYUpRX29LbDZNOHhDcXc4OHQ0OTVNS1I3cElDR1RRNFliRXA0UjV0Y1kzbmdzRzFVSnNYUlZUeEN4OEt1SnZDbXRzQ1hycHoxRTE1RlZzNk5BR1o2LTBTTWZka01pR2oycmV1MWlZY2ZoSjVvRlBvMWVLODJMbnFaZ251aU0zWGZqWHkwX1lMTEZCaC04ZEQwZTNTaU1ycktSUDhuRVRR?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/01/09/el-particular-castigo-de-policia-en-barranquilla-a-un-grupo-de-jovenes-quedo-en-video-el-cuerpo-sufre/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3776,32 +3784,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
+          <t>¿Cuándo entran a clases los colegios públicos y distritales en enero de 2026? - El Espectador</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3811,7 +3819,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVGV3a0tQeW5uLVpJdlBBT3Rrc0NrUm9Va3pHY3NYMko1d1N4bjUzdjVYZ3ZjZWZpQ0xYak0yQVNLdFRsVXJxbnJMSVJVT3ZyaEZ4ZEZIU01RWVoyUHd6Q0hiNFdCMElNeXExYXVrQVJaQU8tN0RUMC0xZERQdFZ2aWo0UXQtZTZ5VmN6NE9YSjlhYUVGd01ycDBCaC1RMEhUcmk5TTdEekozS3g5Ry02SEVTOWprUdIBygFBVV95cUxQMlJDNFNLREl3U2ZaeXVGYy1GS2NmWlVydW1DX24wRE9NOVhBbzhqNWNzMmhTNEdTa0JFa281R1FVRUFfdjlUXzd2Nl8xTGxMb3JIaUVxOG1DTTBwRlluV1B3QVF6QTI1cEd1TTlVQlJiVWJkLWFFRFo1RlVsQjRMS2ZmTDhpUTY3bGdfRzlXWmliT2NybEFPcnRfaWJpX3UtazA0ekRpOFpOeU93TGNsOTV6Ynp3VkhKRnVPcmswemZHYnZNQUxrWHNn?oc=5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3819,32 +3827,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Estudiantes de Medicina anunciaron protesta y Gustavo Petro les respondió: habría plantón en 17 ciudades - Infobae</t>
+          <t>Niños colombianos pasan 8.9 horas diarias frente a pantallas: qué efectos hay en su salud - El Espectador</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3854,7 +3862,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOckVuZWpkQV9QTnd6UzZmSXdvNl9xX3plZHNIRkV1X2liZTJmYjRHY05uVDc5M09nekFlMDVwVS01WWtsZmstN1VtZkc3M0E5d0xGd1lRMzh5c0Qtc09iei1pVmdSekozWUVLenM5YVRtTms0R3BJdEZocU9YVE5wUEo0UVdLRnQ3cENPWm1ETmhsbjFULThLTVRKanQwSTVvM2hCQW5VODlJejZkRkpYUHpzREpEeDY1M29UaV82cUZQVFp6OEpmRVlxRTBzQzFUcWlPbTVWOVQwSG9LVF9KcGhiejZzTWt2S05KYzdyeDgzbThZMmhkdUNQZTBBdGNHN2RletIBnwJBVV95cUxPOTVVOXMyRFBNN21yQnZ5RHkzMTZOMVYybU0xXzNzczIycm95cHdBcEFKc0d0VVlLT25PYWJkVDhnbUVMdlQwTHktNlJqNG9EeXFDQ1RSaG51Tnc4ZXlsWXpVYzZSZWl1MXVRQVdabXI5ZTRUYXdQblUzWmN5NEE3VW1PRF8yNWdHcjVsdXZ3STF2cUJlenZHbTluZkpKYzRvSlhDZVlNVWdnVjBqZEFuSHpuQnNwdUVMMjBkMm5JNUZVZkFfOHFUMHFpeEdLWGFzZ0Q0V0pZdzdrMXdpUkRsRVZQRVppU3hnTXZlU05GRWZlZ3hKUnBKdFlWdy02cXJRdE1YWUFsSDRZTXctSDRhSkRMMV95QlRPUkJIVV92Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPZkRQZ0I3REZBYkZoNlVha2RNQ3F6dmlSYU5hTTBBOGkzMlBSM2xXV0RsMFRKcy1XRG1xWWNmQk5mUWE3ci1BMGZpNGZHeHFjcDBmdGQxb1cwNG95V0R0RVNodGlYcXFFcHRLdWU3bWgtSC1vV2YwTE5wVVpBejlZd2ZmRENoVTl4cDNnNWQwUDBxRFlIak83MjRYelRLRVdodS1wNnRLeC1wS1ViT2Y2SDhOSmdYZ0taY3BDNmxYMUpuUdIB1gFBVV95cUxOTUtIYTlOYUdmTHVzRmZWQVNGRkVsdDk3cEg4bDlRaXhVRUZyd2tBOHFXUWplMUtQYUpRX29LbDZNOHhDcXc4OHQ0OTVNS1I3cElDR1RRNFliRXA0UjV0Y1kzbmdzRzFVSnNYUlZUeEN4OEt1SnZDbXRzQ1hycHoxRTE1RlZzNk5BR1o2LTBTTWZka01pR2oycmV1MWlZY2ZoSjVvRlBvMWVLODJMbnFaZ251aU0zWGZqWHkwX1lMTEZCaC04ZEQwZTNTaU1ycktSUDhuRVRR?oc=5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -3862,12 +3870,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Accidente de estudiantes del Liceo Antioqueño: bus iba con el 97% de su capacidad, sin cinturones y con fallas graves de seguridad - Infobae</t>
+          <t>Aumenta a 1.419 el número de lesionados por pólvora en Colombia; 428 son menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3887,7 +3895,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3897,7 +3905,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZGtNeVVBeHQta1Zhc2Z5YVpZR09qcnJZdnZCOGJ1TGdwbEktWVQ1UElPWmI2bEFEZUlOUGI5Z1J5U053TlBHcHkxclNnYlA2VU8zaWMwN3ZXdW9kdW1wTEJ5akcwcC1kZXk1eFZnQTlNT3JsUnRlRGNwTFpuNFZ4SnowUW5qQnhacGxHSTlCUXdRWDBXRjdHQUd1RGtkUjFJOXZhNmZkWXdfd0I3WGdYcWllRThlRkR4LXdQa1JNbDBlN2pyOUtJSU1zbGhob1cxUWhjeE03aXVJYWpLaTh4QmpyZGpXOVQ4dHJURUd2MWdtb01wd3hISTladGdKbDV1NmfSAZwCQVVfeXFMTmlvd2VmT04wQVNQWEh2LVQ3WXF6M0hZZU4wa3RKa3dUMEU3c3NPQmhONUoxbGNQNnJPR1dsUWp3d3pVT19vM1JoUnZNTWZIR1hWcjZXYXBNcVQ5OVN4dGR2S2dfbXZWclFFeU9GNUM2eEY3OWR5OWo5OUZTeXVSMWhKTHV0VGx6RFc4eVktSGFXdGJwa0FNWTd4b3hyakQxRWNJMXlOUjhiaEhtbXZhWkhDUmZ3ZVVTNGNfTEdUZjl3Z3VPT0VwVjZ5OHBOT0tEVmlZbTFKVUtXcU5JaWN0MnVpNWFLdmVtZTlaQV9Cd0Y3RUc3eXI1R3hrNnRXVnZELVliZTRrVUNaYXNsdFJ1Q2ZkRFpRSnhYcjl3NGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOY1FwS0xiWWVaYl9saTQ5X0xRYnVoR0lwNE5XYUVaaUl3LW8yN0hEZGFnckI5VVlrVnBPSFJpeDNkU1JIaC01dVJVdFJYbEtSVTFXRTBCdTFDSDJ6TXZjc2t5N0t0cVFUY2JGbGZ1NDB5R1FJVG1RX25hREVIMjZlYktrdHc2QUFiZXNQTXFGZk9zeWNJRUl1aWNCbG9OXzZRQVA2dFFUZ1J3UnJrZzU4Qnk5TVBMajBPenJOU0ZBekNheEl2SkV3QVRUc9IB5gFBVV95cUxQeDZfb0gzZm9CTTRpYWx1ZTBielQ1TVgtaHNBOXRVRjBDcVd2V3M2anR3VTJaLU8zUEFkbEJkdDFEcHdHQUlpNGVORDZXV1Jxdzl4YmdPN3F1bk10ODZ1MnpOUjVSRTZscUUzYl80MDVpaHROOXdBNlhoQkFFR3RyVVJ1MWw1WTVZZVcwWnZ6THBEYWkxR1hEMTQzRGIzRWJvWlVUOFFBU2duZE5MRnRoRnQyZDl0ajd2SEpUVVM5ZW5POEpzLUZIcTV1c3RaaHlvanRUcG1oU3REVFVVQk5xTnhuLWk1UQ?oc=5</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -3905,27 +3913,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>¿El alemán será materia obligatoria en colegios públicos? Esto dice el Mineducación - El Espectador</t>
+          <t>Estudiantes de Medicina anunciaron protesta y Gustavo Petro les respondió: habría plantón en 17 ciudades - Infobae</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3940,7 +3948,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFh6ZDVETFROR255WTE1dm1uNXhtaXg4aGNjOUtZblZDbU9RbnFhLU81Z29yVDZzeG1HcFpjeS12UFJNX1lSaXRRVWIyWUFyWkMyaDJobmNReFhjRzREcTFBTGFsX3RwNDRnUHhydUtWdEcyR0VFeVRXUlg5c0hJZlhydURCVG0zcmd0SkNVbk5qak8tbkJGWnducXNZV1hOUFEtSHRWbmVvOFRXSFM4aG5zbU9SOWJ2Y1RTRGNB0gHSAUFVX3lxTE5jTVU1LW82UDhqRVdjVnNNQ29LZXpEdTM1a2NiRlNUaVBBUnVCZ25hamlJM3RiZW9DNzBMYWNBanJaemVuaEdzUUMyOFljN0t3SU1ac0ZRNnBLWm1LNjAycG8yUFRTZllRWVIwTWV0dTN2TTM3WEt5ZWNNWFlia2VvMFdnNEZtMTlDSWhwX1ZLc3hCTDlvT20zd3ZJUEE2UVJVc1Z3bGpnOENxSWNYcExDX0hiaGxTMnE2dXBSaEJnRE9Od2VQdk1vQmVCUy1PdjlSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxOckVuZWpkQV9QTnd6UzZmSXdvNl9xX3plZHNIRkV1X2liZTJmYjRHY05uVDc5M09nekFlMDVwVS01WWtsZmstN1VtZkc3M0E5d0xGd1lRMzh5c0Qtc09iei1pVmdSekozWUVLenM5YVRtTms0R3BJdEZocU9YVE5wUEo0UVdLRnQ3cENPWm1ETmhsbjFULThLTVRKanQwSTVvM2hCQW5VODlJejZkRkpYUHpzREpEeDY1M29UaV82cUZQVFp6OEpmRVlxRTBzQzFUcWlPbTVWOVQwSG9LVF9KcGhiejZzTWt2S05KYzdyeDgzbThZMmhkdUNQZTBBdGNHN2RletIBnwJBVV95cUxPOTVVOXMyRFBNN21yQnZ5RHkzMTZOMVYybU0xXzNzczIycm95cHdBcEFKc0d0VVlLT25PYWJkVDhnbUVMdlQwTHktNlJqNG9EeXFDQ1RSaG51Tnc4ZXlsWXpVYzZSZWl1MXVRQVdabXI5ZTRUYXdQblUzWmN5NEE3VW1PRF8yNWdHcjVsdXZ3STF2cUJlenZHbTluZkpKYzRvSlhDZVlNVWdnVjBqZEFuSHpuQnNwdUVMMjBkMm5JNUZVZkFfOHFUMHFpeEdLWGFzZ0Q0V0pZdzdrMXdpUkRsRVZQRVppU3hnTXZlU05GRWZlZ3hKUnBKdFlWdy02cXJRdE1YWUFsSDRZTXctSDRhSkRMMV95QlRPUkJIVV92Yw?oc=5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3948,17 +3956,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
+          <t>Accidente de estudiantes del Liceo Antioqueño: bus iba con el 97% de su capacidad, sin cinturones y con fallas graves de seguridad - Infobae</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Noticias Caracol</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3968,7 +3976,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3983,7 +3991,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZGtNeVVBeHQta1Zhc2Z5YVpZR09qcnJZdnZCOGJ1TGdwbEktWVQ1UElPWmI2bEFEZUlOUGI5Z1J5U053TlBHcHkxclNnYlA2VU8zaWMwN3ZXdW9kdW1wTEJ5akcwcC1kZXk1eFZnQTlNT3JsUnRlRGNwTFpuNFZ4SnowUW5qQnhacGxHSTlCUXdRWDBXRjdHQUd1RGtkUjFJOXZhNmZkWXdfd0I3WGdYcWllRThlRkR4LXdQa1JNbDBlN2pyOUtJSU1zbGhob1cxUWhjeE03aXVJYWpLaTh4QmpyZGpXOVQ4dHJURUd2MWdtb01wd3hISTladGdKbDV1NmfSAZwCQVVfeXFMTmlvd2VmT04wQVNQWEh2LVQ3WXF6M0hZZU4wa3RKa3dUMEU3c3NPQmhONUoxbGNQNnJPR1dsUWp3d3pVT19vM1JoUnZNTWZIR1hWcjZXYXBNcVQ5OVN4dGR2S2dfbXZWclFFeU9GNUM2eEY3OWR5OWo5OUZTeXVSMWhKTHV0VGx6RFc4eVktSGFXdGJwa0FNWTd4b3hyakQxRWNJMXlOUjhiaEhtbXZhWkhDUmZ3ZVVTNGNfTEdUZjl3Z3VPT0VwVjZ5OHBOT0tEVmlZbTFKVUtXcU5JaWN0MnVpNWFLdmVtZTlaQV9Cd0Y3RUc3eXI1R3hrNnRXVnZELVliZTRrVUNaYXNsdFJ1Q2ZkRFpRSnhYcjl3NGE?oc=5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -3991,27 +3999,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
+          <t>¿El alemán será materia obligatoria en colegios públicos? Esto dice el Mineducación - El Espectador</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4026,7 +4034,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFh6ZDVETFROR255WTE1dm1uNXhtaXg4aGNjOUtZblZDbU9RbnFhLU81Z29yVDZzeG1HcFpjeS12UFJNX1lSaXRRVWIyWUFyWkMyaDJobmNReFhjRzREcTFBTGFsX3RwNDRnUHhydUtWdEcyR0VFeVRXUlg5c0hJZlhydURCVG0zcmd0SkNVbk5qak8tbkJGWnducXNZV1hOUFEtSHRWbmVvOFRXSFM4aG5zbU9SOWJ2Y1RTRGNB0gHSAUFVX3lxTE5jTVU1LW82UDhqRVdjVnNNQ29LZXpEdTM1a2NiRlNUaVBBUnVCZ25hamlJM3RiZW9DNzBMYWNBanJaemVuaEdzUUMyOFljN0t3SU1ac0ZRNnBLWm1LNjAycG8yUFRTZllRWVIwTWV0dTN2TTM3WEt5ZWNNWFlia2VvMFdnNEZtMTlDSWhwX1ZLc3hCTDlvT20zd3ZJUEE2UVJVc1Z3bGpnOENxSWNYcExDX0hiaGxTMnE2dXBSaEJnRE9Od2VQdk1vQmVCUy1PdjlSZw?oc=5</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -4034,17 +4042,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
+          <t>El nuevo idioma que tendrían que aprender estudiantes de colegios públicos desde 2026 - Noticias Caracol</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Noticias Caracol</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4054,22 +4062,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNRENPX0xEVmxGRDFJallZVDY3UmlXZ0Q0bzVWX2kzSFBISXNlMWZ3eWM0Q1R3eE5KdUF3ZWpRcEFRSG5Rbl9wbnZoeTQyckpBX0VuQ0s2aTFoc2lOblVkd1V0b2FGU0tRNnBsUldGLUdoTGJwVFpTZkcyenB5blpDVi11Y3g3Y3JVQ1lUNVpTZTYwZXVmY3ZhR1ozUUNYMDl0bm5PeFRETzZFTlhIamc0LVZXMWhyNnFqNGpSTXBGOGdONDc5UWJRRTZpc19vczJ0LXFV0gHgAUFVX3lxTE40d0Y3d0Y1VDdvd0FnQWpvdGhBTjl2T3Jsc2dkQnlxSF9OQjhiaVM2VkNLckhhSWZpczU2TTlySGx2RHBadTZJT0E3MTdyZU9ZOTQ4cHIzTW5HZ2FXZ182TjJrdm1xeVAwWVVOZmR1SzktLUl0cGl3dEdyZHlUakYtOHFEMVo3NF9PdzdwZXdSR0FiWDJVQm5FcDBhQ3c2T1ZRXzdFeVZDdkJfYms2UFpHM3lKTk15Y0JFWVNGellIekRvUWpPZFFGOTNBQlkxZmhLR2wxV01yOEtWUTh2cmFY?oc=5</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4077,12 +4085,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
+          <t>La SIC impuso medidas a Rappi, Dislicores y Éxito: buscan evitar venta de vapeadores a menores de edad - Infobae</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4102,7 +4110,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4112,7 +4120,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQTDZ6dnN2WnNvMEl4WDlXUjRsY2tRVjUwNDlUekJ3TDl2YWZ1dVQwVjR1bVFYUTQ4d2F1VmRnTG1QQm9GY3NudHZscjVvOXRRaGZHaG53NWVNbkZOWlpvYVR3Ry1ZV3B3TkxmTEVBM19VQXowNEk4V2dwNWJ2YkU5MUNDSDhoejhNeTZ2OWs3bkJoZmktdVdzMHpIMnlLb1AzUWt0OWFiTTAwakNlZGR3ZUhNckstTXB1eGI1ajVvTFZXSjd0Q3kteHJESU50UW5NTGEtR1ptNW1ueHdHTEFKVWpOLWZDRGtibEtidG04TVpLQlYyTlR3NVRPX1drUGh00gGbAkFVX3lxTFBUMk1tdnRwODNzcE02RVVvbWtQd3BjajRfWlQ5aVdScUNHOFNSSlU4cHhZQXJVajJZcEc1aWZBZU9OakE1RXc5cFg0cTJwN3E2RmZBQ21sX3h1YUg0a3d1YjBJdWY4aGl1VU9lTXJKNlphR2FVaU9WVlRuMzJJVGFyX09SNzMyWE5sV0E5THZWd3RWVTF0bVUza0gwWml4U2ExRG1mYmlyMU44RVNCLXZjc1dIcXZESXF2eHRQOWtMLWlQdXlHa05qaFhnMjVQVFQ1elh4MC1VenZKcHV4UzBoRTZ6N0JhN0dPV1FiQjVSSTZ5YmNQV0x0cWpwaVQwMEswTUN5SEw5b2M4VXVUREVnd0IwdTlkaW1fT3M?oc=5</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4120,27 +4128,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>La localidad de Usaquén tiene una Casa de Juventud para beneficiar a más de 100.000 jóvenes</t>
+          <t>Tras el envenenamiento con talio de menores en Bogotá, Zulma Guzmán confesó la relación que tuvo con padre de una de las niñas fallecidas - Infobae</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Política pública</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4155,71 +4163,63 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#74871d874f</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>●Bogotá abre un nuevo espacio para las y los jóvenes de la localidad, ubicado en la calle 155 #7-45, con acto protocolario y participación de autoridades y representantes juveniles. ●Esta casa amplía la cobertura territorial del servicio Casas de...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOYmZ3Tm9XR3FoMXBaa25la2NlYWFPWjFqejhhY0VyWU8yb2VOampHZXIxMlRrVU8wTG9NOTZla1NXeHZsRW9kSWJnaE1QUjFCemJ2bHJWejlMeHlwcHZTOE1Yc2dsY21MUUJ2cGpMX1V0UEVpeDhzRFo4YmwxR2gwaHRVNWJab0N1NnBxaF9HR0VBc2xxUWNSZUhLSXJ6TjRkX1ppT01jQ1YyOXlsSmhWd2lnNXdxQ0xKR19iWF90dC1zY2Jobnk4T0VZRU1yZjJRN1VJT1BNT3l4dW10REVFbWlNd1JPVm5KaFF4NzF5RXlxeU5TUlNpTUFlWdIBlgJBVV95cUxQSUt2Nmk1NTYtZzNZdjYtdzhFV2Ezal9OWEhoY2hjczBUV19UN2UxN3dfYmw5SW5iMEJBY1B1ZUowZlN0a3NpQWROcTR3WjRsRThBV25QU3FLbllrWWxIOUpLamxLNDJUdzU3elVEYzRqbGc1SE5PeDZ1dmNvMmtVZUlCSWNMOTlrcVUzdFlkcThpUmQ0THBTZGEyNkJZUl9UYnFhanVEdlNmaWdNSHNxWTVSVHRLQk1MaElEOWxNUzFZeWczRkdpbHM2bVlZQUdjQ0xkdDJqckNfR2tSckVtQW9hYzlZSTlpS1BwX1pWNXpJa1R2MS1ZSU5rWDRZX1lQVzRud1hoRmk4aXZ3SFRxc2FwdjRpdw?oc=5</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
+          <t>Gobierno condonará créditos del Icetex a más de mil jóvenes en Colombia: quiénes se beneficiarán - Infobae</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZlVSRmszbERPaGNNNjhFRXY3VGVlUjc0eXo5R002RDZTbk15NWlUb1pLeWtWdmtObV9fY2ZxUmQ3cHNacWJoMExhZVZDRjlJM0lYZ2VfUVJOTEJnOXhGeXhtOFdlX3BmdFZTWXNJWHpXSDJsREdSaXJHSmFfY0RCcV8xSFVTLThuS1M4eUwxYTMxdWU2WTY3YUVTaWtLWHJFRUhlM0EtQzFNdDQwNy1wU2NyMDIzSk5rZGI4ZExtcmx1b2R2d01DNzdZT29LanFzXzBaNjluZ0rSAfMBQVVfeXFMT3pmVy1QSHJLaTJmREJmLVNLano0XzdpeW1VemRocGF5eHBVZktPRnNkTnNBUElFMDk1UUQ4MTZRNENCVWpZQVhTRmNrV1dwbDhCQnFvemZKTmZyT2cwdV96a2xOUWZDZEloWEFKcjJ2QkJsX0h3bFZDTkNRNGJOY1U5UGZaN0x6YU1EQlN5ZlFLb0hYQkM1MDdKNWl5TS1OcVNYWHRGXzl5NFp1WnQ2YWJqcWZzZDlDTk5FQ19Sa2lZOXRpOEJ4LV9DUnVOenhkQ3FJUGhkZkExNkNOYlV2Z21iLUQxUmF0eDJ5c3NyekcxTFlF?oc=5</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
+          <t>La localidad de Usaquén tiene una Casa de Juventud para beneficiar a más de 100.000 jóvenes</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Empleo</t>
+          <t>Política pública</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4249,24 +4249,24 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#74871d874f</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
+          <t>●Bogotá abre un nuevo espacio para las y los jóvenes de la localidad, ubicado en la calle 155 #7-45, con acto protocolario y participación de autoridades y representantes juveniles. ●Esta casa amplía la cobertura territorial del servicio Casas de...</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
+          <t>Más de 40 jóvenes de Bogotá fueron reconocidos por su talento, creatividad y liderazgo en la Semana de la Juventud y la Semana Andina 2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4296,24 +4296,24 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c68de3a13a</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
+          <t>• Más de 40 jóvenes y colectivos fueron premiados por su creatividad, liderazgo y compromiso social durante la Semana de la Juventud y la Semana Andina 2025. • La Subdirección para la Juventud de la Secretaría Distrital de Integración Social abrió...</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
+          <t>Jóvenes con Oportunidades abre convocatoria para su ruta de formación en cursos cortos</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Empleo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4343,24 +4343,24 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#28dd65106b</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
+          <t>•La Subdirección para la Juventud anunció la apertura de nuevos cupos en la ruta de formación en cursos cortos, dirigida a jóvenes entre 18 y 28 años que vivan en Bogotá y cuenten con Sisbén IV (A1 a C09). • La ruta combina proyecto de vida, cursos...</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
+          <t>La Academia Ñam busca jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4390,24 +4390,24 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8622ae2557</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años de las localidades de La Candelaria y Santa Fe interesados en formarse en servicio en gastronomía. • Esta formación...</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Últimos días para inscribirse y obtener una beca en formación técnico laboral de la Agencia Atenea</t>
+          <t>La Escuela Distrital de Emprendimiento ya está en marcha en Kennedy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4437,24 +4437,24 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#d7dc735e17</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#09b7d9045f</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>•Son 1.500 cupos y se cubre el 100 % de la matrícula, apoyo económico por semestre y acompañamiento en la ruta educativa y laboral. • La convocatoria se cierra el domingo 21 de septiembre a las 11 y 59 de la noche</t>
+          <t>• 50 jóvenes emprendedores fortalecerán sus proyectos de negocios de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento, que llega a su quinta edición, nace de la alianza del Distrito con la ANDI y la Fundación...</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
+          <t>La Academia Ñam abre una nueva convocatoria para jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4484,24 +4484,24 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#17e48d890a</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
+          <t>• El Distrito, en alianza con la Fundación Gastronomía Social, lanzan convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio en el sector de la gastronomía. • Esta formación gratuita ofrece capacitación a través de...</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+          <t>Últimos días para inscribirse y obtener una beca en formación técnico laboral de la Agencia Atenea</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4531,24 +4531,24 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#d7dc735e17</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
+          <t>•Son 1.500 cupos y se cubre el 100 % de la matrícula, apoyo económico por semestre y acompañamiento en la ruta educativa y laboral. • La convocatoria se cierra el domingo 21 de septiembre a las 11 y 59 de la noche</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
+          <t>Bogotá ofrece más de 1.500 becas para que jóvenes estudien programas técnicos laborales</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4578,57 +4578,151 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#e22c14d73a</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
+          <t>•Se trata de la convocatoria Formación y Educación para el trabajo que les permitirá a los jóvenes de la ciudad formarse en una ocupación que requiere el mercado laboral. •Losbeneficiarios podrán estudiar mercadeo y ventas, mecánica dental, cocina,...</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Jóvenes de la Casa de la Juventud de Suba aprenden sobre medio ambiente y navegan el río Bogotá</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SDIS - Juventud</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#ba7949b3a9</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>•Los navegantes confirmaron que los malos olores quedaron en el pasado y hoy se aprecian algunas especies de fauna que han comenzado a retornar a lo largo del cauce. • Gracias a la Corporación Autónoma Regional de Cundinamarca (CAR), encargada de...</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Está abierta la convocatoria para la Escuela Distrital de Emprendimiento en Kennedy</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SDIS - Juventud</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>institucional</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#2acaf10b23</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>• Jóvenes emprendedores podrán fortalecer sus proyectos de la mano de expertos y líderes empresariales. • La Escuela Distrital de Emprendimiento nace de la alianza del Distrito con la ANDI y la Fundación ANDI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>El Frailejón abre sus puertas: Usme estrena nueva Casa de la Juventud</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>SDIS - Juventud</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>institucional</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Otra</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Bogotá</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#c7eca5d4bd</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>• Aunque ya existía una Casa de la Juventud en Usme, la sede se traslada y reinaugura para ofrecer mejores condiciones, ampliar servicios y fortalecer la atención a los jóvenes. • La reapertura se desarrolló con el acompañamiento de la Plataforma...</t>
         </is>

--- a/data/noticias.xlsx
+++ b/data/noticias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abren 200 becas para jóvenes del Pacífico que lideren proyectos en sus territorios</t>
+          <t>Los therian: un fenómeno que alarma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,29 +513,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abren-200-becas-para-jovenes-del-pacifico-que-lideren-proyectos-en-sus-territorios/</t>
+          <t>https://www.las2orillas.co/los-therian-un-fenomeno-que-alarma/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>El programa DALE lidera Pacífico ofrecerá formación, mentorías y acompañamiento a jóvenes que impulsen iniciativas comunitarias en litoral.</t>
+          <t>Cuando la identificación con un animal es persistente. se recomienda orientación psicológica para ayudar al joven en el desarrollo de una identidad saludableEl artículoLos therian: un fenómeno que alarmafue publicado originalmente enLas2orillas.co:...</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Figura de Independiente Medellín dedicó su gol en la clasificación del equipo en la Copa Libertadores a una persona que “está en tratamiento”</t>
+          <t>Con $86 mil millones de regalías, Bolívar construirá universidad en Montes de María y otros dos proyectos educativos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -545,12 +545,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -560,29 +560,29 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/deportes/2026/03/13/figura-de-independiente-medellin-dedico-su-gol-en-la-clasificacion-del-equipo-en-la-copa-libertadores-a-una-persona-que-esta-en-tratamiento/</t>
+          <t>https://www.las2orillas.co/con-86-mil-millones-de-regalias-bolivar-construira-universidad-en-montes-de-maria-y-otros-dos-proyectos-educativos/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>El equipo dirigido por Alejandro Restrepo venció 2-1 a Juventud de Uruguay ante 12.000 hinchas y clasificó a la fase de grupos, donde acompañará a Deportes Tolima, Junior y Santa Fe en el torneo continental</t>
+          <t>Los proyectos impulsados por Yamil Arana buscan, entre otras cosas, abrir más de 4 mil cupos para jóvenes de una región que durante años fue escenario de conflictoEl artículoCon $86 mil millones de regalías, Bolívar construirá universidad en Montes...</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
+          <t>Pese a todo, la IA podría potenciar el criterio político de la juventud</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>La Silla Vacía</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -607,25 +607,29 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>https://www.lasillavacia.com/red-de-expertos/red-de-democracia-y-tecnologia/pese-a-todo-la-ia-podria-potenciar-el-criterio-politico-de-la-juventud/</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aunque la IA genera inquietudes en el ámbito educativo, también puede formar la conciencia política e histórica entre la juventud.The postPese a todo, la IA podría potenciar el criterio político de la juventudappeared first onLa Silla Vacía.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Solo 1 de cada 4 estudiantes colombianos logra el nivel avanzado en educación media: ¿por qué importa?</t>
+          <t>Murió el influencer colombiano Alejo Little a los 33 años: estos fueron los quebrantos de salud que presentó en los últimos meses</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -635,7 +639,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -650,20 +654,24 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/desigualdad-en-la-educacion-media-en-colombia-solo-el-13-de-estudiantes-logra-competencias-clave-PP5091242A</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>https://www.infobae.com/colombia/2026/03/14/murio-el-influencer-colombiano-alejo-little-a-los-33-anos-estos-fueron-los-quebrantos-de-salud-que-presento-en-los-ultimos-meses/</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>El creador de contenido compartió experiencias sobre el acoso escolar y promovió la aceptación personal a través de sus redes sociales y charlas en instituciones educativas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gobierno geolocaliza casi 1.000 colegios en La Guajira que eran “invisibles”: no figuraban en el mapa</t>
+          <t>Figura de Independiente Medellín dedicó su gol en la clasificación del equipo en la Copa Libertadores a una persona que “está en tratamiento”</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -678,12 +686,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -693,34 +701,34 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/12/gobierno-geolocaliza-casi-1000-colegios-en-la-guajira-que-eran-invisibles-no-figuraban-en-el-mapa/</t>
+          <t>https://www.infobae.com/colombia/deportes/2026/03/13/figura-de-independiente-medellin-dedico-su-gol-en-la-clasificacion-del-equipo-en-la-copa-libertadores-a-una-persona-que-esta-en-tratamiento/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Los pocos planteles educativos con geolocalización en plataformas de ubicación están en las cabeceras municipales del departamento</t>
+          <t>El equipo dirigido por Alejandro Restrepo venció 2-1 a Juventud de Uruguay ante 12.000 hinchas y clasificó a la fase de grupos, donde acompañará a Deportes Tolima, Junior y Santa Fe en el torneo continental</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>La travesía del gigante telescopio que Rodolfo Llinás le regaló al histórico Observatorio de la Universidad Nacional</t>
+          <t>Abren 200 becas para jóvenes del Pacífico que lideren proyectos en sus territorios</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -740,12 +748,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-travesia-del-gigante-telescopio-que-rodolfo-llinas-le-regalo-al-historico-observatorio-de-la-universidad-nacional/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abren-200-becas-para-jovenes-del-pacifico-que-lideren-proyectos-en-sus-territorios/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>En medio del paro de la Nacional, el cientifico donó su telescopio personal, el más grande instalado en Colombia, ahora al servicio de estudiantes e investigadoresEl artículoLa travesía del gigante telescopio que Rodolfo Llinás le regaló al...</t>
+          <t>El programa DALE lidera Pacífico ofrecerá formación, mentorías y acompañamiento a jóvenes que impulsen iniciativas comunitarias en litoral.</t>
         </is>
       </c>
     </row>
@@ -795,17 +803,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs. Juventud: hora y dónde ver el partido decisivo del Poderoso en la Copa Libertadores</t>
+          <t>Nuevo giro en el caso de Tatiana Hernández, joven desaparecida en Cartagena: la buscan en el mar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -815,12 +823,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -830,29 +838,25 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/deportes/2026/03/11/independiente-medellin-vs-juventud-hora-y-donde-ver-el-partido-decisivo-del-poderoso-en-la-copa-libertadores/</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>El rojo paisa quiere estar entre los 32 mejores equipos de América para la edición del 2026</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/caso-tatiana-hernandez-da-giro-autoridades-intensifican-busqueda-mar-PP5091130</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>La crisis de natalidad acaba el negocio de los colegios privados, pero abre una oportunidad para mejorar la educación</t>
+          <t>Solo 1 de cada 4 estudiantes colombianos logra el nivel avanzado en educación media: ¿por qué importa?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las2orillas</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -877,24 +881,20 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/la-crisis-de-natalidad-acaba-el-negocio-de-los-colegios-privados-pero-abre-una-oportunidad-para-mejorar-la-educacion/</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Colombia tiene 33 alumnos por docente, el triple que los países líderes. La crisis de natalidad permite reducir esta brecha y apostar por la equidad socialEl artículoLa crisis de natalidad acaba el negocio de los colegios privados, pero abre una...</t>
-        </is>
-      </c>
+          <t>https://www.pulzo.com/nacion/desigualdad-en-la-educacion-media-en-colombia-solo-el-13-de-estudiantes-logra-competencias-clave-PP5091242A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
+          <t>La travesía del gigante telescopio que Rodolfo Llinás le regaló al histórico Observatorio de la Universidad Nacional</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -924,59 +924,59 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
+          <t>https://www.las2orillas.co/la-travesia-del-gigante-telescopio-que-rodolfo-llinas-le-regalo-al-historico-observatorio-de-la-universidad-nacional/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
+          <t>En medio del paro de la Nacional, el cientifico donó su telescopio personal, el más grande instalado en Colombia, ahora al servicio de estudiantes e investigadoresEl artículoLa travesía del gigante telescopio que Rodolfo Llinás le regaló al...</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prosperidad Social inicia entrega de transferencia monetaria de Jóvenes en Paz</t>
+          <t>Gobierno geolocaliza casi 1.000 colegios en La Guajira que eran “invisibles”: no figuraban en el mapa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-entrega-de-transferencia-monetaria-de-jovenes-en-paz/</t>
+          <t>https://www.infobae.com/colombia/2026/03/12/gobierno-geolocaliza-casi-1000-colegios-en-la-guajira-que-eran-invisibles-no-figuraban-en-el-mapa/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Esta transferencia corresponde al ciclo 1 de 2026. Más de 12.000 jóvenes en el país recibirán los recursos. Bogotá D. C., 24 de febrero de 2026. Prosperidad Social realizará este 27 de febrero la transferencia monetaria condicionada para los...</t>
+          <t>Los pocos planteles educativos con geolocalización en plataformas de ubicación están en las cabeceras municipales del departamento</t>
         </is>
       </c>
     </row>
@@ -1035,42 +1035,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
+          <t>La crisis de natalidad acaba el negocio de los colegios privados, pero abre una oportunidad para mejorar la educación</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
+          <t>https://www.las2orillas.co/la-crisis-de-natalidad-acaba-el-negocio-de-los-colegios-privados-pero-abre-una-oportunidad-para-mejorar-la-educacion/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
+          <t>Colombia tiene 33 alumnos por docente, el triple que los países líderes. La crisis de natalidad permite reducir esta brecha y apostar por la equidad socialEl artículoLa crisis de natalidad acaba el negocio de los colegios privados, pero abre una...</t>
         </is>
       </c>
     </row>
@@ -1082,22 +1082,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Por paro de docentes en Bogotá: Secretaría de Educación advirtió que los profesores tendrían que trabajar en sábado</t>
+          <t>Prosperidad Social responde a inquietudes sobre Renta Joven</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/paro-de-docentes-en-bogota-secretaria-de-educacion-confirmo-reposicion-de-clases-si-el-profesor-se-ausenta/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-responde-a-inquietudes-sobre-renta-joven/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Una estrategia coordinada busca que los centros escolares registren y reporten detalladamente las asistencias, horarios y participación de docentes y estudiantes, a fin de garantizar el desarrollo normal de contenidos curriculares</t>
+          <t>Bogotá D. C, 4 de marzo de 2026. Prosperidad Social se permite aclarar a la ciudadanía y, especialmente, a los participantes de Renta Joven algunas dudas e inquietudes que han expresado los beneficiarios en las redes sociales. Prosperidad Social...</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
+          <t>Prosperidad Social inicia entrega de transferencia monetaria de Jóvenes en Paz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/prosperidad-social-inicia-entrega-de-transferencia-monetaria-de-jovenes-en-paz/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
+          <t>Esta transferencia corresponde al ciclo 1 de 2026. Más de 12.000 jóvenes en el país recibirán los recursos. Bogotá D. C., 24 de febrero de 2026. Prosperidad Social realizará este 27 de febrero la transferencia monetaria condicionada para los...</t>
         </is>
       </c>
     </row>
@@ -1176,106 +1176,106 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
+          <t>Joven rompió el silencio y reveló desgarradores detalles de los feminicidios más brutales del Valle del Cauca</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prosperidad Social</t>
+          <t>Las2orillas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
+          <t>https://www.las2orillas.co/joven-rompio-el-silencio-y-revelo-desgarradores-detalles-de-los-feminicidios-mas-brutales-del-valle-del-cauca/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
+          <t>Mientras la Fiscalía la señala de disparar contra las víctimas, Angy Pérez asegura que fue obligada a desmembrar los cuerpos bajo la amenaza de perder a su bebéEl artículoJoven rompió el silencio y reveló desgarradores detalles de los feminicidios...</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
+          <t>Independiente Medellín vs. Juventud: hora y dónde ver el partido decisivo del Poderoso en la Copa Libertadores</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Medellín</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
+          <t>https://www.infobae.com/colombia/deportes/2026/03/11/independiente-medellin-vs-juventud-hora-y-donde-ver-el-partido-decisivo-del-poderoso-en-la-copa-libertadores/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
+          <t>El rojo paisa quiere estar entre los 32 mejores equipos de América para la edición del 2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
+          <t>Maratón por las generaciones atendió a más de 38.000 jóvenes y personas mayores beneficiarias de Prosperidad Social</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Prosperidad Social</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1300,86 +1300,86 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/maraton-por-las-generaciones-atendio-a-mas-de-38-000-jovenes-y-personas-mayores-beneficiarias-de-prosperidad-social/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
+          <t>Durante 38 horas continuas, se resolvieron inquietudes y dudas a beneficiarias y beneficiarios de los programas Renta Joven y Colombia Mayor. Nueve de cada 10 personas afirmaron haber recibido información clara y efectiva para resolver sus...</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
+          <t>Así fue la despedida de Iván Zuleta a su sobrina Daniela: la joven fue encontrada sin signos vitales en su habitación</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Valledupar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/asi-fue-la-despedida-de-ivan-zuleta-a-su-sobrina-daniela-que-habria-sido-encontrada-sin-signos-vitales-en-su-habitacion/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
+          <t>La partida de la joven Zuleta Gnecco, hija de Fabián Zuleta y nieta de Fabio Zuleta, ha conmovido al mundo del vallenato, reuniendo a familiares y músicos icónicos para despedirla en Valledupar con emotivas muestras de cariño</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
+          <t>Por paro de docentes en Bogotá: Secretaría de Educación advirtió que los profesores tendrían que trabajar en sábado</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultura y deporte</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1394,34 +1394,34 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
+          <t>https://www.infobae.com/colombia/2026/03/11/paro-de-docentes-en-bogota-secretaria-de-educacion-confirmo-reposicion-de-clases-si-el-profesor-se-ausenta/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
+          <t>Una estrategia coordinada busca que los centros escolares registren y reporten detalladamente las asistencias, horarios y participación de docentes y estudiantes, a fin de garantizar el desarrollo normal de contenidos curriculares</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
+          <t>Jóvenes en San Cristóbal inician su formación en servicio para el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1441,213 +1441,217 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#79ade27adc</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
+          <t>•24 chicos y chicas iniciaron su camino en la Academia Ñam, en donde se formarán en servicio a la mesa para mejorar sus oportunidades de empleabilidad en el sector de la gastronomía. •La inducción, que tuvo lugar en el Centro de Desarrollo...</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
+          <t>Bogotá presenta estudio que analiza los factores asociados a la vinculación de adolescentes a conductas punibles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#fb504c6e8d</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
+          <t>• La vinculación de adolescentes a conductas punibles no responde a una sola causa, sino a la convergencia de factores estructurales, familiares, territoriales y personales que requieren respuestas integrales y no únicamente punitivas. • El consumo...</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
+          <t>La Academia Ñam llega a San Cristóbal con oportunidades para los jóvenes interesados en el sector de la gastronomía</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/cultura</t>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#1e64cd90aa</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
+          <t>•El Distrito, en alianza con la Fundación Gastronomía Social, lanzan una nueva convocatoria dirigida a jóvenes de 18 a 30 años interesados en formarse en servicio para el sector de la gastronomía. •Esta formación gratuita ofrece capacitación a...</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
+          <t>El deporte abrió la puerta a nuevas oportunidades y conexión para los jóvenes de Bogotá</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Cultura y deporte</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#8b36ede0c2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>• En la localidad de Kennedy se realizó una jornada deportiva con Futsala Colombia, que acercó a los jóvenes la oferta integral de servicios sociales, digitales y educativos en territorio. • En Jóvenes con Oportunidades, más de 18.000 jóvenes han...</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
+          <t>La primera guardia afro urbana liderada por mujeres surge en Cali</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+          <t>https://www.elespectador.com/colombia/cali/la-primera-guardia-afro-urbana-liderada-por-mujeres-surge-en-cali/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+          <t>En Llano Verde, mujeres desplazadas crearon la primera guardia afro urbana del país para prevenir violencia y proteger a jóvenes.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
+          <t>Persecución del ICE en Georgia termina con la muerte de una profesora: 'Dedicó su carrera a que cada niño se sintiera valorado'</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1657,7 +1661,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1672,67 +1676,71 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/cultura</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Una de sus compañeras afirmó que Linda Davis hacía sentir importantes a todos a su alrededor, desde estudiantes hasta personal administrativo.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
+          <t>Abre 320 becas a jóvenes con proyectos en sus comunidades o entornos, ¿cómo participar?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
+          <t>https://www.elespectador.com/colombia/mas-regiones/abre-320-becas-a-jovenes-con-proyectos-en-sus-comunidades-o-entornos-como-participar/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
+          <t>Abren becas para jóvenes en Medellín, Santa Marta, Cartagena y Bogotá. Tendrán formación, mentorías y acceso a redes de liderazgo.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
+          <t>Gustavo Petro aseguró que ha salvado a “miles de niños” en Colombia y en redes le recordaron la muerte de Kevin Acosta - Infobae</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1747,12 +1755,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1762,57 +1770,57 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNRE1yOXc4NEJZaU8wdFVIY0tmUFdnMTNKOTE3X2ZubVNNOWxfZzdjSWNNbXQxNDRlbE1UenN5OFI0VE5WYzdZTXNIVXkzVFdpT3Z1cnRQRU5Qc0poSno1R29fU0tPTV9PRFJPZWVYcTdqVDY3Nl94R0ZITUNQSllRZUNzTl9LNXpURlBweEdiS0pPaHdHajhkNkJtQUFHbVJrRTViek9NWWtuQThXVTktV3BZWmR3VTJMREdlakJJMzd2YlRFdFB3X0h2MmQ2QnFTMnNiZTZ0dFFUTFVzemFlVUNyMjRmd0pxNzVVN2NfTVF1eHhsMVBQUXAzMF9yUXF3ZlZQNzRiTFJJZ9IBpAJBVV95cUxPRFZUS283NTMwczZpenJCYnotZXBpd1BPTWJ0NWxsTGVVNGdzZkcxR2R1TjFpaTR3ZlNaZ2dHNklweDZtbE9mbERfNVpUMm1yTFNEMER1UF90RnlZb21fZ21FX3dGRngyaE1RaFpjWmVuSWtfU1EtYUtWWjhKUzB5VEhWTEdhdzRYTGIxNGJROGhBUC1JdTFQUWVPanJkWWJTQVBzMmVBVjBwZkhsRTZZcTFlM3VyTm1aaWRQa0JNdy1kUGRqV1ZOendLbW1IRnZVRWMxUVlPWU04VWxuUDFhUHBvVWZtb2ZPS1B4UlhuVWJHQko3V3VXM0JKZFhYOEJJMWlwQllzYkRjdmxQbzB1ZHZDUlZBTVpDN0JLVC1qYmVPTE9X?oc=5</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
+          <t>Bogotá fortalece el proceso de preinscripción de Jóvenes con Oportunidades 2026 y habilita nuevo enlace</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Espectador</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>diario pago</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Protección</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#6c31bba0c9</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>•El Distrito habilitó un nuevo enlace mejorado para garantizar una experiencia más ágil, estable y segura en la convocatoria 2026 de Jóvenes con Oportunidades. •Las y los jóvenes entre 14 y 28 años que vivan en Bogotá y estén clasificados en Sisbén...</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1822,12 +1830,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
+          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1837,22 +1845,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
+          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -1865,40 +1873,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cómo están perros que sobrevivieron a presunto envenenamiento en colegio de Bogotá; niños los cuidaban</t>
+          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>El Espectador</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>diario pago</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Protección</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.pulzo.com/nacion/bogota/como-estan-perros-sobrevivientes-presunto-envenenamiento-colegio-bogota-PP5043509</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1908,7 +1920,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aumenta el número de desaparecidos en Córdoba, dos jóvenes arrastrados por un arroyo</t>
+          <t>Los niños tienen un precio en la guerra: así crece el drama del reclutamiento infantil - El Espectador</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,71 +1950,67 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.elespectador.com/colombia/mas-regiones/dos-campesinos-en-cordoba-desaparecen-tras-intentar-cruzar-un-arroyo/</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Dos jóvenes campesinos permanecen desaparecidos en Córdoba, luego de que una corriente los arrastrara en cuanto intentaban cruzar un arroyo</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPV1dwRWQwYkh3X0U2a29wSGF2emFEU2ZiRzgyREhoUFJPUHdjTVc2dl9NQU5rYkhaWDl5c0k3SGpsQy1nNC0xdkZtRGxIZ25iMWdkWHFRbkdjMnN5MWhZM2lqZVN1eVVCc1IyelBlc001bDVYeC1MRENOZXRuSUtUVWdZX3BRT1JENkJjaEdyLWdPcUE2ckFxRHl6aW9yclRRUEs1a3dTVkJMb2dOeWdxY2ZaRkV6dHpHMzRaeVZ5bkMtYU1fWXEyaUtzeVE1RzBSSGVpVXVvZTRpOWlmZGcybXl0a1Z4RXZVYi1JaTFHUUYtelZ4WDRjTjlETdIBjwJBVV95cUxObmdzakVTVkJwZUpvRkREbllOQ3YzZXVSN1BTTzNhbjJvVnlCYmdkbi1qV2lPQm1VMkZ2TG9YVlhvbkU5dHdUNXM1dnpLbzJ2T1dsZDRPSGNfbGZvUTZTNjZVZjQ3WnJiM0V4aVRqNm9Sb3UxUnNkZDNKcDZtX1ZxSTFpRm5uSjhicElWaDFZNUZoRzBfTldEZktXcGpDamNFN1dLbFBjenpSUl85YVNEajNYVGJHaDRxTUtrRHZnY0RJRENrNjZUMTZzM095Skt0THAxaHdQa2hORjl3X095b0l3MEZTR1F0M2RFR3JRajBnQmF3STBaZ2NzWlotQTB3TjgzWjRUV0prb2VtYkV3?oc=5</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
+          <t>La Defensoría alerta sobre retrocesos en el sistema educativo por recortes fiscales en Costa Rica</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
+          <t>https://www.infobae.com/costa-rica/2026/02/12/la-defensoria-alerta-sobre-retrocesos-en-el-sistema-educativo-por-recortes-fiscales-en-costa-rica/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
+          <t>La institución destaca que los menores recursos afectan gravemente a quienes estudian en comunidades rurales o con discapacidad, evidenciando riesgos persistentes para la equidad, la calidad y la inclusión escolar</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas - Infobae</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2017,22 +2025,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxPYUdxTE4wbVhKbEgzN1NYZm0xcmNxQjNJbllOYmhWTWY0UGJJS3VRMnhRZW1tblhtNEVlQjQ0NHIxSWdLejJrbHIyV2NqSWQ2MU1HS2RCYkJlRDM1cms0QW1wb2ZTX3VmdFNsc3JobDFGcGVRdGxTU1o1dEZOZnFtTUVURmJLR1p1WFJqVnlaRUNvdVI2VWdsb3phbjQwd2ZqeUtWeGpnak13cGhEMHgzUTNrZi1ORWZLdGxuT3ptc00xdjI1MWJVY3RnV21pMWktT0djZnhtd1pLX3VhRDUyZjZGZXd1NkNWS1F4WHZTMkt6QzNWV1VkVDVhV1Z4b0FjQjJXamdiT1lFUkV1ZDhNMVBB0gGsAkFVX3lxTFBJbVlTbjYxN0p5SmttZkFLVHByV0c5NmdkR0FUemxMWk5mcUtuaUV6SWc2RlVxa1FtQ2kzZXpMZHRvYU4tNmhLT2pCaEhGM2xKcG9icFRTUnZUVHZtTnUxamRHbXQyZWdaYll0Y3FTYXdnUWNMUXZIS3hwR2pYUW9vdnUwVm15ZExiRWNuR2RabjVLOG5tcjA0YTB1Tl9vRlc4WjBlSENPbXpvV1BmUGt1ckRuR0tXSHFoWWJmOVR0a2VFUDFWVkhRZ2ZiSzJTYjBvZVh3RjgxTS0tdGRlaW0zaXlBb05UWUlEY0MzdjE3M1BHbjRpdUFfN3VqWlhtTGNlaVRKdjVYSEtlX3BUUE0wSFlCd2JpaVdzNnMwQWdqRDNIdHVwS28tUDl1VA?oc=5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2040,12 +2048,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
+          <t>Adam Mosseri, director de Instagram, desmiente la existencia de “la adicción clínica” a las redes sociales</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2060,35 +2068,39 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>https://www.infobae.com/tecno/2026/02/12/adam-mosseri-director-de-instagram-desmiente-la-existencia-de-la-adiccion-clinica-a-las-redes-sociales/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>El directivo admitió que ciertas funciones de la app como los filtros digitales generan riesgos sobre la imagen corporal y el bienestar de los usuarios jóvenes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
+          <t>La falta de sueño deteriora la salud cerebral y emocional desde la infancia: 60% de los niños y adolescentes no duerme las horas recomendadas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2103,22 +2115,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
+          <t>https://www.infobae.com/colombia/2026/02/12/la-falta-de-sueno-deteriora-la-salud-cerebral-y-emocional-desde-la-infancia-60-de-los-ninos-y-adolescentes-no-duerme-las-horas-recomendadas/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2126,55 +2138,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
+          <t>Bogotá abre convocatoria 2026 del programa Jóvenes con Oportunidades con más de 12.000 nuevos cupos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#9a0f0687f3</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>• El Distrito abre estaconvocatoria de Jóvenes con Oportunidades con más de 8.000 nuevos cupos, en su primera etapa, para jóvenes entre 14 y 28 años de Bogotá, fortaleciendo su acceso a rutas de formación, acompañamiento psicosocial y transferencias...</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2189,22 +2205,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdtIBqwJBVV95cUxPZnpNT2FPSmdUeFl0UmFScGh6MzVlYm9tVWhQekJjVTdRcHM2ZDlEbWFhVUJBX3dudVF2V01OaDdSRWN6c1FXV2thM0VJOHppRWhaWEVpbTVPOTVTd3RKcmJLT1NHa2MwVlR5SzE2TzlHM0RLS3k2VzFKRDdtaTd2M3RCNENTeXByY1BBTjR1SFE3STJQS3JBWURBRER1cTBKQmx2MVR6Sk5xYlpwbTdpNGRyWVBYdmkxTU9JaWNtRlZVM2JzTGtMQUhxaHFnUmVPQlNPbkNYWGlBX2ttc0Y4cjVzR0dVaFBER3lSMWxRZGVGVTRhTFZ6RE82ZzFKeWJnQ0U0bWlINmlXRE9KdUJvbzdpSEg1NURXMzZKeVNHWTd4b0puVldnbFlscw?oc=5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2212,27 +2228,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
+          <t>Menores de edad mataron de 17 puñaladas a un hombre que iba de polizón en un camión de carga en la vía Bogotá-Villavicencio: quedó en video - Infobae</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SDIS - Juventud</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>gratuito</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2247,29 +2263,25 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNYWQxNTA1UWhDOUtWS2dSWXNNQ19idDVRNXV4aktnZzFERmdBaFg0c2lrT2plR0tXcDN1dlFhd0J0Q1BUVmJEVU1YYTR3N0NtQUx2LTQ3amhNR2pNc0tvcjR6X1FfbkIwczFROFJTaFotclVpRGxId2h1eWtqbHMzSkNXc0JCeU1DWjkxOG5qekx4YjZGRlVVckdyX1gyT0luR2Nkd3ZQUTNFM1d1LUlvMzNSSGxiQUZ5V2pqT2E4WXhZWWRpY2JheDhpaWhwOTQwLThDWFlXU1p0N0lZVk5nSHdVZU8zWVlKNE9GTVJKaUxYTkxDMUt1MTF0NzN5MVUxXzBNUjZtZVJsWm9zMkNNdg?oc=5</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
+          <t>Crisis en los colegios privados en Colombia: el Marymount y el Gimnasio Campestre de Bogotá anunciaron trascendental decisión - Infobae</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pulzo</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2284,17 +2296,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNT3E4SHRFSW0tVUVna2NoQzlDQmFUSmxweXVUVzE5ZXA3Um5KdzV5MVFfcl90aExyLUJfUzJxY1ozd1RfdndQNjNmX3d2b2laN1FyLXZiNWtBbEw1OEVZMUNLZDFCZnBjOWlSQkJNUGRMUUFsdTdBdGRGSUtya09tTHBQUEdTcVl6d3J2WFhGUkNPUjhSX2RlRDFwLTV0ZE1EdThDaEVsMzF5UUxQZzd0T1diYm9jR3RNNFppLXlNZlNVMVdaU3VPZlBYbllqckRsV09GNURkXzJ2TFMtejBpeFFjc2s4dmlKRXBPR1hUT1lveTZLV2Y5UVVDbVlhZ9IBmAJBVV95cUxOenZORjNhQTY4T18xRXVmbGpyMjd2cE1MaUVjVmp4c3hEZGtVSmJMUDZlSDZTaEdoaU9IYmMyYkVFRVU1bUdvUEVmckZmTlJiLVRqR2FOVFdSakNpa2FTemdReUxlZ0xXOExEdUliVFNHYkxzTl92bEZKOWhxVDJKNVhpNTZiN3NfTHBoZWlpRGJWLWJia25aRG9kQU5ucHZuMUZlZld5c01Qc2RXX200NEUycUhxU2M0bmVWYmpONWJlREN5eDFZNG5seE5NSTMtRVpoTTNYcm9KcVY5V0xwMDFtRzFnUm5TZ28ta1huSlpIbHNRLWpqZE9LUXk4bWt4OVpUS1paaEkwRDlycUxnbXotQ1pyeFYy?oc=5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2302,12 +2314,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
+          <t>Ropa interior menstrual: en qué consiste esta prenda que colegio en Cundinamarca incorporó al uniforme de las adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2327,7 +2339,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2337,7 +2349,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPUnIyNTdTak1qbjFfN3YxZ0V4SHJ3ajZ1LUZBSlVTd2R6djlJNVgySzJpU0VDWllTUDhHZHJVTXFSZE1tYVJ2dnZiU0diZDFjVjNxY1c4cUFfalBFUFJ4ZGZ6WHB5bUcwb2ZyQVo3VmxJaGIzd2RDdTJfWVhCOXhVUGJqNzVOVmU0LXdsNTdYMllTYlNyQ2tzVnJaU09NSFhoTXRHX0tsZ2FvemliREhOanAtWWp2N2hBdlI5NXdtdjJEZVdpd2U5SXZHX1dNOUt6QmV0NXRjckt2d3lQbWNHa2ZSNzBoZ2pHN1BiS2tGaUhfX2pya0pyVS0zSdIBlgJBVV95cUxQQUJFQ0w5TUgyZ2Z5QjZ0TWJ4dERKMjB2OWpzSVdMS3BwaG5NM094alJ2UzFFTHFnMEc5RnA1LVptNFVQSnhmRS1XSksxRXZNTlBZczRMdVpoZmxENGhmQTI5NnRKX2FsemlSWVVBUjBWNHFXeGdyUEMyODUwbkRpVm5xYWwyQTNxUkFrUGVidU5WM0g0ZmgzMWJ4SDl4U3pERE9fdGRqNFJjWGRBSzd3bjRrQnlFT19xNlRqeXNObU5mMW90TXR4dm1wdHJaUjU0eERCT2diRFd5eXdfTDRDa2JVeFEwQ1JmeEFESnl1ZU1wOHFMbVUzRkRPOVkzaE00aDlZMTZTVHRncEkwSElwZ1Q1Wk52QQ?oc=5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2345,17 +2357,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
+          <t>Jóvenes narraron el calvario sufrido cuando fueron víctimas de presunto abuso en la Universidad de Cartagena: “Causó un gran sangrado”</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Diario ADN</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2365,12 +2377,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2380,72 +2392,72 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.diarioadn.co/seccion/inicio</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
-        </is>
-      </c>
+          <t>https://www.infobae.com/colombia/2026/02/02/jovenes-narraron-el-calvario-sufrido-cuando-fueron-victimas-de-presunto-abuso-en-la-universidad-de-cartagena-causo-un-gran-sangrado/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
+          <t>Bogotá abre nueva convocatoria de Academia Ñam para fortalecer la empleabilidad juvenil en el sector gastronómico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>SDIS - Juventud</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>gratuito</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>https://www.integracionsocial.gov.co/index.php/noticias/94-noticias-juventud#85a520b8bc</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>• La Secretaría Distrital de Integración Social, en alianza con la Fundación Gastronomía Social, abre una nueva convocatoria de Academia Ñam, un programa gratuito de formación y práctica laboral en servicio gastronómico dirigido a jóvenes de 18 a 30...</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frustraron robo en un restaurante en Bosa, Bogotá: un hombre de 23 años y dos menores de edad fueron capturados</t>
+          <t>Universidades en que más se matriculan estudiantes en Colombia: U. San José le gana a los Andes - Pulzo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Pulzo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2455,22 +2467,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/27/frustraron-robo-en-un-restaurante-en-bosa-bogota-un-hombre-de-23-anos-y-dos-menores-de-edad-fueron-capturados/</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOWDZMaWZRYlpZb2pqZDdYaUJtdXlfU1VKTHJPRWg0ZmVlZnV5dC1KRTM1YVVaamZVVzV6djZXU1d2MGp2bVZXcW5vSllmcnVGQ3o4aFlYOGhMbzNMY1dVOC01Q3p4VkRFbm5iSWpYZjI5a3JhRnZEa1AtRnBNQU9BeUE2VVc0cTZqYzc3V09XZFBrS2tUMmYyNThyUlJtRHZFUW1B0gGoAUFVX3lxTFA4MDVZYUt4bXV5WTlKX3hVOHZaRmgxQzhtX292OEVSWC1EQ0FONlI3MEd5S0RObDAzWnM3b3c2XzhVaFF6VnJSQVdtTGh0V29OMW9FQkppblNnZHZwbm8tdGItLXBMX2t3ZWFfLWtWTElDRVdVblRIUW0tWHowZE54c0ZrMVY5d2xRWmZFbkx3WkJXT1FBVi1vMEQ0dDVsaDlOMGUyTGU2UQ?oc=5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2478,12 +2490,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Globo de mecha cayó en una cancha llena de niños y desató pánico en el Valle de Aburrá</t>
+          <t>Estas son las universidades de Colombiamás han ganado y mas han perdido estudiantes en los últimos años - Infobae</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2498,12 +2510,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sin identificar</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2513,7 +2525,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/26/globo-de-mecha-cayo-en-una-cancha-llena-de-ninos-y-desato-panico-en-el-valle-de-aburra/</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOT2ZVRVpaR0pGYnpicTBVZEc2a0tRa2txaXRtUGdMb01zZzZFSmp4TXVFbk9WalhsU3g3NURNNkU2N1ROWU9tZFJQZEctVi1vZlVzMm05Q3Q5UFdZVzFhNXAtWmtOV1dRUkYzTHBUdFZJZUt2ZEVpcElENU5lYXR2REdnY1VMTktyZmpFaHIzb1dYVFc0bGRMa1cxT1BQZ2pYOUFCSjlYcnh3d0JyeVJNRm5FRDkydW53dkJIUExzVWdGdHlDX2E0SFJFdWJsUVItekJFVUt1bzhIaGl3TWVKUlRQNV9LUV9YQWlUUHRYQk9hZHB10gGPAkFVX3lxTFBuSEp2R1NQSm1qeS1sUE9ld0dPNEJEZFpLSFYxX0pGRW0tQmZHZVdPMWowZXVvMDg4Slo0bk1JcmVncDF1Q1htTFB0MExXYlVwQnowak1yRjFLT3ZwNDN5NnJ1ZUxicm1RWWdFaWZnVi12Q1Z2X21INWFWSE95ME05bjg3a1ZsaHBkaTAySHVNZ3RQSDFMbEh1T3MwdVNrejNnN1lWd19TNmttWmVHc0FKN05fMnhVTEVEcFhPdU05eFoxN3F2bXh5bmw5Z2czRzN2S21mbmNYZ1BEX1JUOG12NmxneTlRRTlsbHpJa1dLZXlpZzBUR29sZldJa1pBWkRiRzdWcFVHVzNWZTRLT1E?oc=5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2521,17 +2533,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Programa de Movilidad Escolar 2026 en Bogotá: Aún hay plazo para acceder a transporte y subsidios para estudiantes</t>
+          <t>CNSC abre convocatoria con más de 1.100 vacantes en la Dian y salarios de hasta $17 millones</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Diario ADN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2541,40 +2553,44 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>Sin identificar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/colombia/2026/01/25/programa-de-movilidad-escolar-2026-en-bogota-aun-hay-plazo-para-acceder-a-transporte-y-subsidios-para-estudiantes/</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>https://www.diarioadn.co/seccion/inicio</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Las inscripciones estarán abiertas del 28 de enero al 6 de febrero, con oportunidades para jóvenes sin experiencia y personas con discapacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alerta en Tolima: ya son 4 los muertos por fiebre amarilla en 2026, entre ellos un menor de edad</t>
+          <t>Especialistas alertan por nuevas señales poco visibles de ansiedad y depresión en niños y adolescentes - Infobae</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Blu Radio</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2584,7 +2600,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Otra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2599,7 +2615,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.bluradio.com/nacion/alerta-en-tolima-ya-son-4-los-muertos-por-fiebre-amarilla-en-2026-entre-ellos-un-menor-de-edad-rg10</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPcVZ0TmNveF9iVzl2RXFxWjhYdW9Xb3lCQkdmX2I5ZlpDSndwc3Npby02Z0NnZ0lQVXh3QlZWRjVzT1VEdWFyQnJUd0xaeXYxcWpFUWxYWjJXMG85RzNNd1EzcGRkSkEzV2QtLWotbXFTTm9EcHhiSU9WTFhyT0lTd1NkXzl5d3pScmhRTjBrZ2taYVlQR083dWZ1d3piandoUzhpSlRwT2lmSzhXd2JNNllCTU5DZXVGVWZ5OTB0Slo4V1Q0dGpJOVdNM0NPVHRkVlRQakpUbWdhQzNJU1VGR9IB-wFBVV95cUxNYW5KQWtqQ2tUbDVLdmdoWGc1RTY5bmFpcVdCR09CY210eUFENjR2UDc0NWRiWnJWRFNRUGFVUTZnLUlsa2JPX0JzcThNWGNaclBlckRQU0tIVTNLSUFqZWF0SmdLY0R6UWs3SkdUMkl5Zml3eFlHOW1xNXFpbXF2dU1DRDJNeC0wMFF0cGRoU3FfMzlzbzFYRlRKS2tPWjNILUdUYmhudHJBQVJVVjBTZWV2bFlKa3RRUktjQTJLcThxOGVZdVRSeTQxVnFUZFcyWFZGQ09UOTJhOXdyMXJ3SjVkOVR5QTdWSHlNNGdRbUpLcjBIQmNMSDQtZw?oc=5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2607,12 +2623,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Estados Unidos condenó a cadena perpetua a Manuel Poceiro, turista que llegó a Colombia a explotar sexualmente a menores de edad</t>
+          <t>Frustraron robo en un restaurante en Bo